--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="제안서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="자산군" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="상품" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="출처" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="사용법" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제안서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산군" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상품" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -999,7 +999,7 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-19 01:29:21 · 문서 2026-09-19 08:48 (KST)</t>
+          <t>유니버스 2026-09-19 08:55:38 · 문서 2026-09-19 08:55 (KST)</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>origin/kr100-data</t>
+          <t>야후 파이낸스 일봉 (자료 가지 kr100-data)</t>
         </is>
       </c>
       <c r="C5" s="21" t="n">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E5" s="29" t="inlineStr"/>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>origin/us100-data</t>
+          <t>야후 파이낸스 일봉 (자료 가지 us100-data)</t>
         </is>
       </c>
       <c r="C6" s="21" t="n">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E6" s="29" t="inlineStr"/>
@@ -6851,17 +6851,15 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>네이버 금융 일봉 + 야후 차트 일봉(close, 배당 미보정) + ETFCHECK (https://www.etfcheck.co.kr)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>247</v>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E7" s="29" t="inlineStr"/>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -771,11 +771,11 @@
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>IFERROR(INDEX(자산군!$D$6:$D$10,MATCH($A17,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$6:$D$11,MATCH($A17,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
       <c r="E17" s="15">
-        <f>IFERROR(INDEX(자산군!$E$6:$E$10,MATCH($A17,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$E$6:$E$11,MATCH($A17,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
     </row>
@@ -794,11 +794,11 @@
         <v/>
       </c>
       <c r="D18" s="15">
-        <f>IFERROR(INDEX(자산군!$D$6:$D$10,MATCH($A18,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$6:$D$11,MATCH($A18,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
       <c r="E18" s="15">
-        <f>IFERROR(INDEX(자산군!$E$6:$E$10,MATCH($A18,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$E$6:$E$11,MATCH($A18,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
     </row>
@@ -817,11 +817,11 @@
         <v/>
       </c>
       <c r="D19" s="15">
-        <f>IFERROR(INDEX(자산군!$D$6:$D$10,MATCH($A19,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$6:$D$11,MATCH($A19,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
       <c r="E19" s="15">
-        <f>IFERROR(INDEX(자산군!$E$6:$E$10,MATCH($A19,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$E$6:$E$11,MATCH($A19,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
     </row>
@@ -840,11 +840,11 @@
         <v/>
       </c>
       <c r="D20" s="15">
-        <f>IFERROR(INDEX(자산군!$D$6:$D$10,MATCH($A20,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$6:$D$11,MATCH($A20,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
       <c r="E20" s="15">
-        <f>IFERROR(INDEX(자산군!$E$6:$E$10,MATCH($A20,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$E$6:$E$11,MATCH($A20,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
     </row>
@@ -863,11 +863,11 @@
         <v/>
       </c>
       <c r="D21" s="15">
-        <f>IFERROR(INDEX(자산군!$D$6:$D$10,MATCH($A21,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$6:$D$11,MATCH($A21,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
       <c r="E21" s="15">
-        <f>IFERROR(INDEX(자산군!$E$6:$E$10,MATCH($A21,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$E$6:$E$11,MATCH($A21,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
     </row>
@@ -886,11 +886,11 @@
         <v/>
       </c>
       <c r="D22" s="15">
-        <f>IFERROR(INDEX(자산군!$D$6:$D$10,MATCH($A22,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$6:$D$11,MATCH($A22,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
       <c r="E22" s="15">
-        <f>IFERROR(INDEX(자산군!$E$6:$E$10,MATCH($A22,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$E$6:$E$11,MATCH($A22,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
     </row>
@@ -909,11 +909,11 @@
         <v/>
       </c>
       <c r="D23" s="15">
-        <f>IFERROR(INDEX(자산군!$D$6:$D$10,MATCH($A23,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$6:$D$11,MATCH($A23,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
       <c r="E23" s="15">
-        <f>IFERROR(INDEX(자산군!$E$6:$E$10,MATCH($A23,자산군!$A$6:$A$10,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$E$6:$E$11,MATCH($A23,자산군!$A$6:$A$11,0)),"—")</f>
         <v/>
       </c>
     </row>
@@ -999,7 +999,7 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-19 08:55:38 · 문서 2026-09-19 08:55 (KST)</t>
+          <t>유니버스 2026-09-19 10:13:47 · 문서 2026-09-19 10:13 (KST)</t>
         </is>
       </c>
     </row>
@@ -1128,13 +1128,13 @@
         <v>0.02</v>
       </c>
       <c r="G4" s="22" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="H4" s="22" t="n">
         <v>0.08</v>
       </c>
       <c r="I4" s="22" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="J4" s="22" t="n">
         <v>0.84</v>
@@ -1164,13 +1164,13 @@
         <v>0.035</v>
       </c>
       <c r="G5" s="22" t="n">
-        <v>0</v>
+        <v>0.035</v>
       </c>
       <c r="H5" s="22" t="n">
         <v>0.14</v>
       </c>
       <c r="I5" s="22" t="n">
-        <v>0.105</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J5" s="22" t="n">
         <v>0.72</v>
@@ -1200,13 +1200,13 @@
         <v>0.045</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="H6" s="22" t="n">
         <v>0.18</v>
       </c>
       <c r="I6" s="22" t="n">
-        <v>0.135</v>
+        <v>0.09</v>
       </c>
       <c r="J6" s="22" t="n">
         <v>0.64</v>
@@ -1236,13 +1236,13 @@
         <v>0.05</v>
       </c>
       <c r="G7" s="22" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="H7" s="22" t="n">
         <v>0.2</v>
       </c>
       <c r="I7" s="22" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="J7" s="22" t="n">
         <v>0.6</v>
@@ -1272,13 +1272,13 @@
         <v>0.04</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="H8" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="J8" s="22" t="n">
         <v>0.74</v>
@@ -1308,13 +1308,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H9" s="22" t="n">
         <v>0.175</v>
       </c>
       <c r="I9" s="22" t="n">
-        <v>0.175</v>
+        <v>0.105</v>
       </c>
       <c r="J9" s="22" t="n">
         <v>0.545</v>
@@ -1344,13 +1344,13 @@
         <v>0.09</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>0.225</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>0.225</v>
+        <v>0.135</v>
       </c>
       <c r="J10" s="22" t="n">
         <v>0.415</v>
@@ -1380,13 +1380,13 @@
         <v>0.1</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="H11" s="22" t="n">
         <v>0.25</v>
       </c>
       <c r="I11" s="22" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="J11" s="22" t="n">
         <v>0.35</v>
@@ -1416,13 +1416,13 @@
         <v>0.06</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="H12" s="22" t="n">
         <v>0.08</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="J12" s="22" t="n">
         <v>0.66</v>
@@ -1452,13 +1452,13 @@
         <v>0.105</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0</v>
+        <v>0.105</v>
       </c>
       <c r="H13" s="22" t="n">
         <v>0.14</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>0.245</v>
+        <v>0.14</v>
       </c>
       <c r="J13" s="22" t="n">
         <v>0.405</v>
@@ -1488,13 +1488,13 @@
         <v>0.135</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0</v>
+        <v>0.135</v>
       </c>
       <c r="H14" s="22" t="n">
         <v>0.18</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>0.315</v>
+        <v>0.18</v>
       </c>
       <c r="J14" s="22" t="n">
         <v>0.235</v>
@@ -1524,13 +1524,13 @@
         <v>0.15</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="H15" s="22" t="n">
         <v>0.2</v>
       </c>
       <c r="I15" s="22" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="J15" s="22" t="n">
         <v>0.15</v>
@@ -1560,13 +1560,13 @@
         <v>0.06</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="H16" s="22" t="n">
         <v>0.04</v>
       </c>
       <c r="I16" s="22" t="n">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="J16" s="22" t="n">
         <v>0.62</v>
@@ -1596,13 +1596,13 @@
         <v>0.105</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="H17" s="22" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="I17" s="22" t="n">
-        <v>0.245</v>
+        <v>0.105</v>
       </c>
       <c r="J17" s="22" t="n">
         <v>0.335</v>
@@ -1632,13 +1632,13 @@
         <v>0.135</v>
       </c>
       <c r="G18" s="22" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="H18" s="22" t="n">
         <v>0.09</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>0.315</v>
+        <v>0.135</v>
       </c>
       <c r="J18" s="22" t="n">
         <v>0.145</v>
@@ -1668,13 +1668,13 @@
         <v>0.15</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H19" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="I19" s="22" t="n">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="J19" s="22" t="n">
         <v>0.05</v>
@@ -1704,13 +1704,13 @@
         <v>0.06</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="H20" s="22" t="n">
         <v>0.02</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="J20" s="22" t="n">
         <v>0.6</v>
@@ -1740,13 +1740,13 @@
         <v>0.105</v>
       </c>
       <c r="G21" s="22" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="H21" s="22" t="n">
         <v>0.035</v>
       </c>
       <c r="I21" s="22" t="n">
-        <v>0.175</v>
+        <v>0.035</v>
       </c>
       <c r="J21" s="22" t="n">
         <v>0.3</v>
@@ -1776,13 +1776,13 @@
         <v>0.135</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="H22" s="22" t="n">
         <v>0.045</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>0.225</v>
+        <v>0.045</v>
       </c>
       <c r="J22" s="22" t="n">
         <v>0.1</v>
@@ -1812,13 +1812,13 @@
         <v>0.15</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H23" s="22" t="n">
         <v>0.05</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>0.25</v>
+        <v>0.05</v>
       </c>
       <c r="J23" s="22" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1978,53 +1978,75 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>해외주식</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B9" s="21" t="n">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="C9" s="21" t="n">
-        <v>99</v>
+        <v>19</v>
       </c>
       <c r="D9" s="22" t="n">
-        <v>0.1051235812029279</v>
+        <v>0.1680824723535977</v>
       </c>
       <c r="E9" s="22" t="n">
-        <v>0.2914505456297338</v>
+        <v>0.1542903388794394</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>-0.3235610824922673</v>
+        <v>-0.1653518460082045</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" s="21" t="n">
+        <v>99</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>0.1051235812029279</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>0.2914505456297338</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>-0.3235610824922673</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B10" s="21" t="n">
+      <c r="B11" s="21" t="n">
         <v>436</v>
       </c>
-      <c r="C10" s="21" t="n">
+      <c r="C11" s="21" t="n">
         <v>436</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D11" s="22" t="n">
         <v>0.116974</v>
       </c>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>펀드는 기준가 이력이 7 거래일뿐이라 변동성·최대낙폭을 셈하지 않고 원천의 위험등급을 씁니다.</t>
         </is>
@@ -2041,7 +2063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H130"/>
+  <dimension ref="A1:H149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4822,717 +4844,723 @@
     <row r="81">
       <c r="A81" s="14" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>삼성MMF법인 1</t>
+          <t>SPDR S&amp;P 500</t>
         </is>
       </c>
       <c r="C81" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D81" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용</t>
-        </is>
-      </c>
-      <c r="E81" s="26" t="n">
-        <v>11338987563533</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F81" s="22" t="n">
-        <v>0.029549</v>
-      </c>
-      <c r="G81" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1712168714029432</v>
+      </c>
+      <c r="G81" s="22" t="n">
+        <v>0.1526270353674158</v>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
-          <t>0.05~0.09%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="23" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B82" s="23" t="inlineStr">
         <is>
-          <t>우리큰만족법인MMF 1(국공채)</t>
+          <t>Invesco QQQ (나스닥100)</t>
         </is>
       </c>
       <c r="C82" s="23" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D82" s="23" t="inlineStr">
         <is>
-          <t>우리자산운용</t>
-        </is>
-      </c>
-      <c r="E82" s="24" t="n">
-        <v>8622592894029</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F82" s="25" t="n">
-        <v>0.028073</v>
-      </c>
-      <c r="G82" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.2286861820192689</v>
+      </c>
+      <c r="G82" s="25" t="n">
+        <v>0.2038095515075217</v>
       </c>
       <c r="H82" s="23" t="inlineStr">
         <is>
-          <t>0.08~0.10%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="14" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>IBK그랑프리국공채MMF법인투자신탁 1[국공채]</t>
+          <t>Vanguard 미국 전체시장</t>
         </is>
       </c>
       <c r="C83" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D83" s="14" t="inlineStr">
         <is>
-          <t>아이비케이자산운용</t>
-        </is>
-      </c>
-      <c r="E83" s="26" t="n">
-        <v>8496684909652</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F83" s="22" t="n">
-        <v>0.028188</v>
-      </c>
-      <c r="G83" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1680824723535977</v>
+      </c>
+      <c r="G83" s="22" t="n">
+        <v>0.1542903388794394</v>
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
-          <t>0.09~0.17%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="23" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B84" s="23" t="inlineStr">
         <is>
-          <t>KB법인용MMF I-1(운용)</t>
+          <t>iShares 러셀2000 (미국 중소형)</t>
         </is>
       </c>
       <c r="C84" s="23" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D84" s="23" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
-        </is>
-      </c>
-      <c r="E84" s="24" t="n">
-        <v>8440063369994</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E84" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F84" s="25" t="n">
-        <v>0.029889</v>
-      </c>
-      <c r="G84" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.2013375822034587</v>
+      </c>
+      <c r="G84" s="25" t="n">
+        <v>0.2111022751155888</v>
       </c>
       <c r="H84" s="23" t="inlineStr">
         <is>
-          <t>0.06~0.09%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>우리큰만족신종MMF3</t>
+          <t>Vanguard 선진국(미국 제외)</t>
         </is>
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>우리자산운용</t>
-        </is>
-      </c>
-      <c r="E85" s="26" t="n">
-        <v>7422943031742</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F85" s="22" t="n">
-        <v>0.030522</v>
-      </c>
-      <c r="G85" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.2266691413144159</v>
+      </c>
+      <c r="G85" s="22" t="n">
+        <v>0.1579017670450371</v>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
-          <t>0.09~0.11%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="23" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B86" s="23" t="inlineStr">
         <is>
-          <t>신영법인용MMF4-26_운용</t>
+          <t>Vanguard 신흥국</t>
         </is>
       </c>
       <c r="C86" s="23" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D86" s="23" t="inlineStr">
         <is>
-          <t>신영자산운용</t>
-        </is>
-      </c>
-      <c r="E86" s="24" t="n">
-        <v>6618786412255</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F86" s="25" t="n">
-        <v>0.028373</v>
-      </c>
-      <c r="G86" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1316236092777672</v>
+      </c>
+      <c r="G86" s="25" t="n">
+        <v>0.1645421250031637</v>
       </c>
       <c r="H86" s="23" t="inlineStr">
         <is>
-          <t>0.10~0.15%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="14" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>신한BEST신종법인용MMFGS-2(종류)</t>
+          <t>iShares 미국채 1-3년</t>
         </is>
       </c>
       <c r="C87" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="E87" s="26" t="n">
-        <v>5994110526287</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F87" s="22" t="n">
-        <v>0.029896</v>
-      </c>
-      <c r="G87" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.01505337651433369</v>
+      </c>
+      <c r="G87" s="22" t="n">
+        <v>0.01634004407000697</v>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
-          <t>0.07~0.09%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="23" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B88" s="23" t="inlineStr">
         <is>
-          <t>한화골드법인MMF-KM3(국공채)</t>
+          <t>iShares 미국채 7-10년</t>
         </is>
       </c>
       <c r="C88" s="23" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D88" s="23" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="E88" s="24" t="n">
-        <v>4824524208474</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F88" s="25" t="n">
-        <v>0.028207</v>
-      </c>
-      <c r="G88" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-0.02675355856628381</v>
+      </c>
+      <c r="G88" s="25" t="n">
+        <v>0.06344333160950028</v>
       </c>
       <c r="H88" s="23" t="inlineStr">
         <is>
-          <t>0.06~0.10%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>하나클래스원신종MMF(K-5)</t>
+          <t>iShares 미국채 20년+</t>
         </is>
       </c>
       <c r="C89" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>하나자산운용</t>
-        </is>
-      </c>
-      <c r="E89" s="26" t="n">
-        <v>4606467618325</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E89" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F89" s="22" t="n">
-        <v>0.028155</v>
-      </c>
-      <c r="G89" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-0.05711503892809356</v>
+      </c>
+      <c r="G89" s="22" t="n">
+        <v>0.1348598378668211</v>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
-          <t>0.11~0.16%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="23" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B90" s="23" t="inlineStr">
         <is>
-          <t>한국투자법인용MMF 2(국공채)</t>
+          <t>iShares 미국 종합채권</t>
         </is>
       </c>
       <c r="C90" s="23" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D90" s="23" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
-        </is>
-      </c>
-      <c r="E90" s="24" t="n">
-        <v>4378362865193</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E90" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F90" s="25" t="n">
-        <v>0.028016</v>
-      </c>
-      <c r="G90" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-0.00707032975902111</v>
+      </c>
+      <c r="G90" s="25" t="n">
+        <v>0.05242550774268031</v>
       </c>
       <c r="H90" s="23" t="inlineStr">
         <is>
-          <t>0.06~0.16%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="14" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>미래에셋법인전용MMF 1(국공채)</t>
+          <t>iShares 투자등급 회사채</t>
         </is>
       </c>
       <c r="C91" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="E91" s="26" t="n">
-        <v>4325093122649</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F91" s="22" t="n">
-        <v>0.027934</v>
-      </c>
-      <c r="G91" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-0.02183448542608113</v>
+      </c>
+      <c r="G91" s="22" t="n">
+        <v>0.07104050626038284</v>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
-          <t>0.05~0.15%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="23" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B92" s="23" t="inlineStr">
         <is>
-          <t>브이아이천하제일법인MMF1</t>
+          <t>iShares 하이일드 회사채</t>
         </is>
       </c>
       <c r="C92" s="23" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D92" s="23" t="inlineStr">
         <is>
-          <t>브이아이자산운용</t>
-        </is>
-      </c>
-      <c r="E92" s="24" t="n">
-        <v>4238138300942</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E92" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F92" s="25" t="n">
-        <v>0.028224</v>
-      </c>
-      <c r="G92" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.02786343669994706</v>
+      </c>
+      <c r="G92" s="25" t="n">
+        <v>0.050268463091665</v>
       </c>
       <c r="H92" s="23" t="inlineStr">
         <is>
-          <t>0.09~0.12%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="14" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>NH-Amundi법인MMF 8</t>
+          <t>SPDR 금</t>
         </is>
       </c>
       <c r="C93" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>엔에이치아문디자산운용</t>
-        </is>
-      </c>
-      <c r="E93" s="26" t="n">
-        <v>4198179317175</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F93" s="22" t="n">
-        <v>0.027945</v>
-      </c>
-      <c r="G93" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H93" s="28" t="n">
-        <v>0.001</v>
+        <v>0.1905214114016085</v>
+      </c>
+      <c r="G93" s="22" t="n">
+        <v>0.2154040053034466</v>
+      </c>
+      <c r="H93" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="23" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B94" s="23" t="inlineStr">
         <is>
-          <t>하나신종MMF(S-29)</t>
+          <t>iShares 은</t>
         </is>
       </c>
       <c r="C94" s="23" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D94" s="23" t="inlineStr">
         <is>
-          <t>하나자산운용</t>
-        </is>
-      </c>
-      <c r="E94" s="24" t="n">
-        <v>3951980192407</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E94" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F94" s="25" t="n">
-        <v>0.029723</v>
-      </c>
-      <c r="G94" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.5858692775866632</v>
+      </c>
+      <c r="G94" s="25" t="n">
+        <v>0.4420072503135195</v>
       </c>
       <c r="H94" s="23" t="inlineStr">
         <is>
-          <t>0.09~0.13%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="14" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>삼성스마트MMF법인 1</t>
+          <t>United States 원유</t>
         </is>
       </c>
       <c r="C95" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D95" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용</t>
-        </is>
-      </c>
-      <c r="E95" s="26" t="n">
-        <v>3884061991950</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E95" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F95" s="22" t="n">
-        <v>0.028099</v>
-      </c>
-      <c r="G95" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>1.051754034947312</v>
+      </c>
+      <c r="G95" s="22" t="n">
+        <v>0.3737647369952773</v>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
-          <t>0.07~0.10%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="23" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B96" s="23" t="inlineStr">
         <is>
-          <t>신한 BEST법인용MMF GS- 1(종류)</t>
+          <t>Invesco 원자재</t>
         </is>
       </c>
       <c r="C96" s="23" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D96" s="23" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="E96" s="24" t="n">
-        <v>3871419558918</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E96" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F96" s="25" t="n">
-        <v>0.027833</v>
-      </c>
-      <c r="G96" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.5101417506271237</v>
+      </c>
+      <c r="G96" s="25" t="n">
+        <v>0.1721311332624557</v>
       </c>
       <c r="H96" s="23" t="inlineStr">
         <is>
-          <t>0.06~0.12%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="14" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>KB법인용MMF I-2(국공채)(운용)</t>
+          <t>Vanguard 미국 리츠</t>
         </is>
       </c>
       <c r="C97" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D97" s="14" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
-        </is>
-      </c>
-      <c r="E97" s="26" t="n">
-        <v>3836167684813</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E97" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F97" s="22" t="n">
-        <v>0.027897</v>
-      </c>
-      <c r="G97" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.04842313369172224</v>
+      </c>
+      <c r="G97" s="22" t="n">
+        <v>0.1683615867048639</v>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
-          <t>0.07~0.12%</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="23" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B98" s="23" t="inlineStr">
         <is>
-          <t>BNK법인MMF 1(국공채)</t>
+          <t>Schwab 미국 배당주</t>
         </is>
       </c>
       <c r="C98" s="23" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D98" s="23" t="inlineStr">
         <is>
-          <t>비엔케이자산운용</t>
-        </is>
-      </c>
-      <c r="E98" s="24" t="n">
-        <v>3638336747805</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E98" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F98" s="25" t="n">
-        <v>0.028014</v>
-      </c>
-      <c r="G98" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H98" s="27" t="n">
-        <v>0.001</v>
+        <v>0.2710968871712811</v>
+      </c>
+      <c r="G98" s="25" t="n">
+        <v>0.1321671662551849</v>
+      </c>
+      <c r="H98" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="14" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>교보악사프라임법인MMF J- 1(운용)</t>
+          <t>Vanguard 배당성장</t>
         </is>
       </c>
       <c r="C99" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D99" s="14" t="inlineStr">
         <is>
-          <t>교보악사자산운용</t>
-        </is>
-      </c>
-      <c r="E99" s="26" t="n">
-        <v>3583677561222</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E99" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F99" s="22" t="n">
-        <v>0.028143</v>
-      </c>
-      <c r="G99" s="14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H99" s="28" t="n">
-        <v>0.00108</v>
+        <v>0.1164247275358388</v>
+      </c>
+      <c r="G99" s="22" t="n">
+        <v>0.1223752554121164</v>
+      </c>
+      <c r="H99" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -5543,7 +5571,7 @@
       </c>
       <c r="B100" s="23" t="inlineStr">
         <is>
-          <t>DB클린법인MMF 4운용</t>
+          <t>삼성MMF법인 1</t>
         </is>
       </c>
       <c r="C100" s="23" t="inlineStr">
@@ -5553,22 +5581,24 @@
       </c>
       <c r="D100" s="23" t="inlineStr">
         <is>
-          <t>디비자산운용</t>
+          <t>삼성자산운용</t>
         </is>
       </c>
       <c r="E100" s="24" t="n">
-        <v>2927764530475</v>
+        <v>11338987563533</v>
       </c>
       <c r="F100" s="25" t="n">
-        <v>0.028008</v>
+        <v>0.029549</v>
       </c>
       <c r="G100" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H100" s="27" t="n">
-        <v>0.001</v>
+      <c r="H100" s="23" t="inlineStr">
+        <is>
+          <t>0.05~0.09%</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -5579,7 +5609,7 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>Plus신종법인용MMF 1</t>
+          <t>우리큰만족법인MMF 1(국공채)</t>
         </is>
       </c>
       <c r="C101" s="14" t="inlineStr">
@@ -5589,14 +5619,14 @@
       </c>
       <c r="D101" s="14" t="inlineStr">
         <is>
-          <t>플러스자산운용</t>
+          <t>우리자산운용</t>
         </is>
       </c>
       <c r="E101" s="26" t="n">
-        <v>2916524377928</v>
+        <v>8622592894029</v>
       </c>
       <c r="F101" s="22" t="n">
-        <v>0.029821</v>
+        <v>0.028073</v>
       </c>
       <c r="G101" s="14" t="inlineStr">
         <is>
@@ -5605,7 +5635,7 @@
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
-          <t>0.10~0.11%</t>
+          <t>0.08~0.10%</t>
         </is>
       </c>
     </row>
@@ -5617,7 +5647,7 @@
       </c>
       <c r="B102" s="23" t="inlineStr">
         <is>
-          <t>플러스국공채법인용MMF3</t>
+          <t>IBK그랑프리국공채MMF법인투자신탁 1[국공채]</t>
         </is>
       </c>
       <c r="C102" s="23" t="inlineStr">
@@ -5627,14 +5657,14 @@
       </c>
       <c r="D102" s="23" t="inlineStr">
         <is>
-          <t>플러스자산운용</t>
+          <t>아이비케이자산운용</t>
         </is>
       </c>
       <c r="E102" s="24" t="n">
-        <v>2602484819461</v>
+        <v>8496684909652</v>
       </c>
       <c r="F102" s="25" t="n">
-        <v>0.028117</v>
+        <v>0.028188</v>
       </c>
       <c r="G102" s="23" t="inlineStr">
         <is>
@@ -5643,7 +5673,7 @@
       </c>
       <c r="H102" s="23" t="inlineStr">
         <is>
-          <t>0.06~0.10%</t>
+          <t>0.09~0.17%</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5685,7 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>미래에셋법인전용MMF A-4</t>
+          <t>KB법인용MMF I-1(운용)</t>
         </is>
       </c>
       <c r="C103" s="14" t="inlineStr">
@@ -5665,14 +5695,14 @@
       </c>
       <c r="D103" s="14" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="E103" s="26" t="n">
-        <v>2542177044879</v>
+        <v>8440063369994</v>
       </c>
       <c r="F103" s="22" t="n">
-        <v>0.030076</v>
+        <v>0.029889</v>
       </c>
       <c r="G103" s="14" t="inlineStr">
         <is>
@@ -5681,7 +5711,7 @@
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
-          <t>0.05~0.09%</t>
+          <t>0.06~0.09%</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5723,7 @@
       </c>
       <c r="B104" s="23" t="inlineStr">
         <is>
-          <t>키움프런티어법인용MMF 3[국공채]</t>
+          <t>우리큰만족신종MMF3</t>
         </is>
       </c>
       <c r="C104" s="23" t="inlineStr">
@@ -5703,14 +5733,14 @@
       </c>
       <c r="D104" s="23" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
+          <t>우리자산운용</t>
         </is>
       </c>
       <c r="E104" s="24" t="n">
-        <v>2352868227257</v>
+        <v>7422943031742</v>
       </c>
       <c r="F104" s="25" t="n">
-        <v>0.027922</v>
+        <v>0.030522</v>
       </c>
       <c r="G104" s="23" t="inlineStr">
         <is>
@@ -5719,7 +5749,7 @@
       </c>
       <c r="H104" s="23" t="inlineStr">
         <is>
-          <t>0.10~0.24%</t>
+          <t>0.09~0.11%</t>
         </is>
       </c>
     </row>
@@ -5731,7 +5761,7 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>대신국공채법인전용MMF 1(운용)</t>
+          <t>신영법인용MMF4-26_운용</t>
         </is>
       </c>
       <c r="C105" s="14" t="inlineStr">
@@ -5741,14 +5771,14 @@
       </c>
       <c r="D105" s="14" t="inlineStr">
         <is>
-          <t>대신자산운용</t>
+          <t>신영자산운용</t>
         </is>
       </c>
       <c r="E105" s="26" t="n">
-        <v>2191767203854</v>
+        <v>6618786412255</v>
       </c>
       <c r="F105" s="22" t="n">
-        <v>0.028038</v>
+        <v>0.028373</v>
       </c>
       <c r="G105" s="14" t="inlineStr">
         <is>
@@ -5757,36 +5787,36 @@
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
-          <t>0.07~0.10%</t>
+          <t>0.10~0.15%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="23" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B106" s="23" t="inlineStr">
         <is>
-          <t>피델리티글로벌테크놀로지증권자투자신탁(주식-재간접형)</t>
+          <t>신한BEST신종법인용MMFGS-2(종류)</t>
         </is>
       </c>
       <c r="C106" s="23" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D106" s="23" t="inlineStr">
         <is>
-          <t>피델리티자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="E106" s="24" t="n">
-        <v>921799051290</v>
+        <v>5994110526287</v>
       </c>
       <c r="F106" s="25" t="n">
-        <v>0.20358</v>
+        <v>0.029896</v>
       </c>
       <c r="G106" s="23" t="inlineStr">
         <is>
@@ -5795,36 +5825,36 @@
       </c>
       <c r="H106" s="23" t="inlineStr">
         <is>
-          <t>0.16~1.36%</t>
+          <t>0.07~0.09%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="14" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>피델리티월지급식아시아하이일드증권자투자신탁[채권-재간접형]</t>
+          <t>한화골드법인MMF-KM3(국공채)</t>
         </is>
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D107" s="14" t="inlineStr">
         <is>
-          <t>피델리티자산운용</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="E107" s="26" t="n">
-        <v>736452760783</v>
+        <v>4824524208474</v>
       </c>
       <c r="F107" s="22" t="n">
-        <v>0.051551</v>
+        <v>0.028207</v>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
@@ -5833,36 +5863,36 @@
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
-          <t>0.37~1.17%</t>
+          <t>0.06~0.10%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="23" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B108" s="23" t="inlineStr">
         <is>
-          <t>피델리티글로벌배당인컴증권자투자신탁(주식-재간접형)</t>
+          <t>하나클래스원신종MMF(K-5)</t>
         </is>
       </c>
       <c r="C108" s="23" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D108" s="23" t="inlineStr">
         <is>
-          <t>피델리티자산운용</t>
+          <t>하나자산운용</t>
         </is>
       </c>
       <c r="E108" s="24" t="n">
-        <v>571560295874</v>
+        <v>4606467618325</v>
       </c>
       <c r="F108" s="25" t="n">
-        <v>0.108062</v>
+        <v>0.028155</v>
       </c>
       <c r="G108" s="23" t="inlineStr">
         <is>
@@ -5871,36 +5901,36 @@
       </c>
       <c r="H108" s="23" t="inlineStr">
         <is>
-          <t>0.16~1.36%</t>
+          <t>0.11~0.16%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="14" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>AB월지급글로벌고수익증권투자신탁[채권-재간접형]</t>
+          <t>한국투자법인용MMF 2(국공채)</t>
         </is>
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D109" s="14" t="inlineStr">
         <is>
-          <t>얼라이언스번스틴자산운용</t>
+          <t>한국투자신탁운용</t>
         </is>
       </c>
       <c r="E109" s="26" t="n">
-        <v>546248135264</v>
+        <v>4378362865193</v>
       </c>
       <c r="F109" s="22" t="n">
-        <v>0.018373</v>
+        <v>0.028016</v>
       </c>
       <c r="G109" s="14" t="inlineStr">
         <is>
@@ -5909,36 +5939,36 @@
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
-          <t>0.17~0.71%</t>
+          <t>0.06~0.16%</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="23" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B110" s="23" t="inlineStr">
         <is>
-          <t>한국투자글로벌전기차&amp;자율주행증권투자신탁(주식)(모)</t>
+          <t>미래에셋법인전용MMF 1(국공채)</t>
         </is>
       </c>
       <c r="C110" s="23" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D110" s="23" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="E110" s="24" t="n">
-        <v>476227522659</v>
+        <v>4325093122649</v>
       </c>
       <c r="F110" s="25" t="n">
-        <v>0.178201</v>
+        <v>0.027934</v>
       </c>
       <c r="G110" s="23" t="inlineStr">
         <is>
@@ -5947,36 +5977,36 @@
       </c>
       <c r="H110" s="23" t="inlineStr">
         <is>
-          <t>0.77~2.07%</t>
+          <t>0.05~0.15%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="14" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>AB미국그로스증권투자신탁(주식-재간접형)</t>
+          <t>브이아이천하제일법인MMF1</t>
         </is>
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D111" s="14" t="inlineStr">
         <is>
-          <t>얼라이언스번스틴자산운용</t>
+          <t>브이아이자산운용</t>
         </is>
       </c>
       <c r="E111" s="26" t="n">
-        <v>443774660426</v>
+        <v>4238138300942</v>
       </c>
       <c r="F111" s="22" t="n">
-        <v>0.009127</v>
+        <v>0.028224</v>
       </c>
       <c r="G111" s="14" t="inlineStr">
         <is>
@@ -5985,74 +6015,72 @@
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
-          <t>0.17~1.67%</t>
+          <t>0.09~0.12%</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="23" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B112" s="23" t="inlineStr">
         <is>
-          <t>KB다이나믹적격TDF2030증권자투자신탁(주식혼합-재간접형)(운용)</t>
+          <t>NH-Amundi법인MMF 8</t>
         </is>
       </c>
       <c r="C112" s="23" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D112" s="23" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>엔에이치아문디자산운용</t>
         </is>
       </c>
       <c r="E112" s="24" t="n">
-        <v>415554701169</v>
+        <v>4198179317175</v>
       </c>
       <c r="F112" s="25" t="n">
-        <v>0.189953</v>
+        <v>0.027945</v>
       </c>
       <c r="G112" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H112" s="23" t="inlineStr">
-        <is>
-          <t>0.24~1.19%</t>
-        </is>
+      <c r="H112" s="27" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="14" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>우리미국단기채공모주증권자투자신탁 1(H)(채권혼합)</t>
+          <t>하나신종MMF(S-29)</t>
         </is>
       </c>
       <c r="C113" s="14" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D113" s="14" t="inlineStr">
         <is>
-          <t>우리자산운용</t>
+          <t>하나자산운용</t>
         </is>
       </c>
       <c r="E113" s="26" t="n">
-        <v>355805691737</v>
+        <v>3951980192407</v>
       </c>
       <c r="F113" s="22" t="n">
-        <v>0.052435</v>
+        <v>0.029723</v>
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
@@ -6061,36 +6089,36 @@
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
-          <t>0.80~1.70%</t>
+          <t>0.09~0.13%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="23" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B114" s="23" t="inlineStr">
         <is>
-          <t>한국투자미국장기국채증권자투자신탁H(채권-재간접형)(모)</t>
+          <t>삼성스마트MMF법인 1</t>
         </is>
       </c>
       <c r="C114" s="23" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D114" s="23" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
+          <t>삼성자산운용</t>
         </is>
       </c>
       <c r="E114" s="24" t="n">
-        <v>312359779743</v>
+        <v>3884061991950</v>
       </c>
       <c r="F114" s="25" t="n">
-        <v>-0.063263</v>
+        <v>0.028099</v>
       </c>
       <c r="G114" s="23" t="inlineStr">
         <is>
@@ -6099,24 +6127,24 @@
       </c>
       <c r="H114" s="23" t="inlineStr">
         <is>
-          <t>0.25~0.85%</t>
+          <t>0.07~0.10%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="14" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>신한마음편한적격TDF2050증권자투자신탁[주식혼합-재간접형](종류)</t>
+          <t>신한 BEST법인용MMF GS- 1(종류)</t>
         </is>
       </c>
       <c r="C115" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
@@ -6125,10 +6153,10 @@
         </is>
       </c>
       <c r="E115" s="26" t="n">
-        <v>307888109504</v>
+        <v>3871419558918</v>
       </c>
       <c r="F115" s="22" t="n">
-        <v>0.23546</v>
+        <v>0.027833</v>
       </c>
       <c r="G115" s="14" t="inlineStr">
         <is>
@@ -6137,36 +6165,36 @@
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
-          <t>0.56~1.31%</t>
+          <t>0.06~0.12%</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="23" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B116" s="23" t="inlineStr">
         <is>
-          <t>신한마음편한적격TDF2035증권자투자신탁[주식혼합-재간접형](종류)</t>
+          <t>KB법인용MMF I-2(국공채)(운용)</t>
         </is>
       </c>
       <c r="C116" s="23" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D116" s="23" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="E116" s="24" t="n">
-        <v>305480846988</v>
+        <v>3836167684813</v>
       </c>
       <c r="F116" s="25" t="n">
-        <v>0.177612</v>
+        <v>0.027897</v>
       </c>
       <c r="G116" s="23" t="inlineStr">
         <is>
@@ -6175,150 +6203,144 @@
       </c>
       <c r="H116" s="23" t="inlineStr">
         <is>
-          <t>0.33~0.82%</t>
+          <t>0.07~0.12%</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="14" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B117" s="14" t="inlineStr">
         <is>
-          <t>신한미국S&amp;P500인덱스증권자투자신탁(UH)[주식-파생형]</t>
+          <t>BNK법인MMF 1(국공채)</t>
         </is>
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D117" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>비엔케이자산운용</t>
         </is>
       </c>
       <c r="E117" s="26" t="n">
-        <v>285114854089</v>
+        <v>3638336747805</v>
       </c>
       <c r="F117" s="22" t="n">
-        <v>0.141662</v>
+        <v>0.028014</v>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H117" s="14" t="inlineStr">
-        <is>
-          <t>0.26~1.15%</t>
-        </is>
+      <c r="H117" s="28" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="23" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B118" s="23" t="inlineStr">
         <is>
-          <t>삼성글로벌액티브적격TDF2030증권투자신탁H[주식혼합-재간접형]</t>
+          <t>교보악사프라임법인MMF J- 1(운용)</t>
         </is>
       </c>
       <c r="C118" s="23" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D118" s="23" t="inlineStr">
         <is>
-          <t>삼성자산운용</t>
+          <t>교보악사자산운용</t>
         </is>
       </c>
       <c r="E118" s="24" t="n">
-        <v>284075555238</v>
+        <v>3583677561222</v>
       </c>
       <c r="F118" s="25" t="n">
-        <v>0.097423</v>
+        <v>0.028143</v>
       </c>
       <c r="G118" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H118" s="23" t="inlineStr">
-        <is>
-          <t>0.23~0.76%</t>
-        </is>
+      <c r="H118" s="27" t="n">
+        <v>0.00108</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="14" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B119" s="14" t="inlineStr">
         <is>
-          <t>NH-Amundi하나로적격TDF2030증권투자신탁[주식혼합-재간접형]</t>
+          <t>DB클린법인MMF 4운용</t>
         </is>
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
         <is>
-          <t>엔에이치아문디자산운용</t>
+          <t>디비자산운용</t>
         </is>
       </c>
       <c r="E119" s="26" t="n">
-        <v>274599368395</v>
+        <v>2927764530475</v>
       </c>
       <c r="F119" s="22" t="n">
-        <v>0.110507</v>
+        <v>0.028008</v>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H119" s="14" t="inlineStr">
-        <is>
-          <t>0.35~0.80%</t>
-        </is>
+      <c r="H119" s="28" t="n">
+        <v>0.001</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="23" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B120" s="23" t="inlineStr">
         <is>
-          <t>한국투자MAN다이나믹인컴월배당증권자투자신탁H(채권-재간접형)(모)</t>
+          <t>Plus신종법인용MMF 1</t>
         </is>
       </c>
       <c r="C120" s="23" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D120" s="23" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
+          <t>플러스자산운용</t>
         </is>
       </c>
       <c r="E120" s="24" t="n">
-        <v>272544857205</v>
+        <v>2916524377928</v>
       </c>
       <c r="F120" s="25" t="n">
-        <v>0.06779</v>
+        <v>0.029821</v>
       </c>
       <c r="G120" s="23" t="inlineStr">
         <is>
@@ -6327,36 +6349,36 @@
       </c>
       <c r="H120" s="23" t="inlineStr">
         <is>
-          <t>0.54~1.24%</t>
+          <t>0.10~0.11%</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="14" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B121" s="14" t="inlineStr">
         <is>
-          <t>KB다이나믹적격TDF2040증권자투자신탁(주식혼합-재간접형)(운용)</t>
+          <t>플러스국공채법인용MMF3</t>
         </is>
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>플러스자산운용</t>
         </is>
       </c>
       <c r="E121" s="26" t="n">
-        <v>253133965500</v>
+        <v>2602484819461</v>
       </c>
       <c r="F121" s="22" t="n">
-        <v>0.235043</v>
+        <v>0.028117</v>
       </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
@@ -6365,36 +6387,36 @@
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
-          <t>0.34~1.19%</t>
+          <t>0.06~0.10%</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="23" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B122" s="23" t="inlineStr">
         <is>
-          <t>KCGI샐러리맨증권자투자신탁[주식-재간접형]</t>
+          <t>미래에셋법인전용MMF A-4</t>
         </is>
       </c>
       <c r="C122" s="23" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D122" s="23" t="inlineStr">
         <is>
-          <t>케이씨지아이자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="E122" s="24" t="n">
-        <v>252365682418</v>
+        <v>2542177044879</v>
       </c>
       <c r="F122" s="25" t="n">
-        <v>0.313328</v>
+        <v>0.030076</v>
       </c>
       <c r="G122" s="23" t="inlineStr">
         <is>
@@ -6403,36 +6425,36 @@
       </c>
       <c r="H122" s="23" t="inlineStr">
         <is>
-          <t>0.64~1.01%</t>
+          <t>0.05~0.09%</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="14" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B123" s="14" t="inlineStr">
         <is>
-          <t>NH-Amundi올바른지구OCIO자산배분증권자투자신탁[혼합-재간접형]</t>
+          <t>키움프런티어법인용MMF 3[국공채]</t>
         </is>
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
         <is>
-          <t>엔에이치아문디자산운용</t>
+          <t>키움투자자산운용</t>
         </is>
       </c>
       <c r="E123" s="26" t="n">
-        <v>251911631894</v>
+        <v>2352868227257</v>
       </c>
       <c r="F123" s="22" t="n">
-        <v>0.06297700000000001</v>
+        <v>0.027922</v>
       </c>
       <c r="G123" s="14" t="inlineStr">
         <is>
@@ -6441,36 +6463,36 @@
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
-          <t>0.41~1.01%</t>
+          <t>0.10~0.24%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="23" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="B124" s="23" t="inlineStr">
         <is>
-          <t>KB다이나믹적격TDF2050증권자투자신탁(주식혼합-재간접형)(운용)</t>
+          <t>대신국공채법인전용MMF 1(운용)</t>
         </is>
       </c>
       <c r="C124" s="23" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>MMF</t>
         </is>
       </c>
       <c r="D124" s="23" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>대신자산운용</t>
         </is>
       </c>
       <c r="E124" s="24" t="n">
-        <v>234933545728</v>
+        <v>2191767203854</v>
       </c>
       <c r="F124" s="25" t="n">
-        <v>0.257195</v>
+        <v>0.028038</v>
       </c>
       <c r="G124" s="23" t="inlineStr">
         <is>
@@ -6479,7 +6501,7 @@
       </c>
       <c r="H124" s="23" t="inlineStr">
         <is>
-          <t>0.34~1.19%</t>
+          <t>0.07~0.10%</t>
         </is>
       </c>
     </row>
@@ -6491,24 +6513,24 @@
       </c>
       <c r="B125" s="14" t="inlineStr">
         <is>
-          <t>신한마음편한적격TDF2030증권자투자신탁[주식혼합-재간접형](종류)</t>
+          <t>피델리티글로벌테크놀로지증권자투자신탁(주식-재간접형)</t>
         </is>
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="D125" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>피델리티자산운용</t>
         </is>
       </c>
       <c r="E125" s="26" t="n">
-        <v>231199778656</v>
+        <v>921799051290</v>
       </c>
       <c r="F125" s="22" t="n">
-        <v>0.149587</v>
+        <v>0.20358</v>
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
@@ -6517,7 +6539,7 @@
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
-          <t>0.33~0.82%</t>
+          <t>0.16~1.36%</t>
         </is>
       </c>
     </row>
@@ -6529,24 +6551,24 @@
       </c>
       <c r="B126" s="23" t="inlineStr">
         <is>
-          <t>삼성글로벌액티브적격TDF2045증권투자신탁H[주식혼합-재간접형]</t>
+          <t>피델리티월지급식아시아하이일드증권자투자신탁[채권-재간접형]</t>
         </is>
       </c>
       <c r="C126" s="23" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="D126" s="23" t="inlineStr">
         <is>
-          <t>삼성자산운용</t>
+          <t>피델리티자산운용</t>
         </is>
       </c>
       <c r="E126" s="24" t="n">
-        <v>228747081728</v>
+        <v>736452760783</v>
       </c>
       <c r="F126" s="25" t="n">
-        <v>0.146997</v>
+        <v>0.051551</v>
       </c>
       <c r="G126" s="23" t="inlineStr">
         <is>
@@ -6555,7 +6577,7 @@
       </c>
       <c r="H126" s="23" t="inlineStr">
         <is>
-          <t>0.33~1.30%</t>
+          <t>0.37~1.17%</t>
         </is>
       </c>
     </row>
@@ -6567,24 +6589,24 @@
       </c>
       <c r="B127" s="14" t="inlineStr">
         <is>
-          <t>KCGI프리덤적격TDF2050증권자투자신탁[주식혼합-재간접형]</t>
+          <t>피델리티글로벌배당인컴증권자투자신탁(주식-재간접형)</t>
         </is>
       </c>
       <c r="C127" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="D127" s="14" t="inlineStr">
         <is>
-          <t>케이씨지아이자산운용</t>
+          <t>피델리티자산운용</t>
         </is>
       </c>
       <c r="E127" s="26" t="n">
-        <v>228544238026</v>
+        <v>571560295874</v>
       </c>
       <c r="F127" s="22" t="n">
-        <v>0.223357</v>
+        <v>0.108062</v>
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
@@ -6593,7 +6615,7 @@
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
-          <t>0.56~0.89%</t>
+          <t>0.16~1.36%</t>
         </is>
       </c>
     </row>
@@ -6605,24 +6627,24 @@
       </c>
       <c r="B128" s="23" t="inlineStr">
         <is>
-          <t>키움키워드림적격TDF2030증권투자신탁 1[혼합-재간접형]</t>
+          <t>AB월지급글로벌고수익증권투자신탁[채권-재간접형]</t>
         </is>
       </c>
       <c r="C128" s="23" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="D128" s="23" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
+          <t>얼라이언스번스틴자산운용</t>
         </is>
       </c>
       <c r="E128" s="24" t="n">
-        <v>226050052467</v>
+        <v>546248135264</v>
       </c>
       <c r="F128" s="25" t="n">
-        <v>0.079793</v>
+        <v>0.018373</v>
       </c>
       <c r="G128" s="23" t="inlineStr">
         <is>
@@ -6631,7 +6653,7 @@
       </c>
       <c r="H128" s="23" t="inlineStr">
         <is>
-          <t>0.28~0.66%</t>
+          <t>0.17~0.71%</t>
         </is>
       </c>
     </row>
@@ -6643,32 +6665,34 @@
       </c>
       <c r="B129" s="14" t="inlineStr">
         <is>
-          <t>이지스글로벌공모부동산투자신탁281(파생형)</t>
+          <t>한국투자글로벌전기차&amp;자율주행증권투자신탁(주식)(모)</t>
         </is>
       </c>
       <c r="C129" s="14" t="inlineStr">
         <is>
-          <t>해외대체</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="D129" s="14" t="inlineStr">
         <is>
-          <t>이지스자산운용</t>
+          <t>한국투자신탁운용</t>
         </is>
       </c>
       <c r="E129" s="26" t="n">
-        <v>223655294000</v>
+        <v>476227522659</v>
       </c>
       <c r="F129" s="22" t="n">
-        <v>-0.145053</v>
+        <v>0.178201</v>
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H129" s="28" t="n">
-        <v>0.0054</v>
+      <c r="H129" s="14" t="inlineStr">
+        <is>
+          <t>0.77~2.07%</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -6679,31 +6703,751 @@
       </c>
       <c r="B130" s="23" t="inlineStr">
         <is>
+          <t>AB미국그로스증권투자신탁(주식-재간접형)</t>
+        </is>
+      </c>
+      <c r="C130" s="23" t="inlineStr">
+        <is>
+          <t>해외주식형</t>
+        </is>
+      </c>
+      <c r="D130" s="23" t="inlineStr">
+        <is>
+          <t>얼라이언스번스틴자산운용</t>
+        </is>
+      </c>
+      <c r="E130" s="24" t="n">
+        <v>443774660426</v>
+      </c>
+      <c r="F130" s="25" t="n">
+        <v>0.009127</v>
+      </c>
+      <c r="G130" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H130" s="23" t="inlineStr">
+        <is>
+          <t>0.17~1.67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B131" s="14" t="inlineStr">
+        <is>
+          <t>KB다이나믹적격TDF2030증권자투자신탁(주식혼합-재간접형)(운용)</t>
+        </is>
+      </c>
+      <c r="C131" s="14" t="inlineStr">
+        <is>
+          <t>기타형</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>케이비자산운용</t>
+        </is>
+      </c>
+      <c r="E131" s="26" t="n">
+        <v>415554701169</v>
+      </c>
+      <c r="F131" s="22" t="n">
+        <v>0.189953</v>
+      </c>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H131" s="14" t="inlineStr">
+        <is>
+          <t>0.24~1.19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="23" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B132" s="23" t="inlineStr">
+        <is>
+          <t>우리미국단기채공모주증권자투자신탁 1(H)(채권혼합)</t>
+        </is>
+      </c>
+      <c r="C132" s="23" t="inlineStr">
+        <is>
+          <t>해외혼합형</t>
+        </is>
+      </c>
+      <c r="D132" s="23" t="inlineStr">
+        <is>
+          <t>우리자산운용</t>
+        </is>
+      </c>
+      <c r="E132" s="24" t="n">
+        <v>355805691737</v>
+      </c>
+      <c r="F132" s="25" t="n">
+        <v>0.052435</v>
+      </c>
+      <c r="G132" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H132" s="23" t="inlineStr">
+        <is>
+          <t>0.80~1.70%</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B133" s="14" t="inlineStr">
+        <is>
+          <t>한국투자미국장기국채증권자투자신탁H(채권-재간접형)(모)</t>
+        </is>
+      </c>
+      <c r="C133" s="14" t="inlineStr">
+        <is>
+          <t>해외채권형</t>
+        </is>
+      </c>
+      <c r="D133" s="14" t="inlineStr">
+        <is>
+          <t>한국투자신탁운용</t>
+        </is>
+      </c>
+      <c r="E133" s="26" t="n">
+        <v>312359779743</v>
+      </c>
+      <c r="F133" s="22" t="n">
+        <v>-0.063263</v>
+      </c>
+      <c r="G133" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H133" s="14" t="inlineStr">
+        <is>
+          <t>0.25~0.85%</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="23" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B134" s="23" t="inlineStr">
+        <is>
+          <t>신한마음편한적격TDF2050증권자투자신탁[주식혼합-재간접형](종류)</t>
+        </is>
+      </c>
+      <c r="C134" s="23" t="inlineStr">
+        <is>
+          <t>기타형</t>
+        </is>
+      </c>
+      <c r="D134" s="23" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="E134" s="24" t="n">
+        <v>307888109504</v>
+      </c>
+      <c r="F134" s="25" t="n">
+        <v>0.23546</v>
+      </c>
+      <c r="G134" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H134" s="23" t="inlineStr">
+        <is>
+          <t>0.56~1.31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B135" s="14" t="inlineStr">
+        <is>
+          <t>신한마음편한적격TDF2035증권자투자신탁[주식혼합-재간접형](종류)</t>
+        </is>
+      </c>
+      <c r="C135" s="14" t="inlineStr">
+        <is>
+          <t>기타형</t>
+        </is>
+      </c>
+      <c r="D135" s="14" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="E135" s="26" t="n">
+        <v>305480846988</v>
+      </c>
+      <c r="F135" s="22" t="n">
+        <v>0.177612</v>
+      </c>
+      <c r="G135" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H135" s="14" t="inlineStr">
+        <is>
+          <t>0.33~0.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="23" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B136" s="23" t="inlineStr">
+        <is>
+          <t>신한미국S&amp;P500인덱스증권자투자신탁(UH)[주식-파생형]</t>
+        </is>
+      </c>
+      <c r="C136" s="23" t="inlineStr">
+        <is>
+          <t>해외주식형</t>
+        </is>
+      </c>
+      <c r="D136" s="23" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="E136" s="24" t="n">
+        <v>285114854089</v>
+      </c>
+      <c r="F136" s="25" t="n">
+        <v>0.141662</v>
+      </c>
+      <c r="G136" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H136" s="23" t="inlineStr">
+        <is>
+          <t>0.26~1.15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B137" s="14" t="inlineStr">
+        <is>
+          <t>삼성글로벌액티브적격TDF2030증권투자신탁H[주식혼합-재간접형]</t>
+        </is>
+      </c>
+      <c r="C137" s="14" t="inlineStr">
+        <is>
+          <t>기타형</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="inlineStr">
+        <is>
+          <t>삼성자산운용</t>
+        </is>
+      </c>
+      <c r="E137" s="26" t="n">
+        <v>284075555238</v>
+      </c>
+      <c r="F137" s="22" t="n">
+        <v>0.097423</v>
+      </c>
+      <c r="G137" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H137" s="14" t="inlineStr">
+        <is>
+          <t>0.23~0.76%</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="23" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B138" s="23" t="inlineStr">
+        <is>
+          <t>NH-Amundi하나로적격TDF2030증권투자신탁[주식혼합-재간접형]</t>
+        </is>
+      </c>
+      <c r="C138" s="23" t="inlineStr">
+        <is>
+          <t>기타형</t>
+        </is>
+      </c>
+      <c r="D138" s="23" t="inlineStr">
+        <is>
+          <t>엔에이치아문디자산운용</t>
+        </is>
+      </c>
+      <c r="E138" s="24" t="n">
+        <v>274599368395</v>
+      </c>
+      <c r="F138" s="25" t="n">
+        <v>0.110507</v>
+      </c>
+      <c r="G138" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H138" s="23" t="inlineStr">
+        <is>
+          <t>0.35~0.80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B139" s="14" t="inlineStr">
+        <is>
+          <t>한국투자MAN다이나믹인컴월배당증권자투자신탁H(채권-재간접형)(모)</t>
+        </is>
+      </c>
+      <c r="C139" s="14" t="inlineStr">
+        <is>
+          <t>해외채권형</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="inlineStr">
+        <is>
+          <t>한국투자신탁운용</t>
+        </is>
+      </c>
+      <c r="E139" s="26" t="n">
+        <v>272544857205</v>
+      </c>
+      <c r="F139" s="22" t="n">
+        <v>0.06779</v>
+      </c>
+      <c r="G139" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H139" s="14" t="inlineStr">
+        <is>
+          <t>0.54~1.24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="23" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B140" s="23" t="inlineStr">
+        <is>
+          <t>KB다이나믹적격TDF2040증권자투자신탁(주식혼합-재간접형)(운용)</t>
+        </is>
+      </c>
+      <c r="C140" s="23" t="inlineStr">
+        <is>
+          <t>기타형</t>
+        </is>
+      </c>
+      <c r="D140" s="23" t="inlineStr">
+        <is>
+          <t>케이비자산운용</t>
+        </is>
+      </c>
+      <c r="E140" s="24" t="n">
+        <v>253133965500</v>
+      </c>
+      <c r="F140" s="25" t="n">
+        <v>0.235043</v>
+      </c>
+      <c r="G140" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H140" s="23" t="inlineStr">
+        <is>
+          <t>0.34~1.19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B141" s="14" t="inlineStr">
+        <is>
+          <t>KCGI샐러리맨증권자투자신탁[주식-재간접형]</t>
+        </is>
+      </c>
+      <c r="C141" s="14" t="inlineStr">
+        <is>
+          <t>해외주식형</t>
+        </is>
+      </c>
+      <c r="D141" s="14" t="inlineStr">
+        <is>
+          <t>케이씨지아이자산운용</t>
+        </is>
+      </c>
+      <c r="E141" s="26" t="n">
+        <v>252365682418</v>
+      </c>
+      <c r="F141" s="22" t="n">
+        <v>0.313328</v>
+      </c>
+      <c r="G141" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H141" s="14" t="inlineStr">
+        <is>
+          <t>0.64~1.01%</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="23" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B142" s="23" t="inlineStr">
+        <is>
+          <t>NH-Amundi올바른지구OCIO자산배분증권자투자신탁[혼합-재간접형]</t>
+        </is>
+      </c>
+      <c r="C142" s="23" t="inlineStr">
+        <is>
+          <t>해외혼합형</t>
+        </is>
+      </c>
+      <c r="D142" s="23" t="inlineStr">
+        <is>
+          <t>엔에이치아문디자산운용</t>
+        </is>
+      </c>
+      <c r="E142" s="24" t="n">
+        <v>251911631894</v>
+      </c>
+      <c r="F142" s="25" t="n">
+        <v>0.06297700000000001</v>
+      </c>
+      <c r="G142" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H142" s="23" t="inlineStr">
+        <is>
+          <t>0.41~1.01%</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B143" s="14" t="inlineStr">
+        <is>
+          <t>KB다이나믹적격TDF2050증권자투자신탁(주식혼합-재간접형)(운용)</t>
+        </is>
+      </c>
+      <c r="C143" s="14" t="inlineStr">
+        <is>
+          <t>기타형</t>
+        </is>
+      </c>
+      <c r="D143" s="14" t="inlineStr">
+        <is>
+          <t>케이비자산운용</t>
+        </is>
+      </c>
+      <c r="E143" s="26" t="n">
+        <v>234933545728</v>
+      </c>
+      <c r="F143" s="22" t="n">
+        <v>0.257195</v>
+      </c>
+      <c r="G143" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H143" s="14" t="inlineStr">
+        <is>
+          <t>0.34~1.19%</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="23" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B144" s="23" t="inlineStr">
+        <is>
+          <t>신한마음편한적격TDF2030증권자투자신탁[주식혼합-재간접형](종류)</t>
+        </is>
+      </c>
+      <c r="C144" s="23" t="inlineStr">
+        <is>
+          <t>기타형</t>
+        </is>
+      </c>
+      <c r="D144" s="23" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="E144" s="24" t="n">
+        <v>231199778656</v>
+      </c>
+      <c r="F144" s="25" t="n">
+        <v>0.149587</v>
+      </c>
+      <c r="G144" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H144" s="23" t="inlineStr">
+        <is>
+          <t>0.33~0.82%</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B145" s="14" t="inlineStr">
+        <is>
+          <t>삼성글로벌액티브적격TDF2045증권투자신탁H[주식혼합-재간접형]</t>
+        </is>
+      </c>
+      <c r="C145" s="14" t="inlineStr">
+        <is>
+          <t>기타형</t>
+        </is>
+      </c>
+      <c r="D145" s="14" t="inlineStr">
+        <is>
+          <t>삼성자산운용</t>
+        </is>
+      </c>
+      <c r="E145" s="26" t="n">
+        <v>228747081728</v>
+      </c>
+      <c r="F145" s="22" t="n">
+        <v>0.146997</v>
+      </c>
+      <c r="G145" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H145" s="14" t="inlineStr">
+        <is>
+          <t>0.33~1.30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="23" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B146" s="23" t="inlineStr">
+        <is>
+          <t>KCGI프리덤적격TDF2050증권자투자신탁[주식혼합-재간접형]</t>
+        </is>
+      </c>
+      <c r="C146" s="23" t="inlineStr">
+        <is>
+          <t>기타형</t>
+        </is>
+      </c>
+      <c r="D146" s="23" t="inlineStr">
+        <is>
+          <t>케이씨지아이자산운용</t>
+        </is>
+      </c>
+      <c r="E146" s="24" t="n">
+        <v>228544238026</v>
+      </c>
+      <c r="F146" s="25" t="n">
+        <v>0.223357</v>
+      </c>
+      <c r="G146" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H146" s="23" t="inlineStr">
+        <is>
+          <t>0.56~0.89%</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B147" s="14" t="inlineStr">
+        <is>
+          <t>키움키워드림적격TDF2030증권투자신탁 1[혼합-재간접형]</t>
+        </is>
+      </c>
+      <c r="C147" s="14" t="inlineStr">
+        <is>
+          <t>기타형</t>
+        </is>
+      </c>
+      <c r="D147" s="14" t="inlineStr">
+        <is>
+          <t>키움투자자산운용</t>
+        </is>
+      </c>
+      <c r="E147" s="26" t="n">
+        <v>226050052467</v>
+      </c>
+      <c r="F147" s="22" t="n">
+        <v>0.079793</v>
+      </c>
+      <c r="G147" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H147" s="14" t="inlineStr">
+        <is>
+          <t>0.28~0.66%</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="23" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B148" s="23" t="inlineStr">
+        <is>
+          <t>이지스글로벌공모부동산투자신탁281(파생형)</t>
+        </is>
+      </c>
+      <c r="C148" s="23" t="inlineStr">
+        <is>
+          <t>해외대체</t>
+        </is>
+      </c>
+      <c r="D148" s="23" t="inlineStr">
+        <is>
+          <t>이지스자산운용</t>
+        </is>
+      </c>
+      <c r="E148" s="24" t="n">
+        <v>223655294000</v>
+      </c>
+      <c r="F148" s="25" t="n">
+        <v>-0.145053</v>
+      </c>
+      <c r="G148" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H148" s="27" t="n">
+        <v>0.0054</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B149" s="14" t="inlineStr">
+        <is>
           <t>한화LIFEPLUS적격TDF2050증권자투자신탁(주식혼합-재간접형)</t>
         </is>
       </c>
-      <c r="C130" s="23" t="inlineStr">
+      <c r="C149" s="14" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="D130" s="23" t="inlineStr">
+      <c r="D149" s="14" t="inlineStr">
         <is>
           <t>한화자산운용</t>
         </is>
       </c>
-      <c r="E130" s="24" t="n">
+      <c r="E149" s="26" t="n">
         <v>223261070915</v>
       </c>
-      <c r="F130" s="25" t="n">
+      <c r="F149" s="22" t="n">
         <v>0.229434</v>
       </c>
-      <c r="G130" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H130" s="23" t="inlineStr">
+      <c r="G149" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H149" s="14" t="inlineStr">
         <is>
           <t>0.44~1.33%</t>
         </is>
@@ -6872,22 +7616,18 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>한국투자증권 오픈API (모의투자, HHDFS76240000, 수정주가)</t>
         </is>
       </c>
       <c r="C8" s="21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="29" t="inlineStr">
-        <is>
-          <t>아직 받지 않았습니다 — scripts/fetch_overseas_etf_kis.py 를 러너에서 돌리면 채워집니다. 그 전까지 해외ETF 는 제안에 올리지 않습니다.</t>
-        </is>
-      </c>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="E8" s="29" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -26,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,6 +65,12 @@
     <font>
       <name val="Spoqa Han Sans Neo"/>
       <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Spoqa Han Sans Neo"/>
+      <b val="1"/>
       <color rgb="001A1A1A"/>
       <sz val="11"/>
     </font>
@@ -82,13 +88,13 @@
     <font>
       <name val="Spoqa Han Sans Neo"/>
       <b val="1"/>
-      <color rgb="000000FF"/>
+      <color rgb="006C6C6C"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Spoqa Han Sans Neo"/>
       <b val="1"/>
-      <color rgb="006C6C6C"/>
+      <color rgb="00C62828"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -106,12 +112,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F7F8FA"/>
+        <fgColor rgb="00FFF7E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF7E6"/>
+        <fgColor rgb="00F7F8FA"/>
       </patternFill>
     </fill>
     <fill>
@@ -151,9 +157,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -163,14 +169,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,23 +186,26 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -210,27 +219,27 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -605,13 +614,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col hidden="1" width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
+    <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -635,6 +645,7 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="5" ht="4" customHeight="1">
       <c r="A5" s="3" t="n"/>
@@ -643,6 +654,7 @@
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -726,6 +738,7 @@
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -748,25 +761,30 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>비중</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
+          <t>제안 비중</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>조정 비중</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>쓰는 비중</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>금액(만원)</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>과거 1년(중앙)</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>변동성(중앙)</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>기대수익률 (가정)</t>
         </is>
@@ -782,25 +800,22 @@
         <f>INDEX(배분규칙!$D$4:$J$23,MATCH($B$13,배분규칙!$A$4:$A$23,0),MATCH($A19,배분규칙!$D$3:$J$3,0))</f>
         <v/>
       </c>
-      <c r="C19" s="17">
-        <f>$B$9*$B19</f>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="16">
+        <f>IF($C19="",$B19,$C19)</f>
         <v/>
       </c>
-      <c r="D19" s="16">
+      <c r="E19" s="18">
+        <f>$B$9*$D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="16">
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A19,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="E19" s="16">
-        <f>IFERROR(INDEX(자산군!$E$7:$E$12,MATCH($A19,자산군!$A$7:$A$12,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="F19" s="18" t="n"/>
-      <c r="G19" s="16">
-        <f>IF(ISNUMBER($D19),$D19,0)</f>
-        <v/>
-      </c>
+      <c r="G19" s="17" t="n"/>
       <c r="H19" s="16">
-        <f>IF(ISNUMBER($E19),$E19,0)</f>
+        <f>IF(ISNUMBER($F19),$F19,0)</f>
         <v/>
       </c>
     </row>
@@ -814,25 +829,22 @@
         <f>INDEX(배분규칙!$D$4:$J$23,MATCH($B$13,배분규칙!$A$4:$A$23,0),MATCH($A20,배분규칙!$D$3:$J$3,0))</f>
         <v/>
       </c>
-      <c r="C20" s="17">
-        <f>$B$9*$B20</f>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="16">
+        <f>IF($C20="",$B20,$C20)</f>
         <v/>
       </c>
-      <c r="D20" s="16">
+      <c r="E20" s="18">
+        <f>$B$9*$D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="16">
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A20,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="E20" s="16">
-        <f>IFERROR(INDEX(자산군!$E$7:$E$12,MATCH($A20,자산군!$A$7:$A$12,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="F20" s="18" t="n"/>
-      <c r="G20" s="16">
-        <f>IF(ISNUMBER($D20),$D20,0)</f>
-        <v/>
-      </c>
+      <c r="G20" s="17" t="n"/>
       <c r="H20" s="16">
-        <f>IF(ISNUMBER($E20),$E20,0)</f>
+        <f>IF(ISNUMBER($F20),$F20,0)</f>
         <v/>
       </c>
     </row>
@@ -846,25 +858,22 @@
         <f>INDEX(배분규칙!$D$4:$J$23,MATCH($B$13,배분규칙!$A$4:$A$23,0),MATCH($A21,배분규칙!$D$3:$J$3,0))</f>
         <v/>
       </c>
-      <c r="C21" s="17">
-        <f>$B$9*$B21</f>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="16">
+        <f>IF($C21="",$B21,$C21)</f>
         <v/>
       </c>
-      <c r="D21" s="16">
+      <c r="E21" s="18">
+        <f>$B$9*$D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="16">
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A21,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="E21" s="16">
-        <f>IFERROR(INDEX(자산군!$E$7:$E$12,MATCH($A21,자산군!$A$7:$A$12,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" s="16">
-        <f>IF(ISNUMBER($D21),$D21,0)</f>
-        <v/>
-      </c>
+      <c r="G21" s="17" t="n"/>
       <c r="H21" s="16">
-        <f>IF(ISNUMBER($E21),$E21,0)</f>
+        <f>IF(ISNUMBER($F21),$F21,0)</f>
         <v/>
       </c>
     </row>
@@ -878,25 +887,22 @@
         <f>INDEX(배분규칙!$D$4:$J$23,MATCH($B$13,배분규칙!$A$4:$A$23,0),MATCH($A22,배분규칙!$D$3:$J$3,0))</f>
         <v/>
       </c>
-      <c r="C22" s="17">
-        <f>$B$9*$B22</f>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="16">
+        <f>IF($C22="",$B22,$C22)</f>
         <v/>
       </c>
-      <c r="D22" s="16">
+      <c r="E22" s="18">
+        <f>$B$9*$D22</f>
+        <v/>
+      </c>
+      <c r="F22" s="16">
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A22,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="E22" s="16">
-        <f>IFERROR(INDEX(자산군!$E$7:$E$12,MATCH($A22,자산군!$A$7:$A$12,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="16">
-        <f>IF(ISNUMBER($D22),$D22,0)</f>
-        <v/>
-      </c>
+      <c r="G22" s="17" t="n"/>
       <c r="H22" s="16">
-        <f>IF(ISNUMBER($E22),$E22,0)</f>
+        <f>IF(ISNUMBER($F22),$F22,0)</f>
         <v/>
       </c>
     </row>
@@ -910,25 +916,22 @@
         <f>INDEX(배분규칙!$D$4:$J$23,MATCH($B$13,배분규칙!$A$4:$A$23,0),MATCH($A23,배분규칙!$D$3:$J$3,0))</f>
         <v/>
       </c>
-      <c r="C23" s="17">
-        <f>$B$9*$B23</f>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="16">
+        <f>IF($C23="",$B23,$C23)</f>
         <v/>
       </c>
-      <c r="D23" s="16">
+      <c r="E23" s="18">
+        <f>$B$9*$D23</f>
+        <v/>
+      </c>
+      <c r="F23" s="16">
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A23,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="E23" s="16">
-        <f>IFERROR(INDEX(자산군!$E$7:$E$12,MATCH($A23,자산군!$A$7:$A$12,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="16">
-        <f>IF(ISNUMBER($D23),$D23,0)</f>
-        <v/>
-      </c>
+      <c r="G23" s="17" t="n"/>
       <c r="H23" s="16">
-        <f>IF(ISNUMBER($E23),$E23,0)</f>
+        <f>IF(ISNUMBER($F23),$F23,0)</f>
         <v/>
       </c>
     </row>
@@ -942,25 +945,22 @@
         <f>INDEX(배분규칙!$D$4:$J$23,MATCH($B$13,배분규칙!$A$4:$A$23,0),MATCH($A24,배분규칙!$D$3:$J$3,0))</f>
         <v/>
       </c>
-      <c r="C24" s="17">
-        <f>$B$9*$B24</f>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="16">
+        <f>IF($C24="",$B24,$C24)</f>
         <v/>
       </c>
-      <c r="D24" s="16">
+      <c r="E24" s="18">
+        <f>$B$9*$D24</f>
+        <v/>
+      </c>
+      <c r="F24" s="16">
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A24,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="E24" s="16">
-        <f>IFERROR(INDEX(자산군!$E$7:$E$12,MATCH($A24,자산군!$A$7:$A$12,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="F24" s="18" t="n"/>
-      <c r="G24" s="16">
-        <f>IF(ISNUMBER($D24),$D24,0)</f>
-        <v/>
-      </c>
+      <c r="G24" s="17" t="n"/>
       <c r="H24" s="16">
-        <f>IF(ISNUMBER($E24),$E24,0)</f>
+        <f>IF(ISNUMBER($F24),$F24,0)</f>
         <v/>
       </c>
     </row>
@@ -974,25 +974,22 @@
         <f>INDEX(배분규칙!$D$4:$J$23,MATCH($B$13,배분규칙!$A$4:$A$23,0),MATCH($A25,배분규칙!$D$3:$J$3,0))</f>
         <v/>
       </c>
-      <c r="C25" s="17">
-        <f>$B$9*$B25</f>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="16">
+        <f>IF($C25="",$B25,$C25)</f>
         <v/>
       </c>
-      <c r="D25" s="16">
+      <c r="E25" s="18">
+        <f>$B$9*$D25</f>
+        <v/>
+      </c>
+      <c r="F25" s="16">
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A25,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="E25" s="16">
-        <f>IFERROR(INDEX(자산군!$E$7:$E$12,MATCH($A25,자산군!$A$7:$A$12,0)),"—")</f>
-        <v/>
-      </c>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="16">
-        <f>IF(ISNUMBER($D25),$D25,0)</f>
-        <v/>
-      </c>
+      <c r="G25" s="17" t="n"/>
       <c r="H25" s="16">
-        <f>IF(ISNUMBER($E25),$E25,0)</f>
+        <f>IF(ISNUMBER($F25),$F25,0)</f>
         <v/>
       </c>
     </row>
@@ -1006,31 +1003,39 @@
         <f>SUM($B19:$B25)</f>
         <v/>
       </c>
-      <c r="C26" s="21">
-        <f>SUM($C19:$C25)</f>
+      <c r="C26" s="20">
+        <f>IF(COUNT($C19:$C25)=0,"—",SUM($C19:$C25))</f>
         <v/>
       </c>
       <c r="D26" s="20">
-        <f>SUMPRODUCT($B19:$B25,$G19:$G25)</f>
+        <f>SUM($D19:$D25)</f>
         <v/>
       </c>
-      <c r="E26" s="20">
-        <f>SUMPRODUCT($B19:$B25,$H19:$H25)</f>
+      <c r="E26" s="21">
+        <f>SUM($E19:$E25)</f>
         <v/>
       </c>
       <c r="F26" s="20">
-        <f>IF(COUNT($F19:$F25)=0,"가정 미입력",SUMPRODUCT($B19:$B25,$F19:$F25))</f>
+        <f>SUMPRODUCT($D19:$D25,$H19:$H25)</f>
+        <v/>
+      </c>
+      <c r="G26" s="20">
+        <f>IF(COUNT($G19:$G25)=0,"가정 미입력",SUMPRODUCT($D19:$D25,$G19:$G25))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>가정 넣은 자산군</t>
-        </is>
-      </c>
-      <c r="F27" s="22">
-        <f>COUNT($F19:$F25)&amp;" / 7"</f>
+          <t>점검</t>
+        </is>
+      </c>
+      <c r="B27" s="22">
+        <f>IF(ABS($D26-1)&gt;0.0005,"비중 합계가 100% 가 아닙니다 — 조정 비중을 맞추십시오","비중 합계 100% 입니다")</f>
+        <v/>
+      </c>
+      <c r="G27" s="23">
+        <f>COUNT($G19:$G25)&amp;" / 7 가정"</f>
         <v/>
       </c>
     </row>
@@ -1041,6 +1046,7 @@
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n"/>
       <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
@@ -1056,56 +1062,56 @@
     </row>
     <row r="31" ht="6" customHeight="1"/>
     <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>· 「기대수익률 (가정)」은 비어 있습니다. 사람이 넣는 칸이며 기본값을 두지 않았습니다 — 넣으실 때 근거를 함께 적어 두십시오.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>· 「과거 1년」을 「기대수익률」 칸에 복사해 넣지 마십시오. 「지난해처럼 오른다」고 가정하는 것이 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>· 기대수익률 합계는 빈 칸을 0 으로 셈합니다. 일부만 넣으면 그만큼 낮게 나오므로 아래 「가정 넣은 자산군」 수를 함께 보십시오.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="24" t="inlineStr">
         <is>
           <t>· 「과거 1년」은 실제로 잰 값이며 미래 수익률이 아닙니다 — 최근 1년이 그랬다는 것과 앞으로 그러리라는 것은 다른 말입니다.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="A36" s="24" t="inlineStr">
         <is>
           <t>· 변동성은 상관관계를 셈하지 않은 가중합이라 실제보다 높게 나옵니다. 낮게 보이게 만드는 것보다 안전합니다.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="23" t="inlineStr">
+      <c r="A37" s="24" t="inlineStr">
         <is>
           <t>· 펀드는 이력이 7 거래일뿐이라 변동성을 셈하지 않았습니다. 합계 변동성은 포트폴리오의 일부만 덮습니다 — 「자산군」 시트의 빈칸(—)이 그것입니다.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="23" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>· 「해외펀드」는 해외 설정 뮤추얼펀드가 아니라 해외에 투자하는 국내 설정 공모펀드입니다.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="23" t="inlineStr">
+      <c r="A39" s="24" t="inlineStr">
         <is>
           <t>· 이 자료는 참고용이며 투자 권유가 아닙니다. 제안 전 준법감시 검토를 받으십시오.</t>
         </is>
@@ -1114,20 +1120,21 @@
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-19 10:13:47 · 문서 2026-09-19 10:26 (KST)</t>
+          <t>유니버스 2026-09-19 10:13:47 · 문서 2026-09-19 10:35 (KST)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A39:F39"/>
+  <mergeCells count="9">
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A37:G37"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
@@ -1230,7 +1237,7 @@
           <t>1|1</t>
         </is>
       </c>
-      <c r="B4" s="24" t="n">
+      <c r="B4" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="15" t="inlineStr">
@@ -1238,25 +1245,25 @@
           <t>1년 이내</t>
         </is>
       </c>
-      <c r="D4" s="25" t="n">
+      <c r="D4" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="25" t="n">
+      <c r="E4" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="25" t="n">
+      <c r="F4" s="26" t="n">
         <v>0.02</v>
       </c>
-      <c r="G4" s="25" t="n">
+      <c r="G4" s="26" t="n">
         <v>0.02</v>
       </c>
-      <c r="H4" s="25" t="n">
+      <c r="H4" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="I4" s="25" t="n">
+      <c r="I4" s="26" t="n">
         <v>0.04</v>
       </c>
-      <c r="J4" s="25" t="n">
+      <c r="J4" s="26" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -1266,7 +1273,7 @@
           <t>1|3</t>
         </is>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -1274,25 +1281,25 @@
           <t>3년</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="F5" s="26" t="n">
         <v>0.035</v>
       </c>
-      <c r="G5" s="25" t="n">
+      <c r="G5" s="26" t="n">
         <v>0.035</v>
       </c>
-      <c r="H5" s="25" t="n">
+      <c r="H5" s="26" t="n">
         <v>0.14</v>
       </c>
-      <c r="I5" s="25" t="n">
+      <c r="I5" s="26" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="J5" s="25" t="n">
+      <c r="J5" s="26" t="n">
         <v>0.72</v>
       </c>
     </row>
@@ -1302,7 +1309,7 @@
           <t>1|5</t>
         </is>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -1310,25 +1317,25 @@
           <t>5년</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="25" t="n">
+      <c r="E6" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="26" t="n">
         <v>0.045</v>
       </c>
-      <c r="G6" s="25" t="n">
+      <c r="G6" s="26" t="n">
         <v>0.045</v>
       </c>
-      <c r="H6" s="25" t="n">
+      <c r="H6" s="26" t="n">
         <v>0.18</v>
       </c>
-      <c r="I6" s="25" t="n">
+      <c r="I6" s="26" t="n">
         <v>0.09</v>
       </c>
-      <c r="J6" s="25" t="n">
+      <c r="J6" s="26" t="n">
         <v>0.64</v>
       </c>
     </row>
@@ -1338,7 +1345,7 @@
           <t>1|10</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -1346,25 +1353,25 @@
           <t>5년 초과</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="H7" s="25" t="n">
+      <c r="H7" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="I7" s="25" t="n">
+      <c r="I7" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="J7" s="25" t="n">
+      <c r="J7" s="26" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -1374,7 +1381,7 @@
           <t>2|1</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="25" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -1382,25 +1389,25 @@
           <t>1년 이내</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>0.02</v>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="26" t="n">
         <v>0.04</v>
       </c>
-      <c r="G8" s="25" t="n">
+      <c r="G8" s="26" t="n">
         <v>0.04</v>
       </c>
-      <c r="H8" s="25" t="n">
+      <c r="H8" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="I8" s="25" t="n">
+      <c r="I8" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="J8" s="25" t="n">
+      <c r="J8" s="26" t="n">
         <v>0.74</v>
       </c>
     </row>
@@ -1410,7 +1417,7 @@
           <t>2|3</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="25" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="15" t="inlineStr">
@@ -1418,25 +1425,25 @@
           <t>3년</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="25" t="n">
+      <c r="E9" s="26" t="n">
         <v>0.035</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="26" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G9" s="25" t="n">
+      <c r="G9" s="26" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H9" s="25" t="n">
+      <c r="H9" s="26" t="n">
         <v>0.175</v>
       </c>
-      <c r="I9" s="25" t="n">
+      <c r="I9" s="26" t="n">
         <v>0.105</v>
       </c>
-      <c r="J9" s="25" t="n">
+      <c r="J9" s="26" t="n">
         <v>0.545</v>
       </c>
     </row>
@@ -1446,7 +1453,7 @@
           <t>2|5</t>
         </is>
       </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="25" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="15" t="inlineStr">
@@ -1454,25 +1461,25 @@
           <t>5년</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <v>0.045</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="26" t="n">
         <v>0.09</v>
       </c>
-      <c r="G10" s="25" t="n">
+      <c r="G10" s="26" t="n">
         <v>0.09</v>
       </c>
-      <c r="H10" s="25" t="n">
+      <c r="H10" s="26" t="n">
         <v>0.225</v>
       </c>
-      <c r="I10" s="25" t="n">
+      <c r="I10" s="26" t="n">
         <v>0.135</v>
       </c>
-      <c r="J10" s="25" t="n">
+      <c r="J10" s="26" t="n">
         <v>0.415</v>
       </c>
     </row>
@@ -1482,7 +1489,7 @@
           <t>2|10</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="25" t="n">
         <v>2</v>
       </c>
       <c r="C11" s="15" t="inlineStr">
@@ -1490,25 +1497,25 @@
           <t>5년 초과</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="G11" s="25" t="n">
+      <c r="G11" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="H11" s="25" t="n">
+      <c r="H11" s="26" t="n">
         <v>0.25</v>
       </c>
-      <c r="I11" s="25" t="n">
+      <c r="I11" s="26" t="n">
         <v>0.15</v>
       </c>
-      <c r="J11" s="25" t="n">
+      <c r="J11" s="26" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -1518,7 +1525,7 @@
           <t>3|1</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="25" t="n">
         <v>3</v>
       </c>
       <c r="C12" s="15" t="inlineStr">
@@ -1526,25 +1533,25 @@
           <t>1년 이내</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="26" t="n">
         <v>0.02</v>
       </c>
-      <c r="E12" s="25" t="n">
+      <c r="E12" s="26" t="n">
         <v>0.04</v>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F12" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="G12" s="25" t="n">
+      <c r="G12" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="H12" s="25" t="n">
+      <c r="H12" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="I12" s="25" t="n">
+      <c r="I12" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="J12" s="25" t="n">
+      <c r="J12" s="26" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1554,7 +1561,7 @@
           <t>3|3</t>
         </is>
       </c>
-      <c r="B13" s="24" t="n">
+      <c r="B13" s="25" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -1562,25 +1569,25 @@
           <t>3년</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="26" t="n">
         <v>0.035</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="26" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="26" t="n">
         <v>0.105</v>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G13" s="26" t="n">
         <v>0.105</v>
       </c>
-      <c r="H13" s="25" t="n">
+      <c r="H13" s="26" t="n">
         <v>0.14</v>
       </c>
-      <c r="I13" s="25" t="n">
+      <c r="I13" s="26" t="n">
         <v>0.14</v>
       </c>
-      <c r="J13" s="25" t="n">
+      <c r="J13" s="26" t="n">
         <v>0.405</v>
       </c>
     </row>
@@ -1590,7 +1597,7 @@
           <t>3|5</t>
         </is>
       </c>
-      <c r="B14" s="24" t="n">
+      <c r="B14" s="25" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -1598,25 +1605,25 @@
           <t>5년</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="26" t="n">
         <v>0.045</v>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="E14" s="26" t="n">
         <v>0.09</v>
       </c>
-      <c r="F14" s="25" t="n">
+      <c r="F14" s="26" t="n">
         <v>0.135</v>
       </c>
-      <c r="G14" s="25" t="n">
+      <c r="G14" s="26" t="n">
         <v>0.135</v>
       </c>
-      <c r="H14" s="25" t="n">
+      <c r="H14" s="26" t="n">
         <v>0.18</v>
       </c>
-      <c r="I14" s="25" t="n">
+      <c r="I14" s="26" t="n">
         <v>0.18</v>
       </c>
-      <c r="J14" s="25" t="n">
+      <c r="J14" s="26" t="n">
         <v>0.235</v>
       </c>
     </row>
@@ -1626,7 +1633,7 @@
           <t>3|10</t>
         </is>
       </c>
-      <c r="B15" s="24" t="n">
+      <c r="B15" s="25" t="n">
         <v>3</v>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -1634,25 +1641,25 @@
           <t>5년 초과</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="E15" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="F15" s="25" t="n">
+      <c r="F15" s="26" t="n">
         <v>0.15</v>
       </c>
-      <c r="G15" s="25" t="n">
+      <c r="G15" s="26" t="n">
         <v>0.15</v>
       </c>
-      <c r="H15" s="25" t="n">
+      <c r="H15" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="I15" s="25" t="n">
+      <c r="I15" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="J15" s="25" t="n">
+      <c r="J15" s="26" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -1662,7 +1669,7 @@
           <t>4|1</t>
         </is>
       </c>
-      <c r="B16" s="24" t="n">
+      <c r="B16" s="25" t="n">
         <v>4</v>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -1670,25 +1677,25 @@
           <t>1년 이내</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="E16" s="25" t="n">
+      <c r="E16" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="F16" s="25" t="n">
+      <c r="F16" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="G16" s="25" t="n">
+      <c r="G16" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="H16" s="25" t="n">
+      <c r="H16" s="26" t="n">
         <v>0.04</v>
       </c>
-      <c r="I16" s="25" t="n">
+      <c r="I16" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="J16" s="25" t="n">
+      <c r="J16" s="26" t="n">
         <v>0.62</v>
       </c>
     </row>
@@ -1698,7 +1705,7 @@
           <t>4|3</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n">
+      <c r="B17" s="25" t="n">
         <v>4</v>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -1706,25 +1713,25 @@
           <t>3년</t>
         </is>
       </c>
-      <c r="D17" s="25" t="n">
+      <c r="D17" s="26" t="n">
         <v>0.105</v>
       </c>
-      <c r="E17" s="25" t="n">
+      <c r="E17" s="26" t="n">
         <v>0.14</v>
       </c>
-      <c r="F17" s="25" t="n">
+      <c r="F17" s="26" t="n">
         <v>0.105</v>
       </c>
-      <c r="G17" s="25" t="n">
+      <c r="G17" s="26" t="n">
         <v>0.14</v>
       </c>
-      <c r="H17" s="25" t="n">
+      <c r="H17" s="26" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I17" s="25" t="n">
+      <c r="I17" s="26" t="n">
         <v>0.105</v>
       </c>
-      <c r="J17" s="25" t="n">
+      <c r="J17" s="26" t="n">
         <v>0.335</v>
       </c>
     </row>
@@ -1734,7 +1741,7 @@
           <t>4|5</t>
         </is>
       </c>
-      <c r="B18" s="24" t="n">
+      <c r="B18" s="25" t="n">
         <v>4</v>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -1742,25 +1749,25 @@
           <t>5년</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n">
+      <c r="D18" s="26" t="n">
         <v>0.135</v>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="E18" s="26" t="n">
         <v>0.18</v>
       </c>
-      <c r="F18" s="25" t="n">
+      <c r="F18" s="26" t="n">
         <v>0.135</v>
       </c>
-      <c r="G18" s="25" t="n">
+      <c r="G18" s="26" t="n">
         <v>0.18</v>
       </c>
-      <c r="H18" s="25" t="n">
+      <c r="H18" s="26" t="n">
         <v>0.09</v>
       </c>
-      <c r="I18" s="25" t="n">
+      <c r="I18" s="26" t="n">
         <v>0.135</v>
       </c>
-      <c r="J18" s="25" t="n">
+      <c r="J18" s="26" t="n">
         <v>0.145</v>
       </c>
     </row>
@@ -1770,7 +1777,7 @@
           <t>4|10</t>
         </is>
       </c>
-      <c r="B19" s="24" t="n">
+      <c r="B19" s="25" t="n">
         <v>4</v>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -1778,25 +1785,25 @@
           <t>5년 초과</t>
         </is>
       </c>
-      <c r="D19" s="25" t="n">
+      <c r="D19" s="26" t="n">
         <v>0.15</v>
       </c>
-      <c r="E19" s="25" t="n">
+      <c r="E19" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="F19" s="25" t="n">
+      <c r="F19" s="26" t="n">
         <v>0.15</v>
       </c>
-      <c r="G19" s="25" t="n">
+      <c r="G19" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="H19" s="25" t="n">
+      <c r="H19" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="I19" s="25" t="n">
+      <c r="I19" s="26" t="n">
         <v>0.15</v>
       </c>
-      <c r="J19" s="25" t="n">
+      <c r="J19" s="26" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -1806,7 +1813,7 @@
           <t>5|1</t>
         </is>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="25" t="n">
         <v>5</v>
       </c>
       <c r="C20" s="15" t="inlineStr">
@@ -1814,25 +1821,25 @@
           <t>1년 이내</t>
         </is>
       </c>
-      <c r="D20" s="25" t="n">
+      <c r="D20" s="26" t="n">
         <v>0.1</v>
       </c>
-      <c r="E20" s="25" t="n">
+      <c r="E20" s="26" t="n">
         <v>0.12</v>
       </c>
-      <c r="F20" s="25" t="n">
+      <c r="F20" s="26" t="n">
         <v>0.06</v>
       </c>
-      <c r="G20" s="25" t="n">
+      <c r="G20" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="H20" s="25" t="n">
+      <c r="H20" s="26" t="n">
         <v>0.02</v>
       </c>
-      <c r="I20" s="25" t="n">
+      <c r="I20" s="26" t="n">
         <v>0.02</v>
       </c>
-      <c r="J20" s="25" t="n">
+      <c r="J20" s="26" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -1842,7 +1849,7 @@
           <t>5|3</t>
         </is>
       </c>
-      <c r="B21" s="24" t="n">
+      <c r="B21" s="25" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="15" t="inlineStr">
@@ -1850,25 +1857,25 @@
           <t>3년</t>
         </is>
       </c>
-      <c r="D21" s="25" t="n">
+      <c r="D21" s="26" t="n">
         <v>0.175</v>
       </c>
-      <c r="E21" s="25" t="n">
+      <c r="E21" s="26" t="n">
         <v>0.21</v>
       </c>
-      <c r="F21" s="25" t="n">
+      <c r="F21" s="26" t="n">
         <v>0.105</v>
       </c>
-      <c r="G21" s="25" t="n">
+      <c r="G21" s="26" t="n">
         <v>0.14</v>
       </c>
-      <c r="H21" s="25" t="n">
+      <c r="H21" s="26" t="n">
         <v>0.035</v>
       </c>
-      <c r="I21" s="25" t="n">
+      <c r="I21" s="26" t="n">
         <v>0.035</v>
       </c>
-      <c r="J21" s="25" t="n">
+      <c r="J21" s="26" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -1878,7 +1885,7 @@
           <t>5|5</t>
         </is>
       </c>
-      <c r="B22" s="24" t="n">
+      <c r="B22" s="25" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="15" t="inlineStr">
@@ -1886,25 +1893,25 @@
           <t>5년</t>
         </is>
       </c>
-      <c r="D22" s="25" t="n">
+      <c r="D22" s="26" t="n">
         <v>0.225</v>
       </c>
-      <c r="E22" s="25" t="n">
+      <c r="E22" s="26" t="n">
         <v>0.27</v>
       </c>
-      <c r="F22" s="25" t="n">
+      <c r="F22" s="26" t="n">
         <v>0.135</v>
       </c>
-      <c r="G22" s="25" t="n">
+      <c r="G22" s="26" t="n">
         <v>0.18</v>
       </c>
-      <c r="H22" s="25" t="n">
+      <c r="H22" s="26" t="n">
         <v>0.045</v>
       </c>
-      <c r="I22" s="25" t="n">
+      <c r="I22" s="26" t="n">
         <v>0.045</v>
       </c>
-      <c r="J22" s="25" t="n">
+      <c r="J22" s="26" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -1914,7 +1921,7 @@
           <t>5|10</t>
         </is>
       </c>
-      <c r="B23" s="24" t="n">
+      <c r="B23" s="25" t="n">
         <v>5</v>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -1922,25 +1929,25 @@
           <t>5년 초과</t>
         </is>
       </c>
-      <c r="D23" s="25" t="n">
+      <c r="D23" s="26" t="n">
         <v>0.25</v>
       </c>
-      <c r="E23" s="25" t="n">
+      <c r="E23" s="26" t="n">
         <v>0.3</v>
       </c>
-      <c r="F23" s="25" t="n">
+      <c r="F23" s="26" t="n">
         <v>0.15</v>
       </c>
-      <c r="G23" s="25" t="n">
+      <c r="G23" s="26" t="n">
         <v>0.2</v>
       </c>
-      <c r="H23" s="25" t="n">
+      <c r="H23" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="I23" s="25" t="n">
+      <c r="I23" s="26" t="n">
         <v>0.05</v>
       </c>
-      <c r="J23" s="25" t="n">
+      <c r="J23" s="26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1990,7 +1997,7 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>아래는 원천에서 실제로 잰 값입니다. 미래 수익률이 아닙니다. 빈칸(—)은 원천에 없어 셈하지 않은 것이며 만들어 넣지 않습니다.</t>
         </is>
@@ -2034,19 +2041,19 @@
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B7" s="24" t="n">
+      <c r="B7" s="25" t="n">
         <v>247</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="25" t="n">
         <v>66</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="26" t="n">
         <v>0.2124918732311036</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="26" t="n">
         <v>0.1636</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="26" t="n">
         <v>-0.3638325865485312</v>
       </c>
     </row>
@@ -2056,19 +2063,19 @@
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B8" s="24" t="n">
+      <c r="B8" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="26" t="n">
         <v>0.3582644698360878</v>
       </c>
-      <c r="E8" s="25" t="n">
+      <c r="E8" s="26" t="n">
         <v>0.5728460950188951</v>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="26" t="n">
         <v>-0.4675840087252487</v>
       </c>
     </row>
@@ -2078,21 +2085,21 @@
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="25" t="n">
         <v>615</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="25" t="n">
         <v>606</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="26" t="n">
         <v>0.206671</v>
       </c>
-      <c r="E9" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="24" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2104,19 +2111,19 @@
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="26" t="n">
         <v>0.1680824723535977</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="E10" s="26" t="n">
         <v>0.1542903388794394</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="26" t="n">
         <v>-0.1653518460082045</v>
       </c>
     </row>
@@ -2126,19 +2133,19 @@
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B11" s="24" t="n">
+      <c r="B11" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="C11" s="24" t="n">
+      <c r="C11" s="25" t="n">
         <v>99</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="26" t="n">
         <v>0.1051235812029279</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="E11" s="26" t="n">
         <v>0.2914505456297338</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="26" t="n">
         <v>-0.3235610824922673</v>
       </c>
     </row>
@@ -2148,28 +2155,28 @@
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B12" s="24" t="n">
+      <c r="B12" s="25" t="n">
         <v>436</v>
       </c>
-      <c r="C12" s="24" t="n">
+      <c r="C12" s="25" t="n">
         <v>436</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="26" t="n">
         <v>0.116974</v>
       </c>
-      <c r="E12" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="24" t="inlineStr">
+      <c r="E12" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>펀드는 기준가 이력이 7 거래일뿐이라 변동성·최대낙폭을 셈하지 않고 원천의 위험등급을 씁니다.</t>
         </is>
@@ -2192,17 +2199,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:I150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="4" customHeight="1">
@@ -2229,2915 +2237,3070 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>규모와 보수로 고릅니다. 수익률 순으로 고르지 않습니다 — 지난해 제일 많이 오른 것을 권하는 습관이 고객에게 가장 비쌉니다. 개별 주식은 시가총액 상위 종목이며 종목 추천이 아닙니다.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>채택</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>자산군</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>상품</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>유형</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>운용/발행</t>
         </is>
       </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>규모</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="G6" s="13" t="inlineStr">
         <is>
           <t>과거 1년</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="H6" s="13" t="inlineStr">
         <is>
           <t>변동성</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr">
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>보수</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="C7" s="15" t="inlineStr">
         <is>
           <t>삼성전자</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t>반도체</t>
         </is>
       </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="24" t="inlineStr">
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
         <is>
           <t>1,714조원</t>
         </is>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="G7" s="26" t="n">
         <v>2.723252496433667</v>
       </c>
-      <c r="G7" s="25" t="n">
-        <v>0.5788558858127696</v>
-      </c>
-      <c r="H7" s="24" t="inlineStr">
+      <c r="H7" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>반도체</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E8" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="28" t="inlineStr">
+        <is>
           <t>1,318조원</t>
         </is>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="G8" s="29" t="n">
         <v>5.994350282485875</v>
       </c>
-      <c r="G8" s="28" t="n">
-        <v>0.7344693583081116</v>
-      </c>
-      <c r="H8" s="27" t="inlineStr">
+      <c r="H8" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>SK스퀘어</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>지주</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
         <is>
           <t>142조원</t>
         </is>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="G9" s="26" t="n">
         <v>6.222222222222223</v>
       </c>
-      <c r="G9" s="25" t="n">
-        <v>0.807823901299951</v>
-      </c>
-      <c r="H9" s="24" t="inlineStr">
+      <c r="H9" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="C10" s="27" t="inlineStr">
         <is>
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="D10" s="27" t="inlineStr">
         <is>
           <t>전기전자</t>
         </is>
       </c>
-      <c r="D10" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E10" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="28" t="inlineStr">
+        <is>
           <t>105조원</t>
         </is>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="G10" s="29" t="n">
         <v>6.780269058295964</v>
       </c>
-      <c r="G10" s="28" t="n">
-        <v>0.7112829041110764</v>
-      </c>
-      <c r="H10" s="27" t="inlineStr">
+      <c r="H10" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>현대차</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>자동차</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="25" t="inlineStr">
         <is>
           <t>96조원</t>
         </is>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="G11" s="26" t="n">
         <v>0.6478555304740405</v>
       </c>
-      <c r="G11" s="25" t="n">
-        <v>0.534218514069132</v>
-      </c>
-      <c r="H11" s="24" t="inlineStr">
+      <c r="H11" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="C12" s="26" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>2차전지</t>
         </is>
       </c>
-      <c r="D12" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
+        <is>
           <t>85조원</t>
         </is>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="G12" s="29" t="n">
         <v>0.03703703703703698</v>
       </c>
-      <c r="G12" s="28" t="n">
-        <v>0.5445115864144184</v>
-      </c>
-      <c r="H12" s="27" t="inlineStr">
+      <c r="H12" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>삼성바이오로직스</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>바이오</t>
         </is>
       </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="25" t="inlineStr">
         <is>
           <t>65조원</t>
         </is>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="G13" s="26" t="n">
         <v>-0.1059517520915485</v>
       </c>
-      <c r="G13" s="25" t="n">
-        <v>0.3670791519676143</v>
-      </c>
-      <c r="H13" s="24" t="inlineStr">
+      <c r="H13" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>KB금융</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E14" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="28" t="inlineStr">
+        <is>
           <t>61조원</t>
         </is>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="G14" s="29" t="n">
         <v>0.6119815668202766</v>
       </c>
-      <c r="G14" s="28" t="n">
-        <v>0.3947671146039806</v>
-      </c>
-      <c r="H14" s="27" t="inlineStr">
+      <c r="H14" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>삼성물산</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>지주</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="25" t="inlineStr">
         <is>
           <t>57조원</t>
         </is>
       </c>
-      <c r="F15" s="25" t="n">
+      <c r="G15" s="26" t="n">
         <v>1.013769363166953</v>
       </c>
-      <c r="G15" s="25" t="n">
-        <v>0.5874947216024574</v>
-      </c>
-      <c r="H15" s="24" t="inlineStr">
+      <c r="H15" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>중공업</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E16" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="28" t="inlineStr">
+        <is>
           <t>55조원</t>
         </is>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="G16" s="29" t="n">
         <v>0.1578947368421053</v>
       </c>
-      <c r="G16" s="28" t="n">
-        <v>0.6442375445757537</v>
-      </c>
-      <c r="H16" s="27" t="inlineStr">
+      <c r="H16" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>두산에너빌리티</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>중공업</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
         <is>
           <t>54조원</t>
         </is>
       </c>
-      <c r="F17" s="25" t="n">
+      <c r="G17" s="26" t="n">
         <v>0.3519108280254777</v>
       </c>
-      <c r="G17" s="25" t="n">
-        <v>0.6406934339128944</v>
-      </c>
-      <c r="H17" s="24" t="inlineStr">
+      <c r="H17" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>신한지주</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E18" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="28" t="inlineStr">
+        <is>
           <t>52조원</t>
         </is>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="G18" s="29" t="n">
         <v>0.7069767441860466</v>
       </c>
-      <c r="G18" s="28" t="n">
-        <v>0.3566358597165926</v>
-      </c>
-      <c r="H18" s="27" t="inlineStr">
+      <c r="H18" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="C19" s="15" t="inlineStr">
         <is>
           <t>삼성생명</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="D19" s="15" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="inlineStr">
+      <c r="E19" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="25" t="inlineStr">
         <is>
           <t>51조원</t>
         </is>
       </c>
-      <c r="F19" s="25" t="n">
+      <c r="G19" s="26" t="n">
         <v>0.9026845637583893</v>
       </c>
-      <c r="G19" s="25" t="n">
-        <v>0.5708742695725796</v>
-      </c>
-      <c r="H19" s="24" t="inlineStr">
+      <c r="H19" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="26" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>중공업</t>
         </is>
       </c>
-      <c r="D20" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E20" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
           <t>48조원</t>
         </is>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="G20" s="29" t="n">
         <v>-0.09803921568627449</v>
       </c>
-      <c r="G20" s="28" t="n">
-        <v>0.5776129250813562</v>
-      </c>
-      <c r="H20" s="27" t="inlineStr">
+      <c r="H20" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="C21" s="15" t="inlineStr">
         <is>
           <t>기아</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>자동차</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="25" t="inlineStr">
         <is>
           <t>47조원</t>
         </is>
       </c>
-      <c r="F21" s="25" t="n">
+      <c r="G21" s="26" t="n">
         <v>0.139252336448598</v>
       </c>
-      <c r="G21" s="25" t="n">
-        <v>0.4615148393621581</v>
-      </c>
-      <c r="H21" s="24" t="inlineStr">
+      <c r="H21" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="C22" s="27" t="inlineStr">
         <is>
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="D22" s="27" t="inlineStr">
         <is>
           <t>2차전지</t>
         </is>
       </c>
-      <c r="D22" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E22" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="28" t="inlineStr">
+        <is>
           <t>43조원</t>
         </is>
       </c>
-      <c r="F22" s="28" t="n">
+      <c r="G22" s="29" t="n">
         <v>1.671604938271605</v>
       </c>
-      <c r="G22" s="28" t="n">
-        <v>0.621458113193839</v>
-      </c>
-      <c r="H22" s="27" t="inlineStr">
+      <c r="H22" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>바이오</t>
         </is>
       </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="25" t="inlineStr">
         <is>
           <t>41조원</t>
         </is>
       </c>
-      <c r="F23" s="25" t="n">
+      <c r="G23" s="26" t="n">
         <v>0.10675678198717</v>
       </c>
-      <c r="G23" s="25" t="n">
-        <v>0.3624530149032757</v>
-      </c>
-      <c r="H23" s="24" t="inlineStr">
+      <c r="H23" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="C24" s="27" t="inlineStr">
         <is>
           <t>LG전자</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="D24" s="27" t="inlineStr">
         <is>
           <t>전기전자</t>
         </is>
       </c>
-      <c r="D24" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E24" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="inlineStr">
+        <is>
           <t>36조원</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n">
+      <c r="G24" s="29" t="n">
         <v>1.634794156706507</v>
       </c>
-      <c r="G24" s="28" t="n">
-        <v>0.65254620977482</v>
-      </c>
-      <c r="H24" s="27" t="inlineStr">
+      <c r="H24" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
         <is>
           <t>하나금융지주</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="24" t="inlineStr">
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="25" t="inlineStr">
         <is>
           <t>36조원</t>
         </is>
       </c>
-      <c r="F25" s="25" t="n">
+      <c r="G25" s="26" t="n">
         <v>0.6311274509803921</v>
       </c>
-      <c r="G25" s="25" t="n">
-        <v>0.3725099313235966</v>
-      </c>
-      <c r="H25" s="24" t="inlineStr">
+      <c r="H25" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="C26" s="27" t="inlineStr">
         <is>
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
+      <c r="D26" s="27" t="inlineStr">
         <is>
           <t>자동차</t>
         </is>
       </c>
-      <c r="D26" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E26" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="28" t="inlineStr">
+        <is>
           <t>34조원</t>
         </is>
       </c>
-      <c r="F26" s="28" t="n">
+      <c r="G26" s="29" t="n">
         <v>0.1825273010920437</v>
       </c>
-      <c r="G26" s="28" t="n">
-        <v>0.5377178434190411</v>
-      </c>
-      <c r="H26" s="27" t="inlineStr">
+      <c r="H26" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="C27" s="15" t="inlineStr">
         <is>
           <t>LS일렉트릭</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="D27" s="15" t="inlineStr">
         <is>
           <t>중공업</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="25" t="inlineStr">
         <is>
           <t>31조원</t>
         </is>
       </c>
-      <c r="F27" s="25" t="n">
+      <c r="G27" s="26" t="n">
         <v>2.634020618556701</v>
       </c>
-      <c r="G27" s="25" t="n">
-        <v>0.7659029967676354</v>
-      </c>
-      <c r="H27" s="24" t="inlineStr">
+      <c r="H27" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="C28" s="27" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="D28" s="27" t="inlineStr">
         <is>
           <t>지주</t>
         </is>
       </c>
-      <c r="D28" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E28" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="28" t="inlineStr">
+        <is>
           <t>30조원</t>
         </is>
       </c>
-      <c r="F28" s="28" t="n">
+      <c r="G28" s="29" t="n">
         <v>1.665036674816626</v>
       </c>
-      <c r="G28" s="28" t="n">
-        <v>0.5952380909083713</v>
-      </c>
-      <c r="H28" s="27" t="inlineStr">
+      <c r="H28" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="C29" s="15" t="inlineStr">
         <is>
           <t>NAVER</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="D29" s="15" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E29" s="24" t="inlineStr">
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="25" t="inlineStr">
         <is>
           <t>30조원</t>
         </is>
       </c>
-      <c r="F29" s="25" t="n">
+      <c r="G29" s="26" t="n">
         <v>-0.1290748898678414</v>
       </c>
-      <c r="G29" s="25" t="n">
-        <v>0.4863572524093532</v>
-      </c>
-      <c r="H29" s="24" t="inlineStr">
+      <c r="H29" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="C30" s="27" t="inlineStr">
         <is>
           <t>삼성화재</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
+      <c r="D30" s="27" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D30" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E30" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="28" t="inlineStr">
+        <is>
           <t>29조원</t>
         </is>
       </c>
-      <c r="F30" s="28" t="n">
+      <c r="G30" s="29" t="n">
         <v>0.4304635761589404</v>
       </c>
-      <c r="G30" s="28" t="n">
-        <v>0.5292424615185901</v>
-      </c>
-      <c r="H30" s="27" t="inlineStr">
+      <c r="H30" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr">
         <is>
           <t>효성중공업</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>중공업</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="25" t="inlineStr">
         <is>
           <t>27조원</t>
         </is>
       </c>
-      <c r="F31" s="25" t="n">
+      <c r="G31" s="26" t="n">
         <v>1.411083540115798</v>
       </c>
-      <c r="G31" s="25" t="n">
-        <v>0.6904310161419625</v>
-      </c>
-      <c r="H31" s="24" t="inlineStr">
+      <c r="H31" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="26" t="inlineStr">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="C32" s="27" t="inlineStr">
         <is>
           <t>엔비디아</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
+      <c r="D32" s="27" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D32" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E32" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="28" t="inlineStr">
+        <is>
           <t>7,326조원</t>
         </is>
       </c>
-      <c r="F32" s="28" t="n">
+      <c r="G32" s="29" t="n">
         <v>0.2033755274261604</v>
       </c>
-      <c r="G32" s="28" t="n">
-        <v>0.4435857523813961</v>
-      </c>
-      <c r="H32" s="27" t="inlineStr">
+      <c r="H32" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="C33" s="15" t="inlineStr">
         <is>
           <t>애플</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="D33" s="15" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D33" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="24" t="inlineStr">
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F33" s="25" t="inlineStr">
         <is>
           <t>6,803조원</t>
         </is>
       </c>
-      <c r="F33" s="25" t="n">
+      <c r="G33" s="26" t="n">
         <v>0.4043514997887623</v>
       </c>
-      <c r="G33" s="25" t="n">
-        <v>0.2880986490353247</v>
-      </c>
-      <c r="H33" s="24" t="inlineStr">
+      <c r="H33" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="26" t="inlineStr">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B34" s="27" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="C34" s="27" t="inlineStr">
         <is>
           <t>알파벳(구글)</t>
         </is>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="D34" s="27" t="inlineStr">
         <is>
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D34" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E34" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="28" t="inlineStr">
+        <is>
           <t>5,875조원</t>
         </is>
       </c>
-      <c r="F34" s="28" t="n">
+      <c r="G34" s="29" t="n">
         <v>0.3627041850482891</v>
       </c>
-      <c r="G34" s="28" t="n">
-        <v>0.316769111978901</v>
-      </c>
-      <c r="H34" s="27" t="inlineStr">
+      <c r="H34" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="C35" s="15" t="inlineStr">
         <is>
           <t>마이크로소프트</t>
         </is>
       </c>
-      <c r="C35" s="15" t="inlineStr">
+      <c r="D35" s="15" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="24" t="inlineStr">
+      <c r="E35" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="25" t="inlineStr">
         <is>
           <t>5,112조원</t>
         </is>
       </c>
-      <c r="F35" s="25" t="n">
+      <c r="G35" s="26" t="n">
         <v>-0.04862620304253341</v>
       </c>
-      <c r="G35" s="25" t="n">
-        <v>0.2867568717074502</v>
-      </c>
-      <c r="H35" s="24" t="inlineStr">
+      <c r="H35" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="26" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="C36" s="27" t="inlineStr">
         <is>
           <t>아마존</t>
         </is>
       </c>
-      <c r="C36" s="26" t="inlineStr">
+      <c r="D36" s="27" t="inlineStr">
         <is>
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D36" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E36" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="28" t="inlineStr">
+        <is>
           <t>3,748조원</t>
         </is>
       </c>
-      <c r="F36" s="28" t="n">
+      <c r="G36" s="29" t="n">
         <v>0.06278356306442556</v>
       </c>
-      <c r="G36" s="28" t="n">
-        <v>0.3371178200401745</v>
-      </c>
-      <c r="H36" s="27" t="inlineStr">
+      <c r="H36" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="C37" s="15" t="inlineStr">
         <is>
           <t>TSMC</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="24" t="inlineStr">
+      <c r="E37" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" s="25" t="inlineStr">
         <is>
           <t>3,087조원</t>
         </is>
       </c>
-      <c r="F37" s="25" t="n">
+      <c r="G37" s="26" t="n">
         <v>0.5981329864565001</v>
       </c>
-      <c r="G37" s="25" t="n">
-        <v>0.4135555401445912</v>
-      </c>
-      <c r="H37" s="24" t="inlineStr">
+      <c r="H37" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="26" t="inlineStr">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B38" s="27" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B38" s="26" t="inlineStr">
+      <c r="C38" s="27" t="inlineStr">
         <is>
           <t>스페이스X</t>
         </is>
       </c>
-      <c r="C38" s="26" t="inlineStr">
+      <c r="D38" s="27" t="inlineStr">
         <is>
           <t>산업재</t>
         </is>
       </c>
-      <c r="D38" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E38" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="28" t="inlineStr">
+        <is>
           <t>2,823조원</t>
         </is>
       </c>
-      <c r="F38" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G38" s="28" t="n">
-        <v>0.914155978359349</v>
-      </c>
-      <c r="H38" s="27" t="inlineStr">
+      <c r="G38" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="C39" s="15" t="inlineStr">
         <is>
           <t>메타 플랫폼스</t>
         </is>
       </c>
-      <c r="C39" s="15" t="inlineStr">
+      <c r="D39" s="15" t="inlineStr">
         <is>
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="24" t="inlineStr">
+      <c r="E39" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F39" s="25" t="inlineStr">
         <is>
           <t>2,404조원</t>
         </is>
       </c>
-      <c r="F39" s="25" t="n">
+      <c r="G39" s="26" t="n">
         <v>-0.1195109193147641</v>
       </c>
-      <c r="G39" s="25" t="n">
-        <v>0.3795290483288599</v>
-      </c>
-      <c r="H39" s="24" t="inlineStr">
+      <c r="H39" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="26" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B40" s="27" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B40" s="26" t="inlineStr">
+      <c r="C40" s="27" t="inlineStr">
         <is>
           <t>브로드컴</t>
         </is>
       </c>
-      <c r="C40" s="26" t="inlineStr">
+      <c r="D40" s="27" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D40" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E40" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="28" t="inlineStr">
+        <is>
           <t>2,293조원</t>
         </is>
       </c>
-      <c r="F40" s="28" t="n">
+      <c r="G40" s="29" t="n">
         <v>-0.06751078030157376</v>
       </c>
-      <c r="G40" s="28" t="n">
-        <v>0.5169950668623775</v>
-      </c>
-      <c r="H40" s="27" t="inlineStr">
+      <c r="H40" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="C41" s="15" t="inlineStr">
         <is>
           <t>테슬라</t>
         </is>
       </c>
-      <c r="C41" s="15" t="inlineStr">
+      <c r="D41" s="15" t="inlineStr">
         <is>
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="24" t="inlineStr">
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="25" t="inlineStr">
         <is>
           <t>2,001조원</t>
         </is>
       </c>
-      <c r="F41" s="25" t="n">
+      <c r="G41" s="26" t="n">
         <v>-0.1267193444541996</v>
       </c>
-      <c r="G41" s="25" t="n">
-        <v>0.5963648463773891</v>
-      </c>
-      <c r="H41" s="24" t="inlineStr">
+      <c r="H41" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="26" t="inlineStr">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B42" s="27" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B42" s="26" t="inlineStr">
+      <c r="C42" s="27" t="inlineStr">
         <is>
           <t>마이크론</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
+      <c r="D42" s="27" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D42" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E42" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="28" t="inlineStr">
+        <is>
           <t>1,527조원</t>
         </is>
       </c>
-      <c r="F42" s="28" t="n">
+      <c r="G42" s="29" t="n">
         <v>4.872789503707929</v>
       </c>
-      <c r="G42" s="28" t="n">
-        <v>0.7172278197761155</v>
-      </c>
-      <c r="H42" s="27" t="inlineStr">
+      <c r="H42" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="C43" s="15" t="inlineStr">
         <is>
           <t>버크셔 해서웨이 B</t>
         </is>
       </c>
-      <c r="C43" s="15" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="24" t="inlineStr">
+      <c r="E43" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="25" t="inlineStr">
         <is>
           <t>1,508조원</t>
         </is>
       </c>
-      <c r="F43" s="25" t="n">
+      <c r="G43" s="26" t="n">
         <v>0.05749277780038242</v>
       </c>
-      <c r="G43" s="25" t="n">
-        <v>0.1710229899533426</v>
-      </c>
-      <c r="H43" s="24" t="inlineStr">
+      <c r="H43" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="26" t="inlineStr">
+      <c r="A44" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B44" s="26" t="inlineStr">
+      <c r="C44" s="27" t="inlineStr">
         <is>
           <t>일라이 릴리</t>
         </is>
       </c>
-      <c r="C44" s="26" t="inlineStr">
+      <c r="D44" s="27" t="inlineStr">
         <is>
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D44" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E44" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="28" t="inlineStr">
+        <is>
           <t>1,421조원</t>
         </is>
       </c>
-      <c r="F44" s="28" t="n">
+      <c r="G44" s="29" t="n">
         <v>0.5207633087852015</v>
       </c>
-      <c r="G44" s="28" t="n">
-        <v>0.3806685705829477</v>
-      </c>
-      <c r="H44" s="27" t="inlineStr">
+      <c r="H44" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B45" s="15" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="C45" s="15" t="inlineStr">
         <is>
           <t>JP모간체이스</t>
         </is>
       </c>
-      <c r="C45" s="15" t="inlineStr">
+      <c r="D45" s="15" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D45" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="24" t="inlineStr">
+      <c r="E45" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F45" s="25" t="inlineStr">
         <is>
           <t>1,284조원</t>
         </is>
       </c>
-      <c r="F45" s="25" t="n">
+      <c r="G45" s="26" t="n">
         <v>0.1295564907737132</v>
       </c>
-      <c r="G45" s="25" t="n">
-        <v>0.2471707721158493</v>
-      </c>
-      <c r="H45" s="24" t="inlineStr">
+      <c r="H45" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="26" t="inlineStr">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B46" s="26" t="inlineStr">
+      <c r="C46" s="27" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="C46" s="26" t="inlineStr">
+      <c r="D46" s="27" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D46" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E46" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="28" t="inlineStr">
+        <is>
           <t>1,231조원</t>
         </is>
       </c>
-      <c r="F46" s="28" t="n">
+      <c r="G46" s="29" t="n">
         <v>2.180069496152892</v>
       </c>
-      <c r="G46" s="28" t="n">
-        <v>0.6188828197555165</v>
-      </c>
-      <c r="H46" s="27" t="inlineStr">
+      <c r="H46" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="C47" s="15" t="inlineStr">
         <is>
           <t>월마트</t>
         </is>
       </c>
-      <c r="C47" s="15" t="inlineStr">
+      <c r="D47" s="15" t="inlineStr">
         <is>
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D47" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="24" t="inlineStr">
+      <c r="E47" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F47" s="25" t="inlineStr">
         <is>
           <t>1,175조원</t>
         </is>
       </c>
-      <c r="F47" s="25" t="n">
+      <c r="G47" s="26" t="n">
         <v>0.03674414119008595</v>
       </c>
-      <c r="G47" s="25" t="n">
-        <v>0.2509811690639198</v>
-      </c>
-      <c r="H47" s="24" t="inlineStr">
+      <c r="H47" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="26" t="inlineStr">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B48" s="26" t="inlineStr">
+      <c r="C48" s="27" t="inlineStr">
         <is>
           <t>비자</t>
         </is>
       </c>
-      <c r="C48" s="26" t="inlineStr">
+      <c r="D48" s="27" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D48" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E48" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="28" t="inlineStr">
+        <is>
           <t>955조원</t>
         </is>
       </c>
-      <c r="F48" s="28" t="n">
+      <c r="G48" s="29" t="n">
         <v>0.09402742958265729</v>
       </c>
-      <c r="G48" s="28" t="n">
-        <v>0.2240649506875312</v>
-      </c>
-      <c r="H48" s="27" t="inlineStr">
+      <c r="H48" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="C49" s="15" t="inlineStr">
         <is>
           <t>엑슨모빌</t>
         </is>
       </c>
-      <c r="C49" s="15" t="inlineStr">
+      <c r="D49" s="15" t="inlineStr">
         <is>
           <t>에너지</t>
         </is>
       </c>
-      <c r="D49" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="24" t="inlineStr">
+      <c r="E49" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F49" s="25" t="inlineStr">
         <is>
           <t>929조원</t>
         </is>
       </c>
-      <c r="F49" s="25" t="n">
+      <c r="G49" s="26" t="n">
         <v>0.4536715620827771</v>
       </c>
-      <c r="G49" s="25" t="n">
-        <v>0.2502406417094049</v>
-      </c>
-      <c r="H49" s="24" t="inlineStr">
+      <c r="H49" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="26" t="inlineStr">
+      <c r="A50" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B50" s="26" t="inlineStr">
+      <c r="C50" s="27" t="inlineStr">
         <is>
           <t>존슨앤드존슨</t>
         </is>
       </c>
-      <c r="C50" s="26" t="inlineStr">
+      <c r="D50" s="27" t="inlineStr">
         <is>
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D50" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E50" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="28" t="inlineStr">
+        <is>
           <t>901조원</t>
         </is>
       </c>
-      <c r="F50" s="28" t="n">
+      <c r="G50" s="29" t="n">
         <v>0.5066516347237879</v>
       </c>
-      <c r="G50" s="28" t="n">
-        <v>0.1920429463234355</v>
-      </c>
-      <c r="H50" s="27" t="inlineStr">
+      <c r="H50" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="C51" s="15" t="inlineStr">
         <is>
           <t>ASML</t>
         </is>
       </c>
-      <c r="C51" s="15" t="inlineStr">
+      <c r="D51" s="15" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D51" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E51" s="24" t="inlineStr">
+      <c r="E51" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F51" s="25" t="inlineStr">
         <is>
           <t>866조원</t>
         </is>
       </c>
-      <c r="F51" s="25" t="n">
+      <c r="G51" s="26" t="n">
         <v>0.8473653868326995</v>
       </c>
-      <c r="G51" s="25" t="n">
-        <v>0.4475837102567037</v>
-      </c>
-      <c r="H51" s="24" t="inlineStr">
+      <c r="H51" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="26" t="inlineStr">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B52" s="27" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B52" s="26" t="inlineStr">
+      <c r="C52" s="27" t="inlineStr">
         <is>
           <t>인텔</t>
         </is>
       </c>
-      <c r="C52" s="26" t="inlineStr">
+      <c r="D52" s="27" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D52" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E52" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="28" t="inlineStr">
+        <is>
           <t>796조원</t>
         </is>
       </c>
-      <c r="F52" s="28" t="n">
+      <c r="G52" s="29" t="n">
         <v>3.079531691562374</v>
       </c>
-      <c r="G52" s="28" t="n">
-        <v>0.683100854587897</v>
-      </c>
-      <c r="H52" s="27" t="inlineStr">
+      <c r="H52" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="C53" s="15" t="inlineStr">
         <is>
           <t>마스터카드</t>
         </is>
       </c>
-      <c r="C53" s="15" t="inlineStr">
+      <c r="D53" s="15" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="D53" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E53" s="24" t="inlineStr">
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="25" t="inlineStr">
         <is>
           <t>685조원</t>
         </is>
       </c>
-      <c r="F53" s="25" t="n">
+      <c r="G53" s="26" t="n">
         <v>-0.02609098394400999</v>
       </c>
-      <c r="G53" s="25" t="n">
-        <v>0.2223071018656363</v>
-      </c>
-      <c r="H53" s="24" t="inlineStr">
+      <c r="H53" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="26" t="inlineStr">
+      <c r="A54" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B54" s="27" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B54" s="26" t="inlineStr">
+      <c r="C54" s="27" t="inlineStr">
         <is>
           <t>애브비</t>
         </is>
       </c>
-      <c r="C54" s="26" t="inlineStr">
+      <c r="D54" s="27" t="inlineStr">
         <is>
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D54" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E54" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="28" t="inlineStr">
+        <is>
           <t>645조원</t>
         </is>
       </c>
-      <c r="F54" s="28" t="n">
+      <c r="G54" s="29" t="n">
         <v>0.2063324295758466</v>
       </c>
-      <c r="G54" s="28" t="n">
-        <v>0.2755236036328029</v>
-      </c>
-      <c r="H54" s="27" t="inlineStr">
+      <c r="H54" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="C55" s="15" t="inlineStr">
         <is>
           <t>오라클</t>
         </is>
       </c>
-      <c r="C55" s="15" t="inlineStr">
+      <c r="D55" s="15" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D55" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E55" s="24" t="inlineStr">
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F55" s="25" t="inlineStr">
         <is>
           <t>630조원</t>
         </is>
       </c>
-      <c r="F55" s="25" t="n">
+      <c r="G55" s="26" t="n">
         <v>-0.5261799165949559</v>
       </c>
-      <c r="G55" s="25" t="n">
-        <v>0.5547373559902894</v>
-      </c>
-      <c r="H55" s="24" t="inlineStr">
+      <c r="H55" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="26" t="inlineStr">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B56" s="27" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B56" s="26" t="inlineStr">
+      <c r="C56" s="27" t="inlineStr">
         <is>
           <t>시스코</t>
         </is>
       </c>
-      <c r="C56" s="26" t="inlineStr">
+      <c r="D56" s="27" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="D56" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E56" s="27" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="28" t="inlineStr">
+        <is>
           <t>601조원</t>
         </is>
       </c>
-      <c r="F56" s="28" t="n">
+      <c r="G56" s="29" t="n">
         <v>0.607579826917338</v>
       </c>
-      <c r="G56" s="28" t="n">
-        <v>0.2902001406087171</v>
-      </c>
-      <c r="H56" s="27" t="inlineStr">
+      <c r="H56" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="15" t="inlineStr">
+      <c r="A57" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B57" s="15" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="C57" s="15" t="inlineStr">
         <is>
           <t>TIGER 미국S&amp;P500</t>
         </is>
       </c>
-      <c r="C57" s="15" t="inlineStr">
+      <c r="D57" s="15" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D57" s="15" t="inlineStr">
+      <c r="E57" s="15" t="inlineStr">
         <is>
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="E57" s="24" t="inlineStr">
+      <c r="F57" s="25" t="inlineStr">
         <is>
           <t>21조원</t>
         </is>
       </c>
-      <c r="F57" s="25" t="n">
+      <c r="G57" s="26" t="n">
         <v>0.1782639885222381</v>
       </c>
-      <c r="G57" s="25" t="n">
-        <v>0.1464</v>
-      </c>
-      <c r="H57" s="29" t="n">
+      <c r="H57" s="30" t="n">
         <v>6.8e-05</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="26" t="inlineStr">
+      <c r="A58" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B58" s="27" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B58" s="26" t="inlineStr">
+      <c r="C58" s="27" t="inlineStr">
         <is>
           <t>TIGER 미국나스닥100</t>
         </is>
       </c>
-      <c r="C58" s="26" t="inlineStr">
+      <c r="D58" s="27" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D58" s="26" t="inlineStr">
+      <c r="E58" s="27" t="inlineStr">
         <is>
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="E58" s="27" t="inlineStr">
+      <c r="F58" s="28" t="inlineStr">
         <is>
           <t>12조원</t>
         </is>
       </c>
-      <c r="F58" s="28" t="n">
+      <c r="G58" s="29" t="n">
         <v>0.2434730103402611</v>
       </c>
-      <c r="G58" s="28" t="n">
-        <v>0.2064</v>
-      </c>
-      <c r="H58" s="30" t="n">
+      <c r="H58" s="31" t="n">
         <v>6.8e-05</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="15" t="inlineStr">
+      <c r="A59" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B59" s="15" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="C59" s="15" t="inlineStr">
         <is>
           <t>KODEX 미국S&amp;P500</t>
         </is>
       </c>
-      <c r="C59" s="15" t="inlineStr">
+      <c r="D59" s="15" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D59" s="15" t="inlineStr">
+      <c r="E59" s="15" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="E59" s="24" t="inlineStr">
+      <c r="F59" s="25" t="inlineStr">
         <is>
           <t>10조원</t>
         </is>
       </c>
-      <c r="F59" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" s="25" t="n">
-        <v>0.1473</v>
-      </c>
-      <c r="H59" s="29" t="n">
+      <c r="G59" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="30" t="n">
         <v>6.2e-05</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="26" t="inlineStr">
+      <c r="A60" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B60" s="26" t="inlineStr">
+      <c r="C60" s="27" t="inlineStr">
         <is>
           <t>KODEX 미국나스닥100</t>
         </is>
       </c>
-      <c r="C60" s="26" t="inlineStr">
+      <c r="D60" s="27" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D60" s="26" t="inlineStr">
+      <c r="E60" s="27" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="E60" s="27" t="inlineStr">
+      <c r="F60" s="28" t="inlineStr">
         <is>
           <t>9조원</t>
         </is>
       </c>
-      <c r="F60" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="28" t="n">
-        <v>0.2068</v>
-      </c>
-      <c r="H60" s="30" t="n">
+      <c r="G60" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="31" t="n">
         <v>6.2e-05</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="15" t="inlineStr">
+      <c r="A61" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B61" s="15" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B61" s="15" t="inlineStr">
+      <c r="C61" s="15" t="inlineStr">
         <is>
           <t>KODEX 머니마켓액티브</t>
         </is>
       </c>
-      <c r="C61" s="15" t="inlineStr">
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D61" s="15" t="inlineStr">
+      <c r="E61" s="15" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="E61" s="24" t="inlineStr">
+      <c r="F61" s="25" t="inlineStr">
         <is>
           <t>9조원</t>
         </is>
       </c>
-      <c r="F61" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="25" t="n">
-        <v>0.0146</v>
-      </c>
-      <c r="H61" s="29" t="n">
+      <c r="G61" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="30" t="n">
         <v>0.0005</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="26" t="inlineStr">
+      <c r="A62" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B62" s="27" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B62" s="26" t="inlineStr">
+      <c r="C62" s="27" t="inlineStr">
         <is>
           <t>KODEX CD금리액티브(합성)</t>
         </is>
       </c>
-      <c r="C62" s="26" t="inlineStr">
+      <c r="D62" s="27" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D62" s="26" t="inlineStr">
+      <c r="E62" s="27" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="E62" s="27" t="inlineStr">
+      <c r="F62" s="28" t="inlineStr">
         <is>
           <t>7조원</t>
         </is>
       </c>
-      <c r="F62" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G62" s="28" t="n">
-        <v>0.007900000000000001</v>
-      </c>
-      <c r="H62" s="30" t="n">
+      <c r="G62" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="31" t="n">
         <v>0.0002</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="15" t="inlineStr">
+      <c r="A63" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B63" s="15" t="inlineStr">
+      <c r="C63" s="15" t="inlineStr">
         <is>
           <t>TIGER 미국배당다우존스</t>
         </is>
       </c>
-      <c r="C63" s="15" t="inlineStr">
+      <c r="D63" s="15" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D63" s="15" t="inlineStr">
+      <c r="E63" s="15" t="inlineStr">
         <is>
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="E63" s="24" t="inlineStr">
+      <c r="F63" s="25" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F63" s="25" t="n">
+      <c r="G63" s="26" t="n">
         <v>0.2478942048517521</v>
       </c>
-      <c r="G63" s="25" t="n">
-        <v>0.1415</v>
-      </c>
-      <c r="H63" s="29" t="n">
+      <c r="H63" s="30" t="n">
         <v>0.0001</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="26" t="inlineStr">
+      <c r="A64" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B64" s="27" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B64" s="26" t="inlineStr">
+      <c r="C64" s="27" t="inlineStr">
         <is>
           <t>ACE KRX금현물</t>
         </is>
       </c>
-      <c r="C64" s="26" t="inlineStr">
+      <c r="D64" s="27" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D64" s="26" t="inlineStr">
+      <c r="E64" s="27" t="inlineStr">
         <is>
           <t>한국투자신탁운용</t>
         </is>
       </c>
-      <c r="E64" s="27" t="inlineStr">
+      <c r="F64" s="28" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F64" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G64" s="28" t="n">
-        <v>0.3191</v>
-      </c>
-      <c r="H64" s="30" t="n">
+      <c r="G64" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="31" t="n">
         <v>0.0019</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="15" t="inlineStr">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B65" s="15" t="inlineStr">
+      <c r="C65" s="15" t="inlineStr">
         <is>
           <t>ACE 미국S&amp;P500</t>
         </is>
       </c>
-      <c r="C65" s="15" t="inlineStr">
+      <c r="D65" s="15" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D65" s="15" t="inlineStr">
+      <c r="E65" s="15" t="inlineStr">
         <is>
           <t>한국투신운용(ETF)</t>
         </is>
       </c>
-      <c r="E65" s="24" t="inlineStr">
+      <c r="F65" s="25" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F65" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G65" s="25" t="n">
-        <v>0.1464</v>
-      </c>
-      <c r="H65" s="29" t="n">
+      <c r="G65" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="30" t="n">
         <v>4.7e-05</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="26" t="inlineStr">
+      <c r="A66" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B66" s="27" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B66" s="26" t="inlineStr">
+      <c r="C66" s="27" t="inlineStr">
         <is>
           <t>TIGER 미국테크TOP10 INDXX</t>
         </is>
       </c>
-      <c r="C66" s="26" t="inlineStr">
+      <c r="D66" s="27" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D66" s="26" t="inlineStr">
+      <c r="E66" s="27" t="inlineStr">
         <is>
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="E66" s="27" t="inlineStr">
+      <c r="F66" s="28" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F66" s="28" t="n">
+      <c r="G66" s="29" t="n">
         <v>0.1565284066014312</v>
       </c>
-      <c r="G66" s="28" t="n">
-        <v>0.2107</v>
-      </c>
-      <c r="H66" s="30" t="n">
+      <c r="H66" s="31" t="n">
         <v>0.0049</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="15" t="inlineStr">
+      <c r="A67" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B67" s="15" t="inlineStr">
+      <c r="C67" s="15" t="inlineStr">
         <is>
           <t>KODEX KOFR금리액티브(합성)</t>
         </is>
       </c>
-      <c r="C67" s="15" t="inlineStr">
+      <c r="D67" s="15" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D67" s="15" t="inlineStr">
+      <c r="E67" s="15" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="E67" s="24" t="inlineStr">
+      <c r="F67" s="25" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F67" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G67" s="25" t="n">
-        <v>0.0075</v>
-      </c>
-      <c r="H67" s="29" t="n">
+      <c r="G67" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="30" t="n">
         <v>0.0005</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="26" t="inlineStr">
+      <c r="A68" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B68" s="27" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B68" s="26" t="inlineStr">
+      <c r="C68" s="27" t="inlineStr">
         <is>
           <t>ACE 미국나스닥100</t>
         </is>
       </c>
-      <c r="C68" s="26" t="inlineStr">
+      <c r="D68" s="27" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D68" s="26" t="inlineStr">
+      <c r="E68" s="27" t="inlineStr">
         <is>
           <t>한국투신운용(ETF)</t>
         </is>
       </c>
-      <c r="E68" s="27" t="inlineStr">
+      <c r="F68" s="28" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F68" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="28" t="n">
-        <v>0.2063</v>
-      </c>
-      <c r="H68" s="30" t="n">
+      <c r="G68" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="31" t="n">
         <v>6.2e-05</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="15" t="inlineStr">
+      <c r="A69" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B69" s="15" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B69" s="15" t="inlineStr">
+      <c r="C69" s="15" t="inlineStr">
         <is>
           <t>KODEX 종합채권(AA-이상)액티브</t>
         </is>
       </c>
-      <c r="C69" s="15" t="inlineStr">
+      <c r="D69" s="15" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D69" s="15" t="inlineStr">
+      <c r="E69" s="15" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="E69" s="24" t="inlineStr">
+      <c r="F69" s="25" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F69" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G69" s="25" t="n">
-        <v>0.04099999999999999</v>
-      </c>
-      <c r="H69" s="29" t="n">
+      <c r="G69" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="30" t="n">
         <v>0.00045</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="26" t="inlineStr">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B70" s="27" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B70" s="26" t="inlineStr">
+      <c r="C70" s="27" t="inlineStr">
         <is>
           <t>TIGER CD금리투자KIS(합성)</t>
         </is>
       </c>
-      <c r="C70" s="26" t="inlineStr">
+      <c r="D70" s="27" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D70" s="26" t="inlineStr">
+      <c r="E70" s="27" t="inlineStr">
         <is>
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="E70" s="27" t="inlineStr">
+      <c r="F70" s="28" t="inlineStr">
         <is>
           <t>3조원</t>
         </is>
       </c>
-      <c r="F70" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G70" s="28" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="H70" s="30" t="n">
+      <c r="G70" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H70" s="31" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="15" t="inlineStr">
+      <c r="A71" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B71" s="15" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B71" s="15" t="inlineStr">
+      <c r="C71" s="15" t="inlineStr">
         <is>
           <t>RISE 머니마켓액티브</t>
         </is>
       </c>
-      <c r="C71" s="15" t="inlineStr">
+      <c r="D71" s="15" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D71" s="15" t="inlineStr">
+      <c r="E71" s="15" t="inlineStr">
         <is>
           <t>KB자산운용</t>
         </is>
       </c>
-      <c r="E71" s="24" t="inlineStr">
+      <c r="F71" s="25" t="inlineStr">
         <is>
           <t>3조원</t>
         </is>
       </c>
-      <c r="F71" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G71" s="25" t="n">
-        <v>0.0142</v>
-      </c>
-      <c r="H71" s="29" t="n">
+      <c r="G71" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="30" t="n">
         <v>0.0005</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="26" t="inlineStr">
+      <c r="A72" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B72" s="27" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B72" s="26" t="inlineStr">
+      <c r="C72" s="27" t="inlineStr">
         <is>
           <t>TIGER 머니마켓액티브</t>
         </is>
       </c>
-      <c r="C72" s="26" t="inlineStr">
+      <c r="D72" s="27" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D72" s="26" t="inlineStr">
+      <c r="E72" s="27" t="inlineStr">
         <is>
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="E72" s="27" t="inlineStr">
+      <c r="F72" s="28" t="inlineStr">
         <is>
           <t>3조원</t>
         </is>
       </c>
-      <c r="F72" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G72" s="28" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="H72" s="30" t="n">
+      <c r="G72" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="31" t="n">
         <v>0.0004</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="15" t="inlineStr">
+      <c r="A73" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B73" s="15" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B73" s="15" t="inlineStr">
+      <c r="C73" s="15" t="inlineStr">
         <is>
           <t>KODEX CD1년금리플러스액티브(합성)</t>
         </is>
       </c>
-      <c r="C73" s="15" t="inlineStr">
+      <c r="D73" s="15" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D73" s="15" t="inlineStr">
+      <c r="E73" s="15" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="E73" s="24" t="inlineStr">
+      <c r="F73" s="25" t="inlineStr">
         <is>
           <t>3조원</t>
         </is>
       </c>
-      <c r="F73" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G73" s="25" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H73" s="29" t="n">
+      <c r="G73" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H73" s="30" t="n">
         <v>0.0005</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="26" t="inlineStr">
+      <c r="A74" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B74" s="27" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B74" s="26" t="inlineStr">
+      <c r="C74" s="27" t="inlineStr">
         <is>
           <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
         </is>
       </c>
-      <c r="C74" s="26" t="inlineStr">
+      <c r="D74" s="27" t="inlineStr">
         <is>
           <t>커버드콜</t>
         </is>
       </c>
-      <c r="D74" s="26" t="inlineStr">
+      <c r="E74" s="27" t="inlineStr">
         <is>
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="E74" s="27" t="inlineStr">
+      <c r="F74" s="28" t="inlineStr">
         <is>
           <t>3조원</t>
         </is>
       </c>
-      <c r="F74" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G74" s="28" t="n">
-        <v>0.2078</v>
-      </c>
-      <c r="H74" s="30" t="n">
+      <c r="G74" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H74" s="31" t="n">
         <v>0.0025</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="15" t="inlineStr">
+      <c r="A75" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B75" s="15" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B75" s="15" t="inlineStr">
+      <c r="C75" s="15" t="inlineStr">
         <is>
           <t>PLUS 고배당주</t>
         </is>
       </c>
-      <c r="C75" s="15" t="inlineStr">
+      <c r="D75" s="15" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D75" s="15" t="inlineStr">
+      <c r="E75" s="15" t="inlineStr">
         <is>
           <t>한화자산운용</t>
         </is>
       </c>
-      <c r="E75" s="24" t="inlineStr">
+      <c r="F75" s="25" t="inlineStr">
         <is>
           <t>2조원</t>
         </is>
       </c>
-      <c r="F75" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G75" s="25" t="n">
-        <v>0.3049</v>
-      </c>
-      <c r="H75" s="29" t="n">
+      <c r="G75" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H75" s="30" t="n">
         <v>0.0023</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="26" t="inlineStr">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B76" s="27" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B76" s="26" t="inlineStr">
+      <c r="C76" s="27" t="inlineStr">
         <is>
           <t>TIGER KOFR금리액티브(합성)</t>
         </is>
       </c>
-      <c r="C76" s="26" t="inlineStr">
+      <c r="D76" s="27" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D76" s="26" t="inlineStr">
+      <c r="E76" s="27" t="inlineStr">
         <is>
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="E76" s="27" t="inlineStr">
+      <c r="F76" s="28" t="inlineStr">
         <is>
           <t>2조원</t>
         </is>
       </c>
-      <c r="F76" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G76" s="28" t="n">
-        <v>0.0064</v>
-      </c>
-      <c r="H76" s="30" t="n">
+      <c r="G76" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H76" s="31" t="n">
         <v>0.0003</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="15" t="inlineStr">
+      <c r="A77" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B77" s="15" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B77" s="15" t="inlineStr">
+      <c r="C77" s="15" t="inlineStr">
         <is>
           <t>KODEX 200미국채혼합50</t>
         </is>
       </c>
-      <c r="C77" s="15" t="inlineStr">
+      <c r="D77" s="15" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D77" s="15" t="inlineStr">
+      <c r="E77" s="15" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="E77" s="24" t="inlineStr">
+      <c r="F77" s="25" t="inlineStr">
         <is>
           <t>2조원</t>
         </is>
       </c>
-      <c r="F77" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G77" s="25" t="n">
-        <v>0.2503</v>
-      </c>
-      <c r="H77" s="29" t="n">
+      <c r="G77" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H77" s="30" t="n">
         <v>0.0035</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="26" t="inlineStr">
+      <c r="A78" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B78" s="27" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B78" s="26" t="inlineStr">
+      <c r="C78" s="27" t="inlineStr">
         <is>
           <t>KODEX 단기채권PLUS</t>
         </is>
       </c>
-      <c r="C78" s="26" t="inlineStr">
+      <c r="D78" s="27" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D78" s="26" t="inlineStr">
+      <c r="E78" s="27" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="E78" s="27" t="inlineStr">
+      <c r="F78" s="28" t="inlineStr">
         <is>
           <t>2조원</t>
         </is>
       </c>
-      <c r="F78" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G78" s="28" t="n">
-        <v>0.0083</v>
-      </c>
-      <c r="H78" s="30" t="n">
+      <c r="G78" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H78" s="31" t="n">
         <v>0.0015</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="15" t="inlineStr">
+      <c r="A79" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B79" s="15" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B79" s="15" t="inlineStr">
+      <c r="C79" s="15" t="inlineStr">
         <is>
           <t>KODEX 미국배당커버드콜액티브</t>
         </is>
       </c>
-      <c r="C79" s="15" t="inlineStr">
+      <c r="D79" s="15" t="inlineStr">
         <is>
           <t>커버드콜</t>
         </is>
       </c>
-      <c r="D79" s="15" t="inlineStr">
+      <c r="E79" s="15" t="inlineStr">
         <is>
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="E79" s="24" t="inlineStr">
+      <c r="F79" s="25" t="inlineStr">
         <is>
           <t>2조원</t>
         </is>
       </c>
-      <c r="F79" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G79" s="25" t="n">
-        <v>0.1238</v>
-      </c>
-      <c r="H79" s="29" t="n">
+      <c r="G79" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H79" s="30" t="n">
         <v>0.0019</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="26" t="inlineStr">
+      <c r="A80" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B80" s="27" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B80" s="26" t="inlineStr">
+      <c r="C80" s="27" t="inlineStr">
         <is>
           <t>TIGER CD1년금리액티브(합성)</t>
         </is>
       </c>
-      <c r="C80" s="26" t="inlineStr">
+      <c r="D80" s="27" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D80" s="26" t="inlineStr">
+      <c r="E80" s="27" t="inlineStr">
         <is>
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="E80" s="27" t="inlineStr">
+      <c r="F80" s="28" t="inlineStr">
         <is>
           <t>2조원</t>
         </is>
       </c>
-      <c r="F80" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G80" s="28" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="H80" s="30" t="n">
+      <c r="G80" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H80" s="31" t="n">
         <v>9.8e-05</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="inlineStr">
+      <c r="A81" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B81" s="15" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B81" s="15" t="inlineStr">
+      <c r="C81" s="15" t="inlineStr">
         <is>
           <t>RISE 미국나스닥100</t>
         </is>
       </c>
-      <c r="C81" s="15" t="inlineStr">
+      <c r="D81" s="15" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="D81" s="15" t="inlineStr">
+      <c r="E81" s="15" t="inlineStr">
         <is>
           <t>KB자산운용</t>
         </is>
       </c>
-      <c r="E81" s="24" t="inlineStr">
+      <c r="F81" s="25" t="inlineStr">
         <is>
           <t>2조원</t>
         </is>
       </c>
-      <c r="F81" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G81" s="25" t="n">
-        <v>0.2062</v>
-      </c>
-      <c r="H81" s="29" t="n">
+      <c r="G81" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H81" s="30" t="n">
         <v>6.2e-05</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="26" t="inlineStr">
+      <c r="A82" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B82" s="27" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B82" s="26" t="inlineStr">
+      <c r="C82" s="27" t="inlineStr">
         <is>
           <t>SPDR S&amp;P 500</t>
         </is>
       </c>
-      <c r="C82" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D82" s="26" t="inlineStr">
+      <c r="D82" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5147,73 +5310,77 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F82" s="28" t="n">
+      <c r="F82" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="29" t="n">
         <v>0.1712168714029432</v>
       </c>
-      <c r="G82" s="28" t="n">
-        <v>0.1526270353674158</v>
-      </c>
-      <c r="H82" s="27" t="inlineStr">
+      <c r="H82" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="15" t="inlineStr">
+      <c r="A83" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B83" s="15" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B83" s="15" t="inlineStr">
+      <c r="C83" s="15" t="inlineStr">
         <is>
           <t>Invesco QQQ (나스닥100)</t>
         </is>
       </c>
-      <c r="C83" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="D83" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E83" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="25" t="n">
+      <c r="E83" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="26" t="n">
         <v>0.2286861820192689</v>
       </c>
-      <c r="G83" s="25" t="n">
-        <v>0.2038095515075217</v>
-      </c>
-      <c r="H83" s="24" t="inlineStr">
+      <c r="H83" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="26" t="inlineStr">
+      <c r="A84" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B84" s="27" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B84" s="26" t="inlineStr">
+      <c r="C84" s="27" t="inlineStr">
         <is>
           <t>Vanguard 미국 전체시장</t>
         </is>
       </c>
-      <c r="C84" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D84" s="26" t="inlineStr">
+      <c r="D84" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5223,73 +5390,77 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F84" s="28" t="n">
+      <c r="F84" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="29" t="n">
         <v>0.1680824723535977</v>
       </c>
-      <c r="G84" s="28" t="n">
-        <v>0.1542903388794394</v>
-      </c>
-      <c r="H84" s="27" t="inlineStr">
+      <c r="H84" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="15" t="inlineStr">
+      <c r="A85" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B85" s="15" t="inlineStr">
+      <c r="C85" s="15" t="inlineStr">
         <is>
           <t>iShares 러셀2000 (미국 중소형)</t>
         </is>
       </c>
-      <c r="C85" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="D85" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E85" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F85" s="25" t="n">
+      <c r="E85" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F85" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="26" t="n">
         <v>0.2013375822034587</v>
       </c>
-      <c r="G85" s="25" t="n">
-        <v>0.2111022751155888</v>
-      </c>
-      <c r="H85" s="24" t="inlineStr">
+      <c r="H85" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="26" t="inlineStr">
+      <c r="A86" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B86" s="27" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B86" s="26" t="inlineStr">
+      <c r="C86" s="27" t="inlineStr">
         <is>
           <t>Vanguard 선진국(미국 제외)</t>
         </is>
       </c>
-      <c r="C86" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D86" s="26" t="inlineStr">
+      <c r="D86" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5299,73 +5470,77 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F86" s="28" t="n">
+      <c r="F86" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="29" t="n">
         <v>0.2266691413144159</v>
       </c>
-      <c r="G86" s="28" t="n">
-        <v>0.1579017670450371</v>
-      </c>
-      <c r="H86" s="27" t="inlineStr">
+      <c r="H86" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="15" t="inlineStr">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B87" s="15" t="inlineStr">
+      <c r="C87" s="15" t="inlineStr">
         <is>
           <t>Vanguard 신흥국</t>
         </is>
       </c>
-      <c r="C87" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="D87" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E87" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F87" s="25" t="n">
+      <c r="E87" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F87" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="26" t="n">
         <v>0.1316236092777672</v>
       </c>
-      <c r="G87" s="25" t="n">
-        <v>0.1645421250031637</v>
-      </c>
-      <c r="H87" s="24" t="inlineStr">
+      <c r="H87" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="26" t="inlineStr">
+      <c r="A88" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B88" s="27" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B88" s="26" t="inlineStr">
+      <c r="C88" s="27" t="inlineStr">
         <is>
           <t>iShares 미국채 1-3년</t>
         </is>
       </c>
-      <c r="C88" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D88" s="26" t="inlineStr">
+      <c r="D88" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5375,73 +5550,77 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F88" s="28" t="n">
+      <c r="F88" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="29" t="n">
         <v>0.01505337651433369</v>
       </c>
-      <c r="G88" s="28" t="n">
-        <v>0.01634004407000697</v>
-      </c>
-      <c r="H88" s="27" t="inlineStr">
+      <c r="H88" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="15" t="inlineStr">
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B89" s="15" t="inlineStr">
+      <c r="C89" s="15" t="inlineStr">
         <is>
           <t>iShares 미국채 7-10년</t>
         </is>
       </c>
-      <c r="C89" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="D89" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E89" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F89" s="25" t="n">
+      <c r="E89" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F89" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G89" s="26" t="n">
         <v>-0.02675355856628381</v>
       </c>
-      <c r="G89" s="25" t="n">
-        <v>0.06344333160950028</v>
-      </c>
-      <c r="H89" s="24" t="inlineStr">
+      <c r="H89" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="26" t="inlineStr">
+      <c r="A90" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B90" s="27" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B90" s="26" t="inlineStr">
+      <c r="C90" s="27" t="inlineStr">
         <is>
           <t>iShares 미국채 20년+</t>
         </is>
       </c>
-      <c r="C90" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D90" s="26" t="inlineStr">
+      <c r="D90" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5451,73 +5630,77 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F90" s="28" t="n">
+      <c r="F90" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="29" t="n">
         <v>-0.05711503892809356</v>
       </c>
-      <c r="G90" s="28" t="n">
-        <v>0.1348598378668211</v>
-      </c>
-      <c r="H90" s="27" t="inlineStr">
+      <c r="H90" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="15" t="inlineStr">
+      <c r="A91" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B91" s="15" t="inlineStr">
+      <c r="C91" s="15" t="inlineStr">
         <is>
           <t>iShares 미국 종합채권</t>
         </is>
       </c>
-      <c r="C91" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="D91" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E91" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F91" s="25" t="n">
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F91" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="26" t="n">
         <v>-0.00707032975902111</v>
       </c>
-      <c r="G91" s="25" t="n">
-        <v>0.05242550774268031</v>
-      </c>
-      <c r="H91" s="24" t="inlineStr">
+      <c r="H91" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="26" t="inlineStr">
+      <c r="A92" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B92" s="26" t="inlineStr">
+      <c r="C92" s="27" t="inlineStr">
         <is>
           <t>iShares 투자등급 회사채</t>
         </is>
       </c>
-      <c r="C92" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D92" s="26" t="inlineStr">
+      <c r="D92" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5527,73 +5710,77 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F92" s="28" t="n">
+      <c r="F92" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G92" s="29" t="n">
         <v>-0.02183448542608113</v>
       </c>
-      <c r="G92" s="28" t="n">
-        <v>0.07104050626038284</v>
-      </c>
-      <c r="H92" s="27" t="inlineStr">
+      <c r="H92" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="15" t="inlineStr">
+      <c r="A93" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B93" s="15" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B93" s="15" t="inlineStr">
+      <c r="C93" s="15" t="inlineStr">
         <is>
           <t>iShares 하이일드 회사채</t>
         </is>
       </c>
-      <c r="C93" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="D93" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E93" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F93" s="25" t="n">
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F93" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G93" s="26" t="n">
         <v>0.02786343669994706</v>
       </c>
-      <c r="G93" s="25" t="n">
-        <v>0.050268463091665</v>
-      </c>
-      <c r="H93" s="24" t="inlineStr">
+      <c r="H93" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="26" t="inlineStr">
+      <c r="A94" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B94" s="27" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B94" s="26" t="inlineStr">
+      <c r="C94" s="27" t="inlineStr">
         <is>
           <t>SPDR 금</t>
         </is>
       </c>
-      <c r="C94" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D94" s="26" t="inlineStr">
+      <c r="D94" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5603,73 +5790,77 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F94" s="28" t="n">
+      <c r="F94" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G94" s="29" t="n">
         <v>0.1905214114016085</v>
       </c>
-      <c r="G94" s="28" t="n">
-        <v>0.2154040053034466</v>
-      </c>
-      <c r="H94" s="27" t="inlineStr">
+      <c r="H94" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="15" t="inlineStr">
+      <c r="A95" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B95" s="15" t="inlineStr">
+      <c r="C95" s="15" t="inlineStr">
         <is>
           <t>iShares 은</t>
         </is>
       </c>
-      <c r="C95" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="D95" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E95" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F95" s="25" t="n">
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F95" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="26" t="n">
         <v>0.5858692775866632</v>
       </c>
-      <c r="G95" s="25" t="n">
-        <v>0.4420072503135195</v>
-      </c>
-      <c r="H95" s="24" t="inlineStr">
+      <c r="H95" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="26" t="inlineStr">
+      <c r="A96" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B96" s="27" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B96" s="26" t="inlineStr">
+      <c r="C96" s="27" t="inlineStr">
         <is>
           <t>United States 원유</t>
         </is>
       </c>
-      <c r="C96" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D96" s="26" t="inlineStr">
+      <c r="D96" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5679,73 +5870,77 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F96" s="28" t="n">
+      <c r="F96" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G96" s="29" t="n">
         <v>1.051754034947312</v>
       </c>
-      <c r="G96" s="28" t="n">
-        <v>0.3737647369952773</v>
-      </c>
-      <c r="H96" s="27" t="inlineStr">
+      <c r="H96" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="15" t="inlineStr">
+      <c r="A97" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B97" s="15" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B97" s="15" t="inlineStr">
+      <c r="C97" s="15" t="inlineStr">
         <is>
           <t>Invesco 원자재</t>
         </is>
       </c>
-      <c r="C97" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E97" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F97" s="25" t="n">
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F97" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="26" t="n">
         <v>0.5101417506271237</v>
       </c>
-      <c r="G97" s="25" t="n">
-        <v>0.1721311332624557</v>
-      </c>
-      <c r="H97" s="24" t="inlineStr">
+      <c r="H97" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="26" t="inlineStr">
+      <c r="A98" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B98" s="27" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B98" s="26" t="inlineStr">
+      <c r="C98" s="27" t="inlineStr">
         <is>
           <t>Vanguard 미국 리츠</t>
         </is>
       </c>
-      <c r="C98" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D98" s="26" t="inlineStr">
+      <c r="D98" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5755,73 +5950,77 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F98" s="28" t="n">
+      <c r="F98" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" s="29" t="n">
         <v>0.04842313369172224</v>
       </c>
-      <c r="G98" s="28" t="n">
-        <v>0.1683615867048639</v>
-      </c>
-      <c r="H98" s="27" t="inlineStr">
+      <c r="H98" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="15" t="inlineStr">
+      <c r="A99" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B99" s="15" t="inlineStr">
+      <c r="C99" s="15" t="inlineStr">
         <is>
           <t>Schwab 미국 배당주</t>
         </is>
       </c>
-      <c r="C99" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="D99" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E99" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F99" s="25" t="n">
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F99" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="26" t="n">
         <v>0.2710968871712811</v>
       </c>
-      <c r="G99" s="25" t="n">
-        <v>0.1321671662551849</v>
-      </c>
-      <c r="H99" s="24" t="inlineStr">
+      <c r="H99" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="26" t="inlineStr">
+      <c r="A100" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B100" s="27" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B100" s="26" t="inlineStr">
+      <c r="C100" s="27" t="inlineStr">
         <is>
           <t>Vanguard 배당성장</t>
         </is>
       </c>
-      <c r="C100" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D100" s="26" t="inlineStr">
+      <c r="D100" s="27" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5831,2003 +6030,2005 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F100" s="28" t="n">
+      <c r="F100" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G100" s="29" t="n">
         <v>0.1164247275358388</v>
       </c>
-      <c r="G100" s="28" t="n">
-        <v>0.1223752554121164</v>
-      </c>
-      <c r="H100" s="27" t="inlineStr">
+      <c r="H100" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="15" t="inlineStr">
+      <c r="A101" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B101" s="15" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B101" s="15" t="inlineStr">
+      <c r="C101" s="15" t="inlineStr">
         <is>
           <t>삼성MMF법인 1</t>
         </is>
       </c>
-      <c r="C101" s="15" t="inlineStr">
+      <c r="D101" s="15" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D101" s="15" t="inlineStr">
+      <c r="E101" s="15" t="inlineStr">
         <is>
           <t>삼성자산운용</t>
         </is>
       </c>
-      <c r="E101" s="24" t="inlineStr">
+      <c r="F101" s="25" t="inlineStr">
         <is>
           <t>11조원</t>
         </is>
       </c>
-      <c r="F101" s="25" t="n">
+      <c r="G101" s="26" t="n">
         <v>0.029549</v>
       </c>
-      <c r="G101" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H101" s="24" t="inlineStr">
+      <c r="H101" s="25" t="inlineStr">
         <is>
           <t>0.05~0.09%</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="26" t="inlineStr">
+      <c r="A102" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B102" s="27" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B102" s="26" t="inlineStr">
+      <c r="C102" s="27" t="inlineStr">
         <is>
           <t>우리큰만족법인MMF 1(국공채)</t>
         </is>
       </c>
-      <c r="C102" s="26" t="inlineStr">
+      <c r="D102" s="27" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D102" s="26" t="inlineStr">
+      <c r="E102" s="27" t="inlineStr">
         <is>
           <t>우리자산운용</t>
         </is>
       </c>
-      <c r="E102" s="27" t="inlineStr">
+      <c r="F102" s="28" t="inlineStr">
         <is>
           <t>9조원</t>
         </is>
       </c>
-      <c r="F102" s="28" t="n">
+      <c r="G102" s="29" t="n">
         <v>0.028073</v>
       </c>
-      <c r="G102" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H102" s="27" t="inlineStr">
+      <c r="H102" s="28" t="inlineStr">
         <is>
           <t>0.08~0.10%</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="15" t="inlineStr">
+      <c r="A103" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B103" s="15" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B103" s="15" t="inlineStr">
+      <c r="C103" s="15" t="inlineStr">
         <is>
           <t>IBK그랑프리국공채MMF법인투자신탁 1[국공채]</t>
         </is>
       </c>
-      <c r="C103" s="15" t="inlineStr">
+      <c r="D103" s="15" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D103" s="15" t="inlineStr">
+      <c r="E103" s="15" t="inlineStr">
         <is>
           <t>아이비케이자산운용</t>
         </is>
       </c>
-      <c r="E103" s="24" t="inlineStr">
+      <c r="F103" s="25" t="inlineStr">
         <is>
           <t>8조원</t>
         </is>
       </c>
-      <c r="F103" s="25" t="n">
+      <c r="G103" s="26" t="n">
         <v>0.028188</v>
       </c>
-      <c r="G103" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H103" s="24" t="inlineStr">
+      <c r="H103" s="25" t="inlineStr">
         <is>
           <t>0.09~0.17%</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="26" t="inlineStr">
+      <c r="A104" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B104" s="27" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B104" s="26" t="inlineStr">
+      <c r="C104" s="27" t="inlineStr">
         <is>
           <t>KB법인용MMF I-1(운용)</t>
         </is>
       </c>
-      <c r="C104" s="26" t="inlineStr">
+      <c r="D104" s="27" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D104" s="26" t="inlineStr">
+      <c r="E104" s="27" t="inlineStr">
         <is>
           <t>케이비자산운용</t>
         </is>
       </c>
-      <c r="E104" s="27" t="inlineStr">
+      <c r="F104" s="28" t="inlineStr">
         <is>
           <t>8조원</t>
         </is>
       </c>
-      <c r="F104" s="28" t="n">
+      <c r="G104" s="29" t="n">
         <v>0.029889</v>
       </c>
-      <c r="G104" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H104" s="27" t="inlineStr">
+      <c r="H104" s="28" t="inlineStr">
         <is>
           <t>0.06~0.09%</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="15" t="inlineStr">
+      <c r="A105" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B105" s="15" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B105" s="15" t="inlineStr">
+      <c r="C105" s="15" t="inlineStr">
         <is>
           <t>우리큰만족신종MMF3</t>
         </is>
       </c>
-      <c r="C105" s="15" t="inlineStr">
+      <c r="D105" s="15" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D105" s="15" t="inlineStr">
+      <c r="E105" s="15" t="inlineStr">
         <is>
           <t>우리자산운용</t>
         </is>
       </c>
-      <c r="E105" s="24" t="inlineStr">
+      <c r="F105" s="25" t="inlineStr">
         <is>
           <t>7조원</t>
         </is>
       </c>
-      <c r="F105" s="25" t="n">
+      <c r="G105" s="26" t="n">
         <v>0.030522</v>
       </c>
-      <c r="G105" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H105" s="24" t="inlineStr">
+      <c r="H105" s="25" t="inlineStr">
         <is>
           <t>0.09~0.11%</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="26" t="inlineStr">
+      <c r="A106" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B106" s="27" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B106" s="26" t="inlineStr">
+      <c r="C106" s="27" t="inlineStr">
         <is>
           <t>신영법인용MMF4-26_운용</t>
         </is>
       </c>
-      <c r="C106" s="26" t="inlineStr">
+      <c r="D106" s="27" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D106" s="26" t="inlineStr">
+      <c r="E106" s="27" t="inlineStr">
         <is>
           <t>신영자산운용</t>
         </is>
       </c>
-      <c r="E106" s="27" t="inlineStr">
+      <c r="F106" s="28" t="inlineStr">
         <is>
           <t>7조원</t>
         </is>
       </c>
-      <c r="F106" s="28" t="n">
+      <c r="G106" s="29" t="n">
         <v>0.028373</v>
       </c>
-      <c r="G106" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H106" s="27" t="inlineStr">
+      <c r="H106" s="28" t="inlineStr">
         <is>
           <t>0.10~0.15%</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="15" t="inlineStr">
+      <c r="A107" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B107" s="15" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B107" s="15" t="inlineStr">
+      <c r="C107" s="15" t="inlineStr">
         <is>
           <t>신한BEST신종법인용MMFGS-2(종류)</t>
         </is>
       </c>
-      <c r="C107" s="15" t="inlineStr">
+      <c r="D107" s="15" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D107" s="15" t="inlineStr">
+      <c r="E107" s="15" t="inlineStr">
         <is>
           <t>신한자산운용</t>
         </is>
       </c>
-      <c r="E107" s="24" t="inlineStr">
+      <c r="F107" s="25" t="inlineStr">
         <is>
           <t>6조원</t>
         </is>
       </c>
-      <c r="F107" s="25" t="n">
+      <c r="G107" s="26" t="n">
         <v>0.029896</v>
       </c>
-      <c r="G107" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H107" s="24" t="inlineStr">
+      <c r="H107" s="25" t="inlineStr">
         <is>
           <t>0.07~0.09%</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="26" t="inlineStr">
+      <c r="A108" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B108" s="27" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B108" s="26" t="inlineStr">
+      <c r="C108" s="27" t="inlineStr">
         <is>
           <t>한화골드법인MMF-KM3(국공채)</t>
         </is>
       </c>
-      <c r="C108" s="26" t="inlineStr">
+      <c r="D108" s="27" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D108" s="26" t="inlineStr">
+      <c r="E108" s="27" t="inlineStr">
         <is>
           <t>한화자산운용</t>
         </is>
       </c>
-      <c r="E108" s="27" t="inlineStr">
+      <c r="F108" s="28" t="inlineStr">
         <is>
           <t>5조원</t>
         </is>
       </c>
-      <c r="F108" s="28" t="n">
+      <c r="G108" s="29" t="n">
         <v>0.028207</v>
       </c>
-      <c r="G108" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H108" s="27" t="inlineStr">
+      <c r="H108" s="28" t="inlineStr">
         <is>
           <t>0.06~0.10%</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="15" t="inlineStr">
+      <c r="A109" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B109" s="15" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B109" s="15" t="inlineStr">
+      <c r="C109" s="15" t="inlineStr">
         <is>
           <t>하나클래스원신종MMF(K-5)</t>
         </is>
       </c>
-      <c r="C109" s="15" t="inlineStr">
+      <c r="D109" s="15" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D109" s="15" t="inlineStr">
+      <c r="E109" s="15" t="inlineStr">
         <is>
           <t>하나자산운용</t>
         </is>
       </c>
-      <c r="E109" s="24" t="inlineStr">
+      <c r="F109" s="25" t="inlineStr">
         <is>
           <t>5조원</t>
         </is>
       </c>
-      <c r="F109" s="25" t="n">
+      <c r="G109" s="26" t="n">
         <v>0.028155</v>
       </c>
-      <c r="G109" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H109" s="24" t="inlineStr">
+      <c r="H109" s="25" t="inlineStr">
         <is>
           <t>0.11~0.16%</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="26" t="inlineStr">
+      <c r="A110" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B110" s="27" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B110" s="26" t="inlineStr">
+      <c r="C110" s="27" t="inlineStr">
         <is>
           <t>한국투자법인용MMF 2(국공채)</t>
         </is>
       </c>
-      <c r="C110" s="26" t="inlineStr">
+      <c r="D110" s="27" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D110" s="26" t="inlineStr">
+      <c r="E110" s="27" t="inlineStr">
         <is>
           <t>한국투자신탁운용</t>
         </is>
       </c>
-      <c r="E110" s="27" t="inlineStr">
+      <c r="F110" s="28" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F110" s="28" t="n">
+      <c r="G110" s="29" t="n">
         <v>0.028016</v>
       </c>
-      <c r="G110" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H110" s="27" t="inlineStr">
+      <c r="H110" s="28" t="inlineStr">
         <is>
           <t>0.06~0.16%</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="15" t="inlineStr">
+      <c r="A111" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B111" s="15" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B111" s="15" t="inlineStr">
+      <c r="C111" s="15" t="inlineStr">
         <is>
           <t>미래에셋법인전용MMF 1(국공채)</t>
         </is>
       </c>
-      <c r="C111" s="15" t="inlineStr">
+      <c r="D111" s="15" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D111" s="15" t="inlineStr">
+      <c r="E111" s="15" t="inlineStr">
         <is>
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="E111" s="24" t="inlineStr">
+      <c r="F111" s="25" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F111" s="25" t="n">
+      <c r="G111" s="26" t="n">
         <v>0.027934</v>
       </c>
-      <c r="G111" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H111" s="24" t="inlineStr">
+      <c r="H111" s="25" t="inlineStr">
         <is>
           <t>0.05~0.15%</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="26" t="inlineStr">
+      <c r="A112" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B112" s="27" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B112" s="26" t="inlineStr">
+      <c r="C112" s="27" t="inlineStr">
         <is>
           <t>브이아이천하제일법인MMF1</t>
         </is>
       </c>
-      <c r="C112" s="26" t="inlineStr">
+      <c r="D112" s="27" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D112" s="26" t="inlineStr">
+      <c r="E112" s="27" t="inlineStr">
         <is>
           <t>브이아이자산운용</t>
         </is>
       </c>
-      <c r="E112" s="27" t="inlineStr">
+      <c r="F112" s="28" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F112" s="28" t="n">
+      <c r="G112" s="29" t="n">
         <v>0.028224</v>
       </c>
-      <c r="G112" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H112" s="27" t="inlineStr">
+      <c r="H112" s="28" t="inlineStr">
         <is>
           <t>0.09~0.12%</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="15" t="inlineStr">
+      <c r="A113" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B113" s="15" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B113" s="15" t="inlineStr">
+      <c r="C113" s="15" t="inlineStr">
         <is>
           <t>NH-Amundi법인MMF 8</t>
         </is>
       </c>
-      <c r="C113" s="15" t="inlineStr">
+      <c r="D113" s="15" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D113" s="15" t="inlineStr">
+      <c r="E113" s="15" t="inlineStr">
         <is>
           <t>엔에이치아문디자산운용</t>
         </is>
       </c>
-      <c r="E113" s="24" t="inlineStr">
+      <c r="F113" s="25" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F113" s="25" t="n">
+      <c r="G113" s="26" t="n">
         <v>0.027945</v>
       </c>
-      <c r="G113" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H113" s="29" t="n">
+      <c r="H113" s="30" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="26" t="inlineStr">
+      <c r="A114" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B114" s="27" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B114" s="26" t="inlineStr">
+      <c r="C114" s="27" t="inlineStr">
         <is>
           <t>하나신종MMF(S-29)</t>
         </is>
       </c>
-      <c r="C114" s="26" t="inlineStr">
+      <c r="D114" s="27" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D114" s="26" t="inlineStr">
+      <c r="E114" s="27" t="inlineStr">
         <is>
           <t>하나자산운용</t>
         </is>
       </c>
-      <c r="E114" s="27" t="inlineStr">
+      <c r="F114" s="28" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F114" s="28" t="n">
+      <c r="G114" s="29" t="n">
         <v>0.029723</v>
       </c>
-      <c r="G114" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H114" s="27" t="inlineStr">
+      <c r="H114" s="28" t="inlineStr">
         <is>
           <t>0.09~0.13%</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="15" t="inlineStr">
+      <c r="A115" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B115" s="15" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B115" s="15" t="inlineStr">
+      <c r="C115" s="15" t="inlineStr">
         <is>
           <t>삼성스마트MMF법인 1</t>
         </is>
       </c>
-      <c r="C115" s="15" t="inlineStr">
+      <c r="D115" s="15" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D115" s="15" t="inlineStr">
+      <c r="E115" s="15" t="inlineStr">
         <is>
           <t>삼성자산운용</t>
         </is>
       </c>
-      <c r="E115" s="24" t="inlineStr">
+      <c r="F115" s="25" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F115" s="25" t="n">
+      <c r="G115" s="26" t="n">
         <v>0.028099</v>
       </c>
-      <c r="G115" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H115" s="24" t="inlineStr">
+      <c r="H115" s="25" t="inlineStr">
         <is>
           <t>0.07~0.10%</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="26" t="inlineStr">
+      <c r="A116" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B116" s="27" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B116" s="26" t="inlineStr">
+      <c r="C116" s="27" t="inlineStr">
         <is>
           <t>신한 BEST법인용MMF GS- 1(종류)</t>
         </is>
       </c>
-      <c r="C116" s="26" t="inlineStr">
+      <c r="D116" s="27" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D116" s="26" t="inlineStr">
+      <c r="E116" s="27" t="inlineStr">
         <is>
           <t>신한자산운용</t>
         </is>
       </c>
-      <c r="E116" s="27" t="inlineStr">
+      <c r="F116" s="28" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F116" s="28" t="n">
+      <c r="G116" s="29" t="n">
         <v>0.027833</v>
       </c>
-      <c r="G116" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H116" s="27" t="inlineStr">
+      <c r="H116" s="28" t="inlineStr">
         <is>
           <t>0.06~0.12%</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="15" t="inlineStr">
+      <c r="A117" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B117" s="15" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B117" s="15" t="inlineStr">
+      <c r="C117" s="15" t="inlineStr">
         <is>
           <t>KB법인용MMF I-2(국공채)(운용)</t>
         </is>
       </c>
-      <c r="C117" s="15" t="inlineStr">
+      <c r="D117" s="15" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D117" s="15" t="inlineStr">
+      <c r="E117" s="15" t="inlineStr">
         <is>
           <t>케이비자산운용</t>
         </is>
       </c>
-      <c r="E117" s="24" t="inlineStr">
+      <c r="F117" s="25" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F117" s="25" t="n">
+      <c r="G117" s="26" t="n">
         <v>0.027897</v>
       </c>
-      <c r="G117" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H117" s="24" t="inlineStr">
+      <c r="H117" s="25" t="inlineStr">
         <is>
           <t>0.07~0.12%</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="26" t="inlineStr">
+      <c r="A118" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B118" s="27" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B118" s="26" t="inlineStr">
+      <c r="C118" s="27" t="inlineStr">
         <is>
           <t>BNK법인MMF 1(국공채)</t>
         </is>
       </c>
-      <c r="C118" s="26" t="inlineStr">
+      <c r="D118" s="27" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D118" s="26" t="inlineStr">
+      <c r="E118" s="27" t="inlineStr">
         <is>
           <t>비엔케이자산운용</t>
         </is>
       </c>
-      <c r="E118" s="27" t="inlineStr">
+      <c r="F118" s="28" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F118" s="28" t="n">
+      <c r="G118" s="29" t="n">
         <v>0.028014</v>
       </c>
-      <c r="G118" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H118" s="30" t="n">
+      <c r="H118" s="31" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="15" t="inlineStr">
+      <c r="A119" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B119" s="15" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B119" s="15" t="inlineStr">
+      <c r="C119" s="15" t="inlineStr">
         <is>
           <t>교보악사프라임법인MMF J- 1(운용)</t>
         </is>
       </c>
-      <c r="C119" s="15" t="inlineStr">
+      <c r="D119" s="15" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D119" s="15" t="inlineStr">
+      <c r="E119" s="15" t="inlineStr">
         <is>
           <t>교보악사자산운용</t>
         </is>
       </c>
-      <c r="E119" s="24" t="inlineStr">
+      <c r="F119" s="25" t="inlineStr">
         <is>
           <t>4조원</t>
         </is>
       </c>
-      <c r="F119" s="25" t="n">
+      <c r="G119" s="26" t="n">
         <v>0.028143</v>
       </c>
-      <c r="G119" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H119" s="29" t="n">
+      <c r="H119" s="30" t="n">
         <v>0.00108</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="26" t="inlineStr">
+      <c r="A120" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B120" s="27" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B120" s="26" t="inlineStr">
+      <c r="C120" s="27" t="inlineStr">
         <is>
           <t>DB클린법인MMF 4운용</t>
         </is>
       </c>
-      <c r="C120" s="26" t="inlineStr">
+      <c r="D120" s="27" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D120" s="26" t="inlineStr">
+      <c r="E120" s="27" t="inlineStr">
         <is>
           <t>디비자산운용</t>
         </is>
       </c>
-      <c r="E120" s="27" t="inlineStr">
+      <c r="F120" s="28" t="inlineStr">
         <is>
           <t>3조원</t>
         </is>
       </c>
-      <c r="F120" s="28" t="n">
+      <c r="G120" s="29" t="n">
         <v>0.028008</v>
       </c>
-      <c r="G120" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H120" s="30" t="n">
+      <c r="H120" s="31" t="n">
         <v>0.001</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="15" t="inlineStr">
+      <c r="A121" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B121" s="15" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B121" s="15" t="inlineStr">
+      <c r="C121" s="15" t="inlineStr">
         <is>
           <t>Plus신종법인용MMF 1</t>
         </is>
       </c>
-      <c r="C121" s="15" t="inlineStr">
+      <c r="D121" s="15" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D121" s="15" t="inlineStr">
+      <c r="E121" s="15" t="inlineStr">
         <is>
           <t>플러스자산운용</t>
         </is>
       </c>
-      <c r="E121" s="24" t="inlineStr">
+      <c r="F121" s="25" t="inlineStr">
         <is>
           <t>3조원</t>
         </is>
       </c>
-      <c r="F121" s="25" t="n">
+      <c r="G121" s="26" t="n">
         <v>0.029821</v>
       </c>
-      <c r="G121" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H121" s="24" t="inlineStr">
+      <c r="H121" s="25" t="inlineStr">
         <is>
           <t>0.10~0.11%</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="26" t="inlineStr">
+      <c r="A122" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B122" s="27" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B122" s="26" t="inlineStr">
+      <c r="C122" s="27" t="inlineStr">
         <is>
           <t>플러스국공채법인용MMF3</t>
         </is>
       </c>
-      <c r="C122" s="26" t="inlineStr">
+      <c r="D122" s="27" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D122" s="26" t="inlineStr">
+      <c r="E122" s="27" t="inlineStr">
         <is>
           <t>플러스자산운용</t>
         </is>
       </c>
-      <c r="E122" s="27" t="inlineStr">
+      <c r="F122" s="28" t="inlineStr">
         <is>
           <t>3조원</t>
         </is>
       </c>
-      <c r="F122" s="28" t="n">
+      <c r="G122" s="29" t="n">
         <v>0.028117</v>
       </c>
-      <c r="G122" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H122" s="27" t="inlineStr">
+      <c r="H122" s="28" t="inlineStr">
         <is>
           <t>0.06~0.10%</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="15" t="inlineStr">
+      <c r="A123" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B123" s="15" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B123" s="15" t="inlineStr">
+      <c r="C123" s="15" t="inlineStr">
         <is>
           <t>미래에셋법인전용MMF A-4</t>
         </is>
       </c>
-      <c r="C123" s="15" t="inlineStr">
+      <c r="D123" s="15" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D123" s="15" t="inlineStr">
+      <c r="E123" s="15" t="inlineStr">
         <is>
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="E123" s="24" t="inlineStr">
+      <c r="F123" s="25" t="inlineStr">
         <is>
           <t>3조원</t>
         </is>
       </c>
-      <c r="F123" s="25" t="n">
+      <c r="G123" s="26" t="n">
         <v>0.030076</v>
       </c>
-      <c r="G123" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H123" s="24" t="inlineStr">
+      <c r="H123" s="25" t="inlineStr">
         <is>
           <t>0.05~0.09%</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="26" t="inlineStr">
+      <c r="A124" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B124" s="27" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B124" s="26" t="inlineStr">
+      <c r="C124" s="27" t="inlineStr">
         <is>
           <t>키움프런티어법인용MMF 3[국공채]</t>
         </is>
       </c>
-      <c r="C124" s="26" t="inlineStr">
+      <c r="D124" s="27" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D124" s="26" t="inlineStr">
+      <c r="E124" s="27" t="inlineStr">
         <is>
           <t>키움투자자산운용</t>
         </is>
       </c>
-      <c r="E124" s="27" t="inlineStr">
+      <c r="F124" s="28" t="inlineStr">
         <is>
           <t>2조원</t>
         </is>
       </c>
-      <c r="F124" s="28" t="n">
+      <c r="G124" s="29" t="n">
         <v>0.027922</v>
       </c>
-      <c r="G124" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H124" s="27" t="inlineStr">
+      <c r="H124" s="28" t="inlineStr">
         <is>
           <t>0.10~0.24%</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="15" t="inlineStr">
+      <c r="A125" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B125" s="15" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B125" s="15" t="inlineStr">
+      <c r="C125" s="15" t="inlineStr">
         <is>
           <t>대신국공채법인전용MMF 1(운용)</t>
         </is>
       </c>
-      <c r="C125" s="15" t="inlineStr">
+      <c r="D125" s="15" t="inlineStr">
         <is>
           <t>MMF</t>
         </is>
       </c>
-      <c r="D125" s="15" t="inlineStr">
+      <c r="E125" s="15" t="inlineStr">
         <is>
           <t>대신자산운용</t>
         </is>
       </c>
-      <c r="E125" s="24" t="inlineStr">
+      <c r="F125" s="25" t="inlineStr">
         <is>
           <t>2조원</t>
         </is>
       </c>
-      <c r="F125" s="25" t="n">
+      <c r="G125" s="26" t="n">
         <v>0.028038</v>
       </c>
-      <c r="G125" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H125" s="24" t="inlineStr">
+      <c r="H125" s="25" t="inlineStr">
         <is>
           <t>0.07~0.10%</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="26" t="inlineStr">
+      <c r="A126" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B126" s="27" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B126" s="26" t="inlineStr">
+      <c r="C126" s="27" t="inlineStr">
         <is>
           <t>피델리티글로벌테크놀로지증권자투자신탁(주식-재간접형)</t>
         </is>
       </c>
-      <c r="C126" s="26" t="inlineStr">
+      <c r="D126" s="27" t="inlineStr">
         <is>
           <t>해외주식형</t>
         </is>
       </c>
-      <c r="D126" s="26" t="inlineStr">
+      <c r="E126" s="27" t="inlineStr">
         <is>
           <t>피델리티자산운용</t>
         </is>
       </c>
-      <c r="E126" s="27" t="inlineStr">
+      <c r="F126" s="28" t="inlineStr">
         <is>
           <t>9,218억원</t>
         </is>
       </c>
-      <c r="F126" s="28" t="n">
+      <c r="G126" s="29" t="n">
         <v>0.20358</v>
       </c>
-      <c r="G126" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H126" s="27" t="inlineStr">
+      <c r="H126" s="28" t="inlineStr">
         <is>
           <t>0.16~1.36%</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="15" t="inlineStr">
+      <c r="A127" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B127" s="15" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B127" s="15" t="inlineStr">
+      <c r="C127" s="15" t="inlineStr">
         <is>
           <t>피델리티월지급식아시아하이일드증권자투자신탁[채권-재간접형]</t>
         </is>
       </c>
-      <c r="C127" s="15" t="inlineStr">
+      <c r="D127" s="15" t="inlineStr">
         <is>
           <t>해외채권형</t>
         </is>
       </c>
-      <c r="D127" s="15" t="inlineStr">
+      <c r="E127" s="15" t="inlineStr">
         <is>
           <t>피델리티자산운용</t>
         </is>
       </c>
-      <c r="E127" s="24" t="inlineStr">
+      <c r="F127" s="25" t="inlineStr">
         <is>
           <t>7,365억원</t>
         </is>
       </c>
-      <c r="F127" s="25" t="n">
+      <c r="G127" s="26" t="n">
         <v>0.051551</v>
       </c>
-      <c r="G127" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H127" s="24" t="inlineStr">
+      <c r="H127" s="25" t="inlineStr">
         <is>
           <t>0.37~1.17%</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="26" t="inlineStr">
+      <c r="A128" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B128" s="27" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B128" s="26" t="inlineStr">
+      <c r="C128" s="27" t="inlineStr">
         <is>
           <t>피델리티글로벌배당인컴증권자투자신탁(주식-재간접형)</t>
         </is>
       </c>
-      <c r="C128" s="26" t="inlineStr">
+      <c r="D128" s="27" t="inlineStr">
         <is>
           <t>해외주식형</t>
         </is>
       </c>
-      <c r="D128" s="26" t="inlineStr">
+      <c r="E128" s="27" t="inlineStr">
         <is>
           <t>피델리티자산운용</t>
         </is>
       </c>
-      <c r="E128" s="27" t="inlineStr">
+      <c r="F128" s="28" t="inlineStr">
         <is>
           <t>5,716억원</t>
         </is>
       </c>
-      <c r="F128" s="28" t="n">
+      <c r="G128" s="29" t="n">
         <v>0.108062</v>
       </c>
-      <c r="G128" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H128" s="27" t="inlineStr">
+      <c r="H128" s="28" t="inlineStr">
         <is>
           <t>0.16~1.36%</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="15" t="inlineStr">
+      <c r="A129" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B129" s="15" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B129" s="15" t="inlineStr">
+      <c r="C129" s="15" t="inlineStr">
         <is>
           <t>AB월지급글로벌고수익증권투자신탁[채권-재간접형]</t>
         </is>
       </c>
-      <c r="C129" s="15" t="inlineStr">
+      <c r="D129" s="15" t="inlineStr">
         <is>
           <t>해외채권형</t>
         </is>
       </c>
-      <c r="D129" s="15" t="inlineStr">
+      <c r="E129" s="15" t="inlineStr">
         <is>
           <t>얼라이언스번스틴자산운용</t>
         </is>
       </c>
-      <c r="E129" s="24" t="inlineStr">
+      <c r="F129" s="25" t="inlineStr">
         <is>
           <t>5,462억원</t>
         </is>
       </c>
-      <c r="F129" s="25" t="n">
+      <c r="G129" s="26" t="n">
         <v>0.018373</v>
       </c>
-      <c r="G129" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H129" s="24" t="inlineStr">
+      <c r="H129" s="25" t="inlineStr">
         <is>
           <t>0.17~0.71%</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="26" t="inlineStr">
+      <c r="A130" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B130" s="27" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B130" s="26" t="inlineStr">
+      <c r="C130" s="27" t="inlineStr">
         <is>
           <t>한국투자글로벌전기차&amp;자율주행증권투자신탁(주식)(모)</t>
         </is>
       </c>
-      <c r="C130" s="26" t="inlineStr">
+      <c r="D130" s="27" t="inlineStr">
         <is>
           <t>해외주식형</t>
         </is>
       </c>
-      <c r="D130" s="26" t="inlineStr">
+      <c r="E130" s="27" t="inlineStr">
         <is>
           <t>한국투자신탁운용</t>
         </is>
       </c>
-      <c r="E130" s="27" t="inlineStr">
+      <c r="F130" s="28" t="inlineStr">
         <is>
           <t>4,762억원</t>
         </is>
       </c>
-      <c r="F130" s="28" t="n">
+      <c r="G130" s="29" t="n">
         <v>0.178201</v>
       </c>
-      <c r="G130" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H130" s="27" t="inlineStr">
+      <c r="H130" s="28" t="inlineStr">
         <is>
           <t>0.77~2.07%</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="15" t="inlineStr">
+      <c r="A131" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B131" s="15" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B131" s="15" t="inlineStr">
+      <c r="C131" s="15" t="inlineStr">
         <is>
           <t>AB미국그로스증권투자신탁(주식-재간접형)</t>
         </is>
       </c>
-      <c r="C131" s="15" t="inlineStr">
+      <c r="D131" s="15" t="inlineStr">
         <is>
           <t>해외주식형</t>
         </is>
       </c>
-      <c r="D131" s="15" t="inlineStr">
+      <c r="E131" s="15" t="inlineStr">
         <is>
           <t>얼라이언스번스틴자산운용</t>
         </is>
       </c>
-      <c r="E131" s="24" t="inlineStr">
+      <c r="F131" s="25" t="inlineStr">
         <is>
           <t>4,438억원</t>
         </is>
       </c>
-      <c r="F131" s="25" t="n">
+      <c r="G131" s="26" t="n">
         <v>0.009127</v>
       </c>
-      <c r="G131" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H131" s="24" t="inlineStr">
+      <c r="H131" s="25" t="inlineStr">
         <is>
           <t>0.17~1.67%</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="26" t="inlineStr">
+      <c r="A132" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B132" s="27" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B132" s="26" t="inlineStr">
+      <c r="C132" s="27" t="inlineStr">
         <is>
           <t>KB다이나믹적격TDF2030증권자투자신탁(주식혼합-재간접형)(운용)</t>
         </is>
       </c>
-      <c r="C132" s="26" t="inlineStr">
+      <c r="D132" s="27" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="D132" s="26" t="inlineStr">
+      <c r="E132" s="27" t="inlineStr">
         <is>
           <t>케이비자산운용</t>
         </is>
       </c>
-      <c r="E132" s="27" t="inlineStr">
+      <c r="F132" s="28" t="inlineStr">
         <is>
           <t>4,156억원</t>
         </is>
       </c>
-      <c r="F132" s="28" t="n">
+      <c r="G132" s="29" t="n">
         <v>0.189953</v>
       </c>
-      <c r="G132" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H132" s="27" t="inlineStr">
+      <c r="H132" s="28" t="inlineStr">
         <is>
           <t>0.24~1.19%</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="15" t="inlineStr">
+      <c r="A133" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B133" s="15" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B133" s="15" t="inlineStr">
+      <c r="C133" s="15" t="inlineStr">
         <is>
           <t>우리미국단기채공모주증권자투자신탁 1(H)(채권혼합)</t>
         </is>
       </c>
-      <c r="C133" s="15" t="inlineStr">
+      <c r="D133" s="15" t="inlineStr">
         <is>
           <t>해외혼합형</t>
         </is>
       </c>
-      <c r="D133" s="15" t="inlineStr">
+      <c r="E133" s="15" t="inlineStr">
         <is>
           <t>우리자산운용</t>
         </is>
       </c>
-      <c r="E133" s="24" t="inlineStr">
+      <c r="F133" s="25" t="inlineStr">
         <is>
           <t>3,558억원</t>
         </is>
       </c>
-      <c r="F133" s="25" t="n">
+      <c r="G133" s="26" t="n">
         <v>0.052435</v>
       </c>
-      <c r="G133" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H133" s="24" t="inlineStr">
+      <c r="H133" s="25" t="inlineStr">
         <is>
           <t>0.80~1.70%</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="26" t="inlineStr">
+      <c r="A134" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B134" s="27" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B134" s="26" t="inlineStr">
+      <c r="C134" s="27" t="inlineStr">
         <is>
           <t>한국투자미국장기국채증권자투자신탁H(채권-재간접형)(모)</t>
         </is>
       </c>
-      <c r="C134" s="26" t="inlineStr">
+      <c r="D134" s="27" t="inlineStr">
         <is>
           <t>해외채권형</t>
         </is>
       </c>
-      <c r="D134" s="26" t="inlineStr">
+      <c r="E134" s="27" t="inlineStr">
         <is>
           <t>한국투자신탁운용</t>
         </is>
       </c>
-      <c r="E134" s="27" t="inlineStr">
+      <c r="F134" s="28" t="inlineStr">
         <is>
           <t>3,124억원</t>
         </is>
       </c>
-      <c r="F134" s="28" t="n">
+      <c r="G134" s="29" t="n">
         <v>-0.063263</v>
       </c>
-      <c r="G134" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H134" s="27" t="inlineStr">
+      <c r="H134" s="28" t="inlineStr">
         <is>
           <t>0.25~0.85%</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="15" t="inlineStr">
+      <c r="A135" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B135" s="15" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B135" s="15" t="inlineStr">
+      <c r="C135" s="15" t="inlineStr">
         <is>
           <t>신한마음편한적격TDF2050증권자투자신탁[주식혼합-재간접형](종류)</t>
         </is>
       </c>
-      <c r="C135" s="15" t="inlineStr">
+      <c r="D135" s="15" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="D135" s="15" t="inlineStr">
+      <c r="E135" s="15" t="inlineStr">
         <is>
           <t>신한자산운용</t>
         </is>
       </c>
-      <c r="E135" s="24" t="inlineStr">
+      <c r="F135" s="25" t="inlineStr">
         <is>
           <t>3,079억원</t>
         </is>
       </c>
-      <c r="F135" s="25" t="n">
+      <c r="G135" s="26" t="n">
         <v>0.23546</v>
       </c>
-      <c r="G135" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H135" s="24" t="inlineStr">
+      <c r="H135" s="25" t="inlineStr">
         <is>
           <t>0.56~1.31%</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="26" t="inlineStr">
+      <c r="A136" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B136" s="27" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B136" s="26" t="inlineStr">
+      <c r="C136" s="27" t="inlineStr">
         <is>
           <t>신한마음편한적격TDF2035증권자투자신탁[주식혼합-재간접형](종류)</t>
         </is>
       </c>
-      <c r="C136" s="26" t="inlineStr">
+      <c r="D136" s="27" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="D136" s="26" t="inlineStr">
+      <c r="E136" s="27" t="inlineStr">
         <is>
           <t>신한자산운용</t>
         </is>
       </c>
-      <c r="E136" s="27" t="inlineStr">
+      <c r="F136" s="28" t="inlineStr">
         <is>
           <t>3,055억원</t>
         </is>
       </c>
-      <c r="F136" s="28" t="n">
+      <c r="G136" s="29" t="n">
         <v>0.177612</v>
       </c>
-      <c r="G136" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H136" s="27" t="inlineStr">
+      <c r="H136" s="28" t="inlineStr">
         <is>
           <t>0.33~0.82%</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="15" t="inlineStr">
+      <c r="A137" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B137" s="15" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B137" s="15" t="inlineStr">
+      <c r="C137" s="15" t="inlineStr">
         <is>
           <t>신한미국S&amp;P500인덱스증권자투자신탁(UH)[주식-파생형]</t>
         </is>
       </c>
-      <c r="C137" s="15" t="inlineStr">
+      <c r="D137" s="15" t="inlineStr">
         <is>
           <t>해외주식형</t>
         </is>
       </c>
-      <c r="D137" s="15" t="inlineStr">
+      <c r="E137" s="15" t="inlineStr">
         <is>
           <t>신한자산운용</t>
         </is>
       </c>
-      <c r="E137" s="24" t="inlineStr">
+      <c r="F137" s="25" t="inlineStr">
         <is>
           <t>2,851억원</t>
         </is>
       </c>
-      <c r="F137" s="25" t="n">
+      <c r="G137" s="26" t="n">
         <v>0.141662</v>
       </c>
-      <c r="G137" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H137" s="24" t="inlineStr">
+      <c r="H137" s="25" t="inlineStr">
         <is>
           <t>0.26~1.15%</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="26" t="inlineStr">
+      <c r="A138" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B138" s="27" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B138" s="26" t="inlineStr">
+      <c r="C138" s="27" t="inlineStr">
         <is>
           <t>삼성글로벌액티브적격TDF2030증권투자신탁H[주식혼합-재간접형]</t>
         </is>
       </c>
-      <c r="C138" s="26" t="inlineStr">
+      <c r="D138" s="27" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="D138" s="26" t="inlineStr">
+      <c r="E138" s="27" t="inlineStr">
         <is>
           <t>삼성자산운용</t>
         </is>
       </c>
-      <c r="E138" s="27" t="inlineStr">
+      <c r="F138" s="28" t="inlineStr">
         <is>
           <t>2,841억원</t>
         </is>
       </c>
-      <c r="F138" s="28" t="n">
+      <c r="G138" s="29" t="n">
         <v>0.097423</v>
       </c>
-      <c r="G138" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H138" s="27" t="inlineStr">
+      <c r="H138" s="28" t="inlineStr">
         <is>
           <t>0.23~0.76%</t>
         </is>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="15" t="inlineStr">
+      <c r="A139" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B139" s="15" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B139" s="15" t="inlineStr">
+      <c r="C139" s="15" t="inlineStr">
         <is>
           <t>NH-Amundi하나로적격TDF2030증권투자신탁[주식혼합-재간접형]</t>
         </is>
       </c>
-      <c r="C139" s="15" t="inlineStr">
+      <c r="D139" s="15" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="D139" s="15" t="inlineStr">
+      <c r="E139" s="15" t="inlineStr">
         <is>
           <t>엔에이치아문디자산운용</t>
         </is>
       </c>
-      <c r="E139" s="24" t="inlineStr">
+      <c r="F139" s="25" t="inlineStr">
         <is>
           <t>2,746억원</t>
         </is>
       </c>
-      <c r="F139" s="25" t="n">
+      <c r="G139" s="26" t="n">
         <v>0.110507</v>
       </c>
-      <c r="G139" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H139" s="24" t="inlineStr">
+      <c r="H139" s="25" t="inlineStr">
         <is>
           <t>0.35~0.80%</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="26" t="inlineStr">
+      <c r="A140" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B140" s="27" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B140" s="26" t="inlineStr">
+      <c r="C140" s="27" t="inlineStr">
         <is>
           <t>한국투자MAN다이나믹인컴월배당증권자투자신탁H(채권-재간접형)(모)</t>
         </is>
       </c>
-      <c r="C140" s="26" t="inlineStr">
+      <c r="D140" s="27" t="inlineStr">
         <is>
           <t>해외채권형</t>
         </is>
       </c>
-      <c r="D140" s="26" t="inlineStr">
+      <c r="E140" s="27" t="inlineStr">
         <is>
           <t>한국투자신탁운용</t>
         </is>
       </c>
-      <c r="E140" s="27" t="inlineStr">
+      <c r="F140" s="28" t="inlineStr">
         <is>
           <t>2,725억원</t>
         </is>
       </c>
-      <c r="F140" s="28" t="n">
+      <c r="G140" s="29" t="n">
         <v>0.06779</v>
       </c>
-      <c r="G140" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H140" s="27" t="inlineStr">
+      <c r="H140" s="28" t="inlineStr">
         <is>
           <t>0.54~1.24%</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="15" t="inlineStr">
+      <c r="A141" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B141" s="15" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B141" s="15" t="inlineStr">
+      <c r="C141" s="15" t="inlineStr">
         <is>
           <t>KB다이나믹적격TDF2040증권자투자신탁(주식혼합-재간접형)(운용)</t>
         </is>
       </c>
-      <c r="C141" s="15" t="inlineStr">
+      <c r="D141" s="15" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="D141" s="15" t="inlineStr">
+      <c r="E141" s="15" t="inlineStr">
         <is>
           <t>케이비자산운용</t>
         </is>
       </c>
-      <c r="E141" s="24" t="inlineStr">
+      <c r="F141" s="25" t="inlineStr">
         <is>
           <t>2,531억원</t>
         </is>
       </c>
-      <c r="F141" s="25" t="n">
+      <c r="G141" s="26" t="n">
         <v>0.235043</v>
       </c>
-      <c r="G141" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H141" s="24" t="inlineStr">
+      <c r="H141" s="25" t="inlineStr">
         <is>
           <t>0.34~1.19%</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="26" t="inlineStr">
+      <c r="A142" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B142" s="27" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B142" s="26" t="inlineStr">
+      <c r="C142" s="27" t="inlineStr">
         <is>
           <t>KCGI샐러리맨증권자투자신탁[주식-재간접형]</t>
         </is>
       </c>
-      <c r="C142" s="26" t="inlineStr">
+      <c r="D142" s="27" t="inlineStr">
         <is>
           <t>해외주식형</t>
         </is>
       </c>
-      <c r="D142" s="26" t="inlineStr">
+      <c r="E142" s="27" t="inlineStr">
         <is>
           <t>케이씨지아이자산운용</t>
         </is>
       </c>
-      <c r="E142" s="27" t="inlineStr">
+      <c r="F142" s="28" t="inlineStr">
         <is>
           <t>2,524억원</t>
         </is>
       </c>
-      <c r="F142" s="28" t="n">
+      <c r="G142" s="29" t="n">
         <v>0.313328</v>
       </c>
-      <c r="G142" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H142" s="27" t="inlineStr">
+      <c r="H142" s="28" t="inlineStr">
         <is>
           <t>0.64~1.01%</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="15" t="inlineStr">
+      <c r="A143" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B143" s="15" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B143" s="15" t="inlineStr">
+      <c r="C143" s="15" t="inlineStr">
         <is>
           <t>NH-Amundi올바른지구OCIO자산배분증권자투자신탁[혼합-재간접형]</t>
         </is>
       </c>
-      <c r="C143" s="15" t="inlineStr">
+      <c r="D143" s="15" t="inlineStr">
         <is>
           <t>해외혼합형</t>
         </is>
       </c>
-      <c r="D143" s="15" t="inlineStr">
+      <c r="E143" s="15" t="inlineStr">
         <is>
           <t>엔에이치아문디자산운용</t>
         </is>
       </c>
-      <c r="E143" s="24" t="inlineStr">
+      <c r="F143" s="25" t="inlineStr">
         <is>
           <t>2,519억원</t>
         </is>
       </c>
-      <c r="F143" s="25" t="n">
+      <c r="G143" s="26" t="n">
         <v>0.06297700000000001</v>
       </c>
-      <c r="G143" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H143" s="24" t="inlineStr">
+      <c r="H143" s="25" t="inlineStr">
         <is>
           <t>0.41~1.01%</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="26" t="inlineStr">
+      <c r="A144" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B144" s="27" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B144" s="26" t="inlineStr">
+      <c r="C144" s="27" t="inlineStr">
         <is>
           <t>KB다이나믹적격TDF2050증권자투자신탁(주식혼합-재간접형)(운용)</t>
         </is>
       </c>
-      <c r="C144" s="26" t="inlineStr">
+      <c r="D144" s="27" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="D144" s="26" t="inlineStr">
+      <c r="E144" s="27" t="inlineStr">
         <is>
           <t>케이비자산운용</t>
         </is>
       </c>
-      <c r="E144" s="27" t="inlineStr">
+      <c r="F144" s="28" t="inlineStr">
         <is>
           <t>2,349억원</t>
         </is>
       </c>
-      <c r="F144" s="28" t="n">
+      <c r="G144" s="29" t="n">
         <v>0.257195</v>
       </c>
-      <c r="G144" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H144" s="27" t="inlineStr">
+      <c r="H144" s="28" t="inlineStr">
         <is>
           <t>0.34~1.19%</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="15" t="inlineStr">
+      <c r="A145" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B145" s="15" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B145" s="15" t="inlineStr">
+      <c r="C145" s="15" t="inlineStr">
         <is>
           <t>신한마음편한적격TDF2030증권자투자신탁[주식혼합-재간접형](종류)</t>
         </is>
       </c>
-      <c r="C145" s="15" t="inlineStr">
+      <c r="D145" s="15" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="D145" s="15" t="inlineStr">
+      <c r="E145" s="15" t="inlineStr">
         <is>
           <t>신한자산운용</t>
         </is>
       </c>
-      <c r="E145" s="24" t="inlineStr">
+      <c r="F145" s="25" t="inlineStr">
         <is>
           <t>2,312억원</t>
         </is>
       </c>
-      <c r="F145" s="25" t="n">
+      <c r="G145" s="26" t="n">
         <v>0.149587</v>
       </c>
-      <c r="G145" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H145" s="24" t="inlineStr">
+      <c r="H145" s="25" t="inlineStr">
         <is>
           <t>0.33~0.82%</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="26" t="inlineStr">
+      <c r="A146" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B146" s="27" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B146" s="26" t="inlineStr">
+      <c r="C146" s="27" t="inlineStr">
         <is>
           <t>삼성글로벌액티브적격TDF2045증권투자신탁H[주식혼합-재간접형]</t>
         </is>
       </c>
-      <c r="C146" s="26" t="inlineStr">
+      <c r="D146" s="27" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="D146" s="26" t="inlineStr">
+      <c r="E146" s="27" t="inlineStr">
         <is>
           <t>삼성자산운용</t>
         </is>
       </c>
-      <c r="E146" s="27" t="inlineStr">
+      <c r="F146" s="28" t="inlineStr">
         <is>
           <t>2,287억원</t>
         </is>
       </c>
-      <c r="F146" s="28" t="n">
+      <c r="G146" s="29" t="n">
         <v>0.146997</v>
       </c>
-      <c r="G146" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H146" s="27" t="inlineStr">
+      <c r="H146" s="28" t="inlineStr">
         <is>
           <t>0.33~1.30%</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="15" t="inlineStr">
+      <c r="A147" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B147" s="15" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B147" s="15" t="inlineStr">
+      <c r="C147" s="15" t="inlineStr">
         <is>
           <t>KCGI프리덤적격TDF2050증권자투자신탁[주식혼합-재간접형]</t>
         </is>
       </c>
-      <c r="C147" s="15" t="inlineStr">
+      <c r="D147" s="15" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="D147" s="15" t="inlineStr">
+      <c r="E147" s="15" t="inlineStr">
         <is>
           <t>케이씨지아이자산운용</t>
         </is>
       </c>
-      <c r="E147" s="24" t="inlineStr">
+      <c r="F147" s="25" t="inlineStr">
         <is>
           <t>2,285억원</t>
         </is>
       </c>
-      <c r="F147" s="25" t="n">
+      <c r="G147" s="26" t="n">
         <v>0.223357</v>
       </c>
-      <c r="G147" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H147" s="24" t="inlineStr">
+      <c r="H147" s="25" t="inlineStr">
         <is>
           <t>0.56~0.89%</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="26" t="inlineStr">
+      <c r="A148" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B148" s="27" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B148" s="26" t="inlineStr">
+      <c r="C148" s="27" t="inlineStr">
         <is>
           <t>키움키워드림적격TDF2030증권투자신탁 1[혼합-재간접형]</t>
         </is>
       </c>
-      <c r="C148" s="26" t="inlineStr">
+      <c r="D148" s="27" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="D148" s="26" t="inlineStr">
+      <c r="E148" s="27" t="inlineStr">
         <is>
           <t>키움투자자산운용</t>
         </is>
       </c>
-      <c r="E148" s="27" t="inlineStr">
+      <c r="F148" s="28" t="inlineStr">
         <is>
           <t>2,261억원</t>
         </is>
       </c>
-      <c r="F148" s="28" t="n">
+      <c r="G148" s="29" t="n">
         <v>0.079793</v>
       </c>
-      <c r="G148" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H148" s="27" t="inlineStr">
+      <c r="H148" s="28" t="inlineStr">
         <is>
           <t>0.28~0.66%</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="15" t="inlineStr">
+      <c r="A149" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B149" s="15" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B149" s="15" t="inlineStr">
+      <c r="C149" s="15" t="inlineStr">
         <is>
           <t>이지스글로벌공모부동산투자신탁281(파생형)</t>
         </is>
       </c>
-      <c r="C149" s="15" t="inlineStr">
+      <c r="D149" s="15" t="inlineStr">
         <is>
           <t>해외대체</t>
         </is>
       </c>
-      <c r="D149" s="15" t="inlineStr">
+      <c r="E149" s="15" t="inlineStr">
         <is>
           <t>이지스자산운용</t>
         </is>
       </c>
-      <c r="E149" s="24" t="inlineStr">
+      <c r="F149" s="25" t="inlineStr">
         <is>
           <t>2,237억원</t>
         </is>
       </c>
-      <c r="F149" s="25" t="n">
+      <c r="G149" s="26" t="n">
         <v>-0.145053</v>
       </c>
-      <c r="G149" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H149" s="29" t="n">
+      <c r="H149" s="30" t="n">
         <v>0.0054</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="26" t="inlineStr">
+      <c r="A150" s="14" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B150" s="27" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B150" s="26" t="inlineStr">
+      <c r="C150" s="27" t="inlineStr">
         <is>
           <t>한화LIFEPLUS적격TDF2050증권자투자신탁(주식혼합-재간접형)</t>
         </is>
       </c>
-      <c r="C150" s="26" t="inlineStr">
+      <c r="D150" s="27" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="D150" s="26" t="inlineStr">
+      <c r="E150" s="27" t="inlineStr">
         <is>
           <t>한화자산운용</t>
         </is>
       </c>
-      <c r="E150" s="27" t="inlineStr">
+      <c r="F150" s="28" t="inlineStr">
         <is>
           <t>2,233억원</t>
         </is>
       </c>
-      <c r="F150" s="28" t="n">
+      <c r="G150" s="29" t="n">
         <v>0.229434</v>
       </c>
-      <c r="G150" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H150" s="27" t="inlineStr">
+      <c r="H150" s="28" t="inlineStr">
         <is>
           <t>0.44~1.33%</t>
         </is>
@@ -7913,12 +8114,12 @@
           <t>펀드</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>네이버 Npay 증권 + 금융투자협회 전자공시(투자지역)</t>
         </is>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="25" t="n">
         <v>1051</v>
       </c>
       <c r="D5" s="15" t="inlineStr">
@@ -7926,7 +8127,7 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E5" s="31" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>보수는 클래스마다 달라 하나로 줄이지 않고 범위(feeMin~feeMax)로 싣습니다. 변동성·최대낙폭은 기준가 이력이 7 거래일뿐이라 셈하지 않고 위험등급을 씁니다.</t>
         </is>
@@ -7938,12 +8139,12 @@
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>야후 파이낸스 일봉 (자료 가지 kr100-data)</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="25" t="n">
         <v>100</v>
       </c>
       <c r="D6" s="15" t="inlineStr">
@@ -7951,7 +8152,7 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E6" s="31" t="inlineStr"/>
+      <c r="E6" s="32" t="inlineStr"/>
     </row>
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
@@ -7959,12 +8160,12 @@
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="32" t="inlineStr">
         <is>
           <t>야후 파이낸스 일봉 (자료 가지 us100-data)</t>
         </is>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="25" t="n">
         <v>100</v>
       </c>
       <c r="D7" s="15" t="inlineStr">
@@ -7972,7 +8173,7 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr"/>
+      <c r="E7" s="32" t="inlineStr"/>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
@@ -7980,12 +8181,12 @@
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="32" t="inlineStr">
         <is>
           <t>네이버 금융 일봉 + 야후 차트 일봉(close, 배당 미보정) + ETFCHECK (https://www.etfcheck.co.kr)</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="25" t="n">
         <v>247</v>
       </c>
       <c r="D8" s="15" t="inlineStr">
@@ -7993,7 +8194,7 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E8" s="31" t="inlineStr"/>
+      <c r="E8" s="32" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
@@ -8001,12 +8202,12 @@
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B9" s="31" t="inlineStr">
+      <c r="B9" s="32" t="inlineStr">
         <is>
           <t>한국투자증권 오픈API (모의투자, HHDFS76240000, 수정주가)</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="25" t="n">
         <v>19</v>
       </c>
       <c r="D9" s="15" t="inlineStr">
@@ -8014,10 +8215,10 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="E9" s="31" t="inlineStr"/>
+      <c r="E9" s="32" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>이 자료가 지키는 규칙</t>
         </is>
@@ -8029,7 +8230,7 @@
           <t>수익률계열</t>
         </is>
       </c>
-      <c r="B13" s="33" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>주식·ETF 는 일봉에서 직접 셈합니다(최근 252 거래일). 펀드는 원천이 주는 1 년 수익률을 씁니다 — 두 계열은 기준일이 다를 수 있으므로 상품마다 asOf 를 답니다.</t>
         </is>
@@ -8041,7 +8242,7 @@
           <t>변동성</t>
         </is>
       </c>
-      <c r="B14" s="33" t="inlineStr">
+      <c r="B14" s="34" t="inlineStr">
         <is>
           <t>일봉이 있는 상품만 연변동성(일간 로그수익률 표준편차 × √252)을 셈합니다. 펀드는 이력이 7 거래일뿐이라 셈하지 않고 원천의 위험등급을 씁니다.</t>
         </is>
@@ -8053,7 +8254,7 @@
           <t>펀드보수</t>
         </is>
       </c>
-      <c r="B15" s="33" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>클래스마다 달라 하나로 줄이지 않고 범위로 싣습니다.</t>
         </is>
@@ -8065,7 +8266,7 @@
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B16" s="33" t="inlineStr">
+      <c r="B16" s="34" t="inlineStr">
         <is>
           <t>해외에 설정된 뮤추얼펀드가 아니라 해외에 투자하는, 국내 설정 공모펀드입니다.</t>
         </is>
@@ -8077,7 +8278,7 @@
           <t>최소설정액</t>
         </is>
       </c>
-      <c r="B17" s="33" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>10000000000</t>
         </is>
@@ -8124,76 +8325,76 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="18" customHeight="1">
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="35" t="inlineStr">
         <is>
           <t>1. 「제안서」 시트에서 파란 글씨 칸만 고칩니다 — 고객명·투자금액·투자기간·위험성향.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>2. 나머지 칸은 수식입니다. 손으로 덮어쓰면 다음에 값이 안 따라옵니다.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>3. 「배분규칙」 시트는 proposal_lib.py 가 셈한 것입니다. 고치지 마십시오 — 고치면 화면(proposal.html)·PPT 와 어긋납니다.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>4. 「기대수익률 (가정)」 칸은 비워 두었습니다. 사람이 넣는 가정이며 기본값을 두지 않았습니다 — 넣으실 때 근거를 함께 적어 두십시오.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>5. 자료를 새로 받으면 python3 scripts/build_proposal_universe.py 를 돌린 뒤 이 파일을 다시 만듭니다.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="8" customHeight="1">
-      <c r="B9" s="34" t="inlineStr"/>
+      <c r="B9" s="35" t="inlineStr"/>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="35" t="inlineStr">
         <is>
           <t>셀 색 규칙 (기존 고객제안서와 같습니다)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">      파란 글씨 + 옅은 칠 = 사람이 넣는 칸</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">      검은 글씨            = 수식</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">      회색 글씨            = 원천에서 받아 적은 값</t>
         </is>
       </c>
     </row>
     <row r="14" ht="8" customHeight="1">
-      <c r="B14" s="34" t="inlineStr"/>
+      <c r="B14" s="35" t="inlineStr"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="35" t="inlineStr">
         <is>
           <t>숨은 G·H 열은 합계를 셈하려고 둔 도우미 칸입니다. 표시 칸에 「—」라는 글자가 들어가면 합계가 깨지기 때문입니다. 지우지 마십시오.</t>
         </is>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -1287,7 +1287,7 @@
     <row r="52">
       <c r="A52" s="21" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-19 10:59:20 · 문서 2026-09-19 11:00 (KST)</t>
+          <t>유니버스 2026-09-19 10:59:20 · 문서 2026-09-19 11:34 (KST)</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
     <row r="1">
       <c r="A1" s="21" t="inlineStr">
         <is>
-          <t>이 시트는 proposal_lib.py 가 셈한 배분입니다. 손으로 고치지 마십시오 — 고치면 화면·PPT 와 어긋납니다.</t>
+          <t>이 시트는 proposal_lib.py 가 셈한 배분입니다. 손으로 고치지 마십시오 — 고치면 화면(proposal.html)과 어긋납니다.</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
     <row r="8" ht="18" customHeight="1">
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>3. 「배분규칙」 시트는 proposal_lib.py 가 셈한 것입니다. 고치지 마십시오 — 고치면 화면(proposal.html)·PPT 와 어긋납니다.</t>
+          <t>3. 「배분규칙」 시트는 proposal_lib.py 가 셈한 것입니다. 고치지 마십시오 — 고치면 화면(proposal.html)과 어긋납니다.</t>
         </is>
       </c>
     </row>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -12,10 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산군" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상품" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'상품'!$A$7:$H$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'상품'!$A$7:$H$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,9 +24,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0%;-0.0%"/>
+    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.0%;-0.0%"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -132,7 +134,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -159,11 +161,55 @@
         <color rgb="00F58220"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E5E4E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E5E4E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E4E1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E5E4E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E4E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E5E4E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E4E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E4E1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -199,6 +245,9 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -216,7 +265,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -251,6 +300,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -862,12 +919,14 @@
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A19,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="G19" s="9" t="n"/>
+      <c r="G19" s="17" t="n">
+        <v>0.0781</v>
+      </c>
       <c r="H19" s="15">
         <f>IF(ISNUMBER($F19),$F19,0)</f>
         <v/>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="18">
         <f>IF(AND($A19&lt;&gt;"현금",ISNUMBER($G19)),5,0)</f>
         <v/>
       </c>
@@ -895,12 +954,14 @@
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A20,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="G20" s="9" t="n"/>
+      <c r="G20" s="17" t="n">
+        <v>0.0781</v>
+      </c>
       <c r="H20" s="15">
         <f>IF(ISNUMBER($F20),$F20,0)</f>
         <v/>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="18">
         <f>IF(AND($A20&lt;&gt;"현금",ISNUMBER($G20)),10,0)</f>
         <v/>
       </c>
@@ -928,12 +989,14 @@
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A21,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="G21" s="9" t="n"/>
+      <c r="G21" s="17" t="n">
+        <v>0.0493</v>
+      </c>
       <c r="H21" s="15">
         <f>IF(ISNUMBER($F21),$F21,0)</f>
         <v/>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="18">
         <f>IF(AND($A21&lt;&gt;"현금",ISNUMBER($G21)),15,0)</f>
         <v/>
       </c>
@@ -961,12 +1024,14 @@
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A22,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="G22" s="9" t="n"/>
+      <c r="G22" s="17" t="n">
+        <v>0.0561</v>
+      </c>
       <c r="H22" s="15">
         <f>IF(ISNUMBER($F22),$F22,0)</f>
         <v/>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="18">
         <f>IF(AND($A22&lt;&gt;"현금",ISNUMBER($G22)),15,0)</f>
         <v/>
       </c>
@@ -994,12 +1059,14 @@
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A23,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="G23" s="9" t="n"/>
+      <c r="G23" s="17" t="n">
+        <v>0.05110000000000001</v>
+      </c>
       <c r="H23" s="15">
         <f>IF(ISNUMBER($F23),$F23,0)</f>
         <v/>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="18">
         <f>IF(AND($A23&lt;&gt;"현금",ISNUMBER($G23)),20,0)</f>
         <v/>
       </c>
@@ -1027,12 +1094,14 @@
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A24,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="G24" s="9" t="n"/>
+      <c r="G24" s="17" t="n">
+        <v>0.0561</v>
+      </c>
       <c r="H24" s="15">
         <f>IF(ISNUMBER($F24),$F24,0)</f>
         <v/>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="18">
         <f>IF(AND($A24&lt;&gt;"현금",ISNUMBER($G24)),20,0)</f>
         <v/>
       </c>
@@ -1060,58 +1129,60 @@
         <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A25,자산군!$A$7:$A$12,0)),"—")</f>
         <v/>
       </c>
-      <c r="G25" s="9" t="n"/>
+      <c r="G25" s="17" t="n">
+        <v>0.0281</v>
+      </c>
       <c r="H25" s="15">
         <f>IF(ISNUMBER($F25),$F25,0)</f>
         <v/>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="18">
         <f>IF(AND($A25&lt;&gt;"현금",ISNUMBER($G25)),15,0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B26" s="19">
+      <c r="B26" s="20">
         <f>SUM($B19:$B25)</f>
         <v/>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <f>IF(COUNT($C19:$C25)=0,"—",SUM($C19:$C25))</f>
         <v/>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <f>SUM($D19:$D25)</f>
         <v/>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="21">
         <f>SUM($E19:$E25)</f>
         <v/>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="20">
         <f>SUMPRODUCT($D19:$D25,$H19:$H25)</f>
         <v/>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="20">
         <f>IF(COUNT($G19:$G25)=0,"가정 미입력",SUMPRODUCT($D19:$D25,$G19:$G25))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
         <is>
           <t>점검</t>
         </is>
       </c>
-      <c r="B27" s="22">
+      <c r="B27" s="23">
         <f>IF($H$2="","조회 조건에서 「▶ 조회 실행」을 고르시면 배분이 나옵니다",IF(ABS($D26-1)&gt;0.0005,"비중 합계가 100% 가 아닙니다 — 조정 비중을 맞추십시오","비중 합계 100% 입니다"))</f>
         <v/>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="24">
         <f>COUNT($G19:$G25)&amp;" / 7 가정"</f>
         <v/>
       </c>
@@ -1166,7 +1237,7 @@
           <t>차이 (기대 − 목표)</t>
         </is>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="25">
         <f>IF(OR($B$12="",COUNT($G19:$G25)=0),"—",$G26-$B$12)</f>
         <v/>
       </c>
@@ -1194,13 +1265,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="25">
+      <c r="A37" s="26">
         <f>IF($B$12="","목표 연수익률을 넣으시면 견주어 드립니다.",IF(COUNT($G19:$G25)=0,"자산군별 기대수익률 가정을 넣으셔야 견줄 수 있습니다.",IF($H$5="","가정한 위험자산 기대수익률이 현금보다 높지 않아 역산할 수 없습니다.",IF($H$5&gt;=1,"목표는 현금을 0 으로 해도 닿지 않습니다 — 목표를 낮추거나 가정을 다시 보십시오.",IF($G26&gt;=$B$12,"가정대로라면 목표를 웃돕니다.","가정대로라면 목표에 모자랍니다 — 목표를 낮추거나 위험자산을 늘려야 합니다.")))))</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="26" t="inlineStr">
+      <c r="A38" s="27" t="inlineStr">
         <is>
           <t>⚠ 역산은 「목표를 올리면 위험자산이 이만큼 늘어난다」는 산수일 뿐, 그렇게 하면 목표를 번다는 뜻이 아닙니다. 위험자산 안의 구성은 위험중립형 비율을 그대로 씁니다 — 목표를 맞추려고 한 자산군에 몰아주면 분산이 깨집니다.</t>
         </is>
@@ -1229,65 +1300,65 @@
     </row>
     <row r="42" ht="6" customHeight="1"/>
     <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="26" t="inlineStr">
+      <c r="A43" s="27" t="inlineStr">
         <is>
           <t>· 「기대수익률 (가정)」은 비어 있습니다. 사람이 넣는 칸이며 기본값을 두지 않았습니다 — 넣으실 때 근거를 함께 적어 두십시오.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="26" t="inlineStr">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>· 「과거 1년」을 「기대수익률」 칸에 복사해 넣지 마십시오. 「지난해처럼 오른다」고 가정하는 것이 됩니다.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="26" t="inlineStr">
+      <c r="A45" s="27" t="inlineStr">
         <is>
           <t>· 기대수익률 합계는 빈 칸을 0 으로 셈합니다. 일부만 넣으면 그만큼 낮게 나오므로 아래 「가정 넣은 자산군」 수를 함께 보십시오.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="26" t="inlineStr">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>· 「과거 1년」은 실제로 잰 값이며 미래 수익률이 아닙니다 — 최근 1년이 그랬다는 것과 앞으로 그러리라는 것은 다른 말입니다.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="26" t="inlineStr">
+      <c r="A47" s="27" t="inlineStr">
         <is>
           <t>· 변동성은 상관관계를 셈하지 않은 가중합이라 실제보다 높게 나옵니다. 낮게 보이게 만드는 것보다 안전합니다.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="26" t="inlineStr">
+      <c r="A48" s="27" t="inlineStr">
         <is>
           <t>· 펀드는 이력이 7 거래일뿐이라 변동성을 셈하지 않았습니다. 합계 변동성은 포트폴리오의 일부만 덮습니다 — 「자산군」 시트의 빈칸(—)이 그것입니다.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="26" t="inlineStr">
+      <c r="A49" s="27" t="inlineStr">
         <is>
           <t>· 「해외펀드」는 해외 설정 뮤추얼펀드가 아니라 해외에 투자하는 국내 설정 공모펀드입니다.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="26" t="inlineStr">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>· 이 자료는 참고용이며 투자 권유가 아닙니다. 제안 전 준법감시 검토를 받으십시오.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="21" t="inlineStr">
-        <is>
-          <t>유니버스 2026-09-19 10:59:20 · 문서 2026-09-19 11:34 (KST)</t>
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>유니버스 2026-09-19 12:34:39 · 문서 2026-09-19 12:38 (KST)</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1426,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>이 시트는 proposal_lib.py 가 셈한 배분입니다. 손으로 고치지 마십시오 — 고치면 화면(proposal.html)과 어긋납니다.</t>
         </is>
@@ -1419,7 +1490,7 @@
           <t>1|1</t>
         </is>
       </c>
-      <c r="B4" s="27" t="n">
+      <c r="B4" s="28" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -1427,25 +1498,25 @@
           <t>1년 이내</t>
         </is>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="28" t="n">
+      <c r="E4" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="28" t="n">
+      <c r="F4" s="29" t="n">
         <v>0.02</v>
       </c>
-      <c r="G4" s="28" t="n">
+      <c r="G4" s="29" t="n">
         <v>0.02</v>
       </c>
-      <c r="H4" s="28" t="n">
+      <c r="H4" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="I4" s="28" t="n">
+      <c r="I4" s="29" t="n">
         <v>0.04</v>
       </c>
-      <c r="J4" s="28" t="n">
+      <c r="J4" s="29" t="n">
         <v>0.84</v>
       </c>
     </row>
@@ -1455,7 +1526,7 @@
           <t>1|3</t>
         </is>
       </c>
-      <c r="B5" s="27" t="n">
+      <c r="B5" s="28" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -1463,25 +1534,25 @@
           <t>3년</t>
         </is>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E5" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="29" t="n">
         <v>0.035</v>
       </c>
-      <c r="G5" s="28" t="n">
+      <c r="G5" s="29" t="n">
         <v>0.035</v>
       </c>
-      <c r="H5" s="28" t="n">
+      <c r="H5" s="29" t="n">
         <v>0.14</v>
       </c>
-      <c r="I5" s="28" t="n">
+      <c r="I5" s="29" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="J5" s="28" t="n">
+      <c r="J5" s="29" t="n">
         <v>0.72</v>
       </c>
     </row>
@@ -1491,7 +1562,7 @@
           <t>1|5</t>
         </is>
       </c>
-      <c r="B6" s="27" t="n">
+      <c r="B6" s="28" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="14" t="inlineStr">
@@ -1499,25 +1570,25 @@
           <t>5년</t>
         </is>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="29" t="n">
         <v>0.045</v>
       </c>
-      <c r="G6" s="28" t="n">
+      <c r="G6" s="29" t="n">
         <v>0.045</v>
       </c>
-      <c r="H6" s="28" t="n">
+      <c r="H6" s="29" t="n">
         <v>0.18</v>
       </c>
-      <c r="I6" s="28" t="n">
+      <c r="I6" s="29" t="n">
         <v>0.09</v>
       </c>
-      <c r="J6" s="28" t="n">
+      <c r="J6" s="29" t="n">
         <v>0.64</v>
       </c>
     </row>
@@ -1527,7 +1598,7 @@
           <t>1|10</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
+      <c r="B7" s="28" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -1535,25 +1606,25 @@
           <t>5년 초과</t>
         </is>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F7" s="29" t="n">
         <v>0.05</v>
       </c>
-      <c r="G7" s="28" t="n">
+      <c r="G7" s="29" t="n">
         <v>0.05</v>
       </c>
-      <c r="H7" s="28" t="n">
+      <c r="H7" s="29" t="n">
         <v>0.2</v>
       </c>
-      <c r="I7" s="28" t="n">
+      <c r="I7" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="J7" s="28" t="n">
+      <c r="J7" s="29" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -1563,7 +1634,7 @@
           <t>2|1</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="28" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -1571,25 +1642,25 @@
           <t>1년 이내</t>
         </is>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="E8" s="29" t="n">
         <v>0.02</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="29" t="n">
         <v>0.04</v>
       </c>
-      <c r="G8" s="28" t="n">
+      <c r="G8" s="29" t="n">
         <v>0.04</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="H8" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="I8" s="29" t="n">
         <v>0.06</v>
       </c>
-      <c r="J8" s="28" t="n">
+      <c r="J8" s="29" t="n">
         <v>0.74</v>
       </c>
     </row>
@@ -1599,7 +1670,7 @@
           <t>2|3</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="28" t="n">
         <v>2</v>
       </c>
       <c r="C9" s="14" t="inlineStr">
@@ -1607,25 +1678,25 @@
           <t>3년</t>
         </is>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="28" t="n">
+      <c r="E9" s="29" t="n">
         <v>0.035</v>
       </c>
-      <c r="F9" s="28" t="n">
+      <c r="F9" s="29" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="G9" s="28" t="n">
+      <c r="G9" s="29" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H9" s="28" t="n">
+      <c r="H9" s="29" t="n">
         <v>0.175</v>
       </c>
-      <c r="I9" s="28" t="n">
+      <c r="I9" s="29" t="n">
         <v>0.105</v>
       </c>
-      <c r="J9" s="28" t="n">
+      <c r="J9" s="29" t="n">
         <v>0.545</v>
       </c>
     </row>
@@ -1635,7 +1706,7 @@
           <t>2|5</t>
         </is>
       </c>
-      <c r="B10" s="27" t="n">
+      <c r="B10" s="28" t="n">
         <v>2</v>
       </c>
       <c r="C10" s="14" t="inlineStr">
@@ -1643,25 +1714,25 @@
           <t>5년</t>
         </is>
       </c>
-      <c r="D10" s="28" t="n">
+      <c r="D10" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="28" t="n">
+      <c r="E10" s="29" t="n">
         <v>0.045</v>
       </c>
-      <c r="F10" s="28" t="n">
+      <c r="F10" s="29" t="n">
         <v>0.09</v>
       </c>
-      <c r="G10" s="28" t="n">
+      <c r="G10" s="29" t="n">
         <v>0.09</v>
       </c>
-      <c r="H10" s="28" t="n">
+      <c r="H10" s="29" t="n">
         <v>0.225</v>
       </c>
-      <c r="I10" s="28" t="n">
+      <c r="I10" s="29" t="n">
         <v>0.135</v>
       </c>
-      <c r="J10" s="28" t="n">
+      <c r="J10" s="29" t="n">
         <v>0.415</v>
       </c>
     </row>
@@ -1671,7 +1742,7 @@
           <t>2|10</t>
         </is>
       </c>
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="28" t="n">
         <v>2</v>
       </c>
       <c r="C11" s="14" t="inlineStr">
@@ -1679,25 +1750,25 @@
           <t>5년 초과</t>
         </is>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="28" t="n">
+      <c r="E11" s="29" t="n">
         <v>0.05</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="G11" s="28" t="n">
+      <c r="G11" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="H11" s="28" t="n">
+      <c r="H11" s="29" t="n">
         <v>0.25</v>
       </c>
-      <c r="I11" s="28" t="n">
+      <c r="I11" s="29" t="n">
         <v>0.15</v>
       </c>
-      <c r="J11" s="28" t="n">
+      <c r="J11" s="29" t="n">
         <v>0.35</v>
       </c>
     </row>
@@ -1707,7 +1778,7 @@
           <t>3|1</t>
         </is>
       </c>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="28" t="n">
         <v>3</v>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -1715,25 +1786,25 @@
           <t>1년 이내</t>
         </is>
       </c>
-      <c r="D12" s="28" t="n">
+      <c r="D12" s="29" t="n">
         <v>0.02</v>
       </c>
-      <c r="E12" s="28" t="n">
+      <c r="E12" s="29" t="n">
         <v>0.04</v>
       </c>
-      <c r="F12" s="28" t="n">
+      <c r="F12" s="29" t="n">
         <v>0.06</v>
       </c>
-      <c r="G12" s="28" t="n">
+      <c r="G12" s="29" t="n">
         <v>0.06</v>
       </c>
-      <c r="H12" s="28" t="n">
+      <c r="H12" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="I12" s="28" t="n">
+      <c r="I12" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="J12" s="28" t="n">
+      <c r="J12" s="29" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1743,7 +1814,7 @@
           <t>3|3</t>
         </is>
       </c>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="28" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -1751,25 +1822,25 @@
           <t>3년</t>
         </is>
       </c>
-      <c r="D13" s="28" t="n">
+      <c r="D13" s="29" t="n">
         <v>0.035</v>
       </c>
-      <c r="E13" s="28" t="n">
+      <c r="E13" s="29" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F13" s="29" t="n">
         <v>0.105</v>
       </c>
-      <c r="G13" s="28" t="n">
+      <c r="G13" s="29" t="n">
         <v>0.105</v>
       </c>
-      <c r="H13" s="28" t="n">
+      <c r="H13" s="29" t="n">
         <v>0.14</v>
       </c>
-      <c r="I13" s="28" t="n">
+      <c r="I13" s="29" t="n">
         <v>0.14</v>
       </c>
-      <c r="J13" s="28" t="n">
+      <c r="J13" s="29" t="n">
         <v>0.405</v>
       </c>
     </row>
@@ -1779,7 +1850,7 @@
           <t>3|5</t>
         </is>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="28" t="n">
         <v>3</v>
       </c>
       <c r="C14" s="14" t="inlineStr">
@@ -1787,25 +1858,25 @@
           <t>5년</t>
         </is>
       </c>
-      <c r="D14" s="28" t="n">
+      <c r="D14" s="29" t="n">
         <v>0.045</v>
       </c>
-      <c r="E14" s="28" t="n">
+      <c r="E14" s="29" t="n">
         <v>0.09</v>
       </c>
-      <c r="F14" s="28" t="n">
+      <c r="F14" s="29" t="n">
         <v>0.135</v>
       </c>
-      <c r="G14" s="28" t="n">
+      <c r="G14" s="29" t="n">
         <v>0.135</v>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="H14" s="29" t="n">
         <v>0.18</v>
       </c>
-      <c r="I14" s="28" t="n">
+      <c r="I14" s="29" t="n">
         <v>0.18</v>
       </c>
-      <c r="J14" s="28" t="n">
+      <c r="J14" s="29" t="n">
         <v>0.235</v>
       </c>
     </row>
@@ -1815,7 +1886,7 @@
           <t>3|10</t>
         </is>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="28" t="n">
         <v>3</v>
       </c>
       <c r="C15" s="14" t="inlineStr">
@@ -1823,25 +1894,25 @@
           <t>5년 초과</t>
         </is>
       </c>
-      <c r="D15" s="28" t="n">
+      <c r="D15" s="29" t="n">
         <v>0.05</v>
       </c>
-      <c r="E15" s="28" t="n">
+      <c r="E15" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="F15" s="28" t="n">
+      <c r="F15" s="29" t="n">
         <v>0.15</v>
       </c>
-      <c r="G15" s="28" t="n">
+      <c r="G15" s="29" t="n">
         <v>0.15</v>
       </c>
-      <c r="H15" s="28" t="n">
+      <c r="H15" s="29" t="n">
         <v>0.2</v>
       </c>
-      <c r="I15" s="28" t="n">
+      <c r="I15" s="29" t="n">
         <v>0.2</v>
       </c>
-      <c r="J15" s="28" t="n">
+      <c r="J15" s="29" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -1851,7 +1922,7 @@
           <t>4|1</t>
         </is>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="28" t="n">
         <v>4</v>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -1859,25 +1930,25 @@
           <t>1년 이내</t>
         </is>
       </c>
-      <c r="D16" s="28" t="n">
+      <c r="D16" s="29" t="n">
         <v>0.06</v>
       </c>
-      <c r="E16" s="28" t="n">
+      <c r="E16" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="F16" s="28" t="n">
+      <c r="F16" s="29" t="n">
         <v>0.06</v>
       </c>
-      <c r="G16" s="28" t="n">
+      <c r="G16" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="H16" s="28" t="n">
+      <c r="H16" s="29" t="n">
         <v>0.04</v>
       </c>
-      <c r="I16" s="28" t="n">
+      <c r="I16" s="29" t="n">
         <v>0.06</v>
       </c>
-      <c r="J16" s="28" t="n">
+      <c r="J16" s="29" t="n">
         <v>0.62</v>
       </c>
     </row>
@@ -1887,7 +1958,7 @@
           <t>4|3</t>
         </is>
       </c>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="28" t="n">
         <v>4</v>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -1895,25 +1966,25 @@
           <t>3년</t>
         </is>
       </c>
-      <c r="D17" s="28" t="n">
+      <c r="D17" s="29" t="n">
         <v>0.105</v>
       </c>
-      <c r="E17" s="28" t="n">
+      <c r="E17" s="29" t="n">
         <v>0.14</v>
       </c>
-      <c r="F17" s="28" t="n">
+      <c r="F17" s="29" t="n">
         <v>0.105</v>
       </c>
-      <c r="G17" s="28" t="n">
+      <c r="G17" s="29" t="n">
         <v>0.14</v>
       </c>
-      <c r="H17" s="28" t="n">
+      <c r="H17" s="29" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I17" s="28" t="n">
+      <c r="I17" s="29" t="n">
         <v>0.105</v>
       </c>
-      <c r="J17" s="28" t="n">
+      <c r="J17" s="29" t="n">
         <v>0.335</v>
       </c>
     </row>
@@ -1923,7 +1994,7 @@
           <t>4|5</t>
         </is>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="28" t="n">
         <v>4</v>
       </c>
       <c r="C18" s="14" t="inlineStr">
@@ -1931,25 +2002,25 @@
           <t>5년</t>
         </is>
       </c>
-      <c r="D18" s="28" t="n">
+      <c r="D18" s="29" t="n">
         <v>0.135</v>
       </c>
-      <c r="E18" s="28" t="n">
+      <c r="E18" s="29" t="n">
         <v>0.18</v>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="F18" s="29" t="n">
         <v>0.135</v>
       </c>
-      <c r="G18" s="28" t="n">
+      <c r="G18" s="29" t="n">
         <v>0.18</v>
       </c>
-      <c r="H18" s="28" t="n">
+      <c r="H18" s="29" t="n">
         <v>0.09</v>
       </c>
-      <c r="I18" s="28" t="n">
+      <c r="I18" s="29" t="n">
         <v>0.135</v>
       </c>
-      <c r="J18" s="28" t="n">
+      <c r="J18" s="29" t="n">
         <v>0.145</v>
       </c>
     </row>
@@ -1959,7 +2030,7 @@
           <t>4|10</t>
         </is>
       </c>
-      <c r="B19" s="27" t="n">
+      <c r="B19" s="28" t="n">
         <v>4</v>
       </c>
       <c r="C19" s="14" t="inlineStr">
@@ -1967,25 +2038,25 @@
           <t>5년 초과</t>
         </is>
       </c>
-      <c r="D19" s="28" t="n">
+      <c r="D19" s="29" t="n">
         <v>0.15</v>
       </c>
-      <c r="E19" s="28" t="n">
+      <c r="E19" s="29" t="n">
         <v>0.2</v>
       </c>
-      <c r="F19" s="28" t="n">
+      <c r="F19" s="29" t="n">
         <v>0.15</v>
       </c>
-      <c r="G19" s="28" t="n">
+      <c r="G19" s="29" t="n">
         <v>0.2</v>
       </c>
-      <c r="H19" s="28" t="n">
+      <c r="H19" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="I19" s="28" t="n">
+      <c r="I19" s="29" t="n">
         <v>0.15</v>
       </c>
-      <c r="J19" s="28" t="n">
+      <c r="J19" s="29" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -1995,7 +2066,7 @@
           <t>5|1</t>
         </is>
       </c>
-      <c r="B20" s="27" t="n">
+      <c r="B20" s="28" t="n">
         <v>5</v>
       </c>
       <c r="C20" s="14" t="inlineStr">
@@ -2003,25 +2074,25 @@
           <t>1년 이내</t>
         </is>
       </c>
-      <c r="D20" s="28" t="n">
+      <c r="D20" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="E20" s="28" t="n">
+      <c r="E20" s="29" t="n">
         <v>0.12</v>
       </c>
-      <c r="F20" s="28" t="n">
+      <c r="F20" s="29" t="n">
         <v>0.06</v>
       </c>
-      <c r="G20" s="28" t="n">
+      <c r="G20" s="29" t="n">
         <v>0.08</v>
       </c>
-      <c r="H20" s="28" t="n">
+      <c r="H20" s="29" t="n">
         <v>0.02</v>
       </c>
-      <c r="I20" s="28" t="n">
+      <c r="I20" s="29" t="n">
         <v>0.02</v>
       </c>
-      <c r="J20" s="28" t="n">
+      <c r="J20" s="29" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -2031,7 +2102,7 @@
           <t>5|3</t>
         </is>
       </c>
-      <c r="B21" s="27" t="n">
+      <c r="B21" s="28" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="14" t="inlineStr">
@@ -2039,25 +2110,25 @@
           <t>3년</t>
         </is>
       </c>
-      <c r="D21" s="28" t="n">
+      <c r="D21" s="29" t="n">
         <v>0.175</v>
       </c>
-      <c r="E21" s="28" t="n">
+      <c r="E21" s="29" t="n">
         <v>0.21</v>
       </c>
-      <c r="F21" s="28" t="n">
+      <c r="F21" s="29" t="n">
         <v>0.105</v>
       </c>
-      <c r="G21" s="28" t="n">
+      <c r="G21" s="29" t="n">
         <v>0.14</v>
       </c>
-      <c r="H21" s="28" t="n">
+      <c r="H21" s="29" t="n">
         <v>0.035</v>
       </c>
-      <c r="I21" s="28" t="n">
+      <c r="I21" s="29" t="n">
         <v>0.035</v>
       </c>
-      <c r="J21" s="28" t="n">
+      <c r="J21" s="29" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2067,7 +2138,7 @@
           <t>5|5</t>
         </is>
       </c>
-      <c r="B22" s="27" t="n">
+      <c r="B22" s="28" t="n">
         <v>5</v>
       </c>
       <c r="C22" s="14" t="inlineStr">
@@ -2075,25 +2146,25 @@
           <t>5년</t>
         </is>
       </c>
-      <c r="D22" s="28" t="n">
+      <c r="D22" s="29" t="n">
         <v>0.225</v>
       </c>
-      <c r="E22" s="28" t="n">
+      <c r="E22" s="29" t="n">
         <v>0.27</v>
       </c>
-      <c r="F22" s="28" t="n">
+      <c r="F22" s="29" t="n">
         <v>0.135</v>
       </c>
-      <c r="G22" s="28" t="n">
+      <c r="G22" s="29" t="n">
         <v>0.18</v>
       </c>
-      <c r="H22" s="28" t="n">
+      <c r="H22" s="29" t="n">
         <v>0.045</v>
       </c>
-      <c r="I22" s="28" t="n">
+      <c r="I22" s="29" t="n">
         <v>0.045</v>
       </c>
-      <c r="J22" s="28" t="n">
+      <c r="J22" s="29" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -2103,7 +2174,7 @@
           <t>5|10</t>
         </is>
       </c>
-      <c r="B23" s="27" t="n">
+      <c r="B23" s="28" t="n">
         <v>5</v>
       </c>
       <c r="C23" s="14" t="inlineStr">
@@ -2111,25 +2182,25 @@
           <t>5년 초과</t>
         </is>
       </c>
-      <c r="D23" s="28" t="n">
+      <c r="D23" s="29" t="n">
         <v>0.25</v>
       </c>
-      <c r="E23" s="28" t="n">
+      <c r="E23" s="29" t="n">
         <v>0.3</v>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="F23" s="29" t="n">
         <v>0.15</v>
       </c>
-      <c r="G23" s="28" t="n">
+      <c r="G23" s="29" t="n">
         <v>0.2</v>
       </c>
-      <c r="H23" s="28" t="n">
+      <c r="H23" s="29" t="n">
         <v>0.05</v>
       </c>
-      <c r="I23" s="28" t="n">
+      <c r="I23" s="29" t="n">
         <v>0.05</v>
       </c>
-      <c r="J23" s="28" t="n">
+      <c r="J23" s="29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2179,7 +2250,7 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>아래는 원천에서 실제로 잰 값입니다. 미래 수익률이 아닙니다. 빈칸(—)은 원천에 없어 셈하지 않은 것이며 만들어 넣지 않습니다.</t>
         </is>
@@ -2223,20 +2294,20 @@
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B7" s="27" t="n">
-        <v>247</v>
-      </c>
-      <c r="C7" s="27" t="n">
-        <v>66</v>
-      </c>
-      <c r="D7" s="28" t="n">
-        <v>0.2124918732311036</v>
-      </c>
-      <c r="E7" s="28" t="n">
-        <v>0.1636</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>-0.3638325865485312</v>
+      <c r="B7" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="C7" s="28" t="n">
+        <v>25</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>0.2122905027932962</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>0.23445</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>-0.4063051588931482</v>
       </c>
     </row>
     <row r="8">
@@ -2245,19 +2316,19 @@
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B8" s="27" t="n">
+      <c r="B8" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="29" t="n">
         <v>0.3829843398606768</v>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="E8" s="29" t="n">
         <v>0.5695122538369983</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="29" t="n">
         <v>-0.4675840087252487</v>
       </c>
     </row>
@@ -2267,21 +2338,21 @@
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="B9" s="27" t="n">
-        <v>615</v>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>606</v>
-      </c>
-      <c r="D9" s="28" t="n">
-        <v>0.206671</v>
-      </c>
-      <c r="E9" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="27" t="inlineStr">
+      <c r="B9" s="28" t="n">
+        <v>525</v>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>521</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>0.333284</v>
+      </c>
+      <c r="E9" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2293,20 +2364,20 @@
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B10" s="27" t="n">
-        <v>19</v>
-      </c>
-      <c r="C10" s="27" t="n">
-        <v>19</v>
-      </c>
-      <c r="D10" s="28" t="n">
-        <v>0.1680824723535977</v>
-      </c>
-      <c r="E10" s="28" t="n">
-        <v>0.1542903388794394</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>-0.1653518460082045</v>
+      <c r="B10" s="28" t="n">
+        <v>153</v>
+      </c>
+      <c r="C10" s="28" t="n">
+        <v>60</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>0.1747404299625906</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>0.1769</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <v>-0.2640451703972575</v>
       </c>
     </row>
     <row r="11">
@@ -2315,19 +2386,19 @@
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="28" t="n">
         <v>99</v>
       </c>
-      <c r="D11" s="28" t="n">
+      <c r="D11" s="29" t="n">
         <v>0.1051235812029279</v>
       </c>
-      <c r="E11" s="28" t="n">
+      <c r="E11" s="29" t="n">
         <v>0.2914505456297338</v>
       </c>
-      <c r="F11" s="28" t="n">
+      <c r="F11" s="29" t="n">
         <v>-0.3235610824922673</v>
       </c>
     </row>
@@ -2337,28 +2408,28 @@
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B12" s="27" t="n">
-        <v>436</v>
-      </c>
-      <c r="C12" s="27" t="n">
-        <v>436</v>
-      </c>
-      <c r="D12" s="28" t="n">
-        <v>0.116974</v>
-      </c>
-      <c r="E12" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="27" t="inlineStr">
+      <c r="B12" s="28" t="n">
+        <v>432</v>
+      </c>
+      <c r="C12" s="28" t="n">
+        <v>432</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>0.1178985</v>
+      </c>
+      <c r="E12" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="27" t="inlineStr">
         <is>
           <t>펀드는 기준가 이력이 7 거래일뿐이라 변동성·최대낙폭을 셈하지 않고 원천의 위험등급을 씁니다.</t>
         </is>
@@ -2381,7 +2452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I150"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2419,7 +2490,7 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="27" t="inlineStr">
         <is>
           <t>규모와 보수로 고릅니다. 수익률 순으로 고르지 않습니다 — 지난해 제일 많이 오른 것을 권하는 습관이 고객에게 가장 비쌉니다. 개별 주식은 시가총액 상위 종목이며 종목 추천이 아닙니다.</t>
         </is>
@@ -2498,15 +2569,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>1,707조원</t>
         </is>
       </c>
-      <c r="G7" s="28" t="n">
+      <c r="G7" s="29" t="n">
         <v>2.741007194244604</v>
       </c>
-      <c r="H7" s="28" t="inlineStr">
+      <c r="H7" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2518,35 +2589,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="30" t="inlineStr">
         <is>
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="D8" s="29" t="inlineStr">
+      <c r="D8" s="30" t="inlineStr">
         <is>
           <t>반도체</t>
         </is>
       </c>
-      <c r="E8" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="30" t="inlineStr">
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
         <is>
           <t>1,313조원</t>
         </is>
       </c>
-      <c r="G8" s="31" t="n">
+      <c r="G8" s="32" t="n">
         <v>5.760511882998171</v>
       </c>
-      <c r="H8" s="31" t="inlineStr">
+      <c r="H8" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2578,15 +2649,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="27" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>141조원</t>
         </is>
       </c>
-      <c r="G9" s="28" t="n">
+      <c r="G9" s="29" t="n">
         <v>6.015706806282721</v>
       </c>
-      <c r="H9" s="28" t="inlineStr">
+      <c r="H9" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2598,35 +2669,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>삼성전기</t>
         </is>
       </c>
-      <c r="D10" s="29" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>전기전자</t>
         </is>
       </c>
-      <c r="E10" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="30" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
         <is>
           <t>105조원</t>
         </is>
       </c>
-      <c r="G10" s="31" t="n">
+      <c r="G10" s="32" t="n">
         <v>6.789001122334455</v>
       </c>
-      <c r="H10" s="31" t="inlineStr">
+      <c r="H10" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2658,15 +2729,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="27" t="inlineStr">
+      <c r="F11" s="28" t="inlineStr">
         <is>
           <t>96조원</t>
         </is>
       </c>
-      <c r="G11" s="28" t="n">
+      <c r="G11" s="29" t="n">
         <v>0.6659090909090909</v>
       </c>
-      <c r="H11" s="28" t="inlineStr">
+      <c r="H11" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2678,35 +2749,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="30" t="inlineStr">
         <is>
           <t>LG에너지솔루션</t>
         </is>
       </c>
-      <c r="D12" s="29" t="inlineStr">
+      <c r="D12" s="30" t="inlineStr">
         <is>
           <t>2차전지</t>
         </is>
       </c>
-      <c r="E12" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F12" s="30" t="inlineStr">
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
         <is>
           <t>85조원</t>
         </is>
       </c>
-      <c r="G12" s="31" t="n">
+      <c r="G12" s="32" t="n">
         <v>0.05976676384839652</v>
       </c>
-      <c r="H12" s="31" t="inlineStr">
+      <c r="H12" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2738,15 +2809,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="27" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>65조원</t>
         </is>
       </c>
-      <c r="G13" s="28" t="n">
+      <c r="G13" s="29" t="n">
         <v>-0.07711346952561393</v>
       </c>
-      <c r="H13" s="28" t="inlineStr">
+      <c r="H13" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2758,35 +2829,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
+      <c r="C14" s="30" t="inlineStr">
         <is>
           <t>KB금융</t>
         </is>
       </c>
-      <c r="D14" s="29" t="inlineStr">
+      <c r="D14" s="30" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="E14" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="30" t="inlineStr">
+      <c r="E14" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
         <is>
           <t>62조원</t>
         </is>
       </c>
-      <c r="G14" s="31" t="n">
+      <c r="G14" s="32" t="n">
         <v>0.6178637200736647</v>
       </c>
-      <c r="H14" s="31" t="inlineStr">
+      <c r="H14" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2818,15 +2889,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F15" s="27" t="inlineStr">
+      <c r="F15" s="28" t="inlineStr">
         <is>
           <t>58조원</t>
         </is>
       </c>
-      <c r="G15" s="28" t="n">
+      <c r="G15" s="29" t="n">
         <v>1.02</v>
       </c>
-      <c r="H15" s="28" t="inlineStr">
+      <c r="H15" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2838,35 +2909,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="C16" s="29" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t>한화에어로스페이스</t>
         </is>
       </c>
-      <c r="D16" s="29" t="inlineStr">
+      <c r="D16" s="30" t="inlineStr">
         <is>
           <t>중공업</t>
         </is>
       </c>
-      <c r="E16" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="30" t="inlineStr">
+      <c r="E16" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
         <is>
           <t>56조원</t>
         </is>
       </c>
-      <c r="G16" s="31" t="n">
+      <c r="G16" s="32" t="n">
         <v>0.1869565217391305</v>
       </c>
-      <c r="H16" s="31" t="inlineStr">
+      <c r="H16" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2898,15 +2969,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="27" t="inlineStr">
+      <c r="F17" s="28" t="inlineStr">
         <is>
           <t>55조원</t>
         </is>
       </c>
-      <c r="G17" s="28" t="n">
+      <c r="G17" s="29" t="n">
         <v>0.3867313915857604</v>
       </c>
-      <c r="H17" s="28" t="inlineStr">
+      <c r="H17" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2918,35 +2989,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="C18" s="29" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>신한지주</t>
         </is>
       </c>
-      <c r="D18" s="29" t="inlineStr">
+      <c r="D18" s="30" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="E18" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F18" s="30" t="inlineStr">
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
         <is>
           <t>52조원</t>
         </is>
       </c>
-      <c r="G18" s="31" t="n">
+      <c r="G18" s="32" t="n">
         <v>0.7198142414860682</v>
       </c>
-      <c r="H18" s="31" t="inlineStr">
+      <c r="H18" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2978,15 +3049,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="27" t="inlineStr">
+      <c r="F19" s="28" t="inlineStr">
         <is>
           <t>51조원</t>
         </is>
       </c>
-      <c r="G19" s="28" t="n">
+      <c r="G19" s="29" t="n">
         <v>0.8912608405603737</v>
       </c>
-      <c r="H19" s="28" t="inlineStr">
+      <c r="H19" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2998,35 +3069,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>HD현대중공업</t>
         </is>
       </c>
-      <c r="D20" s="29" t="inlineStr">
+      <c r="D20" s="30" t="inlineStr">
         <is>
           <t>중공업</t>
         </is>
       </c>
-      <c r="E20" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="30" t="inlineStr">
+      <c r="E20" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
         <is>
           <t>48조원</t>
         </is>
       </c>
-      <c r="G20" s="31" t="n">
+      <c r="G20" s="32" t="n">
         <v>-0.09941520467836262</v>
       </c>
-      <c r="H20" s="31" t="inlineStr">
+      <c r="H20" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3058,15 +3129,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="27" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>47조원</t>
         </is>
       </c>
-      <c r="G21" s="28" t="n">
+      <c r="G21" s="29" t="n">
         <v>0.1407129455909943</v>
       </c>
-      <c r="H21" s="28" t="inlineStr">
+      <c r="H21" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3078,35 +3149,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B22" s="29" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
         <is>
           <t>삼성SDI</t>
         </is>
       </c>
-      <c r="D22" s="29" t="inlineStr">
+      <c r="D22" s="30" t="inlineStr">
         <is>
           <t>2차전지</t>
         </is>
       </c>
-      <c r="E22" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="30" t="inlineStr">
+      <c r="E22" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="inlineStr">
         <is>
           <t>43조원</t>
         </is>
       </c>
-      <c r="G22" s="31" t="n">
+      <c r="G22" s="32" t="n">
         <v>1.716791979949875</v>
       </c>
-      <c r="H22" s="31" t="inlineStr">
+      <c r="H22" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3138,15 +3209,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="27" t="inlineStr">
+      <c r="F23" s="28" t="inlineStr">
         <is>
           <t>41조원</t>
         </is>
       </c>
-      <c r="G23" s="28" t="n">
+      <c r="G23" s="29" t="n">
         <v>0.1180432690815407</v>
       </c>
-      <c r="H23" s="28" t="inlineStr">
+      <c r="H23" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3158,35 +3229,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="C24" s="29" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
         <is>
           <t>하나금융지주</t>
         </is>
       </c>
-      <c r="D24" s="29" t="inlineStr">
+      <c r="D24" s="30" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="E24" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F24" s="30" t="inlineStr">
+      <c r="E24" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="inlineStr">
         <is>
           <t>36조원</t>
         </is>
       </c>
-      <c r="G24" s="31" t="n">
+      <c r="G24" s="32" t="n">
         <v>0.646551724137931</v>
       </c>
-      <c r="H24" s="31" t="inlineStr">
+      <c r="H24" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3218,15 +3289,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="27" t="inlineStr">
+      <c r="F25" s="28" t="inlineStr">
         <is>
           <t>36조원</t>
         </is>
       </c>
-      <c r="G25" s="28" t="n">
+      <c r="G25" s="29" t="n">
         <v>1.645805592543275</v>
       </c>
-      <c r="H25" s="28" t="inlineStr">
+      <c r="H25" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3238,35 +3309,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B26" s="29" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="C26" s="29" t="inlineStr">
+      <c r="C26" s="30" t="inlineStr">
         <is>
           <t>현대모비스</t>
         </is>
       </c>
-      <c r="D26" s="29" t="inlineStr">
+      <c r="D26" s="30" t="inlineStr">
         <is>
           <t>자동차</t>
         </is>
       </c>
-      <c r="E26" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="30" t="inlineStr">
+      <c r="E26" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="inlineStr">
         <is>
           <t>34조원</t>
         </is>
       </c>
-      <c r="G26" s="31" t="n">
+      <c r="G26" s="32" t="n">
         <v>0.1780185758513932</v>
       </c>
-      <c r="H26" s="31" t="inlineStr">
+      <c r="H26" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3298,15 +3369,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F27" s="27" t="inlineStr">
+      <c r="F27" s="28" t="inlineStr">
         <is>
           <t>31조원</t>
         </is>
       </c>
-      <c r="G27" s="28" t="n">
+      <c r="G27" s="29" t="n">
         <v>2.5580204778157</v>
       </c>
-      <c r="H27" s="28" t="inlineStr">
+      <c r="H27" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3318,35 +3389,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="C28" s="29" t="inlineStr">
+      <c r="C28" s="30" t="inlineStr">
         <is>
           <t>SK</t>
         </is>
       </c>
-      <c r="D28" s="29" t="inlineStr">
+      <c r="D28" s="30" t="inlineStr">
         <is>
           <t>지주</t>
         </is>
       </c>
-      <c r="E28" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F28" s="30" t="inlineStr">
+      <c r="E28" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="31" t="inlineStr">
         <is>
           <t>30조원</t>
         </is>
       </c>
-      <c r="G28" s="31" t="n">
+      <c r="G28" s="32" t="n">
         <v>1.663438256658595</v>
       </c>
-      <c r="H28" s="31" t="inlineStr">
+      <c r="H28" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3378,15 +3449,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F29" s="27" t="inlineStr">
+      <c r="F29" s="28" t="inlineStr">
         <is>
           <t>30조원</t>
         </is>
       </c>
-      <c r="G29" s="28" t="n">
+      <c r="G29" s="29" t="n">
         <v>-0.1375545851528385</v>
       </c>
-      <c r="H29" s="28" t="inlineStr">
+      <c r="H29" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3398,35 +3469,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>국내주식</t>
         </is>
       </c>
-      <c r="C30" s="29" t="inlineStr">
+      <c r="C30" s="30" t="inlineStr">
         <is>
           <t>삼성화재</t>
         </is>
       </c>
-      <c r="D30" s="29" t="inlineStr">
+      <c r="D30" s="30" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="E30" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="30" t="inlineStr">
+      <c r="E30" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="31" t="inlineStr">
         <is>
           <t>29조원</t>
         </is>
       </c>
-      <c r="G30" s="31" t="n">
+      <c r="G30" s="32" t="n">
         <v>0.4316939890710383</v>
       </c>
-      <c r="H30" s="31" t="inlineStr">
+      <c r="H30" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3458,15 +3529,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="27" t="inlineStr">
+      <c r="F31" s="28" t="inlineStr">
         <is>
           <t>27조원</t>
         </is>
       </c>
-      <c r="G31" s="28" t="n">
+      <c r="G31" s="29" t="n">
         <v>1.344155844155844</v>
       </c>
-      <c r="H31" s="28" t="inlineStr">
+      <c r="H31" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3478,35 +3549,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B32" s="29" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="C32" s="29" t="inlineStr">
+      <c r="C32" s="30" t="inlineStr">
         <is>
           <t>엔비디아</t>
         </is>
       </c>
-      <c r="D32" s="29" t="inlineStr">
+      <c r="D32" s="30" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="E32" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="30" t="inlineStr">
+      <c r="E32" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="31" t="inlineStr">
         <is>
           <t>7,326조원</t>
         </is>
       </c>
-      <c r="G32" s="31" t="n">
+      <c r="G32" s="32" t="n">
         <v>0.2033755274261604</v>
       </c>
-      <c r="H32" s="31" t="inlineStr">
+      <c r="H32" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3538,15 +3609,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F33" s="27" t="inlineStr">
+      <c r="F33" s="28" t="inlineStr">
         <is>
           <t>6,803조원</t>
         </is>
       </c>
-      <c r="G33" s="28" t="n">
+      <c r="G33" s="29" t="n">
         <v>0.4043514997887623</v>
       </c>
-      <c r="H33" s="28" t="inlineStr">
+      <c r="H33" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3558,35 +3629,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B34" s="29" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="C34" s="29" t="inlineStr">
+      <c r="C34" s="30" t="inlineStr">
         <is>
           <t>알파벳(구글)</t>
         </is>
       </c>
-      <c r="D34" s="29" t="inlineStr">
+      <c r="D34" s="30" t="inlineStr">
         <is>
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="E34" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F34" s="30" t="inlineStr">
+      <c r="E34" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="inlineStr">
         <is>
           <t>5,875조원</t>
         </is>
       </c>
-      <c r="G34" s="31" t="n">
+      <c r="G34" s="32" t="n">
         <v>0.3627041850482891</v>
       </c>
-      <c r="H34" s="31" t="inlineStr">
+      <c r="H34" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3618,15 +3689,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="27" t="inlineStr">
+      <c r="F35" s="28" t="inlineStr">
         <is>
           <t>5,112조원</t>
         </is>
       </c>
-      <c r="G35" s="28" t="n">
+      <c r="G35" s="29" t="n">
         <v>-0.04862620304253341</v>
       </c>
-      <c r="H35" s="28" t="inlineStr">
+      <c r="H35" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3638,35 +3709,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B36" s="29" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="C36" s="29" t="inlineStr">
+      <c r="C36" s="30" t="inlineStr">
         <is>
           <t>아마존</t>
         </is>
       </c>
-      <c r="D36" s="29" t="inlineStr">
+      <c r="D36" s="30" t="inlineStr">
         <is>
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="E36" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="30" t="inlineStr">
+      <c r="E36" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="31" t="inlineStr">
         <is>
           <t>3,748조원</t>
         </is>
       </c>
-      <c r="G36" s="31" t="n">
+      <c r="G36" s="32" t="n">
         <v>0.06278356306442556</v>
       </c>
-      <c r="H36" s="31" t="inlineStr">
+      <c r="H36" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3698,15 +3769,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F37" s="27" t="inlineStr">
+      <c r="F37" s="28" t="inlineStr">
         <is>
           <t>3,087조원</t>
         </is>
       </c>
-      <c r="G37" s="28" t="n">
+      <c r="G37" s="29" t="n">
         <v>0.5981329864565001</v>
       </c>
-      <c r="H37" s="28" t="inlineStr">
+      <c r="H37" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3718,37 +3789,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B38" s="29" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="C38" s="29" t="inlineStr">
+      <c r="C38" s="30" t="inlineStr">
         <is>
           <t>스페이스X</t>
         </is>
       </c>
-      <c r="D38" s="29" t="inlineStr">
+      <c r="D38" s="30" t="inlineStr">
         <is>
           <t>산업재</t>
         </is>
       </c>
-      <c r="E38" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F38" s="30" t="inlineStr">
+      <c r="E38" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="31" t="inlineStr">
         <is>
           <t>2,823조원</t>
         </is>
       </c>
-      <c r="G38" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H38" s="31" t="inlineStr">
+      <c r="G38" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H38" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3780,15 +3851,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F39" s="27" t="inlineStr">
+      <c r="F39" s="28" t="inlineStr">
         <is>
           <t>2,404조원</t>
         </is>
       </c>
-      <c r="G39" s="28" t="n">
+      <c r="G39" s="29" t="n">
         <v>-0.1195109193147641</v>
       </c>
-      <c r="H39" s="28" t="inlineStr">
+      <c r="H39" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3800,35 +3871,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B40" s="29" t="inlineStr">
+      <c r="B40" s="30" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="C40" s="29" t="inlineStr">
+      <c r="C40" s="30" t="inlineStr">
         <is>
           <t>브로드컴</t>
         </is>
       </c>
-      <c r="D40" s="29" t="inlineStr">
+      <c r="D40" s="30" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="E40" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F40" s="30" t="inlineStr">
+      <c r="E40" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="31" t="inlineStr">
         <is>
           <t>2,293조원</t>
         </is>
       </c>
-      <c r="G40" s="31" t="n">
+      <c r="G40" s="32" t="n">
         <v>-0.06751078030157376</v>
       </c>
-      <c r="H40" s="31" t="inlineStr">
+      <c r="H40" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3860,15 +3931,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F41" s="27" t="inlineStr">
+      <c r="F41" s="28" t="inlineStr">
         <is>
           <t>2,001조원</t>
         </is>
       </c>
-      <c r="G41" s="28" t="n">
+      <c r="G41" s="29" t="n">
         <v>-0.1267193444541996</v>
       </c>
-      <c r="H41" s="28" t="inlineStr">
+      <c r="H41" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3880,35 +3951,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B42" s="29" t="inlineStr">
+      <c r="B42" s="30" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="C42" s="29" t="inlineStr">
+      <c r="C42" s="30" t="inlineStr">
         <is>
           <t>마이크론</t>
         </is>
       </c>
-      <c r="D42" s="29" t="inlineStr">
+      <c r="D42" s="30" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="E42" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F42" s="30" t="inlineStr">
+      <c r="E42" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="31" t="inlineStr">
         <is>
           <t>1,527조원</t>
         </is>
       </c>
-      <c r="G42" s="31" t="n">
+      <c r="G42" s="32" t="n">
         <v>4.872789503707929</v>
       </c>
-      <c r="H42" s="31" t="inlineStr">
+      <c r="H42" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3940,15 +4011,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F43" s="27" t="inlineStr">
+      <c r="F43" s="28" t="inlineStr">
         <is>
           <t>1,508조원</t>
         </is>
       </c>
-      <c r="G43" s="28" t="n">
+      <c r="G43" s="29" t="n">
         <v>0.05749277780038242</v>
       </c>
-      <c r="H43" s="28" t="inlineStr">
+      <c r="H43" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3960,35 +4031,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B44" s="29" t="inlineStr">
+      <c r="B44" s="30" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="C44" s="29" t="inlineStr">
+      <c r="C44" s="30" t="inlineStr">
         <is>
           <t>일라이 릴리</t>
         </is>
       </c>
-      <c r="D44" s="29" t="inlineStr">
+      <c r="D44" s="30" t="inlineStr">
         <is>
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="E44" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F44" s="30" t="inlineStr">
+      <c r="E44" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F44" s="31" t="inlineStr">
         <is>
           <t>1,421조원</t>
         </is>
       </c>
-      <c r="G44" s="31" t="n">
+      <c r="G44" s="32" t="n">
         <v>0.5207633087852015</v>
       </c>
-      <c r="H44" s="31" t="inlineStr">
+      <c r="H44" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4020,15 +4091,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F45" s="27" t="inlineStr">
+      <c r="F45" s="28" t="inlineStr">
         <is>
           <t>1,284조원</t>
         </is>
       </c>
-      <c r="G45" s="28" t="n">
+      <c r="G45" s="29" t="n">
         <v>0.1295564907737132</v>
       </c>
-      <c r="H45" s="28" t="inlineStr">
+      <c r="H45" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4040,35 +4111,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B46" s="29" t="inlineStr">
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="C46" s="29" t="inlineStr">
+      <c r="C46" s="30" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="D46" s="29" t="inlineStr">
+      <c r="D46" s="30" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="E46" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F46" s="30" t="inlineStr">
+      <c r="E46" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="31" t="inlineStr">
         <is>
           <t>1,231조원</t>
         </is>
       </c>
-      <c r="G46" s="31" t="n">
+      <c r="G46" s="32" t="n">
         <v>2.180069496152892</v>
       </c>
-      <c r="H46" s="31" t="inlineStr">
+      <c r="H46" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4100,15 +4171,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F47" s="27" t="inlineStr">
+      <c r="F47" s="28" t="inlineStr">
         <is>
           <t>1,175조원</t>
         </is>
       </c>
-      <c r="G47" s="28" t="n">
+      <c r="G47" s="29" t="n">
         <v>0.03674414119008595</v>
       </c>
-      <c r="H47" s="28" t="inlineStr">
+      <c r="H47" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4120,35 +4191,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B48" s="29" t="inlineStr">
+      <c r="B48" s="30" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="C48" s="29" t="inlineStr">
+      <c r="C48" s="30" t="inlineStr">
         <is>
           <t>비자</t>
         </is>
       </c>
-      <c r="D48" s="29" t="inlineStr">
+      <c r="D48" s="30" t="inlineStr">
         <is>
           <t>금융</t>
         </is>
       </c>
-      <c r="E48" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F48" s="30" t="inlineStr">
+      <c r="E48" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F48" s="31" t="inlineStr">
         <is>
           <t>955조원</t>
         </is>
       </c>
-      <c r="G48" s="31" t="n">
+      <c r="G48" s="32" t="n">
         <v>0.09402742958265729</v>
       </c>
-      <c r="H48" s="31" t="inlineStr">
+      <c r="H48" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4180,15 +4251,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F49" s="27" t="inlineStr">
+      <c r="F49" s="28" t="inlineStr">
         <is>
           <t>929조원</t>
         </is>
       </c>
-      <c r="G49" s="28" t="n">
+      <c r="G49" s="29" t="n">
         <v>0.4536715620827771</v>
       </c>
-      <c r="H49" s="28" t="inlineStr">
+      <c r="H49" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4200,35 +4271,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B50" s="29" t="inlineStr">
+      <c r="B50" s="30" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="C50" s="29" t="inlineStr">
+      <c r="C50" s="30" t="inlineStr">
         <is>
           <t>존슨앤드존슨</t>
         </is>
       </c>
-      <c r="D50" s="29" t="inlineStr">
+      <c r="D50" s="30" t="inlineStr">
         <is>
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="E50" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="30" t="inlineStr">
+      <c r="E50" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F50" s="31" t="inlineStr">
         <is>
           <t>901조원</t>
         </is>
       </c>
-      <c r="G50" s="31" t="n">
+      <c r="G50" s="32" t="n">
         <v>0.5066516347237879</v>
       </c>
-      <c r="H50" s="31" t="inlineStr">
+      <c r="H50" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4260,15 +4331,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F51" s="27" t="inlineStr">
+      <c r="F51" s="28" t="inlineStr">
         <is>
           <t>866조원</t>
         </is>
       </c>
-      <c r="G51" s="28" t="n">
+      <c r="G51" s="29" t="n">
         <v>0.8473653868326995</v>
       </c>
-      <c r="H51" s="28" t="inlineStr">
+      <c r="H51" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4280,35 +4351,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B52" s="29" t="inlineStr">
+      <c r="B52" s="30" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="C52" s="29" t="inlineStr">
+      <c r="C52" s="30" t="inlineStr">
         <is>
           <t>인텔</t>
         </is>
       </c>
-      <c r="D52" s="29" t="inlineStr">
+      <c r="D52" s="30" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="E52" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="30" t="inlineStr">
+      <c r="E52" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F52" s="31" t="inlineStr">
         <is>
           <t>796조원</t>
         </is>
       </c>
-      <c r="G52" s="31" t="n">
+      <c r="G52" s="32" t="n">
         <v>3.079531691562374</v>
       </c>
-      <c r="H52" s="31" t="inlineStr">
+      <c r="H52" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4340,15 +4411,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F53" s="27" t="inlineStr">
+      <c r="F53" s="28" t="inlineStr">
         <is>
           <t>685조원</t>
         </is>
       </c>
-      <c r="G53" s="28" t="n">
+      <c r="G53" s="29" t="n">
         <v>-0.02609098394400999</v>
       </c>
-      <c r="H53" s="28" t="inlineStr">
+      <c r="H53" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4360,35 +4431,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B54" s="29" t="inlineStr">
+      <c r="B54" s="30" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="C54" s="29" t="inlineStr">
+      <c r="C54" s="30" t="inlineStr">
         <is>
           <t>애브비</t>
         </is>
       </c>
-      <c r="D54" s="29" t="inlineStr">
+      <c r="D54" s="30" t="inlineStr">
         <is>
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="E54" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="30" t="inlineStr">
+      <c r="E54" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F54" s="31" t="inlineStr">
         <is>
           <t>645조원</t>
         </is>
       </c>
-      <c r="G54" s="31" t="n">
+      <c r="G54" s="32" t="n">
         <v>0.2063324295758466</v>
       </c>
-      <c r="H54" s="31" t="inlineStr">
+      <c r="H54" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4420,15 +4491,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F55" s="27" t="inlineStr">
+      <c r="F55" s="28" t="inlineStr">
         <is>
           <t>630조원</t>
         </is>
       </c>
-      <c r="G55" s="28" t="n">
+      <c r="G55" s="29" t="n">
         <v>-0.5261799165949559</v>
       </c>
-      <c r="H55" s="28" t="inlineStr">
+      <c r="H55" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4440,35 +4511,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B56" s="29" t="inlineStr">
+      <c r="B56" s="30" t="inlineStr">
         <is>
           <t>해외주식</t>
         </is>
       </c>
-      <c r="C56" s="29" t="inlineStr">
+      <c r="C56" s="30" t="inlineStr">
         <is>
           <t>시스코</t>
         </is>
       </c>
-      <c r="D56" s="29" t="inlineStr">
+      <c r="D56" s="30" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="E56" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F56" s="30" t="inlineStr">
+      <c r="E56" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F56" s="31" t="inlineStr">
         <is>
           <t>601조원</t>
         </is>
       </c>
-      <c r="G56" s="31" t="n">
+      <c r="G56" s="32" t="n">
         <v>0.607579826917338</v>
       </c>
-      <c r="H56" s="31" t="inlineStr">
+      <c r="H56" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4487,7 +4558,7 @@
       </c>
       <c r="C57" s="14" t="inlineStr">
         <is>
-          <t>TIGER 미국S&amp;P500</t>
+          <t>ACE KRX금현물</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
@@ -4497,19 +4568,21 @@
       </c>
       <c r="E57" s="14" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="F57" s="27" t="inlineStr">
-        <is>
-          <t>21조원</t>
-        </is>
-      </c>
-      <c r="G57" s="28" t="n">
-        <v>0.1782639885222381</v>
-      </c>
-      <c r="H57" s="32" t="n">
-        <v>6.8e-05</v>
+          <t>한국투자신탁운용</t>
+        </is>
+      </c>
+      <c r="F57" s="28" t="inlineStr">
+        <is>
+          <t>4조원</t>
+        </is>
+      </c>
+      <c r="G57" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="33" t="n">
+        <v>0.0019</v>
       </c>
     </row>
     <row r="58">
@@ -4518,36 +4591,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B58" s="29" t="inlineStr">
+      <c r="B58" s="30" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="C58" s="29" t="inlineStr">
-        <is>
-          <t>TIGER 미국나스닥100</t>
-        </is>
-      </c>
-      <c r="D58" s="29" t="inlineStr">
+      <c r="C58" s="30" t="inlineStr">
+        <is>
+          <t>KODEX 종합채권(AA-이상)액티브</t>
+        </is>
+      </c>
+      <c r="D58" s="30" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="E58" s="29" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="F58" s="30" t="inlineStr">
-        <is>
-          <t>12조원</t>
-        </is>
-      </c>
-      <c r="G58" s="31" t="n">
-        <v>0.2434730103402611</v>
-      </c>
-      <c r="H58" s="33" t="n">
-        <v>6.8e-05</v>
+      <c r="E58" s="30" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="F58" s="31" t="inlineStr">
+        <is>
+          <t>4조원</t>
+        </is>
+      </c>
+      <c r="G58" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="34" t="n">
+        <v>0.00045</v>
       </c>
     </row>
     <row r="59">
@@ -4563,7 +4638,7 @@
       </c>
       <c r="C59" s="14" t="inlineStr">
         <is>
-          <t>KODEX 미국S&amp;P500</t>
+          <t>PLUS 고배당주</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
@@ -4573,21 +4648,21 @@
       </c>
       <c r="E59" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="F59" s="27" t="inlineStr">
-        <is>
-          <t>10조원</t>
-        </is>
-      </c>
-      <c r="G59" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="32" t="n">
-        <v>6.2e-05</v>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="F59" s="28" t="inlineStr">
+        <is>
+          <t>2조원</t>
+        </is>
+      </c>
+      <c r="G59" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H59" s="33" t="n">
+        <v>0.0023</v>
       </c>
     </row>
     <row r="60">
@@ -4596,38 +4671,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B60" s="29" t="inlineStr">
+      <c r="B60" s="30" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="C60" s="29" t="inlineStr">
-        <is>
-          <t>KODEX 미국나스닥100</t>
-        </is>
-      </c>
-      <c r="D60" s="29" t="inlineStr">
+      <c r="C60" s="30" t="inlineStr">
+        <is>
+          <t>TIGER 리츠부동산인프라</t>
+        </is>
+      </c>
+      <c r="D60" s="30" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="E60" s="29" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="F60" s="30" t="inlineStr">
-        <is>
-          <t>9조원</t>
-        </is>
-      </c>
-      <c r="G60" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" s="33" t="n">
-        <v>6.2e-05</v>
+      <c r="E60" s="30" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="F60" s="31" t="inlineStr">
+        <is>
+          <t>2조원</t>
+        </is>
+      </c>
+      <c r="G60" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="34" t="n">
+        <v>0.0008</v>
       </c>
     </row>
     <row r="61">
@@ -4643,7 +4718,7 @@
       </c>
       <c r="C61" s="14" t="inlineStr">
         <is>
-          <t>KODEX 머니마켓액티브</t>
+          <t>KODEX 삼성전자채권혼합</t>
         </is>
       </c>
       <c r="D61" s="14" t="inlineStr">
@@ -4656,18 +4731,18 @@
           <t>삼성자산운용(ETF)</t>
         </is>
       </c>
-      <c r="F61" s="27" t="inlineStr">
-        <is>
-          <t>9조원</t>
-        </is>
-      </c>
-      <c r="G61" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" s="32" t="n">
-        <v>0.0005</v>
+      <c r="F61" s="28" t="inlineStr">
+        <is>
+          <t>1조원</t>
+        </is>
+      </c>
+      <c r="G61" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="33" t="n">
+        <v>0.0007000000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -4676,38 +4751,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B62" s="29" t="inlineStr">
+      <c r="B62" s="30" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="C62" s="29" t="inlineStr">
-        <is>
-          <t>KODEX CD금리액티브(합성)</t>
-        </is>
-      </c>
-      <c r="D62" s="29" t="inlineStr">
+      <c r="C62" s="30" t="inlineStr">
+        <is>
+          <t>SOL 종합채권(AA-이상)액티브</t>
+        </is>
+      </c>
+      <c r="D62" s="30" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="E62" s="29" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="F62" s="30" t="inlineStr">
-        <is>
-          <t>7조원</t>
-        </is>
-      </c>
-      <c r="G62" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H62" s="33" t="n">
-        <v>0.0002</v>
+      <c r="E62" s="30" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="F62" s="31" t="inlineStr">
+        <is>
+          <t>1조원</t>
+        </is>
+      </c>
+      <c r="G62" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="34" t="n">
+        <v>0.0004</v>
       </c>
     </row>
     <row r="63">
@@ -4723,7 +4798,7 @@
       </c>
       <c r="C63" s="14" t="inlineStr">
         <is>
-          <t>TIGER 미국배당다우존스</t>
+          <t>TIGER KRX금현물</t>
         </is>
       </c>
       <c r="D63" s="14" t="inlineStr">
@@ -4736,16 +4811,16 @@
           <t>미래에셋자산운용</t>
         </is>
       </c>
-      <c r="F63" s="27" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G63" s="28" t="n">
-        <v>0.2478942048517521</v>
-      </c>
-      <c r="H63" s="32" t="n">
-        <v>0.0001</v>
+      <c r="F63" s="28" t="inlineStr">
+        <is>
+          <t>1조원</t>
+        </is>
+      </c>
+      <c r="G63" s="29" t="n">
+        <v>0.2122905027932962</v>
+      </c>
+      <c r="H63" s="33" t="n">
+        <v>0.0015</v>
       </c>
     </row>
     <row r="64">
@@ -4754,38 +4829,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B64" s="29" t="inlineStr">
+      <c r="B64" s="30" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="C64" s="29" t="inlineStr">
-        <is>
-          <t>ACE KRX금현물</t>
-        </is>
-      </c>
-      <c r="D64" s="29" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
+        <is>
+          <t>ACE 종합채권(AA-이상)액티브</t>
+        </is>
+      </c>
+      <c r="D64" s="30" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="E64" s="29" t="inlineStr">
-        <is>
-          <t>한국투자신탁운용</t>
-        </is>
-      </c>
-      <c r="F64" s="30" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G64" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H64" s="33" t="n">
-        <v>0.0019</v>
+      <c r="E64" s="30" t="inlineStr">
+        <is>
+          <t>한국투신운용(ETF)</t>
+        </is>
+      </c>
+      <c r="F64" s="31" t="inlineStr">
+        <is>
+          <t>1조원</t>
+        </is>
+      </c>
+      <c r="G64" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H64" s="34" t="n">
+        <v>0.0002</v>
       </c>
     </row>
     <row r="65">
@@ -4801,7 +4876,7 @@
       </c>
       <c r="C65" s="14" t="inlineStr">
         <is>
-          <t>ACE 미국S&amp;P500</t>
+          <t>PLUS 고배당주채권혼합</t>
         </is>
       </c>
       <c r="D65" s="14" t="inlineStr">
@@ -4811,21 +4886,21 @@
       </c>
       <c r="E65" s="14" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
-        </is>
-      </c>
-      <c r="F65" s="27" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G65" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H65" s="32" t="n">
-        <v>4.7e-05</v>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="F65" s="28" t="inlineStr">
+        <is>
+          <t>5,956억원</t>
+        </is>
+      </c>
+      <c r="G65" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H65" s="33" t="n">
+        <v>0.002</v>
       </c>
     </row>
     <row r="66">
@@ -4834,36 +4909,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B66" s="29" t="inlineStr">
+      <c r="B66" s="30" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="C66" s="29" t="inlineStr">
-        <is>
-          <t>TIGER 미국테크TOP10 INDXX</t>
-        </is>
-      </c>
-      <c r="D66" s="29" t="inlineStr">
+      <c r="C66" s="30" t="inlineStr">
+        <is>
+          <t>ACE 국고채10년</t>
+        </is>
+      </c>
+      <c r="D66" s="30" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="E66" s="29" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="F66" s="30" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G66" s="31" t="n">
-        <v>0.1565284066014312</v>
-      </c>
-      <c r="H66" s="33" t="n">
-        <v>0.0049</v>
+      <c r="E66" s="30" t="inlineStr">
+        <is>
+          <t>한국투신운용(ETF)</t>
+        </is>
+      </c>
+      <c r="F66" s="31" t="inlineStr">
+        <is>
+          <t>5,152억원</t>
+        </is>
+      </c>
+      <c r="G66" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H66" s="34" t="n">
+        <v>0.0002</v>
       </c>
     </row>
     <row r="67">
@@ -4879,7 +4956,7 @@
       </c>
       <c r="C67" s="14" t="inlineStr">
         <is>
-          <t>KODEX KOFR금리액티브(합성)</t>
+          <t>RISE KIS국고채30년Enhanced</t>
         </is>
       </c>
       <c r="D67" s="14" t="inlineStr">
@@ -4889,20 +4966,20 @@
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="F67" s="27" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G67" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H67" s="32" t="n">
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="F67" s="28" t="inlineStr">
+        <is>
+          <t>4,492억원</t>
+        </is>
+      </c>
+      <c r="G67" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H67" s="33" t="n">
         <v>0.0005</v>
       </c>
     </row>
@@ -4912,38 +4989,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
-        <is>
-          <t>ACE 미국나스닥100</t>
-        </is>
-      </c>
-      <c r="D68" s="29" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
+        <is>
+          <t>SOL 중단기회사채(A-이상)액티브</t>
+        </is>
+      </c>
+      <c r="D68" s="30" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="E68" s="29" t="inlineStr">
-        <is>
-          <t>한국투신운용(ETF)</t>
-        </is>
-      </c>
-      <c r="F68" s="30" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G68" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="33" t="n">
-        <v>6.2e-05</v>
+      <c r="E68" s="30" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="F68" s="31" t="inlineStr">
+        <is>
+          <t>4,279억원</t>
+        </is>
+      </c>
+      <c r="G68" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="34" t="n">
+        <v>0.0005</v>
       </c>
     </row>
     <row r="69">
@@ -4959,7 +5036,7 @@
       </c>
       <c r="C69" s="14" t="inlineStr">
         <is>
-          <t>KODEX 종합채권(AA-이상)액티브</t>
+          <t>KIWOOM 국고채10년</t>
         </is>
       </c>
       <c r="D69" s="14" t="inlineStr">
@@ -4969,21 +5046,21 @@
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="F69" s="27" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G69" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H69" s="32" t="n">
-        <v>0.00045</v>
+          <t>키움투자자산운용</t>
+        </is>
+      </c>
+      <c r="F69" s="28" t="inlineStr">
+        <is>
+          <t>4,141억원</t>
+        </is>
+      </c>
+      <c r="G69" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H69" s="33" t="n">
+        <v>0.0005</v>
       </c>
     </row>
     <row r="70">
@@ -4992,38 +5069,36 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B70" s="29" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="C70" s="29" t="inlineStr">
-        <is>
-          <t>TIGER CD금리투자KIS(합성)</t>
-        </is>
-      </c>
-      <c r="D70" s="29" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
+        <is>
+          <t>RISE TDF2050액티브 적격</t>
+        </is>
+      </c>
+      <c r="D70" s="30" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="E70" s="29" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="F70" s="30" t="inlineStr">
-        <is>
-          <t>3조원</t>
-        </is>
-      </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H70" s="33" t="n">
-        <v>0.0003</v>
+      <c r="E70" s="30" t="inlineStr">
+        <is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>3,461억원</t>
+        </is>
+      </c>
+      <c r="G70" s="32" t="n">
+        <v>0.2268534816588044</v>
+      </c>
+      <c r="H70" s="34" t="n">
+        <v>0.0001</v>
       </c>
     </row>
     <row r="71">
@@ -5039,7 +5114,7 @@
       </c>
       <c r="C71" s="14" t="inlineStr">
         <is>
-          <t>RISE 머니마켓액티브</t>
+          <t>1Q 단기금융채액티브</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
@@ -5049,21 +5124,21 @@
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="F71" s="27" t="inlineStr">
-        <is>
-          <t>3조원</t>
-        </is>
-      </c>
-      <c r="G71" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H71" s="32" t="n">
-        <v>0.0005</v>
+          <t>하나자산운용</t>
+        </is>
+      </c>
+      <c r="F71" s="28" t="inlineStr">
+        <is>
+          <t>1,261억원</t>
+        </is>
+      </c>
+      <c r="G71" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H71" s="33" t="n">
+        <v>0.0008</v>
       </c>
     </row>
     <row r="72">
@@ -5072,38 +5147,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B72" s="29" t="inlineStr">
+      <c r="B72" s="30" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="C72" s="29" t="inlineStr">
-        <is>
-          <t>TIGER 머니마켓액티브</t>
-        </is>
-      </c>
-      <c r="D72" s="29" t="inlineStr">
+      <c r="C72" s="30" t="inlineStr">
+        <is>
+          <t>KIWOOM 단기자금</t>
+        </is>
+      </c>
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
-      <c r="E72" s="29" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="F72" s="30" t="inlineStr">
-        <is>
-          <t>3조원</t>
-        </is>
-      </c>
-      <c r="G72" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H72" s="33" t="n">
-        <v>0.0004</v>
+      <c r="E72" s="30" t="inlineStr">
+        <is>
+          <t>키움투자자산운용</t>
+        </is>
+      </c>
+      <c r="F72" s="31" t="inlineStr">
+        <is>
+          <t>681억원</t>
+        </is>
+      </c>
+      <c r="G72" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H72" s="34" t="n">
+        <v>0.0005</v>
       </c>
     </row>
     <row r="73">
@@ -5119,31 +5194,31 @@
       </c>
       <c r="C73" s="14" t="inlineStr">
         <is>
-          <t>KODEX CD1년금리플러스액티브(합성)</t>
+          <t>TIGER 글로벌AI전력인프라액티브</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>원자력&amp;전력인프라</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="F73" s="27" t="inlineStr">
-        <is>
-          <t>3조원</t>
-        </is>
-      </c>
-      <c r="G73" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H73" s="32" t="n">
-        <v>0.0005</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F73" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="29" t="n">
+        <v>0.515483360710592</v>
+      </c>
+      <c r="H73" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -5152,38 +5227,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B74" s="29" t="inlineStr">
+      <c r="B74" s="30" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="C74" s="29" t="inlineStr">
-        <is>
-          <t>TIGER 미국나스닥100타겟데일리커버드콜</t>
-        </is>
-      </c>
-      <c r="D74" s="29" t="inlineStr">
-        <is>
-          <t>커버드콜</t>
-        </is>
-      </c>
-      <c r="E74" s="29" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="F74" s="30" t="inlineStr">
-        <is>
-          <t>3조원</t>
-        </is>
-      </c>
-      <c r="G74" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H74" s="33" t="n">
-        <v>0.0025</v>
+      <c r="C74" s="30" t="inlineStr">
+        <is>
+          <t>TIGER 중장기국채</t>
+        </is>
+      </c>
+      <c r="D74" s="30" t="inlineStr">
+        <is>
+          <t>채권형</t>
+        </is>
+      </c>
+      <c r="E74" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="32" t="n">
+        <v>-0.04650762373017548</v>
+      </c>
+      <c r="H74" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -5199,31 +5274,31 @@
       </c>
       <c r="C75" s="14" t="inlineStr">
         <is>
-          <t>PLUS 고배당주</t>
+          <t>TIGER 200</t>
         </is>
       </c>
       <c r="D75" s="14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="F75" s="27" t="inlineStr">
-        <is>
-          <t>2조원</t>
-        </is>
-      </c>
-      <c r="G75" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H75" s="32" t="n">
-        <v>0.0023</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F75" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="29" t="n">
+        <v>1.546781654617727</v>
+      </c>
+      <c r="H75" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -5232,38 +5307,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="C76" s="29" t="inlineStr">
-        <is>
-          <t>TIGER KOFR금리액티브(합성)</t>
-        </is>
-      </c>
-      <c r="D76" s="29" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="E76" s="29" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="F76" s="30" t="inlineStr">
-        <is>
-          <t>2조원</t>
-        </is>
-      </c>
-      <c r="G76" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H76" s="33" t="n">
-        <v>0.0003</v>
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>ACE 코스피</t>
+        </is>
+      </c>
+      <c r="D76" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="E76" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F76" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="32" t="n">
+        <v>1.14769647696477</v>
+      </c>
+      <c r="H76" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -5279,31 +5354,31 @@
       </c>
       <c r="C77" s="14" t="inlineStr">
         <is>
-          <t>KODEX 200미국채혼합50</t>
+          <t>TIGER 코스닥150</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="F77" s="27" t="inlineStr">
-        <is>
-          <t>2조원</t>
-        </is>
-      </c>
-      <c r="G77" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H77" s="32" t="n">
-        <v>0.0035</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F77" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="29" t="n">
+        <v>0.01696750902527078</v>
+      </c>
+      <c r="H77" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -5312,38 +5387,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B78" s="29" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>KODEX 단기채권PLUS</t>
-        </is>
-      </c>
-      <c r="D78" s="29" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="E78" s="29" t="inlineStr">
-        <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="F78" s="30" t="inlineStr">
-        <is>
-          <t>2조원</t>
-        </is>
-      </c>
-      <c r="G78" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H78" s="33" t="n">
-        <v>0.0015</v>
+      <c r="C78" s="30" t="inlineStr">
+        <is>
+          <t>TIGER 코리아TOP10</t>
+        </is>
+      </c>
+      <c r="D78" s="30" t="inlineStr">
+        <is>
+          <t>대형주TOP10</t>
+        </is>
+      </c>
+      <c r="E78" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="32" t="n">
+        <v>1.958115183246073</v>
+      </c>
+      <c r="H78" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -5359,31 +5434,31 @@
       </c>
       <c r="C79" s="14" t="inlineStr">
         <is>
-          <t>KODEX 미국배당커버드콜액티브</t>
+          <t>TIGER 배당커버드콜액티브</t>
         </is>
       </c>
       <c r="D79" s="14" t="inlineStr">
         <is>
-          <t>커버드콜</t>
+          <t>배당/커버드콜</t>
         </is>
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
-        </is>
-      </c>
-      <c r="F79" s="27" t="inlineStr">
-        <is>
-          <t>2조원</t>
-        </is>
-      </c>
-      <c r="G79" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H79" s="32" t="n">
-        <v>0.0019</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F79" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="29" t="n">
+        <v>1.291341218478018</v>
+      </c>
+      <c r="H79" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -5392,38 +5467,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B80" s="29" t="inlineStr">
+      <c r="B80" s="30" t="inlineStr">
         <is>
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="C80" s="29" t="inlineStr">
-        <is>
-          <t>TIGER CD1년금리액티브(합성)</t>
-        </is>
-      </c>
-      <c r="D80" s="29" t="inlineStr">
-        <is>
-          <t>일반</t>
-        </is>
-      </c>
-      <c r="E80" s="29" t="inlineStr">
-        <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="F80" s="30" t="inlineStr">
-        <is>
-          <t>2조원</t>
-        </is>
-      </c>
-      <c r="G80" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H80" s="33" t="n">
-        <v>9.8e-05</v>
+      <c r="C80" s="30" t="inlineStr">
+        <is>
+          <t>TIGER 반도체TOP10</t>
+        </is>
+      </c>
+      <c r="D80" s="30" t="inlineStr">
+        <is>
+          <t>반도체/IT</t>
+        </is>
+      </c>
+      <c r="E80" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F80" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="32" t="n">
+        <v>2.170522707797772</v>
+      </c>
+      <c r="H80" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -5439,31 +5514,31 @@
       </c>
       <c r="C81" s="14" t="inlineStr">
         <is>
-          <t>RISE 미국나스닥100</t>
+          <t>RISE AI반도체TOP10</t>
         </is>
       </c>
       <c r="D81" s="14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>반도체/IT</t>
         </is>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>KB자산운용</t>
-        </is>
-      </c>
-      <c r="F81" s="27" t="inlineStr">
-        <is>
-          <t>2조원</t>
-        </is>
-      </c>
-      <c r="G81" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H81" s="32" t="n">
-        <v>6.2e-05</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F81" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="29" t="n">
+        <v>2.108284409654273</v>
+      </c>
+      <c r="H81" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -5472,38 +5547,36 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B82" s="29" t="inlineStr">
+      <c r="B82" s="30" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="C82" s="29" t="inlineStr">
-        <is>
-          <t>SPDR S&amp;P 500</t>
-        </is>
-      </c>
-      <c r="D82" s="29" t="inlineStr">
-        <is>
-          <t>주식</t>
-        </is>
-      </c>
-      <c r="E82" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F82" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G82" s="31" t="n">
-        <v>0.1712168714029432</v>
-      </c>
-      <c r="H82" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C82" s="30" t="inlineStr">
+        <is>
+          <t>TIGER 미국S&amp;P500</t>
+        </is>
+      </c>
+      <c r="D82" s="30" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="E82" s="30" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>21조원</t>
+        </is>
+      </c>
+      <c r="G82" s="32" t="n">
+        <v>0.1782639885222381</v>
+      </c>
+      <c r="H82" s="34" t="n">
+        <v>6.8e-05</v>
       </c>
     </row>
     <row r="83">
@@ -5519,31 +5592,29 @@
       </c>
       <c r="C83" s="14" t="inlineStr">
         <is>
-          <t>Invesco QQQ (나스닥100)</t>
+          <t>TIGER 미국나스닥100</t>
         </is>
       </c>
       <c r="D83" s="14" t="inlineStr">
         <is>
-          <t>주식</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F83" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G83" s="28" t="n">
-        <v>0.2286861820192689</v>
-      </c>
-      <c r="H83" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="F83" s="28" t="inlineStr">
+        <is>
+          <t>12조원</t>
+        </is>
+      </c>
+      <c r="G83" s="29" t="n">
+        <v>0.2434730103402611</v>
+      </c>
+      <c r="H83" s="33" t="n">
+        <v>6.8e-05</v>
       </c>
     </row>
     <row r="84">
@@ -5552,38 +5623,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B84" s="29" t="inlineStr">
+      <c r="B84" s="30" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="C84" s="29" t="inlineStr">
-        <is>
-          <t>Vanguard 미국 전체시장</t>
-        </is>
-      </c>
-      <c r="D84" s="29" t="inlineStr">
-        <is>
-          <t>주식</t>
-        </is>
-      </c>
-      <c r="E84" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F84" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G84" s="31" t="n">
-        <v>0.1680824723535977</v>
-      </c>
-      <c r="H84" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C84" s="30" t="inlineStr">
+        <is>
+          <t>KODEX 200미국채혼합50</t>
+        </is>
+      </c>
+      <c r="D84" s="30" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="E84" s="30" t="inlineStr">
+        <is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="F84" s="31" t="inlineStr">
+        <is>
+          <t>2조원</t>
+        </is>
+      </c>
+      <c r="G84" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H84" s="34" t="n">
+        <v>0.0035</v>
       </c>
     </row>
     <row r="85">
@@ -5599,31 +5670,31 @@
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>iShares 러셀2000 (미국 중소형)</t>
+          <t>KODEX 미국배당커버드콜액티브</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>주식</t>
+          <t>커버드콜</t>
         </is>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F85" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G85" s="28" t="n">
-        <v>0.2013375822034587</v>
-      </c>
-      <c r="H85" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>삼성자산운용(ETF)</t>
+        </is>
+      </c>
+      <c r="F85" s="28" t="inlineStr">
+        <is>
+          <t>2조원</t>
+        </is>
+      </c>
+      <c r="G85" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H85" s="33" t="n">
+        <v>0.0019</v>
       </c>
     </row>
     <row r="86">
@@ -5632,38 +5703,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B86" s="29" t="inlineStr">
+      <c r="B86" s="30" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="C86" s="29" t="inlineStr">
-        <is>
-          <t>Vanguard 선진국(미국 제외)</t>
-        </is>
-      </c>
-      <c r="D86" s="29" t="inlineStr">
-        <is>
-          <t>주식</t>
-        </is>
-      </c>
-      <c r="E86" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F86" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G86" s="31" t="n">
-        <v>0.2266691413144159</v>
-      </c>
-      <c r="H86" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C86" s="30" t="inlineStr">
+        <is>
+          <t>ACE 미국30년국채액티브(H)</t>
+        </is>
+      </c>
+      <c r="D86" s="30" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="E86" s="30" t="inlineStr">
+        <is>
+          <t>한국투자신탁운용</t>
+        </is>
+      </c>
+      <c r="F86" s="31" t="inlineStr">
+        <is>
+          <t>1조원</t>
+        </is>
+      </c>
+      <c r="G86" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H86" s="34" t="n">
+        <v>0.0005</v>
       </c>
     </row>
     <row r="87">
@@ -5679,31 +5750,31 @@
       </c>
       <c r="C87" s="14" t="inlineStr">
         <is>
-          <t>Vanguard 신흥국</t>
+          <t>ACE 미국빅테크TOP7 Plus</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
         <is>
-          <t>주식</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F87" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G87" s="28" t="n">
-        <v>0.1316236092777672</v>
-      </c>
-      <c r="H87" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>한국투신운용(ETF)</t>
+        </is>
+      </c>
+      <c r="F87" s="28" t="inlineStr">
+        <is>
+          <t>1조원</t>
+        </is>
+      </c>
+      <c r="G87" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H87" s="33" t="n">
+        <v>0.003</v>
       </c>
     </row>
     <row r="88">
@@ -5712,38 +5783,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B88" s="29" t="inlineStr">
+      <c r="B88" s="30" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="C88" s="29" t="inlineStr">
-        <is>
-          <t>iShares 미국채 1-3년</t>
-        </is>
-      </c>
-      <c r="D88" s="29" t="inlineStr">
-        <is>
-          <t>채권</t>
-        </is>
-      </c>
-      <c r="E88" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F88" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G88" s="31" t="n">
-        <v>0.01505337651433369</v>
-      </c>
-      <c r="H88" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C88" s="30" t="inlineStr">
+        <is>
+          <t>SOL 미국배당다우존스</t>
+        </is>
+      </c>
+      <c r="D88" s="30" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="E88" s="30" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="F88" s="31" t="inlineStr">
+        <is>
+          <t>1조원</t>
+        </is>
+      </c>
+      <c r="G88" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H88" s="34" t="n">
+        <v>0.0001</v>
       </c>
     </row>
     <row r="89">
@@ -5759,31 +5830,31 @@
       </c>
       <c r="C89" s="14" t="inlineStr">
         <is>
-          <t>iShares 미국채 7-10년</t>
+          <t>RISE 미국테크100데일리고정커버드콜</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
         <is>
-          <t>채권</t>
+          <t>커버드콜</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F89" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G89" s="28" t="n">
-        <v>-0.02675355856628381</v>
-      </c>
-      <c r="H89" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="F89" s="28" t="inlineStr">
+        <is>
+          <t>5,772억원</t>
+        </is>
+      </c>
+      <c r="G89" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H89" s="33" t="n">
+        <v>0.0025</v>
       </c>
     </row>
     <row r="90">
@@ -5792,38 +5863,36 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B90" s="29" t="inlineStr">
+      <c r="B90" s="30" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="C90" s="29" t="inlineStr">
-        <is>
-          <t>iShares 미국채 20년+</t>
-        </is>
-      </c>
-      <c r="D90" s="29" t="inlineStr">
-        <is>
-          <t>채권</t>
-        </is>
-      </c>
-      <c r="E90" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F90" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G90" s="31" t="n">
-        <v>-0.05711503892809356</v>
-      </c>
-      <c r="H90" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C90" s="30" t="inlineStr">
+        <is>
+          <t>SOL 미국배당미국채혼합50</t>
+        </is>
+      </c>
+      <c r="D90" s="30" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="E90" s="30" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="F90" s="31" t="inlineStr">
+        <is>
+          <t>4,730억원</t>
+        </is>
+      </c>
+      <c r="G90" s="32" t="n">
+        <v>0.1038174106241163</v>
+      </c>
+      <c r="H90" s="34" t="n">
+        <v>0.0015</v>
       </c>
     </row>
     <row r="91">
@@ -5839,31 +5908,31 @@
       </c>
       <c r="C91" s="14" t="inlineStr">
         <is>
-          <t>iShares 미국 종합채권</t>
+          <t>ACE 미국30년국채액티브</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
         <is>
-          <t>채권</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F91" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G91" s="28" t="n">
-        <v>-0.00707032975902111</v>
-      </c>
-      <c r="H91" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>한국투자신탁운용</t>
+        </is>
+      </c>
+      <c r="F91" s="28" t="inlineStr">
+        <is>
+          <t>3,871억원</t>
+        </is>
+      </c>
+      <c r="G91" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H91" s="33" t="n">
+        <v>0.0005</v>
       </c>
     </row>
     <row r="92">
@@ -5872,38 +5941,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B92" s="29" t="inlineStr">
+      <c r="B92" s="30" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="C92" s="29" t="inlineStr">
-        <is>
-          <t>iShares 투자등급 회사채</t>
-        </is>
-      </c>
-      <c r="D92" s="29" t="inlineStr">
-        <is>
-          <t>채권</t>
-        </is>
-      </c>
-      <c r="E92" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F92" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G92" s="31" t="n">
-        <v>-0.02183448542608113</v>
-      </c>
-      <c r="H92" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C92" s="30" t="inlineStr">
+        <is>
+          <t>ACE 베트남VN30(합성)</t>
+        </is>
+      </c>
+      <c r="D92" s="30" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="E92" s="30" t="inlineStr">
+        <is>
+          <t>한국투신운용(ETF)</t>
+        </is>
+      </c>
+      <c r="F92" s="31" t="inlineStr">
+        <is>
+          <t>3,787억원</t>
+        </is>
+      </c>
+      <c r="G92" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H92" s="34" t="n">
+        <v>0.006999999999999999</v>
       </c>
     </row>
     <row r="93">
@@ -5919,31 +5988,31 @@
       </c>
       <c r="C93" s="14" t="inlineStr">
         <is>
-          <t>iShares 하이일드 회사채</t>
+          <t>RISE 글로벌자산배분액티브</t>
         </is>
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>채권</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F93" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G93" s="28" t="n">
-        <v>0.02786343669994706</v>
-      </c>
-      <c r="H93" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>KB자산운용</t>
+        </is>
+      </c>
+      <c r="F93" s="28" t="inlineStr">
+        <is>
+          <t>2,812억원</t>
+        </is>
+      </c>
+      <c r="G93" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H93" s="33" t="n">
+        <v>0.0001</v>
       </c>
     </row>
     <row r="94">
@@ -5952,38 +6021,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B94" s="29" t="inlineStr">
+      <c r="B94" s="30" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="C94" s="29" t="inlineStr">
-        <is>
-          <t>SPDR 금</t>
-        </is>
-      </c>
-      <c r="D94" s="29" t="inlineStr">
-        <is>
-          <t>대체</t>
-        </is>
-      </c>
-      <c r="E94" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F94" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G94" s="31" t="n">
-        <v>0.1905214114016085</v>
-      </c>
-      <c r="H94" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C94" s="30" t="inlineStr">
+        <is>
+          <t>TIME 글로벌우주테크&amp;방산액티브</t>
+        </is>
+      </c>
+      <c r="D94" s="30" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="E94" s="30" t="inlineStr">
+        <is>
+          <t>타임폴리오자산운용</t>
+        </is>
+      </c>
+      <c r="F94" s="31" t="inlineStr">
+        <is>
+          <t>2,248억원</t>
+        </is>
+      </c>
+      <c r="G94" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H94" s="34" t="n">
+        <v>0.008</v>
       </c>
     </row>
     <row r="95">
@@ -5999,12 +6068,12 @@
       </c>
       <c r="C95" s="14" t="inlineStr">
         <is>
-          <t>iShares 은</t>
+          <t>TIGER 일본반도체FACTSET</t>
         </is>
       </c>
       <c r="D95" s="14" t="inlineStr">
         <is>
-          <t>대체</t>
+          <t>일본</t>
         </is>
       </c>
       <c r="E95" s="14" t="inlineStr">
@@ -6012,15 +6081,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F95" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G95" s="28" t="n">
-        <v>0.5858692775866632</v>
-      </c>
-      <c r="H95" s="28" t="inlineStr">
+      <c r="F95" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G95" s="29" t="n">
+        <v>0.9668285455593053</v>
+      </c>
+      <c r="H95" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6032,35 +6101,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B96" s="29" t="inlineStr">
+      <c r="B96" s="30" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="C96" s="29" t="inlineStr">
-        <is>
-          <t>United States 원유</t>
-        </is>
-      </c>
-      <c r="D96" s="29" t="inlineStr">
-        <is>
-          <t>대체</t>
-        </is>
-      </c>
-      <c r="E96" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F96" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G96" s="31" t="n">
-        <v>1.051754034947312</v>
-      </c>
-      <c r="H96" s="31" t="inlineStr">
+      <c r="C96" s="30" t="inlineStr">
+        <is>
+          <t>ACE 일본반도체</t>
+        </is>
+      </c>
+      <c r="D96" s="30" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="E96" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F96" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G96" s="32" t="n">
+        <v>0.9853061894598586</v>
+      </c>
+      <c r="H96" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6079,12 +6148,12 @@
       </c>
       <c r="C97" s="14" t="inlineStr">
         <is>
-          <t>Invesco 원자재</t>
+          <t>TIGER 차이나테크TOP10</t>
         </is>
       </c>
       <c r="D97" s="14" t="inlineStr">
         <is>
-          <t>대체</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
@@ -6092,15 +6161,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F97" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G97" s="28" t="n">
-        <v>0.5101417506271237</v>
-      </c>
-      <c r="H97" s="28" t="inlineStr">
+      <c r="F97" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G97" s="29" t="n">
+        <v>0.1009962212298179</v>
+      </c>
+      <c r="H97" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6112,35 +6181,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B98" s="29" t="inlineStr">
+      <c r="B98" s="30" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="C98" s="29" t="inlineStr">
-        <is>
-          <t>Vanguard 미국 리츠</t>
-        </is>
-      </c>
-      <c r="D98" s="29" t="inlineStr">
-        <is>
-          <t>대체</t>
-        </is>
-      </c>
-      <c r="E98" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F98" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G98" s="31" t="n">
-        <v>0.04842313369172224</v>
-      </c>
-      <c r="H98" s="31" t="inlineStr">
+      <c r="C98" s="30" t="inlineStr">
+        <is>
+          <t>TIGER 차이나휴머노이드로봇</t>
+        </is>
+      </c>
+      <c r="D98" s="30" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="E98" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F98" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G98" s="32" t="n">
+        <v>-0.1815528829147506</v>
+      </c>
+      <c r="H98" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6159,12 +6228,12 @@
       </c>
       <c r="C99" s="14" t="inlineStr">
         <is>
-          <t>Schwab 미국 배당주</t>
+          <t>TIGER 차이나반도체FACTSET</t>
         </is>
       </c>
       <c r="D99" s="14" t="inlineStr">
         <is>
-          <t>주식</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr">
@@ -6172,15 +6241,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="F99" s="27" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G99" s="28" t="n">
-        <v>0.2710968871712811</v>
-      </c>
-      <c r="H99" s="28" t="inlineStr">
+      <c r="F99" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G99" s="29" t="n">
+        <v>0.6281575481862804</v>
+      </c>
+      <c r="H99" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6192,35 +6261,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B100" s="29" t="inlineStr">
+      <c r="B100" s="30" t="inlineStr">
         <is>
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="C100" s="29" t="inlineStr">
-        <is>
-          <t>Vanguard 배당성장</t>
-        </is>
-      </c>
-      <c r="D100" s="29" t="inlineStr">
-        <is>
-          <t>주식</t>
-        </is>
-      </c>
-      <c r="E100" s="29" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F100" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G100" s="31" t="n">
-        <v>0.1164247275358388</v>
-      </c>
-      <c r="H100" s="31" t="inlineStr">
+      <c r="C100" s="30" t="inlineStr">
+        <is>
+          <t>TIME 차이나AI테크액티브</t>
+        </is>
+      </c>
+      <c r="D100" s="30" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="E100" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F100" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G100" s="32" t="n">
+        <v>0.5834338560514676</v>
+      </c>
+      <c r="H100" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -6234,35 +6303,35 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>삼성MMF법인 1</t>
+          <t>TIGER 차이나과창판STAR50(합성)</t>
         </is>
       </c>
       <c r="D101" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용</t>
-        </is>
-      </c>
-      <c r="F101" s="27" t="inlineStr">
-        <is>
-          <t>11조원</t>
-        </is>
-      </c>
-      <c r="G101" s="28" t="n">
-        <v>0.029549</v>
-      </c>
-      <c r="H101" s="27" t="inlineStr">
-        <is>
-          <t>0.05~0.09%</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F101" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G101" s="29" t="n">
+        <v>0.3799247673727975</v>
+      </c>
+      <c r="H101" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6272,37 +6341,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B102" s="29" t="inlineStr">
-        <is>
-          <t>국내펀드</t>
-        </is>
-      </c>
-      <c r="C102" s="29" t="inlineStr">
-        <is>
-          <t>우리큰만족법인MMF 1(국공채)</t>
-        </is>
-      </c>
-      <c r="D102" s="29" t="inlineStr">
-        <is>
-          <t>MMF</t>
-        </is>
-      </c>
-      <c r="E102" s="29" t="inlineStr">
-        <is>
-          <t>우리자산운용</t>
-        </is>
-      </c>
-      <c r="F102" s="30" t="inlineStr">
-        <is>
-          <t>9조원</t>
-        </is>
-      </c>
-      <c r="G102" s="31" t="n">
-        <v>0.028073</v>
-      </c>
-      <c r="H102" s="30" t="inlineStr">
-        <is>
-          <t>0.08~0.10%</t>
+      <c r="B102" s="30" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+      <c r="C102" s="30" t="inlineStr">
+        <is>
+          <t>ACE 중국과창판STAR50</t>
+        </is>
+      </c>
+      <c r="D102" s="30" t="inlineStr">
+        <is>
+          <t>중국</t>
+        </is>
+      </c>
+      <c r="E102" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F102" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G102" s="32" t="n">
+        <v>0.3397005678884875</v>
+      </c>
+      <c r="H102" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6314,35 +6383,35 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
-          <t>IBK그랑프리국공채MMF법인투자신탁 1[국공채]</t>
+          <t>TIGER 글로벌AI액티브</t>
         </is>
       </c>
       <c r="D103" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>반도체&amp;A.I.</t>
         </is>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>아이비케이자산운용</t>
-        </is>
-      </c>
-      <c r="F103" s="27" t="inlineStr">
-        <is>
-          <t>8조원</t>
-        </is>
-      </c>
-      <c r="G103" s="28" t="n">
-        <v>0.028188</v>
-      </c>
-      <c r="H103" s="27" t="inlineStr">
-        <is>
-          <t>0.09~0.17%</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F103" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G103" s="29" t="n">
+        <v>0.5453767123287672</v>
+      </c>
+      <c r="H103" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6352,37 +6421,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B104" s="29" t="inlineStr">
-        <is>
-          <t>국내펀드</t>
-        </is>
-      </c>
-      <c r="C104" s="29" t="inlineStr">
-        <is>
-          <t>KB법인용MMF I-1(운용)</t>
-        </is>
-      </c>
-      <c r="D104" s="29" t="inlineStr">
-        <is>
-          <t>MMF</t>
-        </is>
-      </c>
-      <c r="E104" s="29" t="inlineStr">
-        <is>
-          <t>케이비자산운용</t>
-        </is>
-      </c>
-      <c r="F104" s="30" t="inlineStr">
-        <is>
-          <t>8조원</t>
-        </is>
-      </c>
-      <c r="G104" s="31" t="n">
-        <v>0.029889</v>
-      </c>
-      <c r="H104" s="30" t="inlineStr">
-        <is>
-          <t>0.06~0.09%</t>
+      <c r="B104" s="30" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+      <c r="C104" s="30" t="inlineStr">
+        <is>
+          <t>TIGER 미국필라델피아반도체나스닥</t>
+        </is>
+      </c>
+      <c r="D104" s="30" t="inlineStr">
+        <is>
+          <t>반도체&amp;A.I.</t>
+        </is>
+      </c>
+      <c r="E104" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F104" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G104" s="32" t="n">
+        <v>1.028919257049369</v>
+      </c>
+      <c r="H104" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6394,35 +6463,35 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>국내펀드</t>
+          <t>해외ETF</t>
         </is>
       </c>
       <c r="C105" s="14" t="inlineStr">
         <is>
-          <t>우리큰만족신종MMF3</t>
+          <t>RISE 미국반도체NYSE</t>
         </is>
       </c>
       <c r="D105" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>반도체&amp;A.I.</t>
         </is>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>우리자산운용</t>
-        </is>
-      </c>
-      <c r="F105" s="27" t="inlineStr">
-        <is>
-          <t>7조원</t>
-        </is>
-      </c>
-      <c r="G105" s="28" t="n">
-        <v>0.030522</v>
-      </c>
-      <c r="H105" s="27" t="inlineStr">
-        <is>
-          <t>0.09~0.11%</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F105" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G105" s="29" t="n">
+        <v>1.122321919062443</v>
+      </c>
+      <c r="H105" s="29" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6432,37 +6501,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B106" s="29" t="inlineStr">
-        <is>
-          <t>국내펀드</t>
-        </is>
-      </c>
-      <c r="C106" s="29" t="inlineStr">
-        <is>
-          <t>신영법인용MMF4-26_운용</t>
-        </is>
-      </c>
-      <c r="D106" s="29" t="inlineStr">
-        <is>
-          <t>MMF</t>
-        </is>
-      </c>
-      <c r="E106" s="29" t="inlineStr">
-        <is>
-          <t>신영자산운용</t>
-        </is>
-      </c>
-      <c r="F106" s="30" t="inlineStr">
-        <is>
-          <t>7조원</t>
-        </is>
-      </c>
-      <c r="G106" s="31" t="n">
-        <v>0.028373</v>
-      </c>
-      <c r="H106" s="30" t="inlineStr">
-        <is>
-          <t>0.10~0.15%</t>
+      <c r="B106" s="30" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+      <c r="C106" s="30" t="inlineStr">
+        <is>
+          <t>RISE 글로벌원자력</t>
+        </is>
+      </c>
+      <c r="D106" s="30" t="inlineStr">
+        <is>
+          <t>원자력&amp;전력인프라</t>
+        </is>
+      </c>
+      <c r="E106" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F106" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G106" s="32" t="n">
+        <v>0.1217499362732603</v>
+      </c>
+      <c r="H106" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -6479,30 +6548,30 @@
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>신한BEST신종법인용MMFGS-2(종류)</t>
+          <t>코레이트셀렉트단기채증권투자신탁[채권]</t>
         </is>
       </c>
       <c r="D107" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="F107" s="27" t="inlineStr">
-        <is>
-          <t>6조원</t>
-        </is>
-      </c>
-      <c r="G107" s="28" t="n">
-        <v>0.029896</v>
-      </c>
-      <c r="H107" s="27" t="inlineStr">
-        <is>
-          <t>0.07~0.09%</t>
+          <t>코레이트자산운용</t>
+        </is>
+      </c>
+      <c r="F107" s="28" t="inlineStr">
+        <is>
+          <t>2조원</t>
+        </is>
+      </c>
+      <c r="G107" s="29" t="n">
+        <v>0.035442</v>
+      </c>
+      <c r="H107" s="28" t="inlineStr">
+        <is>
+          <t>0.17~0.42%</t>
         </is>
       </c>
     </row>
@@ -6512,37 +6581,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B108" s="29" t="inlineStr">
+      <c r="B108" s="30" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="C108" s="29" t="inlineStr">
-        <is>
-          <t>한화골드법인MMF-KM3(국공채)</t>
-        </is>
-      </c>
-      <c r="D108" s="29" t="inlineStr">
-        <is>
-          <t>MMF</t>
-        </is>
-      </c>
-      <c r="E108" s="29" t="inlineStr">
-        <is>
-          <t>한화자산운용</t>
-        </is>
-      </c>
-      <c r="F108" s="30" t="inlineStr">
-        <is>
-          <t>5조원</t>
-        </is>
-      </c>
-      <c r="G108" s="31" t="n">
-        <v>0.028207</v>
-      </c>
-      <c r="H108" s="30" t="inlineStr">
-        <is>
-          <t>0.06~0.10%</t>
+      <c r="C108" s="30" t="inlineStr">
+        <is>
+          <t>KB내일드림초단기채증권투자신탁(채권)(운용)</t>
+        </is>
+      </c>
+      <c r="D108" s="30" t="inlineStr">
+        <is>
+          <t>국내채권형</t>
+        </is>
+      </c>
+      <c r="E108" s="30" t="inlineStr">
+        <is>
+          <t>케이비자산운용</t>
+        </is>
+      </c>
+      <c r="F108" s="31" t="inlineStr">
+        <is>
+          <t>2조원</t>
+        </is>
+      </c>
+      <c r="G108" s="32" t="n">
+        <v>0.030674</v>
+      </c>
+      <c r="H108" s="31" t="inlineStr">
+        <is>
+          <t>0.09~0.23%</t>
         </is>
       </c>
     </row>
@@ -6559,30 +6628,30 @@
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t>하나클래스원신종MMF(K-5)</t>
+          <t>신한초단기채증권투자신탁[채권](종류)</t>
         </is>
       </c>
       <c r="D109" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>하나자산운용</t>
-        </is>
-      </c>
-      <c r="F109" s="27" t="inlineStr">
-        <is>
-          <t>5조원</t>
-        </is>
-      </c>
-      <c r="G109" s="28" t="n">
-        <v>0.028155</v>
-      </c>
-      <c r="H109" s="27" t="inlineStr">
-        <is>
-          <t>0.11~0.16%</t>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="F109" s="28" t="inlineStr">
+        <is>
+          <t>2조원</t>
+        </is>
+      </c>
+      <c r="G109" s="29" t="n">
+        <v>0.031232</v>
+      </c>
+      <c r="H109" s="28" t="inlineStr">
+        <is>
+          <t>0.08~0.38%</t>
         </is>
       </c>
     </row>
@@ -6592,37 +6661,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B110" s="29" t="inlineStr">
+      <c r="B110" s="30" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="C110" s="29" t="inlineStr">
-        <is>
-          <t>한국투자법인용MMF 2(국공채)</t>
-        </is>
-      </c>
-      <c r="D110" s="29" t="inlineStr">
-        <is>
-          <t>MMF</t>
-        </is>
-      </c>
-      <c r="E110" s="29" t="inlineStr">
-        <is>
-          <t>한국투자신탁운용</t>
-        </is>
-      </c>
-      <c r="F110" s="30" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G110" s="31" t="n">
-        <v>0.028016</v>
-      </c>
-      <c r="H110" s="30" t="inlineStr">
-        <is>
-          <t>0.06~0.16%</t>
+      <c r="C110" s="30" t="inlineStr">
+        <is>
+          <t>KB퇴직연금배당40증권자투자신탁(채권혼합)</t>
+        </is>
+      </c>
+      <c r="D110" s="30" t="inlineStr">
+        <is>
+          <t>국내혼합형</t>
+        </is>
+      </c>
+      <c r="E110" s="30" t="inlineStr">
+        <is>
+          <t>케이비자산운용</t>
+        </is>
+      </c>
+      <c r="F110" s="31" t="inlineStr">
+        <is>
+          <t>1조원</t>
+        </is>
+      </c>
+      <c r="G110" s="32" t="n">
+        <v>0.332035</v>
+      </c>
+      <c r="H110" s="31" t="inlineStr">
+        <is>
+          <t>0.46~0.80%</t>
         </is>
       </c>
     </row>
@@ -6639,30 +6708,30 @@
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>미래에셋법인전용MMF 1(국공채)</t>
+          <t>키움더드림단기채증권투자신탁[채권]</t>
         </is>
       </c>
       <c r="D111" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="F111" s="27" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G111" s="28" t="n">
-        <v>0.027934</v>
-      </c>
-      <c r="H111" s="27" t="inlineStr">
-        <is>
-          <t>0.05~0.15%</t>
+          <t>키움투자자산운용</t>
+        </is>
+      </c>
+      <c r="F111" s="28" t="inlineStr">
+        <is>
+          <t>1조원</t>
+        </is>
+      </c>
+      <c r="G111" s="29" t="n">
+        <v>0.027245</v>
+      </c>
+      <c r="H111" s="28" t="inlineStr">
+        <is>
+          <t>0.07~0.33%</t>
         </is>
       </c>
     </row>
@@ -6672,37 +6741,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B112" s="29" t="inlineStr">
+      <c r="B112" s="30" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="C112" s="29" t="inlineStr">
-        <is>
-          <t>브이아이천하제일법인MMF1</t>
-        </is>
-      </c>
-      <c r="D112" s="29" t="inlineStr">
-        <is>
-          <t>MMF</t>
-        </is>
-      </c>
-      <c r="E112" s="29" t="inlineStr">
-        <is>
-          <t>브이아이자산운용</t>
-        </is>
-      </c>
-      <c r="F112" s="30" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G112" s="31" t="n">
-        <v>0.028224</v>
-      </c>
-      <c r="H112" s="30" t="inlineStr">
-        <is>
-          <t>0.09~0.12%</t>
+      <c r="C112" s="30" t="inlineStr">
+        <is>
+          <t>유진챔피언단기채증권자투자신탁(채권)</t>
+        </is>
+      </c>
+      <c r="D112" s="30" t="inlineStr">
+        <is>
+          <t>국내채권형</t>
+        </is>
+      </c>
+      <c r="E112" s="30" t="inlineStr">
+        <is>
+          <t>유진자산운용</t>
+        </is>
+      </c>
+      <c r="F112" s="31" t="inlineStr">
+        <is>
+          <t>1조원</t>
+        </is>
+      </c>
+      <c r="G112" s="32" t="n">
+        <v>0.025852</v>
+      </c>
+      <c r="H112" s="31" t="inlineStr">
+        <is>
+          <t>0.10~0.39%</t>
         </is>
       </c>
     </row>
@@ -6719,29 +6788,31 @@
       </c>
       <c r="C113" s="14" t="inlineStr">
         <is>
-          <t>NH-Amundi법인MMF 8</t>
+          <t>삼성ABF코리아장기채권인덱스증권투자신탁[채권]</t>
         </is>
       </c>
       <c r="D113" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>엔에이치아문디자산운용</t>
-        </is>
-      </c>
-      <c r="F113" s="27" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G113" s="28" t="n">
-        <v>0.027945</v>
-      </c>
-      <c r="H113" s="32" t="n">
-        <v>0.001</v>
+          <t>삼성자산운용</t>
+        </is>
+      </c>
+      <c r="F113" s="28" t="inlineStr">
+        <is>
+          <t>1조원</t>
+        </is>
+      </c>
+      <c r="G113" s="29" t="n">
+        <v>-0.11508</v>
+      </c>
+      <c r="H113" s="28" t="inlineStr">
+        <is>
+          <t>0.18~0.60%</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -6750,37 +6821,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B114" s="29" t="inlineStr">
+      <c r="B114" s="30" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="C114" s="29" t="inlineStr">
-        <is>
-          <t>하나신종MMF(S-29)</t>
-        </is>
-      </c>
-      <c r="D114" s="29" t="inlineStr">
-        <is>
-          <t>MMF</t>
-        </is>
-      </c>
-      <c r="E114" s="29" t="inlineStr">
-        <is>
-          <t>하나자산운용</t>
-        </is>
-      </c>
-      <c r="F114" s="30" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G114" s="31" t="n">
-        <v>0.029723</v>
-      </c>
-      <c r="H114" s="30" t="inlineStr">
-        <is>
-          <t>0.09~0.13%</t>
+      <c r="C114" s="30" t="inlineStr">
+        <is>
+          <t>코레이트초단기금리혼합자산투자신탁_운용</t>
+        </is>
+      </c>
+      <c r="D114" s="30" t="inlineStr">
+        <is>
+          <t>국내채권형</t>
+        </is>
+      </c>
+      <c r="E114" s="30" t="inlineStr">
+        <is>
+          <t>코레이트자산운용</t>
+        </is>
+      </c>
+      <c r="F114" s="31" t="inlineStr">
+        <is>
+          <t>9,418억원</t>
+        </is>
+      </c>
+      <c r="G114" s="32" t="n">
+        <v>0.032607</v>
+      </c>
+      <c r="H114" s="31" t="inlineStr">
+        <is>
+          <t>0.11~0.27%</t>
         </is>
       </c>
     </row>
@@ -6797,30 +6868,30 @@
       </c>
       <c r="C115" s="14" t="inlineStr">
         <is>
-          <t>삼성스마트MMF법인 1</t>
+          <t>우리하이플러스채권증권자투자신탁 1(채권)</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용</t>
-        </is>
-      </c>
-      <c r="F115" s="27" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G115" s="28" t="n">
-        <v>0.028099</v>
-      </c>
-      <c r="H115" s="27" t="inlineStr">
-        <is>
-          <t>0.07~0.10%</t>
+          <t>우리자산운용</t>
+        </is>
+      </c>
+      <c r="F115" s="28" t="inlineStr">
+        <is>
+          <t>9,400억원</t>
+        </is>
+      </c>
+      <c r="G115" s="29" t="n">
+        <v>0.018987</v>
+      </c>
+      <c r="H115" s="28" t="inlineStr">
+        <is>
+          <t>0.19~0.59%</t>
         </is>
       </c>
     </row>
@@ -6830,37 +6901,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B116" s="29" t="inlineStr">
+      <c r="B116" s="30" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="C116" s="29" t="inlineStr">
-        <is>
-          <t>신한 BEST법인용MMF GS- 1(종류)</t>
-        </is>
-      </c>
-      <c r="D116" s="29" t="inlineStr">
-        <is>
-          <t>MMF</t>
-        </is>
-      </c>
-      <c r="E116" s="29" t="inlineStr">
-        <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="F116" s="30" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G116" s="31" t="n">
-        <v>0.027833</v>
-      </c>
-      <c r="H116" s="30" t="inlineStr">
-        <is>
-          <t>0.06~0.12%</t>
+      <c r="C116" s="30" t="inlineStr">
+        <is>
+          <t>흥국중기국공채증권투자신탁[채권]</t>
+        </is>
+      </c>
+      <c r="D116" s="30" t="inlineStr">
+        <is>
+          <t>국내채권형</t>
+        </is>
+      </c>
+      <c r="E116" s="30" t="inlineStr">
+        <is>
+          <t>흥국자산운용</t>
+        </is>
+      </c>
+      <c r="F116" s="31" t="inlineStr">
+        <is>
+          <t>8,403억원</t>
+        </is>
+      </c>
+      <c r="G116" s="32" t="n">
+        <v>-0.052859</v>
+      </c>
+      <c r="H116" s="31" t="inlineStr">
+        <is>
+          <t>0.10~0.49%</t>
         </is>
       </c>
     </row>
@@ -6877,30 +6948,30 @@
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>KB법인용MMF I-2(국공채)(운용)</t>
+          <t>신영밸류고배당증권자투자신탁(주식)운용</t>
         </is>
       </c>
       <c r="D117" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
-        </is>
-      </c>
-      <c r="F117" s="27" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G117" s="28" t="n">
-        <v>0.027897</v>
-      </c>
-      <c r="H117" s="27" t="inlineStr">
-        <is>
-          <t>0.07~0.12%</t>
+          <t>신영자산운용</t>
+        </is>
+      </c>
+      <c r="F117" s="28" t="inlineStr">
+        <is>
+          <t>8,313억원</t>
+        </is>
+      </c>
+      <c r="G117" s="29" t="n">
+        <v>0.825757</v>
+      </c>
+      <c r="H117" s="28" t="inlineStr">
+        <is>
+          <t>0.45~1.35%</t>
         </is>
       </c>
     </row>
@@ -6910,36 +6981,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B118" s="29" t="inlineStr">
+      <c r="B118" s="30" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="C118" s="29" t="inlineStr">
-        <is>
-          <t>BNK법인MMF 1(국공채)</t>
-        </is>
-      </c>
-      <c r="D118" s="29" t="inlineStr">
-        <is>
-          <t>MMF</t>
-        </is>
-      </c>
-      <c r="E118" s="29" t="inlineStr">
-        <is>
-          <t>비엔케이자산운용</t>
-        </is>
-      </c>
-      <c r="F118" s="30" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G118" s="31" t="n">
-        <v>0.028014</v>
-      </c>
-      <c r="H118" s="33" t="n">
-        <v>0.001</v>
+      <c r="C118" s="30" t="inlineStr">
+        <is>
+          <t>한국투자크레딧포커스ESG증권자투자신탁 1(채권)</t>
+        </is>
+      </c>
+      <c r="D118" s="30" t="inlineStr">
+        <is>
+          <t>국내채권형</t>
+        </is>
+      </c>
+      <c r="E118" s="30" t="inlineStr">
+        <is>
+          <t>한국투자신탁운용</t>
+        </is>
+      </c>
+      <c r="F118" s="31" t="inlineStr">
+        <is>
+          <t>8,211억원</t>
+        </is>
+      </c>
+      <c r="G118" s="32" t="n">
+        <v>0.013955</v>
+      </c>
+      <c r="H118" s="31" t="inlineStr">
+        <is>
+          <t>0.18~0.41%</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -6955,29 +7028,31 @@
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>교보악사프라임법인MMF J- 1(운용)</t>
+          <t>우리단기채권증권투자신탁(채권)</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>교보악사자산운용</t>
-        </is>
-      </c>
-      <c r="F119" s="27" t="inlineStr">
-        <is>
-          <t>4조원</t>
-        </is>
-      </c>
-      <c r="G119" s="28" t="n">
-        <v>0.028143</v>
-      </c>
-      <c r="H119" s="32" t="n">
-        <v>0.00108</v>
+          <t>우리자산운용</t>
+        </is>
+      </c>
+      <c r="F119" s="28" t="inlineStr">
+        <is>
+          <t>8,118억원</t>
+        </is>
+      </c>
+      <c r="G119" s="29" t="n">
+        <v>0.027101</v>
+      </c>
+      <c r="H119" s="28" t="inlineStr">
+        <is>
+          <t>0.10~0.45%</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -6986,36 +7061,38 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B120" s="29" t="inlineStr">
+      <c r="B120" s="30" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="C120" s="29" t="inlineStr">
-        <is>
-          <t>DB클린법인MMF 4운용</t>
-        </is>
-      </c>
-      <c r="D120" s="29" t="inlineStr">
-        <is>
-          <t>MMF</t>
-        </is>
-      </c>
-      <c r="E120" s="29" t="inlineStr">
-        <is>
-          <t>디비자산운용</t>
-        </is>
-      </c>
-      <c r="F120" s="30" t="inlineStr">
-        <is>
-          <t>3조원</t>
-        </is>
-      </c>
-      <c r="G120" s="31" t="n">
-        <v>0.028008</v>
-      </c>
-      <c r="H120" s="33" t="n">
-        <v>0.001</v>
+      <c r="C120" s="30" t="inlineStr">
+        <is>
+          <t>마이다스액티브중기우량채권증권투자신탁(채권)(운용)</t>
+        </is>
+      </c>
+      <c r="D120" s="30" t="inlineStr">
+        <is>
+          <t>국내채권형</t>
+        </is>
+      </c>
+      <c r="E120" s="30" t="inlineStr">
+        <is>
+          <t>마이다스에셋자산운용</t>
+        </is>
+      </c>
+      <c r="F120" s="31" t="inlineStr">
+        <is>
+          <t>7,485억원</t>
+        </is>
+      </c>
+      <c r="G120" s="32" t="n">
+        <v>-0.05042099999999999</v>
+      </c>
+      <c r="H120" s="31" t="inlineStr">
+        <is>
+          <t>0.11~0.12%</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -7031,31 +7108,31 @@
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>Plus신종법인용MMF 1</t>
+          <t>삼성액티브채권증권투자신탁[채권-파생형]</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>플러스자산운용</t>
-        </is>
-      </c>
-      <c r="F121" s="27" t="inlineStr">
-        <is>
-          <t>3조원</t>
-        </is>
-      </c>
-      <c r="G121" s="28" t="n">
-        <v>0.029821</v>
-      </c>
-      <c r="H121" s="27" t="inlineStr">
-        <is>
-          <t>0.10~0.11%</t>
-        </is>
+          <t>삼성자산운용</t>
+        </is>
+      </c>
+      <c r="F121" s="28" t="inlineStr">
+        <is>
+          <t>6,799억원</t>
+        </is>
+      </c>
+      <c r="G121" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H121" s="33" t="n">
+        <v>0.0012</v>
       </c>
     </row>
     <row r="122">
@@ -7064,37 +7141,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B122" s="29" t="inlineStr">
+      <c r="B122" s="30" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="C122" s="29" t="inlineStr">
-        <is>
-          <t>플러스국공채법인용MMF3</t>
-        </is>
-      </c>
-      <c r="D122" s="29" t="inlineStr">
-        <is>
-          <t>MMF</t>
-        </is>
-      </c>
-      <c r="E122" s="29" t="inlineStr">
-        <is>
-          <t>플러스자산운용</t>
-        </is>
-      </c>
-      <c r="F122" s="30" t="inlineStr">
-        <is>
-          <t>3조원</t>
-        </is>
-      </c>
-      <c r="G122" s="31" t="n">
-        <v>0.028117</v>
-      </c>
-      <c r="H122" s="30" t="inlineStr">
-        <is>
-          <t>0.06~0.10%</t>
+      <c r="C122" s="30" t="inlineStr">
+        <is>
+          <t>미래에셋코어테크증권자투자신탁(주식)</t>
+        </is>
+      </c>
+      <c r="D122" s="30" t="inlineStr">
+        <is>
+          <t>국내주식형</t>
+        </is>
+      </c>
+      <c r="E122" s="30" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="F122" s="31" t="inlineStr">
+        <is>
+          <t>5,896억원</t>
+        </is>
+      </c>
+      <c r="G122" s="32" t="n">
+        <v>1.693829</v>
+      </c>
+      <c r="H122" s="31" t="inlineStr">
+        <is>
+          <t>0.76~1.75%</t>
         </is>
       </c>
     </row>
@@ -7111,30 +7188,30 @@
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>미래에셋법인전용MMF A-4</t>
+          <t>하나초단기채증권투자신탁[채권]</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
-        </is>
-      </c>
-      <c r="F123" s="27" t="inlineStr">
-        <is>
-          <t>3조원</t>
-        </is>
-      </c>
-      <c r="G123" s="28" t="n">
-        <v>0.030076</v>
-      </c>
-      <c r="H123" s="27" t="inlineStr">
-        <is>
-          <t>0.05~0.09%</t>
+          <t>하나자산운용</t>
+        </is>
+      </c>
+      <c r="F123" s="28" t="inlineStr">
+        <is>
+          <t>5,886억원</t>
+        </is>
+      </c>
+      <c r="G123" s="29" t="n">
+        <v>0.03154</v>
+      </c>
+      <c r="H123" s="28" t="inlineStr">
+        <is>
+          <t>0.14~0.41%</t>
         </is>
       </c>
     </row>
@@ -7144,37 +7221,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B124" s="29" t="inlineStr">
+      <c r="B124" s="30" t="inlineStr">
         <is>
           <t>국내펀드</t>
         </is>
       </c>
-      <c r="C124" s="29" t="inlineStr">
-        <is>
-          <t>키움프런티어법인용MMF 3[국공채]</t>
-        </is>
-      </c>
-      <c r="D124" s="29" t="inlineStr">
-        <is>
-          <t>MMF</t>
-        </is>
-      </c>
-      <c r="E124" s="29" t="inlineStr">
-        <is>
-          <t>키움투자자산운용</t>
-        </is>
-      </c>
-      <c r="F124" s="30" t="inlineStr">
-        <is>
-          <t>2조원</t>
-        </is>
-      </c>
-      <c r="G124" s="31" t="n">
-        <v>0.027922</v>
-      </c>
-      <c r="H124" s="30" t="inlineStr">
-        <is>
-          <t>0.10~0.24%</t>
+      <c r="C124" s="30" t="inlineStr">
+        <is>
+          <t>교보악사Tomorrow장기우량증권투자신탁K- 1(채권)(운용)</t>
+        </is>
+      </c>
+      <c r="D124" s="30" t="inlineStr">
+        <is>
+          <t>국내채권형</t>
+        </is>
+      </c>
+      <c r="E124" s="30" t="inlineStr">
+        <is>
+          <t>교보악사자산운용</t>
+        </is>
+      </c>
+      <c r="F124" s="31" t="inlineStr">
+        <is>
+          <t>5,515억원</t>
+        </is>
+      </c>
+      <c r="G124" s="32" t="n">
+        <v>-0.05993</v>
+      </c>
+      <c r="H124" s="31" t="inlineStr">
+        <is>
+          <t>0.12~0.42%</t>
         </is>
       </c>
     </row>
@@ -7191,30 +7268,30 @@
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>대신국공채법인전용MMF 1(운용)</t>
+          <t>마이다스초단기채프리미엄증권투자신탁(채권)(운용)</t>
         </is>
       </c>
       <c r="D125" s="14" t="inlineStr">
         <is>
-          <t>MMF</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>대신자산운용</t>
-        </is>
-      </c>
-      <c r="F125" s="27" t="inlineStr">
-        <is>
-          <t>2조원</t>
-        </is>
-      </c>
-      <c r="G125" s="28" t="n">
-        <v>0.028038</v>
-      </c>
-      <c r="H125" s="27" t="inlineStr">
-        <is>
-          <t>0.07~0.10%</t>
+          <t>마이다스에셋자산운용</t>
+        </is>
+      </c>
+      <c r="F125" s="28" t="inlineStr">
+        <is>
+          <t>5,025억원</t>
+        </is>
+      </c>
+      <c r="G125" s="29" t="n">
+        <v>0.036258</v>
+      </c>
+      <c r="H125" s="28" t="inlineStr">
+        <is>
+          <t>0.10~0.40%</t>
         </is>
       </c>
     </row>
@@ -7224,37 +7301,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B126" s="29" t="inlineStr">
-        <is>
-          <t>해외펀드</t>
-        </is>
-      </c>
-      <c r="C126" s="29" t="inlineStr">
-        <is>
-          <t>피델리티글로벌테크놀로지증권자투자신탁(주식-재간접형)</t>
-        </is>
-      </c>
-      <c r="D126" s="29" t="inlineStr">
-        <is>
-          <t>해외주식형</t>
-        </is>
-      </c>
-      <c r="E126" s="29" t="inlineStr">
-        <is>
-          <t>피델리티자산운용</t>
-        </is>
-      </c>
-      <c r="F126" s="30" t="inlineStr">
-        <is>
-          <t>9,218억원</t>
-        </is>
-      </c>
-      <c r="G126" s="31" t="n">
-        <v>0.20358</v>
-      </c>
-      <c r="H126" s="30" t="inlineStr">
-        <is>
-          <t>0.16~1.36%</t>
+      <c r="B126" s="30" t="inlineStr">
+        <is>
+          <t>국내펀드</t>
+        </is>
+      </c>
+      <c r="C126" s="30" t="inlineStr">
+        <is>
+          <t>미래에셋퇴직연금고배당포커스증권자투자신탁 1(주식)</t>
+        </is>
+      </c>
+      <c r="D126" s="30" t="inlineStr">
+        <is>
+          <t>국내주식형</t>
+        </is>
+      </c>
+      <c r="E126" s="30" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="F126" s="31" t="inlineStr">
+        <is>
+          <t>4,993억원</t>
+        </is>
+      </c>
+      <c r="G126" s="32" t="n">
+        <v>1.006412</v>
+      </c>
+      <c r="H126" s="31" t="inlineStr">
+        <is>
+          <t>0.80~1.20%</t>
         </is>
       </c>
     </row>
@@ -7266,35 +7343,35 @@
       </c>
       <c r="B127" s="14" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="C127" s="14" t="inlineStr">
         <is>
-          <t>피델리티월지급식아시아하이일드증권자투자신탁[채권-재간접형]</t>
+          <t>하나파워e단기채증권자투자신탁[채권]</t>
         </is>
       </c>
       <c r="D127" s="14" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>피델리티자산운용</t>
-        </is>
-      </c>
-      <c r="F127" s="27" t="inlineStr">
-        <is>
-          <t>7,365억원</t>
-        </is>
-      </c>
-      <c r="G127" s="28" t="n">
-        <v>0.051551</v>
-      </c>
-      <c r="H127" s="27" t="inlineStr">
-        <is>
-          <t>0.37~1.17%</t>
+          <t>하나자산운용</t>
+        </is>
+      </c>
+      <c r="F127" s="28" t="inlineStr">
+        <is>
+          <t>4,958억원</t>
+        </is>
+      </c>
+      <c r="G127" s="29" t="n">
+        <v>0.028457</v>
+      </c>
+      <c r="H127" s="28" t="inlineStr">
+        <is>
+          <t>0.07~0.19%</t>
         </is>
       </c>
     </row>
@@ -7304,38 +7381,36 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B128" s="29" t="inlineStr">
-        <is>
-          <t>해외펀드</t>
-        </is>
-      </c>
-      <c r="C128" s="29" t="inlineStr">
-        <is>
-          <t>피델리티글로벌배당인컴증권자투자신탁(주식-재간접형)</t>
-        </is>
-      </c>
-      <c r="D128" s="29" t="inlineStr">
-        <is>
-          <t>해외주식형</t>
-        </is>
-      </c>
-      <c r="E128" s="29" t="inlineStr">
-        <is>
-          <t>피델리티자산운용</t>
-        </is>
-      </c>
-      <c r="F128" s="30" t="inlineStr">
-        <is>
-          <t>5,716억원</t>
-        </is>
-      </c>
-      <c r="G128" s="31" t="n">
-        <v>0.108062</v>
-      </c>
-      <c r="H128" s="30" t="inlineStr">
-        <is>
-          <t>0.16~1.36%</t>
-        </is>
+      <c r="B128" s="30" t="inlineStr">
+        <is>
+          <t>국내펀드</t>
+        </is>
+      </c>
+      <c r="C128" s="30" t="inlineStr">
+        <is>
+          <t>한화단기플러스증권투자신탁(채권)[운용]</t>
+        </is>
+      </c>
+      <c r="D128" s="30" t="inlineStr">
+        <is>
+          <t>국내채권형</t>
+        </is>
+      </c>
+      <c r="E128" s="30" t="inlineStr">
+        <is>
+          <t>한화자산운용</t>
+        </is>
+      </c>
+      <c r="F128" s="31" t="inlineStr">
+        <is>
+          <t>4,611억원</t>
+        </is>
+      </c>
+      <c r="G128" s="32" t="n">
+        <v>0.009528999999999999</v>
+      </c>
+      <c r="H128" s="34" t="n">
+        <v>0.0005</v>
       </c>
     </row>
     <row r="129">
@@ -7346,35 +7421,35 @@
       </c>
       <c r="B129" s="14" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="C129" s="14" t="inlineStr">
         <is>
-          <t>AB월지급글로벌고수익증권투자신탁[채권-재간접형]</t>
+          <t>한국투자골드플랜연금증권전환형투자신탁 1(주식)</t>
         </is>
       </c>
       <c r="D129" s="14" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>얼라이언스번스틴자산운용</t>
-        </is>
-      </c>
-      <c r="F129" s="27" t="inlineStr">
-        <is>
-          <t>5,462억원</t>
-        </is>
-      </c>
-      <c r="G129" s="28" t="n">
-        <v>0.018373</v>
-      </c>
-      <c r="H129" s="27" t="inlineStr">
-        <is>
-          <t>0.17~0.71%</t>
+          <t>한국투자신탁운용</t>
+        </is>
+      </c>
+      <c r="F129" s="28" t="inlineStr">
+        <is>
+          <t>4,598억원</t>
+        </is>
+      </c>
+      <c r="G129" s="29" t="n">
+        <v>1.197126</v>
+      </c>
+      <c r="H129" s="28" t="inlineStr">
+        <is>
+          <t>0.51~1.18%</t>
         </is>
       </c>
     </row>
@@ -7384,37 +7459,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B130" s="29" t="inlineStr">
-        <is>
-          <t>해외펀드</t>
-        </is>
-      </c>
-      <c r="C130" s="29" t="inlineStr">
-        <is>
-          <t>한국투자글로벌전기차&amp;자율주행증권투자신탁(주식)(모)</t>
-        </is>
-      </c>
-      <c r="D130" s="29" t="inlineStr">
-        <is>
-          <t>해외주식형</t>
-        </is>
-      </c>
-      <c r="E130" s="29" t="inlineStr">
-        <is>
-          <t>한국투자신탁운용</t>
-        </is>
-      </c>
-      <c r="F130" s="30" t="inlineStr">
-        <is>
-          <t>4,762억원</t>
-        </is>
-      </c>
-      <c r="G130" s="31" t="n">
-        <v>0.178201</v>
-      </c>
-      <c r="H130" s="30" t="inlineStr">
-        <is>
-          <t>0.77~2.07%</t>
+      <c r="B130" s="30" t="inlineStr">
+        <is>
+          <t>국내펀드</t>
+        </is>
+      </c>
+      <c r="C130" s="30" t="inlineStr">
+        <is>
+          <t>VIP한국형가치투자증권자투자신탁[주식]</t>
+        </is>
+      </c>
+      <c r="D130" s="30" t="inlineStr">
+        <is>
+          <t>국내주식형</t>
+        </is>
+      </c>
+      <c r="E130" s="30" t="inlineStr">
+        <is>
+          <t>브이아이피자산운용</t>
+        </is>
+      </c>
+      <c r="F130" s="31" t="inlineStr">
+        <is>
+          <t>4,573억원</t>
+        </is>
+      </c>
+      <c r="G130" s="32" t="n">
+        <v>0.220937</v>
+      </c>
+      <c r="H130" s="31" t="inlineStr">
+        <is>
+          <t>1.66~2.61%</t>
         </is>
       </c>
     </row>
@@ -7426,35 +7501,35 @@
       </c>
       <c r="B131" s="14" t="inlineStr">
         <is>
-          <t>해외펀드</t>
+          <t>국내펀드</t>
         </is>
       </c>
       <c r="C131" s="14" t="inlineStr">
         <is>
-          <t>AB미국그로스증권투자신탁(주식-재간접형)</t>
+          <t>교보악사파워인덱스증권투자신탁 1(주식-파생형)(운용)</t>
         </is>
       </c>
       <c r="D131" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>얼라이언스번스틴자산운용</t>
-        </is>
-      </c>
-      <c r="F131" s="27" t="inlineStr">
-        <is>
-          <t>4,438억원</t>
-        </is>
-      </c>
-      <c r="G131" s="28" t="n">
-        <v>0.009127</v>
-      </c>
-      <c r="H131" s="27" t="inlineStr">
-        <is>
-          <t>0.17~1.67%</t>
+          <t>교보악사자산운용</t>
+        </is>
+      </c>
+      <c r="F131" s="28" t="inlineStr">
+        <is>
+          <t>4,523억원</t>
+        </is>
+      </c>
+      <c r="G131" s="29" t="n">
+        <v>1.514075</v>
+      </c>
+      <c r="H131" s="28" t="inlineStr">
+        <is>
+          <t>0.16~1.16%</t>
         </is>
       </c>
     </row>
@@ -7464,37 +7539,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B132" s="29" t="inlineStr">
+      <c r="B132" s="30" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="C132" s="29" t="inlineStr">
-        <is>
-          <t>KB다이나믹적격TDF2030증권자투자신탁(주식혼합-재간접형)(운용)</t>
-        </is>
-      </c>
-      <c r="D132" s="29" t="inlineStr">
-        <is>
-          <t>기타형</t>
-        </is>
-      </c>
-      <c r="E132" s="29" t="inlineStr">
-        <is>
-          <t>케이비자산운용</t>
-        </is>
-      </c>
-      <c r="F132" s="30" t="inlineStr">
-        <is>
-          <t>4,156억원</t>
-        </is>
-      </c>
-      <c r="G132" s="31" t="n">
-        <v>0.189953</v>
-      </c>
-      <c r="H132" s="30" t="inlineStr">
-        <is>
-          <t>0.24~1.19%</t>
+      <c r="C132" s="30" t="inlineStr">
+        <is>
+          <t>피델리티글로벌테크놀로지증권자투자신탁(주식-재간접형)</t>
+        </is>
+      </c>
+      <c r="D132" s="30" t="inlineStr">
+        <is>
+          <t>해외주식형</t>
+        </is>
+      </c>
+      <c r="E132" s="30" t="inlineStr">
+        <is>
+          <t>피델리티자산운용</t>
+        </is>
+      </c>
+      <c r="F132" s="31" t="inlineStr">
+        <is>
+          <t>9,218억원</t>
+        </is>
+      </c>
+      <c r="G132" s="32" t="n">
+        <v>0.20358</v>
+      </c>
+      <c r="H132" s="31" t="inlineStr">
+        <is>
+          <t>0.16~1.36%</t>
         </is>
       </c>
     </row>
@@ -7511,30 +7586,30 @@
       </c>
       <c r="C133" s="14" t="inlineStr">
         <is>
-          <t>우리미국단기채공모주증권자투자신탁 1(H)(채권혼합)</t>
+          <t>피델리티월지급식아시아하이일드증권자투자신탁[채권-재간접형]</t>
         </is>
       </c>
       <c r="D133" s="14" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>우리자산운용</t>
-        </is>
-      </c>
-      <c r="F133" s="27" t="inlineStr">
-        <is>
-          <t>3,558억원</t>
-        </is>
-      </c>
-      <c r="G133" s="28" t="n">
-        <v>0.052435</v>
-      </c>
-      <c r="H133" s="27" t="inlineStr">
-        <is>
-          <t>0.80~1.70%</t>
+          <t>피델리티자산운용</t>
+        </is>
+      </c>
+      <c r="F133" s="28" t="inlineStr">
+        <is>
+          <t>7,365억원</t>
+        </is>
+      </c>
+      <c r="G133" s="29" t="n">
+        <v>0.051551</v>
+      </c>
+      <c r="H133" s="28" t="inlineStr">
+        <is>
+          <t>0.37~1.17%</t>
         </is>
       </c>
     </row>
@@ -7544,37 +7619,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B134" s="29" t="inlineStr">
+      <c r="B134" s="30" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="C134" s="29" t="inlineStr">
-        <is>
-          <t>한국투자미국장기국채증권자투자신탁H(채권-재간접형)(모)</t>
-        </is>
-      </c>
-      <c r="D134" s="29" t="inlineStr">
+      <c r="C134" s="30" t="inlineStr">
+        <is>
+          <t>AB월지급글로벌고수익증권투자신탁[채권-재간접형]</t>
+        </is>
+      </c>
+      <c r="D134" s="30" t="inlineStr">
         <is>
           <t>해외채권형</t>
         </is>
       </c>
-      <c r="E134" s="29" t="inlineStr">
-        <is>
-          <t>한국투자신탁운용</t>
-        </is>
-      </c>
-      <c r="F134" s="30" t="inlineStr">
-        <is>
-          <t>3,124억원</t>
-        </is>
-      </c>
-      <c r="G134" s="31" t="n">
-        <v>-0.063263</v>
-      </c>
-      <c r="H134" s="30" t="inlineStr">
-        <is>
-          <t>0.25~0.85%</t>
+      <c r="E134" s="30" t="inlineStr">
+        <is>
+          <t>얼라이언스번스틴자산운용</t>
+        </is>
+      </c>
+      <c r="F134" s="31" t="inlineStr">
+        <is>
+          <t>5,462억원</t>
+        </is>
+      </c>
+      <c r="G134" s="32" t="n">
+        <v>0.018373</v>
+      </c>
+      <c r="H134" s="31" t="inlineStr">
+        <is>
+          <t>0.17~0.71%</t>
         </is>
       </c>
     </row>
@@ -7591,30 +7666,30 @@
       </c>
       <c r="C135" s="14" t="inlineStr">
         <is>
-          <t>신한마음편한적격TDF2050증권자투자신탁[주식혼합-재간접형](종류)</t>
+          <t>한국투자글로벌전기차&amp;자율주행증권투자신탁(주식)(모)</t>
         </is>
       </c>
       <c r="D135" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="F135" s="27" t="inlineStr">
-        <is>
-          <t>3,079억원</t>
-        </is>
-      </c>
-      <c r="G135" s="28" t="n">
-        <v>0.23546</v>
-      </c>
-      <c r="H135" s="27" t="inlineStr">
-        <is>
-          <t>0.56~1.31%</t>
+          <t>한국투자신탁운용</t>
+        </is>
+      </c>
+      <c r="F135" s="28" t="inlineStr">
+        <is>
+          <t>4,762억원</t>
+        </is>
+      </c>
+      <c r="G135" s="29" t="n">
+        <v>0.178201</v>
+      </c>
+      <c r="H135" s="28" t="inlineStr">
+        <is>
+          <t>0.77~2.07%</t>
         </is>
       </c>
     </row>
@@ -7624,37 +7699,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B136" s="29" t="inlineStr">
+      <c r="B136" s="30" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="C136" s="29" t="inlineStr">
-        <is>
-          <t>신한마음편한적격TDF2035증권자투자신탁[주식혼합-재간접형](종류)</t>
-        </is>
-      </c>
-      <c r="D136" s="29" t="inlineStr">
-        <is>
-          <t>기타형</t>
-        </is>
-      </c>
-      <c r="E136" s="29" t="inlineStr">
-        <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="F136" s="30" t="inlineStr">
-        <is>
-          <t>3,055억원</t>
-        </is>
-      </c>
-      <c r="G136" s="31" t="n">
-        <v>0.177612</v>
-      </c>
-      <c r="H136" s="30" t="inlineStr">
-        <is>
-          <t>0.33~0.82%</t>
+      <c r="C136" s="30" t="inlineStr">
+        <is>
+          <t>AB미국그로스증권투자신탁(주식-재간접형)</t>
+        </is>
+      </c>
+      <c r="D136" s="30" t="inlineStr">
+        <is>
+          <t>해외주식형</t>
+        </is>
+      </c>
+      <c r="E136" s="30" t="inlineStr">
+        <is>
+          <t>얼라이언스번스틴자산운용</t>
+        </is>
+      </c>
+      <c r="F136" s="31" t="inlineStr">
+        <is>
+          <t>4,438억원</t>
+        </is>
+      </c>
+      <c r="G136" s="32" t="n">
+        <v>0.009127</v>
+      </c>
+      <c r="H136" s="31" t="inlineStr">
+        <is>
+          <t>0.17~1.67%</t>
         </is>
       </c>
     </row>
@@ -7671,30 +7746,30 @@
       </c>
       <c r="C137" s="14" t="inlineStr">
         <is>
-          <t>신한미국S&amp;P500인덱스증권자투자신탁(UH)[주식-파생형]</t>
+          <t>KB다이나믹적격TDF2030증권자투자신탁(주식혼합-재간접형)(운용)</t>
         </is>
       </c>
       <c r="D137" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>기타형</t>
         </is>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="F137" s="27" t="inlineStr">
-        <is>
-          <t>2,851억원</t>
-        </is>
-      </c>
-      <c r="G137" s="28" t="n">
-        <v>0.141662</v>
-      </c>
-      <c r="H137" s="27" t="inlineStr">
-        <is>
-          <t>0.26~1.15%</t>
+          <t>케이비자산운용</t>
+        </is>
+      </c>
+      <c r="F137" s="28" t="inlineStr">
+        <is>
+          <t>4,156억원</t>
+        </is>
+      </c>
+      <c r="G137" s="29" t="n">
+        <v>0.189953</v>
+      </c>
+      <c r="H137" s="28" t="inlineStr">
+        <is>
+          <t>0.24~1.19%</t>
         </is>
       </c>
     </row>
@@ -7704,37 +7779,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B138" s="29" t="inlineStr">
+      <c r="B138" s="30" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="C138" s="29" t="inlineStr">
-        <is>
-          <t>삼성글로벌액티브적격TDF2030증권투자신탁H[주식혼합-재간접형]</t>
-        </is>
-      </c>
-      <c r="D138" s="29" t="inlineStr">
-        <is>
-          <t>기타형</t>
-        </is>
-      </c>
-      <c r="E138" s="29" t="inlineStr">
-        <is>
-          <t>삼성자산운용</t>
-        </is>
-      </c>
-      <c r="F138" s="30" t="inlineStr">
-        <is>
-          <t>2,841억원</t>
-        </is>
-      </c>
-      <c r="G138" s="31" t="n">
-        <v>0.097423</v>
-      </c>
-      <c r="H138" s="30" t="inlineStr">
-        <is>
-          <t>0.23~0.76%</t>
+      <c r="C138" s="30" t="inlineStr">
+        <is>
+          <t>우리미국단기채공모주증권자투자신탁 1(H)(채권혼합)</t>
+        </is>
+      </c>
+      <c r="D138" s="30" t="inlineStr">
+        <is>
+          <t>해외혼합형</t>
+        </is>
+      </c>
+      <c r="E138" s="30" t="inlineStr">
+        <is>
+          <t>우리자산운용</t>
+        </is>
+      </c>
+      <c r="F138" s="31" t="inlineStr">
+        <is>
+          <t>3,558억원</t>
+        </is>
+      </c>
+      <c r="G138" s="32" t="n">
+        <v>0.052435</v>
+      </c>
+      <c r="H138" s="31" t="inlineStr">
+        <is>
+          <t>0.80~1.70%</t>
         </is>
       </c>
     </row>
@@ -7751,30 +7826,30 @@
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>NH-Amundi하나로적격TDF2030증권투자신탁[주식혼합-재간접형]</t>
+          <t>한국투자미국장기국채증권자투자신탁H(채권-재간접형)(모)</t>
         </is>
       </c>
       <c r="D139" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>엔에이치아문디자산운용</t>
-        </is>
-      </c>
-      <c r="F139" s="27" t="inlineStr">
-        <is>
-          <t>2,746억원</t>
-        </is>
-      </c>
-      <c r="G139" s="28" t="n">
-        <v>0.110507</v>
-      </c>
-      <c r="H139" s="27" t="inlineStr">
-        <is>
-          <t>0.35~0.80%</t>
+          <t>한국투자신탁운용</t>
+        </is>
+      </c>
+      <c r="F139" s="28" t="inlineStr">
+        <is>
+          <t>3,124억원</t>
+        </is>
+      </c>
+      <c r="G139" s="29" t="n">
+        <v>-0.063263</v>
+      </c>
+      <c r="H139" s="28" t="inlineStr">
+        <is>
+          <t>0.25~0.85%</t>
         </is>
       </c>
     </row>
@@ -7784,37 +7859,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B140" s="29" t="inlineStr">
+      <c r="B140" s="30" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="C140" s="29" t="inlineStr">
-        <is>
-          <t>한국투자MAN다이나믹인컴월배당증권자투자신탁H(채권-재간접형)(모)</t>
-        </is>
-      </c>
-      <c r="D140" s="29" t="inlineStr">
-        <is>
-          <t>해외채권형</t>
-        </is>
-      </c>
-      <c r="E140" s="29" t="inlineStr">
-        <is>
-          <t>한국투자신탁운용</t>
-        </is>
-      </c>
-      <c r="F140" s="30" t="inlineStr">
-        <is>
-          <t>2,725억원</t>
-        </is>
-      </c>
-      <c r="G140" s="31" t="n">
-        <v>0.06779</v>
-      </c>
-      <c r="H140" s="30" t="inlineStr">
-        <is>
-          <t>0.54~1.24%</t>
+      <c r="C140" s="30" t="inlineStr">
+        <is>
+          <t>신한마음편한적격TDF2050증권자투자신탁[주식혼합-재간접형](종류)</t>
+        </is>
+      </c>
+      <c r="D140" s="30" t="inlineStr">
+        <is>
+          <t>기타형</t>
+        </is>
+      </c>
+      <c r="E140" s="30" t="inlineStr">
+        <is>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="F140" s="31" t="inlineStr">
+        <is>
+          <t>3,079억원</t>
+        </is>
+      </c>
+      <c r="G140" s="32" t="n">
+        <v>0.23546</v>
+      </c>
+      <c r="H140" s="31" t="inlineStr">
+        <is>
+          <t>0.56~1.31%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7906,7 @@
       </c>
       <c r="C141" s="14" t="inlineStr">
         <is>
-          <t>KB다이나믹적격TDF2040증권자투자신탁(주식혼합-재간접형)(운용)</t>
+          <t>신한마음편한적격TDF2035증권자투자신탁[주식혼합-재간접형](종류)</t>
         </is>
       </c>
       <c r="D141" s="14" t="inlineStr">
@@ -7841,20 +7916,20 @@
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
-        </is>
-      </c>
-      <c r="F141" s="27" t="inlineStr">
-        <is>
-          <t>2,531억원</t>
-        </is>
-      </c>
-      <c r="G141" s="28" t="n">
-        <v>0.235043</v>
-      </c>
-      <c r="H141" s="27" t="inlineStr">
-        <is>
-          <t>0.34~1.19%</t>
+          <t>신한자산운용</t>
+        </is>
+      </c>
+      <c r="F141" s="28" t="inlineStr">
+        <is>
+          <t>3,055억원</t>
+        </is>
+      </c>
+      <c r="G141" s="29" t="n">
+        <v>0.177612</v>
+      </c>
+      <c r="H141" s="28" t="inlineStr">
+        <is>
+          <t>0.33~0.82%</t>
         </is>
       </c>
     </row>
@@ -7864,37 +7939,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B142" s="29" t="inlineStr">
+      <c r="B142" s="30" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="C142" s="29" t="inlineStr">
-        <is>
-          <t>KCGI샐러리맨증권자투자신탁[주식-재간접형]</t>
-        </is>
-      </c>
-      <c r="D142" s="29" t="inlineStr">
-        <is>
-          <t>해외주식형</t>
-        </is>
-      </c>
-      <c r="E142" s="29" t="inlineStr">
-        <is>
-          <t>케이씨지아이자산운용</t>
-        </is>
-      </c>
-      <c r="F142" s="30" t="inlineStr">
-        <is>
-          <t>2,524억원</t>
-        </is>
-      </c>
-      <c r="G142" s="31" t="n">
-        <v>0.313328</v>
-      </c>
-      <c r="H142" s="30" t="inlineStr">
-        <is>
-          <t>0.64~1.01%</t>
+      <c r="C142" s="30" t="inlineStr">
+        <is>
+          <t>삼성글로벌액티브적격TDF2030증권투자신탁H[주식혼합-재간접형]</t>
+        </is>
+      </c>
+      <c r="D142" s="30" t="inlineStr">
+        <is>
+          <t>기타형</t>
+        </is>
+      </c>
+      <c r="E142" s="30" t="inlineStr">
+        <is>
+          <t>삼성자산운용</t>
+        </is>
+      </c>
+      <c r="F142" s="31" t="inlineStr">
+        <is>
+          <t>2,841억원</t>
+        </is>
+      </c>
+      <c r="G142" s="32" t="n">
+        <v>0.097423</v>
+      </c>
+      <c r="H142" s="31" t="inlineStr">
+        <is>
+          <t>0.23~0.76%</t>
         </is>
       </c>
     </row>
@@ -7911,12 +7986,12 @@
       </c>
       <c r="C143" s="14" t="inlineStr">
         <is>
-          <t>NH-Amundi올바른지구OCIO자산배분증권자투자신탁[혼합-재간접형]</t>
+          <t>NH-Amundi하나로적격TDF2030증권투자신탁[주식혼합-재간접형]</t>
         </is>
       </c>
       <c r="D143" s="14" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>기타형</t>
         </is>
       </c>
       <c r="E143" s="14" t="inlineStr">
@@ -7924,17 +7999,17 @@
           <t>엔에이치아문디자산운용</t>
         </is>
       </c>
-      <c r="F143" s="27" t="inlineStr">
-        <is>
-          <t>2,519억원</t>
-        </is>
-      </c>
-      <c r="G143" s="28" t="n">
-        <v>0.06297700000000001</v>
-      </c>
-      <c r="H143" s="27" t="inlineStr">
-        <is>
-          <t>0.41~1.01%</t>
+      <c r="F143" s="28" t="inlineStr">
+        <is>
+          <t>2,746억원</t>
+        </is>
+      </c>
+      <c r="G143" s="29" t="n">
+        <v>0.110507</v>
+      </c>
+      <c r="H143" s="28" t="inlineStr">
+        <is>
+          <t>0.35~0.80%</t>
         </is>
       </c>
     </row>
@@ -7944,35 +8019,35 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B144" s="29" t="inlineStr">
+      <c r="B144" s="30" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="C144" s="29" t="inlineStr">
-        <is>
-          <t>KB다이나믹적격TDF2050증권자투자신탁(주식혼합-재간접형)(운용)</t>
-        </is>
-      </c>
-      <c r="D144" s="29" t="inlineStr">
+      <c r="C144" s="30" t="inlineStr">
+        <is>
+          <t>KB다이나믹적격TDF2040증권자투자신탁(주식혼합-재간접형)(운용)</t>
+        </is>
+      </c>
+      <c r="D144" s="30" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="E144" s="29" t="inlineStr">
+      <c r="E144" s="30" t="inlineStr">
         <is>
           <t>케이비자산운용</t>
         </is>
       </c>
-      <c r="F144" s="30" t="inlineStr">
-        <is>
-          <t>2,349억원</t>
-        </is>
-      </c>
-      <c r="G144" s="31" t="n">
-        <v>0.257195</v>
-      </c>
-      <c r="H144" s="30" t="inlineStr">
+      <c r="F144" s="31" t="inlineStr">
+        <is>
+          <t>2,531억원</t>
+        </is>
+      </c>
+      <c r="G144" s="32" t="n">
+        <v>0.235043</v>
+      </c>
+      <c r="H144" s="31" t="inlineStr">
         <is>
           <t>0.34~1.19%</t>
         </is>
@@ -7991,30 +8066,30 @@
       </c>
       <c r="C145" s="14" t="inlineStr">
         <is>
-          <t>신한마음편한적격TDF2030증권자투자신탁[주식혼합-재간접형](종류)</t>
+          <t>KCGI샐러리맨증권자투자신탁[주식-재간접형]</t>
         </is>
       </c>
       <c r="D145" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
-        </is>
-      </c>
-      <c r="F145" s="27" t="inlineStr">
-        <is>
-          <t>2,312억원</t>
-        </is>
-      </c>
-      <c r="G145" s="28" t="n">
-        <v>0.149587</v>
-      </c>
-      <c r="H145" s="27" t="inlineStr">
-        <is>
-          <t>0.33~0.82%</t>
+          <t>케이씨지아이자산운용</t>
+        </is>
+      </c>
+      <c r="F145" s="28" t="inlineStr">
+        <is>
+          <t>2,524억원</t>
+        </is>
+      </c>
+      <c r="G145" s="29" t="n">
+        <v>0.313328</v>
+      </c>
+      <c r="H145" s="28" t="inlineStr">
+        <is>
+          <t>0.64~1.01%</t>
         </is>
       </c>
     </row>
@@ -8024,37 +8099,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B146" s="29" t="inlineStr">
+      <c r="B146" s="30" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="C146" s="29" t="inlineStr">
-        <is>
-          <t>삼성글로벌액티브적격TDF2045증권투자신탁H[주식혼합-재간접형]</t>
-        </is>
-      </c>
-      <c r="D146" s="29" t="inlineStr">
-        <is>
-          <t>기타형</t>
-        </is>
-      </c>
-      <c r="E146" s="29" t="inlineStr">
-        <is>
-          <t>삼성자산운용</t>
-        </is>
-      </c>
-      <c r="F146" s="30" t="inlineStr">
-        <is>
-          <t>2,287억원</t>
-        </is>
-      </c>
-      <c r="G146" s="31" t="n">
-        <v>0.146997</v>
-      </c>
-      <c r="H146" s="30" t="inlineStr">
-        <is>
-          <t>0.33~1.30%</t>
+      <c r="C146" s="30" t="inlineStr">
+        <is>
+          <t>NH-Amundi올바른지구OCIO자산배분증권자투자신탁[혼합-재간접형]</t>
+        </is>
+      </c>
+      <c r="D146" s="30" t="inlineStr">
+        <is>
+          <t>해외혼합형</t>
+        </is>
+      </c>
+      <c r="E146" s="30" t="inlineStr">
+        <is>
+          <t>엔에이치아문디자산운용</t>
+        </is>
+      </c>
+      <c r="F146" s="31" t="inlineStr">
+        <is>
+          <t>2,519억원</t>
+        </is>
+      </c>
+      <c r="G146" s="32" t="n">
+        <v>0.06297700000000001</v>
+      </c>
+      <c r="H146" s="31" t="inlineStr">
+        <is>
+          <t>0.41~1.01%</t>
         </is>
       </c>
     </row>
@@ -8071,7 +8146,7 @@
       </c>
       <c r="C147" s="14" t="inlineStr">
         <is>
-          <t>KCGI프리덤적격TDF2050증권자투자신탁[주식혼합-재간접형]</t>
+          <t>삼성글로벌액티브적격TDF2045증권투자신탁H[주식혼합-재간접형]</t>
         </is>
       </c>
       <c r="D147" s="14" t="inlineStr">
@@ -8081,20 +8156,20 @@
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>케이씨지아이자산운용</t>
-        </is>
-      </c>
-      <c r="F147" s="27" t="inlineStr">
-        <is>
-          <t>2,285억원</t>
-        </is>
-      </c>
-      <c r="G147" s="28" t="n">
-        <v>0.223357</v>
-      </c>
-      <c r="H147" s="27" t="inlineStr">
-        <is>
-          <t>0.56~0.89%</t>
+          <t>삼성자산운용</t>
+        </is>
+      </c>
+      <c r="F147" s="28" t="inlineStr">
+        <is>
+          <t>2,287억원</t>
+        </is>
+      </c>
+      <c r="G147" s="29" t="n">
+        <v>0.146997</v>
+      </c>
+      <c r="H147" s="28" t="inlineStr">
+        <is>
+          <t>0.33~1.30%</t>
         </is>
       </c>
     </row>
@@ -8104,37 +8179,37 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B148" s="29" t="inlineStr">
+      <c r="B148" s="30" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="C148" s="29" t="inlineStr">
-        <is>
-          <t>키움키워드림적격TDF2030증권투자신탁 1[혼합-재간접형]</t>
-        </is>
-      </c>
-      <c r="D148" s="29" t="inlineStr">
+      <c r="C148" s="30" t="inlineStr">
+        <is>
+          <t>KCGI프리덤적격TDF2050증권자투자신탁[주식혼합-재간접형]</t>
+        </is>
+      </c>
+      <c r="D148" s="30" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="E148" s="29" t="inlineStr">
-        <is>
-          <t>키움투자자산운용</t>
-        </is>
-      </c>
-      <c r="F148" s="30" t="inlineStr">
-        <is>
-          <t>2,261억원</t>
-        </is>
-      </c>
-      <c r="G148" s="31" t="n">
-        <v>0.079793</v>
-      </c>
-      <c r="H148" s="30" t="inlineStr">
-        <is>
-          <t>0.28~0.66%</t>
+      <c r="E148" s="30" t="inlineStr">
+        <is>
+          <t>케이씨지아이자산운용</t>
+        </is>
+      </c>
+      <c r="F148" s="31" t="inlineStr">
+        <is>
+          <t>2,285억원</t>
+        </is>
+      </c>
+      <c r="G148" s="32" t="n">
+        <v>0.223357</v>
+      </c>
+      <c r="H148" s="31" t="inlineStr">
+        <is>
+          <t>0.56~0.89%</t>
         </is>
       </c>
     </row>
@@ -8151,29 +8226,31 @@
       </c>
       <c r="C149" s="14" t="inlineStr">
         <is>
-          <t>이지스글로벌공모부동산투자신탁281(파생형)</t>
+          <t>키움키워드림적격TDF2030증권투자신탁 1[혼합-재간접형]</t>
         </is>
       </c>
       <c r="D149" s="14" t="inlineStr">
         <is>
-          <t>해외대체</t>
+          <t>기타형</t>
         </is>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>이지스자산운용</t>
-        </is>
-      </c>
-      <c r="F149" s="27" t="inlineStr">
-        <is>
-          <t>2,237억원</t>
-        </is>
-      </c>
-      <c r="G149" s="28" t="n">
-        <v>-0.145053</v>
-      </c>
-      <c r="H149" s="32" t="n">
-        <v>0.0054</v>
+          <t>키움투자자산운용</t>
+        </is>
+      </c>
+      <c r="F149" s="28" t="inlineStr">
+        <is>
+          <t>2,261억원</t>
+        </is>
+      </c>
+      <c r="G149" s="29" t="n">
+        <v>0.079793</v>
+      </c>
+      <c r="H149" s="28" t="inlineStr">
+        <is>
+          <t>0.28~0.66%</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -8182,42 +8259,280 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="B150" s="29" t="inlineStr">
+      <c r="B150" s="30" t="inlineStr">
         <is>
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="C150" s="29" t="inlineStr">
+      <c r="C150" s="30" t="inlineStr">
+        <is>
+          <t>이지스글로벌공모부동산투자신탁281(파생형)</t>
+        </is>
+      </c>
+      <c r="D150" s="30" t="inlineStr">
+        <is>
+          <t>해외대체</t>
+        </is>
+      </c>
+      <c r="E150" s="30" t="inlineStr">
+        <is>
+          <t>이지스자산운용</t>
+        </is>
+      </c>
+      <c r="F150" s="31" t="inlineStr">
+        <is>
+          <t>2,237억원</t>
+        </is>
+      </c>
+      <c r="G150" s="32" t="n">
+        <v>-0.145053</v>
+      </c>
+      <c r="H150" s="34" t="n">
+        <v>0.0054</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B151" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="C151" s="14" t="inlineStr">
         <is>
           <t>한화LIFEPLUS적격TDF2050증권자투자신탁(주식혼합-재간접형)</t>
         </is>
       </c>
-      <c r="D150" s="29" t="inlineStr">
+      <c r="D151" s="14" t="inlineStr">
         <is>
           <t>기타형</t>
         </is>
       </c>
-      <c r="E150" s="29" t="inlineStr">
+      <c r="E151" s="14" t="inlineStr">
         <is>
           <t>한화자산운용</t>
         </is>
       </c>
-      <c r="F150" s="30" t="inlineStr">
+      <c r="F151" s="28" t="inlineStr">
         <is>
           <t>2,233억원</t>
         </is>
       </c>
-      <c r="G150" s="31" t="n">
+      <c r="G151" s="29" t="n">
         <v>0.229434</v>
       </c>
-      <c r="H150" s="30" t="inlineStr">
+      <c r="H151" s="28" t="inlineStr">
         <is>
           <t>0.44~1.33%</t>
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B152" s="30" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="C152" s="30" t="inlineStr">
+        <is>
+          <t>에셋플러스글로벌리치투게더증권자투자신탁 1(주식)</t>
+        </is>
+      </c>
+      <c r="D152" s="30" t="inlineStr">
+        <is>
+          <t>해외주식형</t>
+        </is>
+      </c>
+      <c r="E152" s="30" t="inlineStr">
+        <is>
+          <t>에셋플러스자산운용</t>
+        </is>
+      </c>
+      <c r="F152" s="31" t="inlineStr">
+        <is>
+          <t>2,158억원</t>
+        </is>
+      </c>
+      <c r="G152" s="32" t="n">
+        <v>0.319127</v>
+      </c>
+      <c r="H152" s="31" t="inlineStr">
+        <is>
+          <t>1.12~2.05%</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B153" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="C153" s="14" t="inlineStr">
+        <is>
+          <t>미래에셋글로벌그레이트컨슈머연금증권전환형자투자신탁 1(주식)</t>
+        </is>
+      </c>
+      <c r="D153" s="14" t="inlineStr">
+        <is>
+          <t>해외주식형</t>
+        </is>
+      </c>
+      <c r="E153" s="14" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="F153" s="28" t="inlineStr">
+        <is>
+          <t>2,135억원</t>
+        </is>
+      </c>
+      <c r="G153" s="29" t="n">
+        <v>0.003213</v>
+      </c>
+      <c r="H153" s="28" t="inlineStr">
+        <is>
+          <t>1.14~1.71%</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B154" s="30" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="C154" s="30" t="inlineStr">
+        <is>
+          <t>IBK플레인바닐라EMP증권투자신탁[혼합-재간접형]</t>
+        </is>
+      </c>
+      <c r="D154" s="30" t="inlineStr">
+        <is>
+          <t>해외혼합형</t>
+        </is>
+      </c>
+      <c r="E154" s="30" t="inlineStr">
+        <is>
+          <t>아이비케이자산운용</t>
+        </is>
+      </c>
+      <c r="F154" s="31" t="inlineStr">
+        <is>
+          <t>1,845억원</t>
+        </is>
+      </c>
+      <c r="G154" s="32" t="n">
+        <v>0.178906</v>
+      </c>
+      <c r="H154" s="31" t="inlineStr">
+        <is>
+          <t>0.49~1.44%</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B155" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="C155" s="14" t="inlineStr">
+        <is>
+          <t>미래에셋글로벌다이나믹증권자투자신탁 1(채권)</t>
+        </is>
+      </c>
+      <c r="D155" s="14" t="inlineStr">
+        <is>
+          <t>해외채권형</t>
+        </is>
+      </c>
+      <c r="E155" s="14" t="inlineStr">
+        <is>
+          <t>미래에셋자산운용</t>
+        </is>
+      </c>
+      <c r="F155" s="28" t="inlineStr">
+        <is>
+          <t>1,737억원</t>
+        </is>
+      </c>
+      <c r="G155" s="29" t="n">
+        <v>0.013867</v>
+      </c>
+      <c r="H155" s="28" t="inlineStr">
+        <is>
+          <t>0.36~0.80%</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="B156" s="30" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="C156" s="30" t="inlineStr">
+        <is>
+          <t>키움슈로더월지급글로벌가치주인컴증권자투자신탁[주식-재간접형]</t>
+        </is>
+      </c>
+      <c r="D156" s="30" t="inlineStr">
+        <is>
+          <t>해외주식형</t>
+        </is>
+      </c>
+      <c r="E156" s="30" t="inlineStr">
+        <is>
+          <t>키움투자자산운용</t>
+        </is>
+      </c>
+      <c r="F156" s="31" t="inlineStr">
+        <is>
+          <t>1,713억원</t>
+        </is>
+      </c>
+      <c r="G156" s="32" t="n">
+        <v>0.17644</v>
+      </c>
+      <c r="H156" s="31" t="inlineStr">
+        <is>
+          <t>0.43~1.21%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A7:H150"/>
+  <autoFilter ref="A7:H156"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -8296,12 +8611,12 @@
           <t>펀드</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>네이버 Npay 증권 + 금융투자협회 전자공시(투자지역)</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="28" t="n">
         <v>1051</v>
       </c>
       <c r="D5" s="14" t="inlineStr">
@@ -8309,7 +8624,7 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="E5" s="34" t="inlineStr">
+      <c r="E5" s="35" t="inlineStr">
         <is>
           <t>보수는 클래스마다 달라 하나로 줄이지 않고 범위(feeMin~feeMax)로 싣습니다. 변동성·최대낙폭은 기준가 이력이 7 거래일뿐이라 셈하지 않고 위험등급을 씁니다.</t>
         </is>
@@ -8321,12 +8636,12 @@
           <t>국내주식</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="35" t="inlineStr">
         <is>
           <t>한국투자증권 오픈API (모의투자) — 100 종 (나머지 0 종은 야후 파이낸스)</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <v>100</v>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -8334,7 +8649,7 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E6" s="34" t="inlineStr">
+      <c r="E6" s="35" t="inlineStr">
         <is>
           <t>야후·네이버를 증권사 값으로 심판한 결과(data/prices_kis/verdict.txt) 야후가 갈리는 봉의 89.1%에서 틀렸으므로, 국내주식은 증권사 일봉으로 갈아 끼웠습니다. 시가총액도 같은 종가로 고쳐 셈했습니다.</t>
         </is>
@@ -8346,12 +8661,12 @@
           <t>해외주식</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>야후 파이낸스 일봉 (자료 가지 us100-data)</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <v>100</v>
       </c>
       <c r="D7" s="14" t="inlineStr">
@@ -8359,7 +8674,7 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="E7" s="34" t="inlineStr"/>
+      <c r="E7" s="35" t="inlineStr"/>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="14" t="inlineStr">
@@ -8367,12 +8682,12 @@
           <t>국내ETF</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="35" t="inlineStr">
         <is>
           <t>네이버 금융 일봉 + 야후 차트 일봉(close, 배당 미보정) + ETFCHECK (https://www.etfcheck.co.kr)</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="28" t="n">
         <v>247</v>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -8380,7 +8695,7 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr"/>
+      <c r="E8" s="35" t="inlineStr"/>
     </row>
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="14" t="inlineStr">
@@ -8388,12 +8703,12 @@
           <t>해외ETF</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="35" t="inlineStr">
         <is>
           <t>한국투자증권 오픈API (모의투자, HHDFS76240000, 수정주가)</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="28" t="n">
         <v>19</v>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -8401,10 +8716,10 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr"/>
+      <c r="E9" s="35" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="36" t="inlineStr">
         <is>
           <t>이 자료가 지키는 규칙</t>
         </is>
@@ -8416,7 +8731,7 @@
           <t>수익률계열</t>
         </is>
       </c>
-      <c r="B13" s="36" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>주식·ETF 는 일봉에서 직접 셈합니다(최근 252 거래일). 펀드는 원천이 주는 1 년 수익률을 씁니다 — 두 계열은 기준일이 다를 수 있으므로 상품마다 asOf 를 답니다.</t>
         </is>
@@ -8428,7 +8743,7 @@
           <t>변동성</t>
         </is>
       </c>
-      <c r="B14" s="36" t="inlineStr">
+      <c r="B14" s="37" t="inlineStr">
         <is>
           <t>일봉이 있는 상품만 연변동성(일간 로그수익률 표준편차 × √252)을 셈합니다. 펀드는 이력이 7 거래일뿐이라 셈하지 않고 원천의 위험등급을 씁니다.</t>
         </is>
@@ -8440,7 +8755,7 @@
           <t>펀드보수</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="37" t="inlineStr">
         <is>
           <t>클래스마다 달라 하나로 줄이지 않고 범위로 싣습니다.</t>
         </is>
@@ -8452,7 +8767,7 @@
           <t>해외펀드</t>
         </is>
       </c>
-      <c r="B16" s="36" t="inlineStr">
+      <c r="B16" s="37" t="inlineStr">
         <is>
           <t>해외에 설정된 뮤추얼펀드가 아니라 해외에 투자하는, 국내 설정 공모펀드입니다.</t>
         </is>
@@ -8464,7 +8779,7 @@
           <t>최소설정액</t>
         </is>
       </c>
-      <c r="B17" s="36" t="inlineStr">
+      <c r="B17" s="37" t="inlineStr">
         <is>
           <t>10000000000</t>
         </is>
@@ -8490,6 +8805,417 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="4" customHeight="1">
+      <c r="A1" s="3" t="n"/>
+      <c r="B1" s="3" t="n"/>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>자산군별 기대수익률 — 두 방식</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="6" customHeight="1"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>기대수익률은 재는 것이 아니라 가정하는 것입니다. 서로 다른 두 길로 세워 보고 어긋나는 곳을 함께 적습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>자산군</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>① 빌딩블록</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>② 장기실적(8년)</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>차이</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>국내주식</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="n">
+        <v>0.0781</v>
+      </c>
+      <c r="C7" s="33" t="n">
+        <v>0.1853</v>
+      </c>
+      <c r="D7" s="38" t="n">
+        <v>0.1072</v>
+      </c>
+      <c r="E7" s="35" t="inlineStr"/>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+      <c r="B8" s="33" t="n">
+        <v>0.0781</v>
+      </c>
+      <c r="C8" s="33" t="n">
+        <v>0.1845</v>
+      </c>
+      <c r="D8" s="38" t="n">
+        <v>0.1064</v>
+      </c>
+      <c r="E8" s="35" t="inlineStr"/>
+    </row>
+    <row r="9" ht="28" customHeight="1">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>국내채권</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="C9" s="33" t="n">
+        <v>0.0105</v>
+      </c>
+      <c r="D9" s="38" t="n">
+        <v>-0.0256</v>
+      </c>
+      <c r="E9" s="35" t="inlineStr"/>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>해외채권</t>
+        </is>
+      </c>
+      <c r="B10" s="33" t="n">
+        <v>0.0381</v>
+      </c>
+      <c r="C10" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="35" t="inlineStr">
+        <is>
+          <t>5해를 채우는 원화 프록시가 없습니다 — 달러 ETF 로 대신하면 환율이 빠진 남의 수익률이 됩니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>대체</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="n">
+        <v>0.0481</v>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="35" t="inlineStr">
+        <is>
+          <t>5해를 채우는 원화 프록시가 없습니다 — 달러 ETF 로 대신하면 환율이 빠진 남의 수익률이 됩니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>현금성</t>
+        </is>
+      </c>
+      <c r="B12" s="33" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="C12" s="33" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="D12" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="35" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>· ① 무위험수익률 2.81% 는 짐작이 아니라 MMF 80종의 1년 수익률 중앙값(실측)입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>· ① 의 리스크프리미엄은 가정입니다. 회사 자산배분본부의 장기 기대수익률(CMA)이 있으면 scripts/proposal_cma.py 의 PREMIUM 을 그 값으로 바꾸십시오 — 화면과 엑셀이 함께 따라옵니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>· ② 를 기준선으로 쓰지 않는 까닭: 창(2018~2026)이 강세장 한 국면에 갇혀 있어 주식이 18%대로 나오고, 같은 국내주식인데 프록시에 따라 TIGER 200 19.8% · 코스닥150 1.8% 로 20%p 가 갈립니다. 해외채권·대체는 5해를 채우는 원화 프록시가 없어 아예 덮지 못합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="27" t="inlineStr">
+        <is>
+          <t>· ② 는 분배금이 빠진 가격 수익률이라 실제보다 낮게 나옵니다. 국내채권이 1.05%로 나오는 것이 그 편향입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="27" t="inlineStr">
+        <is>
+          <t>· 달러 표시 ETF 로 장기 실적을 재지 않았습니다. 그 값은 환율이 빠진 달러 투자자의 수익률이지 한국 고객의 수익률이 아닙니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="4" customHeight="1">
+      <c r="A20" s="3" t="n"/>
+      <c r="B20" s="3" t="n"/>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n"/>
+      <c r="E20" s="3" t="n"/>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>제안 자산군에 적용한 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="6" customHeight="1"/>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>자산군(국내ETF·해외펀드…)은 포장지라 그 자체로 기대수익률이 없습니다. 그 칸에 담긴 상품의 실제 노출로 위 ① 값을 섞어 낸 것입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>자산군</t>
+        </is>
+      </c>
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>기대수익률(가정)</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>섞은 노출</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr"/>
+      <c r="E25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>국내주식</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="n">
+        <v>0.0781</v>
+      </c>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>국내주식 100%</t>
+        </is>
+      </c>
+      <c r="D26" s="40" t="n"/>
+      <c r="E26" s="41" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>해외주식</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="n">
+        <v>0.0781</v>
+      </c>
+      <c r="C27" s="39" t="inlineStr">
+        <is>
+          <t>해외주식 100%</t>
+        </is>
+      </c>
+      <c r="D27" s="40" t="n"/>
+      <c r="E27" s="41" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
+          <t>국내ETF</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="C28" s="39" t="inlineStr">
+        <is>
+          <t>대체 40% · 국내채권 40% · 국내주식 20%</t>
+        </is>
+      </c>
+      <c r="D28" s="40" t="n"/>
+      <c r="E28" s="41" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="14" t="inlineStr">
+        <is>
+          <t>해외ETF</t>
+        </is>
+      </c>
+      <c r="B29" s="33" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="C29" s="39" t="inlineStr">
+        <is>
+          <t>해외주식 40% · 해외채권 40% · 대체 20%</t>
+        </is>
+      </c>
+      <c r="D29" s="40" t="n"/>
+      <c r="E29" s="41" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>국내펀드</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="n">
+        <v>0.05110000000000001</v>
+      </c>
+      <c r="C30" s="39" t="inlineStr">
+        <is>
+          <t>국내채권 50% · 국내주식 30% · 대체 20%</t>
+        </is>
+      </c>
+      <c r="D30" s="40" t="n"/>
+      <c r="E30" s="41" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>해외펀드</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="C31" s="39" t="inlineStr">
+        <is>
+          <t>해외주식 40% · 해외채권 40% · 대체 20%</t>
+        </is>
+      </c>
+      <c r="D31" s="40" t="n"/>
+      <c r="E31" s="41" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>현금</t>
+        </is>
+      </c>
+      <c r="B32" s="33" t="n">
+        <v>0.0281</v>
+      </c>
+      <c r="C32" s="39" t="inlineStr">
+        <is>
+          <t>현금성 100%</t>
+        </is>
+      </c>
+      <c r="D32" s="40" t="n"/>
+      <c r="E32" s="41" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="C32:E32"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8511,90 +9237,90 @@
     </row>
     <row r="3" ht="6" customHeight="1"/>
     <row r="4" ht="18" customHeight="1">
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>1. 「제안서」 시트에서 파란 글씨 칸만 고칩니다 — 고객명·투자금액·투자기간·위험성향·목표 연수익률. 투자기간과 위험성향은 드롭다운입니다.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>1-1. 조건을 다 넣으셨으면 「조회」 칸에서 ▶ 조회 실행 을 고릅니다. … 조건 입력 중 로 두면 표가 비워져 조건만 차분히 채울 수 있습니다. 매크로 없는 .xlsx 에는 누르는 단추를 넣을 수 없어 드롭다운으로 만들었습니다 — .xlsm 으로 만들면 회사 PC 에서 매크로가 막혀 열자마자 「사용 안 함」이 뜹니다.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>1-2. 「목표 연수익률」은 고객이 바라는 수익률이고, 배분표의 「기대수익률 (가정)」은 그것을 어떻게 벌 작정인지에 대한 자산군별 가정입니다. 둘은 다른 것이며, 3 번 섹션이 둘을 견주어 줍니다.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>2. 나머지 칸은 수식입니다. 손으로 덮어쓰면 다음에 값이 안 따라옵니다.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="42" t="inlineStr">
         <is>
           <t>3. 「배분규칙」 시트는 proposal_lib.py 가 셈한 것입니다. 고치지 마십시오 — 고치면 화면(proposal.html)과 어긋납니다.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="42" t="inlineStr">
         <is>
           <t>4. 「기대수익률 (가정)」 칸은 비워 두었습니다. 사람이 넣는 가정이며 기본값을 두지 않았습니다 — 넣으실 때 근거를 함께 적어 두십시오.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="42" t="inlineStr">
         <is>
           <t>5. 자료를 새로 받으면 python3 scripts/build_proposal_universe.py 를 돌린 뒤 이 파일을 다시 만듭니다.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="8" customHeight="1">
-      <c r="B11" s="37" t="inlineStr"/>
+      <c r="B11" s="42" t="inlineStr"/>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="42" t="inlineStr">
         <is>
           <t>셀 색 규칙 (기존 고객제안서와 같습니다)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">      파란 글씨 + 옅은 칠 = 사람이 넣는 칸</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="38" t="inlineStr">
+      <c r="B14" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">      검은 글씨            = 수식</t>
         </is>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">      회색 글씨            = 원천에서 받아 적은 값</t>
         </is>
       </c>
     </row>
     <row r="16" ht="8" customHeight="1">
-      <c r="B16" s="37" t="inlineStr"/>
+      <c r="B16" s="42" t="inlineStr"/>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="37" t="inlineStr">
+      <c r="B17" s="42" t="inlineStr">
         <is>
           <t>숨은 H·I 열은 셈에 쓰는 도우미 칸입니다 — 합계용 숫자(표시 칸에 「—」라는 글자가 들어가면 합계가 깨집니다), 성향 번호, 조회 키, 목표 역산. 지우지 마십시오.</t>
         </is>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -916,7 +916,7 @@
         <v/>
       </c>
       <c r="F19" s="15">
-        <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A19,자산군!$A$7:$A$12,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$7:$D$13,MATCH($A19,자산군!$A$7:$A$13,0)),"—")</f>
         <v/>
       </c>
       <c r="G19" s="17" t="n">
@@ -951,7 +951,7 @@
         <v/>
       </c>
       <c r="F20" s="15">
-        <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A20,자산군!$A$7:$A$12,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$7:$D$13,MATCH($A20,자산군!$A$7:$A$13,0)),"—")</f>
         <v/>
       </c>
       <c r="G20" s="17" t="n">
@@ -986,7 +986,7 @@
         <v/>
       </c>
       <c r="F21" s="15">
-        <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A21,자산군!$A$7:$A$12,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$7:$D$13,MATCH($A21,자산군!$A$7:$A$13,0)),"—")</f>
         <v/>
       </c>
       <c r="G21" s="17" t="n">
@@ -1021,7 +1021,7 @@
         <v/>
       </c>
       <c r="F22" s="15">
-        <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A22,자산군!$A$7:$A$12,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$7:$D$13,MATCH($A22,자산군!$A$7:$A$13,0)),"—")</f>
         <v/>
       </c>
       <c r="G22" s="17" t="n">
@@ -1056,7 +1056,7 @@
         <v/>
       </c>
       <c r="F23" s="15">
-        <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A23,자산군!$A$7:$A$12,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$7:$D$13,MATCH($A23,자산군!$A$7:$A$13,0)),"—")</f>
         <v/>
       </c>
       <c r="G23" s="17" t="n">
@@ -1091,7 +1091,7 @@
         <v/>
       </c>
       <c r="F24" s="15">
-        <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A24,자산군!$A$7:$A$12,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$7:$D$13,MATCH($A24,자산군!$A$7:$A$13,0)),"—")</f>
         <v/>
       </c>
       <c r="G24" s="17" t="n">
@@ -1126,7 +1126,7 @@
         <v/>
       </c>
       <c r="F25" s="15">
-        <f>IFERROR(INDEX(자산군!$D$7:$D$12,MATCH($A25,자산군!$A$7:$A$12,0)),"—")</f>
+        <f>IFERROR(INDEX(자산군!$D$7:$D$13,MATCH($A25,자산군!$A$7:$A$13,0)),"—")</f>
         <v/>
       </c>
       <c r="G25" s="17" t="n">
@@ -1358,7 +1358,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-19 12:34:39 · 문서 2026-09-19 12:38 (KST)</t>
+          <t>유니버스 2026-09-19 13:01:20 · 문서 2026-09-19 13:01 (KST)</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2428,8 +2428,32 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>현금성</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="n">
+        <v>110</v>
+      </c>
+      <c r="C13" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>0.028086</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>0.0097</v>
+      </c>
+      <c r="F13" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>펀드는 기준가 이력이 7 거래일뿐이라 변동성·최대낙폭을 셈하지 않고 원천의 위험등급을 씁니다.</t>
         </is>
@@ -2437,7 +2461,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:F15"/>
     <mergeCell ref="A4:F4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -2636,12 +2660,12 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>지주</t>
+          <t>자동차</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -2651,11 +2675,11 @@
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
-          <t>141조원</t>
+          <t>96조원</t>
         </is>
       </c>
       <c r="G9" s="29" t="n">
-        <v>6.015706806282721</v>
+        <v>0.6659090909090909</v>
       </c>
       <c r="H9" s="29" t="inlineStr">
         <is>
@@ -2676,12 +2700,12 @@
       </c>
       <c r="C10" s="30" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="D10" s="30" t="inlineStr">
         <is>
-          <t>전기전자</t>
+          <t>2차전지</t>
         </is>
       </c>
       <c r="E10" s="30" t="inlineStr">
@@ -2691,11 +2715,11 @@
       </c>
       <c r="F10" s="31" t="inlineStr">
         <is>
-          <t>105조원</t>
+          <t>85조원</t>
         </is>
       </c>
       <c r="G10" s="32" t="n">
-        <v>6.789001122334455</v>
+        <v>0.05976676384839652</v>
       </c>
       <c r="H10" s="32" t="inlineStr">
         <is>
@@ -2716,12 +2740,12 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>자동차</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -2731,11 +2755,11 @@
       </c>
       <c r="F11" s="28" t="inlineStr">
         <is>
-          <t>96조원</t>
+          <t>62조원</t>
         </is>
       </c>
       <c r="G11" s="29" t="n">
-        <v>0.6659090909090909</v>
+        <v>0.6178637200736647</v>
       </c>
       <c r="H11" s="29" t="inlineStr">
         <is>
@@ -2756,12 +2780,12 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="D12" s="30" t="inlineStr">
         <is>
-          <t>2차전지</t>
+          <t>중공업</t>
         </is>
       </c>
       <c r="E12" s="30" t="inlineStr">
@@ -2771,11 +2795,11 @@
       </c>
       <c r="F12" s="31" t="inlineStr">
         <is>
-          <t>85조원</t>
+          <t>56조원</t>
         </is>
       </c>
       <c r="G12" s="32" t="n">
-        <v>0.05976676384839652</v>
+        <v>0.1869565217391305</v>
       </c>
       <c r="H12" s="32" t="inlineStr">
         <is>
@@ -2796,12 +2820,12 @@
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>삼성바이오로직스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>중공업</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -2811,11 +2835,11 @@
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
-          <t>65조원</t>
+          <t>55조원</t>
         </is>
       </c>
       <c r="G13" s="29" t="n">
-        <v>-0.07711346952561393</v>
+        <v>0.3867313915857604</v>
       </c>
       <c r="H13" s="29" t="inlineStr">
         <is>
@@ -2836,7 +2860,7 @@
       </c>
       <c r="C14" s="30" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>신한지주</t>
         </is>
       </c>
       <c r="D14" s="30" t="inlineStr">
@@ -2851,11 +2875,11 @@
       </c>
       <c r="F14" s="31" t="inlineStr">
         <is>
-          <t>62조원</t>
+          <t>52조원</t>
         </is>
       </c>
       <c r="G14" s="32" t="n">
-        <v>0.6178637200736647</v>
+        <v>0.7198142414860682</v>
       </c>
       <c r="H14" s="32" t="inlineStr">
         <is>
@@ -2876,12 +2900,12 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>HD현대중공업</t>
         </is>
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>지주</t>
+          <t>중공업</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -2891,11 +2915,11 @@
       </c>
       <c r="F15" s="28" t="inlineStr">
         <is>
-          <t>58조원</t>
+          <t>48조원</t>
         </is>
       </c>
       <c r="G15" s="29" t="n">
-        <v>1.02</v>
+        <v>-0.09941520467836262</v>
       </c>
       <c r="H15" s="29" t="inlineStr">
         <is>
@@ -2916,12 +2940,12 @@
       </c>
       <c r="C16" s="30" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="D16" s="30" t="inlineStr">
         <is>
-          <t>중공업</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="E16" s="30" t="inlineStr">
@@ -2931,11 +2955,11 @@
       </c>
       <c r="F16" s="31" t="inlineStr">
         <is>
-          <t>56조원</t>
+          <t>41조원</t>
         </is>
       </c>
       <c r="G16" s="32" t="n">
-        <v>0.1869565217391305</v>
+        <v>0.1180432690815407</v>
       </c>
       <c r="H16" s="32" t="inlineStr">
         <is>
@@ -2956,12 +2980,12 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>하나금융지주</t>
         </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>중공업</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -2971,11 +2995,11 @@
       </c>
       <c r="F17" s="28" t="inlineStr">
         <is>
-          <t>55조원</t>
+          <t>36조원</t>
         </is>
       </c>
       <c r="G17" s="29" t="n">
-        <v>0.3867313915857604</v>
+        <v>0.646551724137931</v>
       </c>
       <c r="H17" s="29" t="inlineStr">
         <is>
@@ -2996,12 +3020,12 @@
       </c>
       <c r="C18" s="30" t="inlineStr">
         <is>
-          <t>신한지주</t>
+          <t>LS일렉트릭</t>
         </is>
       </c>
       <c r="D18" s="30" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>중공업</t>
         </is>
       </c>
       <c r="E18" s="30" t="inlineStr">
@@ -3011,11 +3035,11 @@
       </c>
       <c r="F18" s="31" t="inlineStr">
         <is>
-          <t>52조원</t>
+          <t>31조원</t>
         </is>
       </c>
       <c r="G18" s="32" t="n">
-        <v>0.7198142414860682</v>
+        <v>2.5580204778157</v>
       </c>
       <c r="H18" s="32" t="inlineStr">
         <is>
@@ -3036,12 +3060,12 @@
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -3051,11 +3075,11 @@
       </c>
       <c r="F19" s="28" t="inlineStr">
         <is>
-          <t>51조원</t>
+          <t>30조원</t>
         </is>
       </c>
       <c r="G19" s="29" t="n">
-        <v>0.8912608405603737</v>
+        <v>-0.1375545851528385</v>
       </c>
       <c r="H19" s="29" t="inlineStr">
         <is>
@@ -3076,7 +3100,7 @@
       </c>
       <c r="C20" s="30" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
+          <t>효성중공업</t>
         </is>
       </c>
       <c r="D20" s="30" t="inlineStr">
@@ -3091,11 +3115,11 @@
       </c>
       <c r="F20" s="31" t="inlineStr">
         <is>
-          <t>48조원</t>
+          <t>27조원</t>
         </is>
       </c>
       <c r="G20" s="32" t="n">
-        <v>-0.09941520467836262</v>
+        <v>1.344155844155844</v>
       </c>
       <c r="H20" s="32" t="inlineStr">
         <is>
@@ -3116,12 +3140,12 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>자동차</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
@@ -3131,11 +3155,11 @@
       </c>
       <c r="F21" s="28" t="inlineStr">
         <is>
-          <t>47조원</t>
+          <t>26조원</t>
         </is>
       </c>
       <c r="G21" s="29" t="n">
-        <v>0.1407129455909943</v>
+        <v>0.4876543209876543</v>
       </c>
       <c r="H21" s="29" t="inlineStr">
         <is>
@@ -3156,12 +3180,12 @@
       </c>
       <c r="C22" s="30" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>POSCO홀딩스</t>
         </is>
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
-          <t>2차전지</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="E22" s="30" t="inlineStr">
@@ -3171,11 +3195,11 @@
       </c>
       <c r="F22" s="31" t="inlineStr">
         <is>
-          <t>43조원</t>
+          <t>25조원</t>
         </is>
       </c>
       <c r="G22" s="32" t="n">
-        <v>1.716791979949875</v>
+        <v>0.1772151898734178</v>
       </c>
       <c r="H22" s="32" t="inlineStr">
         <is>
@@ -3196,12 +3220,12 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>고려아연</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>바이오</t>
+          <t>철강</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -3211,11 +3235,11 @@
       </c>
       <c r="F23" s="28" t="inlineStr">
         <is>
-          <t>41조원</t>
+          <t>23조원</t>
         </is>
       </c>
       <c r="G23" s="29" t="n">
-        <v>0.1180432690815407</v>
+        <v>0.2563817980022198</v>
       </c>
       <c r="H23" s="29" t="inlineStr">
         <is>
@@ -3236,12 +3260,12 @@
       </c>
       <c r="C24" s="30" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>한미반도체</t>
         </is>
       </c>
       <c r="D24" s="30" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>반도체</t>
         </is>
       </c>
       <c r="E24" s="30" t="inlineStr">
@@ -3251,11 +3275,11 @@
       </c>
       <c r="F24" s="31" t="inlineStr">
         <is>
-          <t>36조원</t>
+          <t>22조원</t>
         </is>
       </c>
       <c r="G24" s="32" t="n">
-        <v>0.646551724137931</v>
+        <v>1.834740651387214</v>
       </c>
       <c r="H24" s="32" t="inlineStr">
         <is>
@@ -3276,12 +3300,12 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>메리츠금융지주</t>
         </is>
       </c>
       <c r="D25" s="14" t="inlineStr">
         <is>
-          <t>전기전자</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E25" s="14" t="inlineStr">
@@ -3291,11 +3315,11 @@
       </c>
       <c r="F25" s="28" t="inlineStr">
         <is>
-          <t>36조원</t>
+          <t>20조원</t>
         </is>
       </c>
       <c r="G25" s="29" t="n">
-        <v>1.645805592543275</v>
+        <v>0.02924451665312744</v>
       </c>
       <c r="H25" s="29" t="inlineStr">
         <is>
@@ -3316,12 +3340,12 @@
       </c>
       <c r="C26" s="30" t="inlineStr">
         <is>
-          <t>현대모비스</t>
+          <t>한국전력</t>
         </is>
       </c>
       <c r="D26" s="30" t="inlineStr">
         <is>
-          <t>자동차</t>
+          <t>인프라</t>
         </is>
       </c>
       <c r="E26" s="30" t="inlineStr">
@@ -3331,11 +3355,11 @@
       </c>
       <c r="F26" s="31" t="inlineStr">
         <is>
-          <t>34조원</t>
+          <t>20조원</t>
         </is>
       </c>
       <c r="G26" s="32" t="n">
-        <v>0.1780185758513932</v>
+        <v>-0.1591836734693878</v>
       </c>
       <c r="H26" s="32" t="inlineStr">
         <is>
@@ -3356,12 +3380,12 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>LS일렉트릭</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
         <is>
-          <t>중공업</t>
+          <t>인프라</t>
         </is>
       </c>
       <c r="E27" s="14" t="inlineStr">
@@ -3371,11 +3395,11 @@
       </c>
       <c r="F27" s="28" t="inlineStr">
         <is>
-          <t>31조원</t>
+          <t>20조원</t>
         </is>
       </c>
       <c r="G27" s="29" t="n">
-        <v>2.5580204778157</v>
+        <v>-0.08714596949891062</v>
       </c>
       <c r="H27" s="29" t="inlineStr">
         <is>
@@ -3396,12 +3420,12 @@
       </c>
       <c r="C28" s="30" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
-          <t>지주</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E28" s="30" t="inlineStr">
@@ -3411,11 +3435,11 @@
       </c>
       <c r="F28" s="31" t="inlineStr">
         <is>
-          <t>30조원</t>
+          <t>18조원</t>
         </is>
       </c>
       <c r="G28" s="32" t="n">
-        <v>1.663438256658595</v>
+        <v>0.6695725682886882</v>
       </c>
       <c r="H28" s="32" t="inlineStr">
         <is>
@@ -3436,12 +3460,12 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>KT&amp;G</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
@@ -3451,11 +3475,11 @@
       </c>
       <c r="F29" s="28" t="inlineStr">
         <is>
-          <t>30조원</t>
+          <t>18조원</t>
         </is>
       </c>
       <c r="G29" s="29" t="n">
-        <v>-0.1375545851528385</v>
+        <v>0.2781065088757397</v>
       </c>
       <c r="H29" s="29" t="inlineStr">
         <is>
@@ -3476,12 +3500,12 @@
       </c>
       <c r="C30" s="30" t="inlineStr">
         <is>
-          <t>삼성화재</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>바이오</t>
         </is>
       </c>
       <c r="E30" s="30" t="inlineStr">
@@ -3491,11 +3515,11 @@
       </c>
       <c r="F30" s="31" t="inlineStr">
         <is>
-          <t>29조원</t>
+          <t>18조원</t>
         </is>
       </c>
       <c r="G30" s="32" t="n">
-        <v>0.4316939890710383</v>
+        <v>-0.3057719324138911</v>
       </c>
       <c r="H30" s="32" t="inlineStr">
         <is>
@@ -3516,12 +3540,12 @@
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>효성중공업</t>
+          <t>에쓰오일</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
         <is>
-          <t>중공업</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="E31" s="14" t="inlineStr">
@@ -3531,11 +3555,11 @@
       </c>
       <c r="F31" s="28" t="inlineStr">
         <is>
-          <t>27조원</t>
+          <t>17조원</t>
         </is>
       </c>
       <c r="G31" s="29" t="n">
-        <v>1.344155844155844</v>
+        <v>1.47029702970297</v>
       </c>
       <c r="H31" s="29" t="inlineStr">
         <is>
@@ -5076,7 +5100,7 @@
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>RISE TDF2050액티브 적격</t>
+          <t>RISE 삼성그룹Top3채권혼합</t>
         </is>
       </c>
       <c r="D70" s="30" t="inlineStr">
@@ -5091,14 +5115,16 @@
       </c>
       <c r="F70" s="31" t="inlineStr">
         <is>
-          <t>3,461억원</t>
-        </is>
-      </c>
-      <c r="G70" s="32" t="n">
-        <v>0.2268534816588044</v>
+          <t>3,260억원</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H70" s="34" t="n">
-        <v>0.0001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="71">
@@ -7746,30 +7772,30 @@
       </c>
       <c r="C137" s="14" t="inlineStr">
         <is>
-          <t>KB다이나믹적격TDF2030증권자투자신탁(주식혼합-재간접형)(운용)</t>
+          <t>우리미국단기채공모주증권자투자신탁 1(H)(채권혼합)</t>
         </is>
       </c>
       <c r="D137" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>우리자산운용</t>
         </is>
       </c>
       <c r="F137" s="28" t="inlineStr">
         <is>
-          <t>4,156억원</t>
+          <t>3,558억원</t>
         </is>
       </c>
       <c r="G137" s="29" t="n">
-        <v>0.189953</v>
+        <v>0.052435</v>
       </c>
       <c r="H137" s="28" t="inlineStr">
         <is>
-          <t>0.24~1.19%</t>
+          <t>0.80~1.70%</t>
         </is>
       </c>
     </row>
@@ -7786,30 +7812,30 @@
       </c>
       <c r="C138" s="30" t="inlineStr">
         <is>
-          <t>우리미국단기채공모주증권자투자신탁 1(H)(채권혼합)</t>
+          <t>한국투자미국장기국채증권자투자신탁H(채권-재간접형)(모)</t>
         </is>
       </c>
       <c r="D138" s="30" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="E138" s="30" t="inlineStr">
         <is>
-          <t>우리자산운용</t>
+          <t>한국투자신탁운용</t>
         </is>
       </c>
       <c r="F138" s="31" t="inlineStr">
         <is>
-          <t>3,558억원</t>
+          <t>3,124억원</t>
         </is>
       </c>
       <c r="G138" s="32" t="n">
-        <v>0.052435</v>
+        <v>-0.063263</v>
       </c>
       <c r="H138" s="31" t="inlineStr">
         <is>
-          <t>0.80~1.70%</t>
+          <t>0.25~0.85%</t>
         </is>
       </c>
     </row>
@@ -7826,30 +7852,30 @@
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>한국투자미국장기국채증권자투자신탁H(채권-재간접형)(모)</t>
+          <t>신한미국S&amp;P500인덱스증권자투자신탁(UH)[주식-파생형]</t>
         </is>
       </c>
       <c r="D139" s="14" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F139" s="28" t="inlineStr">
         <is>
-          <t>3,124억원</t>
+          <t>2,851억원</t>
         </is>
       </c>
       <c r="G139" s="29" t="n">
-        <v>-0.063263</v>
+        <v>0.141662</v>
       </c>
       <c r="H139" s="28" t="inlineStr">
         <is>
-          <t>0.25~0.85%</t>
+          <t>0.26~1.15%</t>
         </is>
       </c>
     </row>
@@ -7866,30 +7892,30 @@
       </c>
       <c r="C140" s="30" t="inlineStr">
         <is>
-          <t>신한마음편한적격TDF2050증권자투자신탁[주식혼합-재간접형](종류)</t>
+          <t>KCGI샐러리맨증권자투자신탁[주식-재간접형]</t>
         </is>
       </c>
       <c r="D140" s="30" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E140" s="30" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>케이씨지아이자산운용</t>
         </is>
       </c>
       <c r="F140" s="31" t="inlineStr">
         <is>
-          <t>3,079억원</t>
+          <t>2,524억원</t>
         </is>
       </c>
       <c r="G140" s="32" t="n">
-        <v>0.23546</v>
+        <v>0.313328</v>
       </c>
       <c r="H140" s="31" t="inlineStr">
         <is>
-          <t>0.56~1.31%</t>
+          <t>0.64~1.01%</t>
         </is>
       </c>
     </row>
@@ -7906,30 +7932,30 @@
       </c>
       <c r="C141" s="14" t="inlineStr">
         <is>
-          <t>신한마음편한적격TDF2035증권자투자신탁[주식혼합-재간접형](종류)</t>
+          <t>NH-Amundi올바른지구OCIO자산배분증권자투자신탁[혼합-재간접형]</t>
         </is>
       </c>
       <c r="D141" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>엔에이치아문디자산운용</t>
         </is>
       </c>
       <c r="F141" s="28" t="inlineStr">
         <is>
-          <t>3,055억원</t>
+          <t>2,519억원</t>
         </is>
       </c>
       <c r="G141" s="29" t="n">
-        <v>0.177612</v>
+        <v>0.06297700000000001</v>
       </c>
       <c r="H141" s="28" t="inlineStr">
         <is>
-          <t>0.33~0.82%</t>
+          <t>0.41~1.01%</t>
         </is>
       </c>
     </row>
@@ -7946,31 +7972,29 @@
       </c>
       <c r="C142" s="30" t="inlineStr">
         <is>
-          <t>삼성글로벌액티브적격TDF2030증권투자신탁H[주식혼합-재간접형]</t>
+          <t>이지스글로벌공모부동산투자신탁281(파생형)</t>
         </is>
       </c>
       <c r="D142" s="30" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외대체</t>
         </is>
       </c>
       <c r="E142" s="30" t="inlineStr">
         <is>
-          <t>삼성자산운용</t>
+          <t>이지스자산운용</t>
         </is>
       </c>
       <c r="F142" s="31" t="inlineStr">
         <is>
-          <t>2,841억원</t>
+          <t>2,237억원</t>
         </is>
       </c>
       <c r="G142" s="32" t="n">
-        <v>0.097423</v>
-      </c>
-      <c r="H142" s="31" t="inlineStr">
-        <is>
-          <t>0.23~0.76%</t>
-        </is>
+        <v>-0.145053</v>
+      </c>
+      <c r="H142" s="34" t="n">
+        <v>0.0054</v>
       </c>
     </row>
     <row r="143">
@@ -7986,30 +8010,30 @@
       </c>
       <c r="C143" s="14" t="inlineStr">
         <is>
-          <t>NH-Amundi하나로적격TDF2030증권투자신탁[주식혼합-재간접형]</t>
+          <t>에셋플러스글로벌리치투게더증권자투자신탁 1(주식)</t>
         </is>
       </c>
       <c r="D143" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>엔에이치아문디자산운용</t>
+          <t>에셋플러스자산운용</t>
         </is>
       </c>
       <c r="F143" s="28" t="inlineStr">
         <is>
-          <t>2,746억원</t>
+          <t>2,158억원</t>
         </is>
       </c>
       <c r="G143" s="29" t="n">
-        <v>0.110507</v>
+        <v>0.319127</v>
       </c>
       <c r="H143" s="28" t="inlineStr">
         <is>
-          <t>0.35~0.80%</t>
+          <t>1.12~2.05%</t>
         </is>
       </c>
     </row>
@@ -8026,30 +8050,30 @@
       </c>
       <c r="C144" s="30" t="inlineStr">
         <is>
-          <t>KB다이나믹적격TDF2040증권자투자신탁(주식혼합-재간접형)(운용)</t>
+          <t>미래에셋글로벌그레이트컨슈머연금증권전환형자투자신탁 1(주식)</t>
         </is>
       </c>
       <c r="D144" s="30" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E144" s="30" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F144" s="31" t="inlineStr">
         <is>
-          <t>2,531억원</t>
+          <t>2,135억원</t>
         </is>
       </c>
       <c r="G144" s="32" t="n">
-        <v>0.235043</v>
+        <v>0.003213</v>
       </c>
       <c r="H144" s="31" t="inlineStr">
         <is>
-          <t>0.34~1.19%</t>
+          <t>1.14~1.71%</t>
         </is>
       </c>
     </row>
@@ -8066,30 +8090,30 @@
       </c>
       <c r="C145" s="14" t="inlineStr">
         <is>
-          <t>KCGI샐러리맨증권자투자신탁[주식-재간접형]</t>
+          <t>KB타겟리턴안정형OCIO증권투자신탁(혼합-재간접형)(운용)</t>
         </is>
       </c>
       <c r="D145" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>케이씨지아이자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F145" s="28" t="inlineStr">
         <is>
-          <t>2,524억원</t>
+          <t>2,079억원</t>
         </is>
       </c>
       <c r="G145" s="29" t="n">
-        <v>0.313328</v>
+        <v>0.100771</v>
       </c>
       <c r="H145" s="28" t="inlineStr">
         <is>
-          <t>0.64~1.01%</t>
+          <t>0.35~0.72%</t>
         </is>
       </c>
     </row>
@@ -8106,30 +8130,30 @@
       </c>
       <c r="C146" s="30" t="inlineStr">
         <is>
-          <t>NH-Amundi올바른지구OCIO자산배분증권자투자신탁[혼합-재간접형]</t>
+          <t>KB스타미국나스닥100인덱스증권자투자신탁(주식-파생형)(H)(운용)</t>
         </is>
       </c>
       <c r="D146" s="30" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E146" s="30" t="inlineStr">
         <is>
-          <t>엔에이치아문디자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F146" s="31" t="inlineStr">
         <is>
-          <t>2,519억원</t>
+          <t>1,847억원</t>
         </is>
       </c>
       <c r="G146" s="32" t="n">
-        <v>0.06297700000000001</v>
+        <v>0.205599</v>
       </c>
       <c r="H146" s="31" t="inlineStr">
         <is>
-          <t>0.41~1.01%</t>
+          <t>0.55~1.55%</t>
         </is>
       </c>
     </row>
@@ -8146,30 +8170,30 @@
       </c>
       <c r="C147" s="14" t="inlineStr">
         <is>
-          <t>삼성글로벌액티브적격TDF2045증권투자신탁H[주식혼합-재간접형]</t>
+          <t>IBK플레인바닐라EMP증권투자신탁[혼합-재간접형]</t>
         </is>
       </c>
       <c r="D147" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용</t>
+          <t>아이비케이자산운용</t>
         </is>
       </c>
       <c r="F147" s="28" t="inlineStr">
         <is>
-          <t>2,287억원</t>
+          <t>1,845억원</t>
         </is>
       </c>
       <c r="G147" s="29" t="n">
-        <v>0.146997</v>
+        <v>0.178906</v>
       </c>
       <c r="H147" s="28" t="inlineStr">
         <is>
-          <t>0.33~1.30%</t>
+          <t>0.49~1.44%</t>
         </is>
       </c>
     </row>
@@ -8186,12 +8210,12 @@
       </c>
       <c r="C148" s="30" t="inlineStr">
         <is>
-          <t>KCGI프리덤적격TDF2050증권자투자신탁[주식혼합-재간접형]</t>
+          <t>KCGI차이나증권투자신탁[주식]</t>
         </is>
       </c>
       <c r="D148" s="30" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E148" s="30" t="inlineStr">
@@ -8201,15 +8225,15 @@
       </c>
       <c r="F148" s="31" t="inlineStr">
         <is>
-          <t>2,285억원</t>
+          <t>1,784억원</t>
         </is>
       </c>
       <c r="G148" s="32" t="n">
-        <v>0.223357</v>
+        <v>-0.024214</v>
       </c>
       <c r="H148" s="31" t="inlineStr">
         <is>
-          <t>0.56~0.89%</t>
+          <t>1.01~2.31%</t>
         </is>
       </c>
     </row>
@@ -8226,30 +8250,30 @@
       </c>
       <c r="C149" s="14" t="inlineStr">
         <is>
-          <t>키움키워드림적격TDF2030증권투자신탁 1[혼합-재간접형]</t>
+          <t>미래에셋글로벌다이나믹증권자투자신탁 1(채권)</t>
         </is>
       </c>
       <c r="D149" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F149" s="28" t="inlineStr">
         <is>
-          <t>2,261억원</t>
+          <t>1,737억원</t>
         </is>
       </c>
       <c r="G149" s="29" t="n">
-        <v>0.079793</v>
+        <v>0.013867</v>
       </c>
       <c r="H149" s="28" t="inlineStr">
         <is>
-          <t>0.28~0.66%</t>
+          <t>0.36~0.80%</t>
         </is>
       </c>
     </row>
@@ -8266,29 +8290,31 @@
       </c>
       <c r="C150" s="30" t="inlineStr">
         <is>
-          <t>이지스글로벌공모부동산투자신탁281(파생형)</t>
+          <t>키움슈로더월지급글로벌가치주인컴증권자투자신탁[주식-재간접형]</t>
         </is>
       </c>
       <c r="D150" s="30" t="inlineStr">
         <is>
-          <t>해외대체</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E150" s="30" t="inlineStr">
         <is>
-          <t>이지스자산운용</t>
+          <t>키움투자자산운용</t>
         </is>
       </c>
       <c r="F150" s="31" t="inlineStr">
         <is>
-          <t>2,237억원</t>
+          <t>1,713억원</t>
         </is>
       </c>
       <c r="G150" s="32" t="n">
-        <v>-0.145053</v>
-      </c>
-      <c r="H150" s="34" t="n">
-        <v>0.0054</v>
+        <v>0.17644</v>
+      </c>
+      <c r="H150" s="31" t="inlineStr">
+        <is>
+          <t>0.43~1.21%</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -8304,30 +8330,30 @@
       </c>
       <c r="C151" s="14" t="inlineStr">
         <is>
-          <t>한화LIFEPLUS적격TDF2050증권자투자신탁(주식혼합-재간접형)</t>
+          <t>NH-Amundi글로벌우주항공증권자투자신탁(UH)[주식]</t>
         </is>
       </c>
       <c r="D151" s="14" t="inlineStr">
         <is>
-          <t>기타형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>엔에이치아문디자산운용</t>
         </is>
       </c>
       <c r="F151" s="28" t="inlineStr">
         <is>
-          <t>2,233억원</t>
+          <t>1,344억원</t>
         </is>
       </c>
       <c r="G151" s="29" t="n">
-        <v>0.229434</v>
+        <v>0.067042</v>
       </c>
       <c r="H151" s="28" t="inlineStr">
         <is>
-          <t>0.44~1.33%</t>
+          <t>0.88~1.88%</t>
         </is>
       </c>
     </row>
@@ -8344,7 +8370,7 @@
       </c>
       <c r="C152" s="30" t="inlineStr">
         <is>
-          <t>에셋플러스글로벌리치투게더증권자투자신탁 1(주식)</t>
+          <t>에셋플러스글로벌리치투게더퇴직연금증권자투자신탁 1[주식]</t>
         </is>
       </c>
       <c r="D152" s="30" t="inlineStr">
@@ -8359,15 +8385,15 @@
       </c>
       <c r="F152" s="31" t="inlineStr">
         <is>
-          <t>2,158억원</t>
+          <t>1,299억원</t>
         </is>
       </c>
       <c r="G152" s="32" t="n">
-        <v>0.319127</v>
+        <v>0.326694</v>
       </c>
       <c r="H152" s="31" t="inlineStr">
         <is>
-          <t>1.12~2.05%</t>
+          <t>1.01~1.65%</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8410,7 @@
       </c>
       <c r="C153" s="14" t="inlineStr">
         <is>
-          <t>미래에셋글로벌그레이트컨슈머연금증권전환형자투자신탁 1(주식)</t>
+          <t>유리필라델피아반도체인덱스증권자투자신탁H[주식]_운용</t>
         </is>
       </c>
       <c r="D153" s="14" t="inlineStr">
@@ -8394,20 +8420,20 @@
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>유리자산운용</t>
         </is>
       </c>
       <c r="F153" s="28" t="inlineStr">
         <is>
-          <t>2,135억원</t>
+          <t>1,276억원</t>
         </is>
       </c>
       <c r="G153" s="29" t="n">
-        <v>0.003213</v>
+        <v>0.8972410000000001</v>
       </c>
       <c r="H153" s="28" t="inlineStr">
         <is>
-          <t>1.14~1.71%</t>
+          <t>0.66~1.66%</t>
         </is>
       </c>
     </row>
@@ -8424,30 +8450,30 @@
       </c>
       <c r="C154" s="30" t="inlineStr">
         <is>
-          <t>IBK플레인바닐라EMP증권투자신탁[혼합-재간접형]</t>
+          <t>한화천연자원증권자투자신탁(주식)</t>
         </is>
       </c>
       <c r="D154" s="30" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E154" s="30" t="inlineStr">
         <is>
-          <t>아이비케이자산운용</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="F154" s="31" t="inlineStr">
         <is>
-          <t>1,845억원</t>
+          <t>1,120억원</t>
         </is>
       </c>
       <c r="G154" s="32" t="n">
-        <v>0.178906</v>
+        <v>0.437201</v>
       </c>
       <c r="H154" s="31" t="inlineStr">
         <is>
-          <t>0.49~1.44%</t>
+          <t>0.94~2.44%</t>
         </is>
       </c>
     </row>
@@ -8464,30 +8490,30 @@
       </c>
       <c r="C155" s="14" t="inlineStr">
         <is>
-          <t>미래에셋글로벌다이나믹증권자투자신탁 1(채권)</t>
+          <t>신한글로벌탄소중립솔루션증권투자신탁(H)[주식](종류)</t>
         </is>
       </c>
       <c r="D155" s="14" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F155" s="28" t="inlineStr">
         <is>
-          <t>1,737억원</t>
+          <t>1,101억원</t>
         </is>
       </c>
       <c r="G155" s="29" t="n">
-        <v>0.013867</v>
+        <v>0.7363230000000001</v>
       </c>
       <c r="H155" s="28" t="inlineStr">
         <is>
-          <t>0.36~0.80%</t>
+          <t>0.92~1.92%</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8530,7 @@
       </c>
       <c r="C156" s="30" t="inlineStr">
         <is>
-          <t>키움슈로더월지급글로벌가치주인컴증권자투자신탁[주식-재간접형]</t>
+          <t>삼성글로벌반도체증권자투자신탁UH[주식]</t>
         </is>
       </c>
       <c r="D156" s="30" t="inlineStr">
@@ -8514,20 +8540,20 @@
       </c>
       <c r="E156" s="30" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
+          <t>삼성자산운용</t>
         </is>
       </c>
       <c r="F156" s="31" t="inlineStr">
         <is>
-          <t>1,713억원</t>
+          <t>1,079억원</t>
         </is>
       </c>
       <c r="G156" s="32" t="n">
-        <v>0.17644</v>
+        <v>1.259453</v>
       </c>
       <c r="H156" s="31" t="inlineStr">
         <is>
-          <t>0.43~1.21%</t>
+          <t>0.84~1.84%</t>
         </is>
       </c>
     </row>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -1358,7 +1358,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-19 13:01:20 · 문서 2026-09-19 13:01 (KST)</t>
+          <t>유니버스 2026-09-19 19:14:39 · 문서 2026-09-19 19:14 (KST)</t>
         </is>
       </c>
     </row>
@@ -8905,10 +8905,10 @@
         <v>0.0781</v>
       </c>
       <c r="C7" s="33" t="n">
-        <v>0.1853</v>
+        <v>0.1488</v>
       </c>
       <c r="D7" s="38" t="n">
-        <v>0.1072</v>
+        <v>0.0707</v>
       </c>
       <c r="E7" s="35" t="inlineStr"/>
     </row>
@@ -8922,10 +8922,10 @@
         <v>0.0781</v>
       </c>
       <c r="C8" s="33" t="n">
-        <v>0.1845</v>
+        <v>0.1849</v>
       </c>
       <c r="D8" s="38" t="n">
-        <v>0.1064</v>
+        <v>0.1068</v>
       </c>
       <c r="E8" s="35" t="inlineStr"/>
     </row>
@@ -8955,21 +8955,13 @@
       <c r="B10" s="33" t="n">
         <v>0.0381</v>
       </c>
-      <c r="C10" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="35" t="inlineStr">
-        <is>
-          <t>5해를 채우는 원화 프록시가 없습니다 — 달러 ETF 로 대신하면 환율이 빠진 남의 수익률이 됩니다</t>
-        </is>
-      </c>
+      <c r="C10" s="33" t="n">
+        <v>-0.0601</v>
+      </c>
+      <c r="D10" s="38" t="n">
+        <v>-0.09820000000000001</v>
+      </c>
+      <c r="E10" s="35" t="inlineStr"/>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="14" t="inlineStr">
@@ -8980,21 +8972,13 @@
       <c r="B11" s="33" t="n">
         <v>0.0481</v>
       </c>
-      <c r="C11" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D11" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="35" t="inlineStr">
-        <is>
-          <t>5해를 채우는 원화 프록시가 없습니다 — 달러 ETF 로 대신하면 환율이 빠진 남의 수익률이 됩니다</t>
-        </is>
-      </c>
+      <c r="C11" s="33" t="n">
+        <v>0.09390000000000001</v>
+      </c>
+      <c r="D11" s="38" t="n">
+        <v>0.0458</v>
+      </c>
+      <c r="E11" s="35" t="inlineStr"/>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="14" t="inlineStr">

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -1376,7 +1376,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-19 23:52:11 · 문서 2026-09-19 23:53 (KST)</t>
+          <t>유니버스 2026-09-20 01:05:58 · 문서 2026-09-20 01:08 (KST)</t>
         </is>
       </c>
     </row>
@@ -2411,10 +2411,10 @@
         <v>99</v>
       </c>
       <c r="D11" s="29" t="n">
-        <v>0.1051235812029279</v>
+        <v>0.1049382716049381</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>0.2914505456297338</v>
+        <v>0.2923973274425171</v>
       </c>
       <c r="F11" s="29" t="n">
         <v>-0.3235610824922673</v>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="C32" s="33" t="inlineStr">
         <is>
-          <t>존슨앤드존슨</t>
+          <t>애브비</t>
         </is>
       </c>
       <c r="D32" s="33" t="inlineStr">
@@ -4167,27 +4167,27 @@
       </c>
       <c r="F32" s="34" t="inlineStr">
         <is>
-          <t>901조원</t>
+          <t>646조원</t>
         </is>
       </c>
       <c r="G32" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H32" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I32" s="36" t="n">
-        <v>0.5054</v>
+        <v>0.2423</v>
       </c>
       <c r="J32" s="36" t="n">
-        <v>0.1908</v>
+        <v>0.2345</v>
       </c>
       <c r="K32" s="37" t="n">
-        <v>-0.1096</v>
+        <v>-0.2192</v>
       </c>
       <c r="L32" s="34" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="M32" s="38" t="inlineStr">
         <is>
-          <t>1해 연50.5% · 변동성 19.1% (위험대비 2.50) · 최대낙폭 -11%</t>
+          <t>5해 연24.2% · 변동성 23.4% (위험대비 0.91) · 최대낙폭 -22% · 가장 나쁜 창 연23.2%</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>코카콜라</t>
+          <t>필립모리스</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
@@ -4228,27 +4228,27 @@
       </c>
       <c r="F33" s="28" t="inlineStr">
         <is>
-          <t>524조원</t>
+          <t>407조원</t>
         </is>
       </c>
       <c r="G33" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H33" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I33" s="29" t="n">
-        <v>0.3264</v>
+        <v>0.1805</v>
       </c>
       <c r="J33" s="29" t="n">
-        <v>0.1875</v>
+        <v>0.233</v>
       </c>
       <c r="K33" s="31" t="n">
-        <v>-0.08500000000000001</v>
+        <v>-0.2278</v>
       </c>
       <c r="L33" s="28" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="M33" s="32" t="inlineStr">
         <is>
-          <t>1해 연32.6% · 변동성 18.8% (위험대비 1.59) · 최대낙폭 -8%</t>
+          <t>5해 연18.1% · 변동성 23.3% (위험대비 0.65) · 최대낙폭 -23% · 가장 나쁜 창 연17.5%</t>
         </is>
       </c>
     </row>
@@ -4274,12 +4274,12 @@
       </c>
       <c r="C34" s="33" t="inlineStr">
         <is>
-          <t>처브</t>
+          <t>엑슨모빌</t>
         </is>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>에너지</t>
         </is>
       </c>
       <c r="E34" s="33" t="inlineStr">
@@ -4289,27 +4289,27 @@
       </c>
       <c r="F34" s="34" t="inlineStr">
         <is>
-          <t>182조원</t>
+          <t>932조원</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H34" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I34" s="36" t="n">
-        <v>0.2444</v>
+        <v>0.2897</v>
       </c>
       <c r="J34" s="36" t="n">
-        <v>0.1939</v>
+        <v>0.2671</v>
       </c>
       <c r="K34" s="37" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.2051</v>
       </c>
       <c r="L34" s="34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="M34" s="38" t="inlineStr">
         <is>
-          <t>1해 연24.4% · 변동성 19.4% (위험대비 1.12) · 최대낙폭 -10%</t>
+          <t>5해 연29.0% · 변동성 26.7% (위험대비 0.98) · 최대낙폭 -21% · 가장 나쁜 창 연15.4%</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>애플</t>
+          <t>길리어드</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>헬스케어</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
@@ -4350,27 +4350,27 @@
       </c>
       <c r="F35" s="28" t="inlineStr">
         <is>
-          <t>6,803조원</t>
+          <t>258조원</t>
         </is>
       </c>
       <c r="G35" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H35" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I35" s="29" t="n">
-        <v>0.4034</v>
+        <v>0.2051</v>
       </c>
       <c r="J35" s="29" t="n">
-        <v>0.2504</v>
+        <v>0.2461</v>
       </c>
       <c r="K35" s="31" t="n">
-        <v>-0.1382</v>
+        <v>-0.2659</v>
       </c>
       <c r="L35" s="28" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="M35" s="32" t="inlineStr">
         <is>
-          <t>1해 연40.3% · 변동성 25.0% (위험대비 1.50) · 최대낙폭 -14%</t>
+          <t>5해 연20.5% · 변동성 24.6% (위험대비 0.72) · 최대낙폭 -27% · 가장 나쁜 창 연20.5%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="C36" s="33" t="inlineStr">
         <is>
-          <t>머크</t>
+          <t>코카콜라</t>
         </is>
       </c>
       <c r="D36" s="33" t="inlineStr">
         <is>
-          <t>헬스케어</t>
+          <t>필수소비재</t>
         </is>
       </c>
       <c r="E36" s="33" t="inlineStr">
@@ -4411,27 +4411,27 @@
       </c>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>502조원</t>
+          <t>526조원</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H36" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I36" s="36" t="n">
-        <v>0.7864</v>
+        <v>0.1304</v>
       </c>
       <c r="J36" s="36" t="n">
-        <v>0.2995</v>
+        <v>0.1665</v>
       </c>
       <c r="K36" s="37" t="n">
-        <v>-0.119</v>
+        <v>-0.1727</v>
       </c>
       <c r="L36" s="34" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="M36" s="38" t="inlineStr">
         <is>
-          <t>1해 연78.6% · 변동성 29.9% (위험대비 2.53) · 최대낙폭 -12%</t>
+          <t>5해 연13.0% · 변동성 16.6% (위험대비 0.61) · 최대낙폭 -17% · 가장 나쁜 창 연13.0%</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>유니온퍼시픽</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
@@ -4472,27 +4472,27 @@
       </c>
       <c r="F37" s="28" t="inlineStr">
         <is>
-          <t>232조원</t>
+          <t>362조원</t>
         </is>
       </c>
       <c r="G37" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H37" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I37" s="29" t="n">
-        <v>0.2984</v>
+        <v>0.2098</v>
       </c>
       <c r="J37" s="29" t="n">
-        <v>0.223</v>
+        <v>0.2431</v>
       </c>
       <c r="K37" s="31" t="n">
-        <v>-0.1228</v>
+        <v>-0.3284</v>
       </c>
       <c r="L37" s="28" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="M37" s="32" t="inlineStr">
         <is>
-          <t>1해 연29.8% · 변동성 22.3% (위험대비 1.21) · 최대낙폭 -12%</t>
+          <t>5해 연21.0% · 변동성 24.3% (위험대비 0.75) · 최대낙폭 -33% · 가장 나쁜 창 연21.0%</t>
         </is>
       </c>
     </row>
@@ -4518,12 +4518,12 @@
       </c>
       <c r="C38" s="33" t="inlineStr">
         <is>
-          <t>프로로지스</t>
+          <t>처브</t>
         </is>
       </c>
       <c r="D38" s="33" t="inlineStr">
         <is>
-          <t>부동산</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E38" s="33" t="inlineStr">
@@ -4538,22 +4538,22 @@
       </c>
       <c r="G38" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H38" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I38" s="36" t="n">
-        <v>0.17</v>
+        <v>0.1527</v>
       </c>
       <c r="J38" s="36" t="n">
-        <v>0.2139</v>
+        <v>0.2041</v>
       </c>
       <c r="K38" s="37" t="n">
-        <v>-0.1088</v>
+        <v>-0.1926</v>
       </c>
       <c r="L38" s="34" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="M38" s="38" t="inlineStr">
         <is>
-          <t>1해 연17.0% · 변동성 21.4% (위험대비 0.66) · 최대낙폭 -11%</t>
+          <t>5해 연15.3% · 변동성 20.4% (위험대비 0.61) · 최대낙폭 -19% · 가장 나쁜 창 연15.3%</t>
         </is>
       </c>
     </row>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>브리스톨마이어스스퀴브</t>
+          <t>존슨앤드존슨</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
@@ -4594,27 +4594,27 @@
       </c>
       <c r="F39" s="28" t="inlineStr">
         <is>
-          <t>178조원</t>
+          <t>902조원</t>
         </is>
       </c>
       <c r="G39" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H39" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I39" s="29" t="n">
-        <v>0.3713</v>
+        <v>0.1315</v>
       </c>
       <c r="J39" s="29" t="n">
-        <v>0.2737</v>
+        <v>0.1756</v>
       </c>
       <c r="K39" s="31" t="n">
-        <v>-0.1342</v>
+        <v>-0.1841</v>
       </c>
       <c r="L39" s="28" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="M39" s="32" t="inlineStr">
         <is>
-          <t>1해 연37.1% · 변동성 27.4% (위험대비 1.25) · 최대낙폭 -13%</t>
+          <t>5해 연13.2% · 변동성 17.6% (위험대비 0.59) · 최대낙폭 -18% · 가장 나쁜 창 연13.2%</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="C40" s="33" t="inlineStr">
         <is>
-          <t>엑슨모빌</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="D40" s="33" t="inlineStr">
@@ -4655,27 +4655,27 @@
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>929조원</t>
+          <t>570조원</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H40" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I40" s="36" t="n">
-        <v>0.4526</v>
+        <v>0.2156</v>
       </c>
       <c r="J40" s="36" t="n">
-        <v>0.2598</v>
+        <v>0.2528</v>
       </c>
       <c r="K40" s="37" t="n">
-        <v>-0.2065</v>
+        <v>-0.2495</v>
       </c>
       <c r="L40" s="34" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="M40" s="38" t="inlineStr">
         <is>
-          <t>1해 연45.3% · 변동성 26.0% (위험대비 1.63) · 최대낙폭 -21%</t>
+          <t>5해 연21.6% · 변동성 25.3% (위험대비 0.74) · 최대낙폭 -25% · 가장 나쁜 창 연12.6%</t>
         </is>
       </c>
     </row>
@@ -4701,12 +4701,12 @@
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>버크셔 해서웨이 B</t>
+          <t>알트리아</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>필수소비재</t>
         </is>
       </c>
       <c r="E41" s="14" t="inlineStr">
@@ -4716,27 +4716,27 @@
       </c>
       <c r="F41" s="28" t="inlineStr">
         <is>
-          <t>1,508조원</t>
+          <t>161조원</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H41" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I41" s="29" t="n">
-        <v>0.0574</v>
+        <v>0.1542</v>
       </c>
       <c r="J41" s="29" t="n">
-        <v>0.1444</v>
+        <v>0.2167</v>
       </c>
       <c r="K41" s="31" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.2583</v>
       </c>
       <c r="L41" s="28" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="M41" s="32" t="inlineStr">
         <is>
-          <t>1해 연5.7% · 변동성 14.4% (위험대비 0.20) · 최대낙폭 -9%</t>
+          <t>5해 연15.4% · 변동성 21.7% (위험대비 0.58) · 최대낙폭 -26% · 가장 나쁜 창 연13.3%</t>
         </is>
       </c>
     </row>
@@ -4762,12 +4762,12 @@
       </c>
       <c r="C42" s="33" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>캐터필러</t>
         </is>
       </c>
       <c r="D42" s="33" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>산업재</t>
         </is>
       </c>
       <c r="E42" s="33" t="inlineStr">
@@ -4777,27 +4777,27 @@
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>574조원</t>
+          <t>515조원</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H42" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I42" s="36" t="n">
-        <v>0.3439</v>
+        <v>0.3371</v>
       </c>
       <c r="J42" s="36" t="n">
-        <v>0.2378</v>
+        <v>0.3169</v>
       </c>
       <c r="K42" s="37" t="n">
-        <v>-0.2153</v>
+        <v>-0.3405</v>
       </c>
       <c r="L42" s="34" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="M42" s="38" t="inlineStr">
         <is>
-          <t>1해 연34.4% · 변동성 23.8% (위험대비 1.33) · 최대낙폭 -22%</t>
+          <t>5해 연33.7% · 변동성 31.7% (위험대비 0.98) · 최대낙폭 -34% · 가장 나쁜 창 연33.7%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>시스코</t>
+          <t>월마트</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>필수소비재</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
@@ -4838,27 +4838,27 @@
       </c>
       <c r="F43" s="28" t="inlineStr">
         <is>
-          <t>601조원</t>
+          <t>1,177조원</t>
         </is>
       </c>
       <c r="G43" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H43" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I43" s="29" t="n">
-        <v>0.606</v>
+        <v>0.1836</v>
       </c>
       <c r="J43" s="29" t="n">
-        <v>0.3417</v>
+        <v>0.2249</v>
       </c>
       <c r="K43" s="31" t="n">
-        <v>-0.1735</v>
+        <v>-0.2574</v>
       </c>
       <c r="L43" s="28" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="M43" s="32" t="inlineStr">
         <is>
-          <t>1해 연60.6% · 변동성 34.2% (위험대비 1.69) · 최대낙폭 -17%</t>
+          <t>5해 연18.4% · 변동성 22.5% (위험대비 0.69) · 최대낙폭 -26% · 가장 나쁜 창 연3.0%</t>
         </is>
       </c>
     </row>
@@ -4899,27 +4899,27 @@
       </c>
       <c r="F44" s="34" t="inlineStr">
         <is>
-          <t>284조원</t>
+          <t>289조원</t>
         </is>
       </c>
       <c r="G44" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H44" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I44" s="36" t="n">
-        <v>0.3707</v>
+        <v>0.1601</v>
       </c>
       <c r="J44" s="36" t="n">
-        <v>0.294</v>
+        <v>0.2458</v>
       </c>
       <c r="K44" s="37" t="n">
-        <v>-0.1657</v>
+        <v>-0.2486</v>
       </c>
       <c r="L44" s="34" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="M44" s="38" t="inlineStr">
         <is>
-          <t>1해 연37.1% · 변동성 29.4% (위험대비 1.17) · 최대낙폭 -17%</t>
+          <t>5해 연16.0% · 변동성 24.6% (위험대비 0.54) · 최대낙폭 -25% · 가장 나쁜 창 연16.0%</t>
         </is>
       </c>
     </row>
@@ -4945,12 +4945,12 @@
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>JP모간체이스</t>
+          <t>일라이 릴리</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>헬스케어</t>
         </is>
       </c>
       <c r="E45" s="14" t="inlineStr">
@@ -4960,27 +4960,27 @@
       </c>
       <c r="F45" s="28" t="inlineStr">
         <is>
-          <t>1,284조원</t>
+          <t>1,425조원</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H45" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I45" s="29" t="n">
-        <v>0.1293</v>
+        <v>0.3799</v>
       </c>
       <c r="J45" s="29" t="n">
-        <v>0.2212</v>
+        <v>0.3256</v>
       </c>
       <c r="K45" s="31" t="n">
-        <v>-0.1547</v>
+        <v>-0.3448</v>
       </c>
       <c r="L45" s="28" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="M45" s="32" t="inlineStr">
         <is>
-          <t>1해 연12.9% · 변동성 22.1% (위험대비 0.46) · 최대낙폭 -15%</t>
+          <t>5해 연38.0% · 변동성 32.6% (위험대비 1.08) · 최대낙폭 -34% · 가장 나쁜 창 연25.1%</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="C46" s="33" t="inlineStr">
         <is>
-          <t>시티그룹</t>
+          <t>골드만삭스</t>
         </is>
       </c>
       <c r="D46" s="33" t="inlineStr">
@@ -5021,27 +5021,27 @@
       </c>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>308조원</t>
+          <t>380조원</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H46" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I46" s="36" t="n">
-        <v>0.3315</v>
+        <v>0.2129</v>
       </c>
       <c r="J46" s="36" t="n">
-        <v>0.2924</v>
+        <v>0.2868</v>
       </c>
       <c r="K46" s="37" t="n">
-        <v>-0.1476</v>
+        <v>-0.3284</v>
       </c>
       <c r="L46" s="34" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="M46" s="38" t="inlineStr">
         <is>
-          <t>1해 연33.1% · 변동성 29.2% (위험대비 1.04) · 최대낙폭 -15%</t>
+          <t>5해 연21.3% · 변동성 28.7% (위험대비 0.64) · 최대낙폭 -33% · 가장 나쁜 창 연20.9%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>화이자</t>
+          <t>팔로알토네트웍스</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>헬스케어</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
@@ -5082,27 +5082,27 @@
       </c>
       <c r="F47" s="28" t="inlineStr">
         <is>
-          <t>218조원</t>
+          <t>412조원</t>
         </is>
       </c>
       <c r="G47" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H47" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I47" s="29" t="n">
-        <v>0.1453</v>
+        <v>0.4321</v>
       </c>
       <c r="J47" s="29" t="n">
-        <v>0.2347</v>
+        <v>0.4356</v>
       </c>
       <c r="K47" s="31" t="n">
-        <v>-0.1709</v>
+        <v>-0.3601</v>
       </c>
       <c r="L47" s="28" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M47" s="32" t="inlineStr">
         <is>
-          <t>1해 연14.5% · 변동성 23.5% (위험대비 0.50) · 최대낙폭 -17%</t>
+          <t>3해 연43.2% · 변동성 43.6% (위험대비 0.93) · 최대낙폭 -36% · 가장 나쁜 창 연43.2%</t>
         </is>
       </c>
     </row>
@@ -5143,27 +5143,27 @@
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>181조원</t>
+          <t>179조원</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H48" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I48" s="36" t="n">
-        <v>0.3046</v>
+        <v>0.2184</v>
       </c>
       <c r="J48" s="36" t="n">
-        <v>0.2846</v>
+        <v>0.2925</v>
       </c>
       <c r="K48" s="37" t="n">
-        <v>-0.1521</v>
+        <v>-0.2907</v>
       </c>
       <c r="L48" s="34" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="M48" s="38" t="inlineStr">
         <is>
-          <t>1해 연30.5% · 변동성 28.5% (위험대비 0.97) · 최대낙폭 -15%</t>
+          <t>5해 연21.8% · 변동성 29.2% (위험대비 0.65) · 최대낙폭 -29% · 가장 나쁜 창 연13.5%</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>뱅크오브아메리카</t>
+          <t>JP모간체이스</t>
         </is>
       </c>
       <c r="D49" s="14" t="inlineStr">
@@ -5204,27 +5204,27 @@
       </c>
       <c r="F49" s="28" t="inlineStr">
         <is>
-          <t>563조원</t>
+          <t>1,288조원</t>
         </is>
       </c>
       <c r="G49" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H49" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I49" s="29" t="n">
-        <v>0.1442</v>
+        <v>0.2019</v>
       </c>
       <c r="J49" s="29" t="n">
-        <v>0.221</v>
+        <v>0.2436</v>
       </c>
       <c r="K49" s="31" t="n">
-        <v>-0.1839</v>
+        <v>-0.3877</v>
       </c>
       <c r="L49" s="28" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="M49" s="32" t="inlineStr">
         <is>
-          <t>1해 연14.4% · 변동성 22.1% (위험대비 0.53) · 최대낙폭 -18%</t>
+          <t>5해 연20.2% · 변동성 24.4% (위험대비 0.71) · 최대낙폭 -39% · 가장 나쁜 창 연14.3%</t>
         </is>
       </c>
     </row>
@@ -5250,12 +5250,12 @@
       </c>
       <c r="C50" s="33" t="inlineStr">
         <is>
-          <t>넥스트에라에너지</t>
+          <t>애플</t>
         </is>
       </c>
       <c r="D50" s="33" t="inlineStr">
         <is>
-          <t>유틸리티</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E50" s="33" t="inlineStr">
@@ -5265,27 +5265,27 @@
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>235조원</t>
+          <t>6,799조원</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H50" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I50" s="36" t="n">
-        <v>0.1238</v>
+        <v>0.1818</v>
       </c>
       <c r="J50" s="36" t="n">
-        <v>0.2128</v>
+        <v>0.2794</v>
       </c>
       <c r="K50" s="37" t="n">
-        <v>-0.1789</v>
+        <v>-0.3336</v>
       </c>
       <c r="L50" s="34" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="M50" s="38" t="inlineStr">
         <is>
-          <t>1해 연12.4% · 변동성 21.3% (위험대비 0.45) · 최대낙폭 -18%</t>
+          <t>5해 연18.2% · 변동성 27.9% (위험대비 0.55) · 최대낙폭 -33% · 가장 나쁜 창 연18.2%</t>
         </is>
       </c>
     </row>
@@ -5311,12 +5311,12 @@
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>스타벅스</t>
+          <t>비자</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>경기소비재</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
@@ -5326,27 +5326,27 @@
       </c>
       <c r="F51" s="28" t="inlineStr">
         <is>
-          <t>152조원</t>
+          <t>958조원</t>
         </is>
       </c>
       <c r="G51" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H51" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I51" s="29" t="n">
-        <v>0.1769</v>
+        <v>0.1116</v>
       </c>
       <c r="J51" s="29" t="n">
-        <v>0.2782</v>
+        <v>0.2287</v>
       </c>
       <c r="K51" s="31" t="n">
-        <v>-0.1451</v>
+        <v>-0.2414</v>
       </c>
       <c r="L51" s="28" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="M51" s="32" t="inlineStr">
         <is>
-          <t>1해 연17.7% · 변동성 27.8% (위험대비 0.53) · 최대낙폭 -15%</t>
+          <t>5해 연11.2% · 변동성 22.9% (위험대비 0.37) · 최대낙폭 -24% · 가장 나쁜 창 연7.2%</t>
         </is>
       </c>
     </row>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="C52" s="33" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>이튼</t>
         </is>
       </c>
       <c r="D52" s="33" t="inlineStr">
@@ -5387,27 +5387,27 @@
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>361조원</t>
+          <t>229조원</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H52" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I52" s="36" t="n">
-        <v>0.2423</v>
+        <v>0.2329</v>
       </c>
       <c r="J52" s="36" t="n">
-        <v>0.2583</v>
+        <v>0.3206</v>
       </c>
       <c r="K52" s="37" t="n">
-        <v>-0.1932</v>
+        <v>-0.3446</v>
       </c>
       <c r="L52" s="34" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="M52" s="38" t="inlineStr">
         <is>
-          <t>1해 연24.2% · 변동성 25.8% (위험대비 0.83) · 최대낙폭 -19%</t>
+          <t>5해 연23.3% · 변동성 32.1% (위험대비 0.64) · 최대낙폭 -34% · 가장 나쁜 창 연18.2%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>비자</t>
+          <t>모간스탠리</t>
         </is>
       </c>
       <c r="D53" s="14" t="inlineStr">
@@ -5448,27 +5448,27 @@
       </c>
       <c r="F53" s="28" t="inlineStr">
         <is>
-          <t>955조원</t>
+          <t>441조원</t>
         </is>
       </c>
       <c r="G53" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H53" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I53" s="29" t="n">
-        <v>0.09380000000000001</v>
+        <v>0.1797</v>
       </c>
       <c r="J53" s="29" t="n">
-        <v>0.2201</v>
+        <v>0.2889</v>
       </c>
       <c r="K53" s="31" t="n">
-        <v>-0.1735</v>
+        <v>-0.3238</v>
       </c>
       <c r="L53" s="28" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="M53" s="32" t="inlineStr">
         <is>
-          <t>1해 연9.4% · 변동성 22.0% (위험대비 0.30) · 최대낙폭 -17%</t>
+          <t>5해 연18.0% · 변동성 28.9% (위험대비 0.52) · 최대낙폭 -32% · 가장 나쁜 창 연18.0%</t>
         </is>
       </c>
     </row>
@@ -5494,12 +5494,12 @@
       </c>
       <c r="C54" s="33" t="inlineStr">
         <is>
-          <t>애브비</t>
+          <t>프로그레시브</t>
         </is>
       </c>
       <c r="D54" s="33" t="inlineStr">
         <is>
-          <t>헬스케어</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E54" s="33" t="inlineStr">
@@ -5509,27 +5509,27 @@
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>645조원</t>
+          <t>172조원</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H54" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I54" s="36" t="n">
-        <v>0.2059</v>
+        <v>0.2061</v>
       </c>
       <c r="J54" s="36" t="n">
-        <v>0.2644</v>
+        <v>0.2553</v>
       </c>
       <c r="K54" s="37" t="n">
-        <v>-0.1923</v>
+        <v>-0.3035</v>
       </c>
       <c r="L54" s="34" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="M54" s="38" t="inlineStr">
         <is>
-          <t>1해 연20.6% · 변동성 26.4% (위험대비 0.67) · 최대낙폭 -19%</t>
+          <t>5해 연20.6% · 변동성 25.5% (위험대비 0.70) · 최대낙폭 -30% · 가장 나쁜 창 연-6.7%</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>디어</t>
+          <t>록히드마틴</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
@@ -5570,27 +5570,27 @@
       </c>
       <c r="F55" s="28" t="inlineStr">
         <is>
-          <t>256조원</t>
+          <t>171조원</t>
         </is>
       </c>
       <c r="G55" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H55" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I55" s="29" t="n">
-        <v>0.4261</v>
+        <v>0.1195</v>
       </c>
       <c r="J55" s="29" t="n">
-        <v>0.3169</v>
+        <v>0.2409</v>
       </c>
       <c r="K55" s="31" t="n">
-        <v>-0.2013</v>
+        <v>-0.3179</v>
       </c>
       <c r="L55" s="28" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="M55" s="32" t="inlineStr">
         <is>
-          <t>1해 연42.6% · 변동성 31.7% (위험대비 1.26) · 최대낙폭 -20%</t>
+          <t>5해 연11.9% · 변동성 24.1% (위험대비 0.38) · 최대낙폭 -32% · 가장 나쁜 창 연11.1%</t>
         </is>
       </c>
     </row>
@@ -5616,12 +5616,12 @@
       </c>
       <c r="C56" s="33" t="inlineStr">
         <is>
-          <t>길리어드</t>
+          <t>시스코</t>
         </is>
       </c>
       <c r="D56" s="33" t="inlineStr">
         <is>
-          <t>헬스케어</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E56" s="33" t="inlineStr">
@@ -5631,27 +5631,27 @@
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>259조원</t>
+          <t>598조원</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H56" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I56" s="36" t="n">
-        <v>0.3115</v>
+        <v>0.1674</v>
       </c>
       <c r="J56" s="36" t="n">
-        <v>0.2644</v>
+        <v>0.2597</v>
       </c>
       <c r="K56" s="37" t="n">
-        <v>-0.2203</v>
+        <v>-0.3668</v>
       </c>
       <c r="L56" s="34" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="M56" s="38" t="inlineStr">
         <is>
-          <t>1해 연31.1% · 변동성 26.4% (위험대비 1.07) · 최대낙폭 -22%</t>
+          <t>5해 연16.7% · 변동성 26.0% (위험대비 0.54) · 최대낙폭 -37% · 가장 나쁜 창 연16.7%</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr"/>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제안서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산군" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상품" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="제안서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="자산군" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="상품" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="출처" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="사용법" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'상품'!$A$7:$M$156</definedName>
@@ -1376,7 +1376,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-20 01:05:58 · 문서 2026-09-20 01:08 (KST)</t>
+          <t>유니버스 2026-09-20 14:07:54 · 문서 2026-09-20 14:07 (KST)</t>
         </is>
       </c>
     </row>
@@ -2411,13 +2411,13 @@
         <v>99</v>
       </c>
       <c r="D11" s="29" t="n">
-        <v>0.1049382716049381</v>
+        <v>0.09780242562454644</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>0.2923973274425171</v>
+        <v>0.2921539773352639</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>-0.3235610824922673</v>
+        <v>-0.3237114148035969</v>
       </c>
     </row>
     <row r="12">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="F34" s="34" t="inlineStr">
         <is>
-          <t>932조원</t>
+          <t>931조원</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="F39" s="28" t="inlineStr">
         <is>
-          <t>902조원</t>
+          <t>901조원</t>
         </is>
       </c>
       <c r="G39" s="30" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>570조원</t>
+          <t>569조원</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="F43" s="28" t="inlineStr">
         <is>
-          <t>1,177조원</t>
+          <t>1,176조원</t>
         </is>
       </c>
       <c r="G43" s="30" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="F45" s="28" t="inlineStr">
         <is>
-          <t>1,425조원</t>
+          <t>1,424조원</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="C46" s="33" t="inlineStr">
         <is>
-          <t>골드만삭스</t>
+          <t>버크셔 해서웨이 B</t>
         </is>
       </c>
       <c r="D46" s="33" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>380조원</t>
+          <t>1,511조원</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -5035,13 +5035,13 @@
         </is>
       </c>
       <c r="I46" s="36" t="n">
-        <v>0.2129</v>
+        <v>0.1287</v>
       </c>
       <c r="J46" s="36" t="n">
-        <v>0.2868</v>
+        <v>0.1716</v>
       </c>
       <c r="K46" s="37" t="n">
-        <v>-0.3284</v>
+        <v>-0.2658</v>
       </c>
       <c r="L46" s="34" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="M46" s="38" t="inlineStr">
         <is>
-          <t>5해 연21.3% · 변동성 28.7% (위험대비 0.64) · 최대낙폭 -33% · 가장 나쁜 창 연20.9%</t>
+          <t>5해 연12.9% · 변동성 17.2% (위험대비 0.59) · 최대낙폭 -27% · 가장 나쁜 창 연3.5%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>팔로알토네트웍스</t>
+          <t>골드만삭스</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="F47" s="28" t="inlineStr">
         <is>
-          <t>412조원</t>
+          <t>380조원</t>
         </is>
       </c>
       <c r="G47" s="30" t="inlineStr">
@@ -5092,17 +5092,17 @@
       </c>
       <c r="H47" s="30" t="inlineStr">
         <is>
-          <t>3해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I47" s="29" t="n">
-        <v>0.4321</v>
+        <v>0.2129</v>
       </c>
       <c r="J47" s="29" t="n">
-        <v>0.4356</v>
+        <v>0.2868</v>
       </c>
       <c r="K47" s="31" t="n">
-        <v>-0.3601</v>
+        <v>-0.3284</v>
       </c>
       <c r="L47" s="28" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M47" s="32" t="inlineStr">
         <is>
-          <t>3해 연43.2% · 변동성 43.6% (위험대비 0.93) · 최대낙폭 -36% · 가장 나쁜 창 연43.2%</t>
+          <t>5해 연21.3% · 변동성 28.7% (위험대비 0.64) · 최대낙폭 -33% · 가장 나쁜 창 연20.9%</t>
         </is>
       </c>
     </row>
@@ -5128,12 +5128,12 @@
       </c>
       <c r="C48" s="33" t="inlineStr">
         <is>
-          <t>버텍스</t>
+          <t>팔로알토네트웍스</t>
         </is>
       </c>
       <c r="D48" s="33" t="inlineStr">
         <is>
-          <t>헬스케어</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E48" s="33" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>179조원</t>
+          <t>412조원</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="H48" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I48" s="36" t="n">
-        <v>0.2184</v>
+        <v>0.4321</v>
       </c>
       <c r="J48" s="36" t="n">
-        <v>0.2925</v>
+        <v>0.4356</v>
       </c>
       <c r="K48" s="37" t="n">
-        <v>-0.2907</v>
+        <v>-0.3601</v>
       </c>
       <c r="L48" s="34" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="M48" s="38" t="inlineStr">
         <is>
-          <t>5해 연21.8% · 변동성 29.2% (위험대비 0.65) · 최대낙폭 -29% · 가장 나쁜 창 연13.5%</t>
+          <t>3해 연43.2% · 변동성 43.6% (위험대비 0.93) · 최대낙폭 -36% · 가장 나쁜 창 연43.2%</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>JP모간체이스</t>
+          <t>버텍스</t>
         </is>
       </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>헬스케어</t>
         </is>
       </c>
       <c r="E49" s="14" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="F49" s="28" t="inlineStr">
         <is>
-          <t>1,288조원</t>
+          <t>178조원</t>
         </is>
       </c>
       <c r="G49" s="30" t="inlineStr">
@@ -5218,13 +5218,13 @@
         </is>
       </c>
       <c r="I49" s="29" t="n">
-        <v>0.2019</v>
+        <v>0.2184</v>
       </c>
       <c r="J49" s="29" t="n">
-        <v>0.2436</v>
+        <v>0.2925</v>
       </c>
       <c r="K49" s="31" t="n">
-        <v>-0.3877</v>
+        <v>-0.2907</v>
       </c>
       <c r="L49" s="28" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="M49" s="32" t="inlineStr">
         <is>
-          <t>5해 연20.2% · 변동성 24.4% (위험대비 0.71) · 최대낙폭 -39% · 가장 나쁜 창 연14.3%</t>
+          <t>5해 연21.8% · 변동성 29.2% (위험대비 0.65) · 최대낙폭 -29% · 가장 나쁜 창 연13.5%</t>
         </is>
       </c>
     </row>
@@ -5250,12 +5250,12 @@
       </c>
       <c r="C50" s="33" t="inlineStr">
         <is>
-          <t>애플</t>
+          <t>JP모간체이스</t>
         </is>
       </c>
       <c r="D50" s="33" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E50" s="33" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>6,799조원</t>
+          <t>1,287조원</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -5279,13 +5279,13 @@
         </is>
       </c>
       <c r="I50" s="36" t="n">
-        <v>0.1818</v>
+        <v>0.2019</v>
       </c>
       <c r="J50" s="36" t="n">
-        <v>0.2794</v>
+        <v>0.2436</v>
       </c>
       <c r="K50" s="37" t="n">
-        <v>-0.3336</v>
+        <v>-0.3877</v>
       </c>
       <c r="L50" s="34" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="M50" s="38" t="inlineStr">
         <is>
-          <t>5해 연18.2% · 변동성 27.9% (위험대비 0.55) · 최대낙폭 -33% · 가장 나쁜 창 연18.2%</t>
+          <t>5해 연20.2% · 변동성 24.4% (위험대비 0.71) · 최대낙폭 -39% · 가장 나쁜 창 연14.3%</t>
         </is>
       </c>
     </row>
@@ -5311,12 +5311,12 @@
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>비자</t>
+          <t>애플</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="F51" s="28" t="inlineStr">
         <is>
-          <t>958조원</t>
+          <t>6,794조원</t>
         </is>
       </c>
       <c r="G51" s="30" t="inlineStr">
@@ -5340,13 +5340,13 @@
         </is>
       </c>
       <c r="I51" s="29" t="n">
-        <v>0.1116</v>
+        <v>0.1818</v>
       </c>
       <c r="J51" s="29" t="n">
-        <v>0.2287</v>
+        <v>0.2794</v>
       </c>
       <c r="K51" s="31" t="n">
-        <v>-0.2414</v>
+        <v>-0.3336</v>
       </c>
       <c r="L51" s="28" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="M51" s="32" t="inlineStr">
         <is>
-          <t>5해 연11.2% · 변동성 22.9% (위험대비 0.37) · 최대낙폭 -24% · 가장 나쁜 창 연7.2%</t>
+          <t>5해 연18.2% · 변동성 27.9% (위험대비 0.55) · 최대낙폭 -33% · 가장 나쁜 창 연18.2%</t>
         </is>
       </c>
     </row>
@@ -5372,12 +5372,12 @@
       </c>
       <c r="C52" s="33" t="inlineStr">
         <is>
-          <t>이튼</t>
+          <t>비자</t>
         </is>
       </c>
       <c r="D52" s="33" t="inlineStr">
         <is>
-          <t>산업재</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E52" s="33" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>229조원</t>
+          <t>958조원</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -5401,13 +5401,13 @@
         </is>
       </c>
       <c r="I52" s="36" t="n">
-        <v>0.2329</v>
+        <v>0.1116</v>
       </c>
       <c r="J52" s="36" t="n">
-        <v>0.3206</v>
+        <v>0.2287</v>
       </c>
       <c r="K52" s="37" t="n">
-        <v>-0.3446</v>
+        <v>-0.2414</v>
       </c>
       <c r="L52" s="34" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="M52" s="38" t="inlineStr">
         <is>
-          <t>5해 연23.3% · 변동성 32.1% (위험대비 0.64) · 최대낙폭 -34% · 가장 나쁜 창 연18.2%</t>
+          <t>5해 연11.2% · 변동성 22.9% (위험대비 0.37) · 최대낙폭 -24% · 가장 나쁜 창 연7.2%</t>
         </is>
       </c>
     </row>
@@ -5433,12 +5433,12 @@
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>모간스탠리</t>
+          <t>이튼</t>
         </is>
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>산업재</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="F53" s="28" t="inlineStr">
         <is>
-          <t>441조원</t>
+          <t>228조원</t>
         </is>
       </c>
       <c r="G53" s="30" t="inlineStr">
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="I53" s="29" t="n">
-        <v>0.1797</v>
+        <v>0.2329</v>
       </c>
       <c r="J53" s="29" t="n">
-        <v>0.2889</v>
+        <v>0.3206</v>
       </c>
       <c r="K53" s="31" t="n">
-        <v>-0.3238</v>
+        <v>-0.3446</v>
       </c>
       <c r="L53" s="28" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="M53" s="32" t="inlineStr">
         <is>
-          <t>5해 연18.0% · 변동성 28.9% (위험대비 0.52) · 최대낙폭 -32% · 가장 나쁜 창 연18.0%</t>
+          <t>5해 연23.3% · 변동성 32.1% (위험대비 0.64) · 최대낙폭 -34% · 가장 나쁜 창 연18.2%</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="C54" s="33" t="inlineStr">
         <is>
-          <t>프로그레시브</t>
+          <t>모간스탠리</t>
         </is>
       </c>
       <c r="D54" s="33" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>172조원</t>
+          <t>441조원</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -5523,13 +5523,13 @@
         </is>
       </c>
       <c r="I54" s="36" t="n">
-        <v>0.2061</v>
+        <v>0.1797</v>
       </c>
       <c r="J54" s="36" t="n">
-        <v>0.2553</v>
+        <v>0.2889</v>
       </c>
       <c r="K54" s="37" t="n">
-        <v>-0.3035</v>
+        <v>-0.3238</v>
       </c>
       <c r="L54" s="34" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="M54" s="38" t="inlineStr">
         <is>
-          <t>5해 연20.6% · 변동성 25.5% (위험대비 0.70) · 최대낙폭 -30% · 가장 나쁜 창 연-6.7%</t>
+          <t>5해 연18.0% · 변동성 28.9% (위험대비 0.52) · 최대낙폭 -32% · 가장 나쁜 창 연18.0%</t>
         </is>
       </c>
     </row>
@@ -5555,12 +5555,12 @@
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>록히드마틴</t>
+          <t>프로그레시브</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
         <is>
-          <t>산업재</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E55" s="14" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="F55" s="28" t="inlineStr">
         <is>
-          <t>171조원</t>
+          <t>172조원</t>
         </is>
       </c>
       <c r="G55" s="30" t="inlineStr">
@@ -5584,13 +5584,13 @@
         </is>
       </c>
       <c r="I55" s="29" t="n">
-        <v>0.1195</v>
+        <v>0.2061</v>
       </c>
       <c r="J55" s="29" t="n">
-        <v>0.2409</v>
+        <v>0.2553</v>
       </c>
       <c r="K55" s="31" t="n">
-        <v>-0.3179</v>
+        <v>-0.3035</v>
       </c>
       <c r="L55" s="28" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="M55" s="32" t="inlineStr">
         <is>
-          <t>5해 연11.9% · 변동성 24.1% (위험대비 0.38) · 최대낙폭 -32% · 가장 나쁜 창 연11.1%</t>
+          <t>5해 연20.6% · 변동성 25.5% (위험대비 0.70) · 최대낙폭 -30% · 가장 나쁜 창 연-6.7%</t>
         </is>
       </c>
     </row>
@@ -5616,12 +5616,12 @@
       </c>
       <c r="C56" s="33" t="inlineStr">
         <is>
-          <t>시스코</t>
+          <t>록히드마틴</t>
         </is>
       </c>
       <c r="D56" s="33" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>산업재</t>
         </is>
       </c>
       <c r="E56" s="33" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>598조원</t>
+          <t>170조원</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -5645,13 +5645,13 @@
         </is>
       </c>
       <c r="I56" s="36" t="n">
-        <v>0.1674</v>
+        <v>0.1195</v>
       </c>
       <c r="J56" s="36" t="n">
-        <v>0.2597</v>
+        <v>0.2409</v>
       </c>
       <c r="K56" s="37" t="n">
-        <v>-0.3668</v>
+        <v>-0.3179</v>
       </c>
       <c r="L56" s="34" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="M56" s="38" t="inlineStr">
         <is>
-          <t>5해 연16.7% · 변동성 26.0% (위험대비 0.54) · 최대낙폭 -37% · 가장 나쁜 창 연16.7%</t>
+          <t>5해 연11.9% · 변동성 24.1% (위험대비 0.38) · 최대낙폭 -32% · 가장 나쁜 창 연11.1%</t>
         </is>
       </c>
     </row>
@@ -12128,7 +12128,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr"/>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="제안서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="자산군" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="상품" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="출처" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="사용법" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제안서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산군" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상품" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'상품'!$A$7:$M$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'상품'!$A$6:$M$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1376,7 +1376,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-20 14:07:54 · 문서 2026-09-20 14:07 (KST)</t>
+          <t>유니버스 2026-09-20 14:07:54 · 문서 2026-09-20 14:10 (KST)</t>
         </is>
       </c>
     </row>
@@ -11989,7 +11989,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:M156"/>
+  <autoFilter ref="A6:M156"/>
   <mergeCells count="1">
     <mergeCell ref="A4:M4"/>
   </mergeCells>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제안서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산군" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상품" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="제안서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="자산군" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="상품" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="출처" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="사용법" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'상품'!$A$6:$M$156</definedName>
@@ -1043,7 +1043,7 @@
         <v/>
       </c>
       <c r="G22" s="17" t="n">
-        <v>0.0621</v>
+        <v>0.0561</v>
       </c>
       <c r="H22" s="15">
         <f>IF(ISNUMBER($F22),$F22,0)</f>
@@ -1376,7 +1376,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-20 14:07:54 · 문서 2026-09-20 14:10 (KST)</t>
+          <t>유니버스 2026-09-20 14:35:38 · 문서 2026-09-20 14:35 (KST)</t>
         </is>
       </c>
     </row>
@@ -4181,13 +4181,13 @@
         </is>
       </c>
       <c r="I32" s="36" t="n">
-        <v>0.2423</v>
+        <v>0.2862</v>
       </c>
       <c r="J32" s="36" t="n">
-        <v>0.2345</v>
+        <v>0.2527</v>
       </c>
       <c r="K32" s="37" t="n">
-        <v>-0.2192</v>
+        <v>-0.2288</v>
       </c>
       <c r="L32" s="34" t="inlineStr">
         <is>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="M32" s="38" t="inlineStr">
         <is>
-          <t>5해 연24.2% · 변동성 23.4% (위험대비 0.91) · 최대낙폭 -22% · 가장 나쁜 창 연23.2%</t>
+          <t>5해 연28.6% · 변동성 25.3% (위험대비 1.02) · 최대낙폭 -23% · 가장 나쁜 창 연24.1%</t>
         </is>
       </c>
     </row>
@@ -4213,7 +4213,7 @@
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>필립모리스</t>
+          <t>코카콜라</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="F33" s="28" t="inlineStr">
         <is>
-          <t>407조원</t>
+          <t>526조원</t>
         </is>
       </c>
       <c r="G33" s="30" t="inlineStr">
@@ -4242,13 +4242,13 @@
         </is>
       </c>
       <c r="I33" s="29" t="n">
-        <v>0.1805</v>
+        <v>0.1704</v>
       </c>
       <c r="J33" s="29" t="n">
-        <v>0.233</v>
+        <v>0.1891</v>
       </c>
       <c r="K33" s="31" t="n">
-        <v>-0.2278</v>
+        <v>-0.1672</v>
       </c>
       <c r="L33" s="28" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="M33" s="32" t="inlineStr">
         <is>
-          <t>5해 연18.1% · 변동성 23.3% (위험대비 0.65) · 최대낙폭 -23% · 가장 나쁜 창 연17.5%</t>
+          <t>5해 연17.0% · 변동성 18.9% (위험대비 0.75) · 최대낙폭 -17% · 가장 나쁜 창 연17.0%</t>
         </is>
       </c>
     </row>
@@ -4274,12 +4274,12 @@
       </c>
       <c r="C34" s="33" t="inlineStr">
         <is>
-          <t>엑슨모빌</t>
+          <t>길리어드</t>
         </is>
       </c>
       <c r="D34" s="33" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>헬스케어</t>
         </is>
       </c>
       <c r="E34" s="33" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="F34" s="34" t="inlineStr">
         <is>
-          <t>931조원</t>
+          <t>258조원</t>
         </is>
       </c>
       <c r="G34" s="35" t="inlineStr">
@@ -4303,13 +4303,13 @@
         </is>
       </c>
       <c r="I34" s="36" t="n">
-        <v>0.2897</v>
+        <v>0.2477</v>
       </c>
       <c r="J34" s="36" t="n">
-        <v>0.2671</v>
+        <v>0.263</v>
       </c>
       <c r="K34" s="37" t="n">
-        <v>-0.2051</v>
+        <v>-0.2465</v>
       </c>
       <c r="L34" s="34" t="inlineStr">
         <is>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="M34" s="38" t="inlineStr">
         <is>
-          <t>5해 연29.0% · 변동성 26.7% (위험대비 0.98) · 최대낙폭 -21% · 가장 나쁜 창 연15.4%</t>
+          <t>5해 연24.8% · 변동성 26.3% (위험대비 0.83) · 최대낙폭 -25% · 가장 나쁜 창 연24.8%</t>
         </is>
       </c>
     </row>
@@ -4335,12 +4335,12 @@
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>길리어드</t>
+          <t>필립모리스</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
         <is>
-          <t>헬스케어</t>
+          <t>필수소비재</t>
         </is>
       </c>
       <c r="E35" s="14" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="F35" s="28" t="inlineStr">
         <is>
-          <t>258조원</t>
+          <t>407조원</t>
         </is>
       </c>
       <c r="G35" s="30" t="inlineStr">
@@ -4364,13 +4364,13 @@
         </is>
       </c>
       <c r="I35" s="29" t="n">
-        <v>0.2051</v>
+        <v>0.2222</v>
       </c>
       <c r="J35" s="29" t="n">
-        <v>0.2461</v>
+        <v>0.2438</v>
       </c>
       <c r="K35" s="31" t="n">
-        <v>-0.2659</v>
+        <v>-0.184</v>
       </c>
       <c r="L35" s="28" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="M35" s="32" t="inlineStr">
         <is>
-          <t>5해 연20.5% · 변동성 24.6% (위험대비 0.72) · 최대낙폭 -27% · 가장 나쁜 창 연20.5%</t>
+          <t>5해 연22.2% · 변동성 24.4% (위험대비 0.80) · 최대낙폭 -18% · 가장 나쁜 창 연18.3%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="C36" s="33" t="inlineStr">
         <is>
-          <t>코카콜라</t>
+          <t>엑슨모빌</t>
         </is>
       </c>
       <c r="D36" s="33" t="inlineStr">
         <is>
-          <t>필수소비재</t>
+          <t>에너지</t>
         </is>
       </c>
       <c r="E36" s="33" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>526조원</t>
+          <t>931조원</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -4425,13 +4425,13 @@
         </is>
       </c>
       <c r="I36" s="36" t="n">
-        <v>0.1304</v>
+        <v>0.3352000000000001</v>
       </c>
       <c r="J36" s="36" t="n">
-        <v>0.1665</v>
+        <v>0.2815</v>
       </c>
       <c r="K36" s="37" t="n">
-        <v>-0.1727</v>
+        <v>-0.2045</v>
       </c>
       <c r="L36" s="34" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="M36" s="38" t="inlineStr">
         <is>
-          <t>5해 연13.0% · 변동성 16.6% (위험대비 0.61) · 최대낙폭 -17% · 가장 나쁜 창 연13.0%</t>
+          <t>5해 연33.5% · 변동성 28.1% (위험대비 1.09) · 최대낙폭 -20% · 가장 나쁜 창 연17.1%</t>
         </is>
       </c>
     </row>
@@ -4457,12 +4457,12 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>RTX</t>
+          <t>처브</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
         <is>
-          <t>산업재</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E37" s="14" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="F37" s="28" t="inlineStr">
         <is>
-          <t>362조원</t>
+          <t>182조원</t>
         </is>
       </c>
       <c r="G37" s="30" t="inlineStr">
@@ -4486,13 +4486,13 @@
         </is>
       </c>
       <c r="I37" s="29" t="n">
-        <v>0.2098</v>
+        <v>0.1934</v>
       </c>
       <c r="J37" s="29" t="n">
-        <v>0.2431</v>
+        <v>0.2271</v>
       </c>
       <c r="K37" s="31" t="n">
-        <v>-0.3284</v>
+        <v>-0.2158</v>
       </c>
       <c r="L37" s="28" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="M37" s="32" t="inlineStr">
         <is>
-          <t>5해 연21.0% · 변동성 24.3% (위험대비 0.75) · 최대낙폭 -33% · 가장 나쁜 창 연21.0%</t>
+          <t>5해 연19.3% · 변동성 22.7% (위험대비 0.73) · 최대낙폭 -22% · 가장 나쁜 창 연19.3%</t>
         </is>
       </c>
     </row>
@@ -4518,12 +4518,12 @@
       </c>
       <c r="C38" s="33" t="inlineStr">
         <is>
-          <t>처브</t>
+          <t>존슨앤드존슨</t>
         </is>
       </c>
       <c r="D38" s="33" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>헬스케어</t>
         </is>
       </c>
       <c r="E38" s="33" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>182조원</t>
+          <t>901조원</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="I38" s="36" t="n">
-        <v>0.1527</v>
+        <v>0.1715</v>
       </c>
       <c r="J38" s="36" t="n">
-        <v>0.2041</v>
+        <v>0.2006</v>
       </c>
       <c r="K38" s="37" t="n">
-        <v>-0.1926</v>
+        <v>-0.2108</v>
       </c>
       <c r="L38" s="34" t="inlineStr">
         <is>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="M38" s="38" t="inlineStr">
         <is>
-          <t>5해 연15.3% · 변동성 20.4% (위험대비 0.61) · 최대낙폭 -19% · 가장 나쁜 창 연15.3%</t>
+          <t>5해 연17.1% · 변동성 20.1% (위험대비 0.71) · 최대낙폭 -21% · 가장 나쁜 창 연17.1%</t>
         </is>
       </c>
     </row>
@@ -4579,12 +4579,12 @@
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>존슨앤드존슨</t>
+          <t>RTX</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>헬스케어</t>
+          <t>산업재</t>
         </is>
       </c>
       <c r="E39" s="14" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="F39" s="28" t="inlineStr">
         <is>
-          <t>901조원</t>
+          <t>362조원</t>
         </is>
       </c>
       <c r="G39" s="30" t="inlineStr">
@@ -4608,13 +4608,13 @@
         </is>
       </c>
       <c r="I39" s="29" t="n">
-        <v>0.1315</v>
+        <v>0.2526</v>
       </c>
       <c r="J39" s="29" t="n">
-        <v>0.1756</v>
+        <v>0.2634</v>
       </c>
       <c r="K39" s="31" t="n">
-        <v>-0.1841</v>
+        <v>-0.317</v>
       </c>
       <c r="L39" s="28" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="M39" s="32" t="inlineStr">
         <is>
-          <t>5해 연13.2% · 변동성 17.6% (위험대비 0.59) · 최대낙폭 -18% · 가장 나쁜 창 연13.2%</t>
+          <t>5해 연25.3% · 변동성 26.3% (위험대비 0.85) · 최대낙폭 -32% · 가장 나쁜 창 연25.2%</t>
         </is>
       </c>
     </row>
@@ -4640,12 +4640,12 @@
       </c>
       <c r="C40" s="33" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>JP모간체이스</t>
         </is>
       </c>
       <c r="D40" s="33" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E40" s="33" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>569조원</t>
+          <t>1,287조원</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -4669,13 +4669,13 @@
         </is>
       </c>
       <c r="I40" s="36" t="n">
-        <v>0.2156</v>
+        <v>0.2444</v>
       </c>
       <c r="J40" s="36" t="n">
-        <v>0.2528</v>
+        <v>0.254</v>
       </c>
       <c r="K40" s="37" t="n">
-        <v>-0.2495</v>
+        <v>-0.2822</v>
       </c>
       <c r="L40" s="34" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
       </c>
       <c r="M40" s="38" t="inlineStr">
         <is>
-          <t>5해 연21.6% · 변동성 25.3% (위험대비 0.74) · 최대낙폭 -25% · 가장 나쁜 창 연12.6%</t>
+          <t>5해 연24.4% · 변동성 25.4% (위험대비 0.85) · 최대낙폭 -28% · 가장 나쁜 창 연15.1%</t>
         </is>
       </c>
     </row>
@@ -4701,12 +4701,12 @@
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>알트리아</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>필수소비재</t>
+          <t>에너지</t>
         </is>
       </c>
       <c r="E41" s="14" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="F41" s="28" t="inlineStr">
         <is>
-          <t>161조원</t>
+          <t>569조원</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I41" s="29" t="n">
-        <v>0.1542</v>
+        <v>0.2585</v>
       </c>
       <c r="J41" s="29" t="n">
-        <v>0.2167</v>
+        <v>0.2673</v>
       </c>
       <c r="K41" s="31" t="n">
-        <v>-0.2583</v>
+        <v>-0.2604</v>
       </c>
       <c r="L41" s="28" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
       </c>
       <c r="M41" s="32" t="inlineStr">
         <is>
-          <t>5해 연15.4% · 변동성 21.7% (위험대비 0.58) · 최대낙폭 -26% · 가장 나쁜 창 연13.3%</t>
+          <t>5해 연25.9% · 변동성 26.7% (위험대비 0.86) · 최대낙폭 -26% · 가장 나쁜 창 연14.2%</t>
         </is>
       </c>
     </row>
@@ -4762,12 +4762,12 @@
       </c>
       <c r="C42" s="33" t="inlineStr">
         <is>
-          <t>캐터필러</t>
+          <t>알트리아</t>
         </is>
       </c>
       <c r="D42" s="33" t="inlineStr">
         <is>
-          <t>산업재</t>
+          <t>필수소비재</t>
         </is>
       </c>
       <c r="E42" s="33" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="F42" s="34" t="inlineStr">
         <is>
-          <t>515조원</t>
+          <t>161조원</t>
         </is>
       </c>
       <c r="G42" s="35" t="inlineStr">
@@ -4791,13 +4791,13 @@
         </is>
       </c>
       <c r="I42" s="36" t="n">
-        <v>0.3371</v>
+        <v>0.195</v>
       </c>
       <c r="J42" s="36" t="n">
-        <v>0.3169</v>
+        <v>0.2341</v>
       </c>
       <c r="K42" s="37" t="n">
-        <v>-0.3405</v>
+        <v>-0.2366</v>
       </c>
       <c r="L42" s="34" t="inlineStr">
         <is>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="M42" s="38" t="inlineStr">
         <is>
-          <t>5해 연33.7% · 변동성 31.7% (위험대비 0.98) · 최대낙폭 -34% · 가장 나쁜 창 연33.7%</t>
+          <t>5해 연19.5% · 변동성 23.4% (위험대비 0.71) · 최대낙폭 -24% · 가장 나쁜 창 연14.1%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>월마트</t>
+          <t>버크셔 해서웨이 B</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>필수소비재</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="F43" s="28" t="inlineStr">
         <is>
-          <t>1,176조원</t>
+          <t>1,511조원</t>
         </is>
       </c>
       <c r="G43" s="30" t="inlineStr">
@@ -4852,13 +4852,13 @@
         </is>
       </c>
       <c r="I43" s="29" t="n">
-        <v>0.1836</v>
+        <v>0.1686</v>
       </c>
       <c r="J43" s="29" t="n">
-        <v>0.2249</v>
+        <v>0.1924</v>
       </c>
       <c r="K43" s="31" t="n">
-        <v>-0.2574</v>
+        <v>-0.2123</v>
       </c>
       <c r="L43" s="28" t="inlineStr">
         <is>
@@ -4867,7 +4867,7 @@
       </c>
       <c r="M43" s="32" t="inlineStr">
         <is>
-          <t>5해 연18.4% · 변동성 22.5% (위험대비 0.69) · 최대낙폭 -26% · 가장 나쁜 창 연3.0%</t>
+          <t>5해 연16.9% · 변동성 19.2% (위험대비 0.73) · 최대낙폭 -21% · 가장 나쁜 창 연4.2%</t>
         </is>
       </c>
     </row>
@@ -4884,12 +4884,12 @@
       </c>
       <c r="C44" s="33" t="inlineStr">
         <is>
-          <t>암젠</t>
+          <t>골드만삭스</t>
         </is>
       </c>
       <c r="D44" s="33" t="inlineStr">
         <is>
-          <t>헬스케어</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E44" s="33" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="F44" s="34" t="inlineStr">
         <is>
-          <t>289조원</t>
+          <t>380조원</t>
         </is>
       </c>
       <c r="G44" s="35" t="inlineStr">
@@ -4913,13 +4913,13 @@
         </is>
       </c>
       <c r="I44" s="36" t="n">
-        <v>0.1601</v>
+        <v>0.2557</v>
       </c>
       <c r="J44" s="36" t="n">
-        <v>0.2458</v>
+        <v>0.2923</v>
       </c>
       <c r="K44" s="37" t="n">
-        <v>-0.2486</v>
+        <v>-0.2931</v>
       </c>
       <c r="L44" s="34" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="M44" s="38" t="inlineStr">
         <is>
-          <t>5해 연16.0% · 변동성 24.6% (위험대비 0.54) · 최대낙폭 -25% · 가장 나쁜 창 연16.0%</t>
+          <t>5해 연25.6% · 변동성 29.2% (위험대비 0.78) · 최대낙폭 -29% · 가장 나쁜 창 연21.7%</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>일라이 릴리</t>
+          <t>암젠</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="F45" s="28" t="inlineStr">
         <is>
-          <t>1,424조원</t>
+          <t>289조원</t>
         </is>
       </c>
       <c r="G45" s="30" t="inlineStr">
@@ -4974,13 +4974,13 @@
         </is>
       </c>
       <c r="I45" s="29" t="n">
-        <v>0.3799</v>
+        <v>0.2011</v>
       </c>
       <c r="J45" s="29" t="n">
-        <v>0.3256</v>
+        <v>0.2618</v>
       </c>
       <c r="K45" s="31" t="n">
-        <v>-0.3448</v>
+        <v>-0.2882</v>
       </c>
       <c r="L45" s="28" t="inlineStr">
         <is>
@@ -4989,7 +4989,7 @@
       </c>
       <c r="M45" s="32" t="inlineStr">
         <is>
-          <t>5해 연38.0% · 변동성 32.6% (위험대비 1.08) · 최대낙폭 -34% · 가장 나쁜 창 연25.1%</t>
+          <t>5해 연20.1% · 변동성 26.2% (위험대비 0.66) · 최대낙폭 -29% · 가장 나쁜 창 연19.6%</t>
         </is>
       </c>
     </row>
@@ -5006,12 +5006,12 @@
       </c>
       <c r="C46" s="33" t="inlineStr">
         <is>
-          <t>버크셔 해서웨이 B</t>
+          <t>캐터필러</t>
         </is>
       </c>
       <c r="D46" s="33" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>산업재</t>
         </is>
       </c>
       <c r="E46" s="33" t="inlineStr">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="F46" s="34" t="inlineStr">
         <is>
-          <t>1,511조원</t>
+          <t>515조원</t>
         </is>
       </c>
       <c r="G46" s="35" t="inlineStr">
@@ -5035,13 +5035,13 @@
         </is>
       </c>
       <c r="I46" s="36" t="n">
-        <v>0.1287</v>
+        <v>0.3844</v>
       </c>
       <c r="J46" s="36" t="n">
-        <v>0.1716</v>
+        <v>0.3214</v>
       </c>
       <c r="K46" s="37" t="n">
-        <v>-0.2658</v>
+        <v>-0.3597</v>
       </c>
       <c r="L46" s="34" t="inlineStr">
         <is>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="M46" s="38" t="inlineStr">
         <is>
-          <t>5해 연12.9% · 변동성 17.2% (위험대비 0.59) · 최대낙폭 -27% · 가장 나쁜 창 연3.5%</t>
+          <t>5해 연38.4% · 변동성 32.1% (위험대비 1.11) · 최대낙폭 -36% · 가장 나쁜 창 연38.4%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>골드만삭스</t>
+          <t>일라이 릴리</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>헬스케어</t>
         </is>
       </c>
       <c r="E47" s="14" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="F47" s="28" t="inlineStr">
         <is>
-          <t>380조원</t>
+          <t>1,424조원</t>
         </is>
       </c>
       <c r="G47" s="30" t="inlineStr">
@@ -5096,13 +5096,13 @@
         </is>
       </c>
       <c r="I47" s="29" t="n">
-        <v>0.2129</v>
+        <v>0.4287</v>
       </c>
       <c r="J47" s="29" t="n">
-        <v>0.2868</v>
+        <v>0.3434</v>
       </c>
       <c r="K47" s="31" t="n">
-        <v>-0.3284</v>
+        <v>-0.357</v>
       </c>
       <c r="L47" s="28" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M47" s="32" t="inlineStr">
         <is>
-          <t>5해 연21.3% · 변동성 28.7% (위험대비 0.64) · 최대낙폭 -33% · 가장 나쁜 창 연20.9%</t>
+          <t>5해 연42.9% · 변동성 34.3% (위험대비 1.17) · 최대낙폭 -36% · 가장 나쁜 창 연26.9%</t>
         </is>
       </c>
     </row>
@@ -5128,12 +5128,12 @@
       </c>
       <c r="C48" s="33" t="inlineStr">
         <is>
-          <t>팔로알토네트웍스</t>
+          <t>월마트</t>
         </is>
       </c>
       <c r="D48" s="33" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>필수소비재</t>
         </is>
       </c>
       <c r="E48" s="33" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>412조원</t>
+          <t>1,176조원</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -5153,17 +5153,17 @@
       </c>
       <c r="H48" s="35" t="inlineStr">
         <is>
-          <t>3해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I48" s="36" t="n">
-        <v>0.4321</v>
+        <v>0.2255</v>
       </c>
       <c r="J48" s="36" t="n">
-        <v>0.4356</v>
+        <v>0.245</v>
       </c>
       <c r="K48" s="37" t="n">
-        <v>-0.3601</v>
+        <v>-0.2999</v>
       </c>
       <c r="L48" s="34" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="M48" s="38" t="inlineStr">
         <is>
-          <t>3해 연43.2% · 변동성 43.6% (위험대비 0.93) · 최대낙폭 -36% · 가장 나쁜 창 연43.2%</t>
+          <t>5해 연22.6% · 변동성 24.5% (위험대비 0.81) · 최대낙폭 -30% · 가장 나쁜 창 연3.7%</t>
         </is>
       </c>
     </row>
@@ -5189,12 +5189,12 @@
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>버텍스</t>
+          <t>시스코</t>
         </is>
       </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>헬스케어</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E49" s="14" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="F49" s="28" t="inlineStr">
         <is>
-          <t>178조원</t>
+          <t>598조원</t>
         </is>
       </c>
       <c r="G49" s="30" t="inlineStr">
@@ -5218,13 +5218,13 @@
         </is>
       </c>
       <c r="I49" s="29" t="n">
-        <v>0.2184</v>
+        <v>0.2087</v>
       </c>
       <c r="J49" s="29" t="n">
-        <v>0.2925</v>
+        <v>0.2738</v>
       </c>
       <c r="K49" s="31" t="n">
-        <v>-0.2907</v>
+        <v>-0.2894</v>
       </c>
       <c r="L49" s="28" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="M49" s="32" t="inlineStr">
         <is>
-          <t>5해 연21.8% · 변동성 29.2% (위험대비 0.65) · 최대낙폭 -29% · 가장 나쁜 창 연13.5%</t>
+          <t>5해 연20.9% · 변동성 27.4% (위험대비 0.66) · 최대낙폭 -29% · 가장 나쁜 창 연20.9%</t>
         </is>
       </c>
     </row>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="C50" s="33" t="inlineStr">
         <is>
-          <t>JP모간체이스</t>
+          <t>비자</t>
         </is>
       </c>
       <c r="D50" s="33" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="F50" s="34" t="inlineStr">
         <is>
-          <t>1,287조원</t>
+          <t>958조원</t>
         </is>
       </c>
       <c r="G50" s="35" t="inlineStr">
@@ -5279,13 +5279,13 @@
         </is>
       </c>
       <c r="I50" s="36" t="n">
-        <v>0.2019</v>
+        <v>0.1509</v>
       </c>
       <c r="J50" s="36" t="n">
-        <v>0.2436</v>
+        <v>0.2408</v>
       </c>
       <c r="K50" s="37" t="n">
-        <v>-0.3877</v>
+        <v>-0.1856</v>
       </c>
       <c r="L50" s="34" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="M50" s="38" t="inlineStr">
         <is>
-          <t>5해 연20.2% · 변동성 24.4% (위험대비 0.71) · 최대낙폭 -39% · 가장 나쁜 창 연14.3%</t>
+          <t>5해 연15.1% · 변동성 24.1% (위험대비 0.51) · 최대낙폭 -19% · 가장 나쁜 창 연8.0%</t>
         </is>
       </c>
     </row>
@@ -5311,12 +5311,12 @@
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>애플</t>
+          <t>모간스탠리</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="E51" s="14" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="F51" s="28" t="inlineStr">
         <is>
-          <t>6,794조원</t>
+          <t>441조원</t>
         </is>
       </c>
       <c r="G51" s="30" t="inlineStr">
@@ -5340,13 +5340,13 @@
         </is>
       </c>
       <c r="I51" s="29" t="n">
-        <v>0.1818</v>
+        <v>0.2214</v>
       </c>
       <c r="J51" s="29" t="n">
-        <v>0.2794</v>
+        <v>0.2919</v>
       </c>
       <c r="K51" s="31" t="n">
-        <v>-0.3336</v>
+        <v>-0.2937</v>
       </c>
       <c r="L51" s="28" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
       </c>
       <c r="M51" s="32" t="inlineStr">
         <is>
-          <t>5해 연18.2% · 변동성 27.9% (위험대비 0.55) · 최대낙폭 -33% · 가장 나쁜 창 연18.2%</t>
+          <t>5해 연22.1% · 변동성 29.2% (위험대비 0.66) · 최대낙폭 -29% · 가장 나쁜 창 연22.1%</t>
         </is>
       </c>
     </row>
@@ -5372,12 +5372,12 @@
       </c>
       <c r="C52" s="33" t="inlineStr">
         <is>
-          <t>비자</t>
+          <t>팔로알토네트웍스</t>
         </is>
       </c>
       <c r="D52" s="33" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E52" s="33" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="F52" s="34" t="inlineStr">
         <is>
-          <t>958조원</t>
+          <t>412조원</t>
         </is>
       </c>
       <c r="G52" s="35" t="inlineStr">
@@ -5397,17 +5397,17 @@
       </c>
       <c r="H52" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I52" s="36" t="n">
-        <v>0.1116</v>
+        <v>0.453</v>
       </c>
       <c r="J52" s="36" t="n">
-        <v>0.2287</v>
+        <v>0.4484</v>
       </c>
       <c r="K52" s="37" t="n">
-        <v>-0.2414</v>
+        <v>-0.3606</v>
       </c>
       <c r="L52" s="34" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
       </c>
       <c r="M52" s="38" t="inlineStr">
         <is>
-          <t>5해 연11.2% · 변동성 22.9% (위험대비 0.37) · 최대낙폭 -24% · 가장 나쁜 창 연7.2%</t>
+          <t>3해 연45.3% · 변동성 44.8% (위험대비 0.95) · 최대낙폭 -36% · 가장 나쁜 창 연45.3%</t>
         </is>
       </c>
     </row>
@@ -5433,12 +5433,12 @@
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>이튼</t>
+          <t>애플</t>
         </is>
       </c>
       <c r="D53" s="14" t="inlineStr">
         <is>
-          <t>산업재</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="E53" s="14" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="F53" s="28" t="inlineStr">
         <is>
-          <t>228조원</t>
+          <t>6,794조원</t>
         </is>
       </c>
       <c r="G53" s="30" t="inlineStr">
@@ -5462,13 +5462,13 @@
         </is>
       </c>
       <c r="I53" s="29" t="n">
-        <v>0.2329</v>
+        <v>0.2236</v>
       </c>
       <c r="J53" s="29" t="n">
-        <v>0.3206</v>
+        <v>0.291</v>
       </c>
       <c r="K53" s="31" t="n">
-        <v>-0.3446</v>
+        <v>-0.3245</v>
       </c>
       <c r="L53" s="28" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="M53" s="32" t="inlineStr">
         <is>
-          <t>5해 연23.3% · 변동성 32.1% (위험대비 0.64) · 최대낙폭 -34% · 가장 나쁜 창 연18.2%</t>
+          <t>5해 연22.4% · 변동성 29.1% (위험대비 0.67) · 최대낙폭 -32% · 가장 나쁜 창 연22.4%</t>
         </is>
       </c>
     </row>
@@ -5494,12 +5494,12 @@
       </c>
       <c r="C54" s="33" t="inlineStr">
         <is>
-          <t>모간스탠리</t>
+          <t>버텍스</t>
         </is>
       </c>
       <c r="D54" s="33" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>헬스케어</t>
         </is>
       </c>
       <c r="E54" s="33" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>441조원</t>
+          <t>178조원</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -5523,13 +5523,13 @@
         </is>
       </c>
       <c r="I54" s="36" t="n">
-        <v>0.1797</v>
+        <v>0.2614</v>
       </c>
       <c r="J54" s="36" t="n">
-        <v>0.2889</v>
+        <v>0.3027</v>
       </c>
       <c r="K54" s="37" t="n">
-        <v>-0.3238</v>
+        <v>-0.3211</v>
       </c>
       <c r="L54" s="34" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="M54" s="38" t="inlineStr">
         <is>
-          <t>5해 연18.0% · 변동성 28.9% (위험대비 0.52) · 최대낙폭 -32% · 가장 나쁜 창 연18.0%</t>
+          <t>5해 연26.1% · 변동성 30.3% (위험대비 0.77) · 최대낙폭 -32% · 가장 나쁜 창 연15.2%</t>
         </is>
       </c>
     </row>
@@ -5555,12 +5555,12 @@
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>프로그레시브</t>
+          <t>유니온퍼시픽</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
         <is>
-          <t>금융</t>
+          <t>산업재</t>
         </is>
       </c>
       <c r="E55" s="14" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="F55" s="28" t="inlineStr">
         <is>
-          <t>172조원</t>
+          <t>230조원</t>
         </is>
       </c>
       <c r="G55" s="30" t="inlineStr">
@@ -5584,13 +5584,13 @@
         </is>
       </c>
       <c r="I55" s="29" t="n">
-        <v>0.2061</v>
+        <v>0.1232</v>
       </c>
       <c r="J55" s="29" t="n">
-        <v>0.2553</v>
+        <v>0.2429</v>
       </c>
       <c r="K55" s="31" t="n">
-        <v>-0.3035</v>
+        <v>-0.2736</v>
       </c>
       <c r="L55" s="28" t="inlineStr">
         <is>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="M55" s="32" t="inlineStr">
         <is>
-          <t>5해 연20.6% · 변동성 25.5% (위험대비 0.70) · 최대낙폭 -30% · 가장 나쁜 창 연-6.7%</t>
+          <t>5해 연12.3% · 변동성 24.3% (위험대비 0.39) · 최대낙폭 -27% · 가장 나쁜 창 연12.3%</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="C56" s="33" t="inlineStr">
         <is>
-          <t>록히드마틴</t>
+          <t>GE에어로스페이스</t>
         </is>
       </c>
       <c r="D56" s="33" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="F56" s="34" t="inlineStr">
         <is>
-          <t>170조원</t>
+          <t>452조원</t>
         </is>
       </c>
       <c r="G56" s="35" t="inlineStr">
@@ -5645,13 +5645,13 @@
         </is>
       </c>
       <c r="I56" s="36" t="n">
-        <v>0.1195</v>
+        <v>0.4306</v>
       </c>
       <c r="J56" s="36" t="n">
-        <v>0.2409</v>
+        <v>0.3175</v>
       </c>
       <c r="K56" s="37" t="n">
-        <v>-0.3179</v>
+        <v>-0.383</v>
       </c>
       <c r="L56" s="34" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="M56" s="38" t="inlineStr">
         <is>
-          <t>5해 연11.9% · 변동성 24.1% (위험대비 0.38) · 최대낙폭 -32% · 가장 나쁜 창 연11.1%</t>
+          <t>5해 연43.1% · 변동성 31.8% (위험대비 1.27) · 최대낙폭 -38% · 가장 나쁜 창 연9.8%</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
       </c>
       <c r="C83" s="14" t="inlineStr">
         <is>
-          <t>SOL 미국S&amp;P500</t>
+          <t>ACE 미국나스닥100미국채혼합50액티브</t>
         </is>
       </c>
       <c r="D83" s="14" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>한국투자신탁운용</t>
         </is>
       </c>
       <c r="F83" s="28" t="inlineStr">
         <is>
-          <t>2,987억원</t>
+          <t>9,455억원</t>
         </is>
       </c>
       <c r="G83" s="30" t="inlineStr">
@@ -7266,20 +7266,20 @@
         </is>
       </c>
       <c r="I83" s="29" t="n">
-        <v>0.2146</v>
+        <v>0.1323</v>
       </c>
       <c r="J83" s="29" t="n">
-        <v>0.1556</v>
+        <v>0.09820000000000001</v>
       </c>
       <c r="K83" s="31" t="n">
-        <v>-0.1924</v>
+        <v>-0.1486</v>
       </c>
       <c r="L83" s="39" t="n">
-        <v>4.7e-05</v>
+        <v>0.0015</v>
       </c>
       <c r="M83" s="32" t="inlineStr">
         <is>
-          <t>3해 연21.5% · 변동성 15.6% (위험대비 1.20) · 최대낙폭 -19% · 보수 0.00% · 가장 나쁜 창 연16.8%</t>
+          <t>3해 연13.2% · 변동성 9.8% (위험대비 1.06) · 최대낙폭 -15% · 보수 0.15% · 가장 나쁜 창 연11.6%</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="C84" s="33" t="inlineStr">
         <is>
-          <t>ACE 미국배당다우존스</t>
+          <t>SOL 미국S&amp;P500</t>
         </is>
       </c>
       <c r="D84" s="33" t="inlineStr">
@@ -7306,12 +7306,12 @@
       </c>
       <c r="E84" s="33" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>9,703억원</t>
+          <t>2,987억원</t>
         </is>
       </c>
       <c r="G84" s="35" t="inlineStr">
@@ -7325,20 +7325,20 @@
         </is>
       </c>
       <c r="I84" s="36" t="n">
-        <v>0.1576</v>
+        <v>0.2146</v>
       </c>
       <c r="J84" s="36" t="n">
-        <v>0.1409</v>
+        <v>0.1556</v>
       </c>
       <c r="K84" s="37" t="n">
-        <v>-0.1321</v>
+        <v>-0.1924</v>
       </c>
       <c r="L84" s="40" t="n">
-        <v>0.0001</v>
+        <v>4.7e-05</v>
       </c>
       <c r="M84" s="38" t="inlineStr">
         <is>
-          <t>3해 연15.8% · 변동성 14.1% (위험대비 0.92) · 최대낙폭 -13% · 보수 0.01% · 가장 나쁜 창 연15.8%</t>
+          <t>3해 연21.5% · 변동성 15.6% (위험대비 1.20) · 최대낙폭 -19% · 보수 0.00% · 가장 나쁜 창 연16.8%</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>ACE 미국나스닥100미국채혼합50액티브</t>
+          <t>SOL 미국TOP5채권혼합50</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F85" s="28" t="inlineStr">
         <is>
-          <t>9,455억원</t>
+          <t>1,248억원</t>
         </is>
       </c>
       <c r="G85" s="30" t="inlineStr">
@@ -7384,20 +7384,20 @@
         </is>
       </c>
       <c r="I85" s="29" t="n">
-        <v>0.1323</v>
+        <v>0.1197</v>
       </c>
       <c r="J85" s="29" t="n">
-        <v>0.09820000000000001</v>
+        <v>0.098</v>
       </c>
       <c r="K85" s="31" t="n">
-        <v>-0.1486</v>
+        <v>-0.113</v>
       </c>
       <c r="L85" s="39" t="n">
-        <v>0.0015</v>
+        <v>0.0025</v>
       </c>
       <c r="M85" s="32" t="inlineStr">
         <is>
-          <t>3해 연13.2% · 변동성 9.8% (위험대비 1.06) · 최대낙폭 -15% · 보수 0.15% · 가장 나쁜 창 연11.6%</t>
+          <t>3해 연12.0% · 변동성 9.8% (위험대비 0.93) · 최대낙폭 -11% · 보수 0.25% · 가장 나쁜 창 연11.9%</t>
         </is>
       </c>
     </row>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="C86" s="33" t="inlineStr">
         <is>
-          <t>SOL 미국TOP5채권혼합50</t>
+          <t>ACE 미국배당다우존스</t>
         </is>
       </c>
       <c r="D86" s="33" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="E86" s="33" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
-          <t>1,248억원</t>
+          <t>9,703억원</t>
         </is>
       </c>
       <c r="G86" s="35" t="inlineStr">
@@ -7443,20 +7443,20 @@
         </is>
       </c>
       <c r="I86" s="36" t="n">
-        <v>0.1197</v>
+        <v>0.1576</v>
       </c>
       <c r="J86" s="36" t="n">
-        <v>0.098</v>
+        <v>0.1409</v>
       </c>
       <c r="K86" s="37" t="n">
-        <v>-0.113</v>
+        <v>-0.1321</v>
       </c>
       <c r="L86" s="40" t="n">
-        <v>0.0025</v>
+        <v>0.0001</v>
       </c>
       <c r="M86" s="38" t="inlineStr">
         <is>
-          <t>3해 연12.0% · 변동성 9.8% (위험대비 0.93) · 최대낙폭 -11% · 보수 0.25% · 가장 나쁜 창 연11.9%</t>
+          <t>3해 연15.8% · 변동성 14.1% (위험대비 0.92) · 최대낙폭 -13% · 보수 0.01% · 가장 나쁜 창 연15.8%</t>
         </is>
       </c>
     </row>
@@ -7473,22 +7473,22 @@
       </c>
       <c r="C87" s="14" t="inlineStr">
         <is>
-          <t>KODEX 미국배당커버드콜액티브</t>
+          <t>ACE 엔비디아채권혼합</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
         <is>
-          <t>커버드콜</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="F87" s="28" t="inlineStr">
         <is>
-          <t>2조원</t>
+          <t>2,464억원</t>
         </is>
       </c>
       <c r="G87" s="30" t="inlineStr">
@@ -7502,20 +7502,20 @@
         </is>
       </c>
       <c r="I87" s="29" t="n">
-        <v>0.1642</v>
+        <v>0.222</v>
       </c>
       <c r="J87" s="29" t="n">
-        <v>0.1268</v>
+        <v>0.1681</v>
       </c>
       <c r="K87" s="31" t="n">
-        <v>-0.137</v>
+        <v>-0.139</v>
       </c>
       <c r="L87" s="39" t="n">
-        <v>0.0019</v>
+        <v>0.0007000000000000001</v>
       </c>
       <c r="M87" s="32" t="inlineStr">
         <is>
-          <t>3해 연16.4% · 변동성 12.7% (위험대비 1.07) · 최대낙폭 -14% · 보수 0.19% · 가장 나쁜 창 연14.1%</t>
+          <t>3해 연22.2% · 변동성 16.8% (위험대비 1.15) · 최대낙폭 -14% · 보수 0.07% · 가장 나쁜 창 연9.9%</t>
         </is>
       </c>
     </row>
@@ -7532,22 +7532,22 @@
       </c>
       <c r="C88" s="33" t="inlineStr">
         <is>
-          <t>ACE 엔비디아채권혼합</t>
+          <t>KODEX 미국배당커버드콜액티브</t>
         </is>
       </c>
       <c r="D88" s="33" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>커버드콜</t>
         </is>
       </c>
       <c r="E88" s="33" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>삼성자산운용(ETF)</t>
         </is>
       </c>
       <c r="F88" s="34" t="inlineStr">
         <is>
-          <t>2,464억원</t>
+          <t>2조원</t>
         </is>
       </c>
       <c r="G88" s="35" t="inlineStr">
@@ -7561,20 +7561,20 @@
         </is>
       </c>
       <c r="I88" s="36" t="n">
-        <v>0.222</v>
+        <v>0.1642</v>
       </c>
       <c r="J88" s="36" t="n">
-        <v>0.1681</v>
+        <v>0.1268</v>
       </c>
       <c r="K88" s="37" t="n">
-        <v>-0.139</v>
+        <v>-0.137</v>
       </c>
       <c r="L88" s="40" t="n">
-        <v>0.0007000000000000001</v>
+        <v>0.0019</v>
       </c>
       <c r="M88" s="38" t="inlineStr">
         <is>
-          <t>3해 연22.2% · 변동성 16.8% (위험대비 1.15) · 최대낙폭 -14% · 보수 0.07% · 가장 나쁜 창 연9.9%</t>
+          <t>3해 연16.4% · 변동성 12.7% (위험대비 1.07) · 최대낙폭 -14% · 보수 0.19% · 가장 나쁜 창 연14.1%</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7650,7 @@
       </c>
       <c r="C90" s="33" t="inlineStr">
         <is>
-          <t>ACE 글로벌인컴TOP10</t>
+          <t>TIGER 일본니케이225</t>
         </is>
       </c>
       <c r="D90" s="33" t="inlineStr">
@@ -7660,12 +7660,12 @@
       </c>
       <c r="E90" s="33" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F90" s="34" t="inlineStr">
         <is>
-          <t>854억원</t>
+          <t>3,967억원</t>
         </is>
       </c>
       <c r="G90" s="35" t="inlineStr">
@@ -7675,24 +7675,24 @@
       </c>
       <c r="H90" s="35" t="inlineStr">
         <is>
-          <t>3해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I90" s="36" t="n">
-        <v>0.0969</v>
+        <v>0.1541</v>
       </c>
       <c r="J90" s="36" t="n">
-        <v>0.09880000000000001</v>
+        <v>0.2107</v>
       </c>
       <c r="K90" s="37" t="n">
-        <v>-0.141</v>
+        <v>-0.2394</v>
       </c>
       <c r="L90" s="40" t="n">
-        <v>0.0024</v>
+        <v>0.0035</v>
       </c>
       <c r="M90" s="38" t="inlineStr">
         <is>
-          <t>3해 연9.7% · 변동성 9.9% (위험대비 0.70) · 최대낙폭 -14% · 보수 0.24% · 가장 나쁜 창 연6.0%</t>
+          <t>5해 연15.4% · 변동성 21.1% (위험대비 0.60) · 최대낙폭 -24% · 보수 0.35% · 가장 나쁜 창 연15.4%</t>
         </is>
       </c>
     </row>
@@ -7709,7 +7709,7 @@
       </c>
       <c r="C91" s="14" t="inlineStr">
         <is>
-          <t>KODEX MSCI선진국</t>
+          <t>TIGER 테슬라채권혼합Fn</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F91" s="28" t="inlineStr">
         <is>
-          <t>4,989억원</t>
+          <t>4,393억원</t>
         </is>
       </c>
       <c r="G91" s="30" t="inlineStr">
@@ -7734,24 +7734,24 @@
       </c>
       <c r="H91" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I91" s="29" t="n">
-        <v>0.1505</v>
+        <v>0.0867</v>
       </c>
       <c r="J91" s="29" t="n">
-        <v>0.1519</v>
+        <v>0.2019</v>
       </c>
       <c r="K91" s="31" t="n">
-        <v>-0.1646</v>
+        <v>-0.2107</v>
       </c>
       <c r="L91" s="39" t="n">
-        <v>0.003</v>
+        <v>0.0025</v>
       </c>
       <c r="M91" s="32" t="inlineStr">
         <is>
-          <t>5해 연15.1% · 변동성 15.2% (위험대비 0.81) · 최대낙폭 -16% · 보수 0.30% · 가장 나쁜 창 연15.1%</t>
+          <t>3해 연8.7% · 변동성 20.2% (위험대비 0.29) · 최대낙폭 -21% · 보수 0.25% · 가장 나쁜 창 연1.2%</t>
         </is>
       </c>
     </row>
@@ -7768,7 +7768,7 @@
       </c>
       <c r="C92" s="33" t="inlineStr">
         <is>
-          <t>KODEX 미국나스닥AI테크액티브</t>
+          <t>ACE 미국30년국채액티브(H)</t>
         </is>
       </c>
       <c r="D92" s="33" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="E92" s="33" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>한국투자신탁운용</t>
         </is>
       </c>
       <c r="F92" s="34" t="inlineStr">
         <is>
-          <t>1,282억원</t>
+          <t>1조원</t>
         </is>
       </c>
       <c r="G92" s="35" t="inlineStr">
@@ -7797,20 +7797,20 @@
         </is>
       </c>
       <c r="I92" s="36" t="n">
-        <v>0.4652000000000001</v>
+        <v>-0.0398</v>
       </c>
       <c r="J92" s="36" t="n">
-        <v>0.304</v>
+        <v>0.137</v>
       </c>
       <c r="K92" s="37" t="n">
-        <v>-0.3126</v>
+        <v>-0.1731</v>
       </c>
       <c r="L92" s="40" t="n">
-        <v>0.005</v>
+        <v>0.0005</v>
       </c>
       <c r="M92" s="38" t="inlineStr">
         <is>
-          <t>3해 연46.5% · 변동성 30.4% (위험대비 1.44) · 최대낙폭 -31% · 보수 0.50% · 가장 나쁜 창 연46.5%</t>
+          <t>3해 연-4.0% · 변동성 13.7% (위험대비 -0.50) · 최대낙폭 -17% · 보수 0.05% · 가장 나쁜 창 연-4.0%</t>
         </is>
       </c>
     </row>
@@ -7827,49 +7827,49 @@
       </c>
       <c r="C93" s="14" t="inlineStr">
         <is>
-          <t>ACE 미국달러SOFR금리(합성)</t>
+          <t>RISE 미국테크100데일리고정커버드콜</t>
         </is>
       </c>
       <c r="D93" s="14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>커버드콜</t>
         </is>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>KB자산운용</t>
         </is>
       </c>
       <c r="F93" s="28" t="inlineStr">
         <is>
-          <t>3,365억원</t>
+          <t>5,772억원</t>
         </is>
       </c>
       <c r="G93" s="30" t="inlineStr">
         <is>
-          <t>다년 실측</t>
+          <t>1해 실측</t>
         </is>
       </c>
       <c r="H93" s="30" t="inlineStr">
         <is>
-          <t>3해</t>
+          <t>1해</t>
         </is>
       </c>
       <c r="I93" s="29" t="n">
-        <v>0.0626</v>
+        <v>0.2319</v>
       </c>
       <c r="J93" s="29" t="n">
-        <v>0.08869999999999999</v>
+        <v>0.1842</v>
       </c>
       <c r="K93" s="31" t="n">
-        <v>-0.1358</v>
+        <v>-0.1436</v>
       </c>
       <c r="L93" s="39" t="n">
-        <v>0.0005</v>
+        <v>0.0025</v>
       </c>
       <c r="M93" s="32" t="inlineStr">
         <is>
-          <t>3해 연6.3% · 변동성 8.9% (위험대비 0.39) · 최대낙폭 -14% · 보수 0.05% · 가장 나쁜 창 연3.1%</t>
+          <t>1해 연23.2% · 변동성 18.4% (위험대비 1.11) · 최대낙폭 -14% · 보수 0.25%</t>
         </is>
       </c>
     </row>
@@ -7886,7 +7886,7 @@
       </c>
       <c r="C94" s="33" t="inlineStr">
         <is>
-          <t>KODEX 200미국채혼합50</t>
+          <t>TIME 글로벌우주테크&amp;방산액티브</t>
         </is>
       </c>
       <c r="D94" s="33" t="inlineStr">
@@ -7896,39 +7896,39 @@
       </c>
       <c r="E94" s="33" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>타임폴리오자산운용</t>
         </is>
       </c>
       <c r="F94" s="34" t="inlineStr">
         <is>
-          <t>2조원</t>
+          <t>2,248억원</t>
         </is>
       </c>
       <c r="G94" s="35" t="inlineStr">
         <is>
-          <t>다년 실측</t>
+          <t>1해 실측</t>
         </is>
       </c>
       <c r="H94" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>1해</t>
         </is>
       </c>
       <c r="I94" s="36" t="n">
-        <v>0.09119999999999999</v>
+        <v>0.0286</v>
       </c>
       <c r="J94" s="36" t="n">
-        <v>0.1365</v>
+        <v>0.2643</v>
       </c>
       <c r="K94" s="37" t="n">
-        <v>-0.2525</v>
+        <v>-0.2932</v>
       </c>
       <c r="L94" s="40" t="n">
-        <v>0.0035</v>
+        <v>0.008</v>
       </c>
       <c r="M94" s="38" t="inlineStr">
         <is>
-          <t>5해 연9.1% · 변동성 13.7% (위험대비 0.46) · 최대낙폭 -25% · 보수 0.35% · 가장 나쁜 창 연9.1%</t>
+          <t>1해 연2.9% · 변동성 26.4% (위험대비 0.00) · 최대낙폭 -29% · 보수 0.80%</t>
         </is>
       </c>
     </row>
@@ -7945,22 +7945,22 @@
       </c>
       <c r="C95" s="14" t="inlineStr">
         <is>
-          <t>TIGER 일본니케이225</t>
+          <t>TIGER 미국투자등급회사채액티브(H)</t>
         </is>
       </c>
       <c r="D95" s="14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>채권형</t>
         </is>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F95" s="28" t="inlineStr">
         <is>
-          <t>3,967억원</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G95" s="30" t="inlineStr">
@@ -7970,24 +7970,26 @@
       </c>
       <c r="H95" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I95" s="29" t="n">
-        <v>0.1541</v>
+        <v>0.0194</v>
       </c>
       <c r="J95" s="29" t="n">
-        <v>0.2107</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="K95" s="31" t="n">
-        <v>-0.2394</v>
-      </c>
-      <c r="L95" s="39" t="n">
-        <v>0.0035</v>
+        <v>-0.0713</v>
+      </c>
+      <c r="L95" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M95" s="32" t="inlineStr">
         <is>
-          <t>5해 연15.4% · 변동성 21.1% (위험대비 0.60) · 최대낙폭 -24% · 보수 0.35% · 가장 나쁜 창 연15.4%</t>
+          <t>3해 연1.9% · 변동성 7.7% (위험대비 -0.11) · 최대낙폭 -7% · 가장 나쁜 창 연-2.0%</t>
         </is>
       </c>
     </row>
@@ -8004,22 +8006,22 @@
       </c>
       <c r="C96" s="33" t="inlineStr">
         <is>
-          <t>TIGER 테슬라채권혼합Fn</t>
+          <t>TIGER 미국필라델피아반도체나스닥</t>
         </is>
       </c>
       <c r="D96" s="33" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>반도체&amp;A.I.</t>
         </is>
       </c>
       <c r="E96" s="33" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F96" s="34" t="inlineStr">
         <is>
-          <t>4,393억원</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G96" s="35" t="inlineStr">
@@ -8029,24 +8031,26 @@
       </c>
       <c r="H96" s="35" t="inlineStr">
         <is>
-          <t>3해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I96" s="36" t="n">
-        <v>0.0867</v>
+        <v>0.329</v>
       </c>
       <c r="J96" s="36" t="n">
-        <v>0.2019</v>
+        <v>0.3539</v>
       </c>
       <c r="K96" s="37" t="n">
-        <v>-0.2107</v>
-      </c>
-      <c r="L96" s="40" t="n">
-        <v>0.0025</v>
+        <v>-0.3968</v>
+      </c>
+      <c r="L96" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M96" s="38" t="inlineStr">
         <is>
-          <t>3해 연8.7% · 변동성 20.2% (위험대비 0.29) · 최대낙폭 -21% · 보수 0.25% · 가장 나쁜 창 연1.2%</t>
+          <t>5해 연32.9% · 변동성 35.4% (위험대비 0.85) · 최대낙폭 -40% · 가장 나쁜 창 연32.9%</t>
         </is>
       </c>
     </row>
@@ -8063,22 +8067,22 @@
       </c>
       <c r="C97" s="14" t="inlineStr">
         <is>
-          <t>KODEX 인도Nifty50</t>
+          <t>RISE 글로벌원자력</t>
         </is>
       </c>
       <c r="D97" s="14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>원자력&amp;전력인프라</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F97" s="28" t="inlineStr">
         <is>
-          <t>3,297억원</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G97" s="30" t="inlineStr">
@@ -8092,20 +8096,22 @@
         </is>
       </c>
       <c r="I97" s="29" t="n">
-        <v>0.0234</v>
+        <v>0.4532</v>
       </c>
       <c r="J97" s="29" t="n">
-        <v>0.1516</v>
+        <v>0.3917</v>
       </c>
       <c r="K97" s="31" t="n">
-        <v>-0.2475</v>
-      </c>
-      <c r="L97" s="39" t="n">
-        <v>0.0019</v>
+        <v>-0.3842</v>
+      </c>
+      <c r="L97" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M97" s="32" t="inlineStr">
         <is>
-          <t>3해 연2.3% · 변동성 15.2% (위험대비 -0.03) · 최대낙폭 -25% · 보수 0.19% · 가장 나쁜 창 연-13.3%</t>
+          <t>3해 연45.3% · 변동성 39.2% (위험대비 1.09) · 최대낙폭 -38% · 가장 나쁜 창 연11.7%</t>
         </is>
       </c>
     </row>
@@ -8122,22 +8128,22 @@
       </c>
       <c r="C98" s="33" t="inlineStr">
         <is>
-          <t>TIGER 미국테크TOP10 INDXX</t>
+          <t>TIGER 차이나반도체FACTSET</t>
         </is>
       </c>
       <c r="D98" s="33" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="E98" s="33" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F98" s="34" t="inlineStr">
         <is>
-          <t>4조원</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G98" s="35" t="inlineStr">
@@ -8147,24 +8153,26 @@
       </c>
       <c r="H98" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I98" s="36" t="n">
-        <v>0.216</v>
+        <v>0.2965</v>
       </c>
       <c r="J98" s="36" t="n">
-        <v>0.2524</v>
+        <v>0.3974</v>
       </c>
       <c r="K98" s="37" t="n">
-        <v>-0.4059</v>
-      </c>
-      <c r="L98" s="40" t="n">
-        <v>0.0049</v>
+        <v>-0.4533</v>
+      </c>
+      <c r="L98" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M98" s="38" t="inlineStr">
         <is>
-          <t>5해 연21.6% · 변동성 25.2% (위험대비 0.74) · 최대낙폭 -41% · 보수 0.49% · 가장 나쁜 창 연15.1%</t>
+          <t>3해 연29.6% · 변동성 39.7% (위험대비 0.68) · 최대낙폭 -45% · 가장 나쁜 창 연29.6%</t>
         </is>
       </c>
     </row>
@@ -8181,22 +8189,22 @@
       </c>
       <c r="C99" s="14" t="inlineStr">
         <is>
-          <t>ACE 미국30년국채액티브(H)</t>
+          <t>TIGER 차이나과창판STAR50(합성)</t>
         </is>
       </c>
       <c r="D99" s="14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F99" s="28" t="inlineStr">
         <is>
-          <t>1조원</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G99" s="30" t="inlineStr">
@@ -8210,20 +8218,22 @@
         </is>
       </c>
       <c r="I99" s="29" t="n">
-        <v>-0.0398</v>
+        <v>0.2444</v>
       </c>
       <c r="J99" s="29" t="n">
-        <v>0.137</v>
+        <v>0.3654</v>
       </c>
       <c r="K99" s="31" t="n">
-        <v>-0.1731</v>
-      </c>
-      <c r="L99" s="39" t="n">
-        <v>0.0005</v>
+        <v>-0.3919</v>
+      </c>
+      <c r="L99" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M99" s="32" t="inlineStr">
         <is>
-          <t>3해 연-4.0% · 변동성 13.7% (위험대비 -0.50) · 최대낙폭 -17% · 보수 0.05% · 가장 나쁜 창 연-4.0%</t>
+          <t>3해 연24.4% · 변동성 36.5% (위험대비 0.59) · 최대낙폭 -39% · 가장 나쁜 창 연24.4%</t>
         </is>
       </c>
     </row>
@@ -8240,22 +8250,22 @@
       </c>
       <c r="C100" s="33" t="inlineStr">
         <is>
-          <t>TIGER 미국채10년선물</t>
+          <t>ACE 중국과창판STAR50</t>
         </is>
       </c>
       <c r="D100" s="33" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>중국</t>
         </is>
       </c>
       <c r="E100" s="33" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F100" s="34" t="inlineStr">
         <is>
-          <t>2,171억원</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G100" s="35" t="inlineStr">
@@ -8265,24 +8275,26 @@
       </c>
       <c r="H100" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I100" s="36" t="n">
-        <v>0.0026</v>
+        <v>0.22</v>
       </c>
       <c r="J100" s="36" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.3696</v>
       </c>
       <c r="K100" s="37" t="n">
-        <v>-0.1589</v>
-      </c>
-      <c r="L100" s="40" t="n">
-        <v>0.0029</v>
+        <v>-0.3923</v>
+      </c>
+      <c r="L100" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M100" s="38" t="inlineStr">
         <is>
-          <t>5해 연0.3% · 변동성 9.7% (위험대비 -0.26) · 최대낙폭 -16% · 보수 0.29% · 가장 나쁜 창 연-3.9%</t>
+          <t>3해 연22.0% · 변동성 37.0% (위험대비 0.52) · 최대낙폭 -39% · 가장 나쁜 창 연22.0%</t>
         </is>
       </c>
     </row>
@@ -8299,49 +8311,51 @@
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>KODEX 미국빅테크10(H)</t>
+          <t>Invesco 원자재</t>
         </is>
       </c>
       <c r="D101" s="14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>대체</t>
         </is>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F101" s="28" t="inlineStr">
         <is>
-          <t>6,596억원</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G101" s="30" t="inlineStr">
         <is>
-          <t>다년 실측</t>
+          <t>1해 실측</t>
         </is>
       </c>
       <c r="H101" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>1해</t>
         </is>
       </c>
       <c r="I101" s="29" t="n">
-        <v>0.1677</v>
+        <v>0.5193</v>
       </c>
       <c r="J101" s="29" t="n">
-        <v>0.2981</v>
+        <v>0.2353</v>
       </c>
       <c r="K101" s="31" t="n">
-        <v>-0.4973</v>
-      </c>
-      <c r="L101" s="39" t="n">
-        <v>0.004500000000000001</v>
+        <v>-0.1529</v>
+      </c>
+      <c r="L101" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M101" s="32" t="inlineStr">
         <is>
-          <t>5해 연16.8% · 변동성 29.8% (위험대비 0.47) · 최대낙폭 -50% · 보수 0.45% · 가장 나쁜 창 연16.1%</t>
+          <t>1해 연51.9% · 변동성 23.5% (위험대비 2.09) · 최대낙폭 -15%</t>
         </is>
       </c>
     </row>
@@ -8358,49 +8372,51 @@
       </c>
       <c r="C102" s="33" t="inlineStr">
         <is>
-          <t>TIGER 미국나스닥바이오</t>
+          <t>Schwab 미국 배당주</t>
         </is>
       </c>
       <c r="D102" s="33" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>주식</t>
         </is>
       </c>
       <c r="E102" s="33" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F102" s="34" t="inlineStr">
         <is>
-          <t>1,075억원</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G102" s="35" t="inlineStr">
         <is>
-          <t>다년 실측</t>
+          <t>1해 실측</t>
         </is>
       </c>
       <c r="H102" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>1해</t>
         </is>
       </c>
       <c r="I102" s="36" t="n">
-        <v>0.1018</v>
+        <v>0.2792</v>
       </c>
       <c r="J102" s="36" t="n">
-        <v>0.2281</v>
+        <v>0.1419</v>
       </c>
       <c r="K102" s="37" t="n">
-        <v>-0.3107</v>
-      </c>
-      <c r="L102" s="40" t="n">
-        <v>0.003</v>
+        <v>-0.092</v>
+      </c>
+      <c r="L102" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M102" s="38" t="inlineStr">
         <is>
-          <t>5해 연10.2% · 변동성 22.8% (위험대비 0.32) · 최대낙폭 -31% · 보수 0.30% · 가장 나쁜 창 연10.2%</t>
+          <t>1해 연27.9% · 변동성 14.2% (위험대비 1.77) · 최대낙폭 -9%</t>
         </is>
       </c>
     </row>
@@ -8417,49 +8433,51 @@
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
-          <t>KODEX 차이나CSI300</t>
+          <t>Vanguard 미국 전체시장</t>
         </is>
       </c>
       <c r="D103" s="14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>주식</t>
         </is>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용(ETF)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F103" s="28" t="inlineStr">
         <is>
-          <t>2,495억원</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G103" s="30" t="inlineStr">
         <is>
-          <t>다년 실측</t>
+          <t>1해 실측</t>
         </is>
       </c>
       <c r="H103" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>1해</t>
         </is>
       </c>
       <c r="I103" s="29" t="n">
-        <v>0.0269</v>
+        <v>0.1758</v>
       </c>
       <c r="J103" s="29" t="n">
-        <v>0.1868</v>
+        <v>0.1455</v>
       </c>
       <c r="K103" s="31" t="n">
-        <v>-0.3717</v>
-      </c>
-      <c r="L103" s="39" t="n">
-        <v>0.0012</v>
+        <v>-0.1283</v>
+      </c>
+      <c r="L103" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M103" s="32" t="inlineStr">
         <is>
-          <t>5해 연2.7% · 변동성 18.7% (위험대비 -0.01) · 최대낙폭 -37% · 보수 0.12% · 가장 나쁜 창 연2.7%</t>
+          <t>1해 연17.6% · 변동성 14.6% (위험대비 1.02) · 최대낙폭 -13%</t>
         </is>
       </c>
     </row>
@@ -8476,49 +8494,51 @@
       </c>
       <c r="C104" s="33" t="inlineStr">
         <is>
-          <t>ACE 베트남VN30(합성)</t>
+          <t>Vanguard 선진국(미국 제외)</t>
         </is>
       </c>
       <c r="D104" s="33" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>주식</t>
         </is>
       </c>
       <c r="E104" s="33" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F104" s="34" t="inlineStr">
         <is>
-          <t>3,787억원</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G104" s="35" t="inlineStr">
         <is>
-          <t>다년 실측</t>
+          <t>1해 실측</t>
         </is>
       </c>
       <c r="H104" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>1해</t>
         </is>
       </c>
       <c r="I104" s="36" t="n">
-        <v>0.0707</v>
+        <v>0.2346</v>
       </c>
       <c r="J104" s="36" t="n">
-        <v>0.2053</v>
+        <v>0.1726</v>
       </c>
       <c r="K104" s="37" t="n">
-        <v>-0.423</v>
-      </c>
-      <c r="L104" s="40" t="n">
-        <v>0.006999999999999999</v>
+        <v>-0.1323</v>
+      </c>
+      <c r="L104" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M104" s="38" t="inlineStr">
         <is>
-          <t>5해 연7.1% · 변동성 20.5% (위험대비 0.21) · 최대낙폭 -42% · 보수 0.70% · 가장 나쁜 창 연3.8%</t>
+          <t>1해 연23.5% · 변동성 17.3% (위험대비 1.20) · 최대낙폭 -13%</t>
         </is>
       </c>
     </row>
@@ -8535,49 +8555,51 @@
       </c>
       <c r="C105" s="14" t="inlineStr">
         <is>
-          <t>TIGER 차이나CSI300</t>
+          <t>Vanguard 배당성장</t>
         </is>
       </c>
       <c r="D105" s="14" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>주식</t>
         </is>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F105" s="28" t="inlineStr">
         <is>
-          <t>1,275억원</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G105" s="30" t="inlineStr">
         <is>
-          <t>다년 실측</t>
+          <t>1해 실측</t>
         </is>
       </c>
       <c r="H105" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>1해</t>
         </is>
       </c>
       <c r="I105" s="29" t="n">
-        <v>0.0215</v>
+        <v>0.1239</v>
       </c>
       <c r="J105" s="29" t="n">
-        <v>0.1969</v>
+        <v>0.127</v>
       </c>
       <c r="K105" s="31" t="n">
-        <v>-0.3801</v>
-      </c>
-      <c r="L105" s="39" t="n">
-        <v>0.0063</v>
+        <v>-0.1365</v>
+      </c>
+      <c r="L105" s="28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M105" s="32" t="inlineStr">
         <is>
-          <t>5해 연2.1% · 변동성 19.7% (위험대비 -0.03) · 최대낙폭 -38% · 보수 0.63% · 가장 나쁜 창 연2.1%</t>
+          <t>1해 연12.4% · 변동성 12.7% (위험대비 0.75) · 최대낙폭 -14%</t>
         </is>
       </c>
     </row>
@@ -8594,49 +8616,51 @@
       </c>
       <c r="C106" s="33" t="inlineStr">
         <is>
-          <t>TIGER 미국30년국채스트립액티브(합성 H)</t>
+          <t>iShares 러셀2000 (미국 중소형)</t>
         </is>
       </c>
       <c r="D106" s="33" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>주식</t>
         </is>
       </c>
       <c r="E106" s="33" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F106" s="34" t="inlineStr">
         <is>
-          <t>3,817억원</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G106" s="35" t="inlineStr">
         <is>
-          <t>다년 실측</t>
+          <t>1해 실측</t>
         </is>
       </c>
       <c r="H106" s="35" t="inlineStr">
         <is>
-          <t>3해</t>
+          <t>1해</t>
         </is>
       </c>
       <c r="I106" s="36" t="n">
-        <v>-0.09630000000000001</v>
+        <v>0.2092</v>
       </c>
       <c r="J106" s="36" t="n">
-        <v>0.2278</v>
+        <v>0.1952</v>
       </c>
       <c r="K106" s="37" t="n">
-        <v>-0.3277</v>
-      </c>
-      <c r="L106" s="40" t="n">
-        <v>0.0015</v>
+        <v>-0.171</v>
+      </c>
+      <c r="L106" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M106" s="38" t="inlineStr">
         <is>
-          <t>3해 연-9.6% · 변동성 22.8% (위험대비 -0.55) · 최대낙폭 -33% · 보수 0.15% · 가장 나쁜 창 연-9.6%</t>
+          <t>1해 연20.9% · 변동성 19.5% (위험대비 0.93) · 최대낙폭 -17%</t>
         </is>
       </c>
     </row>
@@ -12567,11 +12591,11 @@
         </is>
       </c>
       <c r="B29" s="39" t="n">
-        <v>0.0621</v>
+        <v>0.0561</v>
       </c>
       <c r="C29" s="45" t="inlineStr">
         <is>
-          <t>해외주식 60% · 해외채권 40%</t>
+          <t>해외주식 40% · 해외채권 40% · 대체 20%</t>
         </is>
       </c>
       <c r="D29" s="46" t="n"/>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -1376,7 +1376,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-20 14:35:38 · 문서 2026-09-20 14:35 (KST)</t>
+          <t>유니버스 2026-09-20 14:47:28 · 문서 2026-09-20 14:47 (KST)</t>
         </is>
       </c>
     </row>
@@ -2392,10 +2392,10 @@
         <v>0.1747404299625906</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>0.1769</v>
+        <v>0.1834939037658289</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>-0.2640451703972575</v>
+        <v>-0.3371736857143508</v>
       </c>
     </row>
     <row r="11">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="C83" s="14" t="inlineStr">
         <is>
-          <t>ACE 미국나스닥100미국채혼합50액티브</t>
+          <t>ACE 미국배당다우존스</t>
         </is>
       </c>
       <c r="D83" s="14" t="inlineStr">
@@ -7247,12 +7247,12 @@
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
+          <t>한국투신운용(ETF)</t>
         </is>
       </c>
       <c r="F83" s="28" t="inlineStr">
         <is>
-          <t>9,455억원</t>
+          <t>9,703억원</t>
         </is>
       </c>
       <c r="G83" s="30" t="inlineStr">
@@ -7266,20 +7266,20 @@
         </is>
       </c>
       <c r="I83" s="29" t="n">
-        <v>0.1323</v>
+        <v>0.1576</v>
       </c>
       <c r="J83" s="29" t="n">
-        <v>0.09820000000000001</v>
+        <v>0.1409</v>
       </c>
       <c r="K83" s="31" t="n">
-        <v>-0.1486</v>
+        <v>-0.1321</v>
       </c>
       <c r="L83" s="39" t="n">
-        <v>0.0015</v>
+        <v>0.0001</v>
       </c>
       <c r="M83" s="32" t="inlineStr">
         <is>
-          <t>3해 연13.2% · 변동성 9.8% (위험대비 1.06) · 최대낙폭 -15% · 보수 0.15% · 가장 나쁜 창 연11.6%</t>
+          <t>3해 연15.8% · 변동성 14.1% (위험대비 0.92) · 최대낙폭 -13% · 보수 0.01% · 가장 나쁜 창 연15.8%</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="C84" s="33" t="inlineStr">
         <is>
-          <t>SOL 미국S&amp;P500</t>
+          <t>ACE 미국나스닥100미국채혼합50액티브</t>
         </is>
       </c>
       <c r="D84" s="33" t="inlineStr">
@@ -7306,12 +7306,12 @@
       </c>
       <c r="E84" s="33" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>한국투자신탁운용</t>
         </is>
       </c>
       <c r="F84" s="34" t="inlineStr">
         <is>
-          <t>2,987억원</t>
+          <t>9,455억원</t>
         </is>
       </c>
       <c r="G84" s="35" t="inlineStr">
@@ -7325,20 +7325,20 @@
         </is>
       </c>
       <c r="I84" s="36" t="n">
-        <v>0.2146</v>
+        <v>0.1323</v>
       </c>
       <c r="J84" s="36" t="n">
-        <v>0.1556</v>
+        <v>0.09820000000000001</v>
       </c>
       <c r="K84" s="37" t="n">
-        <v>-0.1924</v>
+        <v>-0.1486</v>
       </c>
       <c r="L84" s="40" t="n">
-        <v>4.7e-05</v>
+        <v>0.0015</v>
       </c>
       <c r="M84" s="38" t="inlineStr">
         <is>
-          <t>3해 연21.5% · 변동성 15.6% (위험대비 1.20) · 최대낙폭 -19% · 보수 0.00% · 가장 나쁜 창 연16.8%</t>
+          <t>3해 연13.2% · 변동성 9.8% (위험대비 1.06) · 최대낙폭 -15% · 보수 0.15% · 가장 나쁜 창 연11.6%</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>SOL 미국TOP5채권혼합50</t>
+          <t>SOL 미국S&amp;P500</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="F85" s="28" t="inlineStr">
         <is>
-          <t>1,248억원</t>
+          <t>2,987억원</t>
         </is>
       </c>
       <c r="G85" s="30" t="inlineStr">
@@ -7384,20 +7384,20 @@
         </is>
       </c>
       <c r="I85" s="29" t="n">
-        <v>0.1197</v>
+        <v>0.2146</v>
       </c>
       <c r="J85" s="29" t="n">
-        <v>0.098</v>
+        <v>0.1556</v>
       </c>
       <c r="K85" s="31" t="n">
-        <v>-0.113</v>
+        <v>-0.1924</v>
       </c>
       <c r="L85" s="39" t="n">
-        <v>0.0025</v>
+        <v>4.7e-05</v>
       </c>
       <c r="M85" s="32" t="inlineStr">
         <is>
-          <t>3해 연12.0% · 변동성 9.8% (위험대비 0.93) · 최대낙폭 -11% · 보수 0.25% · 가장 나쁜 창 연11.9%</t>
+          <t>3해 연21.5% · 변동성 15.6% (위험대비 1.20) · 최대낙폭 -19% · 보수 0.00% · 가장 나쁜 창 연16.8%</t>
         </is>
       </c>
     </row>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="C86" s="33" t="inlineStr">
         <is>
-          <t>ACE 미국배당다우존스</t>
+          <t>SOL 미국TOP5채권혼합50</t>
         </is>
       </c>
       <c r="D86" s="33" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="E86" s="33" t="inlineStr">
         <is>
-          <t>한국투신운용(ETF)</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F86" s="34" t="inlineStr">
         <is>
-          <t>9,703억원</t>
+          <t>1,248억원</t>
         </is>
       </c>
       <c r="G86" s="35" t="inlineStr">
@@ -7443,20 +7443,20 @@
         </is>
       </c>
       <c r="I86" s="36" t="n">
-        <v>0.1576</v>
+        <v>0.1197</v>
       </c>
       <c r="J86" s="36" t="n">
-        <v>0.1409</v>
+        <v>0.098</v>
       </c>
       <c r="K86" s="37" t="n">
-        <v>-0.1321</v>
+        <v>-0.113</v>
       </c>
       <c r="L86" s="40" t="n">
-        <v>0.0001</v>
+        <v>0.0025</v>
       </c>
       <c r="M86" s="38" t="inlineStr">
         <is>
-          <t>3해 연15.8% · 변동성 14.1% (위험대비 0.92) · 최대낙폭 -13% · 보수 0.01% · 가장 나쁜 창 연15.8%</t>
+          <t>3해 연12.0% · 변동성 9.8% (위험대비 0.93) · 최대낙폭 -11% · 보수 0.25% · 가장 나쁜 창 연11.9%</t>
         </is>
       </c>
     </row>
@@ -7945,12 +7945,12 @@
       </c>
       <c r="C95" s="14" t="inlineStr">
         <is>
-          <t>TIGER 미국투자등급회사채액티브(H)</t>
+          <t>SPDR 금</t>
         </is>
       </c>
       <c r="D95" s="14" t="inlineStr">
         <is>
-          <t>채권형</t>
+          <t>대체</t>
         </is>
       </c>
       <c r="E95" s="14" t="inlineStr">
@@ -7970,17 +7970,17 @@
       </c>
       <c r="H95" s="30" t="inlineStr">
         <is>
-          <t>3해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I95" s="29" t="n">
-        <v>0.0194</v>
+        <v>0.2325</v>
       </c>
       <c r="J95" s="29" t="n">
-        <v>0.07690000000000001</v>
+        <v>0.2006</v>
       </c>
       <c r="K95" s="31" t="n">
-        <v>-0.0713</v>
+        <v>-0.2618</v>
       </c>
       <c r="L95" s="28" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="M95" s="32" t="inlineStr">
         <is>
-          <t>3해 연1.9% · 변동성 7.7% (위험대비 -0.11) · 최대낙폭 -7% · 가장 나쁜 창 연-2.0%</t>
+          <t>5해 연23.2% · 변동성 20.1% (위험대비 1.02) · 최대낙폭 -26% · 가장 나쁜 창 연19.8%</t>
         </is>
       </c>
     </row>
@@ -8006,12 +8006,12 @@
       </c>
       <c r="C96" s="33" t="inlineStr">
         <is>
-          <t>TIGER 미국필라델피아반도체나스닥</t>
+          <t>Invesco 원자재</t>
         </is>
       </c>
       <c r="D96" s="33" t="inlineStr">
         <is>
-          <t>반도체&amp;A.I.</t>
+          <t>대체</t>
         </is>
       </c>
       <c r="E96" s="33" t="inlineStr">
@@ -8035,13 +8035,13 @@
         </is>
       </c>
       <c r="I96" s="36" t="n">
-        <v>0.329</v>
+        <v>0.1838</v>
       </c>
       <c r="J96" s="36" t="n">
-        <v>0.3539</v>
+        <v>0.2098</v>
       </c>
       <c r="K96" s="37" t="n">
-        <v>-0.3968</v>
+        <v>-0.25</v>
       </c>
       <c r="L96" s="34" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="M96" s="38" t="inlineStr">
         <is>
-          <t>5해 연32.9% · 변동성 35.4% (위험대비 0.85) · 최대낙폭 -40% · 가장 나쁜 창 연32.9%</t>
+          <t>5해 연18.4% · 변동성 21.0% (위험대비 0.74) · 최대낙폭 -25% · 가장 나쁜 창 연15.7%</t>
         </is>
       </c>
     </row>
@@ -8067,12 +8067,12 @@
       </c>
       <c r="C97" s="14" t="inlineStr">
         <is>
-          <t>RISE 글로벌원자력</t>
+          <t>iShares 미국채 1-3년</t>
         </is>
       </c>
       <c r="D97" s="14" t="inlineStr">
         <is>
-          <t>원자력&amp;전력인프라</t>
+          <t>채권</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
@@ -8092,17 +8092,17 @@
       </c>
       <c r="H97" s="30" t="inlineStr">
         <is>
-          <t>3해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I97" s="29" t="n">
-        <v>0.4532</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="J97" s="29" t="n">
-        <v>0.3917</v>
+        <v>0.0968</v>
       </c>
       <c r="K97" s="31" t="n">
-        <v>-0.3842</v>
+        <v>-0.1396</v>
       </c>
       <c r="L97" s="28" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
       </c>
       <c r="M97" s="32" t="inlineStr">
         <is>
-          <t>3해 연45.3% · 변동성 39.2% (위험대비 1.09) · 최대낙폭 -38% · 가장 나쁜 창 연11.7%</t>
+          <t>5해 연5.3% · 변동성 9.7% (위험대비 0.26) · 최대낙폭 -14% · 가장 나쁜 창 연2.2%</t>
         </is>
       </c>
     </row>
@@ -8128,12 +8128,12 @@
       </c>
       <c r="C98" s="33" t="inlineStr">
         <is>
-          <t>TIGER 차이나반도체FACTSET</t>
+          <t>iShares 하이일드 회사채</t>
         </is>
       </c>
       <c r="D98" s="33" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>채권</t>
         </is>
       </c>
       <c r="E98" s="33" t="inlineStr">
@@ -8153,17 +8153,17 @@
       </c>
       <c r="H98" s="35" t="inlineStr">
         <is>
-          <t>3해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I98" s="36" t="n">
-        <v>0.2965</v>
+        <v>0.0709</v>
       </c>
       <c r="J98" s="36" t="n">
-        <v>0.3974</v>
+        <v>0.1136</v>
       </c>
       <c r="K98" s="37" t="n">
-        <v>-0.4533</v>
+        <v>-0.1402</v>
       </c>
       <c r="L98" s="34" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="M98" s="38" t="inlineStr">
         <is>
-          <t>3해 연29.6% · 변동성 39.7% (위험대비 0.68) · 최대낙폭 -45% · 가장 나쁜 창 연29.6%</t>
+          <t>5해 연7.1% · 변동성 11.4% (위험대비 0.38) · 최대낙폭 -14% · 가장 나쁜 창 연3.5%</t>
         </is>
       </c>
     </row>
@@ -8189,12 +8189,12 @@
       </c>
       <c r="C99" s="14" t="inlineStr">
         <is>
-          <t>TIGER 차이나과창판STAR50(합성)</t>
+          <t>TIGER 미국투자등급회사채액티브(H)</t>
         </is>
       </c>
       <c r="D99" s="14" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>채권형</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="I99" s="29" t="n">
-        <v>0.2444</v>
+        <v>0.0194</v>
       </c>
       <c r="J99" s="29" t="n">
-        <v>0.3654</v>
+        <v>0.07690000000000001</v>
       </c>
       <c r="K99" s="31" t="n">
-        <v>-0.3919</v>
+        <v>-0.0713</v>
       </c>
       <c r="L99" s="28" t="inlineStr">
         <is>
@@ -8233,7 +8233,7 @@
       </c>
       <c r="M99" s="32" t="inlineStr">
         <is>
-          <t>3해 연24.4% · 변동성 36.5% (위험대비 0.59) · 최대낙폭 -39% · 가장 나쁜 창 연24.4%</t>
+          <t>3해 연1.9% · 변동성 7.7% (위험대비 -0.11) · 최대낙폭 -7% · 가장 나쁜 창 연-2.0%</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="C100" s="33" t="inlineStr">
         <is>
-          <t>ACE 중국과창판STAR50</t>
+          <t>Vanguard 배당성장</t>
         </is>
       </c>
       <c r="D100" s="33" t="inlineStr">
         <is>
-          <t>중국</t>
+          <t>주식</t>
         </is>
       </c>
       <c r="E100" s="33" t="inlineStr">
@@ -8275,17 +8275,17 @@
       </c>
       <c r="H100" s="35" t="inlineStr">
         <is>
-          <t>3해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I100" s="36" t="n">
-        <v>0.22</v>
+        <v>0.1402</v>
       </c>
       <c r="J100" s="36" t="n">
-        <v>0.3696</v>
+        <v>0.1641</v>
       </c>
       <c r="K100" s="37" t="n">
-        <v>-0.3923</v>
+        <v>-0.1365</v>
       </c>
       <c r="L100" s="34" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="M100" s="38" t="inlineStr">
         <is>
-          <t>3해 연22.0% · 변동성 37.0% (위험대비 0.52) · 최대낙폭 -39% · 가장 나쁜 창 연22.0%</t>
+          <t>5해 연14.0% · 변동성 16.4% (위험대비 0.68) · 최대낙폭 -14% · 가장 나쁜 창 연12.4%</t>
         </is>
       </c>
     </row>
@@ -8311,12 +8311,12 @@
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>Invesco 원자재</t>
+          <t>Schwab 미국 배당주</t>
         </is>
       </c>
       <c r="D101" s="14" t="inlineStr">
         <is>
-          <t>대체</t>
+          <t>주식</t>
         </is>
       </c>
       <c r="E101" s="14" t="inlineStr">
@@ -8331,22 +8331,22 @@
       </c>
       <c r="G101" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H101" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I101" s="29" t="n">
-        <v>0.5193</v>
+        <v>0.1353</v>
       </c>
       <c r="J101" s="29" t="n">
-        <v>0.2353</v>
+        <v>0.1663</v>
       </c>
       <c r="K101" s="31" t="n">
-        <v>-0.1529</v>
+        <v>-0.1455</v>
       </c>
       <c r="L101" s="28" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="M101" s="32" t="inlineStr">
         <is>
-          <t>1해 연51.9% · 변동성 23.5% (위험대비 2.09) · 최대낙폭 -15%</t>
+          <t>5해 연13.5% · 변동성 16.6% (위험대비 0.64) · 최대낙폭 -15% · 가장 나쁜 창 연13.5%</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="C102" s="33" t="inlineStr">
         <is>
-          <t>Schwab 미국 배당주</t>
+          <t>Vanguard 미국 전체시장</t>
         </is>
       </c>
       <c r="D102" s="33" t="inlineStr">
@@ -8392,22 +8392,22 @@
       </c>
       <c r="G102" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H102" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I102" s="36" t="n">
-        <v>0.2792</v>
+        <v>0.1574</v>
       </c>
       <c r="J102" s="36" t="n">
-        <v>0.1419</v>
+        <v>0.1895</v>
       </c>
       <c r="K102" s="37" t="n">
-        <v>-0.092</v>
+        <v>-0.1826</v>
       </c>
       <c r="L102" s="34" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
       </c>
       <c r="M102" s="38" t="inlineStr">
         <is>
-          <t>1해 연27.9% · 변동성 14.2% (위험대비 1.77) · 최대낙폭 -9%</t>
+          <t>5해 연15.7% · 변동성 18.9% (위험대비 0.68) · 최대낙폭 -18% · 가장 나쁜 창 연15.7%</t>
         </is>
       </c>
     </row>
@@ -8433,7 +8433,7 @@
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
-          <t>Vanguard 미국 전체시장</t>
+          <t>Vanguard 선진국(미국 제외)</t>
         </is>
       </c>
       <c r="D103" s="14" t="inlineStr">
@@ -8453,22 +8453,22 @@
       </c>
       <c r="G103" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H103" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I103" s="29" t="n">
-        <v>0.1758</v>
+        <v>0.1349</v>
       </c>
       <c r="J103" s="29" t="n">
-        <v>0.1455</v>
+        <v>0.1707</v>
       </c>
       <c r="K103" s="31" t="n">
-        <v>-0.1283</v>
+        <v>-0.1538</v>
       </c>
       <c r="L103" s="28" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="M103" s="32" t="inlineStr">
         <is>
-          <t>1해 연17.6% · 변동성 14.6% (위험대비 1.02) · 최대낙폭 -13%</t>
+          <t>5해 연13.5% · 변동성 17.1% (위험대비 0.63) · 최대낙폭 -15% · 가장 나쁜 창 연13.5%</t>
         </is>
       </c>
     </row>
@@ -8494,12 +8494,12 @@
       </c>
       <c r="C104" s="33" t="inlineStr">
         <is>
-          <t>Vanguard 선진국(미국 제외)</t>
+          <t>iShares 미국 종합채권</t>
         </is>
       </c>
       <c r="D104" s="33" t="inlineStr">
         <is>
-          <t>주식</t>
+          <t>채권</t>
         </is>
       </c>
       <c r="E104" s="33" t="inlineStr">
@@ -8514,22 +8514,22 @@
       </c>
       <c r="G104" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H104" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I104" s="36" t="n">
-        <v>0.2346</v>
+        <v>0.0301</v>
       </c>
       <c r="J104" s="36" t="n">
-        <v>0.1726</v>
+        <v>0.1102</v>
       </c>
       <c r="K104" s="37" t="n">
-        <v>-0.1323</v>
+        <v>-0.1544</v>
       </c>
       <c r="L104" s="34" t="inlineStr">
         <is>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="M104" s="38" t="inlineStr">
         <is>
-          <t>1해 연23.5% · 변동성 17.3% (위험대비 1.20) · 최대낙폭 -13%</t>
+          <t>5해 연3.0% · 변동성 11.0% (위험대비 0.02) · 최대낙폭 -15% · 가장 나쁜 창 연-0.0%</t>
         </is>
       </c>
     </row>
@@ -8555,12 +8555,12 @@
       </c>
       <c r="C105" s="14" t="inlineStr">
         <is>
-          <t>Vanguard 배당성장</t>
+          <t>TIGER 미국필라델피아반도체나스닥</t>
         </is>
       </c>
       <c r="D105" s="14" t="inlineStr">
         <is>
-          <t>주식</t>
+          <t>반도체&amp;A.I.</t>
         </is>
       </c>
       <c r="E105" s="14" t="inlineStr">
@@ -8575,22 +8575,22 @@
       </c>
       <c r="G105" s="30" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H105" s="30" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I105" s="29" t="n">
-        <v>0.1239</v>
+        <v>0.329</v>
       </c>
       <c r="J105" s="29" t="n">
-        <v>0.127</v>
+        <v>0.3539</v>
       </c>
       <c r="K105" s="31" t="n">
-        <v>-0.1365</v>
+        <v>-0.3968</v>
       </c>
       <c r="L105" s="28" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="M105" s="32" t="inlineStr">
         <is>
-          <t>1해 연12.4% · 변동성 12.7% (위험대비 0.75) · 최대낙폭 -14%</t>
+          <t>5해 연32.9% · 변동성 35.4% (위험대비 0.85) · 최대낙폭 -40% · 가장 나쁜 창 연32.9%</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="C106" s="33" t="inlineStr">
         <is>
-          <t>iShares 러셀2000 (미국 중소형)</t>
+          <t>Vanguard 신흥국</t>
         </is>
       </c>
       <c r="D106" s="33" t="inlineStr">
@@ -8636,22 +8636,22 @@
       </c>
       <c r="G106" s="35" t="inlineStr">
         <is>
-          <t>1해 실측</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H106" s="35" t="inlineStr">
         <is>
-          <t>1해</t>
+          <t>5해</t>
         </is>
       </c>
       <c r="I106" s="36" t="n">
-        <v>0.2092</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="J106" s="36" t="n">
-        <v>0.1952</v>
+        <v>0.1743</v>
       </c>
       <c r="K106" s="37" t="n">
-        <v>-0.171</v>
+        <v>-0.1624</v>
       </c>
       <c r="L106" s="34" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
       </c>
       <c r="M106" s="38" t="inlineStr">
         <is>
-          <t>1해 연20.9% · 변동성 19.5% (위험대비 0.93) · 최대낙폭 -17%</t>
+          <t>5해 연9.7% · 변동성 17.4% (위험대비 0.40) · 최대낙폭 -16% · 가장 나쁜 창 연9.7%</t>
         </is>
       </c>
     </row>
@@ -12194,7 +12194,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="E9" s="41" t="inlineStr"/>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="제안서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="자산군" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="상품" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="출처" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="사용법" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제안서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산군" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상품" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'상품'!$A$6:$M$156</definedName>
@@ -1355,7 +1355,7 @@
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="27" t="inlineStr">
         <is>
-          <t>· 펀드는 이력이 7 거래일뿐이라 변동성을 셈하지 않았습니다. 합계 변동성은 포트폴리오의 일부만 덮습니다 — 「자산군」 시트의 빈칸(—)이 그것입니다.</t>
+          <t>· 펀드 변동성은 달 간격 기준가로 셈한 것이라 결이 다릅니다. 합계 변동성은 포트폴리오의 일부만 덮습니다 — 「자산군」 시트의 빈칸(—)이 그것입니다.</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-20 14:47:28 · 문서 2026-09-20 14:47 (KST)</t>
+          <t>유니버스 2026-09-20 15:44:21 · 문서 2026-09-20 15:44 (KST)</t>
         </is>
       </c>
     </row>
@@ -2365,10 +2365,8 @@
       <c r="D9" s="29" t="n">
         <v>0.333284</v>
       </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E9" s="29" t="n">
+        <v>0.168402030225</v>
       </c>
       <c r="F9" s="28" t="inlineStr">
         <is>
@@ -2411,13 +2409,13 @@
         <v>99</v>
       </c>
       <c r="D11" s="29" t="n">
-        <v>0.09780242562454644</v>
+        <v>0.1049382716049381</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>0.2921539773352639</v>
+        <v>0.2923973274425171</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>-0.3237114148035969</v>
+        <v>-0.3235610824922673</v>
       </c>
     </row>
     <row r="12">
@@ -2435,10 +2433,8 @@
       <c r="D12" s="29" t="n">
         <v>0.1178985</v>
       </c>
-      <c r="E12" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="E12" s="29" t="n">
+        <v>0.132657723045</v>
       </c>
       <c r="F12" s="28" t="inlineStr">
         <is>
@@ -2462,7 +2458,7 @@
         <v>0.028086</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>0.01135</v>
+        <v>0.000591987885</v>
       </c>
       <c r="F13" s="28" t="inlineStr">
         <is>
@@ -2473,7 +2469,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="27" t="inlineStr">
         <is>
-          <t>펀드는 기준가 이력이 7 거래일뿐이라 변동성·최대낙폭을 셈하지 않고 원천의 위험등급을 씁니다.</t>
+          <t>펀드는 달 간격 기준가로 셈합니다 — 일봉보다 거칠어 최대낙폭이 다소 얕게 나옵니다. 계열이 없는 펀드는 원천이 준 누적 수익률과 52주 표준편차를 쓰고, 최대낙폭은 비워 둡니다.</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4407,7 @@
       </c>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>931조원</t>
+          <t>932조원</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -4533,7 +4529,7 @@
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>901조원</t>
+          <t>902조원</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -4655,7 +4651,7 @@
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>1,287조원</t>
+          <t>1,288조원</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -4716,7 +4712,7 @@
       </c>
       <c r="F41" s="28" t="inlineStr">
         <is>
-          <t>569조원</t>
+          <t>570조원</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
@@ -4838,7 +4834,7 @@
       </c>
       <c r="F43" s="28" t="inlineStr">
         <is>
-          <t>1,511조원</t>
+          <t>1,512조원</t>
         </is>
       </c>
       <c r="G43" s="30" t="inlineStr">
@@ -5082,7 +5078,7 @@
       </c>
       <c r="F47" s="28" t="inlineStr">
         <is>
-          <t>1,424조원</t>
+          <t>1,425조원</t>
         </is>
       </c>
       <c r="G47" s="30" t="inlineStr">
@@ -5143,7 +5139,7 @@
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>1,176조원</t>
+          <t>1,177조원</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -5448,7 +5444,7 @@
       </c>
       <c r="F53" s="28" t="inlineStr">
         <is>
-          <t>6,794조원</t>
+          <t>6,799조원</t>
         </is>
       </c>
       <c r="G53" s="30" t="inlineStr">
@@ -5509,7 +5505,7 @@
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>178조원</t>
+          <t>179조원</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -8677,43 +8673,39 @@
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>신한코리아인덱스증권투자신탁[주식-파생형](종류)</t>
+          <t>대신우량단기채증권투자신탁3[채권](운용)</t>
         </is>
       </c>
       <c r="D107" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>대신자산운용</t>
         </is>
       </c>
       <c r="F107" s="28" t="inlineStr">
         <is>
-          <t>3,697억원</t>
+          <t>192억원</t>
         </is>
       </c>
       <c r="G107" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H107" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I107" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J107" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I107" s="29" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="J107" s="29" t="n">
+        <v>0.0012</v>
       </c>
       <c r="K107" s="28" t="inlineStr">
         <is>
@@ -8722,12 +8714,12 @@
       </c>
       <c r="L107" s="28" t="inlineStr">
         <is>
-          <t>0.08~0.10%</t>
+          <t>0.06~0.26%</t>
         </is>
       </c>
       <c r="M107" s="32" t="inlineStr">
         <is>
-          <t>보수 0.08% · 과거 1해 152.2% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.6% · 변동성 0.1% (위험대비 6.83) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.06% · 가장 나쁜 창 연3.2%</t>
         </is>
       </c>
     </row>
@@ -8744,43 +8736,39 @@
       </c>
       <c r="C108" s="33" t="inlineStr">
         <is>
-          <t>우리KOSPI200인덱스증권자투자신탁 1(주식)</t>
+          <t>KB내일드림초단기채증권투자신탁(채권)(운용)</t>
         </is>
       </c>
       <c r="D108" s="33" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E108" s="33" t="inlineStr">
         <is>
-          <t>우리자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F108" s="34" t="inlineStr">
         <is>
-          <t>706억원</t>
+          <t>2조원</t>
         </is>
       </c>
       <c r="G108" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H108" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I108" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J108" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I108" s="36" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="J108" s="36" t="n">
+        <v>0.0011</v>
       </c>
       <c r="K108" s="34" t="inlineStr">
         <is>
@@ -8789,12 +8777,12 @@
       </c>
       <c r="L108" s="34" t="inlineStr">
         <is>
-          <t>0.15~0.95%</t>
+          <t>0.09~0.23%</t>
         </is>
       </c>
       <c r="M108" s="38" t="inlineStr">
         <is>
-          <t>보수 0.15% · 과거 1해 151.7% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연3.6% · 변동성 0.1% (위험대비 7.36) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.09% · 가장 나쁜 창 연3.1%</t>
         </is>
       </c>
     </row>
@@ -8811,43 +8799,39 @@
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t>KB스타코리아밸류업인덱스증권자투자신탁(주식)(운용)</t>
+          <t>마이다스초단기채프리미엄증권투자신탁(채권)(운용)</t>
         </is>
       </c>
       <c r="D109" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>마이다스에셋자산운용</t>
         </is>
       </c>
       <c r="F109" s="28" t="inlineStr">
         <is>
-          <t>776억원</t>
+          <t>5,025억원</t>
         </is>
       </c>
       <c r="G109" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H109" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I109" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J109" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I109" s="29" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="J109" s="29" t="n">
+        <v>0.001</v>
       </c>
       <c r="K109" s="28" t="inlineStr">
         <is>
@@ -8856,12 +8840,12 @@
       </c>
       <c r="L109" s="28" t="inlineStr">
         <is>
-          <t>0.20~0.78%</t>
+          <t>0.10~0.40%</t>
         </is>
       </c>
       <c r="M109" s="32" t="inlineStr">
         <is>
-          <t>보수 0.20% · 과거 1해 152.8% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.4% · 변동성 0.1% (위험대비 6.20) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연3.4%</t>
         </is>
       </c>
     </row>
@@ -8878,43 +8862,39 @@
       </c>
       <c r="C110" s="33" t="inlineStr">
         <is>
-          <t>교보악사파워인덱스증권투자신탁 1(주식-파생형)(운용)</t>
+          <t>코레이트초단기금리혼합자산투자신탁_운용</t>
         </is>
       </c>
       <c r="D110" s="33" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E110" s="33" t="inlineStr">
         <is>
-          <t>교보악사자산운용</t>
+          <t>코레이트자산운용</t>
         </is>
       </c>
       <c r="F110" s="34" t="inlineStr">
         <is>
-          <t>4,523억원</t>
+          <t>9,418억원</t>
         </is>
       </c>
       <c r="G110" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H110" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I110" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J110" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I110" s="36" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="J110" s="36" t="n">
+        <v>0.0008</v>
       </c>
       <c r="K110" s="34" t="inlineStr">
         <is>
@@ -8923,12 +8903,12 @@
       </c>
       <c r="L110" s="34" t="inlineStr">
         <is>
-          <t>0.16~1.16%</t>
+          <t>0.11~0.27%</t>
         </is>
       </c>
       <c r="M110" s="38" t="inlineStr">
         <is>
-          <t>보수 0.16% · 과거 1해 151.4% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연3.7% · 변동성 0.1% (위험대비 11.25) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.11% · 가장 나쁜 창 연3.3%</t>
         </is>
       </c>
     </row>
@@ -8945,43 +8925,39 @@
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>KB연금인덱스증권전환형자투자신탁(주식)(운용)</t>
+          <t>BNK내일환매초단기채증권자투자신탁(채권)</t>
         </is>
       </c>
       <c r="D111" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>비엔케이자산운용</t>
         </is>
       </c>
       <c r="F111" s="28" t="inlineStr">
         <is>
-          <t>160억원</t>
+          <t>182억원</t>
         </is>
       </c>
       <c r="G111" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H111" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I111" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J111" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I111" s="29" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="J111" s="29" t="n">
+        <v>0.0011</v>
       </c>
       <c r="K111" s="28" t="inlineStr">
         <is>
@@ -8990,12 +8966,12 @@
       </c>
       <c r="L111" s="28" t="inlineStr">
         <is>
-          <t>0.28~0.68%</t>
+          <t>0.10~0.29%</t>
         </is>
       </c>
       <c r="M111" s="32" t="inlineStr">
         <is>
-          <t>보수 0.28% · 과거 1해 152.8% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.3% · 변동성 0.1% (위험대비 4.09) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연3.0%</t>
         </is>
       </c>
     </row>
@@ -9012,43 +8988,39 @@
       </c>
       <c r="C112" s="33" t="inlineStr">
         <is>
-          <t>삼성인덱스알파증권투자신탁 1[주식-파생형]</t>
+          <t>NH-Amundi하나로단기채증권투자신탁[채권]</t>
         </is>
       </c>
       <c r="D112" s="33" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E112" s="33" t="inlineStr">
         <is>
-          <t>삼성자산운용</t>
+          <t>엔에이치아문디자산운용</t>
         </is>
       </c>
       <c r="F112" s="34" t="inlineStr">
         <is>
-          <t>214억원</t>
+          <t>3,586억원</t>
         </is>
       </c>
       <c r="G112" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H112" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I112" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J112" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I112" s="36" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="J112" s="36" t="n">
+        <v>0.0019</v>
       </c>
       <c r="K112" s="34" t="inlineStr">
         <is>
@@ -9057,12 +9029,12 @@
       </c>
       <c r="L112" s="34" t="inlineStr">
         <is>
-          <t>0.27~0.93%</t>
+          <t>0.10~0.40%</t>
         </is>
       </c>
       <c r="M112" s="38" t="inlineStr">
         <is>
-          <t>보수 0.27% · 과거 1해 152.6% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.7% · 변동성 0.2% (위험대비 4.63) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연3.0%</t>
         </is>
       </c>
     </row>
@@ -9079,57 +9051,51 @@
       </c>
       <c r="C113" s="14" t="inlineStr">
         <is>
-          <t>DB해오름인덱스알파증권투자회사[주식-파생형]운용</t>
+          <t>코레이트더블루B증권투자신탁[채권]운용</t>
         </is>
       </c>
       <c r="D113" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>디비자산운용</t>
+          <t>코레이트자산운용</t>
         </is>
       </c>
       <c r="F113" s="28" t="inlineStr">
         <is>
-          <t>408억원</t>
+          <t>168억원</t>
         </is>
       </c>
       <c r="G113" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H113" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I113" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J113" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I113" s="29" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="J113" s="29" t="n">
+        <v>0.001</v>
       </c>
       <c r="K113" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L113" s="28" t="inlineStr">
-        <is>
-          <t>0.15~0.84%</t>
-        </is>
+      <c r="L113" s="39" t="n">
+        <v>0.0013</v>
       </c>
       <c r="M113" s="32" t="inlineStr">
         <is>
-          <t>보수 0.15% · 과거 1해 150.6% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연4.2% · 변동성 0.1% (위험대비 14.00) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.13% · 가장 나쁜 창 연3.8%</t>
         </is>
       </c>
     </row>
@@ -9146,43 +9112,39 @@
       </c>
       <c r="C114" s="33" t="inlineStr">
         <is>
-          <t>키움코리아인덱스증권자투자신탁 1[주식]</t>
+          <t>하나파워e단기채증권자투자신탁[채권]</t>
         </is>
       </c>
       <c r="D114" s="33" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E114" s="33" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
+          <t>하나자산운용</t>
         </is>
       </c>
       <c r="F114" s="34" t="inlineStr">
         <is>
-          <t>131억원</t>
+          <t>4,958억원</t>
         </is>
       </c>
       <c r="G114" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H114" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I114" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J114" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I114" s="36" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="J114" s="36" t="n">
+        <v>0.0028</v>
       </c>
       <c r="K114" s="34" t="inlineStr">
         <is>
@@ -9191,12 +9153,12 @@
       </c>
       <c r="L114" s="34" t="inlineStr">
         <is>
-          <t>0.21~1.22%</t>
+          <t>0.07~0.19%</t>
         </is>
       </c>
       <c r="M114" s="38" t="inlineStr">
         <is>
-          <t>보수 0.21% · 과거 1해 151.2% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.6% · 변동성 0.3% (위험대비 2.86) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.07% · 가장 나쁜 창 연2.9%</t>
         </is>
       </c>
     </row>
@@ -9213,7 +9175,7 @@
       </c>
       <c r="C115" s="14" t="inlineStr">
         <is>
-          <t>BNKK200인덱스증권투자신탁(주식-파생형)</t>
+          <t>베어링고배당플러스증권투자신탁(주식)</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
@@ -9223,33 +9185,29 @@
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>비엔케이자산운용</t>
+          <t>베어링자산운용</t>
         </is>
       </c>
       <c r="F115" s="28" t="inlineStr">
         <is>
-          <t>515억원</t>
+          <t>1,834억원</t>
         </is>
       </c>
       <c r="G115" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H115" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I115" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J115" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I115" s="29" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="J115" s="29" t="n">
+        <v>0.277</v>
       </c>
       <c r="K115" s="28" t="inlineStr">
         <is>
@@ -9258,12 +9216,12 @@
       </c>
       <c r="L115" s="28" t="inlineStr">
         <is>
-          <t>0.17~0.95%</t>
+          <t>0.33~0.33%</t>
         </is>
       </c>
       <c r="M115" s="32" t="inlineStr">
         <is>
-          <t>보수 0.17% · 과거 1해 150.6% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연36.2% · 변동성 27.7% (위험대비 1.20) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.33% · 가장 나쁜 창 연36.2%</t>
         </is>
       </c>
     </row>
@@ -9280,43 +9238,39 @@
       </c>
       <c r="C116" s="33" t="inlineStr">
         <is>
-          <t>교보악사파워인덱스증권자투자신탁 1(주식)(운용)</t>
+          <t>현대머니마켓플렉스증권자투자신탁 1[채권](운용)</t>
         </is>
       </c>
       <c r="D116" s="33" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E116" s="33" t="inlineStr">
         <is>
-          <t>교보악사자산운용</t>
+          <t>현대자산운용</t>
         </is>
       </c>
       <c r="F116" s="34" t="inlineStr">
         <is>
-          <t>2,914억원</t>
+          <t>188억원</t>
         </is>
       </c>
       <c r="G116" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H116" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I116" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J116" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I116" s="36" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="J116" s="36" t="n">
+        <v>0.0018</v>
       </c>
       <c r="K116" s="34" t="inlineStr">
         <is>
@@ -9325,12 +9279,12 @@
       </c>
       <c r="L116" s="34" t="inlineStr">
         <is>
-          <t>0.17~1.28%</t>
+          <t>0.10~0.40%</t>
         </is>
       </c>
       <c r="M116" s="38" t="inlineStr">
         <is>
-          <t>보수 0.17% · 과거 1해 150.5% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.5% · 변동성 0.2% (위험대비 3.94) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연2.7%</t>
         </is>
       </c>
     </row>
@@ -9347,43 +9301,39 @@
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>한국투자인덱스플러스증권투자신탁 1(주식-파생형)</t>
+          <t>키움더드림단기채증권투자신탁[채권]</t>
         </is>
       </c>
       <c r="D117" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
+          <t>키움투자자산운용</t>
         </is>
       </c>
       <c r="F117" s="28" t="inlineStr">
         <is>
-          <t>299억원</t>
+          <t>1조원</t>
         </is>
       </c>
       <c r="G117" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H117" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I117" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J117" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I117" s="29" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="J117" s="29" t="n">
+        <v>0.0033</v>
       </c>
       <c r="K117" s="28" t="inlineStr">
         <is>
@@ -9392,12 +9342,12 @@
       </c>
       <c r="L117" s="28" t="inlineStr">
         <is>
-          <t>0.17~1.14%</t>
+          <t>0.07~0.33%</t>
         </is>
       </c>
       <c r="M117" s="32" t="inlineStr">
         <is>
-          <t>보수 0.17% · 과거 1해 149.8% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.7% · 변동성 0.3% (위험대비 2.79) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.07% · 가장 나쁜 창 연2.7%</t>
         </is>
       </c>
     </row>
@@ -9414,43 +9364,39 @@
       </c>
       <c r="C118" s="33" t="inlineStr">
         <is>
-          <t>iM에셋인덱스플러스증권자투자신탁 1(주식-파생형)</t>
+          <t>유경공모부동산투자신탁3(운용)</t>
         </is>
       </c>
       <c r="D118" s="33" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내대체</t>
         </is>
       </c>
       <c r="E118" s="33" t="inlineStr">
         <is>
-          <t>아이엠에셋자산운용</t>
+          <t>유경피에스지자산운용</t>
         </is>
       </c>
       <c r="F118" s="34" t="inlineStr">
         <is>
-          <t>136억원</t>
+          <t>1,021억원</t>
         </is>
       </c>
       <c r="G118" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H118" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I118" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J118" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I118" s="36" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="J118" s="36" t="n">
+        <v>0.0037</v>
       </c>
       <c r="K118" s="34" t="inlineStr">
         <is>
@@ -9459,12 +9405,12 @@
       </c>
       <c r="L118" s="34" t="inlineStr">
         <is>
-          <t>0.04~0.52%</t>
+          <t>0.27~0.46%</t>
         </is>
       </c>
       <c r="M118" s="38" t="inlineStr">
         <is>
-          <t>보수 0.04% · 과거 1해 148.9% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.7% · 변동성 0.4% (위험대비 2.38) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.27% · 가장 나쁜 창 연0.9%</t>
         </is>
       </c>
     </row>
@@ -9481,43 +9427,39 @@
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>대신우량단기채증권투자신탁3[채권](운용)</t>
+          <t>마이다스K200인덱스알파증권자투자신탁(주식-파생형)(운용)</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>대신자산운용</t>
+          <t>마이다스에셋자산운용</t>
         </is>
       </c>
       <c r="F119" s="28" t="inlineStr">
         <is>
-          <t>192억원</t>
+          <t>493억원</t>
         </is>
       </c>
       <c r="G119" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H119" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I119" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J119" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I119" s="29" t="n">
+        <v>0.5527000000000001</v>
+      </c>
+      <c r="J119" s="29" t="n">
+        <v>0.4133</v>
       </c>
       <c r="K119" s="28" t="inlineStr">
         <is>
@@ -9526,12 +9468,12 @@
       </c>
       <c r="L119" s="28" t="inlineStr">
         <is>
-          <t>0.06~0.26%</t>
+          <t>0.06~0.15%</t>
         </is>
       </c>
       <c r="M119" s="32" t="inlineStr">
         <is>
-          <t>보수 0.06% · 과거 1해 3.2% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연55.3% · 변동성 41.3% (위험대비 1.27) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.06% · 가장 나쁜 창 연55.3%</t>
         </is>
       </c>
     </row>
@@ -9548,7 +9490,7 @@
       </c>
       <c r="C120" s="33" t="inlineStr">
         <is>
-          <t>트러스톤인덱스알파증권자투자신탁[주식-파생형]</t>
+          <t>신한코리아인덱스증권투자신탁[주식-파생형](종류)</t>
         </is>
       </c>
       <c r="D120" s="33" t="inlineStr">
@@ -9558,33 +9500,29 @@
       </c>
       <c r="E120" s="33" t="inlineStr">
         <is>
-          <t>트러스톤자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F120" s="34" t="inlineStr">
         <is>
-          <t>326억원</t>
+          <t>3,697억원</t>
         </is>
       </c>
       <c r="G120" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H120" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I120" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J120" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I120" s="36" t="n">
+        <v>0.5354</v>
+      </c>
+      <c r="J120" s="36" t="n">
+        <v>0.4193</v>
       </c>
       <c r="K120" s="34" t="inlineStr">
         <is>
@@ -9593,12 +9531,12 @@
       </c>
       <c r="L120" s="34" t="inlineStr">
         <is>
-          <t>0.10~0.89%</t>
+          <t>0.08~0.10%</t>
         </is>
       </c>
       <c r="M120" s="38" t="inlineStr">
         <is>
-          <t>보수 0.10% · 과거 1해 149.4% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연53.5% · 변동성 41.9% (위험대비 1.21) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.08% · 가장 나쁜 창 연53.5%</t>
         </is>
       </c>
     </row>
@@ -9615,43 +9553,39 @@
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>마이다스K200인덱스알파증권자투자신탁(주식-파생형)(운용)</t>
+          <t>유리빠른환매미국성장주증권투자신탁[주식-재간접형]운용</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>마이다스에셋자산운용</t>
+          <t>유리자산운용</t>
         </is>
       </c>
       <c r="F121" s="28" t="inlineStr">
         <is>
-          <t>493억원</t>
+          <t>547억원</t>
         </is>
       </c>
       <c r="G121" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H121" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I121" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J121" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I121" s="29" t="n">
+        <v>0.2627</v>
+      </c>
+      <c r="J121" s="29" t="n">
+        <v>0.214</v>
       </c>
       <c r="K121" s="28" t="inlineStr">
         <is>
@@ -9660,12 +9594,12 @@
       </c>
       <c r="L121" s="28" t="inlineStr">
         <is>
-          <t>0.06~0.15%</t>
+          <t>0.39~1.34%</t>
         </is>
       </c>
       <c r="M121" s="32" t="inlineStr">
         <is>
-          <t>보수 0.06% · 과거 1해 148.8% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연26.3% · 변동성 21.4% (위험대비 1.10) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.39% · 가장 나쁜 창 연26.3%</t>
         </is>
       </c>
     </row>
@@ -9682,43 +9616,39 @@
       </c>
       <c r="C122" s="33" t="inlineStr">
         <is>
-          <t>한국투자테크증권자투자신탁 1(주식)</t>
+          <t>iM에셋ALL바른ESG단기채증권투자신탁(채권)</t>
         </is>
       </c>
       <c r="D122" s="33" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E122" s="33" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
+          <t>아이엠에셋자산운용</t>
         </is>
       </c>
       <c r="F122" s="34" t="inlineStr">
         <is>
-          <t>322억원</t>
+          <t>266억원</t>
         </is>
       </c>
       <c r="G122" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H122" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I122" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J122" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I122" s="36" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="J122" s="36" t="n">
+        <v>0.0026</v>
       </c>
       <c r="K122" s="34" t="inlineStr">
         <is>
@@ -9727,12 +9657,12 @@
       </c>
       <c r="L122" s="34" t="inlineStr">
         <is>
-          <t>0.42~1.27%</t>
+          <t>0.12~0.41%</t>
         </is>
       </c>
       <c r="M122" s="38" t="inlineStr">
         <is>
-          <t>보수 0.42% · 과거 1해 179.9% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연3.8% · 변동성 0.3% (위험대비 3.69) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.12% · 가장 나쁜 창 연2.8%</t>
         </is>
       </c>
     </row>
@@ -9749,57 +9679,51 @@
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>카디안코리아인덱스증권자투자신탁[주식]</t>
+          <t>흥국내일드림초단기채증권투자신탁[채권]</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>카디안자산운용</t>
+          <t>흥국자산운용</t>
         </is>
       </c>
       <c r="F123" s="28" t="inlineStr">
         <is>
-          <t>235억원</t>
+          <t>512억원</t>
         </is>
       </c>
       <c r="G123" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H123" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I123" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J123" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I123" s="29" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="J123" s="29" t="n">
+        <v>0.0016</v>
       </c>
       <c r="K123" s="28" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L123" s="28" t="inlineStr">
-        <is>
-          <t>0.27~0.61%</t>
-        </is>
+      <c r="L123" s="39" t="n">
+        <v>0.0015</v>
       </c>
       <c r="M123" s="32" t="inlineStr">
         <is>
-          <t>보수 0.27% · 과거 1해 148.7% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연3.6% · 변동성 0.2% (위험대비 4.81) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.15% · 가장 나쁜 창 연2.9%</t>
         </is>
       </c>
     </row>
@@ -9816,43 +9740,39 @@
       </c>
       <c r="C124" s="33" t="inlineStr">
         <is>
-          <t>유진챔피언초단기채증권투자신탁(채권)</t>
+          <t>DB해오름인덱스알파증권투자회사[주식-파생형]운용</t>
         </is>
       </c>
       <c r="D124" s="33" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E124" s="33" t="inlineStr">
         <is>
-          <t>유진자산운용</t>
+          <t>디비자산운용</t>
         </is>
       </c>
       <c r="F124" s="34" t="inlineStr">
         <is>
-          <t>1,025억원</t>
+          <t>408억원</t>
         </is>
       </c>
       <c r="G124" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H124" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I124" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J124" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I124" s="36" t="n">
+        <v>0.5334</v>
+      </c>
+      <c r="J124" s="36" t="n">
+        <v>0.4216</v>
       </c>
       <c r="K124" s="34" t="inlineStr">
         <is>
@@ -9861,12 +9781,12 @@
       </c>
       <c r="L124" s="34" t="inlineStr">
         <is>
-          <t>0.09~0.39%</t>
+          <t>0.15~0.84%</t>
         </is>
       </c>
       <c r="M124" s="38" t="inlineStr">
         <is>
-          <t>보수 0.09% · 과거 1해 3.4% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연53.3% · 변동성 42.2% (위험대비 1.20) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.15% · 가장 나쁜 창 연53.3%</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9803,7 @@
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>삼성내일지급머니마켓증권투자신탁[채권]</t>
+          <t>KB스타단기채증권자투자신탁(채권)(운용)</t>
         </is>
       </c>
       <c r="D125" s="14" t="inlineStr">
@@ -9893,33 +9813,29 @@
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F125" s="28" t="inlineStr">
         <is>
-          <t>1,079억원</t>
+          <t>662억원</t>
         </is>
       </c>
       <c r="G125" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H125" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I125" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J125" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I125" s="29" t="n">
+        <v>0.0338</v>
+      </c>
+      <c r="J125" s="29" t="n">
+        <v>0.0022</v>
       </c>
       <c r="K125" s="28" t="inlineStr">
         <is>
@@ -9928,12 +9844,12 @@
       </c>
       <c r="L125" s="28" t="inlineStr">
         <is>
-          <t>0.09~0.38%</t>
+          <t>0.11~0.28%</t>
         </is>
       </c>
       <c r="M125" s="32" t="inlineStr">
         <is>
-          <t>보수 0.09% · 과거 1해 3.4% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.4% · 변동성 0.2% (위험대비 2.59) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.11% · 가장 나쁜 창 연2.8%</t>
         </is>
       </c>
     </row>
@@ -9950,43 +9866,39 @@
       </c>
       <c r="C126" s="33" t="inlineStr">
         <is>
-          <t>대신내일출금단기채증권투자신탁[채권](운용)</t>
+          <t>한국투자퇴직연금한국의힘증권자투자신탁 1(주식)</t>
         </is>
       </c>
       <c r="D126" s="33" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E126" s="33" t="inlineStr">
         <is>
-          <t>대신자산운용</t>
+          <t>한국투자신탁운용</t>
         </is>
       </c>
       <c r="F126" s="34" t="inlineStr">
         <is>
-          <t>1,333억원</t>
+          <t>990억원</t>
         </is>
       </c>
       <c r="G126" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H126" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I126" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J126" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I126" s="36" t="n">
+        <v>0.4576</v>
+      </c>
+      <c r="J126" s="36" t="n">
+        <v>0.3896</v>
       </c>
       <c r="K126" s="34" t="inlineStr">
         <is>
@@ -9995,12 +9907,12 @@
       </c>
       <c r="L126" s="34" t="inlineStr">
         <is>
-          <t>0.09~0.40%</t>
+          <t>0.39~1.20%</t>
         </is>
       </c>
       <c r="M126" s="38" t="inlineStr">
         <is>
-          <t>보수 0.09% · 과거 1해 3.2% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연45.8% · 변동성 39.0% (위험대비 1.10) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.39% · 가장 나쁜 창 연45.8%</t>
         </is>
       </c>
     </row>
@@ -10017,7 +9929,7 @@
       </c>
       <c r="C127" s="14" t="inlineStr">
         <is>
-          <t>플러스익일지급초단기채증권투자신탁 1(채권)</t>
+          <t>IBK단기채증권자투자신탁[채권]</t>
         </is>
       </c>
       <c r="D127" s="14" t="inlineStr">
@@ -10027,33 +9939,29 @@
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>플러스자산운용</t>
+          <t>아이비케이자산운용</t>
         </is>
       </c>
       <c r="F127" s="28" t="inlineStr">
         <is>
-          <t>302억원</t>
+          <t>1,196억원</t>
         </is>
       </c>
       <c r="G127" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H127" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I127" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J127" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I127" s="29" t="n">
+        <v>0.0356</v>
+      </c>
+      <c r="J127" s="29" t="n">
+        <v>0.0034</v>
       </c>
       <c r="K127" s="28" t="inlineStr">
         <is>
@@ -10062,12 +9970,12 @@
       </c>
       <c r="L127" s="28" t="inlineStr">
         <is>
-          <t>0.08~0.38%</t>
+          <t>0.09~0.23%</t>
         </is>
       </c>
       <c r="M127" s="32" t="inlineStr">
         <is>
-          <t>보수 0.08% · 과거 1해 3.1% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.6% · 변동성 0.3% (위험대비 2.21) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.09% · 가장 나쁜 창 연2.6%</t>
         </is>
       </c>
     </row>
@@ -10084,7 +9992,7 @@
       </c>
       <c r="C128" s="33" t="inlineStr">
         <is>
-          <t>마이다스초단기채프리미엄증권투자신탁(채권)(운용)</t>
+          <t>웰컴베스트단기채증권투자신탁[채권형]</t>
         </is>
       </c>
       <c r="D128" s="33" t="inlineStr">
@@ -10094,33 +10002,29 @@
       </c>
       <c r="E128" s="33" t="inlineStr">
         <is>
-          <t>마이다스에셋자산운용</t>
+          <t>웰컴자산운용</t>
         </is>
       </c>
       <c r="F128" s="34" t="inlineStr">
         <is>
-          <t>5,025억원</t>
+          <t>389억원</t>
         </is>
       </c>
       <c r="G128" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H128" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I128" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J128" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I128" s="36" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="J128" s="36" t="n">
+        <v>0.0021</v>
       </c>
       <c r="K128" s="34" t="inlineStr">
         <is>
@@ -10129,12 +10033,12 @@
       </c>
       <c r="L128" s="34" t="inlineStr">
         <is>
-          <t>0.10~0.40%</t>
+          <t>0.13~0.29%</t>
         </is>
       </c>
       <c r="M128" s="38" t="inlineStr">
         <is>
-          <t>보수 0.10% · 과거 1해 3.6% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연3.5% · 변동성 0.2% (위험대비 3.19) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.13% · 가장 나쁜 창 연2.9%</t>
         </is>
       </c>
     </row>
@@ -10151,43 +10055,39 @@
       </c>
       <c r="C129" s="14" t="inlineStr">
         <is>
-          <t>신한코리아액티브증권투자신탁[주식](종류)</t>
+          <t>우리단기채권증권투자신탁(채권)</t>
         </is>
       </c>
       <c r="D129" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>우리자산운용</t>
         </is>
       </c>
       <c r="F129" s="28" t="inlineStr">
         <is>
-          <t>222억원</t>
+          <t>8,118억원</t>
         </is>
       </c>
       <c r="G129" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H129" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I129" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J129" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I129" s="29" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="J129" s="29" t="n">
+        <v>0.0039</v>
       </c>
       <c r="K129" s="28" t="inlineStr">
         <is>
@@ -10196,12 +10096,12 @@
       </c>
       <c r="L129" s="28" t="inlineStr">
         <is>
-          <t>0.28~0.32%</t>
+          <t>0.10~0.45%</t>
         </is>
       </c>
       <c r="M129" s="32" t="inlineStr">
         <is>
-          <t>보수 0.28% · 과거 1해 143.0% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.7% · 변동성 0.4% (위험대비 2.33) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연2.7%</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10118,7 @@
       </c>
       <c r="C130" s="33" t="inlineStr">
         <is>
-          <t>카디안내일환매초단기채권증권투자신탁[채권]</t>
+          <t>한화내일받는단기국공채증권자투자신탁(채권)</t>
         </is>
       </c>
       <c r="D130" s="33" t="inlineStr">
@@ -10228,33 +10128,29 @@
       </c>
       <c r="E130" s="33" t="inlineStr">
         <is>
-          <t>카디안자산운용</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="F130" s="34" t="inlineStr">
         <is>
-          <t>1,630억원</t>
+          <t>3,825억원</t>
         </is>
       </c>
       <c r="G130" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H130" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I130" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J130" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I130" s="36" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="J130" s="36" t="n">
+        <v>0.0022</v>
       </c>
       <c r="K130" s="34" t="inlineStr">
         <is>
@@ -10263,12 +10159,12 @@
       </c>
       <c r="L130" s="34" t="inlineStr">
         <is>
-          <t>0.09~0.38%</t>
+          <t>0.10~0.25%</t>
         </is>
       </c>
       <c r="M130" s="38" t="inlineStr">
         <is>
-          <t>보수 0.09% · 과거 1해 3.2% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.2% · 변동성 0.2% (위험대비 1.64) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연2.7%</t>
         </is>
       </c>
     </row>
@@ -10285,7 +10181,7 @@
       </c>
       <c r="C131" s="14" t="inlineStr">
         <is>
-          <t>신영내일드림단기금리혼합자산투자신탁운용</t>
+          <t>현대인베스트먼트단기증권자투자신탁 1(채권)</t>
         </is>
       </c>
       <c r="D131" s="14" t="inlineStr">
@@ -10295,33 +10191,29 @@
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>신영자산운용</t>
+          <t>현대인베스트먼트자산운용</t>
         </is>
       </c>
       <c r="F131" s="28" t="inlineStr">
         <is>
-          <t>950억원</t>
+          <t>915억원</t>
         </is>
       </c>
       <c r="G131" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H131" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I131" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J131" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I131" s="29" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="J131" s="29" t="n">
+        <v>0.0023</v>
       </c>
       <c r="K131" s="28" t="inlineStr">
         <is>
@@ -10330,12 +10222,12 @@
       </c>
       <c r="L131" s="28" t="inlineStr">
         <is>
-          <t>0.07~0.27%</t>
+          <t>0.10~0.30%</t>
         </is>
       </c>
       <c r="M131" s="32" t="inlineStr">
         <is>
-          <t>보수 0.07% · 과거 1해 3.0% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.1% · 변동성 0.2% (위험대비 1.48) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연2.7%</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10244,7 @@
       </c>
       <c r="C132" s="33" t="inlineStr">
         <is>
-          <t>KBRISE글로벌AI밸류체인ETF모아드림증권투자신탁(주식-재간접형)(운용)</t>
+          <t>신한누버거버먼미국가치주증권투자신탁(H)[주식-재간접형](종류)</t>
         </is>
       </c>
       <c r="D132" s="33" t="inlineStr">
@@ -10362,33 +10254,29 @@
       </c>
       <c r="E132" s="33" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F132" s="34" t="inlineStr">
         <is>
-          <t>181억원</t>
+          <t>655억원</t>
         </is>
       </c>
       <c r="G132" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H132" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I132" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J132" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I132" s="36" t="n">
+        <v>0.1494</v>
+      </c>
+      <c r="J132" s="36" t="n">
+        <v>0.08990000000000001</v>
       </c>
       <c r="K132" s="34" t="inlineStr">
         <is>
@@ -10397,12 +10285,12 @@
       </c>
       <c r="L132" s="34" t="inlineStr">
         <is>
-          <t>0.07~0.84%</t>
+          <t>0.35~1.35%</t>
         </is>
       </c>
       <c r="M132" s="38" t="inlineStr">
         <is>
-          <t>보수 0.07% · 과거 1해 51.8% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연14.9% · 변동성 9.0% (위험대비 1.35) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.35% · 가장 나쁜 창 연14.9%</t>
         </is>
       </c>
     </row>
@@ -10419,7 +10307,7 @@
       </c>
       <c r="C133" s="14" t="inlineStr">
         <is>
-          <t>우리프랭클린미국바이오헬스케어증권자투자신탁(주식-재간접형)</t>
+          <t>신한미국S&amp;P500인덱스증권자투자신탁(H)[주식-파생형]</t>
         </is>
       </c>
       <c r="D133" s="14" t="inlineStr">
@@ -10429,33 +10317,29 @@
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>우리자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F133" s="28" t="inlineStr">
         <is>
-          <t>225억원</t>
+          <t>1,207억원</t>
         </is>
       </c>
       <c r="G133" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H133" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I133" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J133" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I133" s="29" t="n">
+        <v>0.1789</v>
+      </c>
+      <c r="J133" s="29" t="n">
+        <v>0.1229</v>
       </c>
       <c r="K133" s="28" t="inlineStr">
         <is>
@@ -10464,12 +10348,12 @@
       </c>
       <c r="L133" s="28" t="inlineStr">
         <is>
-          <t>0.14~1.14%</t>
+          <t>0.14~1.15%</t>
         </is>
       </c>
       <c r="M133" s="32" t="inlineStr">
         <is>
-          <t>보수 0.14% · 과거 1해 48.9% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연17.9% · 변동성 12.3% (위험대비 1.23) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.14% · 가장 나쁜 창 연15.8%</t>
         </is>
       </c>
     </row>
@@ -10486,43 +10370,39 @@
       </c>
       <c r="C134" s="33" t="inlineStr">
         <is>
-          <t>피델리티이머징마켓증권자투자신탁(채권-재간접형)</t>
+          <t>삼성글로벌배당성장주증권자투자신탁H[주식]</t>
         </is>
       </c>
       <c r="D134" s="33" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E134" s="33" t="inlineStr">
         <is>
-          <t>피델리티자산운용</t>
+          <t>삼성자산운용</t>
         </is>
       </c>
       <c r="F134" s="34" t="inlineStr">
         <is>
-          <t>172억원</t>
+          <t>278억원</t>
         </is>
       </c>
       <c r="G134" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H134" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I134" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J134" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I134" s="36" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="J134" s="36" t="n">
+        <v>0.08800000000000001</v>
       </c>
       <c r="K134" s="34" t="inlineStr">
         <is>
@@ -10531,12 +10411,12 @@
       </c>
       <c r="L134" s="34" t="inlineStr">
         <is>
-          <t>0.16~1.16%</t>
+          <t>0.49~1.49%</t>
         </is>
       </c>
       <c r="M134" s="38" t="inlineStr">
         <is>
-          <t>보수 0.16% · 과거 1해 4.6% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연14.3% · 변동성 8.8% (위험대비 1.30) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.49% · 가장 나쁜 창 연14.3%</t>
         </is>
       </c>
     </row>
@@ -10553,12 +10433,12 @@
       </c>
       <c r="C135" s="14" t="inlineStr">
         <is>
-          <t>삼성누버거버먼이머징국공채플러스증권자투자신탁H[채권-재간접형]</t>
+          <t>삼성글로벌배당성장주증권자투자신탁UH[주식]</t>
         </is>
       </c>
       <c r="D135" s="14" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E135" s="14" t="inlineStr">
@@ -10568,28 +10448,24 @@
       </c>
       <c r="F135" s="28" t="inlineStr">
         <is>
-          <t>502억원</t>
+          <t>133억원</t>
         </is>
       </c>
       <c r="G135" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H135" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I135" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J135" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I135" s="29" t="n">
+        <v>0.1707</v>
+      </c>
+      <c r="J135" s="29" t="n">
+        <v>0.1115</v>
       </c>
       <c r="K135" s="28" t="inlineStr">
         <is>
@@ -10598,12 +10474,12 @@
       </c>
       <c r="L135" s="28" t="inlineStr">
         <is>
-          <t>0.23~1.13%</t>
+          <t>0.49~1.49%</t>
         </is>
       </c>
       <c r="M135" s="32" t="inlineStr">
         <is>
-          <t>보수 0.23% · 과거 1해 6.5% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연17.1% · 변동성 11.2% (위험대비 1.28) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.49% · 가장 나쁜 창 연17.0%</t>
         </is>
       </c>
     </row>
@@ -10620,43 +10496,39 @@
       </c>
       <c r="C136" s="33" t="inlineStr">
         <is>
-          <t>피델리티재팬증권자투자신탁(주식-재간접형)</t>
+          <t>미래에셋연금동행TRF성장형혼합자산투자신탁(재간접형)</t>
         </is>
       </c>
       <c r="D136" s="33" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E136" s="33" t="inlineStr">
         <is>
-          <t>피델리티자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F136" s="34" t="inlineStr">
         <is>
-          <t>156억원</t>
+          <t>1,276억원</t>
         </is>
       </c>
       <c r="G136" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H136" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I136" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J136" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I136" s="36" t="n">
+        <v>0.1715</v>
+      </c>
+      <c r="J136" s="36" t="n">
+        <v>0.1271</v>
       </c>
       <c r="K136" s="34" t="inlineStr">
         <is>
@@ -10665,12 +10537,12 @@
       </c>
       <c r="L136" s="34" t="inlineStr">
         <is>
-          <t>0.16~1.66%</t>
+          <t>0.55~0.81%</t>
         </is>
       </c>
       <c r="M136" s="38" t="inlineStr">
         <is>
-          <t>보수 0.16% · 과거 1해 36.1% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연17.1% · 변동성 12.7% (위험대비 1.13) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.55% · 가장 나쁜 창 연17.1%</t>
         </is>
       </c>
     </row>
@@ -10687,43 +10559,39 @@
       </c>
       <c r="C137" s="14" t="inlineStr">
         <is>
-          <t>한화그린히어로증권자투자신탁(주식)</t>
+          <t>미래에셋글로벌자산배분밸런스형증권투자신탁(혼합-재간접형)(UH)</t>
         </is>
       </c>
       <c r="D137" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F137" s="28" t="inlineStr">
         <is>
-          <t>446억원</t>
+          <t>231억원</t>
         </is>
       </c>
       <c r="G137" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H137" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I137" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J137" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I137" s="29" t="n">
+        <v>0.1788</v>
+      </c>
+      <c r="J137" s="29" t="n">
+        <v>0.1303</v>
       </c>
       <c r="K137" s="28" t="inlineStr">
         <is>
@@ -10732,12 +10600,12 @@
       </c>
       <c r="L137" s="28" t="inlineStr">
         <is>
-          <t>0.57~1.47%</t>
+          <t>0.40~1.20%</t>
         </is>
       </c>
       <c r="M137" s="32" t="inlineStr">
         <is>
-          <t>보수 0.57% · 과거 1해 92.0% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연17.9% · 변동성 13.0% (위험대비 1.16) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.40% · 가장 나쁜 창 연14.4%</t>
         </is>
       </c>
     </row>
@@ -10754,43 +10622,39 @@
       </c>
       <c r="C138" s="33" t="inlineStr">
         <is>
-          <t>삼성픽테로보틱스증권자투자신탁H[주식-재간접형]</t>
+          <t>KB타겟리턴적극형OCIO증권투자신탁(혼합-재간접형)(운용)</t>
         </is>
       </c>
       <c r="D138" s="33" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E138" s="33" t="inlineStr">
         <is>
-          <t>삼성자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F138" s="34" t="inlineStr">
         <is>
-          <t>417억원</t>
+          <t>234억원</t>
         </is>
       </c>
       <c r="G138" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H138" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I138" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J138" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I138" s="36" t="n">
+        <v>0.1491</v>
+      </c>
+      <c r="J138" s="36" t="n">
+        <v>0.1131</v>
       </c>
       <c r="K138" s="34" t="inlineStr">
         <is>
@@ -10799,12 +10663,12 @@
       </c>
       <c r="L138" s="34" t="inlineStr">
         <is>
-          <t>0.33~1.30%</t>
+          <t>0.55~0.82%</t>
         </is>
       </c>
       <c r="M138" s="38" t="inlineStr">
         <is>
-          <t>보수 0.33% · 과거 1해 36.7% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연14.9% · 변동성 11.3% (위험대비 1.07) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.55% · 가장 나쁜 창 연14.9%</t>
         </is>
       </c>
     </row>
@@ -10821,43 +10685,39 @@
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>유리필라델피아반도체인덱스증권자투자신탁UH[주식]_운용</t>
+          <t>NH-AmundiSignatureOCIO성장형증권자투자신탁(UH)[혼합-재간접형]</t>
         </is>
       </c>
       <c r="D139" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>유리자산운용</t>
+          <t>엔에이치아문디자산운용</t>
         </is>
       </c>
       <c r="F139" s="28" t="inlineStr">
         <is>
-          <t>1,104억원</t>
+          <t>155억원</t>
         </is>
       </c>
       <c r="G139" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H139" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I139" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J139" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I139" s="29" t="n">
+        <v>0.1797</v>
+      </c>
+      <c r="J139" s="29" t="n">
+        <v>0.1123</v>
       </c>
       <c r="K139" s="28" t="inlineStr">
         <is>
@@ -10866,12 +10726,12 @@
       </c>
       <c r="L139" s="28" t="inlineStr">
         <is>
-          <t>0.66~1.66%</t>
+          <t>0.79~1.39%</t>
         </is>
       </c>
       <c r="M139" s="32" t="inlineStr">
         <is>
-          <t>보수 0.66% · 과거 1해 90.0% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연18.0% · 변동성 11.2% (위험대비 1.35) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.79% · 가장 나쁜 창 연13.7%</t>
         </is>
       </c>
     </row>
@@ -10888,43 +10748,39 @@
       </c>
       <c r="C140" s="33" t="inlineStr">
         <is>
-          <t>iM에셋월드광업주증권자투자신탁(주식-재간접형)(H)</t>
+          <t>NH-AmundiSignatureOCIO성장형증권자투자신탁(H)[혼합-재간접형]</t>
         </is>
       </c>
       <c r="D140" s="33" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E140" s="33" t="inlineStr">
         <is>
-          <t>아이엠에셋자산운용</t>
+          <t>엔에이치아문디자산운용</t>
         </is>
       </c>
       <c r="F140" s="34" t="inlineStr">
         <is>
-          <t>387억원</t>
+          <t>356억원</t>
         </is>
       </c>
       <c r="G140" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H140" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I140" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J140" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I140" s="36" t="n">
+        <v>0.1486</v>
+      </c>
+      <c r="J140" s="36" t="n">
+        <v>0.09910000000000001</v>
       </c>
       <c r="K140" s="34" t="inlineStr">
         <is>
@@ -10933,12 +10789,12 @@
       </c>
       <c r="L140" s="34" t="inlineStr">
         <is>
-          <t>0.58~2.06%</t>
+          <t>0.79~1.39%</t>
         </is>
       </c>
       <c r="M140" s="38" t="inlineStr">
         <is>
-          <t>보수 0.58% · 과거 1해 53.7% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연14.9% · 변동성 9.9% (위험대비 1.22) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.79% · 가장 나쁜 창 연14.3%</t>
         </is>
       </c>
     </row>
@@ -10955,43 +10811,39 @@
       </c>
       <c r="C141" s="14" t="inlineStr">
         <is>
-          <t>KBRISE미국ETF모아드림증권투자신탁(주식-재간접형)(운용)</t>
+          <t>iM에셋디딤코어EMP증권투자신탁(혼합-재간접형)</t>
         </is>
       </c>
       <c r="D141" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>아이엠에셋자산운용</t>
         </is>
       </c>
       <c r="F141" s="28" t="inlineStr">
         <is>
-          <t>177억원</t>
+          <t>217억원</t>
         </is>
       </c>
       <c r="G141" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H141" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I141" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J141" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I141" s="29" t="n">
+        <v>0.1115</v>
+      </c>
+      <c r="J141" s="29" t="n">
+        <v>0.0873</v>
       </c>
       <c r="K141" s="28" t="inlineStr">
         <is>
@@ -11000,12 +10852,12 @@
       </c>
       <c r="L141" s="28" t="inlineStr">
         <is>
-          <t>0.07~0.84%</t>
+          <t>0.54~1.46%</t>
         </is>
       </c>
       <c r="M141" s="32" t="inlineStr">
         <is>
-          <t>보수 0.07% · 과거 1해 24.7% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연11.2% · 변동성 8.7% (위험대비 0.96) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.54% · 가장 나쁜 창 연11.2%</t>
         </is>
       </c>
     </row>
@@ -11022,7 +10874,7 @@
       </c>
       <c r="C142" s="33" t="inlineStr">
         <is>
-          <t>한국투자글로벌지수&amp;테마로테이션증권투자신탁(주식-재간접형)(모)</t>
+          <t>AB셀렉트미국증권투자신탁(주식-재간접형)</t>
         </is>
       </c>
       <c r="D142" s="33" t="inlineStr">
@@ -11032,33 +10884,29 @@
       </c>
       <c r="E142" s="33" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
+          <t>얼라이언스번스틴자산운용</t>
         </is>
       </c>
       <c r="F142" s="34" t="inlineStr">
         <is>
-          <t>221억원</t>
+          <t>305억원</t>
         </is>
       </c>
       <c r="G142" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H142" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I142" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J142" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I142" s="36" t="n">
+        <v>0.1012</v>
+      </c>
+      <c r="J142" s="36" t="n">
+        <v>0.1016</v>
       </c>
       <c r="K142" s="34" t="inlineStr">
         <is>
@@ -11067,12 +10915,12 @@
       </c>
       <c r="L142" s="34" t="inlineStr">
         <is>
-          <t>0.08~0.85%</t>
+          <t>0.27~1.56%</t>
         </is>
       </c>
       <c r="M142" s="38" t="inlineStr">
         <is>
-          <t>보수 0.08% · 과거 1해 22.4% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연10.1% · 변동성 10.2% (위험대비 0.72) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.27% · 가장 나쁜 창 연10.1%</t>
         </is>
       </c>
     </row>
@@ -11089,7 +10937,7 @@
       </c>
       <c r="C143" s="14" t="inlineStr">
         <is>
-          <t>미래에셋러시아업종대표증권자투자신탁 1(주식)</t>
+          <t>피델리티재팬증권자투자신탁(주식-재간접형)</t>
         </is>
       </c>
       <c r="D143" s="14" t="inlineStr">
@@ -11099,33 +10947,29 @@
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>피델리티자산운용</t>
         </is>
       </c>
       <c r="F143" s="28" t="inlineStr">
         <is>
-          <t>145억원</t>
+          <t>156억원</t>
         </is>
       </c>
       <c r="G143" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H143" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I143" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J143" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I143" s="29" t="n">
+        <v>0.2139</v>
+      </c>
+      <c r="J143" s="29" t="n">
+        <v>0.2143</v>
       </c>
       <c r="K143" s="28" t="inlineStr">
         <is>
@@ -11134,12 +10978,12 @@
       </c>
       <c r="L143" s="28" t="inlineStr">
         <is>
-          <t>0.44~1.19%</t>
+          <t>0.16~1.66%</t>
         </is>
       </c>
       <c r="M143" s="32" t="inlineStr">
         <is>
-          <t>보수 0.44% · 과거 1해 38.0% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연21.4% · 변동성 21.4% (위험대비 0.87) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.16% · 가장 나쁜 창 연21.4%</t>
         </is>
       </c>
     </row>
@@ -11156,43 +11000,39 @@
       </c>
       <c r="C144" s="33" t="inlineStr">
         <is>
-          <t>미래에셋연금러시아업종대표증권자투자신탁 1(주식)</t>
+          <t>한화단기하이일드증권자투자신탁(채권)</t>
         </is>
       </c>
       <c r="D144" s="33" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="E144" s="33" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="F144" s="34" t="inlineStr">
         <is>
-          <t>188억원</t>
+          <t>169억원</t>
         </is>
       </c>
       <c r="G144" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H144" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I144" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J144" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I144" s="36" t="n">
+        <v>0.0351</v>
+      </c>
+      <c r="J144" s="36" t="n">
+        <v>0.0151</v>
       </c>
       <c r="K144" s="34" t="inlineStr">
         <is>
@@ -11201,12 +11041,12 @@
       </c>
       <c r="L144" s="34" t="inlineStr">
         <is>
-          <t>0.48~1.02%</t>
+          <t>0.71~1.71%</t>
         </is>
       </c>
       <c r="M144" s="38" t="inlineStr">
         <is>
-          <t>보수 0.48% · 과거 1해 37.9% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.5% · 변동성 1.5% (위험대비 0.46) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.71% · 가장 나쁜 창 연3.4%</t>
         </is>
       </c>
     </row>
@@ -11223,7 +11063,7 @@
       </c>
       <c r="C145" s="14" t="inlineStr">
         <is>
-          <t>iM에셋월드에너지증권자투자신탁(주식-재간접형)(H)</t>
+          <t>피델리티글로벌배당인컴증권자투자신탁(주식-재간접형)</t>
         </is>
       </c>
       <c r="D145" s="14" t="inlineStr">
@@ -11233,33 +11073,29 @@
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>아이엠에셋자산운용</t>
+          <t>피델리티자산운용</t>
         </is>
       </c>
       <c r="F145" s="28" t="inlineStr">
         <is>
-          <t>288억원</t>
+          <t>5,716억원</t>
         </is>
       </c>
       <c r="G145" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H145" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I145" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J145" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I145" s="29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J145" s="29" t="n">
+        <v>0.08839999999999999</v>
       </c>
       <c r="K145" s="28" t="inlineStr">
         <is>
@@ -11268,12 +11104,12 @@
       </c>
       <c r="L145" s="28" t="inlineStr">
         <is>
-          <t>0.56~1.66%</t>
+          <t>0.16~1.36%</t>
         </is>
       </c>
       <c r="M145" s="32" t="inlineStr">
         <is>
-          <t>보수 0.56% · 과거 1해 44.0% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연8.0% · 변동성 8.8% (위험대비 0.59) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.16% · 가장 나쁜 창 연8.0%</t>
         </is>
       </c>
     </row>
@@ -11290,43 +11126,39 @@
       </c>
       <c r="C146" s="33" t="inlineStr">
         <is>
-          <t>신한누버거버먼미국가치주증권투자신탁(H)[주식-재간접형](종류)</t>
+          <t>한화연금단기하이일드증권자투자신탁(채권)</t>
         </is>
       </c>
       <c r="D146" s="33" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="E146" s="33" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="F146" s="34" t="inlineStr">
         <is>
-          <t>655억원</t>
+          <t>172억원</t>
         </is>
       </c>
       <c r="G146" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H146" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I146" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J146" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I146" s="36" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="J146" s="36" t="n">
+        <v>0.0156</v>
       </c>
       <c r="K146" s="34" t="inlineStr">
         <is>
@@ -11335,12 +11167,12 @@
       </c>
       <c r="L146" s="34" t="inlineStr">
         <is>
-          <t>0.35~1.35%</t>
+          <t>0.71~0.97%</t>
         </is>
       </c>
       <c r="M146" s="38" t="inlineStr">
         <is>
-          <t>보수 0.35% · 과거 1해 28.4% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연3.5% · 변동성 1.6% (위험대비 0.44) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.71% · 가장 나쁜 창 연3.4%</t>
         </is>
       </c>
     </row>
@@ -11357,7 +11189,7 @@
       </c>
       <c r="C147" s="14" t="inlineStr">
         <is>
-          <t>한국투자글로벌AI&amp;반도체TOP10증권자투자신탁UH(주식)(모)</t>
+          <t>iM에셋월드에너지증권자투자신탁(주식-재간접형)(H)</t>
         </is>
       </c>
       <c r="D147" s="14" t="inlineStr">
@@ -11367,33 +11199,29 @@
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
+          <t>아이엠에셋자산운용</t>
         </is>
       </c>
       <c r="F147" s="28" t="inlineStr">
         <is>
-          <t>1,620억원</t>
+          <t>288억원</t>
         </is>
       </c>
       <c r="G147" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H147" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I147" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J147" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I147" s="29" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="J147" s="29" t="n">
+        <v>0.1806</v>
       </c>
       <c r="K147" s="28" t="inlineStr">
         <is>
@@ -11402,12 +11230,12 @@
       </c>
       <c r="L147" s="28" t="inlineStr">
         <is>
-          <t>0.74~1.74%</t>
+          <t>0.56~1.66%</t>
         </is>
       </c>
       <c r="M147" s="32" t="inlineStr">
         <is>
-          <t>보수 0.74% · 과거 1해 45.9% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연23.6% · 변동성 18.1% (위험대비 1.15) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.56% · 가장 나쁜 창 연14.4%</t>
         </is>
       </c>
     </row>
@@ -11424,7 +11252,7 @@
       </c>
       <c r="C148" s="33" t="inlineStr">
         <is>
-          <t>신한미국나스닥100인덱스증권자투자신탁(UH)[주식-파생형]</t>
+          <t>한국투자글로벌AI&amp;반도체TOP10증권자투자신탁UH(주식)(모)</t>
         </is>
       </c>
       <c r="D148" s="33" t="inlineStr">
@@ -11434,33 +11262,29 @@
       </c>
       <c r="E148" s="33" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>한국투자신탁운용</t>
         </is>
       </c>
       <c r="F148" s="34" t="inlineStr">
         <is>
-          <t>1,081억원</t>
+          <t>1,620억원</t>
         </is>
       </c>
       <c r="G148" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H148" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I148" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J148" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I148" s="36" t="n">
+        <v>0.4327</v>
+      </c>
+      <c r="J148" s="36" t="n">
+        <v>0.2972</v>
       </c>
       <c r="K148" s="34" t="inlineStr">
         <is>
@@ -11469,12 +11293,12 @@
       </c>
       <c r="L148" s="34" t="inlineStr">
         <is>
-          <t>0.15~1.15%</t>
+          <t>0.74~1.74%</t>
         </is>
       </c>
       <c r="M148" s="38" t="inlineStr">
         <is>
-          <t>보수 0.15% · 과거 1해 19.6% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연43.3% · 변동성 29.7% (위험대비 1.36) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.74% · 가장 나쁜 창 연43.3%</t>
         </is>
       </c>
     </row>
@@ -11491,43 +11315,39 @@
       </c>
       <c r="C149" s="14" t="inlineStr">
         <is>
-          <t>KCGI샐러리맨증권자투자신탁[주식-재간접형]</t>
+          <t>KB평생연금밸런스증권자투자신탁(채권혼합-재간접형)(운용)</t>
         </is>
       </c>
       <c r="D149" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>케이씨지아이자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F149" s="28" t="inlineStr">
         <is>
-          <t>2,524억원</t>
+          <t>134억원</t>
         </is>
       </c>
       <c r="G149" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H149" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I149" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J149" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I149" s="29" t="n">
+        <v>0.06059999999999999</v>
+      </c>
+      <c r="J149" s="29" t="n">
+        <v>0.05309999999999999</v>
       </c>
       <c r="K149" s="28" t="inlineStr">
         <is>
@@ -11536,12 +11356,12 @@
       </c>
       <c r="L149" s="28" t="inlineStr">
         <is>
-          <t>0.64~1.01%</t>
+          <t>0.30~0.51%</t>
         </is>
       </c>
       <c r="M149" s="32" t="inlineStr">
         <is>
-          <t>보수 0.64% · 과거 1해 31.3% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연6.1% · 변동성 5.3% (위험대비 0.61) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.30% · 가장 나쁜 창 연5.7%</t>
         </is>
       </c>
     </row>
@@ -11558,55 +11378,53 @@
       </c>
       <c r="C150" s="33" t="inlineStr">
         <is>
-          <t>흥국글로벌EMP증권투자신탁[주식-재간접형]</t>
+          <t>한국투자글로벌AI&amp;반도체TOP10증권자투자신탁H(주식)(모)</t>
         </is>
       </c>
       <c r="D150" s="33" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E150" s="33" t="inlineStr">
         <is>
-          <t>흥국자산운용</t>
+          <t>한국투자신탁운용</t>
         </is>
       </c>
       <c r="F150" s="34" t="inlineStr">
         <is>
-          <t>202억원</t>
+          <t>1,623억원</t>
         </is>
       </c>
       <c r="G150" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H150" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I150" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J150" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>3해</t>
+        </is>
+      </c>
+      <c r="I150" s="36" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="J150" s="36" t="n">
+        <v>0.2845</v>
       </c>
       <c r="K150" s="34" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L150" s="40" t="n">
-        <v>0.0026</v>
+      <c r="L150" s="34" t="inlineStr">
+        <is>
+          <t>0.74~1.74%</t>
+        </is>
       </c>
       <c r="M150" s="38" t="inlineStr">
         <is>
-          <t>보수 0.26% · 과거 1해 18.6% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>3해 연39.6% · 변동성 28.4% (위험대비 1.29) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.74% · 가장 나쁜 창 연39.6%</t>
         </is>
       </c>
     </row>
@@ -11623,7 +11441,7 @@
       </c>
       <c r="C151" s="14" t="inlineStr">
         <is>
-          <t>키움글로벌차세대IT&amp;네트워크증권자투자신탁(H)[주식]</t>
+          <t>KCGI글로벌고배당증권자투자신탁[주식-재간접형]</t>
         </is>
       </c>
       <c r="D151" s="14" t="inlineStr">
@@ -11633,33 +11451,29 @@
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
+          <t>케이씨지아이자산운용</t>
         </is>
       </c>
       <c r="F151" s="28" t="inlineStr">
         <is>
-          <t>353억원</t>
+          <t>189억원</t>
         </is>
       </c>
       <c r="G151" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H151" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I151" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J151" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I151" s="29" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="J151" s="29" t="n">
+        <v>0.101</v>
       </c>
       <c r="K151" s="28" t="inlineStr">
         <is>
@@ -11668,12 +11482,12 @@
       </c>
       <c r="L151" s="28" t="inlineStr">
         <is>
-          <t>0.95~1.95%</t>
+          <t>0.49~0.65%</t>
         </is>
       </c>
       <c r="M151" s="32" t="inlineStr">
         <is>
-          <t>보수 0.95% · 과거 1해 60.0% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연9.0% · 변동성 10.1% (위험대비 0.61) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.49% · 가장 나쁜 창 연9.0%</t>
         </is>
       </c>
     </row>
@@ -11690,43 +11504,39 @@
       </c>
       <c r="C152" s="33" t="inlineStr">
         <is>
-          <t>AB글로벌고수익증권투자신탁(채권-재간접형)</t>
+          <t>키움불리오글로벌멀티에셋EMP증권자투자신탁(UH)[혼합-재간접형]</t>
         </is>
       </c>
       <c r="D152" s="33" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E152" s="33" t="inlineStr">
         <is>
-          <t>얼라이언스번스틴자산운용</t>
+          <t>키움투자자산운용</t>
         </is>
       </c>
       <c r="F152" s="34" t="inlineStr">
         <is>
-          <t>1,629억원</t>
+          <t>659억원</t>
         </is>
       </c>
       <c r="G152" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H152" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I152" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J152" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I152" s="36" t="n">
+        <v>0.1028</v>
+      </c>
+      <c r="J152" s="36" t="n">
+        <v>0.1173</v>
       </c>
       <c r="K152" s="34" t="inlineStr">
         <is>
@@ -11735,12 +11545,12 @@
       </c>
       <c r="L152" s="34" t="inlineStr">
         <is>
-          <t>0.17~1.17%</t>
+          <t>0.70~1.57%</t>
         </is>
       </c>
       <c r="M152" s="38" t="inlineStr">
         <is>
-          <t>보수 0.17% · 과거 1해 2.0% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연10.3% · 변동성 11.7% (위험대비 0.64) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.70% · 가장 나쁜 창 연10.3%</t>
         </is>
       </c>
     </row>
@@ -11757,7 +11567,7 @@
       </c>
       <c r="C153" s="14" t="inlineStr">
         <is>
-          <t>다올글로벌빅테크1등주증권투자신탁[주식](운)</t>
+          <t>키움슈로더월지급글로벌가치주인컴증권자투자신탁[주식-재간접형]</t>
         </is>
       </c>
       <c r="D153" s="14" t="inlineStr">
@@ -11767,33 +11577,29 @@
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>다올자산운용</t>
+          <t>키움투자자산운용</t>
         </is>
       </c>
       <c r="F153" s="28" t="inlineStr">
         <is>
-          <t>917억원</t>
+          <t>1,713억원</t>
         </is>
       </c>
       <c r="G153" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H153" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I153" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J153" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I153" s="29" t="n">
+        <v>0.0755</v>
+      </c>
+      <c r="J153" s="29" t="n">
+        <v>0.1013</v>
       </c>
       <c r="K153" s="28" t="inlineStr">
         <is>
@@ -11802,12 +11608,12 @@
       </c>
       <c r="L153" s="28" t="inlineStr">
         <is>
-          <t>0.74~2.04%</t>
+          <t>0.43~1.21%</t>
         </is>
       </c>
       <c r="M153" s="32" t="inlineStr">
         <is>
-          <t>보수 0.74% · 과거 1해 30.7% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연7.5% · 변동성 10.1% (위험대비 0.47) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.43% · 가장 나쁜 창 연7.5%</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11630,7 @@
       </c>
       <c r="C154" s="33" t="inlineStr">
         <is>
-          <t>AB월지급글로벌고수익증권투자신탁[채권-재간접형]</t>
+          <t>베어링월지급글로벌하이일드증권자투자신탁[H](채권-재간접형)</t>
         </is>
       </c>
       <c r="D154" s="33" t="inlineStr">
@@ -11834,33 +11640,29 @@
       </c>
       <c r="E154" s="33" t="inlineStr">
         <is>
-          <t>얼라이언스번스틴자산운용</t>
+          <t>베어링자산운용</t>
         </is>
       </c>
       <c r="F154" s="34" t="inlineStr">
         <is>
-          <t>5,462억원</t>
+          <t>496억원</t>
         </is>
       </c>
       <c r="G154" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H154" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I154" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J154" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I154" s="36" t="n">
+        <v>0.0282</v>
+      </c>
+      <c r="J154" s="36" t="n">
+        <v>0.0195</v>
       </c>
       <c r="K154" s="34" t="inlineStr">
         <is>
@@ -11869,12 +11671,12 @@
       </c>
       <c r="L154" s="34" t="inlineStr">
         <is>
-          <t>0.17~0.71%</t>
+          <t>0.49~1.19%</t>
         </is>
       </c>
       <c r="M154" s="38" t="inlineStr">
         <is>
-          <t>보수 0.17% · 과거 1해 1.8% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연2.8% · 변동성 1.9% (위험대비 0.01) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.49% · 가장 나쁜 창 연2.8%</t>
         </is>
       </c>
     </row>
@@ -11891,43 +11693,39 @@
       </c>
       <c r="C155" s="14" t="inlineStr">
         <is>
-          <t>마이다스아시아리더스성장주증권자투자신탁(H)(주식)(운용)</t>
+          <t>AB글로벌고수익증권투자신탁(채권-재간접형)</t>
         </is>
       </c>
       <c r="D155" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>마이다스에셋자산운용</t>
+          <t>얼라이언스번스틴자산운용</t>
         </is>
       </c>
       <c r="F155" s="28" t="inlineStr">
         <is>
-          <t>381억원</t>
+          <t>1,629억원</t>
         </is>
       </c>
       <c r="G155" s="30" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H155" s="30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I155" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J155" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I155" s="29" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="J155" s="29" t="n">
+        <v>0.0255</v>
       </c>
       <c r="K155" s="28" t="inlineStr">
         <is>
@@ -11936,12 +11734,12 @@
       </c>
       <c r="L155" s="28" t="inlineStr">
         <is>
-          <t>0.97~2.27%</t>
+          <t>0.17~1.17%</t>
         </is>
       </c>
       <c r="M155" s="32" t="inlineStr">
         <is>
-          <t>보수 0.97% · 과거 1해 53.2% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연1.8% · 변동성 2.5% (위험대비 -0.41) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.17% · 가장 나쁜 창 연1.8%</t>
         </is>
       </c>
     </row>
@@ -11958,7 +11756,7 @@
       </c>
       <c r="C156" s="33" t="inlineStr">
         <is>
-          <t>한화천연자원증권자투자신탁(주식)</t>
+          <t>한국밸류글로벌배당인컴증권자투자신탁(주식)(모)</t>
         </is>
       </c>
       <c r="D156" s="33" t="inlineStr">
@@ -11968,33 +11766,29 @@
       </c>
       <c r="E156" s="33" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>한국투자밸류자산운용</t>
         </is>
       </c>
       <c r="F156" s="34" t="inlineStr">
         <is>
-          <t>1,120억원</t>
+          <t>210억원</t>
         </is>
       </c>
       <c r="G156" s="35" t="inlineStr">
         <is>
-          <t>미측정</t>
+          <t>다년 실측</t>
         </is>
       </c>
       <c r="H156" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I156" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J156" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>5해</t>
+        </is>
+      </c>
+      <c r="I156" s="36" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="J156" s="36" t="n">
+        <v>0.1009</v>
       </c>
       <c r="K156" s="34" t="inlineStr">
         <is>
@@ -12003,12 +11797,12 @@
       </c>
       <c r="L156" s="34" t="inlineStr">
         <is>
-          <t>0.94~2.44%</t>
+          <t>0.91~1.88%</t>
         </is>
       </c>
       <c r="M156" s="38" t="inlineStr">
         <is>
-          <t>보수 0.94% · 과거 1해 43.7% · 시세가 없어 변동성·낙폭을 못 쟀습니다</t>
+          <t>5해 연12.2% · 변동성 10.1% (위험대비 0.94) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.91% · 가장 나쁜 창 연6.2%</t>
         </is>
       </c>
     </row>
@@ -12107,7 +11901,7 @@
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>보수는 클래스마다 달라 하나로 줄이지 않고 범위(feeMin~feeMax)로 싣습니다. 변동성·최대낙폭은 기준가 이력이 7 거래일뿐이라 셈하지 않고 위험등급을 씁니다.</t>
+          <t>보수는 클래스마다 달라 하나로 줄이지 않고 범위(feeMin~feeMax)로 싣습니다. 기간수익률은 **누적**입니다(ETF 는 연율이라 뜻이 다릅니다). 변동성·최대낙폭은 달 간격 기준가 계열에서 셈하고, 계열이 없으면 원천의 52 주 표준편차를 씁니다.</t>
         </is>
       </c>
     </row>
@@ -12152,7 +11946,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr"/>
@@ -12226,7 +12020,7 @@
       </c>
       <c r="B14" s="43" t="inlineStr">
         <is>
-          <t>일봉이 있는 상품만 연변동성(일간 로그수익률 표준편차 × √252)을 셈합니다. 펀드는 이력이 7 거래일뿐이라 셈하지 않고 원천의 위험등급을 씁니다.</t>
+          <t>일봉이 있는 상품만 연변동성(일간 로그수익률 표준편차 × √252)을 셈합니다. 펀드는 달 간격 기준가로 셈하고, 계열이 원천의 위험등급을 씁니다.</t>
         </is>
       </c>
     </row>
@@ -12612,7 +12406,7 @@
       </c>
       <c r="C30" s="45" t="inlineStr">
         <is>
-          <t>국내주식 40% · 국내채권 40% · 대체 20%</t>
+          <t>국내채권 40% · 국내주식 40% · 대체 20%</t>
         </is>
       </c>
       <c r="D30" s="46" t="n"/>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제안서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산군" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상품" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="제안서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="자산군" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="상품" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="출처" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="사용법" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'상품'!$A$6:$M$156</definedName>
@@ -1078,7 +1078,7 @@
         <v/>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.0553</v>
+        <v>0.0535</v>
       </c>
       <c r="H23" s="15">
         <f>IF(ISNUMBER($F23),$F23,0)</f>
@@ -1376,7 +1376,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-20 15:44:21 · 문서 2026-09-20 15:44 (KST)</t>
+          <t>유니버스 2026-09-20 16:00:00 · 문서 2026-09-20 16:00 (KST)</t>
         </is>
       </c>
     </row>
@@ -2366,12 +2366,10 @@
         <v>0.333284</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>0.168402030225</v>
-      </c>
-      <c r="F9" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.18285</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>-0.1577</v>
       </c>
     </row>
     <row r="10">
@@ -2409,13 +2407,13 @@
         <v>99</v>
       </c>
       <c r="D11" s="29" t="n">
-        <v>0.1049382716049381</v>
+        <v>0.09780242562454644</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>0.2923973274425171</v>
+        <v>0.2921539773352639</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>-0.3235610824922673</v>
+        <v>-0.3237114148035969</v>
       </c>
     </row>
     <row r="12">
@@ -2434,12 +2432,10 @@
         <v>0.1178985</v>
       </c>
       <c r="E12" s="29" t="n">
-        <v>0.132657723045</v>
-      </c>
-      <c r="F12" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1361</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>-0.11885</v>
       </c>
     </row>
     <row r="13">
@@ -2458,12 +2454,10 @@
         <v>0.028086</v>
       </c>
       <c r="E13" s="29" t="n">
-        <v>0.000591987885</v>
-      </c>
-      <c r="F13" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.0326</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>-0.0344</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
@@ -4407,7 +4401,7 @@
       </c>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>932조원</t>
+          <t>931조원</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -4529,7 +4523,7 @@
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>902조원</t>
+          <t>901조원</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -4651,7 +4645,7 @@
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>1,288조원</t>
+          <t>1,287조원</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -4712,7 +4706,7 @@
       </c>
       <c r="F41" s="28" t="inlineStr">
         <is>
-          <t>570조원</t>
+          <t>569조원</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
@@ -4834,7 +4828,7 @@
       </c>
       <c r="F43" s="28" t="inlineStr">
         <is>
-          <t>1,512조원</t>
+          <t>1,511조원</t>
         </is>
       </c>
       <c r="G43" s="30" t="inlineStr">
@@ -5078,7 +5072,7 @@
       </c>
       <c r="F47" s="28" t="inlineStr">
         <is>
-          <t>1,425조원</t>
+          <t>1,424조원</t>
         </is>
       </c>
       <c r="G47" s="30" t="inlineStr">
@@ -5139,7 +5133,7 @@
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>1,177조원</t>
+          <t>1,176조원</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -5444,7 +5438,7 @@
       </c>
       <c r="F53" s="28" t="inlineStr">
         <is>
-          <t>6,799조원</t>
+          <t>6,794조원</t>
         </is>
       </c>
       <c r="G53" s="30" t="inlineStr">
@@ -5505,7 +5499,7 @@
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>179조원</t>
+          <t>178조원</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -8673,22 +8667,22 @@
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>대신우량단기채증권투자신탁3[채권](운용)</t>
+          <t>이지스코어리테일부동산투자신탁 126</t>
         </is>
       </c>
       <c r="D107" s="14" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내대체</t>
         </is>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>대신자산운용</t>
+          <t>이지스자산운용</t>
         </is>
       </c>
       <c r="F107" s="28" t="inlineStr">
         <is>
-          <t>192억원</t>
+          <t>606억원</t>
         </is>
       </c>
       <c r="G107" s="30" t="inlineStr">
@@ -8698,28 +8692,26 @@
       </c>
       <c r="H107" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I107" s="29" t="n">
-        <v>0.0363</v>
+        <v>0.0469</v>
       </c>
       <c r="J107" s="29" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="K107" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.0069</v>
+      </c>
+      <c r="K107" s="31" t="n">
+        <v>0</v>
       </c>
       <c r="L107" s="28" t="inlineStr">
         <is>
-          <t>0.06~0.26%</t>
+          <t>0.00~0.00%</t>
         </is>
       </c>
       <c r="M107" s="32" t="inlineStr">
         <is>
-          <t>5해 연3.6% · 변동성 0.1% (위험대비 6.83) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.06% · 가장 나쁜 창 연3.2%</t>
+          <t>3해 연4.7% · 변동성 0.7% (위험대비 2.72) (달 간격) · 최대낙폭 0% · 보수 0.00% · 가장 나쁜 창 연4.7%</t>
         </is>
       </c>
     </row>
@@ -8736,22 +8728,22 @@
       </c>
       <c r="C108" s="33" t="inlineStr">
         <is>
-          <t>KB내일드림초단기채증권투자신탁(채권)(운용)</t>
+          <t>이지스리테일부동산투자신탁299</t>
         </is>
       </c>
       <c r="D108" s="33" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내대체</t>
         </is>
       </c>
       <c r="E108" s="33" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>이지스자산운용</t>
         </is>
       </c>
       <c r="F108" s="34" t="inlineStr">
         <is>
-          <t>2조원</t>
+          <t>211억원</t>
         </is>
       </c>
       <c r="G108" s="35" t="inlineStr">
@@ -8765,24 +8757,20 @@
         </is>
       </c>
       <c r="I108" s="36" t="n">
-        <v>0.0362</v>
+        <v>0.0398</v>
       </c>
       <c r="J108" s="36" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="K108" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L108" s="34" t="inlineStr">
-        <is>
-          <t>0.09~0.23%</t>
-        </is>
+        <v>0.0212</v>
+      </c>
+      <c r="K108" s="37" t="n">
+        <v>-0.0241</v>
+      </c>
+      <c r="L108" s="40" t="n">
+        <v>0.0006400000000000001</v>
       </c>
       <c r="M108" s="38" t="inlineStr">
         <is>
-          <t>3해 연3.6% · 변동성 0.1% (위험대비 7.36) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.09% · 가장 나쁜 창 연3.1%</t>
+          <t>3해 연4.0% · 변동성 2.1% (위험대비 0.55) (달 간격) · 최대낙폭 -2% · 보수 0.06% · 가장 나쁜 창 연4.0%</t>
         </is>
       </c>
     </row>
@@ -8799,12 +8787,12 @@
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t>마이다스초단기채프리미엄증권투자신탁(채권)(운용)</t>
+          <t>마이다스거북이90증권자투자신탁 1(주식)(운용)</t>
         </is>
       </c>
       <c r="D109" s="14" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내대체</t>
         </is>
       </c>
       <c r="E109" s="14" t="inlineStr">
@@ -8814,7 +8802,7 @@
       </c>
       <c r="F109" s="28" t="inlineStr">
         <is>
-          <t>5,025억원</t>
+          <t>1,952억원</t>
         </is>
       </c>
       <c r="G109" s="30" t="inlineStr">
@@ -8824,28 +8812,26 @@
       </c>
       <c r="H109" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I109" s="29" t="n">
-        <v>0.0343</v>
+        <v>0.1644</v>
       </c>
       <c r="J109" s="29" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K109" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.0808</v>
+      </c>
+      <c r="K109" s="31" t="n">
+        <v>-0.0366</v>
       </c>
       <c r="L109" s="28" t="inlineStr">
         <is>
-          <t>0.10~0.40%</t>
+          <t>0.59~2.09%</t>
         </is>
       </c>
       <c r="M109" s="32" t="inlineStr">
         <is>
-          <t>5해 연3.4% · 변동성 0.1% (위험대비 6.20) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연3.4%</t>
+          <t>3해 연16.4% · 변동성 8.1% (위험대비 1.69) (달 간격) · 최대낙폭 -4% · 보수 0.59% · 가장 나쁜 창 연16.4%</t>
         </is>
       </c>
     </row>
@@ -8862,7 +8848,7 @@
       </c>
       <c r="C110" s="33" t="inlineStr">
         <is>
-          <t>코레이트초단기금리혼합자산투자신탁_운용</t>
+          <t>유진챔피언중단기채증권자투자신탁(채권)</t>
         </is>
       </c>
       <c r="D110" s="33" t="inlineStr">
@@ -8872,12 +8858,12 @@
       </c>
       <c r="E110" s="33" t="inlineStr">
         <is>
-          <t>코레이트자산운용</t>
+          <t>유진자산운용</t>
         </is>
       </c>
       <c r="F110" s="34" t="inlineStr">
         <is>
-          <t>9,418억원</t>
+          <t>1,392억원</t>
         </is>
       </c>
       <c r="G110" s="35" t="inlineStr">
@@ -8891,24 +8877,22 @@
         </is>
       </c>
       <c r="I110" s="36" t="n">
-        <v>0.0371</v>
+        <v>0.0073</v>
       </c>
       <c r="J110" s="36" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="K110" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.035</v>
+      </c>
+      <c r="K110" s="37" t="n">
+        <v>-0.04</v>
       </c>
       <c r="L110" s="34" t="inlineStr">
         <is>
-          <t>0.11~0.27%</t>
+          <t>0.11~0.41%</t>
         </is>
       </c>
       <c r="M110" s="38" t="inlineStr">
         <is>
-          <t>3해 연3.7% · 변동성 0.1% (위험대비 11.25) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.11% · 가장 나쁜 창 연3.3%</t>
+          <t>3해 연0.7% · 변동성 3.5% (위험대비 -0.59) (달 간격) · 최대낙폭 -4% · 보수 0.11% · 가장 나쁜 창 연-0.1%</t>
         </is>
       </c>
     </row>
@@ -8925,22 +8909,22 @@
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>BNK내일환매초단기채증권자투자신탁(채권)</t>
+          <t>우리반도체BIG2플러스증권투자신탁(채권혼합)</t>
         </is>
       </c>
       <c r="D111" s="14" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>비엔케이자산운용</t>
+          <t>우리자산운용</t>
         </is>
       </c>
       <c r="F111" s="28" t="inlineStr">
         <is>
-          <t>182억원</t>
+          <t>4,207억원</t>
         </is>
       </c>
       <c r="G111" s="30" t="inlineStr">
@@ -8950,28 +8934,26 @@
       </c>
       <c r="H111" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I111" s="29" t="n">
-        <v>0.0326</v>
+        <v>0.2141</v>
       </c>
       <c r="J111" s="29" t="n">
-        <v>0.0011</v>
-      </c>
-      <c r="K111" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1545</v>
+      </c>
+      <c r="K111" s="31" t="n">
+        <v>-0.09300000000000001</v>
       </c>
       <c r="L111" s="28" t="inlineStr">
         <is>
-          <t>0.10~0.29%</t>
+          <t>0.34~0.89%</t>
         </is>
       </c>
       <c r="M111" s="32" t="inlineStr">
         <is>
-          <t>5해 연3.3% · 변동성 0.1% (위험대비 4.09) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연3.0%</t>
+          <t>3해 연21.4% · 변동성 15.4% (위험대비 1.20) (달 간격) · 최대낙폭 -9% · 보수 0.34% · 가장 나쁜 창 연21.4%</t>
         </is>
       </c>
     </row>
@@ -8988,22 +8970,22 @@
       </c>
       <c r="C112" s="33" t="inlineStr">
         <is>
-          <t>NH-Amundi하나로단기채증권투자신탁[채권]</t>
+          <t>마이다스K200인덱스알파증권자투자신탁(주식-파생형)(운용)</t>
         </is>
       </c>
       <c r="D112" s="33" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E112" s="33" t="inlineStr">
         <is>
-          <t>엔에이치아문디자산운용</t>
+          <t>마이다스에셋자산운용</t>
         </is>
       </c>
       <c r="F112" s="34" t="inlineStr">
         <is>
-          <t>3,586억원</t>
+          <t>493억원</t>
         </is>
       </c>
       <c r="G112" s="35" t="inlineStr">
@@ -9013,28 +8995,26 @@
       </c>
       <c r="H112" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I112" s="36" t="n">
-        <v>0.0369</v>
+        <v>0.509</v>
       </c>
       <c r="J112" s="36" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="K112" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.3986</v>
+      </c>
+      <c r="K112" s="37" t="n">
+        <v>-0.2336</v>
       </c>
       <c r="L112" s="34" t="inlineStr">
         <is>
-          <t>0.10~0.40%</t>
+          <t>0.06~0.15%</t>
         </is>
       </c>
       <c r="M112" s="38" t="inlineStr">
         <is>
-          <t>5해 연3.7% · 변동성 0.2% (위험대비 4.63) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연3.0%</t>
+          <t>3해 연50.9% · 변동성 39.9% (위험대비 1.21) (달 간격) · 최대낙폭 -23% · 보수 0.06% · 가장 나쁜 창 연50.9%</t>
         </is>
       </c>
     </row>
@@ -9051,22 +9031,22 @@
       </c>
       <c r="C113" s="14" t="inlineStr">
         <is>
-          <t>코레이트더블루B증권투자신탁[채권]운용</t>
+          <t>신한퇴직연금커버드콜인덱스증권자투자신탁[주식혼합-파생형] (종류)</t>
         </is>
       </c>
       <c r="D113" s="14" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>코레이트자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F113" s="28" t="inlineStr">
         <is>
-          <t>168억원</t>
+          <t>150억원</t>
         </is>
       </c>
       <c r="G113" s="30" t="inlineStr">
@@ -9076,26 +9056,26 @@
       </c>
       <c r="H113" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I113" s="29" t="n">
-        <v>0.0421</v>
+        <v>0.1302</v>
       </c>
       <c r="J113" s="29" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="K113" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L113" s="39" t="n">
-        <v>0.0013</v>
+        <v>0.0872</v>
+      </c>
+      <c r="K113" s="31" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="L113" s="28" t="inlineStr">
+        <is>
+          <t>0.56~0.79%</t>
+        </is>
       </c>
       <c r="M113" s="32" t="inlineStr">
         <is>
-          <t>5해 연4.2% · 변동성 0.1% (위험대비 14.00) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.13% · 가장 나쁜 창 연3.8%</t>
+          <t>3해 연13.0% · 변동성 8.7% (위험대비 1.17) (달 간격) · 최대낙폭 -6% · 보수 0.56% · 가장 나쁜 창 연13.0%</t>
         </is>
       </c>
     </row>
@@ -9112,22 +9092,22 @@
       </c>
       <c r="C114" s="33" t="inlineStr">
         <is>
-          <t>하나파워e단기채증권자투자신탁[채권]</t>
+          <t>신영밸류고배당증권자투자신탁(주식)운용</t>
         </is>
       </c>
       <c r="D114" s="33" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E114" s="33" t="inlineStr">
         <is>
-          <t>하나자산운용</t>
+          <t>신영자산운용</t>
         </is>
       </c>
       <c r="F114" s="34" t="inlineStr">
         <is>
-          <t>4,958억원</t>
+          <t>8,313억원</t>
         </is>
       </c>
       <c r="G114" s="35" t="inlineStr">
@@ -9137,28 +9117,26 @@
       </c>
       <c r="H114" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I114" s="36" t="n">
-        <v>0.0361</v>
+        <v>0.3287</v>
       </c>
       <c r="J114" s="36" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="K114" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.2543</v>
+      </c>
+      <c r="K114" s="37" t="n">
+        <v>-0.1498</v>
       </c>
       <c r="L114" s="34" t="inlineStr">
         <is>
-          <t>0.07~0.19%</t>
+          <t>0.45~1.35%</t>
         </is>
       </c>
       <c r="M114" s="38" t="inlineStr">
         <is>
-          <t>5해 연3.6% · 변동성 0.3% (위험대비 2.86) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.07% · 가장 나쁜 창 연2.9%</t>
+          <t>3해 연32.9% · 변동성 25.4% (위험대비 1.18) (달 간격) · 최대낙폭 -15% · 보수 0.45% · 가장 나쁜 창 연32.9%</t>
         </is>
       </c>
     </row>
@@ -9175,22 +9153,22 @@
       </c>
       <c r="C115" s="14" t="inlineStr">
         <is>
-          <t>베어링고배당플러스증권투자신탁(주식)</t>
+          <t>신한커버드콜인덱스증권자투자신탁[주식혼합-파생형]</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>베어링자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F115" s="28" t="inlineStr">
         <is>
-          <t>1,834억원</t>
+          <t>161억원</t>
         </is>
       </c>
       <c r="G115" s="30" t="inlineStr">
@@ -9204,24 +9182,22 @@
         </is>
       </c>
       <c r="I115" s="29" t="n">
-        <v>0.3617</v>
+        <v>0.223</v>
       </c>
       <c r="J115" s="29" t="n">
-        <v>0.277</v>
-      </c>
-      <c r="K115" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1433</v>
+      </c>
+      <c r="K115" s="31" t="n">
+        <v>-0.1049</v>
       </c>
       <c r="L115" s="28" t="inlineStr">
         <is>
-          <t>0.33~0.33%</t>
+          <t>0.54~1.34%</t>
         </is>
       </c>
       <c r="M115" s="32" t="inlineStr">
         <is>
-          <t>3해 연36.2% · 변동성 27.7% (위험대비 1.20) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.33% · 가장 나쁜 창 연36.2%</t>
+          <t>3해 연22.3% · 변동성 14.3% (위험대비 1.36) (달 간격) · 최대낙폭 -10% · 보수 0.54% · 가장 나쁜 창 연22.3%</t>
         </is>
       </c>
     </row>
@@ -9238,22 +9214,22 @@
       </c>
       <c r="C116" s="33" t="inlineStr">
         <is>
-          <t>현대머니마켓플렉스증권자투자신탁 1[채권](운용)</t>
+          <t>대신KOSPI200인덱스증권자투자신탁[주식](운용)</t>
         </is>
       </c>
       <c r="D116" s="33" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E116" s="33" t="inlineStr">
         <is>
-          <t>현대자산운용</t>
+          <t>대신자산운용</t>
         </is>
       </c>
       <c r="F116" s="34" t="inlineStr">
         <is>
-          <t>188억원</t>
+          <t>580억원</t>
         </is>
       </c>
       <c r="G116" s="35" t="inlineStr">
@@ -9263,28 +9239,26 @@
       </c>
       <c r="H116" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I116" s="36" t="n">
-        <v>0.0352</v>
+        <v>0.4877</v>
       </c>
       <c r="J116" s="36" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="K116" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.4041</v>
+      </c>
+      <c r="K116" s="37" t="n">
+        <v>-0.237</v>
       </c>
       <c r="L116" s="34" t="inlineStr">
         <is>
-          <t>0.10~0.40%</t>
+          <t>0.20~0.80%</t>
         </is>
       </c>
       <c r="M116" s="38" t="inlineStr">
         <is>
-          <t>5해 연3.5% · 변동성 0.2% (위험대비 3.94) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연2.7%</t>
+          <t>3해 연48.8% · 변동성 40.4% (위험대비 1.14) (달 간격) · 최대낙폭 -24% · 보수 0.20% · 가장 나쁜 창 연48.8%</t>
         </is>
       </c>
     </row>
@@ -9301,22 +9275,22 @@
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>키움더드림단기채증권투자신탁[채권]</t>
+          <t>BNKK200인덱스증권투자신탁(주식-파생형)</t>
         </is>
       </c>
       <c r="D117" s="14" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
+          <t>비엔케이자산운용</t>
         </is>
       </c>
       <c r="F117" s="28" t="inlineStr">
         <is>
-          <t>1조원</t>
+          <t>515억원</t>
         </is>
       </c>
       <c r="G117" s="30" t="inlineStr">
@@ -9326,28 +9300,26 @@
       </c>
       <c r="H117" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I117" s="29" t="n">
-        <v>0.0373</v>
+        <v>0.4905</v>
       </c>
       <c r="J117" s="29" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="K117" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.408</v>
+      </c>
+      <c r="K117" s="31" t="n">
+        <v>-0.2376</v>
       </c>
       <c r="L117" s="28" t="inlineStr">
         <is>
-          <t>0.07~0.33%</t>
+          <t>0.17~0.95%</t>
         </is>
       </c>
       <c r="M117" s="32" t="inlineStr">
         <is>
-          <t>5해 연3.7% · 변동성 0.3% (위험대비 2.79) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.07% · 가장 나쁜 창 연2.7%</t>
+          <t>3해 연49.0% · 변동성 40.8% (위험대비 1.13) (달 간격) · 최대낙폭 -24% · 보수 0.17% · 가장 나쁜 창 연49.0%</t>
         </is>
       </c>
     </row>
@@ -9364,22 +9336,22 @@
       </c>
       <c r="C118" s="33" t="inlineStr">
         <is>
-          <t>유경공모부동산투자신탁3(운용)</t>
+          <t>미래에셋퇴직플랜KRX100인덱스증권자투자신탁 1(주식혼합)</t>
         </is>
       </c>
       <c r="D118" s="33" t="inlineStr">
         <is>
-          <t>국내대체</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E118" s="33" t="inlineStr">
         <is>
-          <t>유경피에스지자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F118" s="34" t="inlineStr">
         <is>
-          <t>1,021억원</t>
+          <t>186억원</t>
         </is>
       </c>
       <c r="G118" s="35" t="inlineStr">
@@ -9389,28 +9361,26 @@
       </c>
       <c r="H118" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I118" s="36" t="n">
-        <v>0.0369</v>
+        <v>0.2895</v>
       </c>
       <c r="J118" s="36" t="n">
-        <v>0.0037</v>
-      </c>
-      <c r="K118" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.2318</v>
+      </c>
+      <c r="K118" s="37" t="n">
+        <v>-0.1349</v>
       </c>
       <c r="L118" s="34" t="inlineStr">
         <is>
-          <t>0.27~0.46%</t>
+          <t>0.44~0.65%</t>
         </is>
       </c>
       <c r="M118" s="38" t="inlineStr">
         <is>
-          <t>5해 연3.7% · 변동성 0.4% (위험대비 2.38) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.27% · 가장 나쁜 창 연0.9%</t>
+          <t>3해 연28.9% · 변동성 23.2% (위험대비 1.13) (달 간격) · 최대낙폭 -13% · 보수 0.44% · 가장 나쁜 창 연28.9%</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9397,7 @@
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>마이다스K200인덱스알파증권자투자신탁(주식-파생형)(운용)</t>
+          <t>신영마라톤지주회사증권자투자신탁(주식)운용</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
@@ -9437,12 +9407,12 @@
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>마이다스에셋자산운용</t>
+          <t>신영자산운용</t>
         </is>
       </c>
       <c r="F119" s="28" t="inlineStr">
         <is>
-          <t>493억원</t>
+          <t>316억원</t>
         </is>
       </c>
       <c r="G119" s="30" t="inlineStr">
@@ -9456,24 +9426,22 @@
         </is>
       </c>
       <c r="I119" s="29" t="n">
-        <v>0.5527000000000001</v>
+        <v>0.4483</v>
       </c>
       <c r="J119" s="29" t="n">
-        <v>0.4133</v>
-      </c>
-      <c r="K119" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.3544</v>
+      </c>
+      <c r="K119" s="31" t="n">
+        <v>-0.2314</v>
       </c>
       <c r="L119" s="28" t="inlineStr">
         <is>
-          <t>0.06~0.15%</t>
+          <t>0.52~1.49%</t>
         </is>
       </c>
       <c r="M119" s="32" t="inlineStr">
         <is>
-          <t>3해 연55.3% · 변동성 41.3% (위험대비 1.27) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.06% · 가장 나쁜 창 연55.3%</t>
+          <t>3해 연44.8% · 변동성 35.4% (위험대비 1.19) (달 간격) · 최대낙폭 -23% · 보수 0.52% · 가장 나쁜 창 연44.8%</t>
         </is>
       </c>
     </row>
@@ -9490,22 +9458,22 @@
       </c>
       <c r="C120" s="33" t="inlineStr">
         <is>
-          <t>신한코리아인덱스증권투자신탁[주식-파생형](종류)</t>
+          <t>KB퇴직연금배당40증권자투자신탁(채권혼합)</t>
         </is>
       </c>
       <c r="D120" s="33" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E120" s="33" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F120" s="34" t="inlineStr">
         <is>
-          <t>3,697억원</t>
+          <t>1조원</t>
         </is>
       </c>
       <c r="G120" s="35" t="inlineStr">
@@ -9519,24 +9487,22 @@
         </is>
       </c>
       <c r="I120" s="36" t="n">
-        <v>0.5354</v>
+        <v>0.1845</v>
       </c>
       <c r="J120" s="36" t="n">
-        <v>0.4193</v>
-      </c>
-      <c r="K120" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1429</v>
+      </c>
+      <c r="K120" s="37" t="n">
+        <v>-0.0965</v>
       </c>
       <c r="L120" s="34" t="inlineStr">
         <is>
-          <t>0.08~0.10%</t>
+          <t>0.46~0.80%</t>
         </is>
       </c>
       <c r="M120" s="38" t="inlineStr">
         <is>
-          <t>3해 연53.5% · 변동성 41.9% (위험대비 1.21) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.08% · 가장 나쁜 창 연53.5%</t>
+          <t>3해 연18.4% · 변동성 14.3% (위험대비 1.09) (달 간격) · 최대낙폭 -10% · 보수 0.46% · 가장 나쁜 창 연18.4%</t>
         </is>
       </c>
     </row>
@@ -9553,22 +9519,22 @@
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>유리빠른환매미국성장주증권투자신탁[주식-재간접형]운용</t>
+          <t>KB퇴직연금배당증권자투자신탁(주식)(운용)</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>유리자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F121" s="28" t="inlineStr">
         <is>
-          <t>547억원</t>
+          <t>1,688억원</t>
         </is>
       </c>
       <c r="G121" s="30" t="inlineStr">
@@ -9582,24 +9548,22 @@
         </is>
       </c>
       <c r="I121" s="29" t="n">
-        <v>0.2627</v>
+        <v>0.522</v>
       </c>
       <c r="J121" s="29" t="n">
-        <v>0.214</v>
-      </c>
-      <c r="K121" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.3632</v>
+      </c>
+      <c r="K121" s="31" t="n">
+        <v>-0.2298</v>
       </c>
       <c r="L121" s="28" t="inlineStr">
         <is>
-          <t>0.39~1.34%</t>
+          <t>0.71~1.20%</t>
         </is>
       </c>
       <c r="M121" s="32" t="inlineStr">
         <is>
-          <t>3해 연26.3% · 변동성 21.4% (위험대비 1.10) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.39% · 가장 나쁜 창 연26.3%</t>
+          <t>3해 연52.2% · 변동성 36.3% (위험대비 1.36) (달 간격) · 최대낙폭 -23% · 보수 0.71% · 가장 나쁜 창 연52.2%</t>
         </is>
       </c>
     </row>
@@ -9616,7 +9580,7 @@
       </c>
       <c r="C122" s="33" t="inlineStr">
         <is>
-          <t>iM에셋ALL바른ESG단기채증권투자신탁(채권)</t>
+          <t>BNK내일환매초단기채증권자투자신탁(채권)</t>
         </is>
       </c>
       <c r="D122" s="33" t="inlineStr">
@@ -9626,12 +9590,12 @@
       </c>
       <c r="E122" s="33" t="inlineStr">
         <is>
-          <t>아이엠에셋자산운용</t>
+          <t>비엔케이자산운용</t>
         </is>
       </c>
       <c r="F122" s="34" t="inlineStr">
         <is>
-          <t>266억원</t>
+          <t>182억원</t>
         </is>
       </c>
       <c r="G122" s="35" t="inlineStr">
@@ -9645,24 +9609,22 @@
         </is>
       </c>
       <c r="I122" s="36" t="n">
-        <v>0.0377</v>
+        <v>0.0027</v>
       </c>
       <c r="J122" s="36" t="n">
-        <v>0.0026</v>
-      </c>
-      <c r="K122" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.0333</v>
+      </c>
+      <c r="K122" s="37" t="n">
+        <v>-0.03759999999999999</v>
       </c>
       <c r="L122" s="34" t="inlineStr">
         <is>
-          <t>0.12~0.41%</t>
+          <t>0.10~0.29%</t>
         </is>
       </c>
       <c r="M122" s="38" t="inlineStr">
         <is>
-          <t>3해 연3.8% · 변동성 0.3% (위험대비 3.69) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.12% · 가장 나쁜 창 연2.8%</t>
+          <t>3해 연0.3% · 변동성 3.3% (위험대비 -0.76) (달 간격) · 최대낙폭 -4% · 보수 0.10% · 가장 나쁜 창 연0.3%</t>
         </is>
       </c>
     </row>
@@ -9679,22 +9641,22 @@
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>흥국내일드림초단기채증권투자신탁[채권]</t>
+          <t>미래에셋소득공제장기배당커버드콜액티브증권전환형자투자신탁 1(주식혼합)</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>흥국자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F123" s="28" t="inlineStr">
         <is>
-          <t>512억원</t>
+          <t>259억원</t>
         </is>
       </c>
       <c r="G123" s="30" t="inlineStr">
@@ -9708,22 +9670,22 @@
         </is>
       </c>
       <c r="I123" s="29" t="n">
-        <v>0.0358</v>
+        <v>0.3794</v>
       </c>
       <c r="J123" s="29" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="K123" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L123" s="39" t="n">
-        <v>0.0015</v>
+        <v>0.2821</v>
+      </c>
+      <c r="K123" s="31" t="n">
+        <v>-0.2063</v>
+      </c>
+      <c r="L123" s="28" t="inlineStr">
+        <is>
+          <t>0.56~1.04%</t>
+        </is>
       </c>
       <c r="M123" s="32" t="inlineStr">
         <is>
-          <t>3해 연3.6% · 변동성 0.2% (위험대비 4.81) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.15% · 가장 나쁜 창 연2.9%</t>
+          <t>3해 연37.9% · 변동성 28.2% (위험대비 1.25) (달 간격) · 최대낙폭 -21% · 보수 0.56% · 가장 나쁜 창 연37.9%</t>
         </is>
       </c>
     </row>
@@ -9740,7 +9702,7 @@
       </c>
       <c r="C124" s="33" t="inlineStr">
         <is>
-          <t>DB해오름인덱스알파증권투자회사[주식-파생형]운용</t>
+          <t>키움코리아인덱스증권자투자신탁 1[주식]</t>
         </is>
       </c>
       <c r="D124" s="33" t="inlineStr">
@@ -9750,12 +9712,12 @@
       </c>
       <c r="E124" s="33" t="inlineStr">
         <is>
-          <t>디비자산운용</t>
+          <t>키움투자자산운용</t>
         </is>
       </c>
       <c r="F124" s="34" t="inlineStr">
         <is>
-          <t>408억원</t>
+          <t>131억원</t>
         </is>
       </c>
       <c r="G124" s="35" t="inlineStr">
@@ -9769,24 +9731,22 @@
         </is>
       </c>
       <c r="I124" s="36" t="n">
-        <v>0.5334</v>
+        <v>0.4842</v>
       </c>
       <c r="J124" s="36" t="n">
-        <v>0.4216</v>
-      </c>
-      <c r="K124" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.4086</v>
+      </c>
+      <c r="K124" s="37" t="n">
+        <v>-0.2355</v>
       </c>
       <c r="L124" s="34" t="inlineStr">
         <is>
-          <t>0.15~0.84%</t>
+          <t>0.21~1.22%</t>
         </is>
       </c>
       <c r="M124" s="38" t="inlineStr">
         <is>
-          <t>3해 연53.3% · 변동성 42.2% (위험대비 1.20) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.15% · 가장 나쁜 창 연53.3%</t>
+          <t>3해 연48.4% · 변동성 40.9% (위험대비 1.12) (달 간격) · 최대낙폭 -24% · 보수 0.21% · 가장 나쁜 창 연48.4%</t>
         </is>
       </c>
     </row>
@@ -9803,22 +9763,22 @@
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>KB스타단기채증권자투자신탁(채권)(운용)</t>
+          <t>DB진주찾기증권자투자신탁 1[주식]_운용</t>
         </is>
       </c>
       <c r="D125" s="14" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>디비자산운용</t>
         </is>
       </c>
       <c r="F125" s="28" t="inlineStr">
         <is>
-          <t>662억원</t>
+          <t>226억원</t>
         </is>
       </c>
       <c r="G125" s="30" t="inlineStr">
@@ -9828,28 +9788,26 @@
       </c>
       <c r="H125" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I125" s="29" t="n">
-        <v>0.0338</v>
+        <v>0.4693</v>
       </c>
       <c r="J125" s="29" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="K125" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.3312</v>
+      </c>
+      <c r="K125" s="31" t="n">
+        <v>-0.1702</v>
       </c>
       <c r="L125" s="28" t="inlineStr">
         <is>
-          <t>0.11~0.28%</t>
+          <t>0.82~1.78%</t>
         </is>
       </c>
       <c r="M125" s="32" t="inlineStr">
         <is>
-          <t>5해 연3.4% · 변동성 0.2% (위험대비 2.59) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.11% · 가장 나쁜 창 연2.8%</t>
+          <t>3해 연46.9% · 변동성 33.1% (위험대비 1.33) (달 간격) · 최대낙폭 -17% · 보수 0.82% · 가장 나쁜 창 연46.9%</t>
         </is>
       </c>
     </row>
@@ -9866,7 +9824,7 @@
       </c>
       <c r="C126" s="33" t="inlineStr">
         <is>
-          <t>한국투자퇴직연금한국의힘증권자투자신탁 1(주식)</t>
+          <t>교보악사파워인덱스증권자투자신탁 2(주식)(운용)</t>
         </is>
       </c>
       <c r="D126" s="33" t="inlineStr">
@@ -9876,12 +9834,12 @@
       </c>
       <c r="E126" s="33" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
+          <t>교보악사자산운용</t>
         </is>
       </c>
       <c r="F126" s="34" t="inlineStr">
         <is>
-          <t>990억원</t>
+          <t>191억원</t>
         </is>
       </c>
       <c r="G126" s="35" t="inlineStr">
@@ -9895,24 +9853,22 @@
         </is>
       </c>
       <c r="I126" s="36" t="n">
-        <v>0.4576</v>
+        <v>0.4859000000000001</v>
       </c>
       <c r="J126" s="36" t="n">
-        <v>0.3896</v>
-      </c>
-      <c r="K126" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.4063000000000001</v>
+      </c>
+      <c r="K126" s="37" t="n">
+        <v>-0.2397</v>
       </c>
       <c r="L126" s="34" t="inlineStr">
         <is>
-          <t>0.39~1.20%</t>
+          <t>0.28~1.17%</t>
         </is>
       </c>
       <c r="M126" s="38" t="inlineStr">
         <is>
-          <t>3해 연45.8% · 변동성 39.0% (위험대비 1.10) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.39% · 가장 나쁜 창 연45.8%</t>
+          <t>3해 연48.6% · 변동성 40.6% (위험대비 1.13) (달 간격) · 최대낙폭 -24% · 보수 0.28% · 가장 나쁜 창 연48.6%</t>
         </is>
       </c>
     </row>
@@ -9929,22 +9885,22 @@
       </c>
       <c r="C127" s="14" t="inlineStr">
         <is>
-          <t>IBK단기채증권자투자신탁[채권]</t>
+          <t>iM에셋인덱스플러스증권자투자신탁 1(주식-파생형)</t>
         </is>
       </c>
       <c r="D127" s="14" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>아이비케이자산운용</t>
+          <t>아이엠에셋자산운용</t>
         </is>
       </c>
       <c r="F127" s="28" t="inlineStr">
         <is>
-          <t>1,196억원</t>
+          <t>136억원</t>
         </is>
       </c>
       <c r="G127" s="30" t="inlineStr">
@@ -9954,28 +9910,26 @@
       </c>
       <c r="H127" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I127" s="29" t="n">
-        <v>0.0356</v>
+        <v>0.481</v>
       </c>
       <c r="J127" s="29" t="n">
-        <v>0.0034</v>
-      </c>
-      <c r="K127" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.4089</v>
+      </c>
+      <c r="K127" s="31" t="n">
+        <v>-0.2383</v>
       </c>
       <c r="L127" s="28" t="inlineStr">
         <is>
-          <t>0.09~0.23%</t>
+          <t>0.04~0.52%</t>
         </is>
       </c>
       <c r="M127" s="32" t="inlineStr">
         <is>
-          <t>5해 연3.6% · 변동성 0.3% (위험대비 2.21) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.09% · 가장 나쁜 창 연2.6%</t>
+          <t>3해 연48.1% · 변동성 40.9% (위험대비 1.11) (달 간격) · 최대낙폭 -24% · 보수 0.04% · 가장 나쁜 창 연48.1%</t>
         </is>
       </c>
     </row>
@@ -9992,22 +9946,22 @@
       </c>
       <c r="C128" s="33" t="inlineStr">
         <is>
-          <t>웰컴베스트단기채증권투자신탁[채권형]</t>
+          <t>카디안코리아인덱스증권자투자신탁[주식]</t>
         </is>
       </c>
       <c r="D128" s="33" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E128" s="33" t="inlineStr">
         <is>
-          <t>웰컴자산운용</t>
+          <t>카디안자산운용</t>
         </is>
       </c>
       <c r="F128" s="34" t="inlineStr">
         <is>
-          <t>389억원</t>
+          <t>235억원</t>
         </is>
       </c>
       <c r="G128" s="35" t="inlineStr">
@@ -10021,24 +9975,22 @@
         </is>
       </c>
       <c r="I128" s="36" t="n">
-        <v>0.0348</v>
+        <v>0.4739</v>
       </c>
       <c r="J128" s="36" t="n">
-        <v>0.0021</v>
-      </c>
-      <c r="K128" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.4068</v>
+      </c>
+      <c r="K128" s="37" t="n">
+        <v>-0.2358</v>
       </c>
       <c r="L128" s="34" t="inlineStr">
         <is>
-          <t>0.13~0.29%</t>
+          <t>0.27~0.61%</t>
         </is>
       </c>
       <c r="M128" s="38" t="inlineStr">
         <is>
-          <t>3해 연3.5% · 변동성 0.2% (위험대비 3.19) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.13% · 가장 나쁜 창 연2.9%</t>
+          <t>3해 연47.4% · 변동성 40.7% (위험대비 1.10) (달 간격) · 최대낙폭 -24% · 보수 0.27% · 가장 나쁜 창 연47.4%</t>
         </is>
       </c>
     </row>
@@ -10055,22 +10007,22 @@
       </c>
       <c r="C129" s="14" t="inlineStr">
         <is>
-          <t>우리단기채권증권투자신탁(채권)</t>
+          <t>교보악사파워인덱스증권자투자신탁 1(주식)(운용)</t>
         </is>
       </c>
       <c r="D129" s="14" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>우리자산운용</t>
+          <t>교보악사자산운용</t>
         </is>
       </c>
       <c r="F129" s="28" t="inlineStr">
         <is>
-          <t>8,118억원</t>
+          <t>2,914억원</t>
         </is>
       </c>
       <c r="G129" s="30" t="inlineStr">
@@ -10080,28 +10032,26 @@
       </c>
       <c r="H129" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I129" s="29" t="n">
-        <v>0.0372</v>
+        <v>0.4796</v>
       </c>
       <c r="J129" s="29" t="n">
-        <v>0.0039</v>
-      </c>
-      <c r="K129" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.4089</v>
+      </c>
+      <c r="K129" s="31" t="n">
+        <v>-0.2396</v>
       </c>
       <c r="L129" s="28" t="inlineStr">
         <is>
-          <t>0.10~0.45%</t>
+          <t>0.17~1.28%</t>
         </is>
       </c>
       <c r="M129" s="32" t="inlineStr">
         <is>
-          <t>5해 연3.7% · 변동성 0.4% (위험대비 2.33) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연2.7%</t>
+          <t>3해 연48.0% · 변동성 40.9% (위험대비 1.10) (달 간격) · 최대낙폭 -24% · 보수 0.17% · 가장 나쁜 창 연48.0%</t>
         </is>
       </c>
     </row>
@@ -10118,22 +10068,22 @@
       </c>
       <c r="C130" s="33" t="inlineStr">
         <is>
-          <t>한화내일받는단기국공채증권자투자신탁(채권)</t>
+          <t>다올퇴직연금40증권자투자신탁[채권혼합](운)</t>
         </is>
       </c>
       <c r="D130" s="33" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E130" s="33" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>다올자산운용</t>
         </is>
       </c>
       <c r="F130" s="34" t="inlineStr">
         <is>
-          <t>3,825억원</t>
+          <t>193억원</t>
         </is>
       </c>
       <c r="G130" s="35" t="inlineStr">
@@ -10143,28 +10093,26 @@
       </c>
       <c r="H130" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I130" s="36" t="n">
-        <v>0.0317</v>
+        <v>0.1779</v>
       </c>
       <c r="J130" s="36" t="n">
-        <v>0.0022</v>
-      </c>
-      <c r="K130" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1425</v>
+      </c>
+      <c r="K130" s="37" t="n">
+        <v>-0.0872</v>
       </c>
       <c r="L130" s="34" t="inlineStr">
         <is>
-          <t>0.10~0.25%</t>
+          <t>0.53~0.80%</t>
         </is>
       </c>
       <c r="M130" s="38" t="inlineStr">
         <is>
-          <t>5해 연3.2% · 변동성 0.2% (위험대비 1.64) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연2.7%</t>
+          <t>3해 연17.8% · 변동성 14.2% (위험대비 1.05) (달 간격) · 최대낙폭 -9% · 보수 0.53% · 가장 나쁜 창 연17.8%</t>
         </is>
       </c>
     </row>
@@ -10181,22 +10129,22 @@
       </c>
       <c r="C131" s="14" t="inlineStr">
         <is>
-          <t>현대인베스트먼트단기증권자투자신탁 1(채권)</t>
+          <t>트러스톤인덱스알파증권자투자신탁[주식-파생형]</t>
         </is>
       </c>
       <c r="D131" s="14" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>현대인베스트먼트자산운용</t>
+          <t>트러스톤자산운용</t>
         </is>
       </c>
       <c r="F131" s="28" t="inlineStr">
         <is>
-          <t>915억원</t>
+          <t>326억원</t>
         </is>
       </c>
       <c r="G131" s="30" t="inlineStr">
@@ -10206,28 +10154,26 @@
       </c>
       <c r="H131" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I131" s="29" t="n">
-        <v>0.0315</v>
+        <v>0.478</v>
       </c>
       <c r="J131" s="29" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="K131" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.4094</v>
+      </c>
+      <c r="K131" s="31" t="n">
+        <v>-0.2398</v>
       </c>
       <c r="L131" s="28" t="inlineStr">
         <is>
-          <t>0.10~0.30%</t>
+          <t>0.10~0.89%</t>
         </is>
       </c>
       <c r="M131" s="32" t="inlineStr">
         <is>
-          <t>5해 연3.1% · 변동성 0.2% (위험대비 1.48) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.10% · 가장 나쁜 창 연2.7%</t>
+          <t>3해 연47.8% · 변동성 40.9% (위험대비 1.10) (달 간격) · 최대낙폭 -24% · 보수 0.10% · 가장 나쁜 창 연47.8%</t>
         </is>
       </c>
     </row>
@@ -10244,22 +10190,22 @@
       </c>
       <c r="C132" s="33" t="inlineStr">
         <is>
-          <t>신한누버거버먼미국가치주증권투자신탁(H)[주식-재간접형](종류)</t>
+          <t>삼성누버거버먼이머징단기채권증권자투자신탁H[채권-재간접형]</t>
         </is>
       </c>
       <c r="D132" s="33" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="E132" s="33" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>삼성자산운용</t>
         </is>
       </c>
       <c r="F132" s="34" t="inlineStr">
         <is>
-          <t>655억원</t>
+          <t>237억원</t>
         </is>
       </c>
       <c r="G132" s="35" t="inlineStr">
@@ -10273,24 +10219,22 @@
         </is>
       </c>
       <c r="I132" s="36" t="n">
-        <v>0.1494</v>
+        <v>0.0607</v>
       </c>
       <c r="J132" s="36" t="n">
-        <v>0.08990000000000001</v>
-      </c>
-      <c r="K132" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.0228</v>
+      </c>
+      <c r="K132" s="37" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="L132" s="34" t="inlineStr">
         <is>
-          <t>0.35~1.35%</t>
+          <t>0.23~1.13%</t>
         </is>
       </c>
       <c r="M132" s="38" t="inlineStr">
         <is>
-          <t>3해 연14.9% · 변동성 9.0% (위험대비 1.35) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.35% · 가장 나쁜 창 연14.9%</t>
+          <t>3해 연6.1% · 변동성 2.3% (위험대비 1.43) (달 간격) · 최대낙폭 -2% · 보수 0.23% · 가장 나쁜 창 연3.7%</t>
         </is>
       </c>
     </row>
@@ -10307,7 +10251,7 @@
       </c>
       <c r="C133" s="14" t="inlineStr">
         <is>
-          <t>신한미국S&amp;P500인덱스증권자투자신탁(H)[주식-파생형]</t>
+          <t>미래에셋MSCIAC월드인덱스증권자투자신탁(주식)(UH)</t>
         </is>
       </c>
       <c r="D133" s="14" t="inlineStr">
@@ -10317,12 +10261,12 @@
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F133" s="28" t="inlineStr">
         <is>
-          <t>1,207억원</t>
+          <t>133억원</t>
         </is>
       </c>
       <c r="G133" s="30" t="inlineStr">
@@ -10336,24 +10280,22 @@
         </is>
       </c>
       <c r="I133" s="29" t="n">
-        <v>0.1789</v>
+        <v>0.2023</v>
       </c>
       <c r="J133" s="29" t="n">
-        <v>0.1229</v>
-      </c>
-      <c r="K133" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1124</v>
+      </c>
+      <c r="K133" s="31" t="n">
+        <v>-0.08460000000000001</v>
       </c>
       <c r="L133" s="28" t="inlineStr">
         <is>
-          <t>0.14~1.15%</t>
+          <t>0.27~0.97%</t>
         </is>
       </c>
       <c r="M133" s="32" t="inlineStr">
         <is>
-          <t>3해 연17.9% · 변동성 12.3% (위험대비 1.23) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.14% · 가장 나쁜 창 연15.8%</t>
+          <t>3해 연20.2% · 변동성 11.2% (위험대비 1.55) (달 간격) · 최대낙폭 -8% · 보수 0.27% · 가장 나쁜 창 연19.1%</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10312,7 @@
       </c>
       <c r="C134" s="33" t="inlineStr">
         <is>
-          <t>삼성글로벌배당성장주증권자투자신탁H[주식]</t>
+          <t>피델리티재팬증권자투자신탁(주식-재간접형)</t>
         </is>
       </c>
       <c r="D134" s="33" t="inlineStr">
@@ -10380,12 +10322,12 @@
       </c>
       <c r="E134" s="33" t="inlineStr">
         <is>
-          <t>삼성자산운용</t>
+          <t>피델리티자산운용</t>
         </is>
       </c>
       <c r="F134" s="34" t="inlineStr">
         <is>
-          <t>278억원</t>
+          <t>156억원</t>
         </is>
       </c>
       <c r="G134" s="35" t="inlineStr">
@@ -10399,24 +10341,22 @@
         </is>
       </c>
       <c r="I134" s="36" t="n">
-        <v>0.1427</v>
+        <v>0.2701</v>
       </c>
       <c r="J134" s="36" t="n">
-        <v>0.08800000000000001</v>
-      </c>
-      <c r="K134" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1494</v>
+      </c>
+      <c r="K134" s="37" t="n">
+        <v>-0.0944</v>
       </c>
       <c r="L134" s="34" t="inlineStr">
         <is>
-          <t>0.49~1.49%</t>
+          <t>0.16~1.66%</t>
         </is>
       </c>
       <c r="M134" s="38" t="inlineStr">
         <is>
-          <t>3해 연14.3% · 변동성 8.8% (위험대비 1.30) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.49% · 가장 나쁜 창 연14.3%</t>
+          <t>3해 연27.0% · 변동성 14.9% (위험대비 1.62) (달 간격) · 최대낙폭 -9% · 보수 0.16% · 가장 나쁜 창 연27.0%</t>
         </is>
       </c>
     </row>
@@ -10433,7 +10373,7 @@
       </c>
       <c r="C135" s="14" t="inlineStr">
         <is>
-          <t>삼성글로벌배당성장주증권자투자신탁UH[주식]</t>
+          <t>피델리티글로벌배당인컴증권자투자신탁(주식-재간접형)</t>
         </is>
       </c>
       <c r="D135" s="14" t="inlineStr">
@@ -10443,12 +10383,12 @@
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>삼성자산운용</t>
+          <t>피델리티자산운용</t>
         </is>
       </c>
       <c r="F135" s="28" t="inlineStr">
         <is>
-          <t>133억원</t>
+          <t>5,716억원</t>
         </is>
       </c>
       <c r="G135" s="30" t="inlineStr">
@@ -10462,24 +10402,22 @@
         </is>
       </c>
       <c r="I135" s="29" t="n">
-        <v>0.1707</v>
+        <v>0.1371</v>
       </c>
       <c r="J135" s="29" t="n">
-        <v>0.1115</v>
-      </c>
-      <c r="K135" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.08130000000000001</v>
+      </c>
+      <c r="K135" s="31" t="n">
+        <v>-0.0654</v>
       </c>
       <c r="L135" s="28" t="inlineStr">
         <is>
-          <t>0.49~1.49%</t>
+          <t>0.16~1.36%</t>
         </is>
       </c>
       <c r="M135" s="32" t="inlineStr">
         <is>
-          <t>3해 연17.1% · 변동성 11.2% (위험대비 1.28) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.49% · 가장 나쁜 창 연17.0%</t>
+          <t>3해 연13.7% · 변동성 8.1% (위험대비 1.34) (달 간격) · 최대낙폭 -7% · 보수 0.16% · 가장 나쁜 창 연13.2%</t>
         </is>
       </c>
     </row>
@@ -10496,22 +10434,22 @@
       </c>
       <c r="C136" s="33" t="inlineStr">
         <is>
-          <t>미래에셋연금동행TRF성장형혼합자산투자신탁(재간접형)</t>
+          <t>KB연금미국S&amp;P500인덱스증권자투자신탁(주식-파생형)(H)(운용)</t>
         </is>
       </c>
       <c r="D136" s="33" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E136" s="33" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F136" s="34" t="inlineStr">
         <is>
-          <t>1,276억원</t>
+          <t>1,626억원</t>
         </is>
       </c>
       <c r="G136" s="35" t="inlineStr">
@@ -10525,24 +10463,22 @@
         </is>
       </c>
       <c r="I136" s="36" t="n">
-        <v>0.1715</v>
+        <v>0.2086</v>
       </c>
       <c r="J136" s="36" t="n">
-        <v>0.1271</v>
-      </c>
-      <c r="K136" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1193</v>
+      </c>
+      <c r="K136" s="37" t="n">
+        <v>-0.08380000000000001</v>
       </c>
       <c r="L136" s="34" t="inlineStr">
         <is>
-          <t>0.55~0.81%</t>
+          <t>0.67~1.23%</t>
         </is>
       </c>
       <c r="M136" s="38" t="inlineStr">
         <is>
-          <t>3해 연17.1% · 변동성 12.7% (위험대비 1.13) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.55% · 가장 나쁜 창 연17.1%</t>
+          <t>3해 연20.9% · 변동성 11.9% (위험대비 1.51) (달 간격) · 최대낙폭 -8% · 보수 0.67% · 가장 나쁜 창 연20.9%</t>
         </is>
       </c>
     </row>
@@ -10559,22 +10495,22 @@
       </c>
       <c r="C137" s="14" t="inlineStr">
         <is>
-          <t>미래에셋글로벌자산배분밸런스형증권투자신탁(혼합-재간접형)(UH)</t>
+          <t>신한누버거버먼미국가치주증권투자신탁(H)[주식-재간접형](종류)</t>
         </is>
       </c>
       <c r="D137" s="14" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F137" s="28" t="inlineStr">
         <is>
-          <t>231억원</t>
+          <t>655억원</t>
         </is>
       </c>
       <c r="G137" s="30" t="inlineStr">
@@ -10588,24 +10524,22 @@
         </is>
       </c>
       <c r="I137" s="29" t="n">
-        <v>0.1788</v>
+        <v>0.1478</v>
       </c>
       <c r="J137" s="29" t="n">
-        <v>0.1303</v>
-      </c>
-      <c r="K137" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1007</v>
+      </c>
+      <c r="K137" s="31" t="n">
+        <v>-0.0694</v>
       </c>
       <c r="L137" s="28" t="inlineStr">
         <is>
-          <t>0.40~1.20%</t>
+          <t>0.35~1.35%</t>
         </is>
       </c>
       <c r="M137" s="32" t="inlineStr">
         <is>
-          <t>3해 연17.9% · 변동성 13.0% (위험대비 1.16) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.40% · 가장 나쁜 창 연14.4%</t>
+          <t>3해 연14.8% · 변동성 10.1% (위험대비 1.19) (달 간격) · 최대낙폭 -7% · 보수 0.35% · 가장 나쁜 창 연14.8%</t>
         </is>
       </c>
     </row>
@@ -10622,7 +10556,7 @@
       </c>
       <c r="C138" s="33" t="inlineStr">
         <is>
-          <t>KB타겟리턴적극형OCIO증권투자신탁(혼합-재간접형)(운용)</t>
+          <t>NH-AmundiSignatureOCIO성장형증권자투자신탁(UH)[혼합-재간접형]</t>
         </is>
       </c>
       <c r="D138" s="33" t="inlineStr">
@@ -10632,12 +10566,12 @@
       </c>
       <c r="E138" s="33" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>엔에이치아문디자산운용</t>
         </is>
       </c>
       <c r="F138" s="34" t="inlineStr">
         <is>
-          <t>234억원</t>
+          <t>155억원</t>
         </is>
       </c>
       <c r="G138" s="35" t="inlineStr">
@@ -10651,24 +10585,22 @@
         </is>
       </c>
       <c r="I138" s="36" t="n">
-        <v>0.1491</v>
+        <v>0.1817</v>
       </c>
       <c r="J138" s="36" t="n">
-        <v>0.1131</v>
-      </c>
-      <c r="K138" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="K138" s="37" t="n">
+        <v>-0.0814</v>
       </c>
       <c r="L138" s="34" t="inlineStr">
         <is>
-          <t>0.55~0.82%</t>
+          <t>0.79~1.39%</t>
         </is>
       </c>
       <c r="M138" s="38" t="inlineStr">
         <is>
-          <t>3해 연14.9% · 변동성 11.3% (위험대비 1.07) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.55% · 가장 나쁜 창 연14.9%</t>
+          <t>3해 연18.2% · 변동성 9.9% (위험대비 1.56) (달 간격) · 최대낙폭 -8% · 보수 0.79% · 가장 나쁜 창 연16.7%</t>
         </is>
       </c>
     </row>
@@ -10685,22 +10617,22 @@
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>NH-AmundiSignatureOCIO성장형증권자투자신탁(UH)[혼합-재간접형]</t>
+          <t>AB셀렉트미국증권투자신탁(주식-재간접형)</t>
         </is>
       </c>
       <c r="D139" s="14" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>엔에이치아문디자산운용</t>
+          <t>얼라이언스번스틴자산운용</t>
         </is>
       </c>
       <c r="F139" s="28" t="inlineStr">
         <is>
-          <t>155억원</t>
+          <t>305억원</t>
         </is>
       </c>
       <c r="G139" s="30" t="inlineStr">
@@ -10714,24 +10646,22 @@
         </is>
       </c>
       <c r="I139" s="29" t="n">
-        <v>0.1797</v>
+        <v>0.1761</v>
       </c>
       <c r="J139" s="29" t="n">
-        <v>0.1123</v>
-      </c>
-      <c r="K139" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1169</v>
+      </c>
+      <c r="K139" s="31" t="n">
+        <v>-0.07870000000000001</v>
       </c>
       <c r="L139" s="28" t="inlineStr">
         <is>
-          <t>0.79~1.39%</t>
+          <t>0.27~1.56%</t>
         </is>
       </c>
       <c r="M139" s="32" t="inlineStr">
         <is>
-          <t>3해 연18.0% · 변동성 11.2% (위험대비 1.35) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.79% · 가장 나쁜 창 연13.7%</t>
+          <t>3해 연17.6% · 변동성 11.7% (위험대비 1.27) (달 간격) · 최대낙폭 -8% · 보수 0.27% · 가장 나쁜 창 연14.5%</t>
         </is>
       </c>
     </row>
@@ -10748,22 +10678,22 @@
       </c>
       <c r="C140" s="33" t="inlineStr">
         <is>
-          <t>NH-AmundiSignatureOCIO성장형증권자투자신탁(H)[혼합-재간접형]</t>
+          <t>AB글로벌고수익증권투자신탁(채권-재간접형)</t>
         </is>
       </c>
       <c r="D140" s="33" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="E140" s="33" t="inlineStr">
         <is>
-          <t>엔에이치아문디자산운용</t>
+          <t>얼라이언스번스틴자산운용</t>
         </is>
       </c>
       <c r="F140" s="34" t="inlineStr">
         <is>
-          <t>356억원</t>
+          <t>1,629억원</t>
         </is>
       </c>
       <c r="G140" s="35" t="inlineStr">
@@ -10777,24 +10707,22 @@
         </is>
       </c>
       <c r="I140" s="36" t="n">
-        <v>0.1486</v>
+        <v>0.0614</v>
       </c>
       <c r="J140" s="36" t="n">
-        <v>0.09910000000000001</v>
-      </c>
-      <c r="K140" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.04389999999999999</v>
+      </c>
+      <c r="K140" s="37" t="n">
+        <v>-0.026</v>
       </c>
       <c r="L140" s="34" t="inlineStr">
         <is>
-          <t>0.79~1.39%</t>
+          <t>0.17~1.17%</t>
         </is>
       </c>
       <c r="M140" s="38" t="inlineStr">
         <is>
-          <t>3해 연14.9% · 변동성 9.9% (위험대비 1.22) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.79% · 가장 나쁜 창 연14.3%</t>
+          <t>3해 연6.1% · 변동성 4.4% (위험대비 0.76) (달 간격) · 최대낙폭 -3% · 보수 0.17% · 가장 나쁜 창 연2.9%</t>
         </is>
       </c>
     </row>
@@ -10811,22 +10739,22 @@
       </c>
       <c r="C141" s="14" t="inlineStr">
         <is>
-          <t>iM에셋디딤코어EMP증권투자신탁(혼합-재간접형)</t>
+          <t>미래에셋미국배당커버드콜액티브증권자투자신탁(주식)(H)</t>
         </is>
       </c>
       <c r="D141" s="14" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>아이엠에셋자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F141" s="28" t="inlineStr">
         <is>
-          <t>217억원</t>
+          <t>234억원</t>
         </is>
       </c>
       <c r="G141" s="30" t="inlineStr">
@@ -10840,24 +10768,22 @@
         </is>
       </c>
       <c r="I141" s="29" t="n">
-        <v>0.1115</v>
+        <v>0.165</v>
       </c>
       <c r="J141" s="29" t="n">
-        <v>0.0873</v>
-      </c>
-      <c r="K141" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1046</v>
+      </c>
+      <c r="K141" s="31" t="n">
+        <v>-0.0725</v>
       </c>
       <c r="L141" s="28" t="inlineStr">
         <is>
-          <t>0.54~1.46%</t>
+          <t>0.66~1.86%</t>
         </is>
       </c>
       <c r="M141" s="32" t="inlineStr">
         <is>
-          <t>3해 연11.2% · 변동성 8.7% (위험대비 0.96) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.54% · 가장 나쁜 창 연11.2%</t>
+          <t>3해 연16.5% · 변동성 10.5% (위험대비 1.31) (달 간격) · 최대낙폭 -7% · 보수 0.66% · 가장 나쁜 창 연16.1%</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10800,7 @@
       </c>
       <c r="C142" s="33" t="inlineStr">
         <is>
-          <t>AB셀렉트미국증권투자신탁(주식-재간접형)</t>
+          <t>신한동유럽플러스증권자투자신탁(H)[주식](종류)</t>
         </is>
       </c>
       <c r="D142" s="33" t="inlineStr">
@@ -10884,12 +10810,12 @@
       </c>
       <c r="E142" s="33" t="inlineStr">
         <is>
-          <t>얼라이언스번스틴자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F142" s="34" t="inlineStr">
         <is>
-          <t>305억원</t>
+          <t>139억원</t>
         </is>
       </c>
       <c r="G142" s="35" t="inlineStr">
@@ -10899,28 +10825,26 @@
       </c>
       <c r="H142" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I142" s="36" t="n">
-        <v>0.1012</v>
+        <v>0.2581</v>
       </c>
       <c r="J142" s="36" t="n">
-        <v>0.1016</v>
-      </c>
-      <c r="K142" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1049</v>
+      </c>
+      <c r="K142" s="37" t="n">
+        <v>-0.0503</v>
       </c>
       <c r="L142" s="34" t="inlineStr">
         <is>
-          <t>0.27~1.56%</t>
+          <t>1.11~1.86%</t>
         </is>
       </c>
       <c r="M142" s="38" t="inlineStr">
         <is>
-          <t>5해 연10.1% · 변동성 10.2% (위험대비 0.72) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.27% · 가장 나쁜 창 연10.1%</t>
+          <t>3해 연25.8% · 변동성 10.5% (위험대비 2.19) (달 간격) · 최대낙폭 -5% · 보수 1.11% · 가장 나쁜 창 연23.3%</t>
         </is>
       </c>
     </row>
@@ -10937,22 +10861,22 @@
       </c>
       <c r="C143" s="14" t="inlineStr">
         <is>
-          <t>피델리티재팬증권자투자신탁(주식-재간접형)</t>
+          <t>키움슈로더글로벌타겟리턴증권투자신탁(주식혼합-재간접형)</t>
         </is>
       </c>
       <c r="D143" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>피델리티자산운용</t>
+          <t>키움투자자산운용</t>
         </is>
       </c>
       <c r="F143" s="28" t="inlineStr">
         <is>
-          <t>156억원</t>
+          <t>125억원</t>
         </is>
       </c>
       <c r="G143" s="30" t="inlineStr">
@@ -10962,28 +10886,26 @@
       </c>
       <c r="H143" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I143" s="29" t="n">
-        <v>0.2139</v>
+        <v>0.1092</v>
       </c>
       <c r="J143" s="29" t="n">
-        <v>0.2143</v>
-      </c>
-      <c r="K143" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.0526</v>
+      </c>
+      <c r="K143" s="31" t="n">
+        <v>-0.0353</v>
       </c>
       <c r="L143" s="28" t="inlineStr">
         <is>
-          <t>0.16~1.66%</t>
+          <t>0.76~1.66%</t>
         </is>
       </c>
       <c r="M143" s="32" t="inlineStr">
         <is>
-          <t>5해 연21.4% · 변동성 21.4% (위험대비 0.87) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.16% · 가장 나쁜 창 연21.4%</t>
+          <t>3해 연10.9% · 변동성 5.3% (위험대비 1.54) (달 간격) · 최대낙폭 -4% · 보수 0.76% · 가장 나쁜 창 연10.9%</t>
         </is>
       </c>
     </row>
@@ -11000,7 +10922,7 @@
       </c>
       <c r="C144" s="33" t="inlineStr">
         <is>
-          <t>한화단기하이일드증권자투자신탁(채권)</t>
+          <t>삼성누버거버먼이머징국공채플러스증권자투자신탁H[채권-재간접형]</t>
         </is>
       </c>
       <c r="D144" s="33" t="inlineStr">
@@ -11010,12 +10932,12 @@
       </c>
       <c r="E144" s="33" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>삼성자산운용</t>
         </is>
       </c>
       <c r="F144" s="34" t="inlineStr">
         <is>
-          <t>169억원</t>
+          <t>502억원</t>
         </is>
       </c>
       <c r="G144" s="35" t="inlineStr">
@@ -11025,28 +10947,26 @@
       </c>
       <c r="H144" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I144" s="36" t="n">
-        <v>0.0351</v>
+        <v>0.1075</v>
       </c>
       <c r="J144" s="36" t="n">
-        <v>0.0151</v>
-      </c>
-      <c r="K144" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.0621</v>
+      </c>
+      <c r="K144" s="37" t="n">
+        <v>-0.0391</v>
       </c>
       <c r="L144" s="34" t="inlineStr">
         <is>
-          <t>0.71~1.71%</t>
+          <t>0.23~1.13%</t>
         </is>
       </c>
       <c r="M144" s="38" t="inlineStr">
         <is>
-          <t>5해 연3.5% · 변동성 1.5% (위험대비 0.46) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.71% · 가장 나쁜 창 연3.4%</t>
+          <t>3해 연10.8% · 변동성 6.2% (위험대비 1.28) (달 간격) · 최대낙폭 -4% · 보수 0.23% · 가장 나쁜 창 연8.1%</t>
         </is>
       </c>
     </row>
@@ -11063,22 +10983,22 @@
       </c>
       <c r="C145" s="14" t="inlineStr">
         <is>
-          <t>피델리티글로벌배당인컴증권자투자신탁(주식-재간접형)</t>
+          <t>베어링월지급글로벌하이일드증권자투자신탁[H](채권-재간접형)</t>
         </is>
       </c>
       <c r="D145" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>피델리티자산운용</t>
+          <t>베어링자산운용</t>
         </is>
       </c>
       <c r="F145" s="28" t="inlineStr">
         <is>
-          <t>5,716억원</t>
+          <t>496억원</t>
         </is>
       </c>
       <c r="G145" s="30" t="inlineStr">
@@ -11088,28 +11008,26 @@
       </c>
       <c r="H145" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I145" s="29" t="n">
-        <v>0.08</v>
+        <v>0.06480000000000001</v>
       </c>
       <c r="J145" s="29" t="n">
-        <v>0.08839999999999999</v>
-      </c>
-      <c r="K145" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.0339</v>
+      </c>
+      <c r="K145" s="31" t="n">
+        <v>-0.0218</v>
       </c>
       <c r="L145" s="28" t="inlineStr">
         <is>
-          <t>0.16~1.36%</t>
+          <t>0.49~1.19%</t>
         </is>
       </c>
       <c r="M145" s="32" t="inlineStr">
         <is>
-          <t>5해 연8.0% · 변동성 8.8% (위험대비 0.59) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.16% · 가장 나쁜 창 연8.0%</t>
+          <t>3해 연6.5% · 변동성 3.4% (위험대비 1.08) (달 간격) · 최대낙폭 -2% · 보수 0.49% · 가장 나쁜 창 연3.7%</t>
         </is>
       </c>
     </row>
@@ -11126,22 +11044,22 @@
       </c>
       <c r="C146" s="33" t="inlineStr">
         <is>
-          <t>한화연금단기하이일드증권자투자신탁(채권)</t>
+          <t>NH-AmundiSignatureOCIO성장형증권자투자신탁(H)[혼합-재간접형]</t>
         </is>
       </c>
       <c r="D146" s="33" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E146" s="33" t="inlineStr">
         <is>
-          <t>한화자산운용</t>
+          <t>엔에이치아문디자산운용</t>
         </is>
       </c>
       <c r="F146" s="34" t="inlineStr">
         <is>
-          <t>172억원</t>
+          <t>356억원</t>
         </is>
       </c>
       <c r="G146" s="35" t="inlineStr">
@@ -11151,28 +11069,26 @@
       </c>
       <c r="H146" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I146" s="36" t="n">
-        <v>0.035</v>
+        <v>0.1396</v>
       </c>
       <c r="J146" s="36" t="n">
-        <v>0.0156</v>
-      </c>
-      <c r="K146" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.0975</v>
+      </c>
+      <c r="K146" s="37" t="n">
+        <v>-0.07240000000000001</v>
       </c>
       <c r="L146" s="34" t="inlineStr">
         <is>
-          <t>0.71~0.97%</t>
+          <t>0.79~1.39%</t>
         </is>
       </c>
       <c r="M146" s="38" t="inlineStr">
         <is>
-          <t>5해 연3.5% · 변동성 1.6% (위험대비 0.44) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.71% · 가장 나쁜 창 연3.4%</t>
+          <t>3해 연14.0% · 변동성 9.8% (위험대비 1.14) (달 간격) · 최대낙폭 -7% · 보수 0.79% · 가장 나쁜 창 연14.0%</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11105,7 @@
       </c>
       <c r="C147" s="14" t="inlineStr">
         <is>
-          <t>iM에셋월드에너지증권자투자신탁(주식-재간접형)(H)</t>
+          <t>한화천연자원증권자투자신탁(주식)</t>
         </is>
       </c>
       <c r="D147" s="14" t="inlineStr">
@@ -11199,12 +11115,12 @@
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>아이엠에셋자산운용</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="F147" s="28" t="inlineStr">
         <is>
-          <t>288억원</t>
+          <t>1,120억원</t>
         </is>
       </c>
       <c r="G147" s="30" t="inlineStr">
@@ -11214,28 +11130,26 @@
       </c>
       <c r="H147" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I147" s="29" t="n">
-        <v>0.2359</v>
+        <v>0.2396</v>
       </c>
       <c r="J147" s="29" t="n">
-        <v>0.1806</v>
-      </c>
-      <c r="K147" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1608</v>
+      </c>
+      <c r="K147" s="31" t="n">
+        <v>-0.08460000000000001</v>
       </c>
       <c r="L147" s="28" t="inlineStr">
         <is>
-          <t>0.56~1.66%</t>
+          <t>0.94~2.44%</t>
         </is>
       </c>
       <c r="M147" s="32" t="inlineStr">
         <is>
-          <t>5해 연23.6% · 변동성 18.1% (위험대비 1.15) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.56% · 가장 나쁜 창 연14.4%</t>
+          <t>3해 연24.0% · 변동성 16.1% (위험대비 1.32) (달 간격) · 최대낙폭 -8% · 보수 0.94% · 가장 나쁜 창 연24.0%</t>
         </is>
       </c>
     </row>
@@ -11252,22 +11166,22 @@
       </c>
       <c r="C148" s="33" t="inlineStr">
         <is>
-          <t>한국투자글로벌AI&amp;반도체TOP10증권자투자신탁UH(주식)(모)</t>
+          <t>우리PIMCO분산투자증권자투자신탁[채권_재간접형](H)운용</t>
         </is>
       </c>
       <c r="D148" s="33" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="E148" s="33" t="inlineStr">
         <is>
-          <t>한국투자신탁운용</t>
+          <t>우리자산운용</t>
         </is>
       </c>
       <c r="F148" s="34" t="inlineStr">
         <is>
-          <t>1,620억원</t>
+          <t>292억원</t>
         </is>
       </c>
       <c r="G148" s="35" t="inlineStr">
@@ -11281,24 +11195,22 @@
         </is>
       </c>
       <c r="I148" s="36" t="n">
-        <v>0.4327</v>
+        <v>0.0582</v>
       </c>
       <c r="J148" s="36" t="n">
-        <v>0.2972</v>
-      </c>
-      <c r="K148" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.0443</v>
+      </c>
+      <c r="K148" s="37" t="n">
+        <v>-0.0282</v>
       </c>
       <c r="L148" s="34" t="inlineStr">
         <is>
-          <t>0.74~1.74%</t>
+          <t>0.29~1.29%</t>
         </is>
       </c>
       <c r="M148" s="38" t="inlineStr">
         <is>
-          <t>3해 연43.3% · 변동성 29.7% (위험대비 1.36) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.74% · 가장 나쁜 창 연43.3%</t>
+          <t>3해 연5.8% · 변동성 4.4% (위험대비 0.68) (달 간격) · 최대낙폭 -3% · 보수 0.29% · 가장 나쁜 창 연3.1%</t>
         </is>
       </c>
     </row>
@@ -11315,22 +11227,22 @@
       </c>
       <c r="C149" s="14" t="inlineStr">
         <is>
-          <t>KB평생연금밸런스증권자투자신탁(채권혼합-재간접형)(운용)</t>
+          <t>한국투자TIF알아서평생소득증권자투자신탁(채권-재간접형)</t>
         </is>
       </c>
       <c r="D149" s="14" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="E149" s="14" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>한국투자신탁운용</t>
         </is>
       </c>
       <c r="F149" s="28" t="inlineStr">
         <is>
-          <t>134억원</t>
+          <t>125억원</t>
         </is>
       </c>
       <c r="G149" s="30" t="inlineStr">
@@ -11344,24 +11256,22 @@
         </is>
       </c>
       <c r="I149" s="29" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.0428</v>
       </c>
       <c r="J149" s="29" t="n">
-        <v>0.05309999999999999</v>
-      </c>
-      <c r="K149" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.0363</v>
+      </c>
+      <c r="K149" s="31" t="n">
+        <v>-0.025</v>
       </c>
       <c r="L149" s="28" t="inlineStr">
         <is>
-          <t>0.30~0.51%</t>
+          <t>0.35~0.82%</t>
         </is>
       </c>
       <c r="M149" s="32" t="inlineStr">
         <is>
-          <t>3해 연6.1% · 변동성 5.3% (위험대비 0.61) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.30% · 가장 나쁜 창 연5.7%</t>
+          <t>3해 연4.3% · 변동성 3.6% (위험대비 0.40) (달 간격) · 최대낙폭 -2% · 보수 0.35% · 가장 나쁜 창 연1.3%</t>
         </is>
       </c>
     </row>
@@ -11378,7 +11288,7 @@
       </c>
       <c r="C150" s="33" t="inlineStr">
         <is>
-          <t>한국투자글로벌AI&amp;반도체TOP10증권자투자신탁H(주식)(모)</t>
+          <t>한국투자웰링턴글로벌퀄리티증권자투자신탁H(주식)</t>
         </is>
       </c>
       <c r="D150" s="33" t="inlineStr">
@@ -11393,7 +11303,7 @@
       </c>
       <c r="F150" s="34" t="inlineStr">
         <is>
-          <t>1,623억원</t>
+          <t>906억원</t>
         </is>
       </c>
       <c r="G150" s="35" t="inlineStr">
@@ -11407,24 +11317,22 @@
         </is>
       </c>
       <c r="I150" s="36" t="n">
-        <v>0.3962</v>
+        <v>0.1715</v>
       </c>
       <c r="J150" s="36" t="n">
-        <v>0.2845</v>
-      </c>
-      <c r="K150" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1123</v>
+      </c>
+      <c r="K150" s="37" t="n">
+        <v>-0.0862</v>
       </c>
       <c r="L150" s="34" t="inlineStr">
         <is>
-          <t>0.74~1.74%</t>
+          <t>0.97~2.17%</t>
         </is>
       </c>
       <c r="M150" s="38" t="inlineStr">
         <is>
-          <t>3해 연39.6% · 변동성 28.4% (위험대비 1.29) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.74% · 가장 나쁜 창 연39.6%</t>
+          <t>3해 연17.1% · 변동성 11.2% (위험대비 1.28) (달 간격) · 최대낙폭 -9% · 보수 0.97% · 가장 나쁜 창 연12.4%</t>
         </is>
       </c>
     </row>
@@ -11441,7 +11349,7 @@
       </c>
       <c r="C151" s="14" t="inlineStr">
         <is>
-          <t>KCGI글로벌고배당증권자투자신탁[주식-재간접형]</t>
+          <t>브이아이아시아넥스트인프라증권자투자신탁 1[주식]</t>
         </is>
       </c>
       <c r="D151" s="14" t="inlineStr">
@@ -11451,12 +11359,12 @@
       </c>
       <c r="E151" s="14" t="inlineStr">
         <is>
-          <t>케이씨지아이자산운용</t>
+          <t>브이아이자산운용</t>
         </is>
       </c>
       <c r="F151" s="28" t="inlineStr">
         <is>
-          <t>189억원</t>
+          <t>127억원</t>
         </is>
       </c>
       <c r="G151" s="30" t="inlineStr">
@@ -11466,28 +11374,26 @@
       </c>
       <c r="H151" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I151" s="29" t="n">
-        <v>0.0902</v>
+        <v>0.1846</v>
       </c>
       <c r="J151" s="29" t="n">
-        <v>0.101</v>
-      </c>
-      <c r="K151" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1316</v>
+      </c>
+      <c r="K151" s="31" t="n">
+        <v>-0.0721</v>
       </c>
       <c r="L151" s="28" t="inlineStr">
         <is>
-          <t>0.49~0.65%</t>
+          <t>1.33~2.08%</t>
         </is>
       </c>
       <c r="M151" s="32" t="inlineStr">
         <is>
-          <t>5해 연9.0% · 변동성 10.1% (위험대비 0.61) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.49% · 가장 나쁜 창 연9.0%</t>
+          <t>3해 연18.5% · 변동성 13.2% (위험대비 1.19) (달 간격) · 최대낙폭 -7% · 보수 1.33% · 가장 나쁜 창 연18.5%</t>
         </is>
       </c>
     </row>
@@ -11504,12 +11410,12 @@
       </c>
       <c r="C152" s="33" t="inlineStr">
         <is>
-          <t>키움불리오글로벌멀티에셋EMP증권자투자신탁(UH)[혼합-재간접형]</t>
+          <t>키움슈로더유로증권자투자신탁(주식-재간접형)</t>
         </is>
       </c>
       <c r="D152" s="33" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E152" s="33" t="inlineStr">
@@ -11519,7 +11425,7 @@
       </c>
       <c r="F152" s="34" t="inlineStr">
         <is>
-          <t>659억원</t>
+          <t>214억원</t>
         </is>
       </c>
       <c r="G152" s="35" t="inlineStr">
@@ -11529,28 +11435,26 @@
       </c>
       <c r="H152" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I152" s="36" t="n">
-        <v>0.1028</v>
+        <v>0.1602</v>
       </c>
       <c r="J152" s="36" t="n">
-        <v>0.1173</v>
-      </c>
-      <c r="K152" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1201</v>
+      </c>
+      <c r="K152" s="37" t="n">
+        <v>-0.0978</v>
       </c>
       <c r="L152" s="34" t="inlineStr">
         <is>
-          <t>0.70~1.57%</t>
+          <t>0.91~2.41%</t>
         </is>
       </c>
       <c r="M152" s="38" t="inlineStr">
         <is>
-          <t>5해 연10.3% · 변동성 11.7% (위험대비 0.64) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.70% · 가장 나쁜 창 연10.3%</t>
+          <t>3해 연16.0% · 변동성 12.0% (위험대비 1.10) (달 간격) · 최대낙폭 -10% · 보수 0.91% · 가장 나쁜 창 연15.1%</t>
         </is>
       </c>
     </row>
@@ -11567,22 +11471,22 @@
       </c>
       <c r="C153" s="14" t="inlineStr">
         <is>
-          <t>키움슈로더월지급글로벌가치주인컴증권자투자신탁[주식-재간접형]</t>
+          <t>하나PIMCO글로벌인컴혼합자산자투자신탁(H)[재간접형]</t>
         </is>
       </c>
       <c r="D153" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외채권형</t>
         </is>
       </c>
       <c r="E153" s="14" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
+          <t>하나자산운용</t>
         </is>
       </c>
       <c r="F153" s="28" t="inlineStr">
         <is>
-          <t>1,713억원</t>
+          <t>700억원</t>
         </is>
       </c>
       <c r="G153" s="30" t="inlineStr">
@@ -11592,28 +11496,26 @@
       </c>
       <c r="H153" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I153" s="29" t="n">
-        <v>0.0755</v>
+        <v>0.0506</v>
       </c>
       <c r="J153" s="29" t="n">
-        <v>0.1013</v>
-      </c>
-      <c r="K153" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.04190000000000001</v>
+      </c>
+      <c r="K153" s="31" t="n">
+        <v>-0.0271</v>
       </c>
       <c r="L153" s="28" t="inlineStr">
         <is>
-          <t>0.43~1.21%</t>
+          <t>0.36~1.16%</t>
         </is>
       </c>
       <c r="M153" s="32" t="inlineStr">
         <is>
-          <t>5해 연7.5% · 변동성 10.1% (위험대비 0.47) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.43% · 가장 나쁜 창 연7.5%</t>
+          <t>3해 연5.1% · 변동성 4.2% (위험대비 0.54) (달 간격) · 최대낙폭 -3% · 보수 0.36% · 가장 나쁜 창 연2.6%</t>
         </is>
       </c>
     </row>
@@ -11630,22 +11532,22 @@
       </c>
       <c r="C154" s="33" t="inlineStr">
         <is>
-          <t>베어링월지급글로벌하이일드증권자투자신탁[H](채권-재간접형)</t>
+          <t>우리프랭클린미국바이오헬스케어증권자투자신탁(주식-재간접형)</t>
         </is>
       </c>
       <c r="D154" s="33" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E154" s="33" t="inlineStr">
         <is>
-          <t>베어링자산운용</t>
+          <t>우리자산운용</t>
         </is>
       </c>
       <c r="F154" s="34" t="inlineStr">
         <is>
-          <t>496억원</t>
+          <t>225억원</t>
         </is>
       </c>
       <c r="G154" s="35" t="inlineStr">
@@ -11655,28 +11557,26 @@
       </c>
       <c r="H154" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I154" s="36" t="n">
-        <v>0.0282</v>
+        <v>0.2481</v>
       </c>
       <c r="J154" s="36" t="n">
-        <v>0.0195</v>
-      </c>
-      <c r="K154" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1977</v>
+      </c>
+      <c r="K154" s="37" t="n">
+        <v>-0.1625</v>
       </c>
       <c r="L154" s="34" t="inlineStr">
         <is>
-          <t>0.49~1.19%</t>
+          <t>0.14~1.14%</t>
         </is>
       </c>
       <c r="M154" s="38" t="inlineStr">
         <is>
-          <t>5해 연2.8% · 변동성 1.9% (위험대비 0.01) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.49% · 가장 나쁜 창 연2.8%</t>
+          <t>3해 연24.8% · 변동성 19.8% (위험대비 1.11) (달 간격) · 최대낙폭 -16% · 보수 0.14% · 가장 나쁜 창 연24.8%</t>
         </is>
       </c>
     </row>
@@ -11693,22 +11593,22 @@
       </c>
       <c r="C155" s="14" t="inlineStr">
         <is>
-          <t>AB글로벌고수익증권투자신탁(채권-재간접형)</t>
+          <t>KB글로벌코어리츠부동산자투자신탁(재간접형)(H)(운용)</t>
         </is>
       </c>
       <c r="D155" s="14" t="inlineStr">
         <is>
-          <t>해외채권형</t>
+          <t>해외대체</t>
         </is>
       </c>
       <c r="E155" s="14" t="inlineStr">
         <is>
-          <t>얼라이언스번스틴자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F155" s="28" t="inlineStr">
         <is>
-          <t>1,629억원</t>
+          <t>217억원</t>
         </is>
       </c>
       <c r="G155" s="30" t="inlineStr">
@@ -11718,28 +11618,26 @@
       </c>
       <c r="H155" s="30" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I155" s="29" t="n">
-        <v>0.0177</v>
+        <v>0.0573</v>
       </c>
       <c r="J155" s="29" t="n">
-        <v>0.0255</v>
-      </c>
-      <c r="K155" s="28" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.1328</v>
+      </c>
+      <c r="K155" s="31" t="n">
+        <v>-0.09609999999999999</v>
       </c>
       <c r="L155" s="28" t="inlineStr">
         <is>
-          <t>0.17~1.17%</t>
+          <t>0.57~1.43%</t>
         </is>
       </c>
       <c r="M155" s="32" t="inlineStr">
         <is>
-          <t>5해 연1.8% · 변동성 2.5% (위험대비 -0.41) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.17% · 가장 나쁜 창 연1.8%</t>
+          <t>3해 연5.7% · 변동성 13.3% (위험대비 0.22) (달 간격) · 최대낙폭 -10% · 보수 0.57% · 가장 나쁜 창 연5.7%</t>
         </is>
       </c>
     </row>
@@ -11756,22 +11654,22 @@
       </c>
       <c r="C156" s="33" t="inlineStr">
         <is>
-          <t>한국밸류글로벌배당인컴증권자투자신탁(주식)(모)</t>
+          <t>iM에셋글로벌자산배분증권투자신탁(주식혼합-재간접형)(H)</t>
         </is>
       </c>
       <c r="D156" s="33" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E156" s="33" t="inlineStr">
         <is>
-          <t>한국투자밸류자산운용</t>
+          <t>아이엠에셋자산운용</t>
         </is>
       </c>
       <c r="F156" s="34" t="inlineStr">
         <is>
-          <t>210억원</t>
+          <t>176억원</t>
         </is>
       </c>
       <c r="G156" s="35" t="inlineStr">
@@ -11781,28 +11679,26 @@
       </c>
       <c r="H156" s="35" t="inlineStr">
         <is>
-          <t>5해</t>
+          <t>3해</t>
         </is>
       </c>
       <c r="I156" s="36" t="n">
-        <v>0.1225</v>
+        <v>0.1046</v>
       </c>
       <c r="J156" s="36" t="n">
-        <v>0.1009</v>
-      </c>
-      <c r="K156" s="34" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="K156" s="37" t="n">
+        <v>-0.0765</v>
       </c>
       <c r="L156" s="34" t="inlineStr">
         <is>
-          <t>0.91~1.88%</t>
+          <t>0.80~2.07%</t>
         </is>
       </c>
       <c r="M156" s="38" t="inlineStr">
         <is>
-          <t>5해 연12.2% · 변동성 10.1% (위험대비 0.94) (원천 제공) · 최대낙폭은 못 쟀습니다 · 보수 0.91% · 가장 나쁜 창 연6.2%</t>
+          <t>3해 연10.5% · 변동성 9.7% (위험대비 0.79) (달 간격) · 최대낙폭 -8% · 보수 0.80% · 가장 나쁜 창 연10.5%</t>
         </is>
       </c>
     </row>
@@ -11946,7 +11842,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr"/>
@@ -12402,11 +12298,11 @@
         </is>
       </c>
       <c r="B30" s="39" t="n">
-        <v>0.0553</v>
+        <v>0.0535</v>
       </c>
       <c r="C30" s="45" t="inlineStr">
         <is>
-          <t>국내채권 40% · 국내주식 40% · 대체 20%</t>
+          <t>대체 40% · 국내채권 30% · 국내주식 30%</t>
         </is>
       </c>
       <c r="D30" s="46" t="n"/>
@@ -12423,7 +12319,7 @@
       </c>
       <c r="C31" s="45" t="inlineStr">
         <is>
-          <t>해외주식 40% · 해외채권 40% · 대체 20%</t>
+          <t>해외채권 40% · 해외주식 40% · 대체 20%</t>
         </is>
       </c>
       <c r="D31" s="46" t="n"/>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="제안서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="자산군" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="상품" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="출처" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="사용법" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제안서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산군" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상품" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'상품'!$A$6:$M$156</definedName>
@@ -1376,7 +1376,7 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-20 16:00:00 · 문서 2026-09-20 16:00 (KST)</t>
+          <t>유니버스 2026-09-20 16:03:37 · 문서 2026-09-20 16:03 (KST)</t>
         </is>
       </c>
     </row>
@@ -2407,13 +2407,13 @@
         <v>99</v>
       </c>
       <c r="D11" s="29" t="n">
-        <v>0.09780242562454644</v>
+        <v>0.1049382716049381</v>
       </c>
       <c r="E11" s="29" t="n">
-        <v>0.2921539773352639</v>
+        <v>0.2923973274425171</v>
       </c>
       <c r="F11" s="29" t="n">
-        <v>-0.3237114148035969</v>
+        <v>-0.3235610824922673</v>
       </c>
     </row>
     <row r="12">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="F36" s="34" t="inlineStr">
         <is>
-          <t>931조원</t>
+          <t>932조원</t>
         </is>
       </c>
       <c r="G36" s="35" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="F38" s="34" t="inlineStr">
         <is>
-          <t>901조원</t>
+          <t>902조원</t>
         </is>
       </c>
       <c r="G38" s="35" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="F40" s="34" t="inlineStr">
         <is>
-          <t>1,287조원</t>
+          <t>1,288조원</t>
         </is>
       </c>
       <c r="G40" s="35" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="F41" s="28" t="inlineStr">
         <is>
-          <t>569조원</t>
+          <t>570조원</t>
         </is>
       </c>
       <c r="G41" s="30" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="F43" s="28" t="inlineStr">
         <is>
-          <t>1,511조원</t>
+          <t>1,512조원</t>
         </is>
       </c>
       <c r="G43" s="30" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="F47" s="28" t="inlineStr">
         <is>
-          <t>1,424조원</t>
+          <t>1,425조원</t>
         </is>
       </c>
       <c r="G47" s="30" t="inlineStr">
@@ -5133,7 +5133,7 @@
       </c>
       <c r="F48" s="34" t="inlineStr">
         <is>
-          <t>1,176조원</t>
+          <t>1,177조원</t>
         </is>
       </c>
       <c r="G48" s="35" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="F53" s="28" t="inlineStr">
         <is>
-          <t>6,794조원</t>
+          <t>6,799조원</t>
         </is>
       </c>
       <c r="G53" s="30" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="F54" s="34" t="inlineStr">
         <is>
-          <t>178조원</t>
+          <t>179조원</t>
         </is>
       </c>
       <c r="G54" s="35" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>이지스코어리테일부동산투자신탁 126</t>
+          <t>마이다스거북이90증권자투자신탁 1(주식)(운용)</t>
         </is>
       </c>
       <c r="D107" s="14" t="inlineStr">
@@ -8677,12 +8677,12 @@
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>이지스자산운용</t>
+          <t>마이다스에셋자산운용</t>
         </is>
       </c>
       <c r="F107" s="28" t="inlineStr">
         <is>
-          <t>606억원</t>
+          <t>1,952억원</t>
         </is>
       </c>
       <c r="G107" s="30" t="inlineStr">
@@ -8696,22 +8696,22 @@
         </is>
       </c>
       <c r="I107" s="29" t="n">
-        <v>0.0469</v>
+        <v>0.1644</v>
       </c>
       <c r="J107" s="29" t="n">
-        <v>0.0069</v>
+        <v>0.0808</v>
       </c>
       <c r="K107" s="31" t="n">
-        <v>0</v>
+        <v>-0.0366</v>
       </c>
       <c r="L107" s="28" t="inlineStr">
         <is>
-          <t>0.00~0.00%</t>
+          <t>0.59~2.09%</t>
         </is>
       </c>
       <c r="M107" s="32" t="inlineStr">
         <is>
-          <t>3해 연4.7% · 변동성 0.7% (위험대비 2.72) (달 간격) · 최대낙폭 0% · 보수 0.00% · 가장 나쁜 창 연4.7%</t>
+          <t>3해 연16.4% · 변동성 8.1% (위험대비 1.69) (달 간격) · 최대낙폭 -4% · 보수 0.59% · 가장 나쁜 창 연16.4%</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="C108" s="33" t="inlineStr">
         <is>
-          <t>이지스리테일부동산투자신탁299</t>
+          <t>이지스코어리테일부동산투자신탁 126</t>
         </is>
       </c>
       <c r="D108" s="33" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="F108" s="34" t="inlineStr">
         <is>
-          <t>211억원</t>
+          <t>606억원</t>
         </is>
       </c>
       <c r="G108" s="35" t="inlineStr">
@@ -8757,20 +8757,22 @@
         </is>
       </c>
       <c r="I108" s="36" t="n">
-        <v>0.0398</v>
+        <v>0.0469</v>
       </c>
       <c r="J108" s="36" t="n">
-        <v>0.0212</v>
+        <v>0.0069</v>
       </c>
       <c r="K108" s="37" t="n">
-        <v>-0.0241</v>
-      </c>
-      <c r="L108" s="40" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0</v>
+      </c>
+      <c r="L108" s="34" t="inlineStr">
+        <is>
+          <t>0.00~0.00%</t>
+        </is>
       </c>
       <c r="M108" s="38" t="inlineStr">
         <is>
-          <t>3해 연4.0% · 변동성 2.1% (위험대비 0.55) (달 간격) · 최대낙폭 -2% · 보수 0.06% · 가장 나쁜 창 연4.0%</t>
+          <t>3해 연4.7% (감정평가 기준가 — 시세가 아니라 위험을 못 쟀습니다) · 보수 0.00% · 가장 나쁜 창 연4.7%</t>
         </is>
       </c>
     </row>
@@ -8787,22 +8789,22 @@
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t>마이다스거북이90증권자투자신탁 1(주식)(운용)</t>
+          <t>유진챔피언중단기채증권자투자신탁(채권)</t>
         </is>
       </c>
       <c r="D109" s="14" t="inlineStr">
         <is>
-          <t>국내대체</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>마이다스에셋자산운용</t>
+          <t>유진자산운용</t>
         </is>
       </c>
       <c r="F109" s="28" t="inlineStr">
         <is>
-          <t>1,952억원</t>
+          <t>1,392억원</t>
         </is>
       </c>
       <c r="G109" s="30" t="inlineStr">
@@ -8816,22 +8818,22 @@
         </is>
       </c>
       <c r="I109" s="29" t="n">
-        <v>0.1644</v>
+        <v>0.0073</v>
       </c>
       <c r="J109" s="29" t="n">
-        <v>0.0808</v>
+        <v>0.035</v>
       </c>
       <c r="K109" s="31" t="n">
-        <v>-0.0366</v>
+        <v>-0.04</v>
       </c>
       <c r="L109" s="28" t="inlineStr">
         <is>
-          <t>0.59~2.09%</t>
+          <t>0.11~0.41%</t>
         </is>
       </c>
       <c r="M109" s="32" t="inlineStr">
         <is>
-          <t>3해 연16.4% · 변동성 8.1% (위험대비 1.69) (달 간격) · 최대낙폭 -4% · 보수 0.59% · 가장 나쁜 창 연16.4%</t>
+          <t>3해 연0.7% · 변동성 3.5% (위험대비 -0.59) (달 간격) · 최대낙폭 -4% · 보수 0.11% · 가장 나쁜 창 연-0.1%</t>
         </is>
       </c>
     </row>
@@ -8848,22 +8850,22 @@
       </c>
       <c r="C110" s="33" t="inlineStr">
         <is>
-          <t>유진챔피언중단기채증권자투자신탁(채권)</t>
+          <t>우리반도체BIG2플러스증권투자신탁(채권혼합)</t>
         </is>
       </c>
       <c r="D110" s="33" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E110" s="33" t="inlineStr">
         <is>
-          <t>유진자산운용</t>
+          <t>우리자산운용</t>
         </is>
       </c>
       <c r="F110" s="34" t="inlineStr">
         <is>
-          <t>1,392억원</t>
+          <t>4,207억원</t>
         </is>
       </c>
       <c r="G110" s="35" t="inlineStr">
@@ -8877,22 +8879,22 @@
         </is>
       </c>
       <c r="I110" s="36" t="n">
-        <v>0.0073</v>
+        <v>0.2141</v>
       </c>
       <c r="J110" s="36" t="n">
-        <v>0.035</v>
+        <v>0.1545</v>
       </c>
       <c r="K110" s="37" t="n">
-        <v>-0.04</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="L110" s="34" t="inlineStr">
         <is>
-          <t>0.11~0.41%</t>
+          <t>0.34~0.89%</t>
         </is>
       </c>
       <c r="M110" s="38" t="inlineStr">
         <is>
-          <t>3해 연0.7% · 변동성 3.5% (위험대비 -0.59) (달 간격) · 최대낙폭 -4% · 보수 0.11% · 가장 나쁜 창 연-0.1%</t>
+          <t>3해 연21.4% · 변동성 15.4% (위험대비 1.20) (달 간격) · 최대낙폭 -9% · 보수 0.34% · 가장 나쁜 창 연21.4%</t>
         </is>
       </c>
     </row>
@@ -8909,22 +8911,22 @@
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>우리반도체BIG2플러스증권투자신탁(채권혼합)</t>
+          <t>마이다스K200인덱스알파증권자투자신탁(주식-파생형)(운용)</t>
         </is>
       </c>
       <c r="D111" s="14" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>우리자산운용</t>
+          <t>마이다스에셋자산운용</t>
         </is>
       </c>
       <c r="F111" s="28" t="inlineStr">
         <is>
-          <t>4,207억원</t>
+          <t>493억원</t>
         </is>
       </c>
       <c r="G111" s="30" t="inlineStr">
@@ -8938,22 +8940,22 @@
         </is>
       </c>
       <c r="I111" s="29" t="n">
-        <v>0.2141</v>
+        <v>0.509</v>
       </c>
       <c r="J111" s="29" t="n">
-        <v>0.1545</v>
+        <v>0.3986</v>
       </c>
       <c r="K111" s="31" t="n">
-        <v>-0.09300000000000001</v>
+        <v>-0.2336</v>
       </c>
       <c r="L111" s="28" t="inlineStr">
         <is>
-          <t>0.34~0.89%</t>
+          <t>0.06~0.15%</t>
         </is>
       </c>
       <c r="M111" s="32" t="inlineStr">
         <is>
-          <t>3해 연21.4% · 변동성 15.4% (위험대비 1.20) (달 간격) · 최대낙폭 -9% · 보수 0.34% · 가장 나쁜 창 연21.4%</t>
+          <t>3해 연50.9% · 변동성 39.9% (위험대비 1.21) (달 간격) · 최대낙폭 -23% · 보수 0.06% · 가장 나쁜 창 연50.9%</t>
         </is>
       </c>
     </row>
@@ -8970,22 +8972,22 @@
       </c>
       <c r="C112" s="33" t="inlineStr">
         <is>
-          <t>마이다스K200인덱스알파증권자투자신탁(주식-파생형)(운용)</t>
+          <t>미래에셋스마트롱숏30증권자투자신탁 1(채권혼합)</t>
         </is>
       </c>
       <c r="D112" s="33" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내대체</t>
         </is>
       </c>
       <c r="E112" s="33" t="inlineStr">
         <is>
-          <t>마이다스에셋자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F112" s="34" t="inlineStr">
         <is>
-          <t>493억원</t>
+          <t>147억원</t>
         </is>
       </c>
       <c r="G112" s="35" t="inlineStr">
@@ -8999,22 +9001,22 @@
         </is>
       </c>
       <c r="I112" s="36" t="n">
-        <v>0.509</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J112" s="36" t="n">
-        <v>0.3986</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="K112" s="37" t="n">
-        <v>-0.2336</v>
+        <v>-0.061</v>
       </c>
       <c r="L112" s="34" t="inlineStr">
         <is>
-          <t>0.06~0.15%</t>
+          <t>0.50~1.10%</t>
         </is>
       </c>
       <c r="M112" s="38" t="inlineStr">
         <is>
-          <t>3해 연50.9% · 변동성 39.9% (위험대비 1.21) (달 간격) · 최대낙폭 -23% · 보수 0.06% · 가장 나쁜 창 연50.9%</t>
+          <t>3해 연4.2% · 변동성 7.8% (위험대비 0.18) (달 간격) · 최대낙폭 -6% · 보수 0.50% · 가장 나쁜 창 연4.2%</t>
         </is>
       </c>
     </row>
@@ -9031,22 +9033,22 @@
       </c>
       <c r="C113" s="14" t="inlineStr">
         <is>
-          <t>신한퇴직연금커버드콜인덱스증권자투자신탁[주식혼합-파생형] (종류)</t>
+          <t>이지스리테일부동산투자신탁299</t>
         </is>
       </c>
       <c r="D113" s="14" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내대체</t>
         </is>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>이지스자산운용</t>
         </is>
       </c>
       <c r="F113" s="28" t="inlineStr">
         <is>
-          <t>150억원</t>
+          <t>211억원</t>
         </is>
       </c>
       <c r="G113" s="30" t="inlineStr">
@@ -9060,22 +9062,20 @@
         </is>
       </c>
       <c r="I113" s="29" t="n">
-        <v>0.1302</v>
+        <v>0.0398</v>
       </c>
       <c r="J113" s="29" t="n">
-        <v>0.0872</v>
+        <v>0.0212</v>
       </c>
       <c r="K113" s="31" t="n">
-        <v>-0.055</v>
-      </c>
-      <c r="L113" s="28" t="inlineStr">
-        <is>
-          <t>0.56~0.79%</t>
-        </is>
+        <v>-0.0241</v>
+      </c>
+      <c r="L113" s="39" t="n">
+        <v>0.0006400000000000001</v>
       </c>
       <c r="M113" s="32" t="inlineStr">
         <is>
-          <t>3해 연13.0% · 변동성 8.7% (위험대비 1.17) (달 간격) · 최대낙폭 -6% · 보수 0.56% · 가장 나쁜 창 연13.0%</t>
+          <t>3해 연4.0% (감정평가 기준가 — 시세가 아니라 위험을 못 쟀습니다) · 보수 0.06% · 가장 나쁜 창 연4.0%</t>
         </is>
       </c>
     </row>
@@ -9092,22 +9092,22 @@
       </c>
       <c r="C114" s="33" t="inlineStr">
         <is>
-          <t>신영밸류고배당증권자투자신탁(주식)운용</t>
+          <t>신한퇴직연금커버드콜인덱스증권자투자신탁[주식혼합-파생형] (종류)</t>
         </is>
       </c>
       <c r="D114" s="33" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E114" s="33" t="inlineStr">
         <is>
-          <t>신영자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F114" s="34" t="inlineStr">
         <is>
-          <t>8,313억원</t>
+          <t>150억원</t>
         </is>
       </c>
       <c r="G114" s="35" t="inlineStr">
@@ -9121,22 +9121,22 @@
         </is>
       </c>
       <c r="I114" s="36" t="n">
-        <v>0.3287</v>
+        <v>0.1302</v>
       </c>
       <c r="J114" s="36" t="n">
-        <v>0.2543</v>
+        <v>0.0872</v>
       </c>
       <c r="K114" s="37" t="n">
-        <v>-0.1498</v>
+        <v>-0.055</v>
       </c>
       <c r="L114" s="34" t="inlineStr">
         <is>
-          <t>0.45~1.35%</t>
+          <t>0.56~0.79%</t>
         </is>
       </c>
       <c r="M114" s="38" t="inlineStr">
         <is>
-          <t>3해 연32.9% · 변동성 25.4% (위험대비 1.18) (달 간격) · 최대낙폭 -15% · 보수 0.45% · 가장 나쁜 창 연32.9%</t>
+          <t>3해 연13.0% · 변동성 8.7% (위험대비 1.17) (달 간격) · 최대낙폭 -6% · 보수 0.56% · 가장 나쁜 창 연13.0%</t>
         </is>
       </c>
     </row>
@@ -9153,22 +9153,22 @@
       </c>
       <c r="C115" s="14" t="inlineStr">
         <is>
-          <t>신한커버드콜인덱스증권자투자신탁[주식혼합-파생형]</t>
+          <t>신영밸류고배당증권자투자신탁(주식)운용</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>신영자산운용</t>
         </is>
       </c>
       <c r="F115" s="28" t="inlineStr">
         <is>
-          <t>161억원</t>
+          <t>8,313억원</t>
         </is>
       </c>
       <c r="G115" s="30" t="inlineStr">
@@ -9182,22 +9182,22 @@
         </is>
       </c>
       <c r="I115" s="29" t="n">
-        <v>0.223</v>
+        <v>0.3287</v>
       </c>
       <c r="J115" s="29" t="n">
-        <v>0.1433</v>
+        <v>0.2543</v>
       </c>
       <c r="K115" s="31" t="n">
-        <v>-0.1049</v>
+        <v>-0.1498</v>
       </c>
       <c r="L115" s="28" t="inlineStr">
         <is>
-          <t>0.54~1.34%</t>
+          <t>0.45~1.35%</t>
         </is>
       </c>
       <c r="M115" s="32" t="inlineStr">
         <is>
-          <t>3해 연22.3% · 변동성 14.3% (위험대비 1.36) (달 간격) · 최대낙폭 -10% · 보수 0.54% · 가장 나쁜 창 연22.3%</t>
+          <t>3해 연32.9% · 변동성 25.4% (위험대비 1.18) (달 간격) · 최대낙폭 -15% · 보수 0.45% · 가장 나쁜 창 연32.9%</t>
         </is>
       </c>
     </row>
@@ -9214,22 +9214,22 @@
       </c>
       <c r="C116" s="33" t="inlineStr">
         <is>
-          <t>대신KOSPI200인덱스증권자투자신탁[주식](운용)</t>
+          <t>신한커버드콜인덱스증권자투자신탁[주식혼합-파생형]</t>
         </is>
       </c>
       <c r="D116" s="33" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E116" s="33" t="inlineStr">
         <is>
-          <t>대신자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F116" s="34" t="inlineStr">
         <is>
-          <t>580억원</t>
+          <t>161억원</t>
         </is>
       </c>
       <c r="G116" s="35" t="inlineStr">
@@ -9243,22 +9243,22 @@
         </is>
       </c>
       <c r="I116" s="36" t="n">
-        <v>0.4877</v>
+        <v>0.223</v>
       </c>
       <c r="J116" s="36" t="n">
-        <v>0.4041</v>
+        <v>0.1433</v>
       </c>
       <c r="K116" s="37" t="n">
-        <v>-0.237</v>
+        <v>-0.1049</v>
       </c>
       <c r="L116" s="34" t="inlineStr">
         <is>
-          <t>0.20~0.80%</t>
+          <t>0.54~1.34%</t>
         </is>
       </c>
       <c r="M116" s="38" t="inlineStr">
         <is>
-          <t>3해 연48.8% · 변동성 40.4% (위험대비 1.14) (달 간격) · 최대낙폭 -24% · 보수 0.20% · 가장 나쁜 창 연48.8%</t>
+          <t>3해 연22.3% · 변동성 14.3% (위험대비 1.36) (달 간격) · 최대낙폭 -10% · 보수 0.54% · 가장 나쁜 창 연22.3%</t>
         </is>
       </c>
     </row>
@@ -9275,7 +9275,7 @@
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>BNKK200인덱스증권투자신탁(주식-파생형)</t>
+          <t>대신KOSPI200인덱스증권자투자신탁[주식](운용)</t>
         </is>
       </c>
       <c r="D117" s="14" t="inlineStr">
@@ -9285,12 +9285,12 @@
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>비엔케이자산운용</t>
+          <t>대신자산운용</t>
         </is>
       </c>
       <c r="F117" s="28" t="inlineStr">
         <is>
-          <t>515억원</t>
+          <t>580억원</t>
         </is>
       </c>
       <c r="G117" s="30" t="inlineStr">
@@ -9304,22 +9304,22 @@
         </is>
       </c>
       <c r="I117" s="29" t="n">
-        <v>0.4905</v>
+        <v>0.4877</v>
       </c>
       <c r="J117" s="29" t="n">
-        <v>0.408</v>
+        <v>0.4041</v>
       </c>
       <c r="K117" s="31" t="n">
-        <v>-0.2376</v>
+        <v>-0.237</v>
       </c>
       <c r="L117" s="28" t="inlineStr">
         <is>
-          <t>0.17~0.95%</t>
+          <t>0.20~0.80%</t>
         </is>
       </c>
       <c r="M117" s="32" t="inlineStr">
         <is>
-          <t>3해 연49.0% · 변동성 40.8% (위험대비 1.13) (달 간격) · 최대낙폭 -24% · 보수 0.17% · 가장 나쁜 창 연49.0%</t>
+          <t>3해 연48.8% · 변동성 40.4% (위험대비 1.14) (달 간격) · 최대낙폭 -24% · 보수 0.20% · 가장 나쁜 창 연48.8%</t>
         </is>
       </c>
     </row>
@@ -9336,22 +9336,22 @@
       </c>
       <c r="C118" s="33" t="inlineStr">
         <is>
-          <t>미래에셋퇴직플랜KRX100인덱스증권자투자신탁 1(주식혼합)</t>
+          <t>BNKK200인덱스증권투자신탁(주식-파생형)</t>
         </is>
       </c>
       <c r="D118" s="33" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E118" s="33" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>비엔케이자산운용</t>
         </is>
       </c>
       <c r="F118" s="34" t="inlineStr">
         <is>
-          <t>186억원</t>
+          <t>515억원</t>
         </is>
       </c>
       <c r="G118" s="35" t="inlineStr">
@@ -9365,22 +9365,22 @@
         </is>
       </c>
       <c r="I118" s="36" t="n">
-        <v>0.2895</v>
+        <v>0.4905</v>
       </c>
       <c r="J118" s="36" t="n">
-        <v>0.2318</v>
+        <v>0.408</v>
       </c>
       <c r="K118" s="37" t="n">
-        <v>-0.1349</v>
+        <v>-0.2376</v>
       </c>
       <c r="L118" s="34" t="inlineStr">
         <is>
-          <t>0.44~0.65%</t>
+          <t>0.17~0.95%</t>
         </is>
       </c>
       <c r="M118" s="38" t="inlineStr">
         <is>
-          <t>3해 연28.9% · 변동성 23.2% (위험대비 1.13) (달 간격) · 최대낙폭 -13% · 보수 0.44% · 가장 나쁜 창 연28.9%</t>
+          <t>3해 연49.0% · 변동성 40.8% (위험대비 1.13) (달 간격) · 최대낙폭 -24% · 보수 0.17% · 가장 나쁜 창 연49.0%</t>
         </is>
       </c>
     </row>
@@ -9397,22 +9397,22 @@
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>신영마라톤지주회사증권자투자신탁(주식)운용</t>
+          <t>미래에셋퇴직플랜KRX100인덱스증권자투자신탁 1(주식혼합)</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>신영자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F119" s="28" t="inlineStr">
         <is>
-          <t>316억원</t>
+          <t>186억원</t>
         </is>
       </c>
       <c r="G119" s="30" t="inlineStr">
@@ -9426,22 +9426,22 @@
         </is>
       </c>
       <c r="I119" s="29" t="n">
-        <v>0.4483</v>
+        <v>0.2895</v>
       </c>
       <c r="J119" s="29" t="n">
-        <v>0.3544</v>
+        <v>0.2318</v>
       </c>
       <c r="K119" s="31" t="n">
-        <v>-0.2314</v>
+        <v>-0.1349</v>
       </c>
       <c r="L119" s="28" t="inlineStr">
         <is>
-          <t>0.52~1.49%</t>
+          <t>0.44~0.65%</t>
         </is>
       </c>
       <c r="M119" s="32" t="inlineStr">
         <is>
-          <t>3해 연44.8% · 변동성 35.4% (위험대비 1.19) (달 간격) · 최대낙폭 -23% · 보수 0.52% · 가장 나쁜 창 연44.8%</t>
+          <t>3해 연28.9% · 변동성 23.2% (위험대비 1.13) (달 간격) · 최대낙폭 -13% · 보수 0.44% · 가장 나쁜 창 연28.9%</t>
         </is>
       </c>
     </row>
@@ -9458,22 +9458,22 @@
       </c>
       <c r="C120" s="33" t="inlineStr">
         <is>
-          <t>KB퇴직연금배당40증권자투자신탁(채권혼합)</t>
+          <t>신영마라톤지주회사증권자투자신탁(주식)운용</t>
         </is>
       </c>
       <c r="D120" s="33" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E120" s="33" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>신영자산운용</t>
         </is>
       </c>
       <c r="F120" s="34" t="inlineStr">
         <is>
-          <t>1조원</t>
+          <t>316억원</t>
         </is>
       </c>
       <c r="G120" s="35" t="inlineStr">
@@ -9487,22 +9487,22 @@
         </is>
       </c>
       <c r="I120" s="36" t="n">
-        <v>0.1845</v>
+        <v>0.4483</v>
       </c>
       <c r="J120" s="36" t="n">
-        <v>0.1429</v>
+        <v>0.3544</v>
       </c>
       <c r="K120" s="37" t="n">
-        <v>-0.0965</v>
+        <v>-0.2314</v>
       </c>
       <c r="L120" s="34" t="inlineStr">
         <is>
-          <t>0.46~0.80%</t>
+          <t>0.52~1.49%</t>
         </is>
       </c>
       <c r="M120" s="38" t="inlineStr">
         <is>
-          <t>3해 연18.4% · 변동성 14.3% (위험대비 1.09) (달 간격) · 최대낙폭 -10% · 보수 0.46% · 가장 나쁜 창 연18.4%</t>
+          <t>3해 연44.8% · 변동성 35.4% (위험대비 1.19) (달 간격) · 최대낙폭 -23% · 보수 0.52% · 가장 나쁜 창 연44.8%</t>
         </is>
       </c>
     </row>
@@ -9519,12 +9519,12 @@
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>KB퇴직연금배당증권자투자신탁(주식)(운용)</t>
+          <t>KB퇴직연금배당40증권자투자신탁(채권혼합)</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="F121" s="28" t="inlineStr">
         <is>
-          <t>1,688억원</t>
+          <t>1조원</t>
         </is>
       </c>
       <c r="G121" s="30" t="inlineStr">
@@ -9548,22 +9548,22 @@
         </is>
       </c>
       <c r="I121" s="29" t="n">
-        <v>0.522</v>
+        <v>0.1845</v>
       </c>
       <c r="J121" s="29" t="n">
-        <v>0.3632</v>
+        <v>0.1429</v>
       </c>
       <c r="K121" s="31" t="n">
-        <v>-0.2298</v>
+        <v>-0.0965</v>
       </c>
       <c r="L121" s="28" t="inlineStr">
         <is>
-          <t>0.71~1.20%</t>
+          <t>0.46~0.80%</t>
         </is>
       </c>
       <c r="M121" s="32" t="inlineStr">
         <is>
-          <t>3해 연52.2% · 변동성 36.3% (위험대비 1.36) (달 간격) · 최대낙폭 -23% · 보수 0.71% · 가장 나쁜 창 연52.2%</t>
+          <t>3해 연18.4% · 변동성 14.3% (위험대비 1.09) (달 간격) · 최대낙폭 -10% · 보수 0.46% · 가장 나쁜 창 연18.4%</t>
         </is>
       </c>
     </row>
@@ -9580,22 +9580,22 @@
       </c>
       <c r="C122" s="33" t="inlineStr">
         <is>
-          <t>BNK내일환매초단기채증권자투자신탁(채권)</t>
+          <t>KB퇴직연금배당증권자투자신탁(주식)(운용)</t>
         </is>
       </c>
       <c r="D122" s="33" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E122" s="33" t="inlineStr">
         <is>
-          <t>비엔케이자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F122" s="34" t="inlineStr">
         <is>
-          <t>182억원</t>
+          <t>1,688억원</t>
         </is>
       </c>
       <c r="G122" s="35" t="inlineStr">
@@ -9609,22 +9609,22 @@
         </is>
       </c>
       <c r="I122" s="36" t="n">
-        <v>0.0027</v>
+        <v>0.522</v>
       </c>
       <c r="J122" s="36" t="n">
-        <v>0.0333</v>
+        <v>0.3632</v>
       </c>
       <c r="K122" s="37" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.2298</v>
       </c>
       <c r="L122" s="34" t="inlineStr">
         <is>
-          <t>0.10~0.29%</t>
+          <t>0.71~1.20%</t>
         </is>
       </c>
       <c r="M122" s="38" t="inlineStr">
         <is>
-          <t>3해 연0.3% · 변동성 3.3% (위험대비 -0.76) (달 간격) · 최대낙폭 -4% · 보수 0.10% · 가장 나쁜 창 연0.3%</t>
+          <t>3해 연52.2% · 변동성 36.3% (위험대비 1.36) (달 간격) · 최대낙폭 -23% · 보수 0.71% · 가장 나쁜 창 연52.2%</t>
         </is>
       </c>
     </row>
@@ -9641,22 +9641,22 @@
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>미래에셋소득공제장기배당커버드콜액티브증권전환형자투자신탁 1(주식혼합)</t>
+          <t>BNK내일환매초단기채증권자투자신탁(채권)</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>비엔케이자산운용</t>
         </is>
       </c>
       <c r="F123" s="28" t="inlineStr">
         <is>
-          <t>259억원</t>
+          <t>182억원</t>
         </is>
       </c>
       <c r="G123" s="30" t="inlineStr">
@@ -9670,22 +9670,22 @@
         </is>
       </c>
       <c r="I123" s="29" t="n">
-        <v>0.3794</v>
+        <v>0.0027</v>
       </c>
       <c r="J123" s="29" t="n">
-        <v>0.2821</v>
+        <v>0.0333</v>
       </c>
       <c r="K123" s="31" t="n">
-        <v>-0.2063</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="L123" s="28" t="inlineStr">
         <is>
-          <t>0.56~1.04%</t>
+          <t>0.10~0.29%</t>
         </is>
       </c>
       <c r="M123" s="32" t="inlineStr">
         <is>
-          <t>3해 연37.9% · 변동성 28.2% (위험대비 1.25) (달 간격) · 최대낙폭 -21% · 보수 0.56% · 가장 나쁜 창 연37.9%</t>
+          <t>3해 연0.3% · 변동성 3.3% (위험대비 -0.76) (달 간격) · 최대낙폭 -4% · 보수 0.10% · 가장 나쁜 창 연0.3%</t>
         </is>
       </c>
     </row>
@@ -11842,7 +11842,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr"/>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -713,10 +713,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:S120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -728,6 +728,7 @@
     <col width="18" customWidth="1" min="7" max="7"/>
     <col hidden="1" width="13" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="13" customWidth="1" min="9" max="9"/>
+    <col hidden="1" width="13" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1239,7 +1240,7 @@
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>「상품」 시트에서 채택을 Y 로 바꾸면 여기에 올라옵니다. 배분액은 그 자산군 금액을 채택한 수로 나눈 것입니다. 상품 아래 회색 줄이 그 상품을 고른 까닭입니다.</t>
+          <t>「상품」 시트에서 채택을 Y 로 바꾸면 여기에 올라옵니다. 배분액은 그 자산군 금액을 채택한 수로 나눈 것입니다. 상품 아래 회색 줄이 고른 까닭입니다 — 왼쪽 여백의 「−」로 접으면 인쇄에서도 빠집니다.</t>
         </is>
       </c>
     </row>
@@ -1311,10 +1312,15 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="24" customHeight="1">
+    <row r="36" outlineLevel="1" ht="24" customHeight="1">
       <c r="A36" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$35&amp;"|"&amp;1,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S36" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1344,10 +1350,15 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="24" customHeight="1">
+    <row r="38" outlineLevel="1" ht="24" customHeight="1">
       <c r="A38" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$35&amp;"|"&amp;2,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S38" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1377,10 +1388,15 @@
         <v/>
       </c>
     </row>
-    <row r="40" ht="24" customHeight="1">
+    <row r="40" outlineLevel="1" ht="24" customHeight="1">
       <c r="A40" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$35&amp;"|"&amp;3,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S40" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -1410,10 +1426,15 @@
         <v/>
       </c>
     </row>
-    <row r="42" ht="24" customHeight="1">
+    <row r="42" outlineLevel="1" ht="24" customHeight="1">
       <c r="A42" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$35&amp;"|"&amp;4,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S42" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -1443,11 +1464,16 @@
         <v/>
       </c>
     </row>
-    <row r="44" ht="24" customHeight="1">
+    <row r="44" outlineLevel="1" ht="24" customHeight="1">
       <c r="A44" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$35&amp;"|"&amp;5,상품!$N$7:$N$156,0)),"")</f>
         <v/>
       </c>
+      <c r="S44" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="14" t="inlineStr">
@@ -1480,10 +1506,15 @@
         <v/>
       </c>
     </row>
-    <row r="46" ht="24" customHeight="1">
+    <row r="46" outlineLevel="1" ht="24" customHeight="1">
       <c r="A46" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$45&amp;"|"&amp;1,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S46" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1513,10 +1544,15 @@
         <v/>
       </c>
     </row>
-    <row r="48" ht="24" customHeight="1">
+    <row r="48" outlineLevel="1" ht="24" customHeight="1">
       <c r="A48" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$45&amp;"|"&amp;2,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S48" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -1546,10 +1582,15 @@
         <v/>
       </c>
     </row>
-    <row r="50" ht="24" customHeight="1">
+    <row r="50" outlineLevel="1" ht="24" customHeight="1">
       <c r="A50" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$45&amp;"|"&amp;3,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S50" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -1579,10 +1620,15 @@
         <v/>
       </c>
     </row>
-    <row r="52" ht="24" customHeight="1">
+    <row r="52" outlineLevel="1" ht="24" customHeight="1">
       <c r="A52" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$45&amp;"|"&amp;4,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S52" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -1612,11 +1658,16 @@
         <v/>
       </c>
     </row>
-    <row r="54" ht="24" customHeight="1">
+    <row r="54" outlineLevel="1" ht="24" customHeight="1">
       <c r="A54" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$45&amp;"|"&amp;5,상품!$N$7:$N$156,0)),"")</f>
         <v/>
       </c>
+      <c r="S54" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
@@ -1649,10 +1700,15 @@
         <v/>
       </c>
     </row>
-    <row r="56" ht="24" customHeight="1">
+    <row r="56" outlineLevel="1" ht="24" customHeight="1">
       <c r="A56" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$55&amp;"|"&amp;1,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S56" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1682,10 +1738,15 @@
         <v/>
       </c>
     </row>
-    <row r="58" ht="24" customHeight="1">
+    <row r="58" outlineLevel="1" ht="24" customHeight="1">
       <c r="A58" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$55&amp;"|"&amp;2,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S58" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -1715,10 +1776,15 @@
         <v/>
       </c>
     </row>
-    <row r="60" ht="24" customHeight="1">
+    <row r="60" outlineLevel="1" ht="24" customHeight="1">
       <c r="A60" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$55&amp;"|"&amp;3,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S60" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -1748,10 +1814,15 @@
         <v/>
       </c>
     </row>
-    <row r="62" ht="24" customHeight="1">
+    <row r="62" outlineLevel="1" ht="24" customHeight="1">
       <c r="A62" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$55&amp;"|"&amp;4,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S62" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -1781,11 +1852,16 @@
         <v/>
       </c>
     </row>
-    <row r="64" ht="24" customHeight="1">
+    <row r="64" outlineLevel="1" ht="24" customHeight="1">
       <c r="A64" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$55&amp;"|"&amp;5,상품!$N$7:$N$156,0)),"")</f>
         <v/>
       </c>
+      <c r="S64" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="14" t="inlineStr">
@@ -1818,10 +1894,15 @@
         <v/>
       </c>
     </row>
-    <row r="66" ht="24" customHeight="1">
+    <row r="66" outlineLevel="1" ht="24" customHeight="1">
       <c r="A66" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$65&amp;"|"&amp;1,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S66" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -1851,10 +1932,15 @@
         <v/>
       </c>
     </row>
-    <row r="68" ht="24" customHeight="1">
+    <row r="68" outlineLevel="1" ht="24" customHeight="1">
       <c r="A68" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$65&amp;"|"&amp;2,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S68" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -1884,10 +1970,15 @@
         <v/>
       </c>
     </row>
-    <row r="70" ht="24" customHeight="1">
+    <row r="70" outlineLevel="1" ht="24" customHeight="1">
       <c r="A70" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$65&amp;"|"&amp;3,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S70" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -1917,10 +2008,15 @@
         <v/>
       </c>
     </row>
-    <row r="72" ht="24" customHeight="1">
+    <row r="72" outlineLevel="1" ht="24" customHeight="1">
       <c r="A72" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$65&amp;"|"&amp;4,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S72" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -1950,11 +2046,16 @@
         <v/>
       </c>
     </row>
-    <row r="74" ht="24" customHeight="1">
+    <row r="74" outlineLevel="1" ht="24" customHeight="1">
       <c r="A74" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$65&amp;"|"&amp;5,상품!$N$7:$N$156,0)),"")</f>
         <v/>
       </c>
+      <c r="S74" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="14" t="inlineStr">
@@ -1987,10 +2088,15 @@
         <v/>
       </c>
     </row>
-    <row r="76" ht="24" customHeight="1">
+    <row r="76" outlineLevel="1" ht="24" customHeight="1">
       <c r="A76" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$75&amp;"|"&amp;1,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S76" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -2020,10 +2126,15 @@
         <v/>
       </c>
     </row>
-    <row r="78" ht="24" customHeight="1">
+    <row r="78" outlineLevel="1" ht="24" customHeight="1">
       <c r="A78" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$75&amp;"|"&amp;2,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S78" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -2053,10 +2164,15 @@
         <v/>
       </c>
     </row>
-    <row r="80" ht="24" customHeight="1">
+    <row r="80" outlineLevel="1" ht="24" customHeight="1">
       <c r="A80" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$75&amp;"|"&amp;3,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S80" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -2086,10 +2202,15 @@
         <v/>
       </c>
     </row>
-    <row r="82" ht="24" customHeight="1">
+    <row r="82" outlineLevel="1" ht="24" customHeight="1">
       <c r="A82" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$75&amp;"|"&amp;4,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S82" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -2119,11 +2240,16 @@
         <v/>
       </c>
     </row>
-    <row r="84" ht="24" customHeight="1">
+    <row r="84" outlineLevel="1" ht="24" customHeight="1">
       <c r="A84" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$75&amp;"|"&amp;5,상품!$N$7:$N$156,0)),"")</f>
         <v/>
       </c>
+      <c r="S84" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="14" t="inlineStr">
@@ -2156,10 +2282,15 @@
         <v/>
       </c>
     </row>
-    <row r="86" ht="24" customHeight="1">
+    <row r="86" outlineLevel="1" ht="24" customHeight="1">
       <c r="A86" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$85&amp;"|"&amp;1,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S86" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -2189,10 +2320,15 @@
         <v/>
       </c>
     </row>
-    <row r="88" ht="24" customHeight="1">
+    <row r="88" outlineLevel="1" ht="24" customHeight="1">
       <c r="A88" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$85&amp;"|"&amp;2,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S88" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -2222,10 +2358,15 @@
         <v/>
       </c>
     </row>
-    <row r="90" ht="24" customHeight="1">
+    <row r="90" outlineLevel="1" ht="24" customHeight="1">
       <c r="A90" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$85&amp;"|"&amp;3,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S90" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -2255,10 +2396,15 @@
         <v/>
       </c>
     </row>
-    <row r="92" ht="24" customHeight="1">
+    <row r="92" outlineLevel="1" ht="24" customHeight="1">
       <c r="A92" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$85&amp;"|"&amp;4,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S92" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -2288,10 +2434,15 @@
         <v/>
       </c>
     </row>
-    <row r="94" ht="24" customHeight="1">
+    <row r="94" outlineLevel="1" ht="24" customHeight="1">
       <c r="A94" s="26">
         <f>IFERROR(INDEX(상품!$M$7:$M$156,MATCH($A$85&amp;"|"&amp;5,상품!$N$7:$N$156,0)),"")</f>
         <v/>
+      </c>
+      <c r="S94" s="22" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
       </c>
     </row>
     <row r="95" ht="26" customHeight="1">
@@ -2472,7 +2623,7 @@
     <row r="120">
       <c r="A120" s="22" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-20 16:03:37 · 문서 2026-09-20 21:00 (KST)</t>
+          <t>유니버스 2026-09-20 16:03:37 · 문서 2026-09-20 21:05 (KST)</t>
         </is>
       </c>
     </row>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제안서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="자산군" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상품" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="출처" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용법" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="제안서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="배분규칙" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="자산군" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="상품" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="출처" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="기대수익률" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="사용법" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'상품'!$A$6:$M$156</definedName>
@@ -2623,7 +2623,7 @@
     <row r="120">
       <c r="A120" s="22" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-20 16:03:37 · 문서 2026-09-20 21:05 (KST)</t>
+          <t>유니버스 2026-10-01 13:45:52 · 문서 2026-10-01 13:46 (KST)</t>
         </is>
       </c>
     </row>
@@ -3598,13 +3598,13 @@
         <v>25</v>
       </c>
       <c r="D7" s="31" t="n">
-        <v>0.2122905027932962</v>
+        <v>0.1469550686966208</v>
       </c>
       <c r="E7" s="31" t="n">
         <v>0.24025</v>
       </c>
       <c r="F7" s="31" t="n">
-        <v>-0.4063051588931482</v>
+        <v>-0.4063048225942869</v>
       </c>
     </row>
     <row r="8">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="B9" s="30" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C9" s="30" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D9" s="31" t="n">
-        <v>0.333284</v>
+        <v>0.294202</v>
       </c>
       <c r="E9" s="31" t="n">
         <v>0.18285</v>
@@ -3664,7 +3664,7 @@
         <v>60</v>
       </c>
       <c r="D10" s="31" t="n">
-        <v>0.1747404299625906</v>
+        <v>0.1673868255660437</v>
       </c>
       <c r="E10" s="31" t="n">
         <v>0.1834939037658289</v>
@@ -3686,13 +3686,13 @@
         <v>99</v>
       </c>
       <c r="D11" s="31" t="n">
-        <v>0.1049382716049381</v>
+        <v>0.06148925357964918</v>
       </c>
       <c r="E11" s="31" t="n">
-        <v>0.2923973274425171</v>
+        <v>0.2930684106655739</v>
       </c>
       <c r="F11" s="31" t="n">
-        <v>-0.3235610824922673</v>
+        <v>-0.3249499680915918</v>
       </c>
     </row>
     <row r="12">
@@ -3702,13 +3702,13 @@
         </is>
       </c>
       <c r="B12" s="30" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C12" s="30" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D12" s="31" t="n">
-        <v>0.1178985</v>
+        <v>0.104064</v>
       </c>
       <c r="E12" s="31" t="n">
         <v>0.1361</v>
@@ -3730,7 +3730,7 @@
         <v>80</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>0.028086</v>
+        <v>0.0281925</v>
       </c>
       <c r="E13" s="31" t="n">
         <v>0.0326</v>
@@ -5537,7 +5537,7 @@
       </c>
       <c r="F32" s="37" t="inlineStr">
         <is>
-          <t>646조원</t>
+          <t>629조원</t>
         </is>
       </c>
       <c r="G32" s="38" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="F33" s="30" t="inlineStr">
         <is>
-          <t>526조원</t>
+          <t>504조원</t>
         </is>
       </c>
       <c r="G33" s="32" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="F34" s="37" t="inlineStr">
         <is>
-          <t>258조원</t>
+          <t>251조원</t>
         </is>
       </c>
       <c r="G34" s="38" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="F35" s="30" t="inlineStr">
         <is>
-          <t>407조원</t>
+          <t>404조원</t>
         </is>
       </c>
       <c r="G35" s="32" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="F36" s="37" t="inlineStr">
         <is>
-          <t>932조원</t>
+          <t>910조원</t>
         </is>
       </c>
       <c r="G36" s="38" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="F37" s="30" t="inlineStr">
         <is>
-          <t>182조원</t>
+          <t>171조원</t>
         </is>
       </c>
       <c r="G37" s="32" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="F38" s="37" t="inlineStr">
         <is>
-          <t>902조원</t>
+          <t>868조원</t>
         </is>
       </c>
       <c r="G38" s="38" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="F39" s="30" t="inlineStr">
         <is>
-          <t>362조원</t>
+          <t>340조원</t>
         </is>
       </c>
       <c r="G39" s="32" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="F40" s="37" t="inlineStr">
         <is>
-          <t>1,288조원</t>
+          <t>1,196조원</t>
         </is>
       </c>
       <c r="G40" s="38" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="F41" s="30" t="inlineStr">
         <is>
-          <t>570조원</t>
+          <t>545조원</t>
         </is>
       </c>
       <c r="G41" s="32" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="F42" s="37" t="inlineStr">
         <is>
-          <t>161조원</t>
+          <t>153조원</t>
         </is>
       </c>
       <c r="G42" s="38" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="F43" s="30" t="inlineStr">
         <is>
-          <t>1,512조원</t>
+          <t>1,450조원</t>
         </is>
       </c>
       <c r="G43" s="32" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="F44" s="37" t="inlineStr">
         <is>
-          <t>380조원</t>
+          <t>357조원</t>
         </is>
       </c>
       <c r="G44" s="38" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="F45" s="30" t="inlineStr">
         <is>
-          <t>289조원</t>
+          <t>310조원</t>
         </is>
       </c>
       <c r="G45" s="32" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="F46" s="37" t="inlineStr">
         <is>
-          <t>515조원</t>
+          <t>507조원</t>
         </is>
       </c>
       <c r="G46" s="38" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="F47" s="30" t="inlineStr">
         <is>
-          <t>1,425조원</t>
+          <t>1,403조원</t>
         </is>
       </c>
       <c r="G47" s="32" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="F48" s="37" t="inlineStr">
         <is>
-          <t>1,177조원</t>
+          <t>1,121조원</t>
         </is>
       </c>
       <c r="G48" s="38" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="F49" s="30" t="inlineStr">
         <is>
-          <t>598조원</t>
+          <t>577조원</t>
         </is>
       </c>
       <c r="G49" s="32" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F50" s="37" t="inlineStr">
         <is>
-          <t>958조원</t>
+          <t>917조원</t>
         </is>
       </c>
       <c r="G50" s="38" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="F51" s="30" t="inlineStr">
         <is>
-          <t>441조원</t>
+          <t>402조원</t>
         </is>
       </c>
       <c r="G51" s="32" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="F52" s="37" t="inlineStr">
         <is>
-          <t>412조원</t>
+          <t>442조원</t>
         </is>
       </c>
       <c r="G52" s="38" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="F53" s="30" t="inlineStr">
         <is>
-          <t>6,799조원</t>
+          <t>6,610조원</t>
         </is>
       </c>
       <c r="G53" s="32" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="F54" s="37" t="inlineStr">
         <is>
-          <t>179조원</t>
+          <t>180조원</t>
         </is>
       </c>
       <c r="G54" s="38" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="F55" s="30" t="inlineStr">
         <is>
-          <t>230조원</t>
+          <t>220조원</t>
         </is>
       </c>
       <c r="G55" s="32" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="F56" s="37" t="inlineStr">
         <is>
-          <t>452조원</t>
+          <t>441조원</t>
         </is>
       </c>
       <c r="G56" s="38" t="inlineStr">
@@ -10362,7 +10362,7 @@
       </c>
       <c r="F107" s="30" t="inlineStr">
         <is>
-          <t>1,952억원</t>
+          <t>1,977억원</t>
         </is>
       </c>
       <c r="G107" s="32" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="F109" s="30" t="inlineStr">
         <is>
-          <t>1,392억원</t>
+          <t>1,384억원</t>
         </is>
       </c>
       <c r="G109" s="32" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="F110" s="37" t="inlineStr">
         <is>
-          <t>4,207억원</t>
+          <t>4,145억원</t>
         </is>
       </c>
       <c r="G110" s="38" t="inlineStr">
@@ -10626,7 +10626,7 @@
       </c>
       <c r="F111" s="30" t="inlineStr">
         <is>
-          <t>493억원</t>
+          <t>494억원</t>
         </is>
       </c>
       <c r="G111" s="32" t="inlineStr">
@@ -10823,7 +10823,7 @@
       </c>
       <c r="F114" s="37" t="inlineStr">
         <is>
-          <t>150억원</t>
+          <t>161억원</t>
         </is>
       </c>
       <c r="G114" s="38" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="F115" s="30" t="inlineStr">
         <is>
-          <t>8,313억원</t>
+          <t>8,311억원</t>
         </is>
       </c>
       <c r="G115" s="32" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="F117" s="30" t="inlineStr">
         <is>
-          <t>580억원</t>
+          <t>582억원</t>
         </is>
       </c>
       <c r="G117" s="32" t="inlineStr">
@@ -11083,7 +11083,7 @@
       </c>
       <c r="F118" s="37" t="inlineStr">
         <is>
-          <t>515억원</t>
+          <t>516억원</t>
         </is>
       </c>
       <c r="G118" s="38" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="F119" s="30" t="inlineStr">
         <is>
-          <t>186억원</t>
+          <t>185억원</t>
         </is>
       </c>
       <c r="G119" s="32" t="inlineStr">
@@ -11198,22 +11198,22 @@
       </c>
       <c r="C120" s="36" t="inlineStr">
         <is>
-          <t>신영마라톤지주회사증권자투자신탁(주식)운용</t>
+          <t>KB퇴직연금배당40증권자투자신탁(채권혼합)</t>
         </is>
       </c>
       <c r="D120" s="36" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E120" s="36" t="inlineStr">
         <is>
-          <t>신영자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F120" s="37" t="inlineStr">
         <is>
-          <t>316억원</t>
+          <t>1조원</t>
         </is>
       </c>
       <c r="G120" s="38" t="inlineStr">
@@ -11227,22 +11227,22 @@
         </is>
       </c>
       <c r="I120" s="39" t="n">
-        <v>0.4483</v>
+        <v>0.1845</v>
       </c>
       <c r="J120" s="39" t="n">
-        <v>0.3544</v>
+        <v>0.1429</v>
       </c>
       <c r="K120" s="40" t="n">
-        <v>-0.2314</v>
+        <v>-0.0965</v>
       </c>
       <c r="L120" s="37" t="inlineStr">
         <is>
-          <t>0.52~1.49%</t>
+          <t>0.46~0.80%</t>
         </is>
       </c>
       <c r="M120" s="41" t="inlineStr">
         <is>
-          <t>3해 연44.8% · 변동성 35.4% (위험대비 1.19) (달 간격) · 최대낙폭 -23% · 보수 0.52% · 가장 나쁜 창 연44.8%</t>
+          <t>3해 연18.4% · 변동성 14.3% (위험대비 1.09) (달 간격) · 최대낙폭 -10% · 보수 0.46% · 가장 나쁜 창 연18.4%</t>
         </is>
       </c>
       <c r="N120" s="35">
@@ -11263,22 +11263,22 @@
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>KB퇴직연금배당40증권자투자신탁(채권혼합)</t>
+          <t>신영마라톤지주회사증권자투자신탁(주식)운용</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>신영자산운용</t>
         </is>
       </c>
       <c r="F121" s="30" t="inlineStr">
         <is>
-          <t>1조원</t>
+          <t>316억원</t>
         </is>
       </c>
       <c r="G121" s="32" t="inlineStr">
@@ -11292,22 +11292,22 @@
         </is>
       </c>
       <c r="I121" s="31" t="n">
-        <v>0.1845</v>
+        <v>0.4483</v>
       </c>
       <c r="J121" s="31" t="n">
-        <v>0.1429</v>
+        <v>0.3544</v>
       </c>
       <c r="K121" s="33" t="n">
-        <v>-0.0965</v>
+        <v>-0.2314</v>
       </c>
       <c r="L121" s="30" t="inlineStr">
         <is>
-          <t>0.46~0.80%</t>
+          <t>0.52~1.49%</t>
         </is>
       </c>
       <c r="M121" s="34" t="inlineStr">
         <is>
-          <t>3해 연18.4% · 변동성 14.3% (위험대비 1.09) (달 간격) · 최대낙폭 -10% · 보수 0.46% · 가장 나쁜 창 연18.4%</t>
+          <t>3해 연44.8% · 변동성 35.4% (위험대비 1.19) (달 간격) · 최대낙폭 -23% · 보수 0.52% · 가장 나쁜 창 연44.8%</t>
         </is>
       </c>
       <c r="N121" s="35">
@@ -11343,7 +11343,7 @@
       </c>
       <c r="F122" s="37" t="inlineStr">
         <is>
-          <t>1,688억원</t>
+          <t>1,685억원</t>
         </is>
       </c>
       <c r="G122" s="38" t="inlineStr">
@@ -11393,22 +11393,22 @@
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>BNK내일환매초단기채증권자투자신탁(채권)</t>
+          <t>키움코리아인덱스증권자투자신탁 1[주식]</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>비엔케이자산운용</t>
+          <t>키움투자자산운용</t>
         </is>
       </c>
       <c r="F123" s="30" t="inlineStr">
         <is>
-          <t>182억원</t>
+          <t>131억원</t>
         </is>
       </c>
       <c r="G123" s="32" t="inlineStr">
@@ -11422,22 +11422,22 @@
         </is>
       </c>
       <c r="I123" s="31" t="n">
-        <v>0.0027</v>
+        <v>0.4842</v>
       </c>
       <c r="J123" s="31" t="n">
-        <v>0.0333</v>
+        <v>0.4086</v>
       </c>
       <c r="K123" s="33" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.2355</v>
       </c>
       <c r="L123" s="30" t="inlineStr">
         <is>
-          <t>0.10~0.29%</t>
+          <t>0.21~1.22%</t>
         </is>
       </c>
       <c r="M123" s="34" t="inlineStr">
         <is>
-          <t>3해 연0.3% · 변동성 3.3% (위험대비 -0.76) (달 간격) · 최대낙폭 -4% · 보수 0.10% · 가장 나쁜 창 연0.3%</t>
+          <t>3해 연48.4% · 변동성 40.9% (위험대비 1.12) (달 간격) · 최대낙폭 -24% · 보수 0.21% · 가장 나쁜 창 연48.4%</t>
         </is>
       </c>
       <c r="N123" s="35">
@@ -11458,22 +11458,22 @@
       </c>
       <c r="C124" s="36" t="inlineStr">
         <is>
-          <t>키움코리아인덱스증권자투자신탁 1[주식]</t>
+          <t>BNK내일환매초단기채증권자투자신탁(채권)</t>
         </is>
       </c>
       <c r="D124" s="36" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E124" s="36" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
+          <t>비엔케이자산운용</t>
         </is>
       </c>
       <c r="F124" s="37" t="inlineStr">
         <is>
-          <t>131억원</t>
+          <t>176억원</t>
         </is>
       </c>
       <c r="G124" s="38" t="inlineStr">
@@ -11487,22 +11487,22 @@
         </is>
       </c>
       <c r="I124" s="39" t="n">
-        <v>0.4842</v>
+        <v>0.0027</v>
       </c>
       <c r="J124" s="39" t="n">
-        <v>0.4086</v>
+        <v>0.0333</v>
       </c>
       <c r="K124" s="40" t="n">
-        <v>-0.2355</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="L124" s="37" t="inlineStr">
         <is>
-          <t>0.21~1.22%</t>
+          <t>0.10~0.29%</t>
         </is>
       </c>
       <c r="M124" s="41" t="inlineStr">
         <is>
-          <t>3해 연48.4% · 변동성 40.9% (위험대비 1.12) (달 간격) · 최대낙폭 -24% · 보수 0.21% · 가장 나쁜 창 연48.4%</t>
+          <t>3해 연0.3% · 변동성 3.3% (위험대비 -0.76) (달 간격) · 최대낙폭 -4% · 보수 0.10% · 가장 나쁜 창 연0.3%</t>
         </is>
       </c>
       <c r="N124" s="35">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>DB진주찾기증권자투자신탁 1[주식]_운용</t>
+          <t>교보악사파워인덱스증권자투자신탁 2(주식)(운용)</t>
         </is>
       </c>
       <c r="D125" s="14" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>디비자산운용</t>
+          <t>교보악사자산운용</t>
         </is>
       </c>
       <c r="F125" s="30" t="inlineStr">
         <is>
-          <t>226억원</t>
+          <t>191억원</t>
         </is>
       </c>
       <c r="G125" s="32" t="inlineStr">
@@ -11552,22 +11552,22 @@
         </is>
       </c>
       <c r="I125" s="31" t="n">
-        <v>0.4693</v>
+        <v>0.4859000000000001</v>
       </c>
       <c r="J125" s="31" t="n">
-        <v>0.3312</v>
+        <v>0.4063000000000001</v>
       </c>
       <c r="K125" s="33" t="n">
-        <v>-0.1702</v>
+        <v>-0.2397</v>
       </c>
       <c r="L125" s="30" t="inlineStr">
         <is>
-          <t>0.82~1.78%</t>
+          <t>0.28~1.17%</t>
         </is>
       </c>
       <c r="M125" s="34" t="inlineStr">
         <is>
-          <t>3해 연46.9% · 변동성 33.1% (위험대비 1.33) (달 간격) · 최대낙폭 -17% · 보수 0.82% · 가장 나쁜 창 연46.9%</t>
+          <t>3해 연48.6% · 변동성 40.6% (위험대비 1.13) (달 간격) · 최대낙폭 -24% · 보수 0.28% · 가장 나쁜 창 연48.6%</t>
         </is>
       </c>
       <c r="N125" s="35">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C126" s="36" t="inlineStr">
         <is>
-          <t>교보악사파워인덱스증권자투자신탁 2(주식)(운용)</t>
+          <t>DB진주찾기증권자투자신탁 1[주식]_운용</t>
         </is>
       </c>
       <c r="D126" s="36" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E126" s="36" t="inlineStr">
         <is>
-          <t>교보악사자산운용</t>
+          <t>디비자산운용</t>
         </is>
       </c>
       <c r="F126" s="37" t="inlineStr">
         <is>
-          <t>191억원</t>
+          <t>226억원</t>
         </is>
       </c>
       <c r="G126" s="38" t="inlineStr">
@@ -11617,22 +11617,22 @@
         </is>
       </c>
       <c r="I126" s="39" t="n">
-        <v>0.4859000000000001</v>
+        <v>0.4693</v>
       </c>
       <c r="J126" s="39" t="n">
-        <v>0.4063000000000001</v>
+        <v>0.3312</v>
       </c>
       <c r="K126" s="40" t="n">
-        <v>-0.2397</v>
+        <v>-0.1702</v>
       </c>
       <c r="L126" s="37" t="inlineStr">
         <is>
-          <t>0.28~1.17%</t>
+          <t>0.82~1.78%</t>
         </is>
       </c>
       <c r="M126" s="41" t="inlineStr">
         <is>
-          <t>3해 연48.6% · 변동성 40.6% (위험대비 1.13) (달 간격) · 최대낙폭 -24% · 보수 0.28% · 가장 나쁜 창 연48.6%</t>
+          <t>3해 연46.9% · 변동성 33.1% (위험대비 1.33) (달 간격) · 최대낙폭 -17% · 보수 0.82% · 가장 나쁜 창 연46.9%</t>
         </is>
       </c>
       <c r="N126" s="35">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="F127" s="30" t="inlineStr">
         <is>
-          <t>136억원</t>
+          <t>137억원</t>
         </is>
       </c>
       <c r="G127" s="32" t="inlineStr">
@@ -11783,22 +11783,22 @@
       </c>
       <c r="C129" s="14" t="inlineStr">
         <is>
-          <t>교보악사파워인덱스증권자투자신탁 1(주식)(운용)</t>
+          <t>다올퇴직연금40증권자투자신탁[채권혼합](운)</t>
         </is>
       </c>
       <c r="D129" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>교보악사자산운용</t>
+          <t>다올자산운용</t>
         </is>
       </c>
       <c r="F129" s="30" t="inlineStr">
         <is>
-          <t>2,914억원</t>
+          <t>193억원</t>
         </is>
       </c>
       <c r="G129" s="32" t="inlineStr">
@@ -11812,22 +11812,22 @@
         </is>
       </c>
       <c r="I129" s="31" t="n">
-        <v>0.4796</v>
+        <v>0.1779</v>
       </c>
       <c r="J129" s="31" t="n">
-        <v>0.4089</v>
+        <v>0.1425</v>
       </c>
       <c r="K129" s="33" t="n">
-        <v>-0.2396</v>
+        <v>-0.0872</v>
       </c>
       <c r="L129" s="30" t="inlineStr">
         <is>
-          <t>0.17~1.28%</t>
+          <t>0.53~0.80%</t>
         </is>
       </c>
       <c r="M129" s="34" t="inlineStr">
         <is>
-          <t>3해 연48.0% · 변동성 40.9% (위험대비 1.10) (달 간격) · 최대낙폭 -24% · 보수 0.17% · 가장 나쁜 창 연48.0%</t>
+          <t>3해 연17.8% · 변동성 14.2% (위험대비 1.05) (달 간격) · 최대낙폭 -9% · 보수 0.53% · 가장 나쁜 창 연17.8%</t>
         </is>
       </c>
       <c r="N129" s="35">
@@ -11848,22 +11848,22 @@
       </c>
       <c r="C130" s="36" t="inlineStr">
         <is>
-          <t>다올퇴직연금40증권자투자신탁[채권혼합](운)</t>
+          <t>교보악사파워인덱스증권자투자신탁 1(주식)(운용)</t>
         </is>
       </c>
       <c r="D130" s="36" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E130" s="36" t="inlineStr">
         <is>
-          <t>다올자산운용</t>
+          <t>교보악사자산운용</t>
         </is>
       </c>
       <c r="F130" s="37" t="inlineStr">
         <is>
-          <t>193억원</t>
+          <t>2,925억원</t>
         </is>
       </c>
       <c r="G130" s="38" t="inlineStr">
@@ -11877,22 +11877,22 @@
         </is>
       </c>
       <c r="I130" s="39" t="n">
-        <v>0.1779</v>
+        <v>0.4796</v>
       </c>
       <c r="J130" s="39" t="n">
-        <v>0.1425</v>
+        <v>0.4089</v>
       </c>
       <c r="K130" s="40" t="n">
-        <v>-0.0872</v>
+        <v>-0.2396</v>
       </c>
       <c r="L130" s="37" t="inlineStr">
         <is>
-          <t>0.53~0.80%</t>
+          <t>0.17~1.28%</t>
         </is>
       </c>
       <c r="M130" s="41" t="inlineStr">
         <is>
-          <t>3해 연17.8% · 변동성 14.2% (위험대비 1.05) (달 간격) · 최대낙폭 -9% · 보수 0.53% · 가장 나쁜 창 연17.8%</t>
+          <t>3해 연48.0% · 변동성 40.9% (위험대비 1.10) (달 간격) · 최대낙폭 -24% · 보수 0.17% · 가장 나쁜 창 연48.0%</t>
         </is>
       </c>
       <c r="N130" s="35">
@@ -11928,7 +11928,7 @@
       </c>
       <c r="F131" s="30" t="inlineStr">
         <is>
-          <t>326억원</t>
+          <t>323억원</t>
         </is>
       </c>
       <c r="G131" s="32" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="F132" s="37" t="inlineStr">
         <is>
-          <t>237억원</t>
+          <t>234억원</t>
         </is>
       </c>
       <c r="G132" s="38" t="inlineStr">
@@ -12058,7 +12058,7 @@
       </c>
       <c r="F133" s="30" t="inlineStr">
         <is>
-          <t>133억원</t>
+          <t>132억원</t>
         </is>
       </c>
       <c r="G133" s="32" t="inlineStr">
@@ -12188,7 +12188,7 @@
       </c>
       <c r="F135" s="30" t="inlineStr">
         <is>
-          <t>5,716억원</t>
+          <t>5,707억원</t>
         </is>
       </c>
       <c r="G135" s="32" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="F136" s="37" t="inlineStr">
         <is>
-          <t>1,626억원</t>
+          <t>1,628억원</t>
         </is>
       </c>
       <c r="G136" s="38" t="inlineStr">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="F137" s="30" t="inlineStr">
         <is>
-          <t>655억원</t>
+          <t>647억원</t>
         </is>
       </c>
       <c r="G137" s="32" t="inlineStr">
@@ -12368,22 +12368,22 @@
       </c>
       <c r="C138" s="36" t="inlineStr">
         <is>
-          <t>NH-AmundiSignatureOCIO성장형증권자투자신탁(UH)[혼합-재간접형]</t>
+          <t>AB셀렉트미국증권투자신탁(주식-재간접형)</t>
         </is>
       </c>
       <c r="D138" s="36" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E138" s="36" t="inlineStr">
         <is>
-          <t>엔에이치아문디자산운용</t>
+          <t>얼라이언스번스틴자산운용</t>
         </is>
       </c>
       <c r="F138" s="37" t="inlineStr">
         <is>
-          <t>155억원</t>
+          <t>304억원</t>
         </is>
       </c>
       <c r="G138" s="38" t="inlineStr">
@@ -12397,22 +12397,22 @@
         </is>
       </c>
       <c r="I138" s="39" t="n">
-        <v>0.1817</v>
+        <v>0.1761</v>
       </c>
       <c r="J138" s="39" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1169</v>
       </c>
       <c r="K138" s="40" t="n">
-        <v>-0.0814</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="L138" s="37" t="inlineStr">
         <is>
-          <t>0.79~1.39%</t>
+          <t>0.27~1.56%</t>
         </is>
       </c>
       <c r="M138" s="41" t="inlineStr">
         <is>
-          <t>3해 연18.2% · 변동성 9.9% (위험대비 1.56) (달 간격) · 최대낙폭 -8% · 보수 0.79% · 가장 나쁜 창 연16.7%</t>
+          <t>3해 연17.6% · 변동성 11.7% (위험대비 1.27) (달 간격) · 최대낙폭 -8% · 보수 0.27% · 가장 나쁜 창 연14.5%</t>
         </is>
       </c>
       <c r="N138" s="35">
@@ -12433,22 +12433,22 @@
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>AB셀렉트미국증권투자신탁(주식-재간접형)</t>
+          <t>NH-AmundiSignatureOCIO성장형증권자투자신탁(UH)[혼합-재간접형]</t>
         </is>
       </c>
       <c r="D139" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>얼라이언스번스틴자산운용</t>
+          <t>엔에이치아문디자산운용</t>
         </is>
       </c>
       <c r="F139" s="30" t="inlineStr">
         <is>
-          <t>305억원</t>
+          <t>160억원</t>
         </is>
       </c>
       <c r="G139" s="32" t="inlineStr">
@@ -12462,22 +12462,22 @@
         </is>
       </c>
       <c r="I139" s="31" t="n">
-        <v>0.1761</v>
+        <v>0.1817</v>
       </c>
       <c r="J139" s="31" t="n">
-        <v>0.1169</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="K139" s="33" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0814</v>
       </c>
       <c r="L139" s="30" t="inlineStr">
         <is>
-          <t>0.27~1.56%</t>
+          <t>0.79~1.39%</t>
         </is>
       </c>
       <c r="M139" s="34" t="inlineStr">
         <is>
-          <t>3해 연17.6% · 변동성 11.7% (위험대비 1.27) (달 간격) · 최대낙폭 -8% · 보수 0.27% · 가장 나쁜 창 연14.5%</t>
+          <t>3해 연18.2% · 변동성 9.9% (위험대비 1.56) (달 간격) · 최대낙폭 -8% · 보수 0.79% · 가장 나쁜 창 연16.7%</t>
         </is>
       </c>
       <c r="N139" s="35">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="F140" s="37" t="inlineStr">
         <is>
-          <t>1,629억원</t>
+          <t>1,614억원</t>
         </is>
       </c>
       <c r="G140" s="38" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="F141" s="30" t="inlineStr">
         <is>
-          <t>234억원</t>
+          <t>277억원</t>
         </is>
       </c>
       <c r="G141" s="32" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="F142" s="37" t="inlineStr">
         <is>
-          <t>139억원</t>
+          <t>138억원</t>
         </is>
       </c>
       <c r="G142" s="38" t="inlineStr">
@@ -12773,7 +12773,7 @@
       </c>
       <c r="F144" s="37" t="inlineStr">
         <is>
-          <t>502억원</t>
+          <t>506억원</t>
         </is>
       </c>
       <c r="G144" s="38" t="inlineStr">
@@ -12838,7 +12838,7 @@
       </c>
       <c r="F145" s="30" t="inlineStr">
         <is>
-          <t>496억원</t>
+          <t>491억원</t>
         </is>
       </c>
       <c r="G145" s="32" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="F146" s="37" t="inlineStr">
         <is>
-          <t>356억원</t>
+          <t>359억원</t>
         </is>
       </c>
       <c r="G146" s="38" t="inlineStr">
@@ -12968,7 +12968,7 @@
       </c>
       <c r="F147" s="30" t="inlineStr">
         <is>
-          <t>1,120억원</t>
+          <t>1,116억원</t>
         </is>
       </c>
       <c r="G147" s="32" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="F148" s="37" t="inlineStr">
         <is>
-          <t>292억원</t>
+          <t>288억원</t>
         </is>
       </c>
       <c r="G148" s="38" t="inlineStr">
@@ -13163,7 +13163,7 @@
       </c>
       <c r="F150" s="37" t="inlineStr">
         <is>
-          <t>906억원</t>
+          <t>904억원</t>
         </is>
       </c>
       <c r="G150" s="38" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="F153" s="30" t="inlineStr">
         <is>
-          <t>700억원</t>
+          <t>696억원</t>
         </is>
       </c>
       <c r="G153" s="32" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="F155" s="30" t="inlineStr">
         <is>
-          <t>217억원</t>
+          <t>216억원</t>
         </is>
       </c>
       <c r="G155" s="32" t="inlineStr">
@@ -13553,7 +13553,7 @@
       </c>
       <c r="F156" s="37" t="inlineStr">
         <is>
-          <t>176억원</t>
+          <t>178억원</t>
         </is>
       </c>
       <c r="G156" s="38" t="inlineStr">
@@ -13676,11 +13676,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E5" s="44" t="inlineStr">
@@ -13730,7 +13730,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E7" s="44" t="inlineStr"/>
@@ -13751,7 +13751,7 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E8" s="44" t="inlineStr"/>

--- a/고객제안서_자산배분.xlsx
+++ b/고객제안서_자산배분.xlsx
@@ -1088,7 +1088,7 @@
         <v/>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0.0535</v>
+        <v>0.0451</v>
       </c>
       <c r="H23" s="15">
         <f>IF(ISNUMBER($F23),$F23,0)</f>
@@ -2623,7 +2623,7 @@
     <row r="120">
       <c r="A120" s="22" t="inlineStr">
         <is>
-          <t>유니버스 2026-09-20 16:03:37 · 문서 2026-09-20 21:05 (KST)</t>
+          <t>유니버스 2026-10-01 13:53:07 · 문서 2026-10-01 13:53 (KST)</t>
         </is>
       </c>
     </row>
@@ -3598,13 +3598,13 @@
         <v>25</v>
       </c>
       <c r="D7" s="31" t="n">
-        <v>0.2122905027932962</v>
+        <v>0.1469550686966208</v>
       </c>
       <c r="E7" s="31" t="n">
         <v>0.24025</v>
       </c>
       <c r="F7" s="31" t="n">
-        <v>-0.4063051588931482</v>
+        <v>-0.4063048225942869</v>
       </c>
     </row>
     <row r="8">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="B9" s="30" t="n">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C9" s="30" t="n">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D9" s="31" t="n">
-        <v>0.333284</v>
+        <v>0.294202</v>
       </c>
       <c r="E9" s="31" t="n">
         <v>0.18285</v>
@@ -3664,7 +3664,7 @@
         <v>60</v>
       </c>
       <c r="D10" s="31" t="n">
-        <v>0.1747404299625906</v>
+        <v>0.1673868255660437</v>
       </c>
       <c r="E10" s="31" t="n">
         <v>0.1834939037658289</v>
@@ -3686,13 +3686,13 @@
         <v>99</v>
       </c>
       <c r="D11" s="31" t="n">
-        <v>0.1049382716049381</v>
+        <v>0.06148925357964918</v>
       </c>
       <c r="E11" s="31" t="n">
-        <v>0.2923973274425171</v>
+        <v>0.2930684106655739</v>
       </c>
       <c r="F11" s="31" t="n">
-        <v>-0.3235610824922673</v>
+        <v>-0.3249499680915918</v>
       </c>
     </row>
     <row r="12">
@@ -3702,13 +3702,13 @@
         </is>
       </c>
       <c r="B12" s="30" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C12" s="30" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D12" s="31" t="n">
-        <v>0.1178985</v>
+        <v>0.104064</v>
       </c>
       <c r="E12" s="31" t="n">
         <v>0.1361</v>
@@ -3730,13 +3730,13 @@
         <v>80</v>
       </c>
       <c r="D13" s="31" t="n">
-        <v>0.028086</v>
+        <v>0.0281925</v>
       </c>
       <c r="E13" s="31" t="n">
-        <v>0.0326</v>
+        <v>0.003</v>
       </c>
       <c r="F13" s="31" t="n">
-        <v>-0.0344</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="F32" s="37" t="inlineStr">
         <is>
-          <t>646조원</t>
+          <t>629조원</t>
         </is>
       </c>
       <c r="G32" s="38" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="F33" s="30" t="inlineStr">
         <is>
-          <t>526조원</t>
+          <t>504조원</t>
         </is>
       </c>
       <c r="G33" s="32" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="F34" s="37" t="inlineStr">
         <is>
-          <t>258조원</t>
+          <t>251조원</t>
         </is>
       </c>
       <c r="G34" s="38" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="F35" s="30" t="inlineStr">
         <is>
-          <t>407조원</t>
+          <t>404조원</t>
         </is>
       </c>
       <c r="G35" s="32" t="inlineStr">
@@ -5797,7 +5797,7 @@
       </c>
       <c r="F36" s="37" t="inlineStr">
         <is>
-          <t>932조원</t>
+          <t>910조원</t>
         </is>
       </c>
       <c r="G36" s="38" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="F37" s="30" t="inlineStr">
         <is>
-          <t>182조원</t>
+          <t>171조원</t>
         </is>
       </c>
       <c r="G37" s="32" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="F38" s="37" t="inlineStr">
         <is>
-          <t>902조원</t>
+          <t>868조원</t>
         </is>
       </c>
       <c r="G38" s="38" t="inlineStr">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="F39" s="30" t="inlineStr">
         <is>
-          <t>362조원</t>
+          <t>340조원</t>
         </is>
       </c>
       <c r="G39" s="32" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="F40" s="37" t="inlineStr">
         <is>
-          <t>1,288조원</t>
+          <t>1,196조원</t>
         </is>
       </c>
       <c r="G40" s="38" t="inlineStr">
@@ -6122,7 +6122,7 @@
       </c>
       <c r="F41" s="30" t="inlineStr">
         <is>
-          <t>570조원</t>
+          <t>545조원</t>
         </is>
       </c>
       <c r="G41" s="32" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="F42" s="37" t="inlineStr">
         <is>
-          <t>161조원</t>
+          <t>153조원</t>
         </is>
       </c>
       <c r="G42" s="38" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="F43" s="30" t="inlineStr">
         <is>
-          <t>1,512조원</t>
+          <t>1,450조원</t>
         </is>
       </c>
       <c r="G43" s="32" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="F44" s="37" t="inlineStr">
         <is>
-          <t>380조원</t>
+          <t>357조원</t>
         </is>
       </c>
       <c r="G44" s="38" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="F45" s="30" t="inlineStr">
         <is>
-          <t>289조원</t>
+          <t>310조원</t>
         </is>
       </c>
       <c r="G45" s="32" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="F46" s="37" t="inlineStr">
         <is>
-          <t>515조원</t>
+          <t>507조원</t>
         </is>
       </c>
       <c r="G46" s="38" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="F47" s="30" t="inlineStr">
         <is>
-          <t>1,425조원</t>
+          <t>1,403조원</t>
         </is>
       </c>
       <c r="G47" s="32" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="F48" s="37" t="inlineStr">
         <is>
-          <t>1,177조원</t>
+          <t>1,121조원</t>
         </is>
       </c>
       <c r="G48" s="38" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="F49" s="30" t="inlineStr">
         <is>
-          <t>598조원</t>
+          <t>577조원</t>
         </is>
       </c>
       <c r="G49" s="32" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F50" s="37" t="inlineStr">
         <is>
-          <t>958조원</t>
+          <t>917조원</t>
         </is>
       </c>
       <c r="G50" s="38" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="F51" s="30" t="inlineStr">
         <is>
-          <t>441조원</t>
+          <t>402조원</t>
         </is>
       </c>
       <c r="G51" s="32" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="F52" s="37" t="inlineStr">
         <is>
-          <t>412조원</t>
+          <t>442조원</t>
         </is>
       </c>
       <c r="G52" s="38" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="F53" s="30" t="inlineStr">
         <is>
-          <t>6,799조원</t>
+          <t>6,610조원</t>
         </is>
       </c>
       <c r="G53" s="32" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="F54" s="37" t="inlineStr">
         <is>
-          <t>179조원</t>
+          <t>180조원</t>
         </is>
       </c>
       <c r="G54" s="38" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="F55" s="30" t="inlineStr">
         <is>
-          <t>230조원</t>
+          <t>220조원</t>
         </is>
       </c>
       <c r="G55" s="32" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="F56" s="37" t="inlineStr">
         <is>
-          <t>452조원</t>
+          <t>441조원</t>
         </is>
       </c>
       <c r="G56" s="38" t="inlineStr">
@@ -10347,22 +10347,22 @@
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>마이다스거북이90증권자투자신탁 1(주식)(운용)</t>
+          <t>현대인베스트먼트단기증권자투자신탁 1(채권)</t>
         </is>
       </c>
       <c r="D107" s="14" t="inlineStr">
         <is>
-          <t>국내대체</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>마이다스에셋자산운용</t>
+          <t>현대인베스트먼트자산운용</t>
         </is>
       </c>
       <c r="F107" s="30" t="inlineStr">
         <is>
-          <t>1,952억원</t>
+          <t>913억원</t>
         </is>
       </c>
       <c r="G107" s="32" t="inlineStr">
@@ -10376,22 +10376,22 @@
         </is>
       </c>
       <c r="I107" s="31" t="n">
-        <v>0.1644</v>
+        <v>0.032</v>
       </c>
       <c r="J107" s="31" t="n">
-        <v>0.0808</v>
+        <v>0.0042</v>
       </c>
       <c r="K107" s="33" t="n">
-        <v>-0.0366</v>
+        <v>0</v>
       </c>
       <c r="L107" s="30" t="inlineStr">
         <is>
-          <t>0.59~2.09%</t>
+          <t>0.10~0.30%</t>
         </is>
       </c>
       <c r="M107" s="34" t="inlineStr">
         <is>
-          <t>3해 연16.4% · 변동성 8.1% (위험대비 1.69) (달 간격) · 최대낙폭 -4% · 보수 0.59% · 가장 나쁜 창 연16.4%</t>
+          <t>3해 연3.2% · 변동성 0.4% (위험대비 0.93) (달 간격) · 최대낙폭 0% · 보수 0.10% · 가장 나쁜 창 연2.4%</t>
         </is>
       </c>
       <c r="N107" s="35">
@@ -10412,22 +10412,22 @@
       </c>
       <c r="C108" s="36" t="inlineStr">
         <is>
-          <t>이지스코어리테일부동산투자신탁 126</t>
+          <t>KB스타단기플러스증권투자신탁(채권)(운용)</t>
         </is>
       </c>
       <c r="D108" s="36" t="inlineStr">
         <is>
-          <t>국내대체</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E108" s="36" t="inlineStr">
         <is>
-          <t>이지스자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F108" s="37" t="inlineStr">
         <is>
-          <t>606억원</t>
+          <t>1,362억원</t>
         </is>
       </c>
       <c r="G108" s="38" t="inlineStr">
@@ -10441,26 +10441,22 @@
         </is>
       </c>
       <c r="I108" s="39" t="n">
-        <v>0.0469</v>
-      </c>
-      <c r="J108" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K108" s="37" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>0.0256</v>
+      </c>
+      <c r="J108" s="39" t="n">
+        <v>0.0223</v>
+      </c>
+      <c r="K108" s="40" t="n">
+        <v>-0.0305</v>
       </c>
       <c r="L108" s="37" t="inlineStr">
         <is>
-          <t>0.00~0.00%</t>
+          <t>0.05~0.06%</t>
         </is>
       </c>
       <c r="M108" s="41" t="inlineStr">
         <is>
-          <t>3해 연4.7% (감정평가 기준가 — 시세가 아니라 위험을 못 쟀습니다) · 보수 0.00% · 가장 나쁜 창 연4.7%</t>
+          <t>3해 연2.6% · 변동성 2.2% (위험대비 -0.11) (달 간격) · 최대낙폭 -3% · 보수 0.05% · 가장 나쁜 창 연1.7%</t>
         </is>
       </c>
       <c r="N108" s="35">
@@ -10471,7 +10467,7 @@
     <row r="109">
       <c r="A109" s="13" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B109" s="14" t="inlineStr">
@@ -10481,7 +10477,7 @@
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t>유진챔피언중단기채증권자투자신탁(채권)</t>
+          <t>우리단기플러스증권투자신탁(채권)[운용]</t>
         </is>
       </c>
       <c r="D109" s="14" t="inlineStr">
@@ -10491,12 +10487,12 @@
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>유진자산운용</t>
+          <t>우리자산운용</t>
         </is>
       </c>
       <c r="F109" s="30" t="inlineStr">
         <is>
-          <t>1,392억원</t>
+          <t>3,686억원</t>
         </is>
       </c>
       <c r="G109" s="32" t="inlineStr">
@@ -10510,22 +10506,20 @@
         </is>
       </c>
       <c r="I109" s="31" t="n">
-        <v>0.0073</v>
+        <v>0.0273</v>
       </c>
       <c r="J109" s="31" t="n">
-        <v>0.035</v>
+        <v>0.0246</v>
       </c>
       <c r="K109" s="33" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L109" s="30" t="inlineStr">
-        <is>
-          <t>0.11~0.41%</t>
-        </is>
+        <v>-0.0341</v>
+      </c>
+      <c r="L109" s="42" t="n">
+        <v>0.0005</v>
       </c>
       <c r="M109" s="34" t="inlineStr">
         <is>
-          <t>3해 연0.7% · 변동성 3.5% (위험대비 -0.59) (달 간격) · 최대낙폭 -4% · 보수 0.11% · 가장 나쁜 창 연-0.1%</t>
+          <t>3해 연2.7% · 변동성 2.5% (위험대비 -0.03) (달 간격) · 최대낙폭 -3% · 보수 0.05% · 가장 나쁜 창 연1.9%</t>
         </is>
       </c>
       <c r="N109" s="35">
@@ -10546,22 +10540,22 @@
       </c>
       <c r="C110" s="36" t="inlineStr">
         <is>
-          <t>우리반도체BIG2플러스증권투자신탁(채권혼합)</t>
+          <t>마이다스거북이90증권자투자신탁 1(주식)(운용)</t>
         </is>
       </c>
       <c r="D110" s="36" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내대체</t>
         </is>
       </c>
       <c r="E110" s="36" t="inlineStr">
         <is>
-          <t>우리자산운용</t>
+          <t>마이다스에셋자산운용</t>
         </is>
       </c>
       <c r="F110" s="37" t="inlineStr">
         <is>
-          <t>4,207억원</t>
+          <t>1,977억원</t>
         </is>
       </c>
       <c r="G110" s="38" t="inlineStr">
@@ -10575,22 +10569,22 @@
         </is>
       </c>
       <c r="I110" s="39" t="n">
-        <v>0.2141</v>
+        <v>0.1644</v>
       </c>
       <c r="J110" s="39" t="n">
-        <v>0.1545</v>
+        <v>0.0808</v>
       </c>
       <c r="K110" s="40" t="n">
-        <v>-0.09300000000000001</v>
+        <v>-0.0366</v>
       </c>
       <c r="L110" s="37" t="inlineStr">
         <is>
-          <t>0.34~0.89%</t>
+          <t>0.59~2.09%</t>
         </is>
       </c>
       <c r="M110" s="41" t="inlineStr">
         <is>
-          <t>3해 연21.4% · 변동성 15.4% (위험대비 1.20) (달 간격) · 최대낙폭 -9% · 보수 0.34% · 가장 나쁜 창 연21.4%</t>
+          <t>3해 연16.4% · 변동성 8.1% (위험대비 1.69) (달 간격) · 최대낙폭 -4% · 보수 0.59% · 가장 나쁜 창 연16.4%</t>
         </is>
       </c>
       <c r="N110" s="35">
@@ -10601,7 +10595,7 @@
     <row r="111">
       <c r="A111" s="13" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B111" s="14" t="inlineStr">
@@ -10611,22 +10605,22 @@
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>마이다스K200인덱스알파증권자투자신탁(주식-파생형)(운용)</t>
+          <t>코레이트더블루B증권투자신탁[채권]운용</t>
         </is>
       </c>
       <c r="D111" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>마이다스에셋자산운용</t>
+          <t>코레이트자산운용</t>
         </is>
       </c>
       <c r="F111" s="30" t="inlineStr">
         <is>
-          <t>493억원</t>
+          <t>168억원</t>
         </is>
       </c>
       <c r="G111" s="32" t="inlineStr">
@@ -10640,22 +10634,20 @@
         </is>
       </c>
       <c r="I111" s="31" t="n">
-        <v>0.509</v>
+        <v>0.0435</v>
       </c>
       <c r="J111" s="31" t="n">
-        <v>0.3986</v>
+        <v>0.0046</v>
       </c>
       <c r="K111" s="33" t="n">
-        <v>-0.2336</v>
-      </c>
-      <c r="L111" s="30" t="inlineStr">
-        <is>
-          <t>0.06~0.15%</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="L111" s="42" t="n">
+        <v>0.0013</v>
       </c>
       <c r="M111" s="34" t="inlineStr">
         <is>
-          <t>3해 연50.9% · 변동성 39.9% (위험대비 1.21) (달 간격) · 최대낙폭 -23% · 보수 0.06% · 가장 나쁜 창 연50.9%</t>
+          <t>3해 연4.3% · 변동성 0.5% (위험대비 3.35) (달 간격) · 최대낙폭 0% · 보수 0.13% · 가장 나쁜 창 연3.5%</t>
         </is>
       </c>
       <c r="N111" s="35">
@@ -10666,7 +10658,7 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B112" s="36" t="inlineStr">
@@ -10676,7 +10668,7 @@
       </c>
       <c r="C112" s="36" t="inlineStr">
         <is>
-          <t>미래에셋스마트롱숏30증권자투자신탁 1(채권혼합)</t>
+          <t>이지스코어리테일부동산투자신탁 126</t>
         </is>
       </c>
       <c r="D112" s="36" t="inlineStr">
@@ -10686,12 +10678,12 @@
       </c>
       <c r="E112" s="36" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>이지스자산운용</t>
         </is>
       </c>
       <c r="F112" s="37" t="inlineStr">
         <is>
-          <t>147억원</t>
+          <t>606억원</t>
         </is>
       </c>
       <c r="G112" s="38" t="inlineStr">
@@ -10705,22 +10697,26 @@
         </is>
       </c>
       <c r="I112" s="39" t="n">
-        <v>0.04190000000000001</v>
-      </c>
-      <c r="J112" s="39" t="n">
-        <v>0.07820000000000001</v>
-      </c>
-      <c r="K112" s="40" t="n">
-        <v>-0.061</v>
+        <v>0.0469</v>
+      </c>
+      <c r="J112" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K112" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="L112" s="37" t="inlineStr">
         <is>
-          <t>0.50~1.10%</t>
+          <t>0.00~0.00%</t>
         </is>
       </c>
       <c r="M112" s="41" t="inlineStr">
         <is>
-          <t>3해 연4.2% · 변동성 7.8% (위험대비 0.18) (달 간격) · 최대낙폭 -6% · 보수 0.50% · 가장 나쁜 창 연4.2%</t>
+          <t>3해 연4.7% (감정평가 기준가 — 시세가 아니라 위험을 못 쟀습니다) · 보수 0.00% · 가장 나쁜 창 연4.7%</t>
         </is>
       </c>
       <c r="N112" s="35">
@@ -10741,22 +10737,22 @@
       </c>
       <c r="C113" s="14" t="inlineStr">
         <is>
-          <t>이지스리테일부동산투자신탁299</t>
+          <t>DB정통크레딧증권자투자신탁[채권]운용</t>
         </is>
       </c>
       <c r="D113" s="14" t="inlineStr">
         <is>
-          <t>국내대체</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>이지스자산운용</t>
+          <t>디비자산운용</t>
         </is>
       </c>
       <c r="F113" s="30" t="inlineStr">
         <is>
-          <t>211억원</t>
+          <t>596억원</t>
         </is>
       </c>
       <c r="G113" s="32" t="inlineStr">
@@ -10770,24 +10766,22 @@
         </is>
       </c>
       <c r="I113" s="31" t="n">
-        <v>0.0398</v>
-      </c>
-      <c r="J113" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K113" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L113" s="42" t="n">
-        <v>0.0006400000000000001</v>
+        <v>0.0348</v>
+      </c>
+      <c r="J113" s="31" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="K113" s="33" t="n">
+        <v>-0.017</v>
+      </c>
+      <c r="L113" s="30" t="inlineStr">
+        <is>
+          <t>0.14~0.37%</t>
+        </is>
       </c>
       <c r="M113" s="34" t="inlineStr">
         <is>
-          <t>3해 연4.0% (감정평가 기준가 — 시세가 아니라 위험을 못 쟀습니다) · 보수 0.06% · 가장 나쁜 창 연4.0%</t>
+          <t>3해 연3.5% · 변동성 1.5% (위험대비 0.44) (달 간격) · 최대낙폭 -2% · 보수 0.14% · 가장 나쁜 창 연0.1%</t>
         </is>
       </c>
       <c r="N113" s="35">
@@ -10808,22 +10802,22 @@
       </c>
       <c r="C114" s="36" t="inlineStr">
         <is>
-          <t>신한퇴직연금커버드콜인덱스증권자투자신탁[주식혼합-파생형] (종류)</t>
+          <t>한화단기플러스증권투자신탁(채권)[운용]</t>
         </is>
       </c>
       <c r="D114" s="36" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E114" s="36" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>한화자산운용</t>
         </is>
       </c>
       <c r="F114" s="37" t="inlineStr">
         <is>
-          <t>150억원</t>
+          <t>4,611억원</t>
         </is>
       </c>
       <c r="G114" s="38" t="inlineStr">
@@ -10837,22 +10831,20 @@
         </is>
       </c>
       <c r="I114" s="39" t="n">
-        <v>0.1302</v>
+        <v>0.0127</v>
       </c>
       <c r="J114" s="39" t="n">
-        <v>0.0872</v>
+        <v>0.035</v>
       </c>
       <c r="K114" s="40" t="n">
-        <v>-0.055</v>
-      </c>
-      <c r="L114" s="37" t="inlineStr">
-        <is>
-          <t>0.56~0.79%</t>
-        </is>
+        <v>-0.0385</v>
+      </c>
+      <c r="L114" s="43" t="n">
+        <v>0.0005</v>
       </c>
       <c r="M114" s="41" t="inlineStr">
         <is>
-          <t>3해 연13.0% · 변동성 8.7% (위험대비 1.17) (달 간격) · 최대낙폭 -6% · 보수 0.56% · 가장 나쁜 창 연13.0%</t>
+          <t>3해 연1.3% · 변동성 3.5% (위험대비 -0.44) (달 간격) · 최대낙폭 -4% · 보수 0.05% · 가장 나쁜 창 연1.3%</t>
         </is>
       </c>
       <c r="N114" s="35">
@@ -10873,22 +10865,22 @@
       </c>
       <c r="C115" s="14" t="inlineStr">
         <is>
-          <t>신영밸류고배당증권자투자신탁(주식)운용</t>
+          <t>칸서스내일드림튼튼단기채증권투자신탁 1(채권)</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
         <is>
-          <t>신영자산운용</t>
+          <t>칸서스자산운용</t>
         </is>
       </c>
       <c r="F115" s="30" t="inlineStr">
         <is>
-          <t>8,313억원</t>
+          <t>284억원</t>
         </is>
       </c>
       <c r="G115" s="32" t="inlineStr">
@@ -10902,22 +10894,22 @@
         </is>
       </c>
       <c r="I115" s="31" t="n">
-        <v>0.3287</v>
+        <v>0.0214</v>
       </c>
       <c r="J115" s="31" t="n">
-        <v>0.2543</v>
+        <v>0.0245</v>
       </c>
       <c r="K115" s="33" t="n">
-        <v>-0.1498</v>
+        <v>-0.0381</v>
       </c>
       <c r="L115" s="30" t="inlineStr">
         <is>
-          <t>0.45~1.35%</t>
+          <t>0.14~0.36%</t>
         </is>
       </c>
       <c r="M115" s="34" t="inlineStr">
         <is>
-          <t>3해 연32.9% · 변동성 25.4% (위험대비 1.18) (달 간격) · 최대낙폭 -15% · 보수 0.45% · 가장 나쁜 창 연32.9%</t>
+          <t>3해 연2.1% · 변동성 2.5% (위험대비 -0.27) (달 간격) · 최대낙폭 -4% · 보수 0.14% · 가장 나쁜 창 연2.1%</t>
         </is>
       </c>
       <c r="N115" s="35">
@@ -10938,22 +10930,22 @@
       </c>
       <c r="C116" s="36" t="inlineStr">
         <is>
-          <t>신한커버드콜인덱스증권자투자신탁[주식혼합-파생형]</t>
+          <t>삼성ESG밸류채권증권투자신탁 1[채권]</t>
         </is>
       </c>
       <c r="D116" s="36" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E116" s="36" t="inlineStr">
         <is>
-          <t>신한자산운용</t>
+          <t>삼성자산운용</t>
         </is>
       </c>
       <c r="F116" s="37" t="inlineStr">
         <is>
-          <t>161억원</t>
+          <t>3,379억원</t>
         </is>
       </c>
       <c r="G116" s="38" t="inlineStr">
@@ -10967,22 +10959,22 @@
         </is>
       </c>
       <c r="I116" s="39" t="n">
-        <v>0.223</v>
+        <v>0.0204</v>
       </c>
       <c r="J116" s="39" t="n">
-        <v>0.1433</v>
+        <v>0.0328</v>
       </c>
       <c r="K116" s="40" t="n">
-        <v>-0.1049</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="L116" s="37" t="inlineStr">
         <is>
-          <t>0.54~1.34%</t>
+          <t>0.08~0.38%</t>
         </is>
       </c>
       <c r="M116" s="41" t="inlineStr">
         <is>
-          <t>3해 연22.3% · 변동성 14.3% (위험대비 1.36) (달 간격) · 최대낙폭 -10% · 보수 0.54% · 가장 나쁜 창 연22.3%</t>
+          <t>3해 연2.0% · 변동성 3.3% (위험대비 -0.23) (달 간격) · 최대낙폭 -5% · 보수 0.08% · 가장 나쁜 창 연0.6%</t>
         </is>
       </c>
       <c r="N116" s="35">
@@ -10993,7 +10985,7 @@
     <row r="117">
       <c r="A117" s="13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B117" s="14" t="inlineStr">
@@ -11003,22 +10995,22 @@
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>대신KOSPI200인덱스증권자투자신탁[주식](운용)</t>
+          <t>우리반도체BIG2플러스증권투자신탁(채권혼합)</t>
         </is>
       </c>
       <c r="D117" s="14" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>대신자산운용</t>
+          <t>우리자산운용</t>
         </is>
       </c>
       <c r="F117" s="30" t="inlineStr">
         <is>
-          <t>580억원</t>
+          <t>4,145억원</t>
         </is>
       </c>
       <c r="G117" s="32" t="inlineStr">
@@ -11032,22 +11024,22 @@
         </is>
       </c>
       <c r="I117" s="31" t="n">
-        <v>0.4877</v>
+        <v>0.2141</v>
       </c>
       <c r="J117" s="31" t="n">
-        <v>0.4041</v>
+        <v>0.1545</v>
       </c>
       <c r="K117" s="33" t="n">
-        <v>-0.237</v>
+        <v>-0.09300000000000001</v>
       </c>
       <c r="L117" s="30" t="inlineStr">
         <is>
-          <t>0.20~0.80%</t>
+          <t>0.34~0.89%</t>
         </is>
       </c>
       <c r="M117" s="34" t="inlineStr">
         <is>
-          <t>3해 연48.8% · 변동성 40.4% (위험대비 1.14) (달 간격) · 최대낙폭 -24% · 보수 0.20% · 가장 나쁜 창 연48.8%</t>
+          <t>3해 연21.4% · 변동성 15.4% (위험대비 1.20) (달 간격) · 최대낙폭 -9% · 보수 0.34% · 가장 나쁜 창 연21.4%</t>
         </is>
       </c>
       <c r="N117" s="35">
@@ -11068,7 +11060,7 @@
       </c>
       <c r="C118" s="36" t="inlineStr">
         <is>
-          <t>BNKK200인덱스증권투자신탁(주식-파생형)</t>
+          <t>마이다스K200인덱스알파증권자투자신탁(주식-파생형)(운용)</t>
         </is>
       </c>
       <c r="D118" s="36" t="inlineStr">
@@ -11078,12 +11070,12 @@
       </c>
       <c r="E118" s="36" t="inlineStr">
         <is>
-          <t>비엔케이자산운용</t>
+          <t>마이다스에셋자산운용</t>
         </is>
       </c>
       <c r="F118" s="37" t="inlineStr">
         <is>
-          <t>515억원</t>
+          <t>494억원</t>
         </is>
       </c>
       <c r="G118" s="38" t="inlineStr">
@@ -11097,22 +11089,22 @@
         </is>
       </c>
       <c r="I118" s="39" t="n">
-        <v>0.4905</v>
+        <v>0.509</v>
       </c>
       <c r="J118" s="39" t="n">
-        <v>0.408</v>
+        <v>0.3986</v>
       </c>
       <c r="K118" s="40" t="n">
-        <v>-0.2376</v>
+        <v>-0.2336</v>
       </c>
       <c r="L118" s="37" t="inlineStr">
         <is>
-          <t>0.17~0.95%</t>
+          <t>0.06~0.15%</t>
         </is>
       </c>
       <c r="M118" s="41" t="inlineStr">
         <is>
-          <t>3해 연49.0% · 변동성 40.8% (위험대비 1.13) (달 간격) · 최대낙폭 -24% · 보수 0.17% · 가장 나쁜 창 연49.0%</t>
+          <t>3해 연50.9% · 변동성 39.9% (위험대비 1.21) (달 간격) · 최대낙폭 -23% · 보수 0.06% · 가장 나쁜 창 연50.9%</t>
         </is>
       </c>
       <c r="N118" s="35">
@@ -11133,22 +11125,22 @@
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>미래에셋퇴직플랜KRX100인덱스증권자투자신탁 1(주식혼합)</t>
+          <t>KB스타ESG우량중단기채증권자투자신탁(채권)(운용)</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
         <is>
-          <t>미래에셋자산운용</t>
+          <t>케이비자산운용</t>
         </is>
       </c>
       <c r="F119" s="30" t="inlineStr">
         <is>
-          <t>186억원</t>
+          <t>596억원</t>
         </is>
       </c>
       <c r="G119" s="32" t="inlineStr">
@@ -11162,22 +11154,22 @@
         </is>
       </c>
       <c r="I119" s="31" t="n">
-        <v>0.2895</v>
+        <v>0.0172</v>
       </c>
       <c r="J119" s="31" t="n">
-        <v>0.2318</v>
+        <v>0.0262</v>
       </c>
       <c r="K119" s="33" t="n">
-        <v>-0.1349</v>
+        <v>-0.04019999999999999</v>
       </c>
       <c r="L119" s="30" t="inlineStr">
         <is>
-          <t>0.44~0.65%</t>
+          <t>0.10~0.29%</t>
         </is>
       </c>
       <c r="M119" s="34" t="inlineStr">
         <is>
-          <t>3해 연28.9% · 변동성 23.2% (위험대비 1.13) (달 간격) · 최대낙폭 -13% · 보수 0.44% · 가장 나쁜 창 연28.9%</t>
+          <t>3해 연1.7% · 변동성 2.6% (위험대비 -0.42) (달 간격) · 최대낙폭 -4% · 보수 0.10% · 가장 나쁜 창 연-0.3%</t>
         </is>
       </c>
       <c r="N119" s="35">
@@ -11198,22 +11190,22 @@
       </c>
       <c r="C120" s="36" t="inlineStr">
         <is>
-          <t>신영마라톤지주회사증권자투자신탁(주식)운용</t>
+          <t>미래에셋스마트롱숏30증권자투자신탁 1(채권혼합)</t>
         </is>
       </c>
       <c r="D120" s="36" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내대체</t>
         </is>
       </c>
       <c r="E120" s="36" t="inlineStr">
         <is>
-          <t>신영자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F120" s="37" t="inlineStr">
         <is>
-          <t>316억원</t>
+          <t>147억원</t>
         </is>
       </c>
       <c r="G120" s="38" t="inlineStr">
@@ -11227,22 +11219,22 @@
         </is>
       </c>
       <c r="I120" s="39" t="n">
-        <v>0.4483</v>
+        <v>0.04190000000000001</v>
       </c>
       <c r="J120" s="39" t="n">
-        <v>0.3544</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="K120" s="40" t="n">
-        <v>-0.2314</v>
+        <v>-0.061</v>
       </c>
       <c r="L120" s="37" t="inlineStr">
         <is>
-          <t>0.52~1.49%</t>
+          <t>0.50~1.10%</t>
         </is>
       </c>
       <c r="M120" s="41" t="inlineStr">
         <is>
-          <t>3해 연44.8% · 변동성 35.4% (위험대비 1.19) (달 간격) · 최대낙폭 -23% · 보수 0.52% · 가장 나쁜 창 연44.8%</t>
+          <t>3해 연4.2% · 변동성 7.8% (위험대비 0.18) (달 간격) · 최대낙폭 -6% · 보수 0.50% · 가장 나쁜 창 연4.2%</t>
         </is>
       </c>
       <c r="N120" s="35">
@@ -11263,22 +11255,22 @@
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>KB퇴직연금배당40증권자투자신탁(채권혼합)</t>
+          <t>이지스리테일부동산투자신탁299</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내대체</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>이지스자산운용</t>
         </is>
       </c>
       <c r="F121" s="30" t="inlineStr">
         <is>
-          <t>1조원</t>
+          <t>211억원</t>
         </is>
       </c>
       <c r="G121" s="32" t="inlineStr">
@@ -11292,22 +11284,24 @@
         </is>
       </c>
       <c r="I121" s="31" t="n">
-        <v>0.1845</v>
-      </c>
-      <c r="J121" s="31" t="n">
-        <v>0.1429</v>
-      </c>
-      <c r="K121" s="33" t="n">
-        <v>-0.0965</v>
-      </c>
-      <c r="L121" s="30" t="inlineStr">
-        <is>
-          <t>0.46~0.80%</t>
-        </is>
+        <v>0.0398</v>
+      </c>
+      <c r="J121" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K121" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L121" s="42" t="n">
+        <v>0.0006400000000000001</v>
       </c>
       <c r="M121" s="34" t="inlineStr">
         <is>
-          <t>3해 연18.4% · 변동성 14.3% (위험대비 1.09) (달 간격) · 최대낙폭 -10% · 보수 0.46% · 가장 나쁜 창 연18.4%</t>
+          <t>3해 연4.0% (감정평가 기준가 — 시세가 아니라 위험을 못 쟀습니다) · 보수 0.06% · 가장 나쁜 창 연4.0%</t>
         </is>
       </c>
       <c r="N121" s="35">
@@ -11328,22 +11322,22 @@
       </c>
       <c r="C122" s="36" t="inlineStr">
         <is>
-          <t>KB퇴직연금배당증권자투자신탁(주식)(운용)</t>
+          <t>신한퇴직연금커버드콜인덱스증권자투자신탁[주식혼합-파생형] (종류)</t>
         </is>
       </c>
       <c r="D122" s="36" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E122" s="36" t="inlineStr">
         <is>
-          <t>케이비자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F122" s="37" t="inlineStr">
         <is>
-          <t>1,688억원</t>
+          <t>161억원</t>
         </is>
       </c>
       <c r="G122" s="38" t="inlineStr">
@@ -11357,22 +11351,22 @@
         </is>
       </c>
       <c r="I122" s="39" t="n">
-        <v>0.522</v>
+        <v>0.1302</v>
       </c>
       <c r="J122" s="39" t="n">
-        <v>0.3632</v>
+        <v>0.0872</v>
       </c>
       <c r="K122" s="40" t="n">
-        <v>-0.2298</v>
+        <v>-0.055</v>
       </c>
       <c r="L122" s="37" t="inlineStr">
         <is>
-          <t>0.71~1.20%</t>
+          <t>0.56~0.79%</t>
         </is>
       </c>
       <c r="M122" s="41" t="inlineStr">
         <is>
-          <t>3해 연52.2% · 변동성 36.3% (위험대비 1.36) (달 간격) · 최대낙폭 -23% · 보수 0.71% · 가장 나쁜 창 연52.2%</t>
+          <t>3해 연13.0% · 변동성 8.7% (위험대비 1.17) (달 간격) · 최대낙폭 -6% · 보수 0.56% · 가장 나쁜 창 연13.0%</t>
         </is>
       </c>
       <c r="N122" s="35">
@@ -11393,22 +11387,22 @@
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>BNK내일환매초단기채증권자투자신탁(채권)</t>
+          <t>신영밸류고배당증권자투자신탁(주식)운용</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
         <is>
-          <t>국내채권형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E123" s="14" t="inlineStr">
         <is>
-          <t>비엔케이자산운용</t>
+          <t>신영자산운용</t>
         </is>
       </c>
       <c r="F123" s="30" t="inlineStr">
         <is>
-          <t>182억원</t>
+          <t>8,311억원</t>
         </is>
       </c>
       <c r="G123" s="32" t="inlineStr">
@@ -11422,22 +11416,22 @@
         </is>
       </c>
       <c r="I123" s="31" t="n">
-        <v>0.0027</v>
+        <v>0.3287</v>
       </c>
       <c r="J123" s="31" t="n">
-        <v>0.0333</v>
+        <v>0.2543</v>
       </c>
       <c r="K123" s="33" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.1498</v>
       </c>
       <c r="L123" s="30" t="inlineStr">
         <is>
-          <t>0.10~0.29%</t>
+          <t>0.45~1.35%</t>
         </is>
       </c>
       <c r="M123" s="34" t="inlineStr">
         <is>
-          <t>3해 연0.3% · 변동성 3.3% (위험대비 -0.76) (달 간격) · 최대낙폭 -4% · 보수 0.10% · 가장 나쁜 창 연0.3%</t>
+          <t>3해 연32.9% · 변동성 25.4% (위험대비 1.18) (달 간격) · 최대낙폭 -15% · 보수 0.45% · 가장 나쁜 창 연32.9%</t>
         </is>
       </c>
       <c r="N123" s="35">
@@ -11458,22 +11452,22 @@
       </c>
       <c r="C124" s="36" t="inlineStr">
         <is>
-          <t>키움코리아인덱스증권자투자신탁 1[주식]</t>
+          <t>신한커버드콜인덱스증권자투자신탁[주식혼합-파생형]</t>
         </is>
       </c>
       <c r="D124" s="36" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E124" s="36" t="inlineStr">
         <is>
-          <t>키움투자자산운용</t>
+          <t>신한자산운용</t>
         </is>
       </c>
       <c r="F124" s="37" t="inlineStr">
         <is>
-          <t>131억원</t>
+          <t>161억원</t>
         </is>
       </c>
       <c r="G124" s="38" t="inlineStr">
@@ -11487,22 +11481,22 @@
         </is>
       </c>
       <c r="I124" s="39" t="n">
-        <v>0.4842</v>
+        <v>0.223</v>
       </c>
       <c r="J124" s="39" t="n">
-        <v>0.4086</v>
+        <v>0.1433</v>
       </c>
       <c r="K124" s="40" t="n">
-        <v>-0.2355</v>
+        <v>-0.1049</v>
       </c>
       <c r="L124" s="37" t="inlineStr">
         <is>
-          <t>0.21~1.22%</t>
+          <t>0.54~1.34%</t>
         </is>
       </c>
       <c r="M124" s="41" t="inlineStr">
         <is>
-          <t>3해 연48.4% · 변동성 40.9% (위험대비 1.12) (달 간격) · 최대낙폭 -24% · 보수 0.21% · 가장 나쁜 창 연48.4%</t>
+          <t>3해 연22.3% · 변동성 14.3% (위험대비 1.36) (달 간격) · 최대낙폭 -10% · 보수 0.54% · 가장 나쁜 창 연22.3%</t>
         </is>
       </c>
       <c r="N124" s="35">
@@ -11523,7 +11517,7 @@
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>DB진주찾기증권자투자신탁 1[주식]_운용</t>
+          <t>대신KOSPI200인덱스증권자투자신탁[주식](운용)</t>
         </is>
       </c>
       <c r="D125" s="14" t="inlineStr">
@@ -11533,12 +11527,12 @@
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>디비자산운용</t>
+          <t>대신자산운용</t>
         </is>
       </c>
       <c r="F125" s="30" t="inlineStr">
         <is>
-          <t>226억원</t>
+          <t>582억원</t>
         </is>
       </c>
       <c r="G125" s="32" t="inlineStr">
@@ -11552,22 +11546,22 @@
         </is>
       </c>
       <c r="I125" s="31" t="n">
-        <v>0.4693</v>
+        <v>0.4877</v>
       </c>
       <c r="J125" s="31" t="n">
-        <v>0.3312</v>
+        <v>0.4041</v>
       </c>
       <c r="K125" s="33" t="n">
-        <v>-0.1702</v>
+        <v>-0.237</v>
       </c>
       <c r="L125" s="30" t="inlineStr">
         <is>
-          <t>0.82~1.78%</t>
+          <t>0.20~0.80%</t>
         </is>
       </c>
       <c r="M125" s="34" t="inlineStr">
         <is>
-          <t>3해 연46.9% · 변동성 33.1% (위험대비 1.33) (달 간격) · 최대낙폭 -17% · 보수 0.82% · 가장 나쁜 창 연46.9%</t>
+          <t>3해 연48.8% · 변동성 40.4% (위험대비 1.14) (달 간격) · 최대낙폭 -24% · 보수 0.20% · 가장 나쁜 창 연48.8%</t>
         </is>
       </c>
       <c r="N125" s="35">
@@ -11588,22 +11582,22 @@
       </c>
       <c r="C126" s="36" t="inlineStr">
         <is>
-          <t>교보악사파워인덱스증권자투자신탁 2(주식)(운용)</t>
+          <t>한국투자퇴직연금증권자투자신탁 1(채권)</t>
         </is>
       </c>
       <c r="D126" s="36" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내채권형</t>
         </is>
       </c>
       <c r="E126" s="36" t="inlineStr">
         <is>
-          <t>교보악사자산운용</t>
+          <t>한국투자신탁운용</t>
         </is>
       </c>
       <c r="F126" s="37" t="inlineStr">
         <is>
-          <t>191억원</t>
+          <t>221억원</t>
         </is>
       </c>
       <c r="G126" s="38" t="inlineStr">
@@ -11617,22 +11611,22 @@
         </is>
       </c>
       <c r="I126" s="39" t="n">
-        <v>0.4859000000000001</v>
+        <v>0.0273</v>
       </c>
       <c r="J126" s="39" t="n">
-        <v>0.4063000000000001</v>
+        <v>0.0214</v>
       </c>
       <c r="K126" s="40" t="n">
-        <v>-0.2397</v>
+        <v>-0.0292</v>
       </c>
       <c r="L126" s="37" t="inlineStr">
         <is>
-          <t>0.28~1.17%</t>
+          <t>0.14~0.54%</t>
         </is>
       </c>
       <c r="M126" s="41" t="inlineStr">
         <is>
-          <t>3해 연48.6% · 변동성 40.6% (위험대비 1.13) (달 간격) · 최대낙폭 -24% · 보수 0.28% · 가장 나쁜 창 연48.6%</t>
+          <t>3해 연2.7% · 변동성 2.1% (위험대비 -0.04) (달 간격) · 최대낙폭 -3% · 보수 0.14% · 가장 나쁜 창 연-1.7%</t>
         </is>
       </c>
       <c r="N126" s="35">
@@ -11653,7 +11647,7 @@
       </c>
       <c r="C127" s="14" t="inlineStr">
         <is>
-          <t>iM에셋인덱스플러스증권자투자신탁 1(주식-파생형)</t>
+          <t>BNKK200인덱스증권투자신탁(주식-파생형)</t>
         </is>
       </c>
       <c r="D127" s="14" t="inlineStr">
@@ -11663,12 +11657,12 @@
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>아이엠에셋자산운용</t>
+          <t>비엔케이자산운용</t>
         </is>
       </c>
       <c r="F127" s="30" t="inlineStr">
         <is>
-          <t>136억원</t>
+          <t>516억원</t>
         </is>
       </c>
       <c r="G127" s="32" t="inlineStr">
@@ -11682,22 +11676,22 @@
         </is>
       </c>
       <c r="I127" s="31" t="n">
-        <v>0.481</v>
+        <v>0.4905</v>
       </c>
       <c r="J127" s="31" t="n">
-        <v>0.4089</v>
+        <v>0.408</v>
       </c>
       <c r="K127" s="33" t="n">
-        <v>-0.2383</v>
+        <v>-0.2376</v>
       </c>
       <c r="L127" s="30" t="inlineStr">
         <is>
-          <t>0.04~0.52%</t>
+          <t>0.17~0.95%</t>
         </is>
       </c>
       <c r="M127" s="34" t="inlineStr">
         <is>
-          <t>3해 연48.1% · 변동성 40.9% (위험대비 1.11) (달 간격) · 최대낙폭 -24% · 보수 0.04% · 가장 나쁜 창 연48.1%</t>
+          <t>3해 연49.0% · 변동성 40.8% (위험대비 1.13) (달 간격) · 최대낙폭 -24% · 보수 0.17% · 가장 나쁜 창 연49.0%</t>
         </is>
       </c>
       <c r="N127" s="35">
@@ -11718,22 +11712,22 @@
       </c>
       <c r="C128" s="36" t="inlineStr">
         <is>
-          <t>카디안코리아인덱스증권자투자신탁[주식]</t>
+          <t>미래에셋퇴직플랜KRX100인덱스증권자투자신탁 1(주식혼합)</t>
         </is>
       </c>
       <c r="D128" s="36" t="inlineStr">
         <is>
-          <t>국내주식형</t>
+          <t>국내혼합형</t>
         </is>
       </c>
       <c r="E128" s="36" t="inlineStr">
         <is>
-          <t>카디안자산운용</t>
+          <t>미래에셋자산운용</t>
         </is>
       </c>
       <c r="F128" s="37" t="inlineStr">
         <is>
-          <t>235억원</t>
+          <t>185억원</t>
         </is>
       </c>
       <c r="G128" s="38" t="inlineStr">
@@ -11747,22 +11741,22 @@
         </is>
       </c>
       <c r="I128" s="39" t="n">
-        <v>0.4739</v>
+        <v>0.2895</v>
       </c>
       <c r="J128" s="39" t="n">
-        <v>0.4068</v>
+        <v>0.2318</v>
       </c>
       <c r="K128" s="40" t="n">
-        <v>-0.2358</v>
+        <v>-0.1349</v>
       </c>
       <c r="L128" s="37" t="inlineStr">
         <is>
-          <t>0.27~0.61%</t>
+          <t>0.44~0.65%</t>
         </is>
       </c>
       <c r="M128" s="41" t="inlineStr">
         <is>
-          <t>3해 연47.4% · 변동성 40.7% (위험대비 1.10) (달 간격) · 최대낙폭 -24% · 보수 0.27% · 가장 나쁜 창 연47.4%</t>
+          <t>3해 연28.9% · 변동성 23.2% (위험대비 1.13) (달 간격) · 최대낙폭 -13% · 보수 0.44% · 가장 나쁜 창 연28.9%</t>
         </is>
       </c>
       <c r="N128" s="35">
@@ -11783,7 +11777,7 @@
       </c>
       <c r="C129" s="14" t="inlineStr">
         <is>
-          <t>교보악사파워인덱스증권자투자신탁 1(주식)(운용)</t>
+          <t>신영마라톤지주회사증권자투자신탁(주식)운용</t>
         </is>
       </c>
       <c r="D129" s="14" t="inlineStr">
@@ -11793,12 +11787,12 @@
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>교보악사자산운용</t>
+          <t>신영자산운용</t>
         </is>
       </c>
       <c r="F129" s="30" t="inlineStr">
         <is>
-          <t>2,914억원</t>
+          <t>316억원</t>
         </is>
       </c>
       <c r="G129" s="32" t="inlineStr">
@@ -11812,22 +11806,22 @@
         </is>
       </c>
       <c r="I129" s="31" t="n">
-        <v>0.4796</v>
+        <v>0.4483</v>
       </c>
       <c r="J129" s="31" t="n">
-        <v>0.4089</v>
+        <v>0.3544</v>
       </c>
       <c r="K129" s="33" t="n">
-        <v>-0.2396</v>
+        <v>-0.2314</v>
       </c>
       <c r="L129" s="30" t="inlineStr">
         <is>
-          <t>0.17~1.28%</t>
+          <t>0.52~1.49%</t>
         </is>
       </c>
       <c r="M129" s="34" t="inlineStr">
         <is>
-          <t>3해 연48.0% · 변동성 40.9% (위험대비 1.10) (달 간격) · 최대낙폭 -24% · 보수 0.17% · 가장 나쁜 창 연48.0%</t>
+          <t>3해 연44.8% · 변동성 35.4% (위험대비 1.19) (달 간격) · 최대낙폭 -23% · 보수 0.52% · 가장 나쁜 창 연44.8%</t>
         </is>
       </c>
       <c r="N129" s="35">
@@ -11848,22 +11842,22 @@
       </c>
       <c r="C130" s="36" t="inlineStr">
         <is>
-          <t>다올퇴직연금40증권자투자신탁[채권혼합](운)</t>
+          <t>키움코리아인덱스증권자투자신탁 1[주식]</t>
         </is>
       </c>
       <c r="D130" s="36" t="inlineStr">
         <is>
-          <t>국내혼합형</t>
+          <t>국내주식형</t>
         </is>
       </c>
       <c r="E130" s="36" t="inlineStr">
         <is>
-          <t>다올자산운용</t>
+          <t>키움투자자산운용</t>
         </is>
       </c>
       <c r="F130" s="37" t="inlineStr">
         <is>
-          <t>193억원</t>
+          <t>131억원</t>
         </is>
       </c>
       <c r="G130" s="38" t="inlineStr">
@@ -11877,22 +11871,22 @@
         </is>
       </c>
       <c r="I130" s="39" t="n">
-        <v>0.1779</v>
+        <v>0.4842</v>
       </c>
       <c r="J130" s="39" t="n">
-        <v>0.1425</v>
+        <v>0.4086</v>
       </c>
       <c r="K130" s="40" t="n">
-        <v>-0.0872</v>
+        <v>-0.2355</v>
       </c>
       <c r="L130" s="37" t="inlineStr">
         <is>
-          <t>0.53~0.80%</t>
+          <t>0.21~1.22%</t>
         </is>
       </c>
       <c r="M130" s="41" t="inlineStr">
         <is>
-          <t>3해 연17.8% · 변동성 14.2% (위험대비 1.05) (달 간격) · 최대낙폭 -9% · 보수 0.53% · 가장 나쁜 창 연17.8%</t>
+          <t>3해 연48.4% · 변동성 40.9% (위험대비 1.12) (달 간격) · 최대낙폭 -24% · 보수 0.21% · 가장 나쁜 창 연48.4%</t>
         </is>
       </c>
       <c r="N130" s="35">
@@ -11913,7 +11907,7 @@
       </c>
       <c r="C131" s="14" t="inlineStr">
         <is>
-          <t>트러스톤인덱스알파증권자투자신탁[주식-파생형]</t>
+          <t>교보악사파워인덱스증권자투자신탁 2(주식)(운용)</t>
         </is>
       </c>
       <c r="D131" s="14" t="inlineStr">
@@ -11923,12 +11917,12 @@
       </c>
       <c r="E131" s="14" t="inlineStr">
         <is>
-          <t>트러스톤자산운용</t>
+          <t>교보악사자산운용</t>
         </is>
       </c>
       <c r="F131" s="30" t="inlineStr">
         <is>
-          <t>326억원</t>
+          <t>191억원</t>
         </is>
       </c>
       <c r="G131" s="32" t="inlineStr">
@@ -11942,22 +11936,22 @@
         </is>
       </c>
       <c r="I131" s="31" t="n">
-        <v>0.478</v>
+        <v>0.4859000000000001</v>
       </c>
       <c r="J131" s="31" t="n">
-        <v>0.4094</v>
+        <v>0.4063000000000001</v>
       </c>
       <c r="K131" s="33" t="n">
-        <v>-0.2398</v>
+        <v>-0.2397</v>
       </c>
       <c r="L131" s="30" t="inlineStr">
         <is>
-          <t>0.10~0.89%</t>
+          <t>0.28~1.17%</t>
         </is>
       </c>
       <c r="M131" s="34" t="inlineStr">
         <is>
-          <t>3해 연47.8% · 변동성 40.9% (위험대비 1.10) (달 간격) · 최대낙폭 -24% · 보수 0.10% · 가장 나쁜 창 연47.8%</t>
+          <t>3해 연48.6% · 변동성 40.6% (위험대비 1.13) (달 간격) · 최대낙폭 -24% · 보수 0.28% · 가장 나쁜 창 연48.6%</t>
         </is>
       </c>
       <c r="N131" s="35">
@@ -11993,7 +11987,7 @@
       </c>
       <c r="F132" s="37" t="inlineStr">
         <is>
-          <t>237억원</t>
+          <t>234억원</t>
         </is>
       </c>
       <c r="G132" s="38" t="inlineStr">
@@ -12058,7 +12052,7 @@
       </c>
       <c r="F133" s="30" t="inlineStr">
         <is>
-          <t>133억원</t>
+          <t>132억원</t>
         </is>
       </c>
       <c r="G133" s="32" t="inlineStr">
@@ -12188,7 +12182,7 @@
       </c>
       <c r="F135" s="30" t="inlineStr">
         <is>
-          <t>5,716억원</t>
+          <t>5,707억원</t>
         </is>
       </c>
       <c r="G135" s="32" t="inlineStr">
@@ -12253,7 +12247,7 @@
       </c>
       <c r="F136" s="37" t="inlineStr">
         <is>
-          <t>1,626억원</t>
+          <t>1,628억원</t>
         </is>
       </c>
       <c r="G136" s="38" t="inlineStr">
@@ -12318,7 +12312,7 @@
       </c>
       <c r="F137" s="30" t="inlineStr">
         <is>
-          <t>655억원</t>
+          <t>647억원</t>
         </is>
       </c>
       <c r="G137" s="32" t="inlineStr">
@@ -12368,22 +12362,22 @@
       </c>
       <c r="C138" s="36" t="inlineStr">
         <is>
-          <t>NH-AmundiSignatureOCIO성장형증권자투자신탁(UH)[혼합-재간접형]</t>
+          <t>AB셀렉트미국증권투자신탁(주식-재간접형)</t>
         </is>
       </c>
       <c r="D138" s="36" t="inlineStr">
         <is>
-          <t>해외혼합형</t>
+          <t>해외주식형</t>
         </is>
       </c>
       <c r="E138" s="36" t="inlineStr">
         <is>
-          <t>엔에이치아문디자산운용</t>
+          <t>얼라이언스번스틴자산운용</t>
         </is>
       </c>
       <c r="F138" s="37" t="inlineStr">
         <is>
-          <t>155억원</t>
+          <t>304억원</t>
         </is>
       </c>
       <c r="G138" s="38" t="inlineStr">
@@ -12397,22 +12391,22 @@
         </is>
       </c>
       <c r="I138" s="39" t="n">
-        <v>0.1817</v>
+        <v>0.1761</v>
       </c>
       <c r="J138" s="39" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1169</v>
       </c>
       <c r="K138" s="40" t="n">
-        <v>-0.0814</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="L138" s="37" t="inlineStr">
         <is>
-          <t>0.79~1.39%</t>
+          <t>0.27~1.56%</t>
         </is>
       </c>
       <c r="M138" s="41" t="inlineStr">
         <is>
-          <t>3해 연18.2% · 변동성 9.9% (위험대비 1.56) (달 간격) · 최대낙폭 -8% · 보수 0.79% · 가장 나쁜 창 연16.7%</t>
+          <t>3해 연17.6% · 변동성 11.7% (위험대비 1.27) (달 간격) · 최대낙폭 -8% · 보수 0.27% · 가장 나쁜 창 연14.5%</t>
         </is>
       </c>
       <c r="N138" s="35">
@@ -12433,22 +12427,22 @@
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>AB셀렉트미국증권투자신탁(주식-재간접형)</t>
+          <t>NH-AmundiSignatureOCIO성장형증권자투자신탁(UH)[혼합-재간접형]</t>
         </is>
       </c>
       <c r="D139" s="14" t="inlineStr">
         <is>
-          <t>해외주식형</t>
+          <t>해외혼합형</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>얼라이언스번스틴자산운용</t>
+          <t>엔에이치아문디자산운용</t>
         </is>
       </c>
       <c r="F139" s="30" t="inlineStr">
         <is>
-          <t>305억원</t>
+          <t>160억원</t>
         </is>
       </c>
       <c r="G139" s="32" t="inlineStr">
@@ -12462,22 +12456,22 @@
         </is>
       </c>
       <c r="I139" s="31" t="n">
-        <v>0.1761</v>
+        <v>0.1817</v>
       </c>
       <c r="J139" s="31" t="n">
-        <v>0.1169</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="K139" s="33" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0814</v>
       </c>
       <c r="L139" s="30" t="inlineStr">
         <is>
-          <t>0.27~1.56%</t>
+          <t>0.79~1.39%</t>
         </is>
       </c>
       <c r="M139" s="34" t="inlineStr">
         <is>
-          <t>3해 연17.6% · 변동성 11.7% (위험대비 1.27) (달 간격) · 최대낙폭 -8% · 보수 0.27% · 가장 나쁜 창 연14.5%</t>
+          <t>3해 연18.2% · 변동성 9.9% (위험대비 1.56) (달 간격) · 최대낙폭 -8% · 보수 0.79% · 가장 나쁜 창 연16.7%</t>
         </is>
       </c>
       <c r="N139" s="35">
@@ -12513,7 +12507,7 @@
       </c>
       <c r="F140" s="37" t="inlineStr">
         <is>
-          <t>1,629억원</t>
+          <t>1,614억원</t>
         </is>
       </c>
       <c r="G140" s="38" t="inlineStr">
@@ -12578,7 +12572,7 @@
       </c>
       <c r="F141" s="30" t="inlineStr">
         <is>
-          <t>234억원</t>
+          <t>277억원</t>
         </is>
       </c>
       <c r="G141" s="32" t="inlineStr">
@@ -12643,7 +12637,7 @@
       </c>
       <c r="F142" s="37" t="inlineStr">
         <is>
-          <t>139억원</t>
+          <t>138억원</t>
         </is>
       </c>
       <c r="G142" s="38" t="inlineStr">
@@ -12773,7 +12767,7 @@
       </c>
       <c r="F144" s="37" t="inlineStr">
         <is>
-          <t>502억원</t>
+          <t>506억원</t>
         </is>
       </c>
       <c r="G144" s="38" t="inlineStr">
@@ -12838,7 +12832,7 @@
       </c>
       <c r="F145" s="30" t="inlineStr">
         <is>
-          <t>496억원</t>
+          <t>491억원</t>
         </is>
       </c>
       <c r="G145" s="32" t="inlineStr">
@@ -12903,7 +12897,7 @@
       </c>
       <c r="F146" s="37" t="inlineStr">
         <is>
-          <t>356억원</t>
+          <t>359억원</t>
         </is>
       </c>
       <c r="G146" s="38" t="inlineStr">
@@ -12968,7 +12962,7 @@
       </c>
       <c r="F147" s="30" t="inlineStr">
         <is>
-          <t>1,120억원</t>
+          <t>1,116억원</t>
         </is>
       </c>
       <c r="G147" s="32" t="inlineStr">
@@ -13033,7 +13027,7 @@
       </c>
       <c r="F148" s="37" t="inlineStr">
         <is>
-          <t>292억원</t>
+          <t>288억원</t>
         </is>
       </c>
       <c r="G148" s="38" t="inlineStr">
@@ -13163,7 +13157,7 @@
       </c>
       <c r="F150" s="37" t="inlineStr">
         <is>
-          <t>906억원</t>
+          <t>904억원</t>
         </is>
       </c>
       <c r="G150" s="38" t="inlineStr">
@@ -13358,7 +13352,7 @@
       </c>
       <c r="F153" s="30" t="inlineStr">
         <is>
-          <t>700억원</t>
+          <t>696억원</t>
         </is>
       </c>
       <c r="G153" s="32" t="inlineStr">
@@ -13488,7 +13482,7 @@
       </c>
       <c r="F155" s="30" t="inlineStr">
         <is>
-          <t>217억원</t>
+          <t>216억원</t>
         </is>
       </c>
       <c r="G155" s="32" t="inlineStr">
@@ -13553,7 +13547,7 @@
       </c>
       <c r="F156" s="37" t="inlineStr">
         <is>
-          <t>176억원</t>
+          <t>178억원</t>
         </is>
       </c>
       <c r="G156" s="38" t="inlineStr">
@@ -13676,11 +13670,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E5" s="44" t="inlineStr">
@@ -13730,7 +13724,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E7" s="44" t="inlineStr"/>
@@ -13751,7 +13745,7 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E8" s="44" t="inlineStr"/>
@@ -14186,11 +14180,11 @@
         </is>
       </c>
       <c r="B30" s="42" t="n">
-        <v>0.0535</v>
+        <v>0.0451</v>
       </c>
       <c r="C30" s="48" t="inlineStr">
         <is>
-          <t>대체 40% · 국내채권 30% · 국내주식 30%</t>
+          <t>국내채권 50% · 대체 40% · 국내주식 10%</t>
         </is>
       </c>
       <c r="D30" s="49" t="n"/>
